--- a/ImportExportExcellApi/Templates/HU_WORKING_BASE_Release.xlsx
+++ b/ImportExportExcellApi/Templates/HU_WORKING_BASE_Release.xlsx
@@ -18557,5989 +18557,5989 @@
     <mergeCell ref="A1:R2"/>
   </mergeCells>
   <dataValidations count="1995">
-    <dataValidation type="list" sqref="B6:B1000" xr:uid="{8F9B50B3-E5CD-4DF3-BB25-F568DA6E792E}">
+    <dataValidation type="list" sqref="B6:B1000" xr:uid="{2D5CAEEC-01BF-4136-A01A-F4D9036D1D0A}">
       <formula1>=DanhSachCode</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D6:D1000" xr:uid="{80CFDDCB-BC3F-45F1-876F-14A950AB7591}">
+    <dataValidation type="list" sqref="D6:D1000" xr:uid="{F5C02CF1-2421-4ACF-B49E-65A7D2D13BA8}">
       <formula1>=DanhSachLoaiQuyetDinh</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I6:I1000" xr:uid="{CE67C409-5CB6-4120-B243-A017F01BBA3F}">
+    <dataValidation type="list" sqref="I6:I1000" xr:uid="{6A6A8D1A-72B7-4405-B8FE-011D8685BE9B}">
       <formula1>=DanhSachPhongBan</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J6:J1000" xr:uid="{37A99357-0A14-45A5-932D-FA3D592E93CB}">
+    <dataValidation type="list" sqref="J6:J1000" xr:uid="{C3FB4B18-1428-4958-A3D5-085D38403153}">
       <formula1>=DanhSachChucDanh</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L6:L1000" xr:uid="{3B3E8AB5-9DED-4267-B5A5-DA5E0CFB605D}">
+    <dataValidation type="list" sqref="L6:L1000" xr:uid="{D64A1838-7FF1-4803-96BE-C3B615E8330E}">
       <formula1>=ThangLuongList</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M6" xr:uid="{42342076-BF76-42F6-9CAD-E93F42BE5821}">
+    <dataValidation type="list" sqref="M6" xr:uid="{2DC2F715-08F7-4A43-932F-425EFCB95873}">
       <formula1>=IF(L6&lt;&gt;"",INDIRECT(VLOOKUP(L6,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N6" xr:uid="{B1567323-05A0-4EF2-B40D-5DA3DAA480DA}">
+    <dataValidation type="list" sqref="N6" xr:uid="{1DDE2273-F63B-4B21-A4C4-BFC20C0BF92D}">
       <formula1>=IF(M6&lt;&gt;"",INDIRECT(VLOOKUP(M6,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M7" xr:uid="{896E52D0-C93C-4E1D-B987-D477EEE09AF7}">
+    <dataValidation type="list" sqref="M7" xr:uid="{C24C273E-86CA-4D4B-A8D3-4BC35CD114C9}">
       <formula1>=IF(L7&lt;&gt;"",INDIRECT(VLOOKUP(L7,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N7" xr:uid="{00542742-6A4A-47B8-BADC-DA98B35F72EB}">
+    <dataValidation type="list" sqref="N7" xr:uid="{C2525AC0-9074-40B2-8470-1CF9F2A5CE2C}">
       <formula1>=IF(M7&lt;&gt;"",INDIRECT(VLOOKUP(M7,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M8" xr:uid="{2FB3F83A-252D-4E3D-B1AA-8FC39EADD294}">
+    <dataValidation type="list" sqref="M8" xr:uid="{B98C3005-CE52-4BA1-B8E3-45FCD47CEBAA}">
       <formula1>=IF(L8&lt;&gt;"",INDIRECT(VLOOKUP(L8,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N8" xr:uid="{656AAEF4-D868-4475-AE3E-82FB0E3700FD}">
+    <dataValidation type="list" sqref="N8" xr:uid="{94D57E4A-9E83-4A48-BF83-CB1688751E04}">
       <formula1>=IF(M8&lt;&gt;"",INDIRECT(VLOOKUP(M8,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M9" xr:uid="{9880963E-C4C0-47E9-BB53-BDD7590D5B9A}">
+    <dataValidation type="list" sqref="M9" xr:uid="{6891827A-5435-4C99-92ED-63AD3D78179F}">
       <formula1>=IF(L9&lt;&gt;"",INDIRECT(VLOOKUP(L9,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N9" xr:uid="{15A32766-FC77-43D2-8932-F66A025D527E}">
+    <dataValidation type="list" sqref="N9" xr:uid="{5F679CE7-4E1D-4D92-9B4C-65535638370B}">
       <formula1>=IF(M9&lt;&gt;"",INDIRECT(VLOOKUP(M9,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M10" xr:uid="{90979CD3-C9B1-476B-A268-96F414CD359F}">
+    <dataValidation type="list" sqref="M10" xr:uid="{5F169095-2832-4EDD-9ABB-5D5B374CCE34}">
       <formula1>=IF(L10&lt;&gt;"",INDIRECT(VLOOKUP(L10,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N10" xr:uid="{2280CF75-86AD-4DD5-9B7D-5FE4B29598DE}">
+    <dataValidation type="list" sqref="N10" xr:uid="{EF9A5623-3A3E-4D6D-AB50-1DD9F295B649}">
       <formula1>=IF(M10&lt;&gt;"",INDIRECT(VLOOKUP(M10,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M11" xr:uid="{0AC72E74-0907-417B-833C-E91656BEDCA4}">
+    <dataValidation type="list" sqref="M11" xr:uid="{9781B897-2E29-4DDB-9196-281502A06FDA}">
       <formula1>=IF(L11&lt;&gt;"",INDIRECT(VLOOKUP(L11,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N11" xr:uid="{E8CAF6E7-16A1-4534-9CCC-038BC438A94C}">
+    <dataValidation type="list" sqref="N11" xr:uid="{35F82365-104D-4C9E-804F-77342C693AFE}">
       <formula1>=IF(M11&lt;&gt;"",INDIRECT(VLOOKUP(M11,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M12" xr:uid="{308A299B-56C4-476D-9E2A-747C5586F479}">
+    <dataValidation type="list" sqref="M12" xr:uid="{494EE163-94C8-448A-AD3D-D4975ACEADE7}">
       <formula1>=IF(L12&lt;&gt;"",INDIRECT(VLOOKUP(L12,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N12" xr:uid="{8843BCE3-04A7-4726-8B7E-DDDC369B378F}">
+    <dataValidation type="list" sqref="N12" xr:uid="{E49352CF-5F87-425F-9860-B503ECA301AF}">
       <formula1>=IF(M12&lt;&gt;"",INDIRECT(VLOOKUP(M12,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M13" xr:uid="{01421121-4853-41F0-A779-82B02B25AD4C}">
+    <dataValidation type="list" sqref="M13" xr:uid="{80593E87-1E34-4303-AFD5-09589EB233E8}">
       <formula1>=IF(L13&lt;&gt;"",INDIRECT(VLOOKUP(L13,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N13" xr:uid="{E72A49F3-B2D8-4813-BB23-4525D3B05BFA}">
+    <dataValidation type="list" sqref="N13" xr:uid="{DBA60F6F-78F3-4A8F-BF92-2CCB9FEE9C93}">
       <formula1>=IF(M13&lt;&gt;"",INDIRECT(VLOOKUP(M13,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M14" xr:uid="{64C92238-58B3-46AE-804F-D176C798800E}">
+    <dataValidation type="list" sqref="M14" xr:uid="{78047F97-F8C1-47B9-BB7D-97E6CE8D438A}">
       <formula1>=IF(L14&lt;&gt;"",INDIRECT(VLOOKUP(L14,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N14" xr:uid="{F1BF9A53-4DDA-4A5B-8690-6FD6C863BB03}">
+    <dataValidation type="list" sqref="N14" xr:uid="{32D818CB-EF34-4BA6-9C57-4B886EB1BC2F}">
       <formula1>=IF(M14&lt;&gt;"",INDIRECT(VLOOKUP(M14,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M15" xr:uid="{D60432DF-0180-4E3E-9978-AE86093360E3}">
+    <dataValidation type="list" sqref="M15" xr:uid="{451FA101-0355-4B63-88CF-8C9EBA100EE7}">
       <formula1>=IF(L15&lt;&gt;"",INDIRECT(VLOOKUP(L15,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N15" xr:uid="{51A27BFC-861D-497F-828B-9B000DB1A55B}">
+    <dataValidation type="list" sqref="N15" xr:uid="{ED95351C-5711-4C80-8DB9-415E65AB4EA2}">
       <formula1>=IF(M15&lt;&gt;"",INDIRECT(VLOOKUP(M15,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M16" xr:uid="{4A2C428E-56CA-4C2B-ACB6-DF5CAE91483E}">
+    <dataValidation type="list" sqref="M16" xr:uid="{67298AE9-87AC-4600-8700-281D1CF00F92}">
       <formula1>=IF(L16&lt;&gt;"",INDIRECT(VLOOKUP(L16,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N16" xr:uid="{B5516A22-81C3-46CC-ABC4-DB535CD7204D}">
+    <dataValidation type="list" sqref="N16" xr:uid="{E12832E4-0912-4E28-BE2F-2E9C0C194D14}">
       <formula1>=IF(M16&lt;&gt;"",INDIRECT(VLOOKUP(M16,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M17" xr:uid="{DFD97112-5919-4C7B-989E-D72306AEFEB8}">
+    <dataValidation type="list" sqref="M17" xr:uid="{13730305-24A8-4FA1-9116-67F2369CBE6C}">
       <formula1>=IF(L17&lt;&gt;"",INDIRECT(VLOOKUP(L17,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N17" xr:uid="{32F69D0D-06CA-4819-B7F8-19FC6488D6F0}">
+    <dataValidation type="list" sqref="N17" xr:uid="{ED282BF1-10FB-49A6-803A-093DD1FB7028}">
       <formula1>=IF(M17&lt;&gt;"",INDIRECT(VLOOKUP(M17,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M18" xr:uid="{3A7AFD98-C328-40AA-A5CA-02B0D094FA9D}">
+    <dataValidation type="list" sqref="M18" xr:uid="{EEC5F48F-6C1E-4F62-9CA0-A92D6A55C95C}">
       <formula1>=IF(L18&lt;&gt;"",INDIRECT(VLOOKUP(L18,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N18" xr:uid="{02833C4D-EBCB-46AF-AFBC-D6E7E941B8AB}">
+    <dataValidation type="list" sqref="N18" xr:uid="{550C0A90-6549-4D3F-B0C6-A5EC498F2102}">
       <formula1>=IF(M18&lt;&gt;"",INDIRECT(VLOOKUP(M18,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M19" xr:uid="{22F952F2-A74F-48CB-A058-2DE14A26407F}">
+    <dataValidation type="list" sqref="M19" xr:uid="{C63E6E96-CD8A-4C16-B3E0-96D789FC072C}">
       <formula1>=IF(L19&lt;&gt;"",INDIRECT(VLOOKUP(L19,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N19" xr:uid="{D260AAB1-A834-4952-A904-61A4170BFA2B}">
+    <dataValidation type="list" sqref="N19" xr:uid="{0909B204-EE23-4DD4-8524-81D11D3AA150}">
       <formula1>=IF(M19&lt;&gt;"",INDIRECT(VLOOKUP(M19,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M20" xr:uid="{605AB93B-B8F3-42FC-9911-458FDD1188B6}">
+    <dataValidation type="list" sqref="M20" xr:uid="{0F1E3A52-89D4-4D3C-B4BF-25E9BF3F329A}">
       <formula1>=IF(L20&lt;&gt;"",INDIRECT(VLOOKUP(L20,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N20" xr:uid="{DB290255-2505-4F58-B7AF-E44A9FEDB25C}">
+    <dataValidation type="list" sqref="N20" xr:uid="{21DB422D-2F81-4A0D-A8C8-71B7386AF20C}">
       <formula1>=IF(M20&lt;&gt;"",INDIRECT(VLOOKUP(M20,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M21" xr:uid="{E4C1A51D-693B-4A42-BBF6-3ABE188C7A59}">
+    <dataValidation type="list" sqref="M21" xr:uid="{AC32B660-BF2E-452E-998F-2FB97F66D930}">
       <formula1>=IF(L21&lt;&gt;"",INDIRECT(VLOOKUP(L21,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N21" xr:uid="{8469105D-2864-4DA1-9A38-28D051F208E7}">
+    <dataValidation type="list" sqref="N21" xr:uid="{48AA9D6B-810C-49ED-BBB9-8A4F42FADBAF}">
       <formula1>=IF(M21&lt;&gt;"",INDIRECT(VLOOKUP(M21,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M22" xr:uid="{D0ABC637-C03D-4B82-90D7-77FE7BB48F24}">
+    <dataValidation type="list" sqref="M22" xr:uid="{AEFB24C6-EC61-4441-A691-7BF20FA53C3B}">
       <formula1>=IF(L22&lt;&gt;"",INDIRECT(VLOOKUP(L22,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N22" xr:uid="{25B2EAE9-0B47-46B0-8FD8-95F9F34CDA2E}">
+    <dataValidation type="list" sqref="N22" xr:uid="{3671DE29-9BD6-458F-A0BE-A613C5D6F70B}">
       <formula1>=IF(M22&lt;&gt;"",INDIRECT(VLOOKUP(M22,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M23" xr:uid="{0861AB4E-14F9-46D2-BCC9-FF688024B25E}">
+    <dataValidation type="list" sqref="M23" xr:uid="{9FFB1D1B-BBCD-4C69-BB50-7524CA47ABAF}">
       <formula1>=IF(L23&lt;&gt;"",INDIRECT(VLOOKUP(L23,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N23" xr:uid="{B5FCE5E4-FDAC-42DE-8AC6-7DBD99D0EAF0}">
+    <dataValidation type="list" sqref="N23" xr:uid="{E8F30E3D-F8C4-41A3-AB81-74C977F8482A}">
       <formula1>=IF(M23&lt;&gt;"",INDIRECT(VLOOKUP(M23,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M24" xr:uid="{3707A210-72B7-4AC6-8200-2F78C86FD44E}">
+    <dataValidation type="list" sqref="M24" xr:uid="{C9A38ADD-F9E0-431B-90A3-25B8F40A30DC}">
       <formula1>=IF(L24&lt;&gt;"",INDIRECT(VLOOKUP(L24,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N24" xr:uid="{F366D420-6032-440D-849D-7493A781216D}">
+    <dataValidation type="list" sqref="N24" xr:uid="{F5456E9C-3DA7-4CE1-BA25-A6D42B966674}">
       <formula1>=IF(M24&lt;&gt;"",INDIRECT(VLOOKUP(M24,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M25" xr:uid="{89C3E546-CFDB-4985-8921-5078A7B17085}">
+    <dataValidation type="list" sqref="M25" xr:uid="{DAE5C61E-99D6-410A-9463-A79ABDDBE7BD}">
       <formula1>=IF(L25&lt;&gt;"",INDIRECT(VLOOKUP(L25,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N25" xr:uid="{00FFBCB8-C7E6-404E-AB04-10901B649986}">
+    <dataValidation type="list" sqref="N25" xr:uid="{6A5DF903-D174-428F-BEE2-2EE099283D38}">
       <formula1>=IF(M25&lt;&gt;"",INDIRECT(VLOOKUP(M25,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M26" xr:uid="{1724FA90-6592-4899-8566-E5C2D07C20A6}">
+    <dataValidation type="list" sqref="M26" xr:uid="{B498D076-E086-47C6-8044-455892D6D7AE}">
       <formula1>=IF(L26&lt;&gt;"",INDIRECT(VLOOKUP(L26,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N26" xr:uid="{7BC28C09-EF9E-49E4-A33B-E06888336C94}">
+    <dataValidation type="list" sqref="N26" xr:uid="{E4953184-3A44-4D29-893C-E1EE58F4748B}">
       <formula1>=IF(M26&lt;&gt;"",INDIRECT(VLOOKUP(M26,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M27" xr:uid="{1B496AAA-BF31-4EFA-85CA-8ABC0382CA23}">
+    <dataValidation type="list" sqref="M27" xr:uid="{DEE66A27-5EFD-49A0-9E60-DADC5C698DB1}">
       <formula1>=IF(L27&lt;&gt;"",INDIRECT(VLOOKUP(L27,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N27" xr:uid="{6FBE5F2E-C0E2-4F69-9FE7-A03976FAED03}">
+    <dataValidation type="list" sqref="N27" xr:uid="{46D0A88E-35A4-4879-A2D1-7B6A609E214F}">
       <formula1>=IF(M27&lt;&gt;"",INDIRECT(VLOOKUP(M27,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M28" xr:uid="{571F6F68-A3BB-4BCB-B476-07651C4F3423}">
+    <dataValidation type="list" sqref="M28" xr:uid="{0E51CC0A-9180-4CD5-A031-38A0470BFDFD}">
       <formula1>=IF(L28&lt;&gt;"",INDIRECT(VLOOKUP(L28,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N28" xr:uid="{312330E2-5E8F-463E-8BB0-DBFF4F61501A}">
+    <dataValidation type="list" sqref="N28" xr:uid="{E42DC0BF-8BC3-49D3-B950-42FF381161EA}">
       <formula1>=IF(M28&lt;&gt;"",INDIRECT(VLOOKUP(M28,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M29" xr:uid="{DA405857-FD8A-47D4-910D-DA81157B9333}">
+    <dataValidation type="list" sqref="M29" xr:uid="{4BB53A58-DA5D-4C8F-A895-A664057EAC1E}">
       <formula1>=IF(L29&lt;&gt;"",INDIRECT(VLOOKUP(L29,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N29" xr:uid="{D5C8CA6F-6EB8-4B31-AA99-85530C9AA6E2}">
+    <dataValidation type="list" sqref="N29" xr:uid="{2BF41A8F-3476-473A-81AC-61F11B0EF0AE}">
       <formula1>=IF(M29&lt;&gt;"",INDIRECT(VLOOKUP(M29,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M30" xr:uid="{76A74252-C99A-4765-95AE-E4E306CB0B83}">
+    <dataValidation type="list" sqref="M30" xr:uid="{B81C1288-2167-4C8A-A17E-B6E27AD8D0B3}">
       <formula1>=IF(L30&lt;&gt;"",INDIRECT(VLOOKUP(L30,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N30" xr:uid="{8F0A8123-3F62-4AF5-91F5-1CF15B74DB2E}">
+    <dataValidation type="list" sqref="N30" xr:uid="{A2CC739F-332C-4495-9FE0-85B7659875CC}">
       <formula1>=IF(M30&lt;&gt;"",INDIRECT(VLOOKUP(M30,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M31" xr:uid="{4373E355-3E21-41B1-848D-0CD34372D838}">
+    <dataValidation type="list" sqref="M31" xr:uid="{502B690D-35CD-41C0-8DDF-879A0A154738}">
       <formula1>=IF(L31&lt;&gt;"",INDIRECT(VLOOKUP(L31,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N31" xr:uid="{D939AE88-344C-4B8A-9A22-EE10F5020080}">
+    <dataValidation type="list" sqref="N31" xr:uid="{69D6C57C-630B-4EE6-986A-071C1D82FC32}">
       <formula1>=IF(M31&lt;&gt;"",INDIRECT(VLOOKUP(M31,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M32" xr:uid="{6EC5B07F-4AF8-4299-893D-B584AAE5EEE2}">
+    <dataValidation type="list" sqref="M32" xr:uid="{C2602373-ADD8-453C-909C-8C8E70556430}">
       <formula1>=IF(L32&lt;&gt;"",INDIRECT(VLOOKUP(L32,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N32" xr:uid="{E5E67617-7A10-4D93-BF77-D336C9B39092}">
+    <dataValidation type="list" sqref="N32" xr:uid="{C1E63CFB-2643-4429-AD31-E0E2E9377065}">
       <formula1>=IF(M32&lt;&gt;"",INDIRECT(VLOOKUP(M32,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M33" xr:uid="{6BEA6B18-B251-4A76-8AEC-23247D006AE9}">
+    <dataValidation type="list" sqref="M33" xr:uid="{7C5E4935-2171-4268-B36B-A6094FCEB078}">
       <formula1>=IF(L33&lt;&gt;"",INDIRECT(VLOOKUP(L33,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N33" xr:uid="{1BA6BF72-BD8E-46BD-A218-BF8E3D264DE2}">
+    <dataValidation type="list" sqref="N33" xr:uid="{A4A57596-5303-486A-80FF-1F89DF4394B6}">
       <formula1>=IF(M33&lt;&gt;"",INDIRECT(VLOOKUP(M33,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M34" xr:uid="{7CC68DDE-D045-4194-8E44-A76E61438A01}">
+    <dataValidation type="list" sqref="M34" xr:uid="{59E3B99F-1384-4AB8-8996-4604E2CAF7B1}">
       <formula1>=IF(L34&lt;&gt;"",INDIRECT(VLOOKUP(L34,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N34" xr:uid="{048F5814-7352-45BC-A9CA-AB008E4E732D}">
+    <dataValidation type="list" sqref="N34" xr:uid="{437B7CB8-BE3C-4069-A863-07A17055CB90}">
       <formula1>=IF(M34&lt;&gt;"",INDIRECT(VLOOKUP(M34,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M35" xr:uid="{3539061A-E5CF-4E14-94F6-9B4338D49A29}">
+    <dataValidation type="list" sqref="M35" xr:uid="{6111BDCF-0139-481D-A108-08D5CDF3A387}">
       <formula1>=IF(L35&lt;&gt;"",INDIRECT(VLOOKUP(L35,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N35" xr:uid="{DF761495-DD6E-46F0-95D1-ED488DBC04C7}">
+    <dataValidation type="list" sqref="N35" xr:uid="{0FED6F50-673A-4B6D-82D3-94233BA325C0}">
       <formula1>=IF(M35&lt;&gt;"",INDIRECT(VLOOKUP(M35,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M36" xr:uid="{BBAC61F7-0B04-4D89-AAA9-44797C402D3F}">
+    <dataValidation type="list" sqref="M36" xr:uid="{B79AEA43-7FFB-4950-A544-54750C16D2FD}">
       <formula1>=IF(L36&lt;&gt;"",INDIRECT(VLOOKUP(L36,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N36" xr:uid="{44F65DE1-4375-4FA0-94B8-F900156DFCA3}">
+    <dataValidation type="list" sqref="N36" xr:uid="{BBBC0057-8E23-4F64-94F2-B302AE654D40}">
       <formula1>=IF(M36&lt;&gt;"",INDIRECT(VLOOKUP(M36,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M37" xr:uid="{4CCF928C-25E1-44A7-81CE-06B39F991F50}">
+    <dataValidation type="list" sqref="M37" xr:uid="{A9D5C355-870D-4B34-8BCF-03C868492A1E}">
       <formula1>=IF(L37&lt;&gt;"",INDIRECT(VLOOKUP(L37,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N37" xr:uid="{AB6FF786-9CDE-46F7-83F0-2E36ADA897A4}">
+    <dataValidation type="list" sqref="N37" xr:uid="{4DCCBF18-D75B-473F-9648-F04D4B358E03}">
       <formula1>=IF(M37&lt;&gt;"",INDIRECT(VLOOKUP(M37,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M38" xr:uid="{B003AE08-656E-4FDD-B961-30E934501FC1}">
+    <dataValidation type="list" sqref="M38" xr:uid="{EF73387C-6FD2-4034-9347-CF6BAD345025}">
       <formula1>=IF(L38&lt;&gt;"",INDIRECT(VLOOKUP(L38,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N38" xr:uid="{3CC9D930-838A-43AF-AB0D-9ED828DB2679}">
+    <dataValidation type="list" sqref="N38" xr:uid="{1FA3E877-A7D2-4C53-AC16-96998BC1918B}">
       <formula1>=IF(M38&lt;&gt;"",INDIRECT(VLOOKUP(M38,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M39" xr:uid="{2DDE7A33-8FD1-4709-9A77-44DBB1050A81}">
+    <dataValidation type="list" sqref="M39" xr:uid="{C0039B13-D91F-4599-A730-5C45E41BC885}">
       <formula1>=IF(L39&lt;&gt;"",INDIRECT(VLOOKUP(L39,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N39" xr:uid="{9A8D00D3-409A-4B75-8A1D-6AD40E1F6A5D}">
+    <dataValidation type="list" sqref="N39" xr:uid="{94BEF9CD-A54C-4A2F-BFE7-C9CE65CC9F77}">
       <formula1>=IF(M39&lt;&gt;"",INDIRECT(VLOOKUP(M39,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M40" xr:uid="{5C00F7E4-C830-4652-9340-77EA670AE01C}">
+    <dataValidation type="list" sqref="M40" xr:uid="{DBC2FC12-77EA-4678-87D3-C8ACBEB58DE2}">
       <formula1>=IF(L40&lt;&gt;"",INDIRECT(VLOOKUP(L40,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N40" xr:uid="{74A2C1F9-A076-4E8E-97E0-6CC86C5A060D}">
+    <dataValidation type="list" sqref="N40" xr:uid="{76E7C18B-E77E-426C-A6BF-A1B4AA78E428}">
       <formula1>=IF(M40&lt;&gt;"",INDIRECT(VLOOKUP(M40,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M41" xr:uid="{E40C977E-BA48-4B0D-B2A2-180D282B40D5}">
+    <dataValidation type="list" sqref="M41" xr:uid="{FC7FD73F-096F-4DA6-95BE-AA45BB178441}">
       <formula1>=IF(L41&lt;&gt;"",INDIRECT(VLOOKUP(L41,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N41" xr:uid="{70AD7889-88D5-41D7-BAA9-D7C3832E3B9F}">
+    <dataValidation type="list" sqref="N41" xr:uid="{2C308D56-D2A3-4BED-9E36-45AE9AEF4E67}">
       <formula1>=IF(M41&lt;&gt;"",INDIRECT(VLOOKUP(M41,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M42" xr:uid="{CD0BEE19-1B1F-48EB-8C61-54283A133748}">
+    <dataValidation type="list" sqref="M42" xr:uid="{87FD8767-D6A6-4CBC-95E1-CF91E70AA9FB}">
       <formula1>=IF(L42&lt;&gt;"",INDIRECT(VLOOKUP(L42,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N42" xr:uid="{FFC36E02-DC05-48EE-9D55-7DDD4D87EF9C}">
+    <dataValidation type="list" sqref="N42" xr:uid="{A9DD5A74-D347-4DF1-81A1-2D9C747867E2}">
       <formula1>=IF(M42&lt;&gt;"",INDIRECT(VLOOKUP(M42,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M43" xr:uid="{3CC947FE-159D-4D2E-9692-3977A33D9FAA}">
+    <dataValidation type="list" sqref="M43" xr:uid="{81DA0FF0-669F-4C8C-AD46-5FB3DDEFFCDF}">
       <formula1>=IF(L43&lt;&gt;"",INDIRECT(VLOOKUP(L43,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N43" xr:uid="{D6A052E3-569D-423B-8D8A-76787B4629E1}">
+    <dataValidation type="list" sqref="N43" xr:uid="{E8065A27-0836-41FE-A791-F315DDC4DC86}">
       <formula1>=IF(M43&lt;&gt;"",INDIRECT(VLOOKUP(M43,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M44" xr:uid="{E2626C6D-33AA-4CC0-ADBB-E8A45D61F818}">
+    <dataValidation type="list" sqref="M44" xr:uid="{81DBEC54-7B91-41FC-8033-B8D5A8FCE152}">
       <formula1>=IF(L44&lt;&gt;"",INDIRECT(VLOOKUP(L44,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N44" xr:uid="{C4278011-6399-43F0-8A08-257CC08C386B}">
+    <dataValidation type="list" sqref="N44" xr:uid="{FAE2606F-ED84-4FFF-82DC-EA1187E4AB37}">
       <formula1>=IF(M44&lt;&gt;"",INDIRECT(VLOOKUP(M44,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M45" xr:uid="{A942CBD7-E37A-4E08-9C9E-772E1E889608}">
+    <dataValidation type="list" sqref="M45" xr:uid="{B9ECF3C1-581A-4EAD-BDC9-C1F3DF8FA397}">
       <formula1>=IF(L45&lt;&gt;"",INDIRECT(VLOOKUP(L45,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N45" xr:uid="{98DAC143-1101-48FE-809F-AEDFAB233572}">
+    <dataValidation type="list" sqref="N45" xr:uid="{7C3B1889-32D2-49C2-A930-D559C31BC15F}">
       <formula1>=IF(M45&lt;&gt;"",INDIRECT(VLOOKUP(M45,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M46" xr:uid="{71B59107-953C-47DB-8545-245266134525}">
+    <dataValidation type="list" sqref="M46" xr:uid="{8D1AF60D-421A-4554-B70E-017B31DCDBCE}">
       <formula1>=IF(L46&lt;&gt;"",INDIRECT(VLOOKUP(L46,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N46" xr:uid="{746D11DA-D84D-4799-B044-FBF2537A2981}">
+    <dataValidation type="list" sqref="N46" xr:uid="{92AE049E-2141-4FD9-A279-EC36C26C1387}">
       <formula1>=IF(M46&lt;&gt;"",INDIRECT(VLOOKUP(M46,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M47" xr:uid="{3F3595A1-FF89-475F-A005-EE20F001EAD8}">
+    <dataValidation type="list" sqref="M47" xr:uid="{3863EB6C-05D7-43EC-868D-82737073A3F7}">
       <formula1>=IF(L47&lt;&gt;"",INDIRECT(VLOOKUP(L47,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N47" xr:uid="{FA8FB03C-C802-4FFC-99EE-0431099F82D6}">
+    <dataValidation type="list" sqref="N47" xr:uid="{4C626BB2-3614-4F02-A846-2E7B101598A8}">
       <formula1>=IF(M47&lt;&gt;"",INDIRECT(VLOOKUP(M47,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M48" xr:uid="{F21FAB6C-0527-4387-86BC-A2C8108F5B33}">
+    <dataValidation type="list" sqref="M48" xr:uid="{87141235-D4E1-4A61-A368-67EA247D3853}">
       <formula1>=IF(L48&lt;&gt;"",INDIRECT(VLOOKUP(L48,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N48" xr:uid="{92266854-ADCB-403C-AF98-B36F0CB43087}">
+    <dataValidation type="list" sqref="N48" xr:uid="{EE2B8FA4-7275-44F5-8B72-C37A988B5576}">
       <formula1>=IF(M48&lt;&gt;"",INDIRECT(VLOOKUP(M48,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M49" xr:uid="{50D307FD-13FB-4AA3-8CAC-2690EE41EE69}">
+    <dataValidation type="list" sqref="M49" xr:uid="{01560651-7D08-461B-958B-06DF3A6423FA}">
       <formula1>=IF(L49&lt;&gt;"",INDIRECT(VLOOKUP(L49,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N49" xr:uid="{1B545C64-FC50-44EC-8091-CE4C90BAFBED}">
+    <dataValidation type="list" sqref="N49" xr:uid="{4F410309-8161-4198-ADCD-B514114EF1FC}">
       <formula1>=IF(M49&lt;&gt;"",INDIRECT(VLOOKUP(M49,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M50" xr:uid="{8324D5C4-423B-49F9-9F15-C8626C5DF808}">
+    <dataValidation type="list" sqref="M50" xr:uid="{9D43B938-AD6D-4D7F-B76E-413B3F9646FF}">
       <formula1>=IF(L50&lt;&gt;"",INDIRECT(VLOOKUP(L50,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N50" xr:uid="{ECBCCFDC-5C33-4A76-89C5-754D1A67AD91}">
+    <dataValidation type="list" sqref="N50" xr:uid="{8D332105-95FB-45DD-9551-298B82984D99}">
       <formula1>=IF(M50&lt;&gt;"",INDIRECT(VLOOKUP(M50,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M51" xr:uid="{4D3ABBF7-54C4-4395-BED2-1ED34BB5D8FD}">
+    <dataValidation type="list" sqref="M51" xr:uid="{D8D493CD-6F8C-499F-A312-33875F8457D7}">
       <formula1>=IF(L51&lt;&gt;"",INDIRECT(VLOOKUP(L51,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N51" xr:uid="{94FC49D1-2C21-4718-B290-F849E83B9732}">
+    <dataValidation type="list" sqref="N51" xr:uid="{CEB722FA-9A68-428D-B86B-1613F34F8866}">
       <formula1>=IF(M51&lt;&gt;"",INDIRECT(VLOOKUP(M51,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M52" xr:uid="{7E601600-FF18-42FB-9C70-C057FF4ED337}">
+    <dataValidation type="list" sqref="M52" xr:uid="{544E65CE-0FF5-49FA-B290-1E7CD1898BE3}">
       <formula1>=IF(L52&lt;&gt;"",INDIRECT(VLOOKUP(L52,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N52" xr:uid="{D4AE083A-7386-4260-858D-3496093DC192}">
+    <dataValidation type="list" sqref="N52" xr:uid="{CADFA794-8390-4A27-9F7C-1507EB559E93}">
       <formula1>=IF(M52&lt;&gt;"",INDIRECT(VLOOKUP(M52,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M53" xr:uid="{D48D9102-6FBA-4D82-ACC3-6EB5797D33CD}">
+    <dataValidation type="list" sqref="M53" xr:uid="{5C89A64E-1BF5-4D3D-8140-EC33DFA4A0BF}">
       <formula1>=IF(L53&lt;&gt;"",INDIRECT(VLOOKUP(L53,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N53" xr:uid="{946B0DA0-DFF3-445D-A8C0-F0E15D75CAD4}">
+    <dataValidation type="list" sqref="N53" xr:uid="{5DB1918D-2CE3-4DDA-AA71-147312C7CD09}">
       <formula1>=IF(M53&lt;&gt;"",INDIRECT(VLOOKUP(M53,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M54" xr:uid="{4029139A-C3BD-4311-8FDF-9F4A885E7ECB}">
+    <dataValidation type="list" sqref="M54" xr:uid="{6242F419-08E2-44E3-B475-10D4698B14B4}">
       <formula1>=IF(L54&lt;&gt;"",INDIRECT(VLOOKUP(L54,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N54" xr:uid="{E8FA3573-A131-47D2-8CD0-323C62510E73}">
+    <dataValidation type="list" sqref="N54" xr:uid="{85A73DD9-AB61-4021-B3E6-35589454A24E}">
       <formula1>=IF(M54&lt;&gt;"",INDIRECT(VLOOKUP(M54,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M55" xr:uid="{3A52F426-B9AB-44C2-ABA9-9AA09A28288C}">
+    <dataValidation type="list" sqref="M55" xr:uid="{CBFA3930-FB8B-4051-AC7A-09B98755D37B}">
       <formula1>=IF(L55&lt;&gt;"",INDIRECT(VLOOKUP(L55,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N55" xr:uid="{C83C3C23-CCFB-4AE1-8C5E-AD087B3DE86F}">
+    <dataValidation type="list" sqref="N55" xr:uid="{DE1CC3D5-5514-4CA1-B91F-058BC7C02631}">
       <formula1>=IF(M55&lt;&gt;"",INDIRECT(VLOOKUP(M55,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M56" xr:uid="{8EAEC4CB-7E01-420E-A949-3167085ADBD7}">
+    <dataValidation type="list" sqref="M56" xr:uid="{EA810CC1-A0AD-422C-B9FC-EEED495ABA7F}">
       <formula1>=IF(L56&lt;&gt;"",INDIRECT(VLOOKUP(L56,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N56" xr:uid="{3E9EA463-8231-483E-BCBD-E167814D5964}">
+    <dataValidation type="list" sqref="N56" xr:uid="{7D50EB0B-1BAB-4903-B1E6-52EE58BA080D}">
       <formula1>=IF(M56&lt;&gt;"",INDIRECT(VLOOKUP(M56,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M57" xr:uid="{E1D07860-93F5-4765-9435-81C1EBB0A7BC}">
+    <dataValidation type="list" sqref="M57" xr:uid="{897FB21A-4E69-4563-9746-DF5C5AD6E1AC}">
       <formula1>=IF(L57&lt;&gt;"",INDIRECT(VLOOKUP(L57,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N57" xr:uid="{771C4E59-B7E2-40E6-B2D9-AF295F4E7935}">
+    <dataValidation type="list" sqref="N57" xr:uid="{CE4E22E4-6E5E-4018-A9E2-9E5ADAABC4D5}">
       <formula1>=IF(M57&lt;&gt;"",INDIRECT(VLOOKUP(M57,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M58" xr:uid="{A894CE73-3287-4F70-8C53-F0C1A98CB387}">
+    <dataValidation type="list" sqref="M58" xr:uid="{A34781E6-C3CE-462E-8D03-379356D7140F}">
       <formula1>=IF(L58&lt;&gt;"",INDIRECT(VLOOKUP(L58,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N58" xr:uid="{77B0E717-87DB-4E17-940D-46E0D7B96BF8}">
+    <dataValidation type="list" sqref="N58" xr:uid="{4921FBF5-C1D5-44AB-8D0F-E647078C6B93}">
       <formula1>=IF(M58&lt;&gt;"",INDIRECT(VLOOKUP(M58,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M59" xr:uid="{F3DF7B08-BCB4-4227-BEFC-1149BBD68DC2}">
+    <dataValidation type="list" sqref="M59" xr:uid="{F37D1C00-EB92-42D9-918D-C7804EA136AD}">
       <formula1>=IF(L59&lt;&gt;"",INDIRECT(VLOOKUP(L59,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N59" xr:uid="{266B2D7F-DB02-446E-91DC-95694A5FA2D0}">
+    <dataValidation type="list" sqref="N59" xr:uid="{BD9065CA-F3E0-4D4F-A864-0CB65C43072A}">
       <formula1>=IF(M59&lt;&gt;"",INDIRECT(VLOOKUP(M59,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M60" xr:uid="{4722F14B-E128-4EAD-BE52-68BBAD6807D1}">
+    <dataValidation type="list" sqref="M60" xr:uid="{3B6D3332-EE87-4E08-B950-A7AD266C0BBD}">
       <formula1>=IF(L60&lt;&gt;"",INDIRECT(VLOOKUP(L60,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N60" xr:uid="{6DFA98C0-E966-45BC-BB4A-43488935504A}">
+    <dataValidation type="list" sqref="N60" xr:uid="{15FEF7B0-BF05-4DC3-9EFF-ECAD65090CEC}">
       <formula1>=IF(M60&lt;&gt;"",INDIRECT(VLOOKUP(M60,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M61" xr:uid="{871D560B-2859-4E24-9EAE-BEAF65D169C4}">
+    <dataValidation type="list" sqref="M61" xr:uid="{2B479462-A30C-47D3-B359-19B6598FCDE3}">
       <formula1>=IF(L61&lt;&gt;"",INDIRECT(VLOOKUP(L61,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N61" xr:uid="{789E5A7E-8183-41CA-B13C-24042E88E76C}">
+    <dataValidation type="list" sqref="N61" xr:uid="{62D615DA-4A42-40E5-8FC2-D4F1C5255D79}">
       <formula1>=IF(M61&lt;&gt;"",INDIRECT(VLOOKUP(M61,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M62" xr:uid="{2277AF98-D03F-463E-B1EB-AEF49305CA62}">
+    <dataValidation type="list" sqref="M62" xr:uid="{9CE0399C-12EA-4218-9FF0-65179BC6C926}">
       <formula1>=IF(L62&lt;&gt;"",INDIRECT(VLOOKUP(L62,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N62" xr:uid="{D977E406-2FBE-4C96-9119-EC387A7FBB84}">
+    <dataValidation type="list" sqref="N62" xr:uid="{4042AEDF-A19F-4823-9C4F-DFD66842ECB9}">
       <formula1>=IF(M62&lt;&gt;"",INDIRECT(VLOOKUP(M62,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M63" xr:uid="{96AD825E-1417-479C-B8EF-14C1275B7683}">
+    <dataValidation type="list" sqref="M63" xr:uid="{777BBCD6-A8DE-4E50-AC17-F8C012BEFF8D}">
       <formula1>=IF(L63&lt;&gt;"",INDIRECT(VLOOKUP(L63,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N63" xr:uid="{F1BFBE55-B3FF-43A0-8B20-EE0214E5E335}">
+    <dataValidation type="list" sqref="N63" xr:uid="{5A2EE76B-7CB3-4F3F-8F66-A01FDAEC174E}">
       <formula1>=IF(M63&lt;&gt;"",INDIRECT(VLOOKUP(M63,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M64" xr:uid="{0DF4C6A8-6853-400C-8D99-39565DFF9341}">
+    <dataValidation type="list" sqref="M64" xr:uid="{3CDF17AB-07F4-428D-91AA-69528C6B50B5}">
       <formula1>=IF(L64&lt;&gt;"",INDIRECT(VLOOKUP(L64,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N64" xr:uid="{A7961BFD-7E61-4A1C-9B90-D95C09D7910D}">
+    <dataValidation type="list" sqref="N64" xr:uid="{5CF52A3D-474B-43F3-BCB4-1E6A4C5AC5CB}">
       <formula1>=IF(M64&lt;&gt;"",INDIRECT(VLOOKUP(M64,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M65" xr:uid="{1FEC3EB0-CFF1-4C42-BCAF-EC694EAB5D8D}">
+    <dataValidation type="list" sqref="M65" xr:uid="{70606A15-F185-41BF-AC62-6DBADA1C5854}">
       <formula1>=IF(L65&lt;&gt;"",INDIRECT(VLOOKUP(L65,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N65" xr:uid="{53BFE412-D085-4AA2-B520-5291E0AEEB71}">
+    <dataValidation type="list" sqref="N65" xr:uid="{E63761D9-8AEF-4208-BF78-2B39258B17D5}">
       <formula1>=IF(M65&lt;&gt;"",INDIRECT(VLOOKUP(M65,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M66" xr:uid="{ACA7B415-C378-4B2D-A4BB-776EF06DBE11}">
+    <dataValidation type="list" sqref="M66" xr:uid="{68C739FE-B09D-4192-AF39-48AE8FC17C43}">
       <formula1>=IF(L66&lt;&gt;"",INDIRECT(VLOOKUP(L66,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N66" xr:uid="{7CB759E1-3C2B-48AA-BC85-E2DEDB58FF94}">
+    <dataValidation type="list" sqref="N66" xr:uid="{D331B7B8-29CB-47E7-9243-7F9B56269FE0}">
       <formula1>=IF(M66&lt;&gt;"",INDIRECT(VLOOKUP(M66,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M67" xr:uid="{782078E6-54D5-46F0-A3D8-12525F313DB6}">
+    <dataValidation type="list" sqref="M67" xr:uid="{BCF2262E-D069-435D-8908-44696B7299FF}">
       <formula1>=IF(L67&lt;&gt;"",INDIRECT(VLOOKUP(L67,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N67" xr:uid="{E6DAF514-6FD6-49C7-B879-15E598C6C392}">
+    <dataValidation type="list" sqref="N67" xr:uid="{68151748-5A53-47A8-821E-3044005073A1}">
       <formula1>=IF(M67&lt;&gt;"",INDIRECT(VLOOKUP(M67,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M68" xr:uid="{63A8616D-39AD-4A63-B5FC-2D5B1D24A02F}">
+    <dataValidation type="list" sqref="M68" xr:uid="{2487522D-7710-468E-A5BD-3A1E2D13F08D}">
       <formula1>=IF(L68&lt;&gt;"",INDIRECT(VLOOKUP(L68,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N68" xr:uid="{D242D5AF-CC7B-402C-A0BC-3F549BB7A8FE}">
+    <dataValidation type="list" sqref="N68" xr:uid="{D027BB49-5CC6-4D17-8E28-8E1FCB252FCC}">
       <formula1>=IF(M68&lt;&gt;"",INDIRECT(VLOOKUP(M68,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M69" xr:uid="{0F51D506-B452-4C99-A700-D022094FD517}">
+    <dataValidation type="list" sqref="M69" xr:uid="{68AE3750-4530-4976-956D-24C9FE6F0C91}">
       <formula1>=IF(L69&lt;&gt;"",INDIRECT(VLOOKUP(L69,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N69" xr:uid="{90083EC9-1805-4685-AC9F-2DB9BED95F88}">
+    <dataValidation type="list" sqref="N69" xr:uid="{6A2A843F-5E6A-4832-9813-1D67B4DC7725}">
       <formula1>=IF(M69&lt;&gt;"",INDIRECT(VLOOKUP(M69,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M70" xr:uid="{CF2DAEEB-C0DF-4DF1-8BB7-5B8BEEA7E64F}">
+    <dataValidation type="list" sqref="M70" xr:uid="{4323138D-92F8-40EA-AB31-C91B861684C3}">
       <formula1>=IF(L70&lt;&gt;"",INDIRECT(VLOOKUP(L70,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N70" xr:uid="{B2D49FA8-58AA-4A1D-9612-73CFDB923BE1}">
+    <dataValidation type="list" sqref="N70" xr:uid="{CB3CECA0-CD54-4E26-98B1-C3DA09EEB5B8}">
       <formula1>=IF(M70&lt;&gt;"",INDIRECT(VLOOKUP(M70,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M71" xr:uid="{0505C0F1-132B-4779-B224-9C0C66D22EFA}">
+    <dataValidation type="list" sqref="M71" xr:uid="{3E016FB4-BA98-4B15-AECB-C1077460DDF2}">
       <formula1>=IF(L71&lt;&gt;"",INDIRECT(VLOOKUP(L71,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N71" xr:uid="{3AEDAD0F-8F31-4A8A-B781-CFD77BEF259E}">
+    <dataValidation type="list" sqref="N71" xr:uid="{B664AB92-3F46-4FA4-B803-48F155226FC9}">
       <formula1>=IF(M71&lt;&gt;"",INDIRECT(VLOOKUP(M71,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M72" xr:uid="{D2A2D88D-EBA4-4CBC-B960-9742D6AC8DE2}">
+    <dataValidation type="list" sqref="M72" xr:uid="{C0C429F9-8D30-4A00-8E5D-3B2A91714987}">
       <formula1>=IF(L72&lt;&gt;"",INDIRECT(VLOOKUP(L72,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N72" xr:uid="{6636E5D9-1471-461E-BF8E-7ABF2EAB572D}">
+    <dataValidation type="list" sqref="N72" xr:uid="{1361FA7E-0B3E-4CE6-99E2-E8F3A55F9748}">
       <formula1>=IF(M72&lt;&gt;"",INDIRECT(VLOOKUP(M72,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M73" xr:uid="{7416EA04-E596-4477-8E8B-95719D06993B}">
+    <dataValidation type="list" sqref="M73" xr:uid="{E9D16B1C-8401-4F01-AB09-99B519164A7E}">
       <formula1>=IF(L73&lt;&gt;"",INDIRECT(VLOOKUP(L73,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N73" xr:uid="{80326A82-740F-4753-B886-1A750284BB92}">
+    <dataValidation type="list" sqref="N73" xr:uid="{86695F69-43EA-447E-A272-F490BF8AAD37}">
       <formula1>=IF(M73&lt;&gt;"",INDIRECT(VLOOKUP(M73,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M74" xr:uid="{56C25670-8488-4F31-9290-E0A831E17E12}">
+    <dataValidation type="list" sqref="M74" xr:uid="{A3BA1900-752C-45A4-A1EF-58355EF1D4F8}">
       <formula1>=IF(L74&lt;&gt;"",INDIRECT(VLOOKUP(L74,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N74" xr:uid="{AC89E489-A60D-4159-9471-EAEFE6F71547}">
+    <dataValidation type="list" sqref="N74" xr:uid="{E5DF84BE-5C24-42BE-BD0B-7901C05875A9}">
       <formula1>=IF(M74&lt;&gt;"",INDIRECT(VLOOKUP(M74,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M75" xr:uid="{64DE1BB1-92BB-4D68-A40B-CE506E1F90BA}">
+    <dataValidation type="list" sqref="M75" xr:uid="{ACFBFD39-206D-4F33-9878-FA860CFCF068}">
       <formula1>=IF(L75&lt;&gt;"",INDIRECT(VLOOKUP(L75,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N75" xr:uid="{6F805948-41A6-4B5A-8891-352BEEAE30F0}">
+    <dataValidation type="list" sqref="N75" xr:uid="{8E24C843-7D69-4EB8-B51E-9A1BF48B2D10}">
       <formula1>=IF(M75&lt;&gt;"",INDIRECT(VLOOKUP(M75,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M76" xr:uid="{E13EEE41-9FE8-40D3-BAF7-670EC5925D82}">
+    <dataValidation type="list" sqref="M76" xr:uid="{DF456784-DC72-49AE-8F99-049BC78CC8F7}">
       <formula1>=IF(L76&lt;&gt;"",INDIRECT(VLOOKUP(L76,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N76" xr:uid="{FC1BB35D-E4D0-4BCB-85C2-842373D90661}">
+    <dataValidation type="list" sqref="N76" xr:uid="{C2F8F5E4-A7C3-48EB-9ABF-6E4FEF9D6129}">
       <formula1>=IF(M76&lt;&gt;"",INDIRECT(VLOOKUP(M76,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M77" xr:uid="{9644C601-4E20-4BF0-BC32-E4D48D9DB68D}">
+    <dataValidation type="list" sqref="M77" xr:uid="{D479CBC2-7918-426C-8188-0CD2D4FEDC0B}">
       <formula1>=IF(L77&lt;&gt;"",INDIRECT(VLOOKUP(L77,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N77" xr:uid="{E844C865-76DD-4F85-8E5F-98708CB609BD}">
+    <dataValidation type="list" sqref="N77" xr:uid="{13B595CA-240C-4906-8EE8-45CCED6686C0}">
       <formula1>=IF(M77&lt;&gt;"",INDIRECT(VLOOKUP(M77,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M78" xr:uid="{2E9D0D78-492D-4E31-B132-1CAA30F0B0B6}">
+    <dataValidation type="list" sqref="M78" xr:uid="{2C05F384-E40B-4AB1-A587-19354717BAB4}">
       <formula1>=IF(L78&lt;&gt;"",INDIRECT(VLOOKUP(L78,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N78" xr:uid="{9657D196-3C09-4706-9D34-2957C4784EE6}">
+    <dataValidation type="list" sqref="N78" xr:uid="{A39D21B8-3164-43AB-950D-D0E51E0B8DF1}">
       <formula1>=IF(M78&lt;&gt;"",INDIRECT(VLOOKUP(M78,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M79" xr:uid="{42962B52-A0A8-4B8F-805C-8F8BBCD0873C}">
+    <dataValidation type="list" sqref="M79" xr:uid="{FD513C2A-D006-4B5E-A302-E26D73384462}">
       <formula1>=IF(L79&lt;&gt;"",INDIRECT(VLOOKUP(L79,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N79" xr:uid="{F2D4A209-DE03-45A3-A579-8062C41AB200}">
+    <dataValidation type="list" sqref="N79" xr:uid="{3F82FD0E-5D94-479A-9443-DE2FE6BDA35A}">
       <formula1>=IF(M79&lt;&gt;"",INDIRECT(VLOOKUP(M79,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M80" xr:uid="{377FBCC1-7BF0-45D3-B15E-F09AB2B788EC}">
+    <dataValidation type="list" sqref="M80" xr:uid="{789AFDE3-B9A5-47FA-BE83-0E390B78CD2E}">
       <formula1>=IF(L80&lt;&gt;"",INDIRECT(VLOOKUP(L80,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N80" xr:uid="{AF01BD2B-0B46-487D-8FE2-EC8D0227C269}">
+    <dataValidation type="list" sqref="N80" xr:uid="{8F474111-F7A3-467F-94BF-8269BEDA1E86}">
       <formula1>=IF(M80&lt;&gt;"",INDIRECT(VLOOKUP(M80,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M81" xr:uid="{38ADD641-2E5E-4A4F-B855-908AF5A7B2EC}">
+    <dataValidation type="list" sqref="M81" xr:uid="{6E8D3C17-0D82-4D4F-AECA-9B3A662D11EC}">
       <formula1>=IF(L81&lt;&gt;"",INDIRECT(VLOOKUP(L81,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N81" xr:uid="{7B85C975-9E34-4187-AD6E-B7089CDF100F}">
+    <dataValidation type="list" sqref="N81" xr:uid="{C2B09A5B-43BA-4C1E-9272-03AF232CB14F}">
       <formula1>=IF(M81&lt;&gt;"",INDIRECT(VLOOKUP(M81,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M82" xr:uid="{71BCE8D1-0F8F-46FE-8B7B-1D8FCCFF9F4B}">
+    <dataValidation type="list" sqref="M82" xr:uid="{1C01374D-006A-464E-B242-F93DBD704B7A}">
       <formula1>=IF(L82&lt;&gt;"",INDIRECT(VLOOKUP(L82,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N82" xr:uid="{BDED3832-5A6F-41EC-B7B1-08285025C0FB}">
+    <dataValidation type="list" sqref="N82" xr:uid="{57BB9A04-8899-475F-BEC5-4D703ACCEC49}">
       <formula1>=IF(M82&lt;&gt;"",INDIRECT(VLOOKUP(M82,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M83" xr:uid="{9CDF8373-A41F-4B3E-BAE3-14B7575D4C37}">
+    <dataValidation type="list" sqref="M83" xr:uid="{23D456E9-3948-49C8-9CAC-F462666EBDD3}">
       <formula1>=IF(L83&lt;&gt;"",INDIRECT(VLOOKUP(L83,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N83" xr:uid="{F71010E5-8C90-4523-BEA8-EEC0D35A447C}">
+    <dataValidation type="list" sqref="N83" xr:uid="{0F784CE8-8ADC-4733-8609-E69B108AF7BF}">
       <formula1>=IF(M83&lt;&gt;"",INDIRECT(VLOOKUP(M83,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M84" xr:uid="{B1B3779B-C294-4F3D-AA78-8C70133CC99E}">
+    <dataValidation type="list" sqref="M84" xr:uid="{B1AE32FA-3D73-40B6-BF45-31DADA1C96F5}">
       <formula1>=IF(L84&lt;&gt;"",INDIRECT(VLOOKUP(L84,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N84" xr:uid="{6857CD0A-2CF2-45DB-B898-8B545F0B215E}">
+    <dataValidation type="list" sqref="N84" xr:uid="{E2AFCFFF-A6AA-4A4A-B8B6-9EBDEDBED0A1}">
       <formula1>=IF(M84&lt;&gt;"",INDIRECT(VLOOKUP(M84,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M85" xr:uid="{B3DC59EE-3272-4E8E-A53D-2BFBEBC512D8}">
+    <dataValidation type="list" sqref="M85" xr:uid="{AE6F905B-86F8-4D86-9BC3-AF27CA849D7A}">
       <formula1>=IF(L85&lt;&gt;"",INDIRECT(VLOOKUP(L85,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N85" xr:uid="{520A93AC-B6D2-49EB-B54E-1BA9C1C1A2DD}">
+    <dataValidation type="list" sqref="N85" xr:uid="{C9D6BE84-8244-4911-A0A3-97B225C17134}">
       <formula1>=IF(M85&lt;&gt;"",INDIRECT(VLOOKUP(M85,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M86" xr:uid="{6AD96C43-96D2-47AD-8AF1-11F04763D002}">
+    <dataValidation type="list" sqref="M86" xr:uid="{4313C3AE-1F1E-4AD9-BB8E-F42FF91EB752}">
       <formula1>=IF(L86&lt;&gt;"",INDIRECT(VLOOKUP(L86,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N86" xr:uid="{2913B15B-B2F2-4A07-BFC7-F0EFBC7E5D69}">
+    <dataValidation type="list" sqref="N86" xr:uid="{567E795E-28F4-451C-A162-7A435F997423}">
       <formula1>=IF(M86&lt;&gt;"",INDIRECT(VLOOKUP(M86,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M87" xr:uid="{D45714B2-FF15-4E53-A129-C1619B0F1BBC}">
+    <dataValidation type="list" sqref="M87" xr:uid="{70F61F5E-52D3-4BA5-8383-1890E349683E}">
       <formula1>=IF(L87&lt;&gt;"",INDIRECT(VLOOKUP(L87,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N87" xr:uid="{249457CE-F289-42E1-B580-3713B650E453}">
+    <dataValidation type="list" sqref="N87" xr:uid="{6BB6D045-1D27-455D-9F3E-AD51BF00581E}">
       <formula1>=IF(M87&lt;&gt;"",INDIRECT(VLOOKUP(M87,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M88" xr:uid="{457134B9-01CA-4208-B3F1-EFE20F72EDC1}">
+    <dataValidation type="list" sqref="M88" xr:uid="{6B5E2737-2613-4F78-8CB9-8049A6486E93}">
       <formula1>=IF(L88&lt;&gt;"",INDIRECT(VLOOKUP(L88,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N88" xr:uid="{5F25315B-785F-4989-AA52-36DD76FE95B4}">
+    <dataValidation type="list" sqref="N88" xr:uid="{BAA101A8-AF68-4B80-8B6B-B05C8C10CDC6}">
       <formula1>=IF(M88&lt;&gt;"",INDIRECT(VLOOKUP(M88,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M89" xr:uid="{0C537E10-3C1E-498F-BA3C-4D4C14F79DB5}">
+    <dataValidation type="list" sqref="M89" xr:uid="{80E9AF4E-2B62-46F4-B334-1F8334D287F4}">
       <formula1>=IF(L89&lt;&gt;"",INDIRECT(VLOOKUP(L89,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N89" xr:uid="{7A238919-11B3-4764-B134-2442E0F95AAD}">
+    <dataValidation type="list" sqref="N89" xr:uid="{57D84DD9-320A-4135-AE41-F9897DEA039D}">
       <formula1>=IF(M89&lt;&gt;"",INDIRECT(VLOOKUP(M89,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M90" xr:uid="{A75E8969-E596-41F6-A65F-77CB4F4AEC16}">
+    <dataValidation type="list" sqref="M90" xr:uid="{13A8686F-792F-4467-B0CC-E6A530FA5CDD}">
       <formula1>=IF(L90&lt;&gt;"",INDIRECT(VLOOKUP(L90,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N90" xr:uid="{08C0FE1B-258F-4D58-A926-B44665245938}">
+    <dataValidation type="list" sqref="N90" xr:uid="{12E82F8B-C2B9-474C-8492-4999F47C7763}">
       <formula1>=IF(M90&lt;&gt;"",INDIRECT(VLOOKUP(M90,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M91" xr:uid="{000E0597-9B85-4850-B429-5D678F65D2E4}">
+    <dataValidation type="list" sqref="M91" xr:uid="{3B0C3D29-5036-47D0-BBB0-87926D9CC043}">
       <formula1>=IF(L91&lt;&gt;"",INDIRECT(VLOOKUP(L91,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N91" xr:uid="{982AB3AD-254C-4AE9-AE9B-3C10BED3A619}">
+    <dataValidation type="list" sqref="N91" xr:uid="{C64CFDBA-C7A7-4681-A43F-6FFAF2309415}">
       <formula1>=IF(M91&lt;&gt;"",INDIRECT(VLOOKUP(M91,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M92" xr:uid="{73F1B4F5-EF89-4B81-8DE0-FB28660AA936}">
+    <dataValidation type="list" sqref="M92" xr:uid="{756542EB-F73A-4158-9824-8AED7FD94F17}">
       <formula1>=IF(L92&lt;&gt;"",INDIRECT(VLOOKUP(L92,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N92" xr:uid="{7EEB7467-4ABF-44A6-A9B5-A29D5C69DC8C}">
+    <dataValidation type="list" sqref="N92" xr:uid="{4BE53481-4C2B-4E7C-836C-C05AA7D4F5A5}">
       <formula1>=IF(M92&lt;&gt;"",INDIRECT(VLOOKUP(M92,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M93" xr:uid="{C55AD802-40A7-4210-A721-CE18F2E763FF}">
+    <dataValidation type="list" sqref="M93" xr:uid="{C87F9A3E-A540-4D96-9FBD-9056B0DA540D}">
       <formula1>=IF(L93&lt;&gt;"",INDIRECT(VLOOKUP(L93,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N93" xr:uid="{FC4BA724-BD58-489A-B7DB-10D991F0AD21}">
+    <dataValidation type="list" sqref="N93" xr:uid="{C54F1FB9-AD24-46EC-B106-1685C80325B1}">
       <formula1>=IF(M93&lt;&gt;"",INDIRECT(VLOOKUP(M93,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M94" xr:uid="{12C80FB8-EAC2-478E-822F-1966C744774E}">
+    <dataValidation type="list" sqref="M94" xr:uid="{6D008264-57A7-4326-BFFE-73DD71297E90}">
       <formula1>=IF(L94&lt;&gt;"",INDIRECT(VLOOKUP(L94,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N94" xr:uid="{1CF2FB25-451C-4F30-B0B5-D864A254317C}">
+    <dataValidation type="list" sqref="N94" xr:uid="{F92F4C2B-A6AF-425A-9E07-A81A8DE4E6AE}">
       <formula1>=IF(M94&lt;&gt;"",INDIRECT(VLOOKUP(M94,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M95" xr:uid="{42FBF5F1-9848-4312-884B-A40DD60C2757}">
+    <dataValidation type="list" sqref="M95" xr:uid="{775F7717-A851-4B34-86B6-F07F285CA067}">
       <formula1>=IF(L95&lt;&gt;"",INDIRECT(VLOOKUP(L95,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N95" xr:uid="{185DB9E6-4260-4175-9028-F72202164907}">
+    <dataValidation type="list" sqref="N95" xr:uid="{BFB7A94D-E30E-4964-A890-41AD3377B89D}">
       <formula1>=IF(M95&lt;&gt;"",INDIRECT(VLOOKUP(M95,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M96" xr:uid="{23427D93-A5F9-4D8C-9F4F-E64793164BEE}">
+    <dataValidation type="list" sqref="M96" xr:uid="{54501E82-F8CC-42F1-974C-5D1374A6E5D8}">
       <formula1>=IF(L96&lt;&gt;"",INDIRECT(VLOOKUP(L96,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N96" xr:uid="{E739CC8F-EBA7-4F98-B653-1D4C2AE0DDEC}">
+    <dataValidation type="list" sqref="N96" xr:uid="{C33DA351-41F9-436C-8A5E-6B3C25B74B52}">
       <formula1>=IF(M96&lt;&gt;"",INDIRECT(VLOOKUP(M96,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M97" xr:uid="{68B9C16A-6E7A-4342-B2EA-FE81BDCB73E4}">
+    <dataValidation type="list" sqref="M97" xr:uid="{A4786721-BC5C-475F-88B9-0890CF519A93}">
       <formula1>=IF(L97&lt;&gt;"",INDIRECT(VLOOKUP(L97,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N97" xr:uid="{B449E748-530E-4F2A-8A43-9D8C8264B65C}">
+    <dataValidation type="list" sqref="N97" xr:uid="{4468663E-7364-40CC-B56E-3BF80CB7304E}">
       <formula1>=IF(M97&lt;&gt;"",INDIRECT(VLOOKUP(M97,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M98" xr:uid="{B4867892-CD0A-4343-9D4F-9713E05CF900}">
+    <dataValidation type="list" sqref="M98" xr:uid="{F0BDE4EE-C95F-4B48-BF1E-FA0F9B185F6A}">
       <formula1>=IF(L98&lt;&gt;"",INDIRECT(VLOOKUP(L98,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N98" xr:uid="{630089C7-C33E-4152-B4CE-FADA864671A9}">
+    <dataValidation type="list" sqref="N98" xr:uid="{E2E5C908-C125-48ED-81A2-0BEAB9E256F7}">
       <formula1>=IF(M98&lt;&gt;"",INDIRECT(VLOOKUP(M98,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M99" xr:uid="{92608419-1969-4437-8208-40A2B1504C3E}">
+    <dataValidation type="list" sqref="M99" xr:uid="{E226D0E5-07D2-4EA8-BE06-2F864867C08E}">
       <formula1>=IF(L99&lt;&gt;"",INDIRECT(VLOOKUP(L99,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N99" xr:uid="{20823314-7441-423C-918F-9755294F6D36}">
+    <dataValidation type="list" sqref="N99" xr:uid="{2920F4FB-D740-4088-8E5F-8D744B4B89C1}">
       <formula1>=IF(M99&lt;&gt;"",INDIRECT(VLOOKUP(M99,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M100" xr:uid="{55CA1021-C0BD-4F5C-99E2-D4F589C3AED6}">
+    <dataValidation type="list" sqref="M100" xr:uid="{778AA6E1-AA14-4B0C-8939-0878EE103F25}">
       <formula1>=IF(L100&lt;&gt;"",INDIRECT(VLOOKUP(L100,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N100" xr:uid="{F05C60C7-1DDA-4AD9-A7D9-88293594C404}">
+    <dataValidation type="list" sqref="N100" xr:uid="{95A465AE-2804-4BFC-B013-146B8FF6294B}">
       <formula1>=IF(M100&lt;&gt;"",INDIRECT(VLOOKUP(M100,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M101" xr:uid="{51023FE3-0D68-4EBD-BCBC-211230C0E337}">
+    <dataValidation type="list" sqref="M101" xr:uid="{8A81AD29-E417-4C1F-9945-EB78CDCDD25D}">
       <formula1>=IF(L101&lt;&gt;"",INDIRECT(VLOOKUP(L101,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N101" xr:uid="{BFD82682-4370-4E1D-9BB5-06B5AF7419ED}">
+    <dataValidation type="list" sqref="N101" xr:uid="{85E85262-BC42-4B44-89A3-F4DDF99A1894}">
       <formula1>=IF(M101&lt;&gt;"",INDIRECT(VLOOKUP(M101,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M102" xr:uid="{C0AC80EE-5912-4ADB-BA17-B03B7F2C7AD3}">
+    <dataValidation type="list" sqref="M102" xr:uid="{27E2192E-5B77-4B92-8F9A-53572817A317}">
       <formula1>=IF(L102&lt;&gt;"",INDIRECT(VLOOKUP(L102,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N102" xr:uid="{53E2AD86-4750-45D8-BD09-6BBD6EF45F05}">
+    <dataValidation type="list" sqref="N102" xr:uid="{E71F8DDD-2F3A-4B32-AD16-26BB9092FE02}">
       <formula1>=IF(M102&lt;&gt;"",INDIRECT(VLOOKUP(M102,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M103" xr:uid="{4F2CBD1C-BFE2-48DF-8A3E-DECAACCD4839}">
+    <dataValidation type="list" sqref="M103" xr:uid="{5B358DE8-8C50-42B3-9C6E-666DEA7D6A10}">
       <formula1>=IF(L103&lt;&gt;"",INDIRECT(VLOOKUP(L103,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N103" xr:uid="{C299C9FE-3155-475A-A12A-F21BC140B7DD}">
+    <dataValidation type="list" sqref="N103" xr:uid="{290FF201-2282-4293-BAE9-1374BAF84438}">
       <formula1>=IF(M103&lt;&gt;"",INDIRECT(VLOOKUP(M103,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M104" xr:uid="{3AD84C9E-C221-411D-A790-8EFD5549C32B}">
+    <dataValidation type="list" sqref="M104" xr:uid="{06740BEB-456E-469E-9474-5467A9C426BC}">
       <formula1>=IF(L104&lt;&gt;"",INDIRECT(VLOOKUP(L104,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N104" xr:uid="{D90665B9-0DCB-4474-A124-7C0176EEE108}">
+    <dataValidation type="list" sqref="N104" xr:uid="{B83A8214-897C-4ABE-8C4B-CC219037A16A}">
       <formula1>=IF(M104&lt;&gt;"",INDIRECT(VLOOKUP(M104,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M105" xr:uid="{644238DF-DAD3-421D-9A19-B34617E74712}">
+    <dataValidation type="list" sqref="M105" xr:uid="{687E6DF4-0B8C-4CF8-806A-C45F423B1A50}">
       <formula1>=IF(L105&lt;&gt;"",INDIRECT(VLOOKUP(L105,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N105" xr:uid="{8B614E3B-B89C-4480-8058-E89543B199EA}">
+    <dataValidation type="list" sqref="N105" xr:uid="{793D380F-E49C-4F1F-B837-1E29C6376003}">
       <formula1>=IF(M105&lt;&gt;"",INDIRECT(VLOOKUP(M105,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M106" xr:uid="{0747A70F-F833-4AE5-8D86-E112F4073B0A}">
+    <dataValidation type="list" sqref="M106" xr:uid="{3E059FB6-CEF6-4A2F-87AE-2E88C5C0BE6B}">
       <formula1>=IF(L106&lt;&gt;"",INDIRECT(VLOOKUP(L106,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N106" xr:uid="{6E8E3A28-0D70-41CC-B8EF-19A8DF2D2983}">
+    <dataValidation type="list" sqref="N106" xr:uid="{458A0610-1CF7-4050-9F00-E6F36CB1B80B}">
       <formula1>=IF(M106&lt;&gt;"",INDIRECT(VLOOKUP(M106,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M107" xr:uid="{7F38F621-C321-4131-923A-AFFD357F1B0D}">
+    <dataValidation type="list" sqref="M107" xr:uid="{2931F7E5-9890-4BC0-949A-D28847052B4E}">
       <formula1>=IF(L107&lt;&gt;"",INDIRECT(VLOOKUP(L107,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N107" xr:uid="{2870B568-2B6E-4B15-8A70-80C69B08AE0E}">
+    <dataValidation type="list" sqref="N107" xr:uid="{3D30A43D-EAEE-45A3-A37F-9088E8327D94}">
       <formula1>=IF(M107&lt;&gt;"",INDIRECT(VLOOKUP(M107,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M108" xr:uid="{96364CFF-AB16-4934-A618-F54E8C11DF44}">
+    <dataValidation type="list" sqref="M108" xr:uid="{BD5E943A-82C5-4F56-94BB-014CC1621A51}">
       <formula1>=IF(L108&lt;&gt;"",INDIRECT(VLOOKUP(L108,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N108" xr:uid="{03D98A95-31D1-465F-B9D5-A2A51F30B756}">
+    <dataValidation type="list" sqref="N108" xr:uid="{E5EA4287-08BA-430E-BA5C-7681282B7330}">
       <formula1>=IF(M108&lt;&gt;"",INDIRECT(VLOOKUP(M108,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M109" xr:uid="{7C2AC632-E1E1-419A-B7A6-FB2A63C2B957}">
+    <dataValidation type="list" sqref="M109" xr:uid="{4D6EFAE4-E142-44AC-82A4-3D728DCE225E}">
       <formula1>=IF(L109&lt;&gt;"",INDIRECT(VLOOKUP(L109,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N109" xr:uid="{FE2212A0-598A-4EA7-986D-291524834CF7}">
+    <dataValidation type="list" sqref="N109" xr:uid="{2A42AC2D-B540-405A-B420-FB895BD2E9E3}">
       <formula1>=IF(M109&lt;&gt;"",INDIRECT(VLOOKUP(M109,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M110" xr:uid="{32B7C9E0-238C-4301-95FB-BD886904F359}">
+    <dataValidation type="list" sqref="M110" xr:uid="{5339B808-75B8-47B6-8DBB-F02CDBCFF606}">
       <formula1>=IF(L110&lt;&gt;"",INDIRECT(VLOOKUP(L110,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N110" xr:uid="{5BCB7F6B-BA53-41DF-9B72-D6AEC8E322B9}">
+    <dataValidation type="list" sqref="N110" xr:uid="{21B5F13B-2E1C-44CF-8AEF-05B25AA6A436}">
       <formula1>=IF(M110&lt;&gt;"",INDIRECT(VLOOKUP(M110,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M111" xr:uid="{CCC7F2E5-9BE7-4942-BD66-D90347D2EFB7}">
+    <dataValidation type="list" sqref="M111" xr:uid="{355D6899-9483-4E43-ACFE-2D13C1E7CACE}">
       <formula1>=IF(L111&lt;&gt;"",INDIRECT(VLOOKUP(L111,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N111" xr:uid="{51E1C862-ACD7-45F4-B7E1-45EA21E5BADB}">
+    <dataValidation type="list" sqref="N111" xr:uid="{FC042C12-CFB5-4BDC-B433-2984B85BED27}">
       <formula1>=IF(M111&lt;&gt;"",INDIRECT(VLOOKUP(M111,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M112" xr:uid="{F0A15E55-0B8D-44A4-B7E5-D4BCE26EE356}">
+    <dataValidation type="list" sqref="M112" xr:uid="{86AA7837-F10A-4787-AC84-BBCCAB050353}">
       <formula1>=IF(L112&lt;&gt;"",INDIRECT(VLOOKUP(L112,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N112" xr:uid="{43FB3755-C8D2-4855-8DAF-1E6011E99C29}">
+    <dataValidation type="list" sqref="N112" xr:uid="{7D12BC37-0FF8-4206-86F0-6F38B1243E48}">
       <formula1>=IF(M112&lt;&gt;"",INDIRECT(VLOOKUP(M112,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M113" xr:uid="{802294C7-5300-409E-B91D-79686C94D84F}">
+    <dataValidation type="list" sqref="M113" xr:uid="{81CB3BCD-9FD2-4234-8466-F7703D57233F}">
       <formula1>=IF(L113&lt;&gt;"",INDIRECT(VLOOKUP(L113,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N113" xr:uid="{9369DC81-2B1C-49CF-9258-64E7D7A25F9F}">
+    <dataValidation type="list" sqref="N113" xr:uid="{5D167AF0-67DC-48BB-937F-64CA70FAFD6D}">
       <formula1>=IF(M113&lt;&gt;"",INDIRECT(VLOOKUP(M113,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M114" xr:uid="{70CAA3A1-1096-420C-8480-7F833971616D}">
+    <dataValidation type="list" sqref="M114" xr:uid="{44F1CFE4-CB81-4738-9426-1B97B00D66FF}">
       <formula1>=IF(L114&lt;&gt;"",INDIRECT(VLOOKUP(L114,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N114" xr:uid="{21938BCF-74B2-4249-B9EB-762CE5ECBBB4}">
+    <dataValidation type="list" sqref="N114" xr:uid="{D5BAD910-DA6B-41C5-8DA7-4ECFC3D4DEF4}">
       <formula1>=IF(M114&lt;&gt;"",INDIRECT(VLOOKUP(M114,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M115" xr:uid="{26ABAB60-85A0-4A29-97B0-9C29DF4EAD13}">
+    <dataValidation type="list" sqref="M115" xr:uid="{ACFB7A91-6435-4868-AF59-A9FD36BD9B0F}">
       <formula1>=IF(L115&lt;&gt;"",INDIRECT(VLOOKUP(L115,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N115" xr:uid="{2B37D944-555A-4835-9DDA-1B787BAA5B32}">
+    <dataValidation type="list" sqref="N115" xr:uid="{B7815F6A-BFED-482A-A92B-1F8FA815E891}">
       <formula1>=IF(M115&lt;&gt;"",INDIRECT(VLOOKUP(M115,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M116" xr:uid="{140D8BC8-4514-4B9E-834F-13FC6840BA0F}">
+    <dataValidation type="list" sqref="M116" xr:uid="{46E5CF94-8F14-4742-8C27-A591B079643A}">
       <formula1>=IF(L116&lt;&gt;"",INDIRECT(VLOOKUP(L116,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N116" xr:uid="{C5931A2D-22BF-4076-ABDB-91CEC7783DB1}">
+    <dataValidation type="list" sqref="N116" xr:uid="{FAF28F92-45E6-4FF4-8E15-3B8C882104A7}">
       <formula1>=IF(M116&lt;&gt;"",INDIRECT(VLOOKUP(M116,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M117" xr:uid="{14B6AAFB-09B0-47B8-9E52-5FB731130548}">
+    <dataValidation type="list" sqref="M117" xr:uid="{79499A68-F985-4575-B12D-07D302A0077C}">
       <formula1>=IF(L117&lt;&gt;"",INDIRECT(VLOOKUP(L117,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N117" xr:uid="{DD80F490-B3FB-4C6E-AC82-970D0D62BC8F}">
+    <dataValidation type="list" sqref="N117" xr:uid="{43B0E19F-CF02-4FCF-A63C-8043C37D6BBA}">
       <formula1>=IF(M117&lt;&gt;"",INDIRECT(VLOOKUP(M117,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M118" xr:uid="{A83F2A37-8E2F-49B8-8587-272138C96D29}">
+    <dataValidation type="list" sqref="M118" xr:uid="{4EC685F2-8353-47DA-962E-3B484AC9B45A}">
       <formula1>=IF(L118&lt;&gt;"",INDIRECT(VLOOKUP(L118,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N118" xr:uid="{F7B7AABC-9059-4C89-95FE-6BB4D2D9BAED}">
+    <dataValidation type="list" sqref="N118" xr:uid="{E045FCE9-F98A-4CD4-A39A-DD907E870095}">
       <formula1>=IF(M118&lt;&gt;"",INDIRECT(VLOOKUP(M118,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M119" xr:uid="{1B8FBC8D-1DF1-419F-9947-80D1DEFE3CF1}">
+    <dataValidation type="list" sqref="M119" xr:uid="{0BE3EB00-5845-427D-9BBF-D5F9336EFB36}">
       <formula1>=IF(L119&lt;&gt;"",INDIRECT(VLOOKUP(L119,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N119" xr:uid="{0388C82C-65A1-4399-9F79-2CE9619BADDA}">
+    <dataValidation type="list" sqref="N119" xr:uid="{88CB6754-D9DE-43CB-833A-901E8687CD59}">
       <formula1>=IF(M119&lt;&gt;"",INDIRECT(VLOOKUP(M119,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M120" xr:uid="{F0F02869-AD0A-4E54-8EE7-7DA29FB91CE5}">
+    <dataValidation type="list" sqref="M120" xr:uid="{59603DDA-8924-4F6A-BB24-00F1BDFE793E}">
       <formula1>=IF(L120&lt;&gt;"",INDIRECT(VLOOKUP(L120,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N120" xr:uid="{F09C153E-4AF8-4577-90CF-C2B1B276C33D}">
+    <dataValidation type="list" sqref="N120" xr:uid="{F930B301-6C9E-4F94-9DCB-0AC020637F06}">
       <formula1>=IF(M120&lt;&gt;"",INDIRECT(VLOOKUP(M120,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M121" xr:uid="{BBE21A06-431B-4222-BCB1-0476E9A168D9}">
+    <dataValidation type="list" sqref="M121" xr:uid="{BA67210C-FA19-4828-8CD0-5D5B931A4101}">
       <formula1>=IF(L121&lt;&gt;"",INDIRECT(VLOOKUP(L121,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N121" xr:uid="{219E0B97-F9F6-4A3B-8A48-628705C5F06A}">
+    <dataValidation type="list" sqref="N121" xr:uid="{D45000C0-510C-46D0-9D6D-EC290DB73A6F}">
       <formula1>=IF(M121&lt;&gt;"",INDIRECT(VLOOKUP(M121,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M122" xr:uid="{C19FAF56-B077-4549-9CB6-2477AACCBFFE}">
+    <dataValidation type="list" sqref="M122" xr:uid="{F2F7FF08-4726-4FCA-97A6-217DFDCE682B}">
       <formula1>=IF(L122&lt;&gt;"",INDIRECT(VLOOKUP(L122,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N122" xr:uid="{B1DF4CEE-3728-4755-893E-613F8DBF587B}">
+    <dataValidation type="list" sqref="N122" xr:uid="{FA1AB3C9-AEE3-4C0F-BC16-65C05026448F}">
       <formula1>=IF(M122&lt;&gt;"",INDIRECT(VLOOKUP(M122,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M123" xr:uid="{FBA8FA7D-FA69-4704-8DE7-9368709292ED}">
+    <dataValidation type="list" sqref="M123" xr:uid="{A56D630D-9EF2-4EBB-9890-B57EC8FBAF33}">
       <formula1>=IF(L123&lt;&gt;"",INDIRECT(VLOOKUP(L123,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N123" xr:uid="{7E9D875A-3091-4129-8E9D-897F3BB25BD3}">
+    <dataValidation type="list" sqref="N123" xr:uid="{E0C89DF3-E7A2-4591-9948-96E3C268B039}">
       <formula1>=IF(M123&lt;&gt;"",INDIRECT(VLOOKUP(M123,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M124" xr:uid="{3D88AE9D-93B5-4467-9FAC-50ED788983EE}">
+    <dataValidation type="list" sqref="M124" xr:uid="{E9307E07-95D0-49B6-9D40-849EF734CDDA}">
       <formula1>=IF(L124&lt;&gt;"",INDIRECT(VLOOKUP(L124,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N124" xr:uid="{3292240A-83AA-464F-9224-1BB46ACB9E40}">
+    <dataValidation type="list" sqref="N124" xr:uid="{FFA5BC71-743B-4B18-9963-D9027819DB2D}">
       <formula1>=IF(M124&lt;&gt;"",INDIRECT(VLOOKUP(M124,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M125" xr:uid="{2A0E0EB0-2E09-48B1-AD8F-8337C202AC42}">
+    <dataValidation type="list" sqref="M125" xr:uid="{4DFAC669-2D17-4635-AFC6-A2084B8D6679}">
       <formula1>=IF(L125&lt;&gt;"",INDIRECT(VLOOKUP(L125,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N125" xr:uid="{358F6709-69AD-4CDC-BC47-7ED667063F39}">
+    <dataValidation type="list" sqref="N125" xr:uid="{DC7683D7-F13C-4322-A01C-683D49F9D05B}">
       <formula1>=IF(M125&lt;&gt;"",INDIRECT(VLOOKUP(M125,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M126" xr:uid="{4127DF81-247D-4461-B3C6-08939D1048DC}">
+    <dataValidation type="list" sqref="M126" xr:uid="{5345991E-9FFA-4AAF-8F5A-21BD93EF01AB}">
       <formula1>=IF(L126&lt;&gt;"",INDIRECT(VLOOKUP(L126,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N126" xr:uid="{CC74E6A5-1F3A-49D3-88CA-BC3BD36BD163}">
+    <dataValidation type="list" sqref="N126" xr:uid="{224675C0-769F-4001-B6FF-1EF0AD7220D8}">
       <formula1>=IF(M126&lt;&gt;"",INDIRECT(VLOOKUP(M126,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M127" xr:uid="{2BD448A8-934C-4427-8F55-07BF18A98A7C}">
+    <dataValidation type="list" sqref="M127" xr:uid="{17E2C0D3-ED6E-4D8D-A3F5-273A6299433F}">
       <formula1>=IF(L127&lt;&gt;"",INDIRECT(VLOOKUP(L127,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N127" xr:uid="{6D48E737-06AE-470A-A411-559BE9BE2B03}">
+    <dataValidation type="list" sqref="N127" xr:uid="{4F13541B-8943-4192-9A28-31C5F7125D8C}">
       <formula1>=IF(M127&lt;&gt;"",INDIRECT(VLOOKUP(M127,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M128" xr:uid="{DFED2F2E-4540-4CBB-9D3A-9E823D8BC9F4}">
+    <dataValidation type="list" sqref="M128" xr:uid="{CF5EE0CC-A8C7-4532-8FC7-E340F3A37F23}">
       <formula1>=IF(L128&lt;&gt;"",INDIRECT(VLOOKUP(L128,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N128" xr:uid="{0D0576B5-2DE6-404C-88EF-A1F214C8CB8C}">
+    <dataValidation type="list" sqref="N128" xr:uid="{36786B6C-BBE1-4155-ABDF-2F303EB31D1B}">
       <formula1>=IF(M128&lt;&gt;"",INDIRECT(VLOOKUP(M128,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M129" xr:uid="{5C1D1739-5678-4FAA-8C6A-9C7C689B9E8E}">
+    <dataValidation type="list" sqref="M129" xr:uid="{1E985F31-46A0-43B2-9DAC-FC9F3D688CAA}">
       <formula1>=IF(L129&lt;&gt;"",INDIRECT(VLOOKUP(L129,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N129" xr:uid="{9BCDBA88-3543-4843-BF08-23AA3A24D529}">
+    <dataValidation type="list" sqref="N129" xr:uid="{879C4BA8-F57C-420B-949A-9DD13E37BF10}">
       <formula1>=IF(M129&lt;&gt;"",INDIRECT(VLOOKUP(M129,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M130" xr:uid="{974AB64E-B128-472A-83AF-AB05869D58EA}">
+    <dataValidation type="list" sqref="M130" xr:uid="{72B81CDD-CCDC-41A6-8083-DD37EF8CA6D7}">
       <formula1>=IF(L130&lt;&gt;"",INDIRECT(VLOOKUP(L130,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N130" xr:uid="{B63F2C7F-517C-4F2D-912E-CC90AB587969}">
+    <dataValidation type="list" sqref="N130" xr:uid="{1ABD5DFB-889F-41D7-B3B4-1E4B19A7F057}">
       <formula1>=IF(M130&lt;&gt;"",INDIRECT(VLOOKUP(M130,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M131" xr:uid="{29FEE640-0905-48A2-BF0D-21A9EAE3A543}">
+    <dataValidation type="list" sqref="M131" xr:uid="{BFDEBC8C-E1C4-4560-988C-08E8BE14E071}">
       <formula1>=IF(L131&lt;&gt;"",INDIRECT(VLOOKUP(L131,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N131" xr:uid="{67685248-D40E-454A-BAB9-8A4C25482878}">
+    <dataValidation type="list" sqref="N131" xr:uid="{4BB2794C-919E-4425-A224-E0FC71CBEC7E}">
       <formula1>=IF(M131&lt;&gt;"",INDIRECT(VLOOKUP(M131,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M132" xr:uid="{920867B1-7328-4323-8CA8-940DE412CD57}">
+    <dataValidation type="list" sqref="M132" xr:uid="{4E6B565F-0ADD-4F7B-B1F1-B1B95DB3AF84}">
       <formula1>=IF(L132&lt;&gt;"",INDIRECT(VLOOKUP(L132,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N132" xr:uid="{D1E3E9EF-1B63-4D5B-A913-B71CE490F91B}">
+    <dataValidation type="list" sqref="N132" xr:uid="{C49B8C08-4DB7-4A6E-9917-D1F337953DA5}">
       <formula1>=IF(M132&lt;&gt;"",INDIRECT(VLOOKUP(M132,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M133" xr:uid="{469ECAF0-80F6-4522-B334-73F2D64C04FB}">
+    <dataValidation type="list" sqref="M133" xr:uid="{B08949D1-6E78-4D67-A70D-019ADAF6B699}">
       <formula1>=IF(L133&lt;&gt;"",INDIRECT(VLOOKUP(L133,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N133" xr:uid="{9C8CF3F6-1304-4116-B15B-F64C03D49B77}">
+    <dataValidation type="list" sqref="N133" xr:uid="{86E4661E-2549-4DB9-B58F-CD37DF30D526}">
       <formula1>=IF(M133&lt;&gt;"",INDIRECT(VLOOKUP(M133,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M134" xr:uid="{8B540E8A-0EEF-4D92-8739-A056FF73F1B3}">
+    <dataValidation type="list" sqref="M134" xr:uid="{9E91AED7-0907-4544-AC78-EF4F8CDAAC73}">
       <formula1>=IF(L134&lt;&gt;"",INDIRECT(VLOOKUP(L134,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N134" xr:uid="{2D05A413-1851-4C8A-873C-4590398A10C4}">
+    <dataValidation type="list" sqref="N134" xr:uid="{CB131930-EF48-4CB3-AECD-0B00902E57BA}">
       <formula1>=IF(M134&lt;&gt;"",INDIRECT(VLOOKUP(M134,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M135" xr:uid="{63263096-D21F-4029-AC24-58FAA413937D}">
+    <dataValidation type="list" sqref="M135" xr:uid="{B3B6DC31-B6A1-4881-B7D1-55640845E47A}">
       <formula1>=IF(L135&lt;&gt;"",INDIRECT(VLOOKUP(L135,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N135" xr:uid="{FA302716-EFF4-4F64-B855-3D9A4BF63EDF}">
+    <dataValidation type="list" sqref="N135" xr:uid="{2BD96D19-648F-4A2A-BFA8-7032ADB766C8}">
       <formula1>=IF(M135&lt;&gt;"",INDIRECT(VLOOKUP(M135,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M136" xr:uid="{001769A6-5AE1-4B4D-B3F3-B97FEC00E5A6}">
+    <dataValidation type="list" sqref="M136" xr:uid="{8FCD3B87-8129-4D6B-BE41-8CF417655D1A}">
       <formula1>=IF(L136&lt;&gt;"",INDIRECT(VLOOKUP(L136,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N136" xr:uid="{90AAB88E-FDCE-44D5-9A7D-93E2B1908170}">
+    <dataValidation type="list" sqref="N136" xr:uid="{A3FF4637-CE71-441B-B39F-AF63529FFC0C}">
       <formula1>=IF(M136&lt;&gt;"",INDIRECT(VLOOKUP(M136,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M137" xr:uid="{F13ABC48-796C-4D79-A0E3-E9C0D07370C6}">
+    <dataValidation type="list" sqref="M137" xr:uid="{951CD547-66E0-4F60-8B9C-5A2BE5BA9A9F}">
       <formula1>=IF(L137&lt;&gt;"",INDIRECT(VLOOKUP(L137,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N137" xr:uid="{D974FF68-3960-4299-825A-DA34A4087DC6}">
+    <dataValidation type="list" sqref="N137" xr:uid="{7BCA6799-6579-49C2-A6BC-5ED9D63D2017}">
       <formula1>=IF(M137&lt;&gt;"",INDIRECT(VLOOKUP(M137,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M138" xr:uid="{42411CC4-0170-4BA3-ACA6-02CBBD88C945}">
+    <dataValidation type="list" sqref="M138" xr:uid="{967B5862-0947-4423-8C46-38B67E0B351B}">
       <formula1>=IF(L138&lt;&gt;"",INDIRECT(VLOOKUP(L138,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N138" xr:uid="{9F05E55C-35EC-46C5-B32F-84F0BE929F0A}">
+    <dataValidation type="list" sqref="N138" xr:uid="{3DB72D2C-FAB9-4969-8BC5-AC150E2E08B7}">
       <formula1>=IF(M138&lt;&gt;"",INDIRECT(VLOOKUP(M138,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M139" xr:uid="{9A8FF1D8-3976-4202-B960-B97B8C5A403C}">
+    <dataValidation type="list" sqref="M139" xr:uid="{1DCDAA76-CB5E-41A9-AA19-1F208CAF2D2C}">
       <formula1>=IF(L139&lt;&gt;"",INDIRECT(VLOOKUP(L139,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N139" xr:uid="{EDCD3E58-1CA2-452B-B438-FAEA90351A59}">
+    <dataValidation type="list" sqref="N139" xr:uid="{28F4CFE9-4BD8-474C-B4EE-78DAFC089D95}">
       <formula1>=IF(M139&lt;&gt;"",INDIRECT(VLOOKUP(M139,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M140" xr:uid="{0F3D7361-84CF-4A35-B74D-68836ACF1C67}">
+    <dataValidation type="list" sqref="M140" xr:uid="{9AF7C953-65D4-4923-8517-C32C06A5042F}">
       <formula1>=IF(L140&lt;&gt;"",INDIRECT(VLOOKUP(L140,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N140" xr:uid="{9C4BAE37-62B2-44AB-8856-C66339C4824C}">
+    <dataValidation type="list" sqref="N140" xr:uid="{44545154-5F96-4653-9410-28F19AFB819B}">
       <formula1>=IF(M140&lt;&gt;"",INDIRECT(VLOOKUP(M140,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M141" xr:uid="{3C830AFB-EE3C-41E1-A2D7-785C8B62268C}">
+    <dataValidation type="list" sqref="M141" xr:uid="{27209100-2B4C-4A22-B39A-60CC9B43E4F7}">
       <formula1>=IF(L141&lt;&gt;"",INDIRECT(VLOOKUP(L141,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N141" xr:uid="{FC53EFAF-8FD4-4E2F-B0BD-6E0433A41126}">
+    <dataValidation type="list" sqref="N141" xr:uid="{64975D70-76BD-4EE8-A6F9-20B9230DCF2C}">
       <formula1>=IF(M141&lt;&gt;"",INDIRECT(VLOOKUP(M141,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M142" xr:uid="{A40D20D5-52FB-4D7F-9E36-A8DB42A67522}">
+    <dataValidation type="list" sqref="M142" xr:uid="{E67142BE-9A9C-4ED0-83A8-9732FFC8EA5E}">
       <formula1>=IF(L142&lt;&gt;"",INDIRECT(VLOOKUP(L142,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N142" xr:uid="{D3207588-8AE2-41BA-A963-C3E4BC82051F}">
+    <dataValidation type="list" sqref="N142" xr:uid="{6E8DF800-0B65-42C7-90C4-BF371049C8A6}">
       <formula1>=IF(M142&lt;&gt;"",INDIRECT(VLOOKUP(M142,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M143" xr:uid="{E1D6AE45-25C2-4A67-8A1C-8F39542CD906}">
+    <dataValidation type="list" sqref="M143" xr:uid="{A891B64B-3BF1-415C-BE7A-71D24070CDAF}">
       <formula1>=IF(L143&lt;&gt;"",INDIRECT(VLOOKUP(L143,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N143" xr:uid="{424730BD-A03E-41F6-85CD-E34038257F80}">
+    <dataValidation type="list" sqref="N143" xr:uid="{9B65D205-8601-4F88-A16C-B89D3C887F6D}">
       <formula1>=IF(M143&lt;&gt;"",INDIRECT(VLOOKUP(M143,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M144" xr:uid="{3944B3AA-7976-4897-A7D3-0A39E7903558}">
+    <dataValidation type="list" sqref="M144" xr:uid="{70E266A7-A29A-41C9-A12E-3E1DD1882409}">
       <formula1>=IF(L144&lt;&gt;"",INDIRECT(VLOOKUP(L144,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N144" xr:uid="{378D5D13-4D68-472F-B205-BCA9784371AE}">
+    <dataValidation type="list" sqref="N144" xr:uid="{667843B0-8A37-4A27-A4AB-D3FA0716993D}">
       <formula1>=IF(M144&lt;&gt;"",INDIRECT(VLOOKUP(M144,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M145" xr:uid="{E188479F-87A0-4181-BBD7-DE94C1AB2D72}">
+    <dataValidation type="list" sqref="M145" xr:uid="{2559FBAF-B6F8-459D-8ABE-A652DFA98C22}">
       <formula1>=IF(L145&lt;&gt;"",INDIRECT(VLOOKUP(L145,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N145" xr:uid="{C5DFE997-579F-4382-B365-2990B20EB8F1}">
+    <dataValidation type="list" sqref="N145" xr:uid="{8189AC76-9BB3-4F15-856C-A3275F6C3C03}">
       <formula1>=IF(M145&lt;&gt;"",INDIRECT(VLOOKUP(M145,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M146" xr:uid="{F5D4C045-1E97-456C-B5F4-1CBD13724977}">
+    <dataValidation type="list" sqref="M146" xr:uid="{0917C0D0-E429-4EC2-9196-992E15C81398}">
       <formula1>=IF(L146&lt;&gt;"",INDIRECT(VLOOKUP(L146,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N146" xr:uid="{5FA7ACB2-3B04-422C-A112-3C904BF3A634}">
+    <dataValidation type="list" sqref="N146" xr:uid="{8F1F6A5A-4462-4EA7-9A90-814531780574}">
       <formula1>=IF(M146&lt;&gt;"",INDIRECT(VLOOKUP(M146,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M147" xr:uid="{97D31FEA-DCD8-4D6E-A289-AEE00E4B0029}">
+    <dataValidation type="list" sqref="M147" xr:uid="{369352D7-0AAA-4D14-B156-425AD06D0B12}">
       <formula1>=IF(L147&lt;&gt;"",INDIRECT(VLOOKUP(L147,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N147" xr:uid="{0F7BD9C1-5436-41CB-A8DE-FDEC407A1257}">
+    <dataValidation type="list" sqref="N147" xr:uid="{A13A3970-1DA4-4236-8EFF-710C3358667F}">
       <formula1>=IF(M147&lt;&gt;"",INDIRECT(VLOOKUP(M147,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M148" xr:uid="{D1F8BA05-CB87-4C50-909A-4C48140D631F}">
+    <dataValidation type="list" sqref="M148" xr:uid="{24F8225E-E863-4068-A872-D496558A232C}">
       <formula1>=IF(L148&lt;&gt;"",INDIRECT(VLOOKUP(L148,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N148" xr:uid="{9C04AF65-A3C8-4707-83C1-A31B19BC1614}">
+    <dataValidation type="list" sqref="N148" xr:uid="{88D6A5C0-0CB9-45D3-B48F-89379733FA93}">
       <formula1>=IF(M148&lt;&gt;"",INDIRECT(VLOOKUP(M148,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M149" xr:uid="{3F3ED2CD-A553-4FD4-A183-9C2DCD50A4D8}">
+    <dataValidation type="list" sqref="M149" xr:uid="{402C1075-A335-4971-A1D6-C0C9895D2272}">
       <formula1>=IF(L149&lt;&gt;"",INDIRECT(VLOOKUP(L149,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N149" xr:uid="{1AC69999-B860-4AD9-B2C7-4BF513D8C6B8}">
+    <dataValidation type="list" sqref="N149" xr:uid="{695896DF-8D3A-4FF8-9679-D66F0C5FE4D5}">
       <formula1>=IF(M149&lt;&gt;"",INDIRECT(VLOOKUP(M149,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M150" xr:uid="{4388678E-EAC3-4803-BA1D-6FA27AAC4A21}">
+    <dataValidation type="list" sqref="M150" xr:uid="{F8E05C3D-CD50-41C1-88F5-BADCFF2620E7}">
       <formula1>=IF(L150&lt;&gt;"",INDIRECT(VLOOKUP(L150,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N150" xr:uid="{59054C08-45B4-435F-888C-E56A47B849D0}">
+    <dataValidation type="list" sqref="N150" xr:uid="{1B056B00-9C07-44A4-894C-7C4888E1E6BB}">
       <formula1>=IF(M150&lt;&gt;"",INDIRECT(VLOOKUP(M150,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M151" xr:uid="{58AFAE00-1F54-485C-97E4-04CFDD6D5679}">
+    <dataValidation type="list" sqref="M151" xr:uid="{6AF94592-9EA0-465C-9448-FA80432E5AAC}">
       <formula1>=IF(L151&lt;&gt;"",INDIRECT(VLOOKUP(L151,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N151" xr:uid="{E93F5347-4075-4524-B517-0602CF1B08E5}">
+    <dataValidation type="list" sqref="N151" xr:uid="{7D9B5725-2D2C-4A6F-AFAE-7BE47BBE0DD0}">
       <formula1>=IF(M151&lt;&gt;"",INDIRECT(VLOOKUP(M151,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M152" xr:uid="{87E3FCE7-E986-4D03-94A7-3A0018E1C86F}">
+    <dataValidation type="list" sqref="M152" xr:uid="{91913848-24E8-46E7-8411-E5EAD59D7F68}">
       <formula1>=IF(L152&lt;&gt;"",INDIRECT(VLOOKUP(L152,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N152" xr:uid="{6688B1E8-E5B5-492B-84F3-064ED0E019D1}">
+    <dataValidation type="list" sqref="N152" xr:uid="{A06D95B3-C5EF-4A33-A8BD-5D29B6A2D577}">
       <formula1>=IF(M152&lt;&gt;"",INDIRECT(VLOOKUP(M152,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M153" xr:uid="{7635E370-B8BF-4F59-A2B8-EC17B5FC35DD}">
+    <dataValidation type="list" sqref="M153" xr:uid="{B95EB610-8003-4B3A-98CC-12CC6B6319FB}">
       <formula1>=IF(L153&lt;&gt;"",INDIRECT(VLOOKUP(L153,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N153" xr:uid="{8C483F8D-B6FD-465F-9343-4D57D654510C}">
+    <dataValidation type="list" sqref="N153" xr:uid="{83570171-BDAE-4401-90BE-D630424057DD}">
       <formula1>=IF(M153&lt;&gt;"",INDIRECT(VLOOKUP(M153,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M154" xr:uid="{D3C9AF01-10E2-4D1D-BE92-C34F5DA033D1}">
+    <dataValidation type="list" sqref="M154" xr:uid="{8171F9A5-201C-48D0-8364-51EB22153A6D}">
       <formula1>=IF(L154&lt;&gt;"",INDIRECT(VLOOKUP(L154,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N154" xr:uid="{FE187A43-5573-42F7-AE60-55EA1715CCC8}">
+    <dataValidation type="list" sqref="N154" xr:uid="{D4C525E0-72C5-4E29-9EDE-C20AF579727F}">
       <formula1>=IF(M154&lt;&gt;"",INDIRECT(VLOOKUP(M154,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M155" xr:uid="{0F94681B-EEAE-424F-88B6-D6960397C485}">
+    <dataValidation type="list" sqref="M155" xr:uid="{257C250C-9A08-4657-8988-22079B97C547}">
       <formula1>=IF(L155&lt;&gt;"",INDIRECT(VLOOKUP(L155,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N155" xr:uid="{8F0F3FAB-476C-406D-A836-035D8903C220}">
+    <dataValidation type="list" sqref="N155" xr:uid="{2C4F7DA4-5C35-4F0B-ACC3-1D2D46FAEE17}">
       <formula1>=IF(M155&lt;&gt;"",INDIRECT(VLOOKUP(M155,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M156" xr:uid="{30F1C66C-B3EA-4B4A-A435-D2F907102500}">
+    <dataValidation type="list" sqref="M156" xr:uid="{FD6BD2B3-3E17-45AA-AC55-A1433F00D392}">
       <formula1>=IF(L156&lt;&gt;"",INDIRECT(VLOOKUP(L156,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N156" xr:uid="{03E80E12-444B-4F21-8F48-918DD7E1AB96}">
+    <dataValidation type="list" sqref="N156" xr:uid="{F0EF2243-09F5-4D13-A31F-3699254FE23D}">
       <formula1>=IF(M156&lt;&gt;"",INDIRECT(VLOOKUP(M156,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M157" xr:uid="{6A5AD085-BEB9-4B36-9578-3E18439F3CA5}">
+    <dataValidation type="list" sqref="M157" xr:uid="{CAAA34D2-7471-49F6-90E0-3A9132E0B911}">
       <formula1>=IF(L157&lt;&gt;"",INDIRECT(VLOOKUP(L157,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N157" xr:uid="{7F091DAE-0005-4585-96FD-FD21DACBEC72}">
+    <dataValidation type="list" sqref="N157" xr:uid="{B8276AC0-9035-422C-AC86-3B7EC42F9281}">
       <formula1>=IF(M157&lt;&gt;"",INDIRECT(VLOOKUP(M157,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M158" xr:uid="{467A4668-1443-4BBC-9E34-18A509A76B2E}">
+    <dataValidation type="list" sqref="M158" xr:uid="{2CE62458-A2AB-465D-9D78-B04BB136B149}">
       <formula1>=IF(L158&lt;&gt;"",INDIRECT(VLOOKUP(L158,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N158" xr:uid="{2289D7B0-F9C1-431F-A879-89250C170FE8}">
+    <dataValidation type="list" sqref="N158" xr:uid="{A36FCF52-BF2B-4A5D-9EE7-267926604017}">
       <formula1>=IF(M158&lt;&gt;"",INDIRECT(VLOOKUP(M158,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M159" xr:uid="{FF524428-D5A8-4461-A5C9-E8E4A0D433DD}">
+    <dataValidation type="list" sqref="M159" xr:uid="{333A3485-0C66-43F8-9112-3EC0874C6FB6}">
       <formula1>=IF(L159&lt;&gt;"",INDIRECT(VLOOKUP(L159,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N159" xr:uid="{D62FC20F-EECB-481B-83AB-BCBB2BED5305}">
+    <dataValidation type="list" sqref="N159" xr:uid="{8A8CE326-FB07-479A-ABC7-54E3C9BCBCB6}">
       <formula1>=IF(M159&lt;&gt;"",INDIRECT(VLOOKUP(M159,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M160" xr:uid="{EFC94CDD-0C3F-46A0-A415-BBBF4BA2A739}">
+    <dataValidation type="list" sqref="M160" xr:uid="{B30A5A9B-78E7-4FCE-92E3-EBC8BA44E99A}">
       <formula1>=IF(L160&lt;&gt;"",INDIRECT(VLOOKUP(L160,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N160" xr:uid="{4D36F889-3D29-40D3-93D0-50116C204FB2}">
+    <dataValidation type="list" sqref="N160" xr:uid="{3FE77D11-D4E3-43A5-ABCA-46C7FF2B98C5}">
       <formula1>=IF(M160&lt;&gt;"",INDIRECT(VLOOKUP(M160,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M161" xr:uid="{D05E8655-0731-4423-910E-3C1BDB421DAD}">
+    <dataValidation type="list" sqref="M161" xr:uid="{6607F9BC-01E0-4978-A474-1AD716138431}">
       <formula1>=IF(L161&lt;&gt;"",INDIRECT(VLOOKUP(L161,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N161" xr:uid="{8BE56AD0-693D-4616-A5CC-1286A3146C7D}">
+    <dataValidation type="list" sqref="N161" xr:uid="{9A637B2F-1182-48EB-BA8B-03F3437EC966}">
       <formula1>=IF(M161&lt;&gt;"",INDIRECT(VLOOKUP(M161,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M162" xr:uid="{B9DB1F55-60AC-426C-824E-436D017A85FB}">
+    <dataValidation type="list" sqref="M162" xr:uid="{D8C5D817-9B33-4BC3-AC0A-307D4FADD516}">
       <formula1>=IF(L162&lt;&gt;"",INDIRECT(VLOOKUP(L162,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N162" xr:uid="{5285A340-2CB2-451E-A318-19B7A8C52652}">
+    <dataValidation type="list" sqref="N162" xr:uid="{20B90C17-D459-4863-B6F9-8C965C0BF2E5}">
       <formula1>=IF(M162&lt;&gt;"",INDIRECT(VLOOKUP(M162,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M163" xr:uid="{60D3E12C-E062-4FFF-A4A2-2EA839D3461A}">
+    <dataValidation type="list" sqref="M163" xr:uid="{A2D36859-3342-4376-B8BB-57C5659E3F7B}">
       <formula1>=IF(L163&lt;&gt;"",INDIRECT(VLOOKUP(L163,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N163" xr:uid="{C595104C-C1ED-4546-B2E4-2FBE30BA5395}">
+    <dataValidation type="list" sqref="N163" xr:uid="{8F939DE0-FC6F-48CE-8C5E-69415EDE681C}">
       <formula1>=IF(M163&lt;&gt;"",INDIRECT(VLOOKUP(M163,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M164" xr:uid="{7CB36B21-DFA9-43C1-9FCE-DB8DA3B60B41}">
+    <dataValidation type="list" sqref="M164" xr:uid="{CCC010DE-6B21-4D01-AF33-8A66386D2E0E}">
       <formula1>=IF(L164&lt;&gt;"",INDIRECT(VLOOKUP(L164,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N164" xr:uid="{F2ABA7C8-B4D5-470D-A9CC-35A1C810E3DA}">
+    <dataValidation type="list" sqref="N164" xr:uid="{38B42E97-C015-45DB-B4BB-39A2872D448A}">
       <formula1>=IF(M164&lt;&gt;"",INDIRECT(VLOOKUP(M164,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M165" xr:uid="{BDC9ACFD-650D-479F-94C4-CC902146FA50}">
+    <dataValidation type="list" sqref="M165" xr:uid="{A3F8786C-FA4E-4BAC-B6AE-E9EDCF650733}">
       <formula1>=IF(L165&lt;&gt;"",INDIRECT(VLOOKUP(L165,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N165" xr:uid="{23ED0535-4073-42BE-B135-D930ABBE237E}">
+    <dataValidation type="list" sqref="N165" xr:uid="{A2BB3E2D-260C-4F29-BF9B-E231B021781C}">
       <formula1>=IF(M165&lt;&gt;"",INDIRECT(VLOOKUP(M165,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M166" xr:uid="{CB1DC729-35AC-4A06-885A-AB816D91F307}">
+    <dataValidation type="list" sqref="M166" xr:uid="{F77D32A9-F56C-4B06-B236-AF767A5F582B}">
       <formula1>=IF(L166&lt;&gt;"",INDIRECT(VLOOKUP(L166,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N166" xr:uid="{BCDB5F1A-E712-4BE8-901F-0A47BD0B338D}">
+    <dataValidation type="list" sqref="N166" xr:uid="{A135995A-8ADA-4C19-B510-39818E01BB5B}">
       <formula1>=IF(M166&lt;&gt;"",INDIRECT(VLOOKUP(M166,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M167" xr:uid="{73B4D651-D1C3-4E70-A9F0-B276A857FAC3}">
+    <dataValidation type="list" sqref="M167" xr:uid="{18C94130-0BC1-4549-81EA-847D15412CA9}">
       <formula1>=IF(L167&lt;&gt;"",INDIRECT(VLOOKUP(L167,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N167" xr:uid="{B0BA11BB-772F-4AB4-9E04-4DD80C7AE1E9}">
+    <dataValidation type="list" sqref="N167" xr:uid="{9518EE3C-935E-4514-863D-7F64226EB5F1}">
       <formula1>=IF(M167&lt;&gt;"",INDIRECT(VLOOKUP(M167,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M168" xr:uid="{90990138-D665-4449-AB28-D1453EF3236A}">
+    <dataValidation type="list" sqref="M168" xr:uid="{4DC1FCA4-86E9-4586-BE38-BA028117E523}">
       <formula1>=IF(L168&lt;&gt;"",INDIRECT(VLOOKUP(L168,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N168" xr:uid="{81FE1E85-CD48-42C6-A0BF-2DCE834C4668}">
+    <dataValidation type="list" sqref="N168" xr:uid="{0ED1A2F3-22A1-4956-B5CA-72F388AAE01C}">
       <formula1>=IF(M168&lt;&gt;"",INDIRECT(VLOOKUP(M168,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M169" xr:uid="{1E7D067E-7583-4AF7-AFAA-B4F97F5E35FD}">
+    <dataValidation type="list" sqref="M169" xr:uid="{C2722FD9-DD99-4A5A-9523-4D533A040F9D}">
       <formula1>=IF(L169&lt;&gt;"",INDIRECT(VLOOKUP(L169,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N169" xr:uid="{B65020CB-DE15-4FD7-A3D6-604CD30CB432}">
+    <dataValidation type="list" sqref="N169" xr:uid="{64BF2168-DAC1-440B-9CFF-17AF39D1A91D}">
       <formula1>=IF(M169&lt;&gt;"",INDIRECT(VLOOKUP(M169,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M170" xr:uid="{BC2E5BDC-AE60-4E05-8060-E5D26B71E401}">
+    <dataValidation type="list" sqref="M170" xr:uid="{DC69B10D-511F-4DA2-A869-54362FA8E505}">
       <formula1>=IF(L170&lt;&gt;"",INDIRECT(VLOOKUP(L170,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N170" xr:uid="{549F09B1-24B5-4813-BE23-7A080C48FDFB}">
+    <dataValidation type="list" sqref="N170" xr:uid="{CFCC37CB-664A-45C3-88A8-DCCA56C9D224}">
       <formula1>=IF(M170&lt;&gt;"",INDIRECT(VLOOKUP(M170,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M171" xr:uid="{E3BB6B41-6AFE-4641-B367-78A535BBB2CB}">
+    <dataValidation type="list" sqref="M171" xr:uid="{51E12B38-7C31-4C18-B81A-DACF996C1D68}">
       <formula1>=IF(L171&lt;&gt;"",INDIRECT(VLOOKUP(L171,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N171" xr:uid="{7D4D16A6-C1F0-4C6A-88A1-5AF281C92524}">
+    <dataValidation type="list" sqref="N171" xr:uid="{AAEA3381-87EB-439C-BC03-931850683700}">
       <formula1>=IF(M171&lt;&gt;"",INDIRECT(VLOOKUP(M171,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M172" xr:uid="{0D1CEF00-7530-4759-AC54-B491EE353D35}">
+    <dataValidation type="list" sqref="M172" xr:uid="{C1CC3B3F-CFBA-4548-BF32-7777650B498E}">
       <formula1>=IF(L172&lt;&gt;"",INDIRECT(VLOOKUP(L172,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N172" xr:uid="{CA42EB66-49E7-4A4E-A5D7-AD941B9F7AE9}">
+    <dataValidation type="list" sqref="N172" xr:uid="{91A93B46-0830-449E-A1C7-A677228DF48F}">
       <formula1>=IF(M172&lt;&gt;"",INDIRECT(VLOOKUP(M172,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M173" xr:uid="{306D8E4B-3721-4AA9-8681-6CF6FAAF3F79}">
+    <dataValidation type="list" sqref="M173" xr:uid="{44A8A50E-D235-4AED-A52A-139C53F0F942}">
       <formula1>=IF(L173&lt;&gt;"",INDIRECT(VLOOKUP(L173,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N173" xr:uid="{8480DBE9-9F32-493F-BDA1-C4509489677F}">
+    <dataValidation type="list" sqref="N173" xr:uid="{D5D7EEBE-D4F0-4B92-83D5-6DC8852C44CE}">
       <formula1>=IF(M173&lt;&gt;"",INDIRECT(VLOOKUP(M173,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M174" xr:uid="{98F5EE60-1578-4820-9FC3-B3D43B429F32}">
+    <dataValidation type="list" sqref="M174" xr:uid="{892D95E1-A008-419D-9775-4C99615E0F8E}">
       <formula1>=IF(L174&lt;&gt;"",INDIRECT(VLOOKUP(L174,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N174" xr:uid="{87F6E994-17D1-45A5-87B5-93028382E50E}">
+    <dataValidation type="list" sqref="N174" xr:uid="{C784948F-4E8A-42D7-AF7C-AD3C4D9E7891}">
       <formula1>=IF(M174&lt;&gt;"",INDIRECT(VLOOKUP(M174,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M175" xr:uid="{450CB5D7-1992-460D-BA4A-82A3E6EB1CE4}">
+    <dataValidation type="list" sqref="M175" xr:uid="{D5EB5A8E-1463-404E-A1A7-3DBA01B0D199}">
       <formula1>=IF(L175&lt;&gt;"",INDIRECT(VLOOKUP(L175,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N175" xr:uid="{4D68B8FA-CB16-4BC1-9E47-454501D49F6D}">
+    <dataValidation type="list" sqref="N175" xr:uid="{E2F24478-9E6E-471C-9CAB-8D94C38E15E0}">
       <formula1>=IF(M175&lt;&gt;"",INDIRECT(VLOOKUP(M175,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M176" xr:uid="{B9B48D0B-CBFF-43EF-8B72-D8AC66C53245}">
+    <dataValidation type="list" sqref="M176" xr:uid="{1CBB680A-201A-494C-B474-AF0AAC1AC077}">
       <formula1>=IF(L176&lt;&gt;"",INDIRECT(VLOOKUP(L176,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N176" xr:uid="{43DEEF02-7189-4F8B-8401-7BD6977CBBB5}">
+    <dataValidation type="list" sqref="N176" xr:uid="{341F23A5-E39F-4F9D-BDDD-FE371F93EE52}">
       <formula1>=IF(M176&lt;&gt;"",INDIRECT(VLOOKUP(M176,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M177" xr:uid="{C41669AA-B69F-4D3F-995F-40ACB7F3C3E1}">
+    <dataValidation type="list" sqref="M177" xr:uid="{F2E4896D-4079-4EF1-BB06-C4444DD12FA3}">
       <formula1>=IF(L177&lt;&gt;"",INDIRECT(VLOOKUP(L177,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N177" xr:uid="{606F342A-241B-4F2B-BF82-02090947AA24}">
+    <dataValidation type="list" sqref="N177" xr:uid="{E6471823-87ED-405D-9ECB-7E0AE3ECB3FF}">
       <formula1>=IF(M177&lt;&gt;"",INDIRECT(VLOOKUP(M177,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M178" xr:uid="{5BD78AE1-A873-4929-9E66-4E8641233895}">
+    <dataValidation type="list" sqref="M178" xr:uid="{65229F55-1D02-49C0-995C-11E7138079A2}">
       <formula1>=IF(L178&lt;&gt;"",INDIRECT(VLOOKUP(L178,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N178" xr:uid="{61B85A3F-7840-4E7D-B440-2C9583D9CB9C}">
+    <dataValidation type="list" sqref="N178" xr:uid="{05E798C6-E664-4D38-BCBC-B944187D9FDF}">
       <formula1>=IF(M178&lt;&gt;"",INDIRECT(VLOOKUP(M178,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M179" xr:uid="{F800D850-9FE2-4567-B61A-FF66F23E2BAD}">
+    <dataValidation type="list" sqref="M179" xr:uid="{B8231F9D-C46F-41B4-AE15-371E8B885582}">
       <formula1>=IF(L179&lt;&gt;"",INDIRECT(VLOOKUP(L179,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N179" xr:uid="{FC8E7B10-AEBD-4BDD-8CFE-12CAEC9A7CBB}">
+    <dataValidation type="list" sqref="N179" xr:uid="{2A636106-CF23-46A6-A7BA-866718421E48}">
       <formula1>=IF(M179&lt;&gt;"",INDIRECT(VLOOKUP(M179,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M180" xr:uid="{DBC14DC8-327A-489F-887C-F5381091B47A}">
+    <dataValidation type="list" sqref="M180" xr:uid="{A76ECAAA-0F4B-4103-861F-581F0218424B}">
       <formula1>=IF(L180&lt;&gt;"",INDIRECT(VLOOKUP(L180,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N180" xr:uid="{A10B8FBC-330F-48D0-A1BE-4B214E6CF011}">
+    <dataValidation type="list" sqref="N180" xr:uid="{A9A0ECEE-2341-47CA-A32E-7F16FA0B09B2}">
       <formula1>=IF(M180&lt;&gt;"",INDIRECT(VLOOKUP(M180,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M181" xr:uid="{8F2037ED-058F-49AA-A856-C687DEED2616}">
+    <dataValidation type="list" sqref="M181" xr:uid="{9BEF7036-240A-4643-BFA5-EDF3CF3E3EB0}">
       <formula1>=IF(L181&lt;&gt;"",INDIRECT(VLOOKUP(L181,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N181" xr:uid="{EF65A4B5-A790-43E4-B9D8-C39DAB8D5F99}">
+    <dataValidation type="list" sqref="N181" xr:uid="{14AC8FAD-EECF-4A5E-BD0D-2A628205B2B7}">
       <formula1>=IF(M181&lt;&gt;"",INDIRECT(VLOOKUP(M181,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M182" xr:uid="{A6D1B654-BE2F-43E1-8D0E-DA2F885FDAB5}">
+    <dataValidation type="list" sqref="M182" xr:uid="{6652A67C-1C1C-461F-BFF2-FFBA9F077C8D}">
       <formula1>=IF(L182&lt;&gt;"",INDIRECT(VLOOKUP(L182,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N182" xr:uid="{19D2961E-FA88-40C7-A875-57929C9C8C31}">
+    <dataValidation type="list" sqref="N182" xr:uid="{3DE28051-8235-48EC-9A5A-9D6E967D5FC3}">
       <formula1>=IF(M182&lt;&gt;"",INDIRECT(VLOOKUP(M182,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M183" xr:uid="{81971ED0-BC52-4EA9-A0E4-D1C8C9BB47AB}">
+    <dataValidation type="list" sqref="M183" xr:uid="{87CACB2C-B32C-4ABB-BDB3-D50297443B01}">
       <formula1>=IF(L183&lt;&gt;"",INDIRECT(VLOOKUP(L183,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N183" xr:uid="{A74A3893-C385-4232-ACAF-05D0DD691CA4}">
+    <dataValidation type="list" sqref="N183" xr:uid="{58FB2636-99EF-4574-8D6E-2C232665CC4B}">
       <formula1>=IF(M183&lt;&gt;"",INDIRECT(VLOOKUP(M183,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M184" xr:uid="{0A68281A-F3DE-4E50-A4D9-3E117E248520}">
+    <dataValidation type="list" sqref="M184" xr:uid="{E0D4A301-D2DF-4E3D-A66E-60A844015CD1}">
       <formula1>=IF(L184&lt;&gt;"",INDIRECT(VLOOKUP(L184,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N184" xr:uid="{26D12CFC-0EAF-40EB-A4E1-FCACE746DA26}">
+    <dataValidation type="list" sqref="N184" xr:uid="{FA13CA52-8353-4467-A799-722C2558ED7E}">
       <formula1>=IF(M184&lt;&gt;"",INDIRECT(VLOOKUP(M184,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M185" xr:uid="{D9E1D241-672E-4D85-89D4-084959B300D0}">
+    <dataValidation type="list" sqref="M185" xr:uid="{E41E3519-BA9B-4D33-89E8-8667DF2645A9}">
       <formula1>=IF(L185&lt;&gt;"",INDIRECT(VLOOKUP(L185,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N185" xr:uid="{CCF8E5C7-2E04-4EBE-A7F0-47F98D2467AB}">
+    <dataValidation type="list" sqref="N185" xr:uid="{4E949582-C56D-458C-AF16-0241B6D56189}">
       <formula1>=IF(M185&lt;&gt;"",INDIRECT(VLOOKUP(M185,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M186" xr:uid="{9FB3236B-C809-4B01-BD37-85CB12F17E03}">
+    <dataValidation type="list" sqref="M186" xr:uid="{20213086-5DEB-4B16-9C96-84C7FF52323F}">
       <formula1>=IF(L186&lt;&gt;"",INDIRECT(VLOOKUP(L186,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N186" xr:uid="{5E98B356-157D-41C5-AEED-52FA77F94EC6}">
+    <dataValidation type="list" sqref="N186" xr:uid="{B60F35DF-471C-44D1-B2AE-DC8F440F032A}">
       <formula1>=IF(M186&lt;&gt;"",INDIRECT(VLOOKUP(M186,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M187" xr:uid="{B9E93AEF-EDA3-416D-A806-0EF026495339}">
+    <dataValidation type="list" sqref="M187" xr:uid="{D1027CE3-D53B-47EA-83FC-EABC69E1F6CA}">
       <formula1>=IF(L187&lt;&gt;"",INDIRECT(VLOOKUP(L187,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N187" xr:uid="{D2C26762-2024-4A7C-946C-9784D2029841}">
+    <dataValidation type="list" sqref="N187" xr:uid="{A7B27CCD-AF77-456C-8B81-22DEAF5E53F7}">
       <formula1>=IF(M187&lt;&gt;"",INDIRECT(VLOOKUP(M187,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M188" xr:uid="{99F0B84C-BAE1-4985-80D1-E4FB70AC3117}">
+    <dataValidation type="list" sqref="M188" xr:uid="{1462A48F-E024-4FE7-A2E4-BF9880D0F6CF}">
       <formula1>=IF(L188&lt;&gt;"",INDIRECT(VLOOKUP(L188,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N188" xr:uid="{909AD48E-F20E-4762-A22A-E493CA983E3F}">
+    <dataValidation type="list" sqref="N188" xr:uid="{8F40C6D5-704E-430F-BC8E-85B38CE9B3D6}">
       <formula1>=IF(M188&lt;&gt;"",INDIRECT(VLOOKUP(M188,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M189" xr:uid="{27161A29-088D-48E0-AB3F-B2ABF70AAE48}">
+    <dataValidation type="list" sqref="M189" xr:uid="{9952E59E-5F4E-47CF-AFF5-525300B7DE9B}">
       <formula1>=IF(L189&lt;&gt;"",INDIRECT(VLOOKUP(L189,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N189" xr:uid="{8B4CDB3E-D9C6-48AB-BB13-6727DD08C587}">
+    <dataValidation type="list" sqref="N189" xr:uid="{6335C727-F730-46C5-B2A9-2A26EEF63EC2}">
       <formula1>=IF(M189&lt;&gt;"",INDIRECT(VLOOKUP(M189,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M190" xr:uid="{146EA143-1DEB-4E7B-A27D-AD5EED138E87}">
+    <dataValidation type="list" sqref="M190" xr:uid="{B6E8268E-0DE7-46C0-B508-B479F6E6F00A}">
       <formula1>=IF(L190&lt;&gt;"",INDIRECT(VLOOKUP(L190,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N190" xr:uid="{E404AAF5-5B72-460B-BCA7-364C0A9E2FBD}">
+    <dataValidation type="list" sqref="N190" xr:uid="{CF554800-098A-4DD6-A470-A9D3967C0AFC}">
       <formula1>=IF(M190&lt;&gt;"",INDIRECT(VLOOKUP(M190,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M191" xr:uid="{417FC1C3-9F8F-4836-BD10-0581C5610C63}">
+    <dataValidation type="list" sqref="M191" xr:uid="{72C701CB-305F-4859-A90A-7BB45F8FB5A0}">
       <formula1>=IF(L191&lt;&gt;"",INDIRECT(VLOOKUP(L191,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N191" xr:uid="{75FDE1A6-7E56-4BD2-945D-69F1BC06D192}">
+    <dataValidation type="list" sqref="N191" xr:uid="{7313C011-FFA9-49A0-A331-3CF8277B496B}">
       <formula1>=IF(M191&lt;&gt;"",INDIRECT(VLOOKUP(M191,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M192" xr:uid="{3DEF46D8-955C-4810-A1E8-23BA32A9080D}">
+    <dataValidation type="list" sqref="M192" xr:uid="{340AF5F1-4852-4A89-97CA-224F4818251B}">
       <formula1>=IF(L192&lt;&gt;"",INDIRECT(VLOOKUP(L192,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N192" xr:uid="{52142D20-8EF0-4B9E-AC11-6D139230FF96}">
+    <dataValidation type="list" sqref="N192" xr:uid="{74A7C048-14D3-4B80-8A5A-C11E940E218F}">
       <formula1>=IF(M192&lt;&gt;"",INDIRECT(VLOOKUP(M192,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M193" xr:uid="{DE79F334-95A1-40DB-9A19-9E8AEEFF0BBD}">
+    <dataValidation type="list" sqref="M193" xr:uid="{818B851F-0C58-4DA0-9156-8960AAFD504D}">
       <formula1>=IF(L193&lt;&gt;"",INDIRECT(VLOOKUP(L193,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N193" xr:uid="{52B8500C-81D9-4FCA-9E88-3DB4B4CD6AAA}">
+    <dataValidation type="list" sqref="N193" xr:uid="{81BFAB9F-CDFE-4002-B138-6C02B2E245C2}">
       <formula1>=IF(M193&lt;&gt;"",INDIRECT(VLOOKUP(M193,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M194" xr:uid="{800D9DD6-7DB9-4028-BD53-1590F503481B}">
+    <dataValidation type="list" sqref="M194" xr:uid="{A4FD009A-A387-4AAB-BCC1-870E218447B5}">
       <formula1>=IF(L194&lt;&gt;"",INDIRECT(VLOOKUP(L194,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N194" xr:uid="{8E81503A-BF0D-4A03-A91B-A95D8C98F96D}">
+    <dataValidation type="list" sqref="N194" xr:uid="{9EE105EE-3E07-4E8A-BF9F-11CC3C0B635D}">
       <formula1>=IF(M194&lt;&gt;"",INDIRECT(VLOOKUP(M194,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M195" xr:uid="{C037BBAB-96FF-4ACB-9271-ED270A845401}">
+    <dataValidation type="list" sqref="M195" xr:uid="{4CC1A6FD-E625-41A6-A76C-BBBB0FF29CCB}">
       <formula1>=IF(L195&lt;&gt;"",INDIRECT(VLOOKUP(L195,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N195" xr:uid="{2BF2E224-8CAC-4517-B076-6F46F45BEBE1}">
+    <dataValidation type="list" sqref="N195" xr:uid="{11075640-DD93-4ECA-B1E6-83A972A1BB00}">
       <formula1>=IF(M195&lt;&gt;"",INDIRECT(VLOOKUP(M195,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M196" xr:uid="{5858A343-99D4-4C1F-9C27-089BE4365B20}">
+    <dataValidation type="list" sqref="M196" xr:uid="{C74E183B-18A1-4A21-B077-7580C88345F2}">
       <formula1>=IF(L196&lt;&gt;"",INDIRECT(VLOOKUP(L196,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N196" xr:uid="{63E9AEFD-02DC-46E4-BEF4-F7986330C84C}">
+    <dataValidation type="list" sqref="N196" xr:uid="{0480752C-164A-4D50-9D93-56216C2783CD}">
       <formula1>=IF(M196&lt;&gt;"",INDIRECT(VLOOKUP(M196,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M197" xr:uid="{21E461A8-E7F1-4CF2-AD1B-7F3549406C13}">
+    <dataValidation type="list" sqref="M197" xr:uid="{4F63C19B-7B54-47AA-8012-3ABD1F922E33}">
       <formula1>=IF(L197&lt;&gt;"",INDIRECT(VLOOKUP(L197,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N197" xr:uid="{2D761588-6AE2-4982-B32B-97AF9A1ACB43}">
+    <dataValidation type="list" sqref="N197" xr:uid="{3E269673-55A3-4ABE-BB1C-03F3F8A4D81D}">
       <formula1>=IF(M197&lt;&gt;"",INDIRECT(VLOOKUP(M197,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M198" xr:uid="{1EB6CC30-DFA7-4D79-82BB-639B4AB311EF}">
+    <dataValidation type="list" sqref="M198" xr:uid="{3635E46E-E044-45ED-B6C2-6B8D975CADD9}">
       <formula1>=IF(L198&lt;&gt;"",INDIRECT(VLOOKUP(L198,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N198" xr:uid="{D7D30661-2A6D-4E16-9774-A6336F2467E5}">
+    <dataValidation type="list" sqref="N198" xr:uid="{E3276C49-AE2D-4B8A-9246-6B5C9B934D15}">
       <formula1>=IF(M198&lt;&gt;"",INDIRECT(VLOOKUP(M198,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M199" xr:uid="{C3F2089F-A461-44B0-A4C9-176287690E30}">
+    <dataValidation type="list" sqref="M199" xr:uid="{E5D9A7D7-6F21-4484-ADE3-63053F76AFA9}">
       <formula1>=IF(L199&lt;&gt;"",INDIRECT(VLOOKUP(L199,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N199" xr:uid="{5708EE16-76E9-4BFB-B625-54FE08005578}">
+    <dataValidation type="list" sqref="N199" xr:uid="{19D6FB13-5EDC-42D2-8E48-0C3F8470AB62}">
       <formula1>=IF(M199&lt;&gt;"",INDIRECT(VLOOKUP(M199,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M200" xr:uid="{403EA37C-47E8-4826-AA96-2BD7A1FCD512}">
+    <dataValidation type="list" sqref="M200" xr:uid="{CA415B7B-E435-4359-9D09-678DC1A94717}">
       <formula1>=IF(L200&lt;&gt;"",INDIRECT(VLOOKUP(L200,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N200" xr:uid="{14027761-F86C-4918-AE5C-552C756722CC}">
+    <dataValidation type="list" sqref="N200" xr:uid="{B72DD11F-801E-428A-8267-41CFEA7ED1E9}">
       <formula1>=IF(M200&lt;&gt;"",INDIRECT(VLOOKUP(M200,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M201" xr:uid="{88BAD81C-5F0E-4530-873D-611AFB8FBC85}">
+    <dataValidation type="list" sqref="M201" xr:uid="{8EC4EB0D-B134-4E5B-B940-DB2A417E3AB8}">
       <formula1>=IF(L201&lt;&gt;"",INDIRECT(VLOOKUP(L201,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N201" xr:uid="{EC101775-6854-4384-A6A3-43F8F93C0DCC}">
+    <dataValidation type="list" sqref="N201" xr:uid="{04AD2964-5B13-48C9-A932-56D7946EC642}">
       <formula1>=IF(M201&lt;&gt;"",INDIRECT(VLOOKUP(M201,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M202" xr:uid="{917353C1-69E3-485C-A1EC-E8D21F3D8C34}">
+    <dataValidation type="list" sqref="M202" xr:uid="{A03691DD-79FD-401B-954F-A83C593225EE}">
       <formula1>=IF(L202&lt;&gt;"",INDIRECT(VLOOKUP(L202,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N202" xr:uid="{B2995DB4-775F-4BB3-BB59-003839CE7893}">
+    <dataValidation type="list" sqref="N202" xr:uid="{669A2EF0-3CC2-4B19-8B5D-68A52540DCD1}">
       <formula1>=IF(M202&lt;&gt;"",INDIRECT(VLOOKUP(M202,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M203" xr:uid="{803D76A9-1466-4239-BCEA-C76B54064097}">
+    <dataValidation type="list" sqref="M203" xr:uid="{9AE2AAC0-5290-497C-9264-2CEC1378C657}">
       <formula1>=IF(L203&lt;&gt;"",INDIRECT(VLOOKUP(L203,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N203" xr:uid="{B07FDB09-BB27-4C12-9C24-BC6DF751417A}">
+    <dataValidation type="list" sqref="N203" xr:uid="{9018035B-F9C0-43BD-8B10-5D960DFB0FF0}">
       <formula1>=IF(M203&lt;&gt;"",INDIRECT(VLOOKUP(M203,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M204" xr:uid="{85A62E43-DE87-409A-9D8D-2FD337DF54A7}">
+    <dataValidation type="list" sqref="M204" xr:uid="{A3034A1C-B8CD-4A00-9D4F-043E2A115B4B}">
       <formula1>=IF(L204&lt;&gt;"",INDIRECT(VLOOKUP(L204,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N204" xr:uid="{149A304F-7D0F-44FF-9FD6-202CD706994A}">
+    <dataValidation type="list" sqref="N204" xr:uid="{36D7B107-3901-4FB1-83DE-4B7C04224BB9}">
       <formula1>=IF(M204&lt;&gt;"",INDIRECT(VLOOKUP(M204,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M205" xr:uid="{B5035752-76DE-4FFD-A53E-60F8A038D4F7}">
+    <dataValidation type="list" sqref="M205" xr:uid="{AF9F6D25-58EE-40DB-BF3E-57CFDE3D33E5}">
       <formula1>=IF(L205&lt;&gt;"",INDIRECT(VLOOKUP(L205,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N205" xr:uid="{104D7DBC-BDB1-47D2-A6A4-C28D4CF8D94C}">
+    <dataValidation type="list" sqref="N205" xr:uid="{A29E48A2-7A55-4560-8DCC-CFD32D6AE1F2}">
       <formula1>=IF(M205&lt;&gt;"",INDIRECT(VLOOKUP(M205,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M206" xr:uid="{EF938D24-DC41-438D-B571-9F8DB90A9A01}">
+    <dataValidation type="list" sqref="M206" xr:uid="{731DA6C1-D2DD-43C5-BB4B-65FF9EF0B329}">
       <formula1>=IF(L206&lt;&gt;"",INDIRECT(VLOOKUP(L206,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N206" xr:uid="{D3939325-F8E4-43AC-8FCC-4E93F98800D0}">
+    <dataValidation type="list" sqref="N206" xr:uid="{EEC833E2-4340-4EA9-AF74-2B0C78349494}">
       <formula1>=IF(M206&lt;&gt;"",INDIRECT(VLOOKUP(M206,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M207" xr:uid="{6972F59E-831D-4C58-B02D-8ADF1F9EE3A4}">
+    <dataValidation type="list" sqref="M207" xr:uid="{97964A79-6AED-4629-836C-DC81402E25FE}">
       <formula1>=IF(L207&lt;&gt;"",INDIRECT(VLOOKUP(L207,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N207" xr:uid="{79A47371-C4BC-4D4E-9BD7-817D4E51B8B9}">
+    <dataValidation type="list" sqref="N207" xr:uid="{0DD46BB5-52D9-4E3A-89B6-72D8F9548607}">
       <formula1>=IF(M207&lt;&gt;"",INDIRECT(VLOOKUP(M207,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M208" xr:uid="{CC38ABCB-8027-45DB-B2DD-3D12E3E71813}">
+    <dataValidation type="list" sqref="M208" xr:uid="{766ABEE8-02AE-485F-B3AE-1C91819FF294}">
       <formula1>=IF(L208&lt;&gt;"",INDIRECT(VLOOKUP(L208,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N208" xr:uid="{CE5002BE-3DF7-4F0B-B5BB-DF5292F140F6}">
+    <dataValidation type="list" sqref="N208" xr:uid="{B6889AA2-A449-42B4-AD2E-F97180278A04}">
       <formula1>=IF(M208&lt;&gt;"",INDIRECT(VLOOKUP(M208,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M209" xr:uid="{E0B15E7A-C7A2-4CEA-9EF0-AA7E7980C996}">
+    <dataValidation type="list" sqref="M209" xr:uid="{0F22834F-A5FC-4064-9867-7A36D9D95FA1}">
       <formula1>=IF(L209&lt;&gt;"",INDIRECT(VLOOKUP(L209,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N209" xr:uid="{A7FCDE12-B02A-4053-B77C-4560CC9961D2}">
+    <dataValidation type="list" sqref="N209" xr:uid="{A69833E8-FDC7-40A0-9F36-6ECC4439A9FB}">
       <formula1>=IF(M209&lt;&gt;"",INDIRECT(VLOOKUP(M209,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M210" xr:uid="{7B4D03B5-A01C-4B8C-B163-34CBD66873DC}">
+    <dataValidation type="list" sqref="M210" xr:uid="{552D5307-ABEB-4088-9ACC-BDC8ECE186BF}">
       <formula1>=IF(L210&lt;&gt;"",INDIRECT(VLOOKUP(L210,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N210" xr:uid="{754C7703-6E4E-4023-917A-54BEFFF98075}">
+    <dataValidation type="list" sqref="N210" xr:uid="{A41CF7F9-793C-48DA-B068-D33C49616BC4}">
       <formula1>=IF(M210&lt;&gt;"",INDIRECT(VLOOKUP(M210,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M211" xr:uid="{E8BE28A3-81AD-4C7A-86CC-078B4A9135A7}">
+    <dataValidation type="list" sqref="M211" xr:uid="{3480B751-C490-4ADB-8333-EC93AA677600}">
       <formula1>=IF(L211&lt;&gt;"",INDIRECT(VLOOKUP(L211,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N211" xr:uid="{9B844270-D3D9-4C6C-9658-C60CD895198B}">
+    <dataValidation type="list" sqref="N211" xr:uid="{A529DBFA-99FD-40CA-93F4-9E15CFEF6770}">
       <formula1>=IF(M211&lt;&gt;"",INDIRECT(VLOOKUP(M211,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M212" xr:uid="{AF66DE12-72CD-40DC-835D-8AF0473AE3CD}">
+    <dataValidation type="list" sqref="M212" xr:uid="{745B1D13-2E24-430F-94F5-DC5EDE141701}">
       <formula1>=IF(L212&lt;&gt;"",INDIRECT(VLOOKUP(L212,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N212" xr:uid="{1161249B-072A-4E95-9135-D695D69282FC}">
+    <dataValidation type="list" sqref="N212" xr:uid="{62FD921F-F7A7-444E-93AB-C96DBC08019E}">
       <formula1>=IF(M212&lt;&gt;"",INDIRECT(VLOOKUP(M212,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M213" xr:uid="{1437D0B7-0CD6-4E73-8C57-96081BC97FC7}">
+    <dataValidation type="list" sqref="M213" xr:uid="{F837B8B0-D25D-481D-AFA3-88D66FC60E92}">
       <formula1>=IF(L213&lt;&gt;"",INDIRECT(VLOOKUP(L213,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N213" xr:uid="{2DD2A4CF-A485-4107-BCD4-4DEC98822939}">
+    <dataValidation type="list" sqref="N213" xr:uid="{157AB12B-B13D-4452-A215-F11EBC8EBB6C}">
       <formula1>=IF(M213&lt;&gt;"",INDIRECT(VLOOKUP(M213,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M214" xr:uid="{00B0A419-A09D-4893-A766-757C354B5381}">
+    <dataValidation type="list" sqref="M214" xr:uid="{D1CA6126-C81F-4285-882B-F7BB06B7A010}">
       <formula1>=IF(L214&lt;&gt;"",INDIRECT(VLOOKUP(L214,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N214" xr:uid="{24B9976C-183F-46FF-84F6-4698E97B61CA}">
+    <dataValidation type="list" sqref="N214" xr:uid="{7D2F1E92-24C4-4CB0-816F-E043EA09933E}">
       <formula1>=IF(M214&lt;&gt;"",INDIRECT(VLOOKUP(M214,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M215" xr:uid="{B1F7F1E7-6FF5-41F7-A2FF-A0CE809B6BF9}">
+    <dataValidation type="list" sqref="M215" xr:uid="{839C0B29-B88B-4780-996A-A485F84CA83D}">
       <formula1>=IF(L215&lt;&gt;"",INDIRECT(VLOOKUP(L215,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N215" xr:uid="{AC936413-92FE-4611-B51D-C6D9DEE2D874}">
+    <dataValidation type="list" sqref="N215" xr:uid="{4EA58B2F-6A7E-40DA-812D-3613B63F0F68}">
       <formula1>=IF(M215&lt;&gt;"",INDIRECT(VLOOKUP(M215,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M216" xr:uid="{E03BBC65-5F75-4E8A-9861-184B97B96AB4}">
+    <dataValidation type="list" sqref="M216" xr:uid="{541DFB41-9E82-4A06-BEBD-864BBC34AC5A}">
       <formula1>=IF(L216&lt;&gt;"",INDIRECT(VLOOKUP(L216,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N216" xr:uid="{5A6B0B35-5AD9-4F7D-AFE7-007398D6E192}">
+    <dataValidation type="list" sqref="N216" xr:uid="{E0A50043-D27D-48E7-BF4A-D01728D46988}">
       <formula1>=IF(M216&lt;&gt;"",INDIRECT(VLOOKUP(M216,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M217" xr:uid="{06434E2B-83C5-4A1E-8AEA-0913BD1D57AF}">
+    <dataValidation type="list" sqref="M217" xr:uid="{07C86ADA-75FC-4989-A06A-529D26823612}">
       <formula1>=IF(L217&lt;&gt;"",INDIRECT(VLOOKUP(L217,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N217" xr:uid="{B0D06FA9-F95D-44EE-B4A3-932867CC9BC7}">
+    <dataValidation type="list" sqref="N217" xr:uid="{49DC4650-AEAC-4010-8B48-F97AAF506691}">
       <formula1>=IF(M217&lt;&gt;"",INDIRECT(VLOOKUP(M217,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M218" xr:uid="{F56F5A31-86C5-4A68-ADFC-70063C98CED2}">
+    <dataValidation type="list" sqref="M218" xr:uid="{7A3F5976-3756-4C4E-B051-1A9630004251}">
       <formula1>=IF(L218&lt;&gt;"",INDIRECT(VLOOKUP(L218,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N218" xr:uid="{A8C400D5-0F97-480F-B052-2654BD42634D}">
+    <dataValidation type="list" sqref="N218" xr:uid="{CE9DEDFC-3AAD-4085-8E4D-285293314CEC}">
       <formula1>=IF(M218&lt;&gt;"",INDIRECT(VLOOKUP(M218,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M219" xr:uid="{A0CF2CE0-76AD-4FF7-9A2D-D05272C6BED1}">
+    <dataValidation type="list" sqref="M219" xr:uid="{6DCD91F1-0DD9-4D2A-ADFD-20805089A72A}">
       <formula1>=IF(L219&lt;&gt;"",INDIRECT(VLOOKUP(L219,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N219" xr:uid="{2995EE15-0B94-4DE2-A5BC-69F91CB9CD51}">
+    <dataValidation type="list" sqref="N219" xr:uid="{930EE925-D3EA-4AE8-BC74-2F8053D2AA27}">
       <formula1>=IF(M219&lt;&gt;"",INDIRECT(VLOOKUP(M219,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M220" xr:uid="{7DEBE48A-767E-466D-90DD-6A5D765787F9}">
+    <dataValidation type="list" sqref="M220" xr:uid="{77B92A5D-CE19-4A6F-8512-484CDCE596AD}">
       <formula1>=IF(L220&lt;&gt;"",INDIRECT(VLOOKUP(L220,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N220" xr:uid="{249DB576-EA95-42F5-AF0C-EBAC94D862DC}">
+    <dataValidation type="list" sqref="N220" xr:uid="{665C479C-F9EF-44F7-8E03-DD815F9453C3}">
       <formula1>=IF(M220&lt;&gt;"",INDIRECT(VLOOKUP(M220,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M221" xr:uid="{73243169-4FE2-4637-AFAA-C5D7CAA2446F}">
+    <dataValidation type="list" sqref="M221" xr:uid="{5E0F8E75-0BDA-4C05-94E3-2483952C8924}">
       <formula1>=IF(L221&lt;&gt;"",INDIRECT(VLOOKUP(L221,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N221" xr:uid="{BF3E8099-859C-4E15-9731-B08543523A26}">
+    <dataValidation type="list" sqref="N221" xr:uid="{ED524CC0-FDC4-49F5-BE46-9DF24014AF30}">
       <formula1>=IF(M221&lt;&gt;"",INDIRECT(VLOOKUP(M221,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M222" xr:uid="{71056C02-A1B4-4406-81D3-2D69002BCF74}">
+    <dataValidation type="list" sqref="M222" xr:uid="{479D51FC-AA15-4EE9-A0C7-D054C4002E78}">
       <formula1>=IF(L222&lt;&gt;"",INDIRECT(VLOOKUP(L222,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N222" xr:uid="{B3658B75-F449-4A38-8466-F8AE3D2C2790}">
+    <dataValidation type="list" sqref="N222" xr:uid="{581163D6-6605-485E-A8A9-E2843FC4FFE2}">
       <formula1>=IF(M222&lt;&gt;"",INDIRECT(VLOOKUP(M222,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M223" xr:uid="{A6DAE933-B716-4DB1-ACE7-50F45A79829E}">
+    <dataValidation type="list" sqref="M223" xr:uid="{C5460A84-DC30-40AD-A030-9480BEED0350}">
       <formula1>=IF(L223&lt;&gt;"",INDIRECT(VLOOKUP(L223,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N223" xr:uid="{89756D2A-EDE5-4889-9FB7-74FE026ECA82}">
+    <dataValidation type="list" sqref="N223" xr:uid="{97FB1832-B012-499F-946F-8F3CE42F7502}">
       <formula1>=IF(M223&lt;&gt;"",INDIRECT(VLOOKUP(M223,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M224" xr:uid="{F0F02554-52C2-4EB5-92F2-7E5B45027BE9}">
+    <dataValidation type="list" sqref="M224" xr:uid="{C6CD0E0D-65F6-4075-ABDF-BC2C3CCB55FA}">
       <formula1>=IF(L224&lt;&gt;"",INDIRECT(VLOOKUP(L224,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N224" xr:uid="{A74B83C2-BEC0-4A4D-8228-1ABE359E7C62}">
+    <dataValidation type="list" sqref="N224" xr:uid="{D4B7434B-A9D3-44E1-9030-599581A14EE3}">
       <formula1>=IF(M224&lt;&gt;"",INDIRECT(VLOOKUP(M224,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M225" xr:uid="{B6445E16-3CC6-48D4-BA1C-9369382E7160}">
+    <dataValidation type="list" sqref="M225" xr:uid="{F1FDF15C-CB33-4EA9-A2A5-339DDC42E0B2}">
       <formula1>=IF(L225&lt;&gt;"",INDIRECT(VLOOKUP(L225,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N225" xr:uid="{5C36CF4E-A56D-46A5-9B93-1FE85B1F22D2}">
+    <dataValidation type="list" sqref="N225" xr:uid="{7990CBAC-4AAC-41FB-9391-056945A7626B}">
       <formula1>=IF(M225&lt;&gt;"",INDIRECT(VLOOKUP(M225,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M226" xr:uid="{284787FB-FCD6-40B2-A08E-83CE7740E600}">
+    <dataValidation type="list" sqref="M226" xr:uid="{86135229-3418-435C-BD03-3C1343CC4AAD}">
       <formula1>=IF(L226&lt;&gt;"",INDIRECT(VLOOKUP(L226,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N226" xr:uid="{34A6AE9A-FD3E-45ED-80E2-AED9D06F1F7F}">
+    <dataValidation type="list" sqref="N226" xr:uid="{3394141E-5135-42F8-BCE5-D95AA75DA53C}">
       <formula1>=IF(M226&lt;&gt;"",INDIRECT(VLOOKUP(M226,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M227" xr:uid="{3C291D83-ABD3-4582-ACED-99A7BA613D0A}">
+    <dataValidation type="list" sqref="M227" xr:uid="{391BB86A-44EF-477E-9F2D-42D0BA2A1CD9}">
       <formula1>=IF(L227&lt;&gt;"",INDIRECT(VLOOKUP(L227,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N227" xr:uid="{D0A1614D-27B3-4C07-BE18-7338F60D823D}">
+    <dataValidation type="list" sqref="N227" xr:uid="{3B5C74E5-6AAA-40FC-9F58-4C0CAD9B1965}">
       <formula1>=IF(M227&lt;&gt;"",INDIRECT(VLOOKUP(M227,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M228" xr:uid="{EFD6A9D4-73E8-4470-8050-A1640F350B1D}">
+    <dataValidation type="list" sqref="M228" xr:uid="{8C8E2B95-7D7C-4A9F-91CC-FB3969F0D42F}">
       <formula1>=IF(L228&lt;&gt;"",INDIRECT(VLOOKUP(L228,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N228" xr:uid="{19362204-3C3C-4637-A0D9-F6B45323FF1D}">
+    <dataValidation type="list" sqref="N228" xr:uid="{901A2C87-75A4-44F4-A94F-C9356950B698}">
       <formula1>=IF(M228&lt;&gt;"",INDIRECT(VLOOKUP(M228,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M229" xr:uid="{391B7C97-12C3-4DEF-B5CA-4D8C66A1DFD7}">
+    <dataValidation type="list" sqref="M229" xr:uid="{1CCE4949-D06B-4439-B028-F219001E01FA}">
       <formula1>=IF(L229&lt;&gt;"",INDIRECT(VLOOKUP(L229,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N229" xr:uid="{EF5FE9DD-82B7-487F-BE45-A94160B91373}">
+    <dataValidation type="list" sqref="N229" xr:uid="{2FC49E9D-2322-4C80-B280-4FC08C17DBCC}">
       <formula1>=IF(M229&lt;&gt;"",INDIRECT(VLOOKUP(M229,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M230" xr:uid="{5E1528EB-1DA1-4D86-B2D5-3D819F90EE66}">
+    <dataValidation type="list" sqref="M230" xr:uid="{E0DA57F8-3907-4908-9675-D32F2A1FF8E0}">
       <formula1>=IF(L230&lt;&gt;"",INDIRECT(VLOOKUP(L230,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N230" xr:uid="{99DFFFC4-F849-42FC-A070-EE746C591899}">
+    <dataValidation type="list" sqref="N230" xr:uid="{3153D486-BD88-4D80-9A8F-3CE0457B7CA7}">
       <formula1>=IF(M230&lt;&gt;"",INDIRECT(VLOOKUP(M230,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M231" xr:uid="{28703C12-9F0B-4898-A4F1-72E6420999F1}">
+    <dataValidation type="list" sqref="M231" xr:uid="{3120026D-E719-4F22-AD50-B376E36F7834}">
       <formula1>=IF(L231&lt;&gt;"",INDIRECT(VLOOKUP(L231,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N231" xr:uid="{859C05C8-B4AA-44CA-8958-7E644A8164BF}">
+    <dataValidation type="list" sqref="N231" xr:uid="{764A0B50-1826-49EB-BB91-52A772BAEEF0}">
       <formula1>=IF(M231&lt;&gt;"",INDIRECT(VLOOKUP(M231,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M232" xr:uid="{C60ECB6A-44ED-49EC-8231-6498D9B355BA}">
+    <dataValidation type="list" sqref="M232" xr:uid="{90280712-37DD-4515-9C16-71C21E21EE49}">
       <formula1>=IF(L232&lt;&gt;"",INDIRECT(VLOOKUP(L232,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N232" xr:uid="{663B6891-A733-4E8E-87CC-A7D785F59872}">
+    <dataValidation type="list" sqref="N232" xr:uid="{554CD51A-3748-432D-9180-19D0BEDC70CE}">
       <formula1>=IF(M232&lt;&gt;"",INDIRECT(VLOOKUP(M232,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M233" xr:uid="{345B5DCC-9B28-4E09-9583-DAB4A9D4AFB0}">
+    <dataValidation type="list" sqref="M233" xr:uid="{18F094B2-A208-4D05-BAE4-973B96EC0AB8}">
       <formula1>=IF(L233&lt;&gt;"",INDIRECT(VLOOKUP(L233,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N233" xr:uid="{93C1121E-42F2-4092-8CDE-CA8F9E3E7CDF}">
+    <dataValidation type="list" sqref="N233" xr:uid="{1CD3F1CB-87DE-47A5-AA0D-41E1089C1212}">
       <formula1>=IF(M233&lt;&gt;"",INDIRECT(VLOOKUP(M233,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M234" xr:uid="{D1FE03E1-8C10-48B8-A0E9-F243BCBA1348}">
+    <dataValidation type="list" sqref="M234" xr:uid="{F1479239-EB13-4210-91B2-2F4F4EAC64E3}">
       <formula1>=IF(L234&lt;&gt;"",INDIRECT(VLOOKUP(L234,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N234" xr:uid="{580B7BDB-2912-4167-B2BA-68A37E353D1F}">
+    <dataValidation type="list" sqref="N234" xr:uid="{85C5C184-727C-4B94-9BC3-59CF7DB730E2}">
       <formula1>=IF(M234&lt;&gt;"",INDIRECT(VLOOKUP(M234,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M235" xr:uid="{EDDC292D-9AFC-4B12-96D4-6FDBD1D07ABC}">
+    <dataValidation type="list" sqref="M235" xr:uid="{CB4C9E43-5E30-4BE4-83E3-F3E7D1908017}">
       <formula1>=IF(L235&lt;&gt;"",INDIRECT(VLOOKUP(L235,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N235" xr:uid="{FB713D1B-0CC1-4F74-8F11-57D3A60AB52C}">
+    <dataValidation type="list" sqref="N235" xr:uid="{B60E8DF1-C987-4061-90D1-382DEA93FE1E}">
       <formula1>=IF(M235&lt;&gt;"",INDIRECT(VLOOKUP(M235,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M236" xr:uid="{DDF84068-1DF1-4E02-A1AA-72F4228AE33F}">
+    <dataValidation type="list" sqref="M236" xr:uid="{D8ACC17E-F51D-40D4-AE78-4680CA408D22}">
       <formula1>=IF(L236&lt;&gt;"",INDIRECT(VLOOKUP(L236,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N236" xr:uid="{4634408E-1C4A-4684-9AF5-FCDCE2B24497}">
+    <dataValidation type="list" sqref="N236" xr:uid="{89187CFC-58B5-4171-BF41-3A6D2C8B3BF5}">
       <formula1>=IF(M236&lt;&gt;"",INDIRECT(VLOOKUP(M236,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M237" xr:uid="{8B13B151-4F4A-4A0D-A3B2-44D0C77F547C}">
+    <dataValidation type="list" sqref="M237" xr:uid="{FEB1F90A-88D3-48DB-876A-E4B8B0E57DDC}">
       <formula1>=IF(L237&lt;&gt;"",INDIRECT(VLOOKUP(L237,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N237" xr:uid="{87FECF3E-2C24-4E5F-A41C-407ECBE16B6F}">
+    <dataValidation type="list" sqref="N237" xr:uid="{64A229CB-EDEE-4F1E-B1FA-29C5CC744589}">
       <formula1>=IF(M237&lt;&gt;"",INDIRECT(VLOOKUP(M237,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M238" xr:uid="{FCA6D049-84B7-4CFB-95C3-8D1678044154}">
+    <dataValidation type="list" sqref="M238" xr:uid="{C957F322-0CD4-4D32-93A9-0514788ACCC8}">
       <formula1>=IF(L238&lt;&gt;"",INDIRECT(VLOOKUP(L238,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N238" xr:uid="{0FDE5BAC-4585-4331-8300-D87BF975C0C4}">
+    <dataValidation type="list" sqref="N238" xr:uid="{294EAA26-1B02-4396-91A7-D0CB3D2DE60A}">
       <formula1>=IF(M238&lt;&gt;"",INDIRECT(VLOOKUP(M238,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M239" xr:uid="{EE8E2AFB-9FF0-4030-AA64-89068EB6131C}">
+    <dataValidation type="list" sqref="M239" xr:uid="{C1EA698C-BDC1-4AF2-B911-153BEFD986CA}">
       <formula1>=IF(L239&lt;&gt;"",INDIRECT(VLOOKUP(L239,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N239" xr:uid="{CE53DC6A-7384-43AD-AA70-3ABB30F4230A}">
+    <dataValidation type="list" sqref="N239" xr:uid="{CC1A4BED-106F-4DE9-9B04-E29710429A46}">
       <formula1>=IF(M239&lt;&gt;"",INDIRECT(VLOOKUP(M239,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M240" xr:uid="{2C2EB470-E097-4496-97C6-CE10344675F5}">
+    <dataValidation type="list" sqref="M240" xr:uid="{93A0C37A-C792-4DE6-82FD-B3E1AE2E7DE6}">
       <formula1>=IF(L240&lt;&gt;"",INDIRECT(VLOOKUP(L240,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N240" xr:uid="{AB4737F5-4E20-44E3-81B4-EC942198A754}">
+    <dataValidation type="list" sqref="N240" xr:uid="{82628ACC-5C7A-4684-AEF7-1E9DD4830E7F}">
       <formula1>=IF(M240&lt;&gt;"",INDIRECT(VLOOKUP(M240,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M241" xr:uid="{CCD4FCB2-E983-4692-AD0A-2949694F7B35}">
+    <dataValidation type="list" sqref="M241" xr:uid="{40C8F5AC-4916-4D66-B8EF-A60BAA7BE949}">
       <formula1>=IF(L241&lt;&gt;"",INDIRECT(VLOOKUP(L241,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N241" xr:uid="{FC3379D8-2CD4-42EA-A570-FA6E62156E6B}">
+    <dataValidation type="list" sqref="N241" xr:uid="{17A2608C-291C-48C2-931E-C9D52899AFFE}">
       <formula1>=IF(M241&lt;&gt;"",INDIRECT(VLOOKUP(M241,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M242" xr:uid="{D347AC00-90E5-4512-A525-642344AE007C}">
+    <dataValidation type="list" sqref="M242" xr:uid="{75885200-F01E-4E1E-A6E2-84A1320BE3D5}">
       <formula1>=IF(L242&lt;&gt;"",INDIRECT(VLOOKUP(L242,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N242" xr:uid="{80F3B8F3-A401-4FCB-99B3-18FFEC27C36C}">
+    <dataValidation type="list" sqref="N242" xr:uid="{718A7375-B7FC-4B47-A63B-800CA2378317}">
       <formula1>=IF(M242&lt;&gt;"",INDIRECT(VLOOKUP(M242,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M243" xr:uid="{236390CF-E7BE-4437-BA2F-F28321AEDD4E}">
+    <dataValidation type="list" sqref="M243" xr:uid="{A89CD6E8-9BEA-4849-8A9F-8E65AA2235A0}">
       <formula1>=IF(L243&lt;&gt;"",INDIRECT(VLOOKUP(L243,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N243" xr:uid="{E568658D-E409-4284-BEB2-F3586BB544BA}">
+    <dataValidation type="list" sqref="N243" xr:uid="{F6672E3E-5C36-4596-AB7F-70378412C31E}">
       <formula1>=IF(M243&lt;&gt;"",INDIRECT(VLOOKUP(M243,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M244" xr:uid="{1F927829-59F9-4CBE-9029-483200DF34E1}">
+    <dataValidation type="list" sqref="M244" xr:uid="{90B94F3E-2F89-4239-9C5D-ED0779EEBC3E}">
       <formula1>=IF(L244&lt;&gt;"",INDIRECT(VLOOKUP(L244,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N244" xr:uid="{DC3B72DC-3456-4414-A588-E9B461FD7977}">
+    <dataValidation type="list" sqref="N244" xr:uid="{BAF8F234-F846-4373-95D5-13EEAD3FC986}">
       <formula1>=IF(M244&lt;&gt;"",INDIRECT(VLOOKUP(M244,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M245" xr:uid="{97D37402-134F-4305-8D00-6397E2AB0EB9}">
+    <dataValidation type="list" sqref="M245" xr:uid="{B86CF448-216E-4284-8292-6C73760790C4}">
       <formula1>=IF(L245&lt;&gt;"",INDIRECT(VLOOKUP(L245,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N245" xr:uid="{17E6208E-1923-4D3C-A0D7-1DB76A0FE1EE}">
+    <dataValidation type="list" sqref="N245" xr:uid="{2DFE43A5-050A-49FF-8685-F4FC92370118}">
       <formula1>=IF(M245&lt;&gt;"",INDIRECT(VLOOKUP(M245,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M246" xr:uid="{4B71073F-09EF-4CDC-9203-59DF173E197A}">
+    <dataValidation type="list" sqref="M246" xr:uid="{4A5E4E1B-E8EC-4326-85BD-06A6CF346F01}">
       <formula1>=IF(L246&lt;&gt;"",INDIRECT(VLOOKUP(L246,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N246" xr:uid="{CC65D99A-5525-49D6-B416-ED037CA3E292}">
+    <dataValidation type="list" sqref="N246" xr:uid="{8CCAC228-07CF-4B75-9BAB-F1ED742D61DA}">
       <formula1>=IF(M246&lt;&gt;"",INDIRECT(VLOOKUP(M246,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M247" xr:uid="{0D8A9C0A-D43D-4008-92EC-B9D5FAC59922}">
+    <dataValidation type="list" sqref="M247" xr:uid="{FE4B4697-278C-49FD-88E5-5A1920601510}">
       <formula1>=IF(L247&lt;&gt;"",INDIRECT(VLOOKUP(L247,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N247" xr:uid="{8459AC30-2B7D-4112-8155-F59D8936FB32}">
+    <dataValidation type="list" sqref="N247" xr:uid="{B878E4A4-2712-40D3-B65D-E8CB77EBCA33}">
       <formula1>=IF(M247&lt;&gt;"",INDIRECT(VLOOKUP(M247,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M248" xr:uid="{D43BBE92-624F-4D85-82CA-76FAAE288703}">
+    <dataValidation type="list" sqref="M248" xr:uid="{FC756187-1D5E-4D8C-86E6-57640F4665F1}">
       <formula1>=IF(L248&lt;&gt;"",INDIRECT(VLOOKUP(L248,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N248" xr:uid="{D70FBDE6-C226-408E-9A6B-CE23CFB203AB}">
+    <dataValidation type="list" sqref="N248" xr:uid="{1653B0EA-95F3-4FD5-AF1A-055F41A90C31}">
       <formula1>=IF(M248&lt;&gt;"",INDIRECT(VLOOKUP(M248,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M249" xr:uid="{D973B3B9-552B-456D-884B-9B065AE5D148}">
+    <dataValidation type="list" sqref="M249" xr:uid="{A97F21EA-D109-471A-91C9-51504CCD674C}">
       <formula1>=IF(L249&lt;&gt;"",INDIRECT(VLOOKUP(L249,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N249" xr:uid="{876FA18C-FB36-48AA-AB9E-6E8EEE8DC8A6}">
+    <dataValidation type="list" sqref="N249" xr:uid="{8B2FFF78-19BF-47A1-A45C-FF0425873FF9}">
       <formula1>=IF(M249&lt;&gt;"",INDIRECT(VLOOKUP(M249,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M250" xr:uid="{053FDEDD-A150-4E09-B0B1-7094B136685E}">
+    <dataValidation type="list" sqref="M250" xr:uid="{A0D2B9E9-0C27-4C8A-99EE-8BE7B9C85D1B}">
       <formula1>=IF(L250&lt;&gt;"",INDIRECT(VLOOKUP(L250,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N250" xr:uid="{57DB04F2-7AD1-4ABC-A6D7-8B0C24E04262}">
+    <dataValidation type="list" sqref="N250" xr:uid="{F4393D89-FD9E-4A2E-8D5F-FB587D3568D9}">
       <formula1>=IF(M250&lt;&gt;"",INDIRECT(VLOOKUP(M250,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M251" xr:uid="{2765D1A6-243B-47C1-BAAF-6F6851B0CB27}">
+    <dataValidation type="list" sqref="M251" xr:uid="{7D617609-7EFB-49E7-8160-ED8B04860C76}">
       <formula1>=IF(L251&lt;&gt;"",INDIRECT(VLOOKUP(L251,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N251" xr:uid="{FD9E108F-1F29-4150-B7C5-9E1700289436}">
+    <dataValidation type="list" sqref="N251" xr:uid="{7CD3838A-BB14-4704-9253-E8DCEB5823ED}">
       <formula1>=IF(M251&lt;&gt;"",INDIRECT(VLOOKUP(M251,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M252" xr:uid="{30BA92DB-EB8B-4A95-BF01-7CDDEAA9434B}">
+    <dataValidation type="list" sqref="M252" xr:uid="{FBAF3E10-E32B-4BAD-A5DF-3EBF3AED078D}">
       <formula1>=IF(L252&lt;&gt;"",INDIRECT(VLOOKUP(L252,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N252" xr:uid="{52B6DF06-DB4F-4C87-B279-6723D8C8AF80}">
+    <dataValidation type="list" sqref="N252" xr:uid="{3DD2B0AF-F243-4004-96D2-392F4838B359}">
       <formula1>=IF(M252&lt;&gt;"",INDIRECT(VLOOKUP(M252,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M253" xr:uid="{DD31CBC2-B4A9-4206-BE07-2BC76322CDFF}">
+    <dataValidation type="list" sqref="M253" xr:uid="{E2CEE408-D583-4463-8CA7-4F0D09C2C128}">
       <formula1>=IF(L253&lt;&gt;"",INDIRECT(VLOOKUP(L253,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N253" xr:uid="{ED34A459-0F03-4EE7-BA17-E07EE04D35DD}">
+    <dataValidation type="list" sqref="N253" xr:uid="{89B2168D-E28D-488C-967D-9F786B1FC167}">
       <formula1>=IF(M253&lt;&gt;"",INDIRECT(VLOOKUP(M253,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M254" xr:uid="{863BF3C3-EB85-422B-8B04-2FA6CC0ED97F}">
+    <dataValidation type="list" sqref="M254" xr:uid="{925E78AA-E4E7-47A7-BB39-4F6668F41087}">
       <formula1>=IF(L254&lt;&gt;"",INDIRECT(VLOOKUP(L254,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N254" xr:uid="{A612C13C-E026-41E5-AF3F-5C5F325BF025}">
+    <dataValidation type="list" sqref="N254" xr:uid="{5B332030-172D-4745-9835-93F06C7CAB6B}">
       <formula1>=IF(M254&lt;&gt;"",INDIRECT(VLOOKUP(M254,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M255" xr:uid="{8BE85867-85A5-448D-A036-ECBA5FE3D964}">
+    <dataValidation type="list" sqref="M255" xr:uid="{2D7EE504-9AA5-4832-AD3E-C93DC7AAB065}">
       <formula1>=IF(L255&lt;&gt;"",INDIRECT(VLOOKUP(L255,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N255" xr:uid="{9A4C94E1-9D22-4C02-98B1-F131C2CA3383}">
+    <dataValidation type="list" sqref="N255" xr:uid="{FC47D10C-4026-47B7-B4D6-DB7ABF0E410C}">
       <formula1>=IF(M255&lt;&gt;"",INDIRECT(VLOOKUP(M255,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M256" xr:uid="{6583C65D-34A5-4472-8ECC-0CD57E6CC257}">
+    <dataValidation type="list" sqref="M256" xr:uid="{493C31FD-BDC0-4EF7-89ED-DBD85EA7752A}">
       <formula1>=IF(L256&lt;&gt;"",INDIRECT(VLOOKUP(L256,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N256" xr:uid="{43F0A959-7D4E-4D7F-9F1B-AD6197400C63}">
+    <dataValidation type="list" sqref="N256" xr:uid="{5E034F75-8773-4BB1-B764-6828D0C35008}">
       <formula1>=IF(M256&lt;&gt;"",INDIRECT(VLOOKUP(M256,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M257" xr:uid="{BEF1D8AF-3813-4AC6-8C0F-7AD238689147}">
+    <dataValidation type="list" sqref="M257" xr:uid="{095F4F55-8F97-4E42-985A-2D623EDAD65A}">
       <formula1>=IF(L257&lt;&gt;"",INDIRECT(VLOOKUP(L257,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N257" xr:uid="{F5703F7C-71C6-4252-A4D3-CFEAEE15E7DE}">
+    <dataValidation type="list" sqref="N257" xr:uid="{9AFCC8AE-7D3A-4FC8-BB14-58B641F7A9CC}">
       <formula1>=IF(M257&lt;&gt;"",INDIRECT(VLOOKUP(M257,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M258" xr:uid="{8E4D72BD-1875-47C5-9C04-5275ABF78975}">
+    <dataValidation type="list" sqref="M258" xr:uid="{96D80A68-F4C1-451E-A451-EAC905A07046}">
       <formula1>=IF(L258&lt;&gt;"",INDIRECT(VLOOKUP(L258,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N258" xr:uid="{AB1C7B87-515D-4410-A08E-678809F3E28C}">
+    <dataValidation type="list" sqref="N258" xr:uid="{8AF8B75B-47AC-426F-AD2C-3A996F5B4B48}">
       <formula1>=IF(M258&lt;&gt;"",INDIRECT(VLOOKUP(M258,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M259" xr:uid="{30A9C062-B92C-4D27-81D8-DBA7AFB10841}">
+    <dataValidation type="list" sqref="M259" xr:uid="{0DDEF89F-E2B5-42B5-82F5-E4204312C485}">
       <formula1>=IF(L259&lt;&gt;"",INDIRECT(VLOOKUP(L259,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N259" xr:uid="{54B3DB0B-3DA0-4EA6-B65F-6DD0E60EE083}">
+    <dataValidation type="list" sqref="N259" xr:uid="{8ADB70EE-4B29-4AF0-90D9-0F0052CFA1E0}">
       <formula1>=IF(M259&lt;&gt;"",INDIRECT(VLOOKUP(M259,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M260" xr:uid="{8670636D-809D-4412-9757-5A7C9AC99928}">
+    <dataValidation type="list" sqref="M260" xr:uid="{AA25FEB1-AAD4-4D61-A483-DEAC778B0421}">
       <formula1>=IF(L260&lt;&gt;"",INDIRECT(VLOOKUP(L260,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N260" xr:uid="{58BC5DB3-C15C-422E-8813-5DE8176E6C46}">
+    <dataValidation type="list" sqref="N260" xr:uid="{3C192A4E-9979-46CE-96AB-B4C1BC0B1184}">
       <formula1>=IF(M260&lt;&gt;"",INDIRECT(VLOOKUP(M260,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M261" xr:uid="{2D0DF7FF-A7B9-4AB5-BA51-7384458CA060}">
+    <dataValidation type="list" sqref="M261" xr:uid="{545A1CE6-EDB2-49A8-AFEE-2648395A9C29}">
       <formula1>=IF(L261&lt;&gt;"",INDIRECT(VLOOKUP(L261,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N261" xr:uid="{A3BEF06F-8E14-4526-83B2-212691B077C6}">
+    <dataValidation type="list" sqref="N261" xr:uid="{53CDCCA6-12DF-466D-BD87-13DC53F6F27B}">
       <formula1>=IF(M261&lt;&gt;"",INDIRECT(VLOOKUP(M261,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M262" xr:uid="{36BD736A-CEC4-493E-8F10-E07F094EDE07}">
+    <dataValidation type="list" sqref="M262" xr:uid="{63DB3B93-F654-430B-9E5D-48365C270F91}">
       <formula1>=IF(L262&lt;&gt;"",INDIRECT(VLOOKUP(L262,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N262" xr:uid="{E23F9439-0DC4-4C0B-8B25-B8D0C89A490A}">
+    <dataValidation type="list" sqref="N262" xr:uid="{0F3CC473-568F-42C8-ADFD-499B38A410CD}">
       <formula1>=IF(M262&lt;&gt;"",INDIRECT(VLOOKUP(M262,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M263" xr:uid="{A67F57F3-D71A-45A0-8E69-726726C04784}">
+    <dataValidation type="list" sqref="M263" xr:uid="{420B6FE4-FA9D-46DE-B818-C7D8710DC443}">
       <formula1>=IF(L263&lt;&gt;"",INDIRECT(VLOOKUP(L263,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N263" xr:uid="{A539376A-71F8-4457-A04B-260EB5FAB59D}">
+    <dataValidation type="list" sqref="N263" xr:uid="{FA08FBE1-7865-4B57-8B7C-E61057AC79EB}">
       <formula1>=IF(M263&lt;&gt;"",INDIRECT(VLOOKUP(M263,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M264" xr:uid="{DC137E18-A2C7-48CD-A57B-22316EAF5882}">
+    <dataValidation type="list" sqref="M264" xr:uid="{1AB844EB-467B-4E1A-AC92-C4F0B4E24098}">
       <formula1>=IF(L264&lt;&gt;"",INDIRECT(VLOOKUP(L264,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N264" xr:uid="{0E0B3B2E-CC24-4464-B6E4-ED8164796928}">
+    <dataValidation type="list" sqref="N264" xr:uid="{B9C72E31-2179-45F4-B995-027B9E513E46}">
       <formula1>=IF(M264&lt;&gt;"",INDIRECT(VLOOKUP(M264,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M265" xr:uid="{1159290F-3708-44DB-B027-D46D6CB055D2}">
+    <dataValidation type="list" sqref="M265" xr:uid="{A8A37E20-4513-419E-A2CE-4E058C087941}">
       <formula1>=IF(L265&lt;&gt;"",INDIRECT(VLOOKUP(L265,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N265" xr:uid="{2C522D64-3FB4-4EF8-B3DC-0C6C19D4FF16}">
+    <dataValidation type="list" sqref="N265" xr:uid="{56EF5331-1453-4039-8C94-DE4DDB4F2C96}">
       <formula1>=IF(M265&lt;&gt;"",INDIRECT(VLOOKUP(M265,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M266" xr:uid="{E71BB54C-43BD-4864-A15F-4105649ACA65}">
+    <dataValidation type="list" sqref="M266" xr:uid="{4BE3EFFD-B246-4379-95D3-43363DE9626A}">
       <formula1>=IF(L266&lt;&gt;"",INDIRECT(VLOOKUP(L266,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N266" xr:uid="{807A41F9-1C01-4E3A-AC38-61D8F3861A4B}">
+    <dataValidation type="list" sqref="N266" xr:uid="{946AD097-462D-4F37-9AF8-3653907796DD}">
       <formula1>=IF(M266&lt;&gt;"",INDIRECT(VLOOKUP(M266,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M267" xr:uid="{AE0074B9-F294-4C9D-87BD-6CCE57DFE0D7}">
+    <dataValidation type="list" sqref="M267" xr:uid="{54008AA4-DD4E-4950-90C8-F8622A921327}">
       <formula1>=IF(L267&lt;&gt;"",INDIRECT(VLOOKUP(L267,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N267" xr:uid="{E4785D5B-3304-4937-8C1B-A85492818589}">
+    <dataValidation type="list" sqref="N267" xr:uid="{08AB29F1-AA18-4F0E-A11E-BCE43F44745D}">
       <formula1>=IF(M267&lt;&gt;"",INDIRECT(VLOOKUP(M267,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M268" xr:uid="{1E219ECC-3527-46C8-B1FD-433229CFA90E}">
+    <dataValidation type="list" sqref="M268" xr:uid="{DBE1CAA1-F270-47E6-B561-81008E09D79B}">
       <formula1>=IF(L268&lt;&gt;"",INDIRECT(VLOOKUP(L268,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N268" xr:uid="{E45427D7-F1B5-47F4-BF80-FCB27A238776}">
+    <dataValidation type="list" sqref="N268" xr:uid="{9315E172-E178-4D76-8C6D-382B2291410B}">
       <formula1>=IF(M268&lt;&gt;"",INDIRECT(VLOOKUP(M268,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M269" xr:uid="{FAA820F7-8623-4BBA-928D-354B9D76392A}">
+    <dataValidation type="list" sqref="M269" xr:uid="{B88AE2AD-B466-475C-B5A6-1316DFC39D06}">
       <formula1>=IF(L269&lt;&gt;"",INDIRECT(VLOOKUP(L269,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N269" xr:uid="{9FDEB0E4-CB08-40F4-9355-9AE7768A2F64}">
+    <dataValidation type="list" sqref="N269" xr:uid="{44ECDC16-2A2A-40EF-87A3-90E62B9593C2}">
       <formula1>=IF(M269&lt;&gt;"",INDIRECT(VLOOKUP(M269,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M270" xr:uid="{C9391D7F-C254-4432-B0ED-A70328A57B40}">
+    <dataValidation type="list" sqref="M270" xr:uid="{CD8AFFF1-5781-4DC8-A116-61A0D73A1961}">
       <formula1>=IF(L270&lt;&gt;"",INDIRECT(VLOOKUP(L270,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N270" xr:uid="{362EA106-865B-4886-BFA4-36B2120291B7}">
+    <dataValidation type="list" sqref="N270" xr:uid="{794DD21C-7C4A-4252-AFA4-7202183243B7}">
       <formula1>=IF(M270&lt;&gt;"",INDIRECT(VLOOKUP(M270,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M271" xr:uid="{AAB2848C-C463-43BB-A16E-3C57052D7B37}">
+    <dataValidation type="list" sqref="M271" xr:uid="{6F022DFC-B446-4C5D-940F-80090DC27997}">
       <formula1>=IF(L271&lt;&gt;"",INDIRECT(VLOOKUP(L271,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N271" xr:uid="{164D7A30-B852-4AE2-AB65-B19EC24F3159}">
+    <dataValidation type="list" sqref="N271" xr:uid="{2EF469F7-53D8-4B8D-955D-435E4B8A4ADA}">
       <formula1>=IF(M271&lt;&gt;"",INDIRECT(VLOOKUP(M271,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M272" xr:uid="{2C1A8111-2D95-4FF4-BB62-80C201BB9091}">
+    <dataValidation type="list" sqref="M272" xr:uid="{13FD62BD-1989-4B75-8D33-D0988E0CF30B}">
       <formula1>=IF(L272&lt;&gt;"",INDIRECT(VLOOKUP(L272,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N272" xr:uid="{6D33E210-BBCF-4C20-BA48-8C3D0B259C92}">
+    <dataValidation type="list" sqref="N272" xr:uid="{65C32B7C-408C-40AD-BA52-8FDDB907E093}">
       <formula1>=IF(M272&lt;&gt;"",INDIRECT(VLOOKUP(M272,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M273" xr:uid="{DF1FA038-B489-4982-A752-ED0242D1A3C6}">
+    <dataValidation type="list" sqref="M273" xr:uid="{992853B3-71DE-4E38-B541-0858F3661669}">
       <formula1>=IF(L273&lt;&gt;"",INDIRECT(VLOOKUP(L273,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N273" xr:uid="{5E61E097-30DE-4423-B123-74AD8A7E6D4F}">
+    <dataValidation type="list" sqref="N273" xr:uid="{0ACC6C07-02A8-41DC-92D5-97D97211845F}">
       <formula1>=IF(M273&lt;&gt;"",INDIRECT(VLOOKUP(M273,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M274" xr:uid="{CB927577-5E67-4020-96A9-F504D3F0E222}">
+    <dataValidation type="list" sqref="M274" xr:uid="{04E26CE1-1522-47B1-A89E-C9E57028653F}">
       <formula1>=IF(L274&lt;&gt;"",INDIRECT(VLOOKUP(L274,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N274" xr:uid="{267C9873-2710-4BCC-A19E-6295E908A200}">
+    <dataValidation type="list" sqref="N274" xr:uid="{B0684373-2689-482C-B07A-3538A56CD2F7}">
       <formula1>=IF(M274&lt;&gt;"",INDIRECT(VLOOKUP(M274,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M275" xr:uid="{5B791D95-3E09-4A6C-9405-5C69EA45976D}">
+    <dataValidation type="list" sqref="M275" xr:uid="{8D97DC61-400C-42E8-986D-44776097B715}">
       <formula1>=IF(L275&lt;&gt;"",INDIRECT(VLOOKUP(L275,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N275" xr:uid="{9BFB9CF7-A21D-448D-883B-12E54094B28D}">
+    <dataValidation type="list" sqref="N275" xr:uid="{C70A9DB6-E537-4E1B-8C4C-2D64811BFA16}">
       <formula1>=IF(M275&lt;&gt;"",INDIRECT(VLOOKUP(M275,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M276" xr:uid="{A0052B4F-15A0-4CD8-9B95-66439D0DC63B}">
+    <dataValidation type="list" sqref="M276" xr:uid="{B2A77ED5-9EB0-499A-80B5-6C7CFDCFFE7E}">
       <formula1>=IF(L276&lt;&gt;"",INDIRECT(VLOOKUP(L276,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N276" xr:uid="{26213781-6B89-4DB9-9615-3E89F59F1635}">
+    <dataValidation type="list" sqref="N276" xr:uid="{DA964F1B-9BC4-4356-8940-81CF6B85A8C4}">
       <formula1>=IF(M276&lt;&gt;"",INDIRECT(VLOOKUP(M276,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M277" xr:uid="{F6484448-9393-4DBE-BAB9-72720F1FF0CE}">
+    <dataValidation type="list" sqref="M277" xr:uid="{D98F5371-91ED-48F2-8FD0-36E22185DE08}">
       <formula1>=IF(L277&lt;&gt;"",INDIRECT(VLOOKUP(L277,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N277" xr:uid="{7C92166E-8489-4D7F-AD64-1244293DEE5B}">
+    <dataValidation type="list" sqref="N277" xr:uid="{60A49879-EEC2-496E-9EA6-3F2976CD8ECC}">
       <formula1>=IF(M277&lt;&gt;"",INDIRECT(VLOOKUP(M277,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M278" xr:uid="{846A2A34-56C9-4B60-A40A-E2FB24EDAE68}">
+    <dataValidation type="list" sqref="M278" xr:uid="{67C519EE-535B-4DEA-9E2A-3AB5FBEB39EF}">
       <formula1>=IF(L278&lt;&gt;"",INDIRECT(VLOOKUP(L278,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N278" xr:uid="{5D7C056D-F2DD-47DE-8850-F7EE6ACEF1C4}">
+    <dataValidation type="list" sqref="N278" xr:uid="{63059AB6-0320-4FB7-908E-3C0C349A1802}">
       <formula1>=IF(M278&lt;&gt;"",INDIRECT(VLOOKUP(M278,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M279" xr:uid="{7B4E3366-126E-4ED7-B1D1-61399CB91D84}">
+    <dataValidation type="list" sqref="M279" xr:uid="{8F397BD2-4363-47E2-A6D4-1E40257FD078}">
       <formula1>=IF(L279&lt;&gt;"",INDIRECT(VLOOKUP(L279,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N279" xr:uid="{C5092DF0-7CFA-4174-A7C0-72B5B31EA8A0}">
+    <dataValidation type="list" sqref="N279" xr:uid="{A860FAC6-F367-4517-8BE7-63E1EEFB8075}">
       <formula1>=IF(M279&lt;&gt;"",INDIRECT(VLOOKUP(M279,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M280" xr:uid="{3D4FB05F-4916-4FB8-9AB5-4EA0903FA49E}">
+    <dataValidation type="list" sqref="M280" xr:uid="{EFA15FC9-19C6-4369-9B69-8DAB57C62A89}">
       <formula1>=IF(L280&lt;&gt;"",INDIRECT(VLOOKUP(L280,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N280" xr:uid="{A12795A9-CCA3-49B1-A3E2-E0C679FFFB45}">
+    <dataValidation type="list" sqref="N280" xr:uid="{D4D5B9D4-1E1D-4115-9879-7D4A8F6C71FE}">
       <formula1>=IF(M280&lt;&gt;"",INDIRECT(VLOOKUP(M280,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M281" xr:uid="{A646E445-7F99-46CC-A9EF-F12CA6042D7A}">
+    <dataValidation type="list" sqref="M281" xr:uid="{9734EFAE-7080-4DDA-A3D8-E1971ACAB2CF}">
       <formula1>=IF(L281&lt;&gt;"",INDIRECT(VLOOKUP(L281,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N281" xr:uid="{578BBE9D-58FD-42C9-B43C-1CB2D881952A}">
+    <dataValidation type="list" sqref="N281" xr:uid="{C1BA46EC-EAA1-495C-9F64-6B871F748B00}">
       <formula1>=IF(M281&lt;&gt;"",INDIRECT(VLOOKUP(M281,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M282" xr:uid="{F78548B8-8754-4448-A033-1552160D7AC3}">
+    <dataValidation type="list" sqref="M282" xr:uid="{7F8CBF32-3C4D-4BD2-AFFD-950926A1FC8C}">
       <formula1>=IF(L282&lt;&gt;"",INDIRECT(VLOOKUP(L282,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N282" xr:uid="{7BDBE4CF-C872-4902-B403-DC0340ACEEDC}">
+    <dataValidation type="list" sqref="N282" xr:uid="{D558CA4B-FB5C-47E2-B1C7-A441EBED2905}">
       <formula1>=IF(M282&lt;&gt;"",INDIRECT(VLOOKUP(M282,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M283" xr:uid="{03435F06-B336-4E8E-906A-B3BBC1085B83}">
+    <dataValidation type="list" sqref="M283" xr:uid="{48A062AB-E3E0-4028-97C3-2C4A3DB97A14}">
       <formula1>=IF(L283&lt;&gt;"",INDIRECT(VLOOKUP(L283,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N283" xr:uid="{AE2BBF3F-71AD-491B-BD35-B45BE795D9D0}">
+    <dataValidation type="list" sqref="N283" xr:uid="{D63D53BD-5E85-422F-A206-B58C5604119E}">
       <formula1>=IF(M283&lt;&gt;"",INDIRECT(VLOOKUP(M283,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M284" xr:uid="{D1CFF810-6BED-4376-AB1B-B3937CD2BE9B}">
+    <dataValidation type="list" sqref="M284" xr:uid="{EE1AD87E-1DDB-4F29-890E-AA1B453DD50B}">
       <formula1>=IF(L284&lt;&gt;"",INDIRECT(VLOOKUP(L284,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N284" xr:uid="{C56D7D6E-25DF-4CC3-8A4C-A7F848846935}">
+    <dataValidation type="list" sqref="N284" xr:uid="{306AA7A5-0669-432F-915E-57A657976054}">
       <formula1>=IF(M284&lt;&gt;"",INDIRECT(VLOOKUP(M284,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M285" xr:uid="{33971F6C-30C6-435E-9DAC-AE873661908B}">
+    <dataValidation type="list" sqref="M285" xr:uid="{B9888C55-F3C6-46B6-9F60-0C8B859E822D}">
       <formula1>=IF(L285&lt;&gt;"",INDIRECT(VLOOKUP(L285,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N285" xr:uid="{DAF00483-B229-43CC-BD83-F844EB891198}">
+    <dataValidation type="list" sqref="N285" xr:uid="{0B904153-5EE1-457F-AA67-694B94378174}">
       <formula1>=IF(M285&lt;&gt;"",INDIRECT(VLOOKUP(M285,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M286" xr:uid="{A80333E0-9E7C-4C43-ABAB-C472FBDDBA55}">
+    <dataValidation type="list" sqref="M286" xr:uid="{9E8E3F27-32A9-40A0-A0C7-889CBF19FD12}">
       <formula1>=IF(L286&lt;&gt;"",INDIRECT(VLOOKUP(L286,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N286" xr:uid="{016BF880-513C-4187-9902-93B5335FCDF6}">
+    <dataValidation type="list" sqref="N286" xr:uid="{1421EBBE-05B7-4BE0-9E42-B0239E05A88A}">
       <formula1>=IF(M286&lt;&gt;"",INDIRECT(VLOOKUP(M286,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M287" xr:uid="{1B8DEEC6-615E-40FA-9E58-9B3659FD4D3A}">
+    <dataValidation type="list" sqref="M287" xr:uid="{2B621780-37D5-4CAF-943E-DBF5B074E1F6}">
       <formula1>=IF(L287&lt;&gt;"",INDIRECT(VLOOKUP(L287,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N287" xr:uid="{0E633431-9269-4776-9F0A-5AB43DAEF2CA}">
+    <dataValidation type="list" sqref="N287" xr:uid="{F6E8CA5D-28A4-4D4E-897A-F90D2FAFFFED}">
       <formula1>=IF(M287&lt;&gt;"",INDIRECT(VLOOKUP(M287,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M288" xr:uid="{EFFCE42E-DB0A-4447-9583-F942C93B8448}">
+    <dataValidation type="list" sqref="M288" xr:uid="{FB9A2433-9CAF-489A-850B-4A362AFA3438}">
       <formula1>=IF(L288&lt;&gt;"",INDIRECT(VLOOKUP(L288,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N288" xr:uid="{D17595EB-B027-4914-B57E-CA6CD7EE18F7}">
+    <dataValidation type="list" sqref="N288" xr:uid="{8AA617E4-BD8F-4D31-BAFF-1B8471E8E603}">
       <formula1>=IF(M288&lt;&gt;"",INDIRECT(VLOOKUP(M288,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M289" xr:uid="{EA74DD18-9A81-4036-8447-6A859E97CA19}">
+    <dataValidation type="list" sqref="M289" xr:uid="{FBD384BA-EB32-4E14-A4C1-EC6EA52415E0}">
       <formula1>=IF(L289&lt;&gt;"",INDIRECT(VLOOKUP(L289,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N289" xr:uid="{DFF3F33B-BE07-4F31-B6DE-3734FEF24DCC}">
+    <dataValidation type="list" sqref="N289" xr:uid="{ADDBC4E1-23F5-49E9-A5E3-A8113FD69A96}">
       <formula1>=IF(M289&lt;&gt;"",INDIRECT(VLOOKUP(M289,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M290" xr:uid="{1765DAD2-8775-47B2-866C-90099C976D4E}">
+    <dataValidation type="list" sqref="M290" xr:uid="{7E590AAB-2BB0-4B84-AFB7-DEFC6D9758D7}">
       <formula1>=IF(L290&lt;&gt;"",INDIRECT(VLOOKUP(L290,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N290" xr:uid="{EE96F359-4C27-4D09-A7BD-7E07CC0748F3}">
+    <dataValidation type="list" sqref="N290" xr:uid="{EAC6BAA0-8B29-414F-9B59-3F11FEEA7A1B}">
       <formula1>=IF(M290&lt;&gt;"",INDIRECT(VLOOKUP(M290,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M291" xr:uid="{FBE779C7-B51B-4BEC-9F30-3ED81F0BCDA4}">
+    <dataValidation type="list" sqref="M291" xr:uid="{48C43E0E-8C79-4A5B-91CF-DD12844D50B5}">
       <formula1>=IF(L291&lt;&gt;"",INDIRECT(VLOOKUP(L291,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N291" xr:uid="{367DA888-D101-4F0F-A250-511610236044}">
+    <dataValidation type="list" sqref="N291" xr:uid="{199708B3-BCE7-47ED-8988-089C03DE6E6B}">
       <formula1>=IF(M291&lt;&gt;"",INDIRECT(VLOOKUP(M291,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M292" xr:uid="{AB782027-8971-4FEF-B576-A7A5844B0EBF}">
+    <dataValidation type="list" sqref="M292" xr:uid="{3A7153E6-3380-4B79-BBCC-85208FD41583}">
       <formula1>=IF(L292&lt;&gt;"",INDIRECT(VLOOKUP(L292,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N292" xr:uid="{B8151F89-043E-447C-B6A2-197192086893}">
+    <dataValidation type="list" sqref="N292" xr:uid="{EDF1168B-7EF1-4AA9-9E6C-E0D4C3C33A12}">
       <formula1>=IF(M292&lt;&gt;"",INDIRECT(VLOOKUP(M292,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M293" xr:uid="{42565DA8-40EC-4885-BDA0-5EFBE591AE0C}">
+    <dataValidation type="list" sqref="M293" xr:uid="{B1A78247-D259-4173-B30C-931ED2C0518A}">
       <formula1>=IF(L293&lt;&gt;"",INDIRECT(VLOOKUP(L293,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N293" xr:uid="{E0EBC025-E73D-419C-957D-54F3C05515B2}">
+    <dataValidation type="list" sqref="N293" xr:uid="{ECCC1994-A719-4A1E-843E-4A54D590D645}">
       <formula1>=IF(M293&lt;&gt;"",INDIRECT(VLOOKUP(M293,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M294" xr:uid="{22C01B71-90AF-4850-A537-0045C8172B4B}">
+    <dataValidation type="list" sqref="M294" xr:uid="{4C74ECF0-82B8-4BBD-9B7C-D59FC0F0DC22}">
       <formula1>=IF(L294&lt;&gt;"",INDIRECT(VLOOKUP(L294,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N294" xr:uid="{20AFE228-7A84-4D89-8431-6A74977DBABE}">
+    <dataValidation type="list" sqref="N294" xr:uid="{707AC9BA-9D9E-491A-B376-7FBAF5390267}">
       <formula1>=IF(M294&lt;&gt;"",INDIRECT(VLOOKUP(M294,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M295" xr:uid="{A0D31B94-F450-4934-9AFD-A44BB0347012}">
+    <dataValidation type="list" sqref="M295" xr:uid="{706A4D3C-4CA1-477B-81A5-8AF91040EAEA}">
       <formula1>=IF(L295&lt;&gt;"",INDIRECT(VLOOKUP(L295,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N295" xr:uid="{BAA1BD9E-2BCE-49D9-8642-DB9E475E9BAB}">
+    <dataValidation type="list" sqref="N295" xr:uid="{25B5A118-0849-48B7-85BF-238BC0C071FC}">
       <formula1>=IF(M295&lt;&gt;"",INDIRECT(VLOOKUP(M295,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M296" xr:uid="{0C96163D-325E-40DF-8B16-63E49FB7F065}">
+    <dataValidation type="list" sqref="M296" xr:uid="{277D4619-9FC0-4183-827F-0D502F3F460C}">
       <formula1>=IF(L296&lt;&gt;"",INDIRECT(VLOOKUP(L296,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N296" xr:uid="{D79A2AD7-85AC-42E0-B40B-65C2EDC4056C}">
+    <dataValidation type="list" sqref="N296" xr:uid="{7ED6622F-03F4-42FD-B1B9-9447AA4C44E3}">
       <formula1>=IF(M296&lt;&gt;"",INDIRECT(VLOOKUP(M296,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M297" xr:uid="{39801889-8A52-4788-9700-61E9DF48F0C9}">
+    <dataValidation type="list" sqref="M297" xr:uid="{67453929-8257-4469-86AA-FC12DF43C912}">
       <formula1>=IF(L297&lt;&gt;"",INDIRECT(VLOOKUP(L297,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N297" xr:uid="{791F5A8D-C991-4C05-83E2-4EB51CB5FCC6}">
+    <dataValidation type="list" sqref="N297" xr:uid="{8AF9E2E5-6F52-4077-9E04-44A88B37E2A0}">
       <formula1>=IF(M297&lt;&gt;"",INDIRECT(VLOOKUP(M297,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M298" xr:uid="{244D328B-3EDD-4A3E-932F-4EFC984A6870}">
+    <dataValidation type="list" sqref="M298" xr:uid="{3254FA49-474E-442B-A296-03D6175826F2}">
       <formula1>=IF(L298&lt;&gt;"",INDIRECT(VLOOKUP(L298,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N298" xr:uid="{F066A0BD-21A8-4B9A-BE5F-57E677BD8781}">
+    <dataValidation type="list" sqref="N298" xr:uid="{8D62F9ED-14FE-49D4-9BE8-8CB6F908B7CD}">
       <formula1>=IF(M298&lt;&gt;"",INDIRECT(VLOOKUP(M298,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M299" xr:uid="{256F6C5C-7FCC-401C-96FD-EBD9F3B18BD8}">
+    <dataValidation type="list" sqref="M299" xr:uid="{476B2F13-164D-4945-B6D7-848897E16E5B}">
       <formula1>=IF(L299&lt;&gt;"",INDIRECT(VLOOKUP(L299,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N299" xr:uid="{A34280F1-A65D-4C56-8FF8-600ED71AFFAA}">
+    <dataValidation type="list" sqref="N299" xr:uid="{F465204A-307C-4740-B94D-8A9F0D026D24}">
       <formula1>=IF(M299&lt;&gt;"",INDIRECT(VLOOKUP(M299,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M300" xr:uid="{25BD292E-F657-414A-B048-64753F3B2EAC}">
+    <dataValidation type="list" sqref="M300" xr:uid="{7ECC2C4E-A6CF-4055-8B42-4F255D402088}">
       <formula1>=IF(L300&lt;&gt;"",INDIRECT(VLOOKUP(L300,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N300" xr:uid="{C08C86B4-7D1B-4E43-967A-F823FEE914B5}">
+    <dataValidation type="list" sqref="N300" xr:uid="{73C4B8D2-31B8-40B5-A035-2CC37B602A5D}">
       <formula1>=IF(M300&lt;&gt;"",INDIRECT(VLOOKUP(M300,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M301" xr:uid="{95462033-C93C-4E0C-8019-5E69016848CC}">
+    <dataValidation type="list" sqref="M301" xr:uid="{E16AA7D9-5765-4961-BFE6-C1D7C265BF22}">
       <formula1>=IF(L301&lt;&gt;"",INDIRECT(VLOOKUP(L301,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N301" xr:uid="{6170A842-F629-4F06-8207-CAF5075668D8}">
+    <dataValidation type="list" sqref="N301" xr:uid="{4E16A1D8-65D6-44B0-9731-6EFD0EF2A14E}">
       <formula1>=IF(M301&lt;&gt;"",INDIRECT(VLOOKUP(M301,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M302" xr:uid="{DF9D58F7-2EFB-4FC2-8F37-BC909A28C547}">
+    <dataValidation type="list" sqref="M302" xr:uid="{40408C2F-8F6C-4C67-BE3C-B1A54B87C56C}">
       <formula1>=IF(L302&lt;&gt;"",INDIRECT(VLOOKUP(L302,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N302" xr:uid="{DF8E4FE1-3512-409E-8477-668853C1B556}">
+    <dataValidation type="list" sqref="N302" xr:uid="{BD9897E9-890C-4352-AD24-80426A8F6FC6}">
       <formula1>=IF(M302&lt;&gt;"",INDIRECT(VLOOKUP(M302,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M303" xr:uid="{59A95F00-D6D6-46FB-9FEC-39E59272E746}">
+    <dataValidation type="list" sqref="M303" xr:uid="{A6411DF6-7E34-4B81-8D06-525541E1A1CC}">
       <formula1>=IF(L303&lt;&gt;"",INDIRECT(VLOOKUP(L303,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N303" xr:uid="{C48C4E76-1BE1-4CD7-A147-8503469C8D60}">
+    <dataValidation type="list" sqref="N303" xr:uid="{A5CBF23A-89EE-4485-BC7E-2011C7CC6818}">
       <formula1>=IF(M303&lt;&gt;"",INDIRECT(VLOOKUP(M303,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M304" xr:uid="{E3A2782C-05ED-414C-B8ED-1DFE31F39F00}">
+    <dataValidation type="list" sqref="M304" xr:uid="{941EB399-22BF-45DF-A81D-C1586F9AAC1C}">
       <formula1>=IF(L304&lt;&gt;"",INDIRECT(VLOOKUP(L304,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N304" xr:uid="{A53A669C-7032-4D39-AFF8-0CD67FCECCEE}">
+    <dataValidation type="list" sqref="N304" xr:uid="{409EE0A1-3753-4C1F-BD06-D0EEEFEF7169}">
       <formula1>=IF(M304&lt;&gt;"",INDIRECT(VLOOKUP(M304,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M305" xr:uid="{098CA636-0CFF-4F2B-B22E-20E39CF0D9F5}">
+    <dataValidation type="list" sqref="M305" xr:uid="{F591E369-55BB-41B9-BE6F-0262EB224F3A}">
       <formula1>=IF(L305&lt;&gt;"",INDIRECT(VLOOKUP(L305,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N305" xr:uid="{C57739A6-4B8B-405D-B39C-83753F823376}">
+    <dataValidation type="list" sqref="N305" xr:uid="{1998BEE5-1A96-401E-B52B-FB82EFB29A53}">
       <formula1>=IF(M305&lt;&gt;"",INDIRECT(VLOOKUP(M305,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M306" xr:uid="{25EAEC7C-ECF0-4E07-B09D-3590B46705FE}">
+    <dataValidation type="list" sqref="M306" xr:uid="{E35117D3-705C-4454-BF79-B728466E4D5C}">
       <formula1>=IF(L306&lt;&gt;"",INDIRECT(VLOOKUP(L306,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N306" xr:uid="{8AAD34A9-0DE3-4E55-86EC-B432189F53FA}">
+    <dataValidation type="list" sqref="N306" xr:uid="{57D99754-F128-494E-8A1E-5063786AD072}">
       <formula1>=IF(M306&lt;&gt;"",INDIRECT(VLOOKUP(M306,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M307" xr:uid="{A96B590F-FC68-4DE3-8886-9A962C1841CE}">
+    <dataValidation type="list" sqref="M307" xr:uid="{FF544374-2170-4C99-9F2E-F6CFF02C9586}">
       <formula1>=IF(L307&lt;&gt;"",INDIRECT(VLOOKUP(L307,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N307" xr:uid="{68399F79-7115-402D-9E71-BF3C682A43CD}">
+    <dataValidation type="list" sqref="N307" xr:uid="{490B0137-1E50-46AA-B7B1-3D950604A76F}">
       <formula1>=IF(M307&lt;&gt;"",INDIRECT(VLOOKUP(M307,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M308" xr:uid="{89AA31B4-861F-421E-B355-7C0383BD6F36}">
+    <dataValidation type="list" sqref="M308" xr:uid="{522FBDF7-1A03-46B7-9358-E8F81947AE14}">
       <formula1>=IF(L308&lt;&gt;"",INDIRECT(VLOOKUP(L308,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N308" xr:uid="{AFA431F2-B4B4-4E4B-AE0A-B6F93F08BCC6}">
+    <dataValidation type="list" sqref="N308" xr:uid="{7D4A059E-2387-4064-8EF1-B13F0CA5A2EF}">
       <formula1>=IF(M308&lt;&gt;"",INDIRECT(VLOOKUP(M308,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M309" xr:uid="{902937EB-B195-40B3-9C4A-98136DD15D63}">
+    <dataValidation type="list" sqref="M309" xr:uid="{90BF65DA-0D66-45AA-AAFC-1CF3FB0421FE}">
       <formula1>=IF(L309&lt;&gt;"",INDIRECT(VLOOKUP(L309,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N309" xr:uid="{7AE9EC09-F46A-4B61-9178-B3A1EBC8893D}">
+    <dataValidation type="list" sqref="N309" xr:uid="{F26E4F59-B9DC-4D8E-BA78-1A6E03CB0A29}">
       <formula1>=IF(M309&lt;&gt;"",INDIRECT(VLOOKUP(M309,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M310" xr:uid="{95A2360D-4A91-4AC8-B9FB-C699ED8C1A30}">
+    <dataValidation type="list" sqref="M310" xr:uid="{A508EF54-B9F4-4629-9C5E-13D1278C26B7}">
       <formula1>=IF(L310&lt;&gt;"",INDIRECT(VLOOKUP(L310,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N310" xr:uid="{E8822FFB-4B65-4987-B646-AA920029E666}">
+    <dataValidation type="list" sqref="N310" xr:uid="{33794222-25C5-4857-BDC0-F51F2D304DDA}">
       <formula1>=IF(M310&lt;&gt;"",INDIRECT(VLOOKUP(M310,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M311" xr:uid="{8D4991A8-A7C9-4724-A2FF-DEB7F83FEF07}">
+    <dataValidation type="list" sqref="M311" xr:uid="{BE11121B-E0DC-4897-ADE2-FC8D76A779ED}">
       <formula1>=IF(L311&lt;&gt;"",INDIRECT(VLOOKUP(L311,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N311" xr:uid="{6CE81F4D-2366-4B32-977A-F5437802CDBF}">
+    <dataValidation type="list" sqref="N311" xr:uid="{BB106BCC-CC0E-4FAF-AC31-A87A5993E104}">
       <formula1>=IF(M311&lt;&gt;"",INDIRECT(VLOOKUP(M311,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M312" xr:uid="{94EEF1A3-1D5F-47AC-BA51-B8809470CE28}">
+    <dataValidation type="list" sqref="M312" xr:uid="{596B3CC7-329C-482E-B184-7A4320B966C8}">
       <formula1>=IF(L312&lt;&gt;"",INDIRECT(VLOOKUP(L312,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N312" xr:uid="{3013196B-6F2D-4A7B-A759-1F515950E8B7}">
+    <dataValidation type="list" sqref="N312" xr:uid="{AC206D24-7765-481A-8FB7-F4F58FE2E98F}">
       <formula1>=IF(M312&lt;&gt;"",INDIRECT(VLOOKUP(M312,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M313" xr:uid="{3B36AE27-84CA-4F6E-839A-E1F3AD8AD3F8}">
+    <dataValidation type="list" sqref="M313" xr:uid="{7C0C8B46-9B21-4B5A-8092-DFE3BCEF9933}">
       <formula1>=IF(L313&lt;&gt;"",INDIRECT(VLOOKUP(L313,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N313" xr:uid="{6F6D3A03-9CD1-4838-8EF4-A2675DEAF496}">
+    <dataValidation type="list" sqref="N313" xr:uid="{0D58694E-46B1-45B8-8068-82C8DAFF9CF0}">
       <formula1>=IF(M313&lt;&gt;"",INDIRECT(VLOOKUP(M313,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M314" xr:uid="{72406E33-C2A2-4AEB-8DDB-6560A0F02198}">
+    <dataValidation type="list" sqref="M314" xr:uid="{8D366901-2C40-4E75-A0B0-0EDFEF670DE1}">
       <formula1>=IF(L314&lt;&gt;"",INDIRECT(VLOOKUP(L314,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N314" xr:uid="{FBD700E5-B72E-4BE8-9656-7C51FDC9A082}">
+    <dataValidation type="list" sqref="N314" xr:uid="{B9D6941D-27BC-45AB-8611-7DB2CA03C3A2}">
       <formula1>=IF(M314&lt;&gt;"",INDIRECT(VLOOKUP(M314,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M315" xr:uid="{97637140-B60C-4CE6-A476-F5760C22E066}">
+    <dataValidation type="list" sqref="M315" xr:uid="{7DD06461-339A-4FC5-BF80-73871D8E2A01}">
       <formula1>=IF(L315&lt;&gt;"",INDIRECT(VLOOKUP(L315,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N315" xr:uid="{406F1B73-173B-42F1-8C6F-6A4DFCA14C9B}">
+    <dataValidation type="list" sqref="N315" xr:uid="{52ADF523-9A8D-4B9D-9CA3-964B99AEA0C6}">
       <formula1>=IF(M315&lt;&gt;"",INDIRECT(VLOOKUP(M315,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M316" xr:uid="{F7AEF932-5493-447B-B01F-5886309C9093}">
+    <dataValidation type="list" sqref="M316" xr:uid="{6FF69409-1E40-4388-B473-06E4CF0B68CF}">
       <formula1>=IF(L316&lt;&gt;"",INDIRECT(VLOOKUP(L316,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N316" xr:uid="{3E1A13EA-3EBC-4C9D-BBBA-78190AFBEA32}">
+    <dataValidation type="list" sqref="N316" xr:uid="{A61A2CFD-4F82-41C9-A5C2-51B02E520558}">
       <formula1>=IF(M316&lt;&gt;"",INDIRECT(VLOOKUP(M316,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M317" xr:uid="{D66C7A16-5620-4735-BF25-DDBA8C15025C}">
+    <dataValidation type="list" sqref="M317" xr:uid="{4F2086ED-7EF5-4E19-BB49-B24191958120}">
       <formula1>=IF(L317&lt;&gt;"",INDIRECT(VLOOKUP(L317,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N317" xr:uid="{A8226108-A223-45C1-87D1-71B87C7A6F60}">
+    <dataValidation type="list" sqref="N317" xr:uid="{00B5B5D8-B026-4345-A0F6-0EF80714F863}">
       <formula1>=IF(M317&lt;&gt;"",INDIRECT(VLOOKUP(M317,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M318" xr:uid="{C8995DEE-367B-4895-8C65-60FAE015BE5E}">
+    <dataValidation type="list" sqref="M318" xr:uid="{72C14B48-FFC5-457E-8E28-67FF8327E381}">
       <formula1>=IF(L318&lt;&gt;"",INDIRECT(VLOOKUP(L318,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N318" xr:uid="{BA1D7577-B8C3-4E50-A47B-71073C8CE986}">
+    <dataValidation type="list" sqref="N318" xr:uid="{ABBB35C0-1CA7-4C5A-AB1B-7C75DC1C690D}">
       <formula1>=IF(M318&lt;&gt;"",INDIRECT(VLOOKUP(M318,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M319" xr:uid="{A7FB5029-737A-4C16-83AC-B3030957D939}">
+    <dataValidation type="list" sqref="M319" xr:uid="{1A3243E7-6FB3-4434-A629-83D74D6DEB7C}">
       <formula1>=IF(L319&lt;&gt;"",INDIRECT(VLOOKUP(L319,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N319" xr:uid="{DECAAD75-6007-42EC-A989-21E9C0D9B11C}">
+    <dataValidation type="list" sqref="N319" xr:uid="{8705765C-2330-4353-A235-F8A3EE799EE5}">
       <formula1>=IF(M319&lt;&gt;"",INDIRECT(VLOOKUP(M319,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M320" xr:uid="{D4B85D1D-C376-4CE7-B0A0-8329D4B0470F}">
+    <dataValidation type="list" sqref="M320" xr:uid="{900A0C92-07A8-46EC-80AB-91D19D3E99A8}">
       <formula1>=IF(L320&lt;&gt;"",INDIRECT(VLOOKUP(L320,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N320" xr:uid="{D6BBCE6F-40A3-498F-BC73-274DC086FB36}">
+    <dataValidation type="list" sqref="N320" xr:uid="{83342555-46A8-4C54-AFA1-2B2556D7033C}">
       <formula1>=IF(M320&lt;&gt;"",INDIRECT(VLOOKUP(M320,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M321" xr:uid="{25294CDA-1DFA-4EC7-AC11-72D3FB3D5964}">
+    <dataValidation type="list" sqref="M321" xr:uid="{75786BAD-88A1-44BB-B5C3-2C34B2E343CA}">
       <formula1>=IF(L321&lt;&gt;"",INDIRECT(VLOOKUP(L321,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N321" xr:uid="{C1F2AC01-CF5B-4A1A-9D80-353BE3E46482}">
+    <dataValidation type="list" sqref="N321" xr:uid="{D6732935-76B4-4FFD-B4E1-A8597B74AA3F}">
       <formula1>=IF(M321&lt;&gt;"",INDIRECT(VLOOKUP(M321,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M322" xr:uid="{C14EAB77-C405-47DF-AC98-75446D152140}">
+    <dataValidation type="list" sqref="M322" xr:uid="{B7978C4D-BF1C-45A3-85E0-A3D491FFF052}">
       <formula1>=IF(L322&lt;&gt;"",INDIRECT(VLOOKUP(L322,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N322" xr:uid="{93DD22CE-003B-42A2-BE2A-E24E796E7E7C}">
+    <dataValidation type="list" sqref="N322" xr:uid="{061219E5-0EC5-48C9-8023-FB4616C05B63}">
       <formula1>=IF(M322&lt;&gt;"",INDIRECT(VLOOKUP(M322,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M323" xr:uid="{786CBC0A-99A4-45E9-896C-D90282A7FA0C}">
+    <dataValidation type="list" sqref="M323" xr:uid="{EED0BFC4-70AE-41A7-9A9B-3E5A140F0418}">
       <formula1>=IF(L323&lt;&gt;"",INDIRECT(VLOOKUP(L323,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N323" xr:uid="{CEFFAA33-EBB8-42D5-A20A-EA71F9453898}">
+    <dataValidation type="list" sqref="N323" xr:uid="{98BCA6CC-70BF-4C7A-95DD-11F170EFA3D3}">
       <formula1>=IF(M323&lt;&gt;"",INDIRECT(VLOOKUP(M323,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M324" xr:uid="{BD35B2A7-EF8B-4AC2-91E5-26E1F1F0ADC7}">
+    <dataValidation type="list" sqref="M324" xr:uid="{01A6883C-05AB-4339-B3C8-2C4744FDC013}">
       <formula1>=IF(L324&lt;&gt;"",INDIRECT(VLOOKUP(L324,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N324" xr:uid="{0D6D77C8-F60C-4117-8764-BA2A146D1607}">
+    <dataValidation type="list" sqref="N324" xr:uid="{9439C5A8-5864-4543-9D67-7A6AF417C84B}">
       <formula1>=IF(M324&lt;&gt;"",INDIRECT(VLOOKUP(M324,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M325" xr:uid="{92F5748C-A320-43F7-B618-A2565FCA1F61}">
+    <dataValidation type="list" sqref="M325" xr:uid="{CD9E450B-5C9D-4179-8C79-081E9D1C0947}">
       <formula1>=IF(L325&lt;&gt;"",INDIRECT(VLOOKUP(L325,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N325" xr:uid="{DA565DBC-BC77-4541-A998-207DA1B538F6}">
+    <dataValidation type="list" sqref="N325" xr:uid="{9AB3F867-6088-4A3A-942B-069D2C94A586}">
       <formula1>=IF(M325&lt;&gt;"",INDIRECT(VLOOKUP(M325,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M326" xr:uid="{007723B0-8E97-42D5-BCFE-7563E9311BC7}">
+    <dataValidation type="list" sqref="M326" xr:uid="{EE6ED264-4DBB-43B6-9C42-F685402EA96E}">
       <formula1>=IF(L326&lt;&gt;"",INDIRECT(VLOOKUP(L326,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N326" xr:uid="{593451FB-DC54-4368-B43B-09E959C9CF08}">
+    <dataValidation type="list" sqref="N326" xr:uid="{8A01D548-2D66-4B76-88D0-2D0B2CF110B1}">
       <formula1>=IF(M326&lt;&gt;"",INDIRECT(VLOOKUP(M326,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M327" xr:uid="{5BC664E6-332E-4694-B422-EFBFA5A6297E}">
+    <dataValidation type="list" sqref="M327" xr:uid="{5A7496EB-EA0A-4221-AAD0-847CD9B7C01B}">
       <formula1>=IF(L327&lt;&gt;"",INDIRECT(VLOOKUP(L327,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N327" xr:uid="{5ED48E6A-52CE-4691-9255-1360A6F61ED0}">
+    <dataValidation type="list" sqref="N327" xr:uid="{871DF6A1-4051-4C55-B52B-D53AC6C697B6}">
       <formula1>=IF(M327&lt;&gt;"",INDIRECT(VLOOKUP(M327,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M328" xr:uid="{B70A5C45-3CB2-4430-9225-E77BD0C9E7D9}">
+    <dataValidation type="list" sqref="M328" xr:uid="{B0638444-C107-48A1-89AC-C4D3E8A840AF}">
       <formula1>=IF(L328&lt;&gt;"",INDIRECT(VLOOKUP(L328,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N328" xr:uid="{A284221B-CE56-431A-AE03-BF64F5859B97}">
+    <dataValidation type="list" sqref="N328" xr:uid="{D8DDDC2B-6453-4E37-B4A9-5014CB73CB26}">
       <formula1>=IF(M328&lt;&gt;"",INDIRECT(VLOOKUP(M328,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M329" xr:uid="{4DA33CFE-36A6-4A2F-AD39-978DF061D0BC}">
+    <dataValidation type="list" sqref="M329" xr:uid="{8BA78D9F-3D5C-415D-AA84-5B217C921555}">
       <formula1>=IF(L329&lt;&gt;"",INDIRECT(VLOOKUP(L329,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N329" xr:uid="{3EBFC7A8-A87C-43E4-8E87-6761F9192733}">
+    <dataValidation type="list" sqref="N329" xr:uid="{1096C171-BE79-4E34-B9A3-0977B61BFE7D}">
       <formula1>=IF(M329&lt;&gt;"",INDIRECT(VLOOKUP(M329,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M330" xr:uid="{97CF05DB-772A-4FF0-B9FD-305913B7C936}">
+    <dataValidation type="list" sqref="M330" xr:uid="{4E044BD2-E11F-4F85-854D-B98A18794E1F}">
       <formula1>=IF(L330&lt;&gt;"",INDIRECT(VLOOKUP(L330,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N330" xr:uid="{6BCC729A-F86D-4DAF-99CE-161B2F722847}">
+    <dataValidation type="list" sqref="N330" xr:uid="{B8F6AA5E-F343-4F1C-B5C7-8820E94AB8FD}">
       <formula1>=IF(M330&lt;&gt;"",INDIRECT(VLOOKUP(M330,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M331" xr:uid="{E01BBEC0-B315-477B-9A61-97611C69FDC6}">
+    <dataValidation type="list" sqref="M331" xr:uid="{6F04EA7D-1972-4744-827E-14EFED9CF0D3}">
       <formula1>=IF(L331&lt;&gt;"",INDIRECT(VLOOKUP(L331,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N331" xr:uid="{49F04FF0-58DC-486E-B48B-B8809C4B17F9}">
+    <dataValidation type="list" sqref="N331" xr:uid="{1010E65A-C496-449F-9CCF-546472CC2361}">
       <formula1>=IF(M331&lt;&gt;"",INDIRECT(VLOOKUP(M331,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M332" xr:uid="{AF0E3BB2-1674-47CB-8993-B3D7D2542D69}">
+    <dataValidation type="list" sqref="M332" xr:uid="{0C0DE107-EEC4-4171-8B00-6384986BC1BA}">
       <formula1>=IF(L332&lt;&gt;"",INDIRECT(VLOOKUP(L332,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N332" xr:uid="{2F6C258C-7175-47E0-B219-E3C238944AA8}">
+    <dataValidation type="list" sqref="N332" xr:uid="{BB36B4D0-8B6F-46A7-88EE-9BFA5AF4B699}">
       <formula1>=IF(M332&lt;&gt;"",INDIRECT(VLOOKUP(M332,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M333" xr:uid="{484275F1-F110-4F87-8707-581A018BAA57}">
+    <dataValidation type="list" sqref="M333" xr:uid="{A829E500-5875-4946-9AFD-5E23AD833DAB}">
       <formula1>=IF(L333&lt;&gt;"",INDIRECT(VLOOKUP(L333,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N333" xr:uid="{D4F37EAB-2661-4373-A141-D5C8760BB863}">
+    <dataValidation type="list" sqref="N333" xr:uid="{8D1C1587-7D51-4BF0-9B43-2393008FB641}">
       <formula1>=IF(M333&lt;&gt;"",INDIRECT(VLOOKUP(M333,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M334" xr:uid="{5188CB49-747E-4A8D-BEEF-B82C83281775}">
+    <dataValidation type="list" sqref="M334" xr:uid="{4A4CEE00-3B9E-46AB-88D3-832706C94FEC}">
       <formula1>=IF(L334&lt;&gt;"",INDIRECT(VLOOKUP(L334,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N334" xr:uid="{7D886CF6-A609-4BF0-9206-62FD243FB21C}">
+    <dataValidation type="list" sqref="N334" xr:uid="{4E621388-37C4-44B1-9236-FEF2E547BA9E}">
       <formula1>=IF(M334&lt;&gt;"",INDIRECT(VLOOKUP(M334,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M335" xr:uid="{954F1808-4C9A-43B2-A271-2EECA2FCFE81}">
+    <dataValidation type="list" sqref="M335" xr:uid="{5D18FAA5-E683-4B19-B206-4A027EA816D3}">
       <formula1>=IF(L335&lt;&gt;"",INDIRECT(VLOOKUP(L335,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N335" xr:uid="{E6A6C3A8-F25D-4396-A98E-D4B31D23F466}">
+    <dataValidation type="list" sqref="N335" xr:uid="{DFAC2FD0-0BA7-4ABD-9E72-F25AD6369C8C}">
       <formula1>=IF(M335&lt;&gt;"",INDIRECT(VLOOKUP(M335,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M336" xr:uid="{99DCA64B-1C5A-40F8-BE8F-EC086C6DED5D}">
+    <dataValidation type="list" sqref="M336" xr:uid="{3AA30C00-0B8C-479C-961A-1E364F2FFB17}">
       <formula1>=IF(L336&lt;&gt;"",INDIRECT(VLOOKUP(L336,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N336" xr:uid="{584F8767-2937-4EDC-9DA0-411274546A5D}">
+    <dataValidation type="list" sqref="N336" xr:uid="{919784B8-B54E-4A16-8056-F6957EDFF4DB}">
       <formula1>=IF(M336&lt;&gt;"",INDIRECT(VLOOKUP(M336,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M337" xr:uid="{DA4DA8A4-45E1-43CC-A242-3D66666F8F6A}">
+    <dataValidation type="list" sqref="M337" xr:uid="{356E0498-3290-4796-85EB-2EBA30854A3F}">
       <formula1>=IF(L337&lt;&gt;"",INDIRECT(VLOOKUP(L337,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N337" xr:uid="{488BF36C-907D-45DD-854F-29A7DD227595}">
+    <dataValidation type="list" sqref="N337" xr:uid="{4BE88E49-F07A-4B46-AA70-11990A1E8A3B}">
       <formula1>=IF(M337&lt;&gt;"",INDIRECT(VLOOKUP(M337,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M338" xr:uid="{2366C830-E636-47F1-9BFE-F651B89D1EF7}">
+    <dataValidation type="list" sqref="M338" xr:uid="{BE7E7573-3AA6-488F-A9F8-AFD0544162B6}">
       <formula1>=IF(L338&lt;&gt;"",INDIRECT(VLOOKUP(L338,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N338" xr:uid="{6AF4DEED-5D42-454C-876C-D9C22FB163DC}">
+    <dataValidation type="list" sqref="N338" xr:uid="{F279159E-17F3-4B21-9279-C0943C90B3E7}">
       <formula1>=IF(M338&lt;&gt;"",INDIRECT(VLOOKUP(M338,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M339" xr:uid="{1621DB9C-9C0A-4BF0-9C52-E5363CE24C09}">
+    <dataValidation type="list" sqref="M339" xr:uid="{E922E3B6-DD57-4581-9FE5-386CDE0A77FB}">
       <formula1>=IF(L339&lt;&gt;"",INDIRECT(VLOOKUP(L339,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N339" xr:uid="{0C6C2992-3092-41F2-81EB-8CF2E5D198C1}">
+    <dataValidation type="list" sqref="N339" xr:uid="{C67DAFE8-0AB0-49E9-AF8F-247839DDBA61}">
       <formula1>=IF(M339&lt;&gt;"",INDIRECT(VLOOKUP(M339,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M340" xr:uid="{51AA26D3-0FCC-403E-B9AA-C479BED3A7C1}">
+    <dataValidation type="list" sqref="M340" xr:uid="{D802C5E2-428F-4AF6-91C6-29BD8343C2A6}">
       <formula1>=IF(L340&lt;&gt;"",INDIRECT(VLOOKUP(L340,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N340" xr:uid="{8FF14215-7C92-43BE-B96D-3F6116BBBD0E}">
+    <dataValidation type="list" sqref="N340" xr:uid="{18EEE1A8-17FB-4D50-9609-E7B662080C76}">
       <formula1>=IF(M340&lt;&gt;"",INDIRECT(VLOOKUP(M340,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M341" xr:uid="{1CF5295A-CB00-4639-9FA6-CC53FE910E18}">
+    <dataValidation type="list" sqref="M341" xr:uid="{BFA68EA0-19E9-42B9-A83D-6CA70DA596E5}">
       <formula1>=IF(L341&lt;&gt;"",INDIRECT(VLOOKUP(L341,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N341" xr:uid="{D2AB6A0C-03EA-47BA-AFF2-5091B74E1DC1}">
+    <dataValidation type="list" sqref="N341" xr:uid="{D3F9488C-EDE7-47F5-8B7D-81CCBE0830B5}">
       <formula1>=IF(M341&lt;&gt;"",INDIRECT(VLOOKUP(M341,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M342" xr:uid="{D9C800E3-FE22-4C03-8562-280C8A902B33}">
+    <dataValidation type="list" sqref="M342" xr:uid="{0DE357B6-2C9E-4896-9DE2-0382698CB3FC}">
       <formula1>=IF(L342&lt;&gt;"",INDIRECT(VLOOKUP(L342,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N342" xr:uid="{C8504821-7A0F-4AEB-94C7-998DE8C33C69}">
+    <dataValidation type="list" sqref="N342" xr:uid="{F669B9BC-FEBD-41D8-8D78-97DB856B5B6E}">
       <formula1>=IF(M342&lt;&gt;"",INDIRECT(VLOOKUP(M342,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M343" xr:uid="{E1A61397-DBC0-406F-B104-1A57ECB61D55}">
+    <dataValidation type="list" sqref="M343" xr:uid="{FB7AB26E-2BD3-4713-B96E-37AFF73DB38F}">
       <formula1>=IF(L343&lt;&gt;"",INDIRECT(VLOOKUP(L343,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N343" xr:uid="{2DCCAAB7-EC89-4F2C-892E-522E65B0D787}">
+    <dataValidation type="list" sqref="N343" xr:uid="{90E8160A-DEDA-42CC-A760-92C1069298E6}">
       <formula1>=IF(M343&lt;&gt;"",INDIRECT(VLOOKUP(M343,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M344" xr:uid="{D1672970-0735-469A-8AE6-6124EB3DB59F}">
+    <dataValidation type="list" sqref="M344" xr:uid="{1D300E8E-C0C1-496C-B0CD-03F3C030769F}">
       <formula1>=IF(L344&lt;&gt;"",INDIRECT(VLOOKUP(L344,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N344" xr:uid="{71932622-6299-481F-83F6-93D411854CC1}">
+    <dataValidation type="list" sqref="N344" xr:uid="{7B0280C5-2747-450F-A99B-43337B9A026E}">
       <formula1>=IF(M344&lt;&gt;"",INDIRECT(VLOOKUP(M344,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M345" xr:uid="{C3189182-7CB1-4B82-A97E-C2D464F0F2BC}">
+    <dataValidation type="list" sqref="M345" xr:uid="{2699CE29-0AA0-4E07-9AED-5ECDAD491A0B}">
       <formula1>=IF(L345&lt;&gt;"",INDIRECT(VLOOKUP(L345,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N345" xr:uid="{17A16A8B-E21B-4FBF-B906-BC51D6702AA7}">
+    <dataValidation type="list" sqref="N345" xr:uid="{D204EA73-11CF-4A6A-9680-230A8BC14618}">
       <formula1>=IF(M345&lt;&gt;"",INDIRECT(VLOOKUP(M345,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M346" xr:uid="{1DC253AA-6E23-4814-837C-033C66725985}">
+    <dataValidation type="list" sqref="M346" xr:uid="{1BFA1A75-1C88-44FD-856B-1A25D4621E96}">
       <formula1>=IF(L346&lt;&gt;"",INDIRECT(VLOOKUP(L346,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N346" xr:uid="{29A1A6A9-166D-45A3-B215-8FBFB13C0DE3}">
+    <dataValidation type="list" sqref="N346" xr:uid="{5FD065D6-1C47-437F-95B5-507EE6593351}">
       <formula1>=IF(M346&lt;&gt;"",INDIRECT(VLOOKUP(M346,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M347" xr:uid="{539154A4-7EE9-42F0-BAB0-DFC0C8967B7F}">
+    <dataValidation type="list" sqref="M347" xr:uid="{1B65C33F-CC6C-4A8C-853A-918C7AA4C357}">
       <formula1>=IF(L347&lt;&gt;"",INDIRECT(VLOOKUP(L347,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N347" xr:uid="{88464E49-ED61-4015-A870-438D43CC5A6C}">
+    <dataValidation type="list" sqref="N347" xr:uid="{EA96B2A2-9E9C-470C-BDF6-30C43D2434E1}">
       <formula1>=IF(M347&lt;&gt;"",INDIRECT(VLOOKUP(M347,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M348" xr:uid="{5F1A9908-7F46-48A8-88B6-8A90DDFA045E}">
+    <dataValidation type="list" sqref="M348" xr:uid="{D2DCA402-10D2-4317-8CE0-85A9A83A4D5E}">
       <formula1>=IF(L348&lt;&gt;"",INDIRECT(VLOOKUP(L348,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N348" xr:uid="{744F9162-246C-4F18-AAA9-4EF3DCDD4A7C}">
+    <dataValidation type="list" sqref="N348" xr:uid="{33632A3C-6A1B-4AEE-80F0-829BB2B9ED6F}">
       <formula1>=IF(M348&lt;&gt;"",INDIRECT(VLOOKUP(M348,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M349" xr:uid="{6D97FA64-068E-489B-A9FE-1F8CB943977E}">
+    <dataValidation type="list" sqref="M349" xr:uid="{3A97BEF6-EEE3-4554-8D49-18B0432EF394}">
       <formula1>=IF(L349&lt;&gt;"",INDIRECT(VLOOKUP(L349,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N349" xr:uid="{82A1B682-65B5-4540-A5D4-8E88CB95F5BE}">
+    <dataValidation type="list" sqref="N349" xr:uid="{612C7BE4-808A-456C-8E36-A6E1540D2120}">
       <formula1>=IF(M349&lt;&gt;"",INDIRECT(VLOOKUP(M349,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M350" xr:uid="{F013E2E5-2A67-4786-8A7C-9D9CABAD9400}">
+    <dataValidation type="list" sqref="M350" xr:uid="{A2E88802-7FE7-4814-97CC-119850D936D6}">
       <formula1>=IF(L350&lt;&gt;"",INDIRECT(VLOOKUP(L350,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N350" xr:uid="{0666F5D4-95E7-4882-A33A-03D49748FA35}">
+    <dataValidation type="list" sqref="N350" xr:uid="{E256F1A8-93D9-4751-9571-DA4960666F59}">
       <formula1>=IF(M350&lt;&gt;"",INDIRECT(VLOOKUP(M350,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M351" xr:uid="{9018363C-787A-4550-A10D-02218D04C5EC}">
+    <dataValidation type="list" sqref="M351" xr:uid="{3CBAC05F-BDDD-4DA2-9CAA-6B923C4AFF5A}">
       <formula1>=IF(L351&lt;&gt;"",INDIRECT(VLOOKUP(L351,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N351" xr:uid="{6456FA28-1BC0-45A4-A409-D6463F101F78}">
+    <dataValidation type="list" sqref="N351" xr:uid="{08200D9F-E006-4DA9-9924-1F2A09961AAC}">
       <formula1>=IF(M351&lt;&gt;"",INDIRECT(VLOOKUP(M351,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M352" xr:uid="{07BA2028-E25B-4845-85A2-7A069693A7F1}">
+    <dataValidation type="list" sqref="M352" xr:uid="{81EE10F6-2897-4D9C-932D-7EAA68D92B4C}">
       <formula1>=IF(L352&lt;&gt;"",INDIRECT(VLOOKUP(L352,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N352" xr:uid="{59DA6E05-EFC0-4A7D-A9FF-07EBBC3FC92F}">
+    <dataValidation type="list" sqref="N352" xr:uid="{F9796CDB-2CB9-457D-815D-2E508E57192A}">
       <formula1>=IF(M352&lt;&gt;"",INDIRECT(VLOOKUP(M352,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M353" xr:uid="{A010DB68-C65B-4708-96A1-997B362DD337}">
+    <dataValidation type="list" sqref="M353" xr:uid="{B677DEE8-E913-4F67-9628-432FD738EA73}">
       <formula1>=IF(L353&lt;&gt;"",INDIRECT(VLOOKUP(L353,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N353" xr:uid="{2D962098-0309-4D25-8681-D44B49512BC3}">
+    <dataValidation type="list" sqref="N353" xr:uid="{426D3FA4-62B1-4B60-9F25-D379AC193A22}">
       <formula1>=IF(M353&lt;&gt;"",INDIRECT(VLOOKUP(M353,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M354" xr:uid="{C2B934DD-941F-41F2-B42E-493D82446A4B}">
+    <dataValidation type="list" sqref="M354" xr:uid="{9E9387CC-315B-48E5-8B68-89707FAC3A75}">
       <formula1>=IF(L354&lt;&gt;"",INDIRECT(VLOOKUP(L354,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N354" xr:uid="{25E08BBF-6230-4BD8-AAD9-5A8B6D0294D8}">
+    <dataValidation type="list" sqref="N354" xr:uid="{8DE506A8-08CB-4D94-B68A-57990F6B025F}">
       <formula1>=IF(M354&lt;&gt;"",INDIRECT(VLOOKUP(M354,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M355" xr:uid="{8933D198-8D46-4EF9-A864-4858FA548018}">
+    <dataValidation type="list" sqref="M355" xr:uid="{9C867E0C-A6D4-406D-9A84-88D274289FA9}">
       <formula1>=IF(L355&lt;&gt;"",INDIRECT(VLOOKUP(L355,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N355" xr:uid="{ED713B99-7A5E-4CCB-BB70-225314CF9F8B}">
+    <dataValidation type="list" sqref="N355" xr:uid="{071BF5B9-84D9-4DC5-BA8E-EE27EF6E99EC}">
       <formula1>=IF(M355&lt;&gt;"",INDIRECT(VLOOKUP(M355,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M356" xr:uid="{206780F6-19D5-4B8F-B20F-156E31F881E9}">
+    <dataValidation type="list" sqref="M356" xr:uid="{6F9132E2-E376-466B-97F6-AE7EDB12C09B}">
       <formula1>=IF(L356&lt;&gt;"",INDIRECT(VLOOKUP(L356,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N356" xr:uid="{E659BB7E-6EEF-4006-90A3-41FB86B8211F}">
+    <dataValidation type="list" sqref="N356" xr:uid="{44201E87-FCB9-495B-997C-C96A77063922}">
       <formula1>=IF(M356&lt;&gt;"",INDIRECT(VLOOKUP(M356,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M357" xr:uid="{95EA50FC-C66B-493E-9354-04EBB84DAAB6}">
+    <dataValidation type="list" sqref="M357" xr:uid="{D093FEEA-D85C-4085-BE19-D922F7BE3995}">
       <formula1>=IF(L357&lt;&gt;"",INDIRECT(VLOOKUP(L357,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N357" xr:uid="{9D7AA368-59B6-489C-874F-9FFBA7AA0A31}">
+    <dataValidation type="list" sqref="N357" xr:uid="{95DF5EFF-FEB0-4A36-897E-C12278912215}">
       <formula1>=IF(M357&lt;&gt;"",INDIRECT(VLOOKUP(M357,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M358" xr:uid="{EC15E681-EDA7-4D2E-A838-BDAACC9B7726}">
+    <dataValidation type="list" sqref="M358" xr:uid="{54A0D1BE-A67A-410F-BE1A-6A592EF0A1CE}">
       <formula1>=IF(L358&lt;&gt;"",INDIRECT(VLOOKUP(L358,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N358" xr:uid="{AAA16396-5240-4A13-B03A-F5D23744FBDD}">
+    <dataValidation type="list" sqref="N358" xr:uid="{8DB3B683-FAD9-4612-8093-9658BB01E369}">
       <formula1>=IF(M358&lt;&gt;"",INDIRECT(VLOOKUP(M358,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M359" xr:uid="{0329CBD0-8B51-410D-B53E-AB07D6FB2DC6}">
+    <dataValidation type="list" sqref="M359" xr:uid="{98C95B9E-3EE8-48B7-BDDE-9FBFEE90B334}">
       <formula1>=IF(L359&lt;&gt;"",INDIRECT(VLOOKUP(L359,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N359" xr:uid="{03F1A03E-F41F-4530-B868-7F5E239DF98F}">
+    <dataValidation type="list" sqref="N359" xr:uid="{964A138C-4945-48AC-98E3-8098AE2C89F8}">
       <formula1>=IF(M359&lt;&gt;"",INDIRECT(VLOOKUP(M359,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M360" xr:uid="{9D0FC236-4F5F-4B8E-AD33-0585C367B9F6}">
+    <dataValidation type="list" sqref="M360" xr:uid="{FDA1FA9B-922D-4A48-9D0D-674158D479AE}">
       <formula1>=IF(L360&lt;&gt;"",INDIRECT(VLOOKUP(L360,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N360" xr:uid="{07CC6955-76FA-467D-8E7D-570E4729F4E5}">
+    <dataValidation type="list" sqref="N360" xr:uid="{F35DA161-834B-4502-B3EE-4D9744F865E9}">
       <formula1>=IF(M360&lt;&gt;"",INDIRECT(VLOOKUP(M360,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M361" xr:uid="{376F6012-B13D-45CA-8519-5C6B77CF41B1}">
+    <dataValidation type="list" sqref="M361" xr:uid="{C5BC65E6-B96B-4752-9196-694D8DBDF95D}">
       <formula1>=IF(L361&lt;&gt;"",INDIRECT(VLOOKUP(L361,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N361" xr:uid="{E97D799D-3517-45C1-8877-F8E7FAB08F4F}">
+    <dataValidation type="list" sqref="N361" xr:uid="{D7F4193E-7AC4-4D14-AA1D-73A4EB2C99FB}">
       <formula1>=IF(M361&lt;&gt;"",INDIRECT(VLOOKUP(M361,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M362" xr:uid="{1BFA8BB7-2CF0-46C9-94DA-36A15AB69603}">
+    <dataValidation type="list" sqref="M362" xr:uid="{6009887E-85AE-403E-86D5-92C23CDDA18B}">
       <formula1>=IF(L362&lt;&gt;"",INDIRECT(VLOOKUP(L362,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N362" xr:uid="{153644F0-B368-46DE-84BE-15754C3CC297}">
+    <dataValidation type="list" sqref="N362" xr:uid="{39D2B13D-26CE-42BB-B73F-A8B96E1E5621}">
       <formula1>=IF(M362&lt;&gt;"",INDIRECT(VLOOKUP(M362,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M363" xr:uid="{31B35233-AFB8-4424-88F0-C017C766B17F}">
+    <dataValidation type="list" sqref="M363" xr:uid="{4E71C43B-19C4-4DCA-B03B-84D55DD466D0}">
       <formula1>=IF(L363&lt;&gt;"",INDIRECT(VLOOKUP(L363,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N363" xr:uid="{528C13B5-E4B0-41F8-85A4-72689395FB57}">
+    <dataValidation type="list" sqref="N363" xr:uid="{717AFD61-B4A7-451F-BC67-3F38DBEF63BE}">
       <formula1>=IF(M363&lt;&gt;"",INDIRECT(VLOOKUP(M363,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M364" xr:uid="{9346A8FE-72EF-4360-B364-AF5538A2C845}">
+    <dataValidation type="list" sqref="M364" xr:uid="{6022C49B-1952-4E3E-842B-AC8A3E2A71A2}">
       <formula1>=IF(L364&lt;&gt;"",INDIRECT(VLOOKUP(L364,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N364" xr:uid="{023C025D-A5D5-441D-A1BE-F812B1D85200}">
+    <dataValidation type="list" sqref="N364" xr:uid="{BBE532E1-39FF-4473-A523-FB8DED265D2A}">
       <formula1>=IF(M364&lt;&gt;"",INDIRECT(VLOOKUP(M364,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M365" xr:uid="{A73E381A-B729-4316-A46F-911AC3291B66}">
+    <dataValidation type="list" sqref="M365" xr:uid="{6308F528-C952-417C-97A5-6F7BDF8CE96B}">
       <formula1>=IF(L365&lt;&gt;"",INDIRECT(VLOOKUP(L365,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N365" xr:uid="{DB532F7C-EB6A-43F1-8610-48446C2736B3}">
+    <dataValidation type="list" sqref="N365" xr:uid="{C677AAA7-BCC2-47AE-AC72-D38FCB567110}">
       <formula1>=IF(M365&lt;&gt;"",INDIRECT(VLOOKUP(M365,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M366" xr:uid="{09C2DBCE-A7D3-4507-864C-306736DE34D8}">
+    <dataValidation type="list" sqref="M366" xr:uid="{8A3BDE63-7ACC-4B8B-9471-695B200BDCD9}">
       <formula1>=IF(L366&lt;&gt;"",INDIRECT(VLOOKUP(L366,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N366" xr:uid="{753C920C-C343-4660-8A16-367D255FD756}">
+    <dataValidation type="list" sqref="N366" xr:uid="{428D25FD-45E2-4D64-9C11-ECD4BC45830B}">
       <formula1>=IF(M366&lt;&gt;"",INDIRECT(VLOOKUP(M366,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M367" xr:uid="{05796DB3-69CF-47A3-ADF8-DABC34077670}">
+    <dataValidation type="list" sqref="M367" xr:uid="{BDA287EC-1506-4664-BA45-A40AF9D93CD4}">
       <formula1>=IF(L367&lt;&gt;"",INDIRECT(VLOOKUP(L367,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N367" xr:uid="{A64CD3C6-4C3F-4035-99EE-DACF5C56F562}">
+    <dataValidation type="list" sqref="N367" xr:uid="{53E6EF25-D8A6-41FA-95DC-F5F632F91B19}">
       <formula1>=IF(M367&lt;&gt;"",INDIRECT(VLOOKUP(M367,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M368" xr:uid="{AEE957A2-9D6F-41D2-93B3-E710144B07DA}">
+    <dataValidation type="list" sqref="M368" xr:uid="{2241A5AB-F961-4A64-8837-45EC59D97B35}">
       <formula1>=IF(L368&lt;&gt;"",INDIRECT(VLOOKUP(L368,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N368" xr:uid="{002DBA2A-A715-4AD4-903D-E79EA5787FE0}">
+    <dataValidation type="list" sqref="N368" xr:uid="{4656C7AC-72AB-41EF-A613-C5CB916E158B}">
       <formula1>=IF(M368&lt;&gt;"",INDIRECT(VLOOKUP(M368,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M369" xr:uid="{956FFC50-32B6-41C6-B5B3-35C158431359}">
+    <dataValidation type="list" sqref="M369" xr:uid="{0DF8D63E-53D0-4FB3-867A-5939AD8C4414}">
       <formula1>=IF(L369&lt;&gt;"",INDIRECT(VLOOKUP(L369,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N369" xr:uid="{14AAA75E-212D-412A-890F-58620FA31E3A}">
+    <dataValidation type="list" sqref="N369" xr:uid="{129C12AB-2E60-40A9-B361-11491BA97877}">
       <formula1>=IF(M369&lt;&gt;"",INDIRECT(VLOOKUP(M369,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M370" xr:uid="{A2883624-2B8A-4630-97BC-A1B315E58152}">
+    <dataValidation type="list" sqref="M370" xr:uid="{D1369FFB-55E4-4B02-986F-06AB6871E5E6}">
       <formula1>=IF(L370&lt;&gt;"",INDIRECT(VLOOKUP(L370,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N370" xr:uid="{8D784518-8653-4911-A98A-9A7A92EAFDB4}">
+    <dataValidation type="list" sqref="N370" xr:uid="{869C1127-A2D1-48B8-804B-B7B3CEBC6F77}">
       <formula1>=IF(M370&lt;&gt;"",INDIRECT(VLOOKUP(M370,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M371" xr:uid="{F78D89E0-B46E-475C-A183-2F65AAD0CEAC}">
+    <dataValidation type="list" sqref="M371" xr:uid="{D5005FED-2320-4F8B-BCD7-39FCA966C7C1}">
       <formula1>=IF(L371&lt;&gt;"",INDIRECT(VLOOKUP(L371,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N371" xr:uid="{A94AF9BA-99D5-4B47-A634-18D30D344E3B}">
+    <dataValidation type="list" sqref="N371" xr:uid="{C64C8DFC-A51A-4AEC-9253-C46F111E9FC6}">
       <formula1>=IF(M371&lt;&gt;"",INDIRECT(VLOOKUP(M371,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M372" xr:uid="{9E1F35C3-036E-4ED4-B18E-007432613401}">
+    <dataValidation type="list" sqref="M372" xr:uid="{07857ECD-9F2C-4B32-9BBA-61CC1FB2948A}">
       <formula1>=IF(L372&lt;&gt;"",INDIRECT(VLOOKUP(L372,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N372" xr:uid="{4D8C67C2-F826-4053-9016-9F750D891F47}">
+    <dataValidation type="list" sqref="N372" xr:uid="{8EB6C6E2-6DAF-4DAF-9E7B-16D405F1B20F}">
       <formula1>=IF(M372&lt;&gt;"",INDIRECT(VLOOKUP(M372,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M373" xr:uid="{36D1D393-AC08-438C-A493-6D0B8F0936BC}">
+    <dataValidation type="list" sqref="M373" xr:uid="{738CB923-C8A3-4B8C-8F41-CED476B93EE9}">
       <formula1>=IF(L373&lt;&gt;"",INDIRECT(VLOOKUP(L373,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N373" xr:uid="{E77F8B13-1336-4753-B269-977A30EDE641}">
+    <dataValidation type="list" sqref="N373" xr:uid="{9F282A25-B217-4AD4-9C98-997749C43EF7}">
       <formula1>=IF(M373&lt;&gt;"",INDIRECT(VLOOKUP(M373,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M374" xr:uid="{542EE042-E9C1-4D4A-B26C-38855BEC5649}">
+    <dataValidation type="list" sqref="M374" xr:uid="{675FDA31-DA13-46B1-AF4E-8A120692B6DD}">
       <formula1>=IF(L374&lt;&gt;"",INDIRECT(VLOOKUP(L374,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N374" xr:uid="{9F05D587-43F5-416C-B88C-0A686B308955}">
+    <dataValidation type="list" sqref="N374" xr:uid="{EFF51B60-8E74-43B4-AD86-236359A305D1}">
       <formula1>=IF(M374&lt;&gt;"",INDIRECT(VLOOKUP(M374,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M375" xr:uid="{53822EB1-9BB5-4507-9431-A030C08A9FB9}">
+    <dataValidation type="list" sqref="M375" xr:uid="{65F1E3A8-A08B-4ADB-BF06-82B1BF46B1E0}">
       <formula1>=IF(L375&lt;&gt;"",INDIRECT(VLOOKUP(L375,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N375" xr:uid="{C2446AD0-33D0-4407-BC21-B976F0CA3006}">
+    <dataValidation type="list" sqref="N375" xr:uid="{AA04AB16-4166-4D83-9391-E27C3F7F3D2D}">
       <formula1>=IF(M375&lt;&gt;"",INDIRECT(VLOOKUP(M375,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M376" xr:uid="{FB7EF20F-ECF4-4D24-9782-06AFDF99EA6B}">
+    <dataValidation type="list" sqref="M376" xr:uid="{FD3833E9-8150-4DDA-9522-6F3D81D4CB84}">
       <formula1>=IF(L376&lt;&gt;"",INDIRECT(VLOOKUP(L376,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N376" xr:uid="{4C2B1AB7-C169-4DA6-9D62-F6564CAC081B}">
+    <dataValidation type="list" sqref="N376" xr:uid="{2ED0FB75-5287-4683-B502-C1EE35628D5D}">
       <formula1>=IF(M376&lt;&gt;"",INDIRECT(VLOOKUP(M376,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M377" xr:uid="{899783B9-9639-4AA2-A00B-ACD2715D2E18}">
+    <dataValidation type="list" sqref="M377" xr:uid="{C8C1105D-DA1A-47C7-B9FB-EE14632483FA}">
       <formula1>=IF(L377&lt;&gt;"",INDIRECT(VLOOKUP(L377,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N377" xr:uid="{CA31FD9E-EA93-4670-B0FE-AADB2C6B2DD7}">
+    <dataValidation type="list" sqref="N377" xr:uid="{48CA75D3-D9B9-4C16-8DB9-A4C717026118}">
       <formula1>=IF(M377&lt;&gt;"",INDIRECT(VLOOKUP(M377,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M378" xr:uid="{6FE23A6F-F424-4C70-9CBB-948B88872217}">
+    <dataValidation type="list" sqref="M378" xr:uid="{264EC2C1-2562-4514-886F-7BDB2E79462E}">
       <formula1>=IF(L378&lt;&gt;"",INDIRECT(VLOOKUP(L378,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N378" xr:uid="{1225FA3C-7B38-4706-B363-92729D5BBE20}">
+    <dataValidation type="list" sqref="N378" xr:uid="{2E4A4167-D31A-454D-92FE-6E3601C0C6B4}">
       <formula1>=IF(M378&lt;&gt;"",INDIRECT(VLOOKUP(M378,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M379" xr:uid="{5694F898-2EF1-4292-A132-74A2B2AD960D}">
+    <dataValidation type="list" sqref="M379" xr:uid="{9675D742-6EB9-4AD4-84A7-4E81BEC8A67B}">
       <formula1>=IF(L379&lt;&gt;"",INDIRECT(VLOOKUP(L379,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N379" xr:uid="{716E3170-8F75-4C32-BB1D-ED3F19F13577}">
+    <dataValidation type="list" sqref="N379" xr:uid="{09B7FC94-E100-4588-9192-A4DB8A3B12D7}">
       <formula1>=IF(M379&lt;&gt;"",INDIRECT(VLOOKUP(M379,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M380" xr:uid="{573277C7-678C-4310-BF83-CE539D15E1E5}">
+    <dataValidation type="list" sqref="M380" xr:uid="{717654CB-0686-4226-A5F8-BA98F21322BD}">
       <formula1>=IF(L380&lt;&gt;"",INDIRECT(VLOOKUP(L380,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N380" xr:uid="{06D91303-93CB-455B-A2F2-2E491C13C83B}">
+    <dataValidation type="list" sqref="N380" xr:uid="{733C23EF-2046-473A-8C5E-280EACD26775}">
       <formula1>=IF(M380&lt;&gt;"",INDIRECT(VLOOKUP(M380,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M381" xr:uid="{E33EB9FE-584B-4B7E-82E1-DC1F8E000CA1}">
+    <dataValidation type="list" sqref="M381" xr:uid="{49411AA1-83E2-4EAE-9A0A-99C9F60EE8CD}">
       <formula1>=IF(L381&lt;&gt;"",INDIRECT(VLOOKUP(L381,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N381" xr:uid="{EAD57FA5-6B58-4C2E-BBB6-9908B840251E}">
+    <dataValidation type="list" sqref="N381" xr:uid="{BFAB3F5D-AE14-4E61-9E75-920B0587CA1C}">
       <formula1>=IF(M381&lt;&gt;"",INDIRECT(VLOOKUP(M381,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M382" xr:uid="{C60EFA91-5632-478F-B2B1-C76832BDAC5C}">
+    <dataValidation type="list" sqref="M382" xr:uid="{679F3B63-7F37-49F0-8A0B-9F56B798C782}">
       <formula1>=IF(L382&lt;&gt;"",INDIRECT(VLOOKUP(L382,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N382" xr:uid="{FF8434F3-E97F-4DD1-A5FB-C7B1B9634882}">
+    <dataValidation type="list" sqref="N382" xr:uid="{20635424-C226-4CEC-BDE9-FAD723E7706C}">
       <formula1>=IF(M382&lt;&gt;"",INDIRECT(VLOOKUP(M382,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M383" xr:uid="{7C3169FC-E94B-4259-8652-6A0D76C15354}">
+    <dataValidation type="list" sqref="M383" xr:uid="{A0E21AC0-3F38-42F0-ABCC-77ABEED19512}">
       <formula1>=IF(L383&lt;&gt;"",INDIRECT(VLOOKUP(L383,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N383" xr:uid="{B73B0751-A92E-4FF8-9C86-BEB00D4B1ADE}">
+    <dataValidation type="list" sqref="N383" xr:uid="{60EA9EE7-4523-4D05-8CC9-081A44732118}">
       <formula1>=IF(M383&lt;&gt;"",INDIRECT(VLOOKUP(M383,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M384" xr:uid="{6A3B84DB-68C1-4A7E-AF0F-A0E7233C6A51}">
+    <dataValidation type="list" sqref="M384" xr:uid="{4E16AA84-6B5D-4429-8A75-131C4C082A84}">
       <formula1>=IF(L384&lt;&gt;"",INDIRECT(VLOOKUP(L384,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N384" xr:uid="{B6DA3D85-00E7-4E4C-BED2-47550921ED38}">
+    <dataValidation type="list" sqref="N384" xr:uid="{74EB22DB-6D9D-4E56-BD71-DA89267487C1}">
       <formula1>=IF(M384&lt;&gt;"",INDIRECT(VLOOKUP(M384,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M385" xr:uid="{AC5D33AB-AE6E-4231-A0AD-68F4958DA790}">
+    <dataValidation type="list" sqref="M385" xr:uid="{3806EDB9-8B22-4FCA-BE1E-5C60074B5EED}">
       <formula1>=IF(L385&lt;&gt;"",INDIRECT(VLOOKUP(L385,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N385" xr:uid="{82CA05E6-1ECE-4562-AF3D-D30DC45CDDA1}">
+    <dataValidation type="list" sqref="N385" xr:uid="{D7778FEC-2ED9-4247-AC30-F800B60FCE9A}">
       <formula1>=IF(M385&lt;&gt;"",INDIRECT(VLOOKUP(M385,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M386" xr:uid="{125A89D1-8F60-4888-94BC-867BC8215AC9}">
+    <dataValidation type="list" sqref="M386" xr:uid="{A6E2705B-153D-40E3-BE83-398D1B3B8CF6}">
       <formula1>=IF(L386&lt;&gt;"",INDIRECT(VLOOKUP(L386,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N386" xr:uid="{CB6EDF45-E680-4447-8CA7-7E4C668E9F25}">
+    <dataValidation type="list" sqref="N386" xr:uid="{EDB95191-F346-4381-9BD8-CD66971003B3}">
       <formula1>=IF(M386&lt;&gt;"",INDIRECT(VLOOKUP(M386,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M387" xr:uid="{5B4720FF-F76D-49DA-844D-222FC0D36FA6}">
+    <dataValidation type="list" sqref="M387" xr:uid="{6283953B-E716-495B-A28A-2488244B6C37}">
       <formula1>=IF(L387&lt;&gt;"",INDIRECT(VLOOKUP(L387,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N387" xr:uid="{E67920DB-8F06-4239-ACFA-DC276F0B7B71}">
+    <dataValidation type="list" sqref="N387" xr:uid="{A12FF69E-A5BE-44BB-9A5A-03254A1C040A}">
       <formula1>=IF(M387&lt;&gt;"",INDIRECT(VLOOKUP(M387,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M388" xr:uid="{3BABB16E-1B10-4D1C-B622-1B32494AEA8D}">
+    <dataValidation type="list" sqref="M388" xr:uid="{399CAE88-E181-4721-9FEB-FF1410008264}">
       <formula1>=IF(L388&lt;&gt;"",INDIRECT(VLOOKUP(L388,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N388" xr:uid="{726F25AB-B65C-4298-A383-811FEEF93C2B}">
+    <dataValidation type="list" sqref="N388" xr:uid="{06D43E7A-3B86-453F-846B-C688AE9FAA8D}">
       <formula1>=IF(M388&lt;&gt;"",INDIRECT(VLOOKUP(M388,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M389" xr:uid="{D871857B-DA0E-4FA4-9B49-E2A0D5149B2B}">
+    <dataValidation type="list" sqref="M389" xr:uid="{F8D8BA3C-080E-411A-A62F-1D606821D286}">
       <formula1>=IF(L389&lt;&gt;"",INDIRECT(VLOOKUP(L389,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N389" xr:uid="{72F53D8B-3C8A-4268-8511-C5F3191674F1}">
+    <dataValidation type="list" sqref="N389" xr:uid="{74540B87-2955-4317-AB4C-6F97C1119642}">
       <formula1>=IF(M389&lt;&gt;"",INDIRECT(VLOOKUP(M389,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M390" xr:uid="{7F9A256E-B940-42FE-BD1D-ADDD123E8826}">
+    <dataValidation type="list" sqref="M390" xr:uid="{902FE08B-C1A8-4342-AB75-C4F28A82629B}">
       <formula1>=IF(L390&lt;&gt;"",INDIRECT(VLOOKUP(L390,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N390" xr:uid="{D8D1E7E1-1067-4797-8774-D89F846C348C}">
+    <dataValidation type="list" sqref="N390" xr:uid="{2BEABD47-CD81-42F4-A38B-7B53FACD0A74}">
       <formula1>=IF(M390&lt;&gt;"",INDIRECT(VLOOKUP(M390,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M391" xr:uid="{7D49CEF1-4BEB-4F77-9ACE-9E08FA8B8254}">
+    <dataValidation type="list" sqref="M391" xr:uid="{B67A0441-2F95-453C-9B62-C81D267288AF}">
       <formula1>=IF(L391&lt;&gt;"",INDIRECT(VLOOKUP(L391,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N391" xr:uid="{FCF2AA76-C3CD-42EA-85D0-8EC9434BAEF2}">
+    <dataValidation type="list" sqref="N391" xr:uid="{B9343F15-99DF-4084-BD39-F13D69C0C6D8}">
       <formula1>=IF(M391&lt;&gt;"",INDIRECT(VLOOKUP(M391,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M392" xr:uid="{B111A974-A94E-439C-BB8E-76B48FE34E65}">
+    <dataValidation type="list" sqref="M392" xr:uid="{DEF8829E-47D2-4A5C-9C02-D07899F22C56}">
       <formula1>=IF(L392&lt;&gt;"",INDIRECT(VLOOKUP(L392,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N392" xr:uid="{2ED66647-ED81-46E8-B5D2-FD5EEC6D8675}">
+    <dataValidation type="list" sqref="N392" xr:uid="{D6A2E648-C973-472F-9AA9-E7814FAA18B6}">
       <formula1>=IF(M392&lt;&gt;"",INDIRECT(VLOOKUP(M392,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M393" xr:uid="{8548CDBC-DF9D-4E07-9D52-9B716F922E1E}">
+    <dataValidation type="list" sqref="M393" xr:uid="{5C8FD48D-02DE-4B69-98EF-CC226F1031C8}">
       <formula1>=IF(L393&lt;&gt;"",INDIRECT(VLOOKUP(L393,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N393" xr:uid="{BE25BC98-FCD1-4883-8916-8240DBD44377}">
+    <dataValidation type="list" sqref="N393" xr:uid="{C751FB89-DCC9-4D22-B46A-8E3B82AC3BCF}">
       <formula1>=IF(M393&lt;&gt;"",INDIRECT(VLOOKUP(M393,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M394" xr:uid="{B2ECA8C6-7E85-4F1B-A3D0-B962D8E38B65}">
+    <dataValidation type="list" sqref="M394" xr:uid="{9B8601A6-C448-4372-8632-A46A37DCBD80}">
       <formula1>=IF(L394&lt;&gt;"",INDIRECT(VLOOKUP(L394,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N394" xr:uid="{D1437B04-F406-4FA0-BD5F-D259E7DA8024}">
+    <dataValidation type="list" sqref="N394" xr:uid="{BD94A041-1EDA-4BCF-8DC6-846E0EDD0751}">
       <formula1>=IF(M394&lt;&gt;"",INDIRECT(VLOOKUP(M394,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M395" xr:uid="{E44CF97F-621E-4FC3-B713-6EF549180A1C}">
+    <dataValidation type="list" sqref="M395" xr:uid="{7EA6695E-9965-4B19-8FED-1E629863CB0B}">
       <formula1>=IF(L395&lt;&gt;"",INDIRECT(VLOOKUP(L395,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N395" xr:uid="{234607CB-0DF1-44F9-96B4-CB19C7D39C3C}">
+    <dataValidation type="list" sqref="N395" xr:uid="{D7C691C4-682A-40D5-B5E5-E0E0129E01D0}">
       <formula1>=IF(M395&lt;&gt;"",INDIRECT(VLOOKUP(M395,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M396" xr:uid="{18443D40-9E4A-406F-B59D-35579D82B08B}">
+    <dataValidation type="list" sqref="M396" xr:uid="{5603C1EA-8AA0-48C4-A306-0F1FD7E150A6}">
       <formula1>=IF(L396&lt;&gt;"",INDIRECT(VLOOKUP(L396,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N396" xr:uid="{CFDC3940-E6FB-49EE-B14F-CD64638FAA15}">
+    <dataValidation type="list" sqref="N396" xr:uid="{1A80B56B-8CB5-47BD-BFA0-ACC8AFEAAE1A}">
       <formula1>=IF(M396&lt;&gt;"",INDIRECT(VLOOKUP(M396,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M397" xr:uid="{BFCA823D-8830-49BC-8C48-C899DB461197}">
+    <dataValidation type="list" sqref="M397" xr:uid="{61090B25-6DAE-4F82-9554-252D008577A4}">
       <formula1>=IF(L397&lt;&gt;"",INDIRECT(VLOOKUP(L397,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N397" xr:uid="{7FD54E60-D991-4DE6-92AA-C50D001A8BBB}">
+    <dataValidation type="list" sqref="N397" xr:uid="{6204C41D-7636-49E7-B096-517CE9880AE6}">
       <formula1>=IF(M397&lt;&gt;"",INDIRECT(VLOOKUP(M397,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M398" xr:uid="{5747A86F-BEDB-4923-8FAA-6B7CF4635DB2}">
+    <dataValidation type="list" sqref="M398" xr:uid="{42BB19B4-A930-4BD8-9993-C24221F625CF}">
       <formula1>=IF(L398&lt;&gt;"",INDIRECT(VLOOKUP(L398,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N398" xr:uid="{EC0457B1-140E-4273-9E41-A0F6AD8DC396}">
+    <dataValidation type="list" sqref="N398" xr:uid="{D58ED163-AD35-4D6A-B369-97F1E99D5BA7}">
       <formula1>=IF(M398&lt;&gt;"",INDIRECT(VLOOKUP(M398,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M399" xr:uid="{9EC4F950-02AA-42D0-B61C-654AF98DA707}">
+    <dataValidation type="list" sqref="M399" xr:uid="{41BCC9A1-DA14-4D3E-A779-16224116E227}">
       <formula1>=IF(L399&lt;&gt;"",INDIRECT(VLOOKUP(L399,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N399" xr:uid="{2363E6CF-A459-481D-8157-0DF468F7F55A}">
+    <dataValidation type="list" sqref="N399" xr:uid="{37F8D5F1-DDA9-4E82-96B5-DD96CD8B2BFC}">
       <formula1>=IF(M399&lt;&gt;"",INDIRECT(VLOOKUP(M399,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M400" xr:uid="{30B1F380-A5DD-4973-B039-E5B5D270EACF}">
+    <dataValidation type="list" sqref="M400" xr:uid="{9D9FE8FE-6A90-47AF-AE22-4AC3F2F2BC9D}">
       <formula1>=IF(L400&lt;&gt;"",INDIRECT(VLOOKUP(L400,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N400" xr:uid="{017006A6-0EAA-4946-8541-E1D53E70A40C}">
+    <dataValidation type="list" sqref="N400" xr:uid="{4B6E3D64-D37B-47A8-A3E2-54097D3452C7}">
       <formula1>=IF(M400&lt;&gt;"",INDIRECT(VLOOKUP(M400,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M401" xr:uid="{7DBF19CF-31CF-48B0-B189-C8407E7EEF05}">
+    <dataValidation type="list" sqref="M401" xr:uid="{03DD5F0A-7A18-4860-BC7C-BBA83A4AEAD0}">
       <formula1>=IF(L401&lt;&gt;"",INDIRECT(VLOOKUP(L401,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N401" xr:uid="{05BEC216-18D6-4823-927A-754440325C11}">
+    <dataValidation type="list" sqref="N401" xr:uid="{93A0D8C6-5360-4ED4-9B4B-D07BBBAAD5F9}">
       <formula1>=IF(M401&lt;&gt;"",INDIRECT(VLOOKUP(M401,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M402" xr:uid="{12D8A9D6-659B-4244-BDCE-A7948D9F7FA1}">
+    <dataValidation type="list" sqref="M402" xr:uid="{750C9B1C-27CD-43F7-8845-1967C0030842}">
       <formula1>=IF(L402&lt;&gt;"",INDIRECT(VLOOKUP(L402,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N402" xr:uid="{D06825E0-4A4C-4146-985C-FDDA89A163B9}">
+    <dataValidation type="list" sqref="N402" xr:uid="{938B0075-35C1-4959-A53A-E30AE9C67A17}">
       <formula1>=IF(M402&lt;&gt;"",INDIRECT(VLOOKUP(M402,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M403" xr:uid="{FA88B89C-FE67-41DB-BB37-ADB0C65755C4}">
+    <dataValidation type="list" sqref="M403" xr:uid="{2051B02B-A88E-4455-B9D8-61E1BF63D976}">
       <formula1>=IF(L403&lt;&gt;"",INDIRECT(VLOOKUP(L403,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N403" xr:uid="{CBB2956A-4A38-44EF-85B9-12C76A04FB8D}">
+    <dataValidation type="list" sqref="N403" xr:uid="{8381499D-3EE4-4800-AB51-2F81D77F6B37}">
       <formula1>=IF(M403&lt;&gt;"",INDIRECT(VLOOKUP(M403,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M404" xr:uid="{E16C614E-E1BE-472E-893B-A6E261BDE783}">
+    <dataValidation type="list" sqref="M404" xr:uid="{CB63D0FF-0C1E-47EA-8B17-2028183650F4}">
       <formula1>=IF(L404&lt;&gt;"",INDIRECT(VLOOKUP(L404,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N404" xr:uid="{795C3802-D7AC-4C72-A838-964ECE6C481A}">
+    <dataValidation type="list" sqref="N404" xr:uid="{0803E6B2-14CA-4CAF-9DFA-81D33C637367}">
       <formula1>=IF(M404&lt;&gt;"",INDIRECT(VLOOKUP(M404,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M405" xr:uid="{41D6688B-D4BE-4BF3-8CC7-D00BA40544EA}">
+    <dataValidation type="list" sqref="M405" xr:uid="{567AC2F9-EC2D-4D0F-975F-18946E74A4E3}">
       <formula1>=IF(L405&lt;&gt;"",INDIRECT(VLOOKUP(L405,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N405" xr:uid="{2DC2E5F5-6C61-4E2C-AD5F-B9D55F5D500E}">
+    <dataValidation type="list" sqref="N405" xr:uid="{930D94DE-5312-4935-B50E-B4D7B2F65FA9}">
       <formula1>=IF(M405&lt;&gt;"",INDIRECT(VLOOKUP(M405,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M406" xr:uid="{23E45A9D-D025-454D-932A-756307F806A2}">
+    <dataValidation type="list" sqref="M406" xr:uid="{03DA8B68-A6E7-4FE1-841A-8AA8F3FE9399}">
       <formula1>=IF(L406&lt;&gt;"",INDIRECT(VLOOKUP(L406,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N406" xr:uid="{193741D8-C25F-4917-A29B-5DC75B37A313}">
+    <dataValidation type="list" sqref="N406" xr:uid="{BBF6AC42-DBBA-4F0C-B0D6-D6FCA21E5148}">
       <formula1>=IF(M406&lt;&gt;"",INDIRECT(VLOOKUP(M406,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M407" xr:uid="{6FA6B96A-5D31-42BE-B81D-953939A7E5F6}">
+    <dataValidation type="list" sqref="M407" xr:uid="{40EF253A-E679-4781-A421-FB6DA13D302F}">
       <formula1>=IF(L407&lt;&gt;"",INDIRECT(VLOOKUP(L407,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N407" xr:uid="{AC3F2A56-3528-4F74-98E4-05D3B7A44EFC}">
+    <dataValidation type="list" sqref="N407" xr:uid="{614A285C-5E0A-4F41-987B-57523ACE8D9D}">
       <formula1>=IF(M407&lt;&gt;"",INDIRECT(VLOOKUP(M407,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M408" xr:uid="{DBAE2F50-DAB1-403A-B2F7-D598FBF4EF8D}">
+    <dataValidation type="list" sqref="M408" xr:uid="{D0CCDCC1-0702-4EB9-91C8-ED9C6684041C}">
       <formula1>=IF(L408&lt;&gt;"",INDIRECT(VLOOKUP(L408,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N408" xr:uid="{77045A05-78A9-4FC6-892F-681ABD806724}">
+    <dataValidation type="list" sqref="N408" xr:uid="{5481BB5E-0CE7-46DF-9AB5-F53F48EADFEB}">
       <formula1>=IF(M408&lt;&gt;"",INDIRECT(VLOOKUP(M408,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M409" xr:uid="{A918341F-D95F-407F-A7FC-007DD860E630}">
+    <dataValidation type="list" sqref="M409" xr:uid="{AD7CD579-66B8-4521-8880-E8AEA3E1B174}">
       <formula1>=IF(L409&lt;&gt;"",INDIRECT(VLOOKUP(L409,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N409" xr:uid="{1555526D-4D79-446D-9076-5B98413AF8BC}">
+    <dataValidation type="list" sqref="N409" xr:uid="{F23C9FD7-2D3B-414F-A882-70F80997F75F}">
       <formula1>=IF(M409&lt;&gt;"",INDIRECT(VLOOKUP(M409,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M410" xr:uid="{69E768D2-8871-493D-A166-79412445AB3C}">
+    <dataValidation type="list" sqref="M410" xr:uid="{460EEC5E-1924-414D-B777-A048C07722E5}">
       <formula1>=IF(L410&lt;&gt;"",INDIRECT(VLOOKUP(L410,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N410" xr:uid="{88F9B01A-D412-4E14-A2EC-CFEF47D54428}">
+    <dataValidation type="list" sqref="N410" xr:uid="{0B04B3F6-FB0F-424F-B1E7-9539BA7598F4}">
       <formula1>=IF(M410&lt;&gt;"",INDIRECT(VLOOKUP(M410,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M411" xr:uid="{D4C03A76-DF10-4C87-8048-6C4BEBBFA7BC}">
+    <dataValidation type="list" sqref="M411" xr:uid="{2B019089-0F90-4136-83EB-39971500D573}">
       <formula1>=IF(L411&lt;&gt;"",INDIRECT(VLOOKUP(L411,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N411" xr:uid="{973B8262-8033-49F5-BDB6-1250F9FACD63}">
+    <dataValidation type="list" sqref="N411" xr:uid="{64EA68FD-053E-4CB3-8FF2-3EB3E3C45635}">
       <formula1>=IF(M411&lt;&gt;"",INDIRECT(VLOOKUP(M411,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M412" xr:uid="{2579FA79-A669-4B73-8728-1B41C4AD8427}">
+    <dataValidation type="list" sqref="M412" xr:uid="{C91A218E-3104-4E35-B4AE-AD716FBFC552}">
       <formula1>=IF(L412&lt;&gt;"",INDIRECT(VLOOKUP(L412,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N412" xr:uid="{C7950FBA-BCCD-4FDB-B5E1-095D5F4085F9}">
+    <dataValidation type="list" sqref="N412" xr:uid="{37D12146-3D9E-406B-B801-0205858B15AE}">
       <formula1>=IF(M412&lt;&gt;"",INDIRECT(VLOOKUP(M412,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M413" xr:uid="{C61D4E91-5E39-428F-9BD7-F238C7845F12}">
+    <dataValidation type="list" sqref="M413" xr:uid="{2E28DDBF-6690-45DE-A9EF-1AC915578C97}">
       <formula1>=IF(L413&lt;&gt;"",INDIRECT(VLOOKUP(L413,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N413" xr:uid="{35F3B1AD-44FC-4B76-8FAF-275857F95973}">
+    <dataValidation type="list" sqref="N413" xr:uid="{1638AD38-AC03-44B9-A88C-E95DE99BD4FA}">
       <formula1>=IF(M413&lt;&gt;"",INDIRECT(VLOOKUP(M413,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M414" xr:uid="{21C0F06C-0FA1-494C-8E18-202266111971}">
+    <dataValidation type="list" sqref="M414" xr:uid="{E2122F90-CF2C-481C-B2E0-61220077F93A}">
       <formula1>=IF(L414&lt;&gt;"",INDIRECT(VLOOKUP(L414,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N414" xr:uid="{9A4B487C-9E20-4122-BFC7-9FA97D0938FF}">
+    <dataValidation type="list" sqref="N414" xr:uid="{3BE8BCD6-B035-40E2-B855-449EA52EBD36}">
       <formula1>=IF(M414&lt;&gt;"",INDIRECT(VLOOKUP(M414,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M415" xr:uid="{4A640F76-8FF0-48CA-AFBC-6C6E37387F8D}">
+    <dataValidation type="list" sqref="M415" xr:uid="{A2081919-A1D1-49DB-A01E-ACAFAFCCAC73}">
       <formula1>=IF(L415&lt;&gt;"",INDIRECT(VLOOKUP(L415,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N415" xr:uid="{722F37BB-B616-438C-8760-E92EA2415583}">
+    <dataValidation type="list" sqref="N415" xr:uid="{F5006E63-B1D5-4C20-A5D4-EE4C1DEE897A}">
       <formula1>=IF(M415&lt;&gt;"",INDIRECT(VLOOKUP(M415,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M416" xr:uid="{957E277B-CECD-4CEE-80FD-4613BA67F0CA}">
+    <dataValidation type="list" sqref="M416" xr:uid="{A1D25317-E2DE-4710-9DAE-3276575AE26E}">
       <formula1>=IF(L416&lt;&gt;"",INDIRECT(VLOOKUP(L416,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N416" xr:uid="{9134AE4F-C305-4283-B57F-E4A257EEFD48}">
+    <dataValidation type="list" sqref="N416" xr:uid="{23A672BD-3A93-4EF0-8703-BC3AD1589D57}">
       <formula1>=IF(M416&lt;&gt;"",INDIRECT(VLOOKUP(M416,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M417" xr:uid="{F04D890F-AB81-425B-9698-435F59A8D62D}">
+    <dataValidation type="list" sqref="M417" xr:uid="{B2173843-C8CF-479A-8253-2C319572A93E}">
       <formula1>=IF(L417&lt;&gt;"",INDIRECT(VLOOKUP(L417,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N417" xr:uid="{6388C078-6DB9-4074-8AA2-AA303BDE95F7}">
+    <dataValidation type="list" sqref="N417" xr:uid="{5310C1A5-EEF3-49F9-8F5E-267706DDE6E0}">
       <formula1>=IF(M417&lt;&gt;"",INDIRECT(VLOOKUP(M417,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M418" xr:uid="{31529489-0A00-4263-BA83-07C29E48D883}">
+    <dataValidation type="list" sqref="M418" xr:uid="{9C865950-AD13-4B0D-B28E-86CAEA90AD78}">
       <formula1>=IF(L418&lt;&gt;"",INDIRECT(VLOOKUP(L418,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N418" xr:uid="{C0CE1222-1B88-4388-A8B4-7C7B0F3B313D}">
+    <dataValidation type="list" sqref="N418" xr:uid="{71110688-F02F-4ED6-9141-354CE3D59D2B}">
       <formula1>=IF(M418&lt;&gt;"",INDIRECT(VLOOKUP(M418,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M419" xr:uid="{048B82D4-C4CC-4318-87E0-58A7E17F3CED}">
+    <dataValidation type="list" sqref="M419" xr:uid="{D7F45CE1-FFB0-48CB-8531-8A207D6101FB}">
       <formula1>=IF(L419&lt;&gt;"",INDIRECT(VLOOKUP(L419,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N419" xr:uid="{1642207C-5062-4B7F-A4E6-97EA87A57270}">
+    <dataValidation type="list" sqref="N419" xr:uid="{15310057-C1C9-4886-B367-05B197834CE6}">
       <formula1>=IF(M419&lt;&gt;"",INDIRECT(VLOOKUP(M419,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M420" xr:uid="{1CAFBB7C-238D-4E24-B2F2-8EE9CCC98FDE}">
+    <dataValidation type="list" sqref="M420" xr:uid="{91DBD65F-1750-4E91-9B6C-1AC934DA4047}">
       <formula1>=IF(L420&lt;&gt;"",INDIRECT(VLOOKUP(L420,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N420" xr:uid="{B7682BFE-5CFB-4347-833C-D93EFA085908}">
+    <dataValidation type="list" sqref="N420" xr:uid="{C452CCA5-5878-433F-A9EB-C7E25AF84104}">
       <formula1>=IF(M420&lt;&gt;"",INDIRECT(VLOOKUP(M420,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M421" xr:uid="{9C6D3E7C-0FCB-43C1-8684-DFAE7F14FC49}">
+    <dataValidation type="list" sqref="M421" xr:uid="{EE914D6E-A033-4E72-B0A8-D522098F213F}">
       <formula1>=IF(L421&lt;&gt;"",INDIRECT(VLOOKUP(L421,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N421" xr:uid="{C7D47C3A-621B-4676-9E1C-99B72DDCD1D1}">
+    <dataValidation type="list" sqref="N421" xr:uid="{AF8EEEB6-F75A-494E-80EB-EA0D66CA8D7B}">
       <formula1>=IF(M421&lt;&gt;"",INDIRECT(VLOOKUP(M421,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M422" xr:uid="{973CEBF2-5DDB-4E55-A72D-1FA54E0CE4B9}">
+    <dataValidation type="list" sqref="M422" xr:uid="{8CDE9417-DE0C-412E-B1CB-726EB924A85C}">
       <formula1>=IF(L422&lt;&gt;"",INDIRECT(VLOOKUP(L422,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N422" xr:uid="{BEB2E00C-6F36-4138-BD52-920DFDF76FDC}">
+    <dataValidation type="list" sqref="N422" xr:uid="{8AFD3DE8-3E7F-4964-92C5-5E27EF7E6D9A}">
       <formula1>=IF(M422&lt;&gt;"",INDIRECT(VLOOKUP(M422,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M423" xr:uid="{DFD9D21A-F069-45A1-80E3-51699B1C60BD}">
+    <dataValidation type="list" sqref="M423" xr:uid="{4B73CF17-679F-4D18-96B7-222765667C14}">
       <formula1>=IF(L423&lt;&gt;"",INDIRECT(VLOOKUP(L423,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N423" xr:uid="{0089442F-80C0-4D12-A1DA-78438ECE2EA0}">
+    <dataValidation type="list" sqref="N423" xr:uid="{61EF61EF-5D58-4B05-B8CF-07D075B976AD}">
       <formula1>=IF(M423&lt;&gt;"",INDIRECT(VLOOKUP(M423,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M424" xr:uid="{E806A6A8-F63C-4442-92AC-DEFC6D4592ED}">
+    <dataValidation type="list" sqref="M424" xr:uid="{E07F3552-58CF-41BB-A319-C74AF956DE3A}">
       <formula1>=IF(L424&lt;&gt;"",INDIRECT(VLOOKUP(L424,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N424" xr:uid="{83AB80DC-2BFF-4D6E-AFF9-8BE2B8739EDB}">
+    <dataValidation type="list" sqref="N424" xr:uid="{B2A92D0B-FEDA-432A-B352-B02C027C802A}">
       <formula1>=IF(M424&lt;&gt;"",INDIRECT(VLOOKUP(M424,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M425" xr:uid="{301D36F2-5074-4D64-8A6B-78A5791FA54C}">
+    <dataValidation type="list" sqref="M425" xr:uid="{A070BDD6-45EF-4FE2-8645-A67AE065AC3E}">
       <formula1>=IF(L425&lt;&gt;"",INDIRECT(VLOOKUP(L425,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N425" xr:uid="{FB207B25-E66E-49AA-8350-16E661829246}">
+    <dataValidation type="list" sqref="N425" xr:uid="{1A19677A-6E40-4E10-BB33-A2A572B83A65}">
       <formula1>=IF(M425&lt;&gt;"",INDIRECT(VLOOKUP(M425,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M426" xr:uid="{E05AD8C4-C07F-4BB0-9D8B-4917CBEC75CB}">
+    <dataValidation type="list" sqref="M426" xr:uid="{A5C21E5E-E58A-4459-BC7D-7BD7E25C8B3F}">
       <formula1>=IF(L426&lt;&gt;"",INDIRECT(VLOOKUP(L426,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N426" xr:uid="{86CB6806-3437-41FE-8D17-6E17C49E485B}">
+    <dataValidation type="list" sqref="N426" xr:uid="{9FF1D65A-11C8-4272-A851-F8D2F7FD3B6B}">
       <formula1>=IF(M426&lt;&gt;"",INDIRECT(VLOOKUP(M426,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M427" xr:uid="{CFF91E4C-822A-4F6C-A2FE-00CB68A062F9}">
+    <dataValidation type="list" sqref="M427" xr:uid="{5D2B2042-5CCC-4BAA-B31E-B838F06F3E43}">
       <formula1>=IF(L427&lt;&gt;"",INDIRECT(VLOOKUP(L427,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N427" xr:uid="{A538225C-28FB-4883-B813-475EA9E77201}">
+    <dataValidation type="list" sqref="N427" xr:uid="{51375259-A78C-4D2D-84D4-9371A16CAD20}">
       <formula1>=IF(M427&lt;&gt;"",INDIRECT(VLOOKUP(M427,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M428" xr:uid="{06ECC670-3774-4A91-AEFC-2E3AD9B3015C}">
+    <dataValidation type="list" sqref="M428" xr:uid="{1B47409A-EA69-4C65-8462-82EA70D97D1B}">
       <formula1>=IF(L428&lt;&gt;"",INDIRECT(VLOOKUP(L428,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N428" xr:uid="{9F86332E-C06E-48D8-8E55-517AC7AF7F8D}">
+    <dataValidation type="list" sqref="N428" xr:uid="{C7F29899-75C2-45E9-92CB-E22DADD559BD}">
       <formula1>=IF(M428&lt;&gt;"",INDIRECT(VLOOKUP(M428,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M429" xr:uid="{687E39F2-44D0-41D0-9D47-A79022BF613F}">
+    <dataValidation type="list" sqref="M429" xr:uid="{3476223B-AC19-4E07-A884-E2A28BE1C8C8}">
       <formula1>=IF(L429&lt;&gt;"",INDIRECT(VLOOKUP(L429,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N429" xr:uid="{70C2AC63-07B8-4642-A041-DD4CCAE19ADE}">
+    <dataValidation type="list" sqref="N429" xr:uid="{8DD41FB5-813D-4A9D-83F4-A97FB1C7BB15}">
       <formula1>=IF(M429&lt;&gt;"",INDIRECT(VLOOKUP(M429,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M430" xr:uid="{2DAD96F9-E25D-41D2-8A99-0B885887629A}">
+    <dataValidation type="list" sqref="M430" xr:uid="{332DD984-C96C-4224-ACA5-1BE1607E42B5}">
       <formula1>=IF(L430&lt;&gt;"",INDIRECT(VLOOKUP(L430,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N430" xr:uid="{E271C47C-5615-4984-98C0-45F7FA653A6D}">
+    <dataValidation type="list" sqref="N430" xr:uid="{D20190EF-3158-421E-8DE2-54C7DFFC8094}">
       <formula1>=IF(M430&lt;&gt;"",INDIRECT(VLOOKUP(M430,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M431" xr:uid="{F196898E-B424-418F-8D75-303BC00F578C}">
+    <dataValidation type="list" sqref="M431" xr:uid="{A5B144C1-D42E-4F4A-B819-2045CCBF751C}">
       <formula1>=IF(L431&lt;&gt;"",INDIRECT(VLOOKUP(L431,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N431" xr:uid="{6372CD9C-CE77-4477-8CDC-F5567AA1091E}">
+    <dataValidation type="list" sqref="N431" xr:uid="{C241010D-792C-4278-9600-E25215F8EB70}">
       <formula1>=IF(M431&lt;&gt;"",INDIRECT(VLOOKUP(M431,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M432" xr:uid="{B43C24F0-45FC-4011-BE63-E0EF46A1018C}">
+    <dataValidation type="list" sqref="M432" xr:uid="{9CDC1063-20AF-4EBE-BB8B-B354051E2E77}">
       <formula1>=IF(L432&lt;&gt;"",INDIRECT(VLOOKUP(L432,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N432" xr:uid="{D48CEA3D-6AD7-4FF9-B3D0-EF9640701EE6}">
+    <dataValidation type="list" sqref="N432" xr:uid="{3514A261-C8E7-4AAE-AB4F-4C9B91228EE7}">
       <formula1>=IF(M432&lt;&gt;"",INDIRECT(VLOOKUP(M432,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M433" xr:uid="{517D4292-CD0A-4214-85B3-E1464AD1F89F}">
+    <dataValidation type="list" sqref="M433" xr:uid="{2B4FDEEA-5AC2-4FB7-B8BB-BA83A1527D07}">
       <formula1>=IF(L433&lt;&gt;"",INDIRECT(VLOOKUP(L433,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N433" xr:uid="{2454AF69-7CB7-4CB3-9D59-31FDB3DDFC14}">
+    <dataValidation type="list" sqref="N433" xr:uid="{DB7E0271-D964-485C-B7E0-1C9CDAB2FFB5}">
       <formula1>=IF(M433&lt;&gt;"",INDIRECT(VLOOKUP(M433,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M434" xr:uid="{D048099F-D51C-4F89-96F3-137103F5C047}">
+    <dataValidation type="list" sqref="M434" xr:uid="{BDE12444-1701-4C7C-88CB-F517B2850E4C}">
       <formula1>=IF(L434&lt;&gt;"",INDIRECT(VLOOKUP(L434,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N434" xr:uid="{ABC13EC3-58BA-4944-81FD-963466A17966}">
+    <dataValidation type="list" sqref="N434" xr:uid="{AA79BEFD-7ED4-4711-A537-92164F5B9F9C}">
       <formula1>=IF(M434&lt;&gt;"",INDIRECT(VLOOKUP(M434,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M435" xr:uid="{0D15CA98-8666-49EB-B959-23436C021882}">
+    <dataValidation type="list" sqref="M435" xr:uid="{9B51D36E-E218-404E-A3B1-0106A9A8FB3B}">
       <formula1>=IF(L435&lt;&gt;"",INDIRECT(VLOOKUP(L435,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N435" xr:uid="{75DE2000-2E50-46AA-A833-F82ECF88DC0F}">
+    <dataValidation type="list" sqref="N435" xr:uid="{3DA33F04-E3F5-495E-9773-434F3115D623}">
       <formula1>=IF(M435&lt;&gt;"",INDIRECT(VLOOKUP(M435,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M436" xr:uid="{4CC83DCE-9D4C-4983-A732-8C4D92D27606}">
+    <dataValidation type="list" sqref="M436" xr:uid="{6B466472-977F-4B83-96FF-B6A23C889FA5}">
       <formula1>=IF(L436&lt;&gt;"",INDIRECT(VLOOKUP(L436,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N436" xr:uid="{D6A6E0E9-F966-47A8-B505-7FB5C6A00E05}">
+    <dataValidation type="list" sqref="N436" xr:uid="{EFDD9009-207D-404D-8B9A-94B1604EBD3F}">
       <formula1>=IF(M436&lt;&gt;"",INDIRECT(VLOOKUP(M436,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M437" xr:uid="{50954141-999D-4B9C-A0F0-C09795C47793}">
+    <dataValidation type="list" sqref="M437" xr:uid="{BFAD82B9-7C35-425A-9AF0-AD69C95F682E}">
       <formula1>=IF(L437&lt;&gt;"",INDIRECT(VLOOKUP(L437,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N437" xr:uid="{E7D83596-8C66-4854-A8DD-9844D9B33F5A}">
+    <dataValidation type="list" sqref="N437" xr:uid="{39CC0045-0C0F-46E9-8947-CE279FC88A89}">
       <formula1>=IF(M437&lt;&gt;"",INDIRECT(VLOOKUP(M437,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M438" xr:uid="{86DDB2CF-B9A1-4434-BF6A-1DD65E9682F2}">
+    <dataValidation type="list" sqref="M438" xr:uid="{AA5B6AEE-CC09-4255-BC45-4CEC57BA77D0}">
       <formula1>=IF(L438&lt;&gt;"",INDIRECT(VLOOKUP(L438,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N438" xr:uid="{24931997-B3AF-45DB-8D04-F71E502E8A1A}">
+    <dataValidation type="list" sqref="N438" xr:uid="{9C54FD77-A4EB-4E4A-9116-761A7590EFD8}">
       <formula1>=IF(M438&lt;&gt;"",INDIRECT(VLOOKUP(M438,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M439" xr:uid="{A5D56C37-E329-4FD4-A033-710EEE4F9B15}">
+    <dataValidation type="list" sqref="M439" xr:uid="{C5C249EB-EBB5-428A-B91D-B9F2E0CDBA1D}">
       <formula1>=IF(L439&lt;&gt;"",INDIRECT(VLOOKUP(L439,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N439" xr:uid="{16B81DA5-E98E-4E2B-BE6F-7D4052D96F89}">
+    <dataValidation type="list" sqref="N439" xr:uid="{33D38398-41EE-4719-9266-E2830444C9A2}">
       <formula1>=IF(M439&lt;&gt;"",INDIRECT(VLOOKUP(M439,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M440" xr:uid="{69F6E6BB-B0D9-44E5-B119-B2FC68431507}">
+    <dataValidation type="list" sqref="M440" xr:uid="{F697A6C6-D28F-453D-8ABD-D6BC22F0C87D}">
       <formula1>=IF(L440&lt;&gt;"",INDIRECT(VLOOKUP(L440,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N440" xr:uid="{96763FA9-7D58-4AB6-AFE6-CFCC78166EFF}">
+    <dataValidation type="list" sqref="N440" xr:uid="{F3A72379-37ED-4F52-98D9-5D115AA1C927}">
       <formula1>=IF(M440&lt;&gt;"",INDIRECT(VLOOKUP(M440,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M441" xr:uid="{CD04D1D6-18F6-4A41-89F2-0B2E273B1FB8}">
+    <dataValidation type="list" sqref="M441" xr:uid="{CA3AB286-11FC-45AF-BA61-E72031CD4651}">
       <formula1>=IF(L441&lt;&gt;"",INDIRECT(VLOOKUP(L441,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N441" xr:uid="{8CEC1282-34C5-4DFA-ABF3-A47FD860876D}">
+    <dataValidation type="list" sqref="N441" xr:uid="{6C318091-109B-498C-908F-5243014DD3F0}">
       <formula1>=IF(M441&lt;&gt;"",INDIRECT(VLOOKUP(M441,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M442" xr:uid="{B230B05B-2CE3-40B9-8362-5016878E9465}">
+    <dataValidation type="list" sqref="M442" xr:uid="{DEEDF88C-DF63-41B8-9611-5C811B90402D}">
       <formula1>=IF(L442&lt;&gt;"",INDIRECT(VLOOKUP(L442,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N442" xr:uid="{FB1C208A-43AF-48B7-83C1-D5EE62FA97EE}">
+    <dataValidation type="list" sqref="N442" xr:uid="{1F737B19-A5A1-448D-8791-9427B36910E1}">
       <formula1>=IF(M442&lt;&gt;"",INDIRECT(VLOOKUP(M442,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M443" xr:uid="{42FA6E1A-0137-49A4-AE63-713C95635892}">
+    <dataValidation type="list" sqref="M443" xr:uid="{0E219D77-9F6F-4D14-B7B4-EB4A043BD401}">
       <formula1>=IF(L443&lt;&gt;"",INDIRECT(VLOOKUP(L443,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N443" xr:uid="{0F8A0AEA-C6AF-4360-97A1-F447201C40FA}">
+    <dataValidation type="list" sqref="N443" xr:uid="{D25E30CF-4B16-4831-A093-411944C86103}">
       <formula1>=IF(M443&lt;&gt;"",INDIRECT(VLOOKUP(M443,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M444" xr:uid="{226AB64E-6382-4CD6-9AA8-BC34A948467F}">
+    <dataValidation type="list" sqref="M444" xr:uid="{5FCF5F7A-E362-4131-BD57-2CE4B92FC71F}">
       <formula1>=IF(L444&lt;&gt;"",INDIRECT(VLOOKUP(L444,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N444" xr:uid="{BF23D387-97A1-4F0F-9844-5211DA7A439A}">
+    <dataValidation type="list" sqref="N444" xr:uid="{8EDC7B65-C336-4B8C-A586-250EBF5171CF}">
       <formula1>=IF(M444&lt;&gt;"",INDIRECT(VLOOKUP(M444,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M445" xr:uid="{EA127991-39DB-4BDB-B9C2-5A562BD2BDE4}">
+    <dataValidation type="list" sqref="M445" xr:uid="{C397307C-467C-4EFF-8707-D979700162DA}">
       <formula1>=IF(L445&lt;&gt;"",INDIRECT(VLOOKUP(L445,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N445" xr:uid="{FB816C7C-FF45-4D0D-B985-809B9D591067}">
+    <dataValidation type="list" sqref="N445" xr:uid="{C46A5373-715E-48B9-848B-C724358D94F6}">
       <formula1>=IF(M445&lt;&gt;"",INDIRECT(VLOOKUP(M445,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M446" xr:uid="{D1BBE4DC-75AE-47E1-8A71-EA4C8525EB5A}">
+    <dataValidation type="list" sqref="M446" xr:uid="{47E5112C-5C9E-4A06-953D-4C8BEA70DAE1}">
       <formula1>=IF(L446&lt;&gt;"",INDIRECT(VLOOKUP(L446,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N446" xr:uid="{C13ADA1F-557B-46EC-AFCA-0AC87C2C2653}">
+    <dataValidation type="list" sqref="N446" xr:uid="{4046B6CE-C920-457C-B6DE-F84D57DABCA9}">
       <formula1>=IF(M446&lt;&gt;"",INDIRECT(VLOOKUP(M446,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M447" xr:uid="{154028DC-3432-47AE-891B-06FA11D7EF6C}">
+    <dataValidation type="list" sqref="M447" xr:uid="{7634C25E-E946-4DC3-9799-B7EAFDA829CB}">
       <formula1>=IF(L447&lt;&gt;"",INDIRECT(VLOOKUP(L447,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N447" xr:uid="{497D3E1A-0D4A-42B5-B05A-8DE7DD224F75}">
+    <dataValidation type="list" sqref="N447" xr:uid="{6089F48B-7D0B-4EF4-9AF5-C877E436150D}">
       <formula1>=IF(M447&lt;&gt;"",INDIRECT(VLOOKUP(M447,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M448" xr:uid="{885BC3EC-5DBE-454B-BB11-A66FF43C1241}">
+    <dataValidation type="list" sqref="M448" xr:uid="{18F0C80F-9CC9-495F-A730-764EF3FF555D}">
       <formula1>=IF(L448&lt;&gt;"",INDIRECT(VLOOKUP(L448,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N448" xr:uid="{FAD656FA-044B-4596-A44F-51C7F6159576}">
+    <dataValidation type="list" sqref="N448" xr:uid="{B95F3649-F7D8-4750-80BD-7191AA2835CE}">
       <formula1>=IF(M448&lt;&gt;"",INDIRECT(VLOOKUP(M448,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M449" xr:uid="{70FD2285-61DF-4993-ACCE-12B06BC8F171}">
+    <dataValidation type="list" sqref="M449" xr:uid="{DCFB8BDC-95CF-4D1D-B58A-711950894B41}">
       <formula1>=IF(L449&lt;&gt;"",INDIRECT(VLOOKUP(L449,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N449" xr:uid="{F3495269-2CBA-43E2-A966-05B852D8B3D6}">
+    <dataValidation type="list" sqref="N449" xr:uid="{14FFDE0D-8B8D-4CE6-B8CD-C252152F0C34}">
       <formula1>=IF(M449&lt;&gt;"",INDIRECT(VLOOKUP(M449,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M450" xr:uid="{8122A73B-BDBC-41C4-9E26-D527EF415F3F}">
+    <dataValidation type="list" sqref="M450" xr:uid="{4ED81E45-3B59-46A8-B987-E9CC04232752}">
       <formula1>=IF(L450&lt;&gt;"",INDIRECT(VLOOKUP(L450,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N450" xr:uid="{F930E7E7-B69A-4EB8-AA91-3053F0D38D6D}">
+    <dataValidation type="list" sqref="N450" xr:uid="{5CB7DFBB-E64A-4EEF-BD71-A9FF95F5B55A}">
       <formula1>=IF(M450&lt;&gt;"",INDIRECT(VLOOKUP(M450,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M451" xr:uid="{D193189D-EFAB-455E-A583-28F94B527680}">
+    <dataValidation type="list" sqref="M451" xr:uid="{2191372F-F404-4743-859D-559CED4A4429}">
       <formula1>=IF(L451&lt;&gt;"",INDIRECT(VLOOKUP(L451,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N451" xr:uid="{DCAEFA12-376C-4DF8-AFC4-169C91174D06}">
+    <dataValidation type="list" sqref="N451" xr:uid="{152E40C9-DDA9-46A5-AEA7-FD27B185F1C3}">
       <formula1>=IF(M451&lt;&gt;"",INDIRECT(VLOOKUP(M451,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M452" xr:uid="{43203CD1-0009-4662-BFF4-870FCACFAE7F}">
+    <dataValidation type="list" sqref="M452" xr:uid="{D456E1C5-1D42-4BA9-8B43-3A2C902A871B}">
       <formula1>=IF(L452&lt;&gt;"",INDIRECT(VLOOKUP(L452,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N452" xr:uid="{B824281B-5CF8-4E1F-B9D2-2F240D528BD8}">
+    <dataValidation type="list" sqref="N452" xr:uid="{A3AF3756-4539-4E89-9AF1-AF888B31B918}">
       <formula1>=IF(M452&lt;&gt;"",INDIRECT(VLOOKUP(M452,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M453" xr:uid="{C5183E50-2E15-473F-9F61-BDD6DAE3BFA7}">
+    <dataValidation type="list" sqref="M453" xr:uid="{1DC3E356-231A-4995-9D07-1F4FB49A9209}">
       <formula1>=IF(L453&lt;&gt;"",INDIRECT(VLOOKUP(L453,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N453" xr:uid="{EF0C4AD5-E080-4068-B5B8-E35F12EAE229}">
+    <dataValidation type="list" sqref="N453" xr:uid="{3801A8C3-45F7-4AB6-95BA-40210F5B6871}">
       <formula1>=IF(M453&lt;&gt;"",INDIRECT(VLOOKUP(M453,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M454" xr:uid="{F092E0B3-1149-4A41-A4EB-DB7DB4B5273D}">
+    <dataValidation type="list" sqref="M454" xr:uid="{70923914-20B4-44AD-A9D9-45C22EF6CDFC}">
       <formula1>=IF(L454&lt;&gt;"",INDIRECT(VLOOKUP(L454,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N454" xr:uid="{C917E34A-9080-4C69-8D18-5658309D9D2A}">
+    <dataValidation type="list" sqref="N454" xr:uid="{810D96A9-341C-4BF7-8DD9-E06CC687CEB8}">
       <formula1>=IF(M454&lt;&gt;"",INDIRECT(VLOOKUP(M454,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M455" xr:uid="{7D0A54AB-7042-4E33-8D5C-0FC4B53BEBB3}">
+    <dataValidation type="list" sqref="M455" xr:uid="{5F2C8633-F5E8-402F-9778-8C3532DC76F1}">
       <formula1>=IF(L455&lt;&gt;"",INDIRECT(VLOOKUP(L455,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N455" xr:uid="{4F710BF7-26E1-4E9C-AD90-6FBBCE2AE878}">
+    <dataValidation type="list" sqref="N455" xr:uid="{BB971342-1AB5-44F9-BF1E-A1341D84A691}">
       <formula1>=IF(M455&lt;&gt;"",INDIRECT(VLOOKUP(M455,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M456" xr:uid="{DED0E3C9-2921-4855-93D5-B13F8C6FBC3E}">
+    <dataValidation type="list" sqref="M456" xr:uid="{8DE17E00-DF1C-41F8-9515-E34983ECB05A}">
       <formula1>=IF(L456&lt;&gt;"",INDIRECT(VLOOKUP(L456,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N456" xr:uid="{55BDE295-C1E4-4837-A512-33F4C789A8DD}">
+    <dataValidation type="list" sqref="N456" xr:uid="{1A95495F-BEEA-4F64-A979-1CC43A6B8179}">
       <formula1>=IF(M456&lt;&gt;"",INDIRECT(VLOOKUP(M456,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M457" xr:uid="{2A480D20-ABE1-4671-B03D-BA1A7E0395B4}">
+    <dataValidation type="list" sqref="M457" xr:uid="{0F709B1D-A110-4990-B581-F6D51B376DE7}">
       <formula1>=IF(L457&lt;&gt;"",INDIRECT(VLOOKUP(L457,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N457" xr:uid="{16142AA2-A68D-4D55-BBBA-598BF1EE1CE9}">
+    <dataValidation type="list" sqref="N457" xr:uid="{A605DF01-3174-4AAE-8EE8-7B2CBDA91382}">
       <formula1>=IF(M457&lt;&gt;"",INDIRECT(VLOOKUP(M457,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M458" xr:uid="{F9DC0C7B-3B4D-493C-A7C2-0EA918205F58}">
+    <dataValidation type="list" sqref="M458" xr:uid="{1A3846EC-AC7A-41F9-BA3E-394E769C500F}">
       <formula1>=IF(L458&lt;&gt;"",INDIRECT(VLOOKUP(L458,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N458" xr:uid="{3C05599B-CC0E-468E-8AE3-425C54C45DEC}">
+    <dataValidation type="list" sqref="N458" xr:uid="{F9E91BC8-1E73-4CBB-B554-008734C175EF}">
       <formula1>=IF(M458&lt;&gt;"",INDIRECT(VLOOKUP(M458,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M459" xr:uid="{1C7222B7-F16F-438E-B4A5-61DD146F91E1}">
+    <dataValidation type="list" sqref="M459" xr:uid="{94D22AD7-4551-42C1-AD97-AD2B75C1B6E8}">
       <formula1>=IF(L459&lt;&gt;"",INDIRECT(VLOOKUP(L459,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N459" xr:uid="{A7C7CB70-0948-4A93-8CF7-AE3AACBB2E96}">
+    <dataValidation type="list" sqref="N459" xr:uid="{055BB586-CA9F-4688-8AF0-6526021E9058}">
       <formula1>=IF(M459&lt;&gt;"",INDIRECT(VLOOKUP(M459,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M460" xr:uid="{A1539F7D-CEFC-43E5-AC34-B9814A4CB68E}">
+    <dataValidation type="list" sqref="M460" xr:uid="{7D3DCB65-2260-4A9B-8D30-6AABF6626CF8}">
       <formula1>=IF(L460&lt;&gt;"",INDIRECT(VLOOKUP(L460,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N460" xr:uid="{3F67B399-9B9B-4D04-A90E-A2B952D076CB}">
+    <dataValidation type="list" sqref="N460" xr:uid="{C9D86D7C-2FBF-45E0-9FFA-84C18878BAC8}">
       <formula1>=IF(M460&lt;&gt;"",INDIRECT(VLOOKUP(M460,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M461" xr:uid="{EA5D6E3B-91EE-4224-8DCA-8160DD059CAC}">
+    <dataValidation type="list" sqref="M461" xr:uid="{CA362120-4B71-4A27-A423-4C5361D72D13}">
       <formula1>=IF(L461&lt;&gt;"",INDIRECT(VLOOKUP(L461,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N461" xr:uid="{98C72A00-6C10-47E0-BD16-E76AA3CCB72F}">
+    <dataValidation type="list" sqref="N461" xr:uid="{5B6638A1-4EE5-47F0-A045-2CF9A0B42530}">
       <formula1>=IF(M461&lt;&gt;"",INDIRECT(VLOOKUP(M461,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M462" xr:uid="{13720F49-BADF-4778-B3C9-7DAF61005EC9}">
+    <dataValidation type="list" sqref="M462" xr:uid="{3C17455B-627A-4DAE-B43C-586876ACFBD4}">
       <formula1>=IF(L462&lt;&gt;"",INDIRECT(VLOOKUP(L462,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N462" xr:uid="{C85BB5B0-E0FE-4E4E-A768-A3A6C96F06B4}">
+    <dataValidation type="list" sqref="N462" xr:uid="{60243C83-6419-42AE-9844-35C84D724D53}">
       <formula1>=IF(M462&lt;&gt;"",INDIRECT(VLOOKUP(M462,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M463" xr:uid="{C0BB20FF-861D-49AF-8DCF-170B67C6501B}">
+    <dataValidation type="list" sqref="M463" xr:uid="{0486E928-A3DE-48DC-A9F8-9973ADE3BE72}">
       <formula1>=IF(L463&lt;&gt;"",INDIRECT(VLOOKUP(L463,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N463" xr:uid="{C74CF9E4-C03D-451F-A560-52DD2E6684C6}">
+    <dataValidation type="list" sqref="N463" xr:uid="{33CFC3B8-CA54-40FA-8C71-0E1BF73BF38B}">
       <formula1>=IF(M463&lt;&gt;"",INDIRECT(VLOOKUP(M463,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M464" xr:uid="{F6CD0D97-77B8-44C4-9AA0-78935EC96452}">
+    <dataValidation type="list" sqref="M464" xr:uid="{758AE716-FB5E-4C4B-9A8C-53A32D36A018}">
       <formula1>=IF(L464&lt;&gt;"",INDIRECT(VLOOKUP(L464,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N464" xr:uid="{6FFB463A-C03B-49BF-9362-DD1CB5662032}">
+    <dataValidation type="list" sqref="N464" xr:uid="{F49E4CC6-3C21-4F05-A00B-0DEC6326F827}">
       <formula1>=IF(M464&lt;&gt;"",INDIRECT(VLOOKUP(M464,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M465" xr:uid="{17F471AB-4BE8-416C-AA1F-F5AF7408098C}">
+    <dataValidation type="list" sqref="M465" xr:uid="{541360D6-EE68-4C93-9F19-1F0148EEB940}">
       <formula1>=IF(L465&lt;&gt;"",INDIRECT(VLOOKUP(L465,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N465" xr:uid="{AB9D9B65-5C7F-4867-B373-AB14DB85E953}">
+    <dataValidation type="list" sqref="N465" xr:uid="{DE5F8070-33CE-48CE-A1E5-1EA5BFCF9706}">
       <formula1>=IF(M465&lt;&gt;"",INDIRECT(VLOOKUP(M465,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M466" xr:uid="{E140FA1E-28C6-4241-87E8-FA667E10C017}">
+    <dataValidation type="list" sqref="M466" xr:uid="{8763BC97-F356-4ABE-A64B-36006EC2C1B8}">
       <formula1>=IF(L466&lt;&gt;"",INDIRECT(VLOOKUP(L466,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N466" xr:uid="{CF05F71D-DC52-4A9D-9875-07242F8CBFF5}">
+    <dataValidation type="list" sqref="N466" xr:uid="{9D812AAA-0DFF-4EDA-A945-6D2A2E7D43DB}">
       <formula1>=IF(M466&lt;&gt;"",INDIRECT(VLOOKUP(M466,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M467" xr:uid="{2B4FDB5E-96A6-4FA7-B3CD-DF32914967FF}">
+    <dataValidation type="list" sqref="M467" xr:uid="{FA9299BC-7BCD-4EA6-98FA-8E0F9E86506F}">
       <formula1>=IF(L467&lt;&gt;"",INDIRECT(VLOOKUP(L467,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N467" xr:uid="{D74D8A04-033D-4404-A468-142C40F899B5}">
+    <dataValidation type="list" sqref="N467" xr:uid="{B022AEDA-1DD6-476D-8FD2-AB395BFE0101}">
       <formula1>=IF(M467&lt;&gt;"",INDIRECT(VLOOKUP(M467,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M468" xr:uid="{6E0DE311-F73D-42AC-9F3B-CBC003018FFA}">
+    <dataValidation type="list" sqref="M468" xr:uid="{05BB300E-9DE0-41CB-A111-FDEA10BF4935}">
       <formula1>=IF(L468&lt;&gt;"",INDIRECT(VLOOKUP(L468,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N468" xr:uid="{63C6234F-2DE4-4874-B95E-ED90DAE621B7}">
+    <dataValidation type="list" sqref="N468" xr:uid="{B5354119-DEE3-43BB-9D0F-1CC7DCF5AB80}">
       <formula1>=IF(M468&lt;&gt;"",INDIRECT(VLOOKUP(M468,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M469" xr:uid="{444F71E5-266B-4157-8FEB-292B038051B3}">
+    <dataValidation type="list" sqref="M469" xr:uid="{78E74261-5A56-4666-8CFF-F497F984485F}">
       <formula1>=IF(L469&lt;&gt;"",INDIRECT(VLOOKUP(L469,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N469" xr:uid="{32E49E79-DFCB-4771-886A-04922F92F0BD}">
+    <dataValidation type="list" sqref="N469" xr:uid="{7D06D97D-7F25-4972-841E-D1217AAECCD7}">
       <formula1>=IF(M469&lt;&gt;"",INDIRECT(VLOOKUP(M469,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M470" xr:uid="{D5AA775E-6061-4A1D-8D6F-33272E1377A2}">
+    <dataValidation type="list" sqref="M470" xr:uid="{6967C34F-0D4E-4FF0-ABAD-73FD31A2AADA}">
       <formula1>=IF(L470&lt;&gt;"",INDIRECT(VLOOKUP(L470,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N470" xr:uid="{6559178B-4E04-496E-BFD1-4B3F7F847359}">
+    <dataValidation type="list" sqref="N470" xr:uid="{ECFC107A-67C2-4D44-8EEC-31304052577C}">
       <formula1>=IF(M470&lt;&gt;"",INDIRECT(VLOOKUP(M470,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M471" xr:uid="{F617FE02-7970-4F0D-8AE6-C50B6EB9C9A2}">
+    <dataValidation type="list" sqref="M471" xr:uid="{55BA78D3-3A5B-489E-AB1C-44820FF2244B}">
       <formula1>=IF(L471&lt;&gt;"",INDIRECT(VLOOKUP(L471,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N471" xr:uid="{A2180781-0A0B-49C0-8C3C-061B4F23280F}">
+    <dataValidation type="list" sqref="N471" xr:uid="{DF5D8D90-41CC-454B-AE43-DB4391577E67}">
       <formula1>=IF(M471&lt;&gt;"",INDIRECT(VLOOKUP(M471,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M472" xr:uid="{7B7F556F-6D91-4ACD-9D34-03FB88FC0C7C}">
+    <dataValidation type="list" sqref="M472" xr:uid="{CA4CA0DE-E7C6-403D-ABFA-7EEF401F63B4}">
       <formula1>=IF(L472&lt;&gt;"",INDIRECT(VLOOKUP(L472,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N472" xr:uid="{11C693AB-D4B4-48E5-B789-6FE2D116B2C8}">
+    <dataValidation type="list" sqref="N472" xr:uid="{96D48542-F45F-415C-8454-04CE8F729E38}">
       <formula1>=IF(M472&lt;&gt;"",INDIRECT(VLOOKUP(M472,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M473" xr:uid="{8D347501-3FE0-412C-BFBB-6E58E30717F9}">
+    <dataValidation type="list" sqref="M473" xr:uid="{FBA5B41B-5054-4EF7-A287-00389BF86035}">
       <formula1>=IF(L473&lt;&gt;"",INDIRECT(VLOOKUP(L473,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N473" xr:uid="{A225835F-983F-43AD-97FD-5006427B83DA}">
+    <dataValidation type="list" sqref="N473" xr:uid="{09C006BE-B7F9-45CB-89D1-1CA7E017BC18}">
       <formula1>=IF(M473&lt;&gt;"",INDIRECT(VLOOKUP(M473,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M474" xr:uid="{F55241F4-6B6E-4D8D-A2EA-2FDEC078FF30}">
+    <dataValidation type="list" sqref="M474" xr:uid="{55E2D0A2-0373-4CCE-829E-8A586656B6E8}">
       <formula1>=IF(L474&lt;&gt;"",INDIRECT(VLOOKUP(L474,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N474" xr:uid="{4D7BF811-8F3A-4680-B171-F8F5BA8C03EF}">
+    <dataValidation type="list" sqref="N474" xr:uid="{342C0603-ABB1-42BC-B2DB-62EAC4E2549D}">
       <formula1>=IF(M474&lt;&gt;"",INDIRECT(VLOOKUP(M474,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M475" xr:uid="{E16563F1-5F7F-436C-B7BD-912E5351F707}">
+    <dataValidation type="list" sqref="M475" xr:uid="{4D1426DD-BCB0-4DA0-8B07-69DC430579F1}">
       <formula1>=IF(L475&lt;&gt;"",INDIRECT(VLOOKUP(L475,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N475" xr:uid="{3A9564D7-87A1-4950-90B8-E1A533D48961}">
+    <dataValidation type="list" sqref="N475" xr:uid="{932F006C-4D4D-4AAF-95B5-567A8454B843}">
       <formula1>=IF(M475&lt;&gt;"",INDIRECT(VLOOKUP(M475,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M476" xr:uid="{E3CA93DB-8E65-44AD-9DCA-FBF61E448444}">
+    <dataValidation type="list" sqref="M476" xr:uid="{FFBAFEC9-F3DB-4DDB-AC57-2F4379184089}">
       <formula1>=IF(L476&lt;&gt;"",INDIRECT(VLOOKUP(L476,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N476" xr:uid="{7713DA2E-09F1-4D1A-9B88-07D8623AC4DF}">
+    <dataValidation type="list" sqref="N476" xr:uid="{2F259F3B-337B-4554-B32D-2D0ED9AD1C6F}">
       <formula1>=IF(M476&lt;&gt;"",INDIRECT(VLOOKUP(M476,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M477" xr:uid="{02457439-1D44-4AD7-9B8E-89CCF36999C6}">
+    <dataValidation type="list" sqref="M477" xr:uid="{67CE16F7-33BC-4426-90C2-45713DD703B5}">
       <formula1>=IF(L477&lt;&gt;"",INDIRECT(VLOOKUP(L477,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N477" xr:uid="{478211A6-8AFD-429C-ACFD-A9ADCD688709}">
+    <dataValidation type="list" sqref="N477" xr:uid="{835C6DF6-F17C-40EC-B1CE-8F525E49E2B4}">
       <formula1>=IF(M477&lt;&gt;"",INDIRECT(VLOOKUP(M477,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M478" xr:uid="{84961761-50DB-4D6F-A552-DF39E8A306E4}">
+    <dataValidation type="list" sqref="M478" xr:uid="{5D42B4E3-D5C9-4039-B463-9B671162D5C2}">
       <formula1>=IF(L478&lt;&gt;"",INDIRECT(VLOOKUP(L478,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N478" xr:uid="{C9AF8483-D2E7-454F-9AF2-9B8CE9DD9CD3}">
+    <dataValidation type="list" sqref="N478" xr:uid="{B4B666E7-23A2-496A-87EE-1591B26146DD}">
       <formula1>=IF(M478&lt;&gt;"",INDIRECT(VLOOKUP(M478,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M479" xr:uid="{6B19458F-9F16-4B38-985A-35D5938D8064}">
+    <dataValidation type="list" sqref="M479" xr:uid="{655537D8-6061-42B9-8D8E-BD0547682F56}">
       <formula1>=IF(L479&lt;&gt;"",INDIRECT(VLOOKUP(L479,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N479" xr:uid="{E50D51DF-EBA5-4547-82BC-169BBF70F511}">
+    <dataValidation type="list" sqref="N479" xr:uid="{5624270A-2B4D-4937-95F8-81748EF58FE1}">
       <formula1>=IF(M479&lt;&gt;"",INDIRECT(VLOOKUP(M479,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M480" xr:uid="{57DCA82E-6BCB-4A8A-8675-BDC0FC92A84A}">
+    <dataValidation type="list" sqref="M480" xr:uid="{3C403CDA-A97F-4AAB-AD68-1518A29C2F6C}">
       <formula1>=IF(L480&lt;&gt;"",INDIRECT(VLOOKUP(L480,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N480" xr:uid="{3E3C05AB-0066-40BA-9E3C-A690D7549E9B}">
+    <dataValidation type="list" sqref="N480" xr:uid="{2593D767-BA88-4B35-A465-1C3D0664E1D5}">
       <formula1>=IF(M480&lt;&gt;"",INDIRECT(VLOOKUP(M480,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M481" xr:uid="{C1AA96DD-5EC5-40C0-B50C-DBD097B917D4}">
+    <dataValidation type="list" sqref="M481" xr:uid="{D2AE0E7D-E96C-47F1-AB02-4E9245CE9CC6}">
       <formula1>=IF(L481&lt;&gt;"",INDIRECT(VLOOKUP(L481,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N481" xr:uid="{32AE106C-E173-42E7-9220-04BAD7FAA238}">
+    <dataValidation type="list" sqref="N481" xr:uid="{BEEE3AD9-DF2D-49B7-93E2-EA47E13E735F}">
       <formula1>=IF(M481&lt;&gt;"",INDIRECT(VLOOKUP(M481,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M482" xr:uid="{D52C97EA-A766-4AA0-B4D7-1D825ECC14FB}">
+    <dataValidation type="list" sqref="M482" xr:uid="{93719694-142D-43DD-AABD-9773317A1DBA}">
       <formula1>=IF(L482&lt;&gt;"",INDIRECT(VLOOKUP(L482,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N482" xr:uid="{458A18F8-FBB7-4400-8847-3AEDB795EE30}">
+    <dataValidation type="list" sqref="N482" xr:uid="{59E019C5-CE28-4002-B4F4-60EBC3AEE395}">
       <formula1>=IF(M482&lt;&gt;"",INDIRECT(VLOOKUP(M482,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M483" xr:uid="{A127E8FF-AC1E-44BB-AE8A-56B650A424F5}">
+    <dataValidation type="list" sqref="M483" xr:uid="{33E0994B-04A7-421F-AAAD-ECD91C50405F}">
       <formula1>=IF(L483&lt;&gt;"",INDIRECT(VLOOKUP(L483,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N483" xr:uid="{93AB3A38-4673-4BD1-B9EF-5FC618ABFF5E}">
+    <dataValidation type="list" sqref="N483" xr:uid="{9955E8D3-CD59-40C6-AD33-027746FA2965}">
       <formula1>=IF(M483&lt;&gt;"",INDIRECT(VLOOKUP(M483,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M484" xr:uid="{E392A74E-5954-489B-96DA-5C32F8F054EE}">
+    <dataValidation type="list" sqref="M484" xr:uid="{4142F18E-5BDC-45D7-A9C9-5CBD91E98763}">
       <formula1>=IF(L484&lt;&gt;"",INDIRECT(VLOOKUP(L484,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N484" xr:uid="{16E5C2BD-CE76-4137-8A9C-7FBE94F1D14C}">
+    <dataValidation type="list" sqref="N484" xr:uid="{52E71ED4-D22A-44A5-B4F9-F882751E1A35}">
       <formula1>=IF(M484&lt;&gt;"",INDIRECT(VLOOKUP(M484,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M485" xr:uid="{96795F4E-796D-4616-B314-62865B90164E}">
+    <dataValidation type="list" sqref="M485" xr:uid="{562D6411-9A41-4125-8779-DCBBCCD93440}">
       <formula1>=IF(L485&lt;&gt;"",INDIRECT(VLOOKUP(L485,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N485" xr:uid="{88D10B8A-3162-493D-914B-14659AF7C26B}">
+    <dataValidation type="list" sqref="N485" xr:uid="{E180584F-FBD9-4EEB-9091-C2568CD85F4C}">
       <formula1>=IF(M485&lt;&gt;"",INDIRECT(VLOOKUP(M485,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M486" xr:uid="{094E96CD-2D54-4564-812C-E1C031E6E423}">
+    <dataValidation type="list" sqref="M486" xr:uid="{29DD6C71-E535-4AD2-9D38-3C092EAFB4DC}">
       <formula1>=IF(L486&lt;&gt;"",INDIRECT(VLOOKUP(L486,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N486" xr:uid="{DC525D7F-003E-4356-A01D-04745C0280BD}">
+    <dataValidation type="list" sqref="N486" xr:uid="{745D8E58-F35E-457E-B626-CAFD58132BFF}">
       <formula1>=IF(M486&lt;&gt;"",INDIRECT(VLOOKUP(M486,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M487" xr:uid="{88ADC1BB-3408-4D57-8369-4181A8E4C77E}">
+    <dataValidation type="list" sqref="M487" xr:uid="{FEB240C2-7669-48EA-9C56-752E2961B0DB}">
       <formula1>=IF(L487&lt;&gt;"",INDIRECT(VLOOKUP(L487,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N487" xr:uid="{7E96930E-8054-4004-AA70-65B0F9C59136}">
+    <dataValidation type="list" sqref="N487" xr:uid="{1DD2FC3F-C974-4742-9E98-4C8BDB36C1D6}">
       <formula1>=IF(M487&lt;&gt;"",INDIRECT(VLOOKUP(M487,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M488" xr:uid="{EC7A6237-A092-4437-8143-351CA371B11E}">
+    <dataValidation type="list" sqref="M488" xr:uid="{0032DB23-2A9D-4096-A6BE-C6AAFE8DD1B9}">
       <formula1>=IF(L488&lt;&gt;"",INDIRECT(VLOOKUP(L488,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N488" xr:uid="{DE55F784-F25E-42C7-A562-910C5F5EBFC0}">
+    <dataValidation type="list" sqref="N488" xr:uid="{E9D53B1F-1F42-4771-9843-D8192E1EEA49}">
       <formula1>=IF(M488&lt;&gt;"",INDIRECT(VLOOKUP(M488,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M489" xr:uid="{E32D1255-CC7D-411E-8670-D9706F8658E0}">
+    <dataValidation type="list" sqref="M489" xr:uid="{111E36E0-50BC-43C7-B335-4F4499661D9A}">
       <formula1>=IF(L489&lt;&gt;"",INDIRECT(VLOOKUP(L489,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N489" xr:uid="{E92C556D-BD6F-43D8-AD7E-A3D8200323B4}">
+    <dataValidation type="list" sqref="N489" xr:uid="{F420A2D8-A7E9-41A6-9D91-A42880D6B32B}">
       <formula1>=IF(M489&lt;&gt;"",INDIRECT(VLOOKUP(M489,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M490" xr:uid="{6FD35D47-A8AB-47C9-869A-95257991F20A}">
+    <dataValidation type="list" sqref="M490" xr:uid="{BBA9FA7B-A04F-4EC5-9BBB-ABA106256F12}">
       <formula1>=IF(L490&lt;&gt;"",INDIRECT(VLOOKUP(L490,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N490" xr:uid="{400A18D6-C8A6-455D-883E-F863A4AA7692}">
+    <dataValidation type="list" sqref="N490" xr:uid="{64DA3710-C2E3-4811-829B-2DC8B396E467}">
       <formula1>=IF(M490&lt;&gt;"",INDIRECT(VLOOKUP(M490,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M491" xr:uid="{CDDBE83B-D74A-461E-AC03-B88C20536CF4}">
+    <dataValidation type="list" sqref="M491" xr:uid="{B0743528-8305-4FAF-ABEA-D465D3AB4A59}">
       <formula1>=IF(L491&lt;&gt;"",INDIRECT(VLOOKUP(L491,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N491" xr:uid="{C5792330-27E3-4CF1-AD22-888AAB0DC391}">
+    <dataValidation type="list" sqref="N491" xr:uid="{B0B72AA1-D12D-47F5-8171-94BE424E1987}">
       <formula1>=IF(M491&lt;&gt;"",INDIRECT(VLOOKUP(M491,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M492" xr:uid="{3BD42829-8035-4FFA-8275-1FD81E0E2706}">
+    <dataValidation type="list" sqref="M492" xr:uid="{34B1890B-DC19-4B33-9830-3BB963EB53A7}">
       <formula1>=IF(L492&lt;&gt;"",INDIRECT(VLOOKUP(L492,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N492" xr:uid="{C83A76C3-1431-4DF0-AE25-5C4E3C5B7762}">
+    <dataValidation type="list" sqref="N492" xr:uid="{E0B753C2-FA92-4D7D-8154-F1A8F4FCD188}">
       <formula1>=IF(M492&lt;&gt;"",INDIRECT(VLOOKUP(M492,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M493" xr:uid="{4747077D-A216-44D7-96AE-CCC1BF55AE57}">
+    <dataValidation type="list" sqref="M493" xr:uid="{D38FA8E0-94D0-43FC-98D7-5F4F60935013}">
       <formula1>=IF(L493&lt;&gt;"",INDIRECT(VLOOKUP(L493,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N493" xr:uid="{E0D87855-06E4-41EA-8289-716EA4EB032A}">
+    <dataValidation type="list" sqref="N493" xr:uid="{43A4DE54-B6C2-49EE-9F1E-07079496477E}">
       <formula1>=IF(M493&lt;&gt;"",INDIRECT(VLOOKUP(M493,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M494" xr:uid="{76FEE1A1-0FC8-43C7-A31E-EED01A9F18F8}">
+    <dataValidation type="list" sqref="M494" xr:uid="{92DB97F0-9474-4B46-BB1B-3FC5F10B85E3}">
       <formula1>=IF(L494&lt;&gt;"",INDIRECT(VLOOKUP(L494,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N494" xr:uid="{9146E072-41E5-4E75-BE64-A13AC242DAE2}">
+    <dataValidation type="list" sqref="N494" xr:uid="{74990605-6284-44F1-965D-DAD2ABC9B60A}">
       <formula1>=IF(M494&lt;&gt;"",INDIRECT(VLOOKUP(M494,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M495" xr:uid="{6E06693A-99AA-437D-B544-B10B12AF9287}">
+    <dataValidation type="list" sqref="M495" xr:uid="{61E3EA76-29B4-4DE7-A2E6-D05939BB49CD}">
       <formula1>=IF(L495&lt;&gt;"",INDIRECT(VLOOKUP(L495,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N495" xr:uid="{4164B20D-341B-4BE8-B5CA-B88176B61E87}">
+    <dataValidation type="list" sqref="N495" xr:uid="{00DF8CF6-21EA-4B80-AAC2-FCBE8B29AF35}">
       <formula1>=IF(M495&lt;&gt;"",INDIRECT(VLOOKUP(M495,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M496" xr:uid="{89F648B9-5D38-410A-B317-76BC0EC7F906}">
+    <dataValidation type="list" sqref="M496" xr:uid="{B61D40E3-9218-42D3-B3E5-88D9C73D274A}">
       <formula1>=IF(L496&lt;&gt;"",INDIRECT(VLOOKUP(L496,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N496" xr:uid="{7EC59C33-D92E-4CDC-9D28-29F105391377}">
+    <dataValidation type="list" sqref="N496" xr:uid="{2531C4C2-D7DD-4265-84C9-1D74956496B6}">
       <formula1>=IF(M496&lt;&gt;"",INDIRECT(VLOOKUP(M496,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M497" xr:uid="{2556FD92-6D46-408F-BA36-36DB2522654B}">
+    <dataValidation type="list" sqref="M497" xr:uid="{CF4059E7-8A19-4FA0-BAFD-284BDD24C308}">
       <formula1>=IF(L497&lt;&gt;"",INDIRECT(VLOOKUP(L497,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N497" xr:uid="{E38D2879-C8A6-4C48-9FCD-EA6EBE8FC752}">
+    <dataValidation type="list" sqref="N497" xr:uid="{7F58B41C-E07D-43C0-976B-C0FA7457816A}">
       <formula1>=IF(M497&lt;&gt;"",INDIRECT(VLOOKUP(M497,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M498" xr:uid="{6CD69CB8-46D0-44F6-B028-79DD17A8950B}">
+    <dataValidation type="list" sqref="M498" xr:uid="{5480E5BB-7D1A-4A7B-A479-2E43CB1C3A96}">
       <formula1>=IF(L498&lt;&gt;"",INDIRECT(VLOOKUP(L498,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N498" xr:uid="{30751D19-21B4-43BA-82BF-BD1C5F632FED}">
+    <dataValidation type="list" sqref="N498" xr:uid="{D63C52C4-5D01-4AF7-A17E-AF60B00CFDAF}">
       <formula1>=IF(M498&lt;&gt;"",INDIRECT(VLOOKUP(M498,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M499" xr:uid="{1C9723C3-9B3C-4C8F-93AD-19AD406FC7B9}">
+    <dataValidation type="list" sqref="M499" xr:uid="{0D47561D-E0CD-4940-869F-B4A74F0341D2}">
       <formula1>=IF(L499&lt;&gt;"",INDIRECT(VLOOKUP(L499,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N499" xr:uid="{18957E39-15C3-492A-A685-0820121A32AC}">
+    <dataValidation type="list" sqref="N499" xr:uid="{399B6EC6-9429-4E08-967B-A57B1F1B43F4}">
       <formula1>=IF(M499&lt;&gt;"",INDIRECT(VLOOKUP(M499,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M500" xr:uid="{27E375C6-106B-47FF-8D81-7CCBCA7EABA0}">
+    <dataValidation type="list" sqref="M500" xr:uid="{6227B32E-F4A9-47DC-9FDD-53F00288C8B7}">
       <formula1>=IF(L500&lt;&gt;"",INDIRECT(VLOOKUP(L500,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N500" xr:uid="{92F430AC-3B07-45E0-9A9F-81D27ADE69AD}">
+    <dataValidation type="list" sqref="N500" xr:uid="{E48976CE-95F4-4491-B612-E7C38DFD26A6}">
       <formula1>=IF(M500&lt;&gt;"",INDIRECT(VLOOKUP(M500,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M501" xr:uid="{4CE3E3AE-BDE4-445D-B9BC-AAE538E9EB9D}">
+    <dataValidation type="list" sqref="M501" xr:uid="{62539C21-761F-4035-9F9F-934AFEFD12CB}">
       <formula1>=IF(L501&lt;&gt;"",INDIRECT(VLOOKUP(L501,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N501" xr:uid="{C59F4F0F-6EEB-4BD3-9AC4-A330842555EB}">
+    <dataValidation type="list" sqref="N501" xr:uid="{CF96623C-41F3-4180-BE32-13749E6E5085}">
       <formula1>=IF(M501&lt;&gt;"",INDIRECT(VLOOKUP(M501,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M502" xr:uid="{5C1D5A03-2C67-410A-B983-1DE8F64011DB}">
+    <dataValidation type="list" sqref="M502" xr:uid="{590E62DC-7BF3-42ED-BC1E-39B3A463B779}">
       <formula1>=IF(L502&lt;&gt;"",INDIRECT(VLOOKUP(L502,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N502" xr:uid="{A6C39EC4-86DB-4C1C-96A1-D530EC9C437E}">
+    <dataValidation type="list" sqref="N502" xr:uid="{E8D7CD82-F6CB-45A1-A576-F86A977BFBD6}">
       <formula1>=IF(M502&lt;&gt;"",INDIRECT(VLOOKUP(M502,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M503" xr:uid="{7A643838-BC9E-4D83-9027-F333DDCDB210}">
+    <dataValidation type="list" sqref="M503" xr:uid="{54FAEBCF-7C82-4895-90E0-8B215713DE1C}">
       <formula1>=IF(L503&lt;&gt;"",INDIRECT(VLOOKUP(L503,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N503" xr:uid="{07A00BEC-8B09-40D1-AD87-1F14651B481E}">
+    <dataValidation type="list" sqref="N503" xr:uid="{FD984CD8-D18F-4151-8844-8EBEE27D4200}">
       <formula1>=IF(M503&lt;&gt;"",INDIRECT(VLOOKUP(M503,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M504" xr:uid="{CE0A7E8D-20D1-4397-9F35-FD72F523E144}">
+    <dataValidation type="list" sqref="M504" xr:uid="{783620EC-C7C2-4023-932E-002D2FCDF382}">
       <formula1>=IF(L504&lt;&gt;"",INDIRECT(VLOOKUP(L504,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N504" xr:uid="{8801D71C-8B23-4F7A-99A3-85BD4C895CBD}">
+    <dataValidation type="list" sqref="N504" xr:uid="{9A153570-F574-4BB3-B189-85A1240E6031}">
       <formula1>=IF(M504&lt;&gt;"",INDIRECT(VLOOKUP(M504,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M505" xr:uid="{52A9FD0B-E1E9-40F3-9ECA-A1CBC7461CA9}">
+    <dataValidation type="list" sqref="M505" xr:uid="{DCD2FFD6-552B-458A-BE50-0BC23C195952}">
       <formula1>=IF(L505&lt;&gt;"",INDIRECT(VLOOKUP(L505,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N505" xr:uid="{553B0BCD-6C8D-42F9-85C5-39869CA0A77B}">
+    <dataValidation type="list" sqref="N505" xr:uid="{ED8B43EF-90E5-4940-A15D-CAB3FFC3496A}">
       <formula1>=IF(M505&lt;&gt;"",INDIRECT(VLOOKUP(M505,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M506" xr:uid="{0BD81C5F-1A8A-45FD-B220-33DD99E35D80}">
+    <dataValidation type="list" sqref="M506" xr:uid="{75E4CE57-0669-4054-9F91-C45367A62BA5}">
       <formula1>=IF(L506&lt;&gt;"",INDIRECT(VLOOKUP(L506,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N506" xr:uid="{E8E2714E-4CFD-427A-94FA-8D5B030D451E}">
+    <dataValidation type="list" sqref="N506" xr:uid="{A72F450A-E979-4BBD-8B41-5F1114410832}">
       <formula1>=IF(M506&lt;&gt;"",INDIRECT(VLOOKUP(M506,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M507" xr:uid="{8D5BED6C-D43A-4F83-8FEC-248D6402A02E}">
+    <dataValidation type="list" sqref="M507" xr:uid="{17610CD6-277E-4BFE-9AFD-95AEBFFB6077}">
       <formula1>=IF(L507&lt;&gt;"",INDIRECT(VLOOKUP(L507,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N507" xr:uid="{7F49D4AB-E5B3-47B6-9A5C-FBC9132D4E75}">
+    <dataValidation type="list" sqref="N507" xr:uid="{72081543-DBB5-4938-AB15-A49203DC15BA}">
       <formula1>=IF(M507&lt;&gt;"",INDIRECT(VLOOKUP(M507,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M508" xr:uid="{7AFC5545-A512-4B1B-85F6-1CA0B3BC89B9}">
+    <dataValidation type="list" sqref="M508" xr:uid="{06BFD672-B0EC-4B11-9ADD-3981376636CC}">
       <formula1>=IF(L508&lt;&gt;"",INDIRECT(VLOOKUP(L508,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N508" xr:uid="{672938B6-9F15-4711-8AC1-815ECA5378B6}">
+    <dataValidation type="list" sqref="N508" xr:uid="{1EE77418-AAB7-4BB5-B85E-3AF43903BF73}">
       <formula1>=IF(M508&lt;&gt;"",INDIRECT(VLOOKUP(M508,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M509" xr:uid="{E9E15291-E456-4918-9FDB-B6845FF0B828}">
+    <dataValidation type="list" sqref="M509" xr:uid="{0ABEF1A3-3204-4ED0-B0BA-BBBEC04852D5}">
       <formula1>=IF(L509&lt;&gt;"",INDIRECT(VLOOKUP(L509,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N509" xr:uid="{25471C0D-8121-4259-9915-94AC51CA4A47}">
+    <dataValidation type="list" sqref="N509" xr:uid="{A9287071-A597-486F-AC80-718BC8C8CD1D}">
       <formula1>=IF(M509&lt;&gt;"",INDIRECT(VLOOKUP(M509,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M510" xr:uid="{B40F4321-8B72-40FC-A4C8-EEA9C47732C7}">
+    <dataValidation type="list" sqref="M510" xr:uid="{5E931A8D-564F-4A35-A7B8-C59A70D0D44C}">
       <formula1>=IF(L510&lt;&gt;"",INDIRECT(VLOOKUP(L510,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N510" xr:uid="{4E048F39-F386-4B84-BF49-D7AB9360E59F}">
+    <dataValidation type="list" sqref="N510" xr:uid="{606FAA5A-F20C-4B44-A26C-704BE646BA8C}">
       <formula1>=IF(M510&lt;&gt;"",INDIRECT(VLOOKUP(M510,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M511" xr:uid="{DA97D593-FE69-440A-9F86-6A30B76780A3}">
+    <dataValidation type="list" sqref="M511" xr:uid="{B5180C4A-04E4-4AB5-9CF0-344080BE7F64}">
       <formula1>=IF(L511&lt;&gt;"",INDIRECT(VLOOKUP(L511,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N511" xr:uid="{437F1610-4EC2-4FBE-BB54-F232DB4F9D2F}">
+    <dataValidation type="list" sqref="N511" xr:uid="{B6106765-9D31-4DFC-8206-6DB8892FF8DB}">
       <formula1>=IF(M511&lt;&gt;"",INDIRECT(VLOOKUP(M511,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M512" xr:uid="{3D8537A4-66FE-4C15-A672-4666BBEA3605}">
+    <dataValidation type="list" sqref="M512" xr:uid="{C8964828-4209-4C6C-88D7-3D58F22E525B}">
       <formula1>=IF(L512&lt;&gt;"",INDIRECT(VLOOKUP(L512,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N512" xr:uid="{4D084228-3AE5-41D9-ABA6-146E3A6E5660}">
+    <dataValidation type="list" sqref="N512" xr:uid="{A14DC3F7-F46E-40DC-8727-F0DF5848B494}">
       <formula1>=IF(M512&lt;&gt;"",INDIRECT(VLOOKUP(M512,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M513" xr:uid="{4E4D441F-BA41-4A80-B07A-6A3CC921D314}">
+    <dataValidation type="list" sqref="M513" xr:uid="{05364429-FE5A-4FE8-BD63-1E3673B897F2}">
       <formula1>=IF(L513&lt;&gt;"",INDIRECT(VLOOKUP(L513,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N513" xr:uid="{EF6320FB-5DDB-4F4B-9804-0263EB601488}">
+    <dataValidation type="list" sqref="N513" xr:uid="{A1308F9F-C129-44D1-9E1B-FD989A3189A8}">
       <formula1>=IF(M513&lt;&gt;"",INDIRECT(VLOOKUP(M513,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M514" xr:uid="{4E371F24-CDAD-4556-A108-5192CFA03667}">
+    <dataValidation type="list" sqref="M514" xr:uid="{7F542114-4D74-47CB-86C6-25CA82797BD9}">
       <formula1>=IF(L514&lt;&gt;"",INDIRECT(VLOOKUP(L514,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N514" xr:uid="{4DBA4D2C-C985-40AB-89C2-C9E7A945C479}">
+    <dataValidation type="list" sqref="N514" xr:uid="{EB3FE997-7A35-48B1-AFBE-3B6FEB6D8966}">
       <formula1>=IF(M514&lt;&gt;"",INDIRECT(VLOOKUP(M514,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M515" xr:uid="{E9D72418-DF4E-4703-BA7F-4121E9F98B77}">
+    <dataValidation type="list" sqref="M515" xr:uid="{FAB08075-3A25-4CC2-BD52-EA30E3C39ED2}">
       <formula1>=IF(L515&lt;&gt;"",INDIRECT(VLOOKUP(L515,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N515" xr:uid="{010B3574-3927-4195-A2B8-B1B5380D3FBB}">
+    <dataValidation type="list" sqref="N515" xr:uid="{AC32FB9F-6F3D-4BC6-8014-C76B5F3B8FAF}">
       <formula1>=IF(M515&lt;&gt;"",INDIRECT(VLOOKUP(M515,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M516" xr:uid="{40ECFB21-63E0-46C7-AC1E-5EF7CCE0837D}">
+    <dataValidation type="list" sqref="M516" xr:uid="{91136729-0F25-4797-B818-71D597D980A7}">
       <formula1>=IF(L516&lt;&gt;"",INDIRECT(VLOOKUP(L516,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N516" xr:uid="{2D613C6C-1331-4F49-944B-C4302EFC4F1E}">
+    <dataValidation type="list" sqref="N516" xr:uid="{46134A26-E7E0-410E-8B32-186722D8C5BE}">
       <formula1>=IF(M516&lt;&gt;"",INDIRECT(VLOOKUP(M516,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M517" xr:uid="{BD22A6C9-B9ED-4991-AC5B-944C477EE8C0}">
+    <dataValidation type="list" sqref="M517" xr:uid="{6BA8E48D-1CAB-49DC-B0EB-DF6FDE202484}">
       <formula1>=IF(L517&lt;&gt;"",INDIRECT(VLOOKUP(L517,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N517" xr:uid="{F7FB80E8-8836-4A5A-AE36-C626669301AC}">
+    <dataValidation type="list" sqref="N517" xr:uid="{9AC23F10-FF65-4493-8615-1172C4EB780B}">
       <formula1>=IF(M517&lt;&gt;"",INDIRECT(VLOOKUP(M517,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M518" xr:uid="{8B0F4AD6-A2F2-4507-8D3A-FCD4C83A8FB4}">
+    <dataValidation type="list" sqref="M518" xr:uid="{0E893F2C-3CD1-4B07-A9D6-93CEAF4E1D83}">
       <formula1>=IF(L518&lt;&gt;"",INDIRECT(VLOOKUP(L518,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N518" xr:uid="{4E4943B9-624F-4AEF-96EF-4D191CFDFA32}">
+    <dataValidation type="list" sqref="N518" xr:uid="{9459A785-5D1A-42EA-8C8C-096530DB3F4A}">
       <formula1>=IF(M518&lt;&gt;"",INDIRECT(VLOOKUP(M518,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M519" xr:uid="{F8E95EF5-0F13-41CB-B46C-3A320AEAB72A}">
+    <dataValidation type="list" sqref="M519" xr:uid="{9B03E841-8629-4E17-A754-BE7BDD638B46}">
       <formula1>=IF(L519&lt;&gt;"",INDIRECT(VLOOKUP(L519,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N519" xr:uid="{CF35931D-F7FC-40AC-9986-7B8795CE96D6}">
+    <dataValidation type="list" sqref="N519" xr:uid="{2351B1DD-F337-4447-839A-3ACD714B484E}">
       <formula1>=IF(M519&lt;&gt;"",INDIRECT(VLOOKUP(M519,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M520" xr:uid="{A15D7A0A-4721-42C0-B814-5EF24086DDBA}">
+    <dataValidation type="list" sqref="M520" xr:uid="{B80A71CF-AA0D-439D-89DF-561FA85BFBF5}">
       <formula1>=IF(L520&lt;&gt;"",INDIRECT(VLOOKUP(L520,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N520" xr:uid="{EF0FA447-9D50-451C-BAB2-8AEC769EADD3}">
+    <dataValidation type="list" sqref="N520" xr:uid="{00D69C7C-7D10-4719-8D1C-D1BBD88BC7AC}">
       <formula1>=IF(M520&lt;&gt;"",INDIRECT(VLOOKUP(M520,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M521" xr:uid="{7D11468C-FB2C-463D-BE5E-68D5C01336EB}">
+    <dataValidation type="list" sqref="M521" xr:uid="{95B164BE-216D-4D55-BF5A-CFB76AFE68C2}">
       <formula1>=IF(L521&lt;&gt;"",INDIRECT(VLOOKUP(L521,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N521" xr:uid="{ECACC9B3-259E-4B48-8DBD-902F4471281A}">
+    <dataValidation type="list" sqref="N521" xr:uid="{723705EE-F8BA-45E1-885D-B068235F3102}">
       <formula1>=IF(M521&lt;&gt;"",INDIRECT(VLOOKUP(M521,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M522" xr:uid="{18EFE5F0-5E22-4FD4-B85C-DBAFA15D670C}">
+    <dataValidation type="list" sqref="M522" xr:uid="{4E194D89-A32D-4269-A656-EB292EFF002C}">
       <formula1>=IF(L522&lt;&gt;"",INDIRECT(VLOOKUP(L522,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N522" xr:uid="{238F6BE7-C212-4C5C-90BA-662F15EAC563}">
+    <dataValidation type="list" sqref="N522" xr:uid="{B7DAFC11-32CE-4266-94D5-A4BAA0CE2F22}">
       <formula1>=IF(M522&lt;&gt;"",INDIRECT(VLOOKUP(M522,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M523" xr:uid="{4AC7D80D-958F-4641-91D8-AE7AC8B592E6}">
+    <dataValidation type="list" sqref="M523" xr:uid="{F4286875-26E9-4756-AC19-DC1CD4AFE4BB}">
       <formula1>=IF(L523&lt;&gt;"",INDIRECT(VLOOKUP(L523,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N523" xr:uid="{8B23DA62-828B-476F-9F98-9241C8AF01E0}">
+    <dataValidation type="list" sqref="N523" xr:uid="{BFA264EC-0AAD-47E0-9503-4177548FB7C9}">
       <formula1>=IF(M523&lt;&gt;"",INDIRECT(VLOOKUP(M523,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M524" xr:uid="{CB6F2A7A-6E73-4229-BA53-E44F11EB2E2B}">
+    <dataValidation type="list" sqref="M524" xr:uid="{3FBDABCD-6145-4FAC-9EC6-D5E693596F88}">
       <formula1>=IF(L524&lt;&gt;"",INDIRECT(VLOOKUP(L524,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N524" xr:uid="{4388CA1F-94B1-4014-A4CD-486FF53EDB35}">
+    <dataValidation type="list" sqref="N524" xr:uid="{DC049DE9-096B-4799-8BC3-EC712CB0C504}">
       <formula1>=IF(M524&lt;&gt;"",INDIRECT(VLOOKUP(M524,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M525" xr:uid="{E016E1BF-815E-43F8-875C-16DDC2FE723E}">
+    <dataValidation type="list" sqref="M525" xr:uid="{F89BCFBE-2A25-49A5-9262-78F6DEDEECFA}">
       <formula1>=IF(L525&lt;&gt;"",INDIRECT(VLOOKUP(L525,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N525" xr:uid="{1B136457-0E7C-4CB3-8D23-CD414CEDE8BF}">
+    <dataValidation type="list" sqref="N525" xr:uid="{98AEA1B5-11DC-4B22-B416-F30C1EB8895A}">
       <formula1>=IF(M525&lt;&gt;"",INDIRECT(VLOOKUP(M525,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M526" xr:uid="{3376655B-8B4D-4736-B53D-B8210A5D1EEE}">
+    <dataValidation type="list" sqref="M526" xr:uid="{2596CDD3-E5A6-4E00-B458-B68788D707F2}">
       <formula1>=IF(L526&lt;&gt;"",INDIRECT(VLOOKUP(L526,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N526" xr:uid="{2D2C562E-C95D-44DC-BC32-B488590CBFB7}">
+    <dataValidation type="list" sqref="N526" xr:uid="{EFC6645F-8B61-4321-8B07-0B94EDE29FB5}">
       <formula1>=IF(M526&lt;&gt;"",INDIRECT(VLOOKUP(M526,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M527" xr:uid="{0FDC05E2-76D4-438C-8717-A92894F93205}">
+    <dataValidation type="list" sqref="M527" xr:uid="{F618C7B8-37AC-47D1-B921-8B6B9D090BAF}">
       <formula1>=IF(L527&lt;&gt;"",INDIRECT(VLOOKUP(L527,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N527" xr:uid="{A051CBF8-B0EF-41B1-979D-0C9E71FC963E}">
+    <dataValidation type="list" sqref="N527" xr:uid="{23D6F293-CC6E-4FAF-9F20-BAE9043AD848}">
       <formula1>=IF(M527&lt;&gt;"",INDIRECT(VLOOKUP(M527,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M528" xr:uid="{7A21DFD4-A854-4395-A490-A5058691B6E8}">
+    <dataValidation type="list" sqref="M528" xr:uid="{E8421DE5-D4A3-48E1-BB8D-14F06BA8A2B9}">
       <formula1>=IF(L528&lt;&gt;"",INDIRECT(VLOOKUP(L528,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N528" xr:uid="{0D85F885-5FCE-4C8C-A49C-15E87C56B457}">
+    <dataValidation type="list" sqref="N528" xr:uid="{A0371A26-941D-43A2-A04C-89353BD2C35B}">
       <formula1>=IF(M528&lt;&gt;"",INDIRECT(VLOOKUP(M528,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M529" xr:uid="{6CB2E664-C92D-4966-A7A4-940D62AB0267}">
+    <dataValidation type="list" sqref="M529" xr:uid="{3038B615-F354-495D-A6EA-21132E5D1659}">
       <formula1>=IF(L529&lt;&gt;"",INDIRECT(VLOOKUP(L529,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N529" xr:uid="{D96EC38D-FFE4-4735-A995-F3DCA0D63005}">
+    <dataValidation type="list" sqref="N529" xr:uid="{6C58C655-70CF-438F-9954-DFF92FC4F9A9}">
       <formula1>=IF(M529&lt;&gt;"",INDIRECT(VLOOKUP(M529,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M530" xr:uid="{C4C5A58F-A42D-4701-86EA-944E84497315}">
+    <dataValidation type="list" sqref="M530" xr:uid="{CCA271DB-D304-470B-A964-6B0640DAE954}">
       <formula1>=IF(L530&lt;&gt;"",INDIRECT(VLOOKUP(L530,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N530" xr:uid="{6BEBD742-06AD-42D2-AF5A-E92F538C7A97}">
+    <dataValidation type="list" sqref="N530" xr:uid="{0BCA4C0F-5E48-456F-8210-E9F22388F2ED}">
       <formula1>=IF(M530&lt;&gt;"",INDIRECT(VLOOKUP(M530,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M531" xr:uid="{4A02DD7D-66C1-49C2-80B1-28DF78771775}">
+    <dataValidation type="list" sqref="M531" xr:uid="{F9A6D82B-9E13-4AE0-ADAD-0711D98938BF}">
       <formula1>=IF(L531&lt;&gt;"",INDIRECT(VLOOKUP(L531,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N531" xr:uid="{158879E5-B12B-46AC-B176-FACC188F7665}">
+    <dataValidation type="list" sqref="N531" xr:uid="{EF7E75BD-96E6-4BA0-AFF2-2B0B1F047A09}">
       <formula1>=IF(M531&lt;&gt;"",INDIRECT(VLOOKUP(M531,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M532" xr:uid="{23D4D278-7BCE-4F94-B356-853E68545784}">
+    <dataValidation type="list" sqref="M532" xr:uid="{1E05DC81-2E94-4479-A316-EADD63779231}">
       <formula1>=IF(L532&lt;&gt;"",INDIRECT(VLOOKUP(L532,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N532" xr:uid="{D1E7E395-E85D-4F85-9D9D-A77E3DF231DC}">
+    <dataValidation type="list" sqref="N532" xr:uid="{56DEB36F-8096-41C2-96F8-14B4CCE9DBEF}">
       <formula1>=IF(M532&lt;&gt;"",INDIRECT(VLOOKUP(M532,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M533" xr:uid="{D34E065C-3A5C-4072-A1B7-EB7085B84B40}">
+    <dataValidation type="list" sqref="M533" xr:uid="{D7E0A014-7D5B-4302-B625-1A7841D9679B}">
       <formula1>=IF(L533&lt;&gt;"",INDIRECT(VLOOKUP(L533,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N533" xr:uid="{2AC230A5-8297-4551-8DBF-91E7BE0F7DB5}">
+    <dataValidation type="list" sqref="N533" xr:uid="{AD6F3C0A-55AC-4408-9213-5C222E9072CE}">
       <formula1>=IF(M533&lt;&gt;"",INDIRECT(VLOOKUP(M533,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M534" xr:uid="{7E2D83EF-BA39-4D7E-BDCD-A58516BBB127}">
+    <dataValidation type="list" sqref="M534" xr:uid="{DF99DF19-7417-42EE-A5F6-0AFC915FFD4C}">
       <formula1>=IF(L534&lt;&gt;"",INDIRECT(VLOOKUP(L534,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N534" xr:uid="{F7423AC4-E315-4155-B254-CF31889C398B}">
+    <dataValidation type="list" sqref="N534" xr:uid="{413CFF69-7D53-475C-A077-D6893CE1D078}">
       <formula1>=IF(M534&lt;&gt;"",INDIRECT(VLOOKUP(M534,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M535" xr:uid="{57BF8FFD-EE7A-43E5-8CEE-EDA5DA7F1CDA}">
+    <dataValidation type="list" sqref="M535" xr:uid="{B4AAC9C1-F30F-4D3B-9E68-B3DE7CFBC5ED}">
       <formula1>=IF(L535&lt;&gt;"",INDIRECT(VLOOKUP(L535,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N535" xr:uid="{59A61AC9-F2E2-4C99-B3D3-D8837090B502}">
+    <dataValidation type="list" sqref="N535" xr:uid="{D239E841-3969-43EC-9ABC-92F5CA4A6685}">
       <formula1>=IF(M535&lt;&gt;"",INDIRECT(VLOOKUP(M535,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M536" xr:uid="{926D968C-E3C6-426A-BF40-4187E665D7E8}">
+    <dataValidation type="list" sqref="M536" xr:uid="{92AEA53E-1926-46C2-8155-2BACFBC1D3A6}">
       <formula1>=IF(L536&lt;&gt;"",INDIRECT(VLOOKUP(L536,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N536" xr:uid="{78831075-D07F-4CD5-926E-5F07C3FCAAFD}">
+    <dataValidation type="list" sqref="N536" xr:uid="{809EB82F-E312-4F95-A058-44273EA555A5}">
       <formula1>=IF(M536&lt;&gt;"",INDIRECT(VLOOKUP(M536,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M537" xr:uid="{7491DD6E-D4F7-4AD1-B683-0386C6B4E34D}">
+    <dataValidation type="list" sqref="M537" xr:uid="{E4F29005-CF7B-4701-94C7-A87C1BAEFCEC}">
       <formula1>=IF(L537&lt;&gt;"",INDIRECT(VLOOKUP(L537,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N537" xr:uid="{1783A110-FCCF-4300-9591-0AAA6191085C}">
+    <dataValidation type="list" sqref="N537" xr:uid="{C7CCC073-07E1-4843-9577-763CF747D7C5}">
       <formula1>=IF(M537&lt;&gt;"",INDIRECT(VLOOKUP(M537,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M538" xr:uid="{FFCDCE1A-1C00-42ED-B898-E33C69DE0020}">
+    <dataValidation type="list" sqref="M538" xr:uid="{B87A271D-300D-44CA-BD79-8DE92B5E2A6F}">
       <formula1>=IF(L538&lt;&gt;"",INDIRECT(VLOOKUP(L538,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N538" xr:uid="{6883DD58-E949-494F-A32A-B514CA8412AF}">
+    <dataValidation type="list" sqref="N538" xr:uid="{B804D918-15B4-4185-9324-928736EF1A21}">
       <formula1>=IF(M538&lt;&gt;"",INDIRECT(VLOOKUP(M538,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M539" xr:uid="{090D3471-92CA-493F-9526-4CFDC997F812}">
+    <dataValidation type="list" sqref="M539" xr:uid="{E35A1D05-F7B2-479F-9E56-70C65A6BAE99}">
       <formula1>=IF(L539&lt;&gt;"",INDIRECT(VLOOKUP(L539,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N539" xr:uid="{556EAAE3-3AA6-4BCB-9795-D1C4BEB621B5}">
+    <dataValidation type="list" sqref="N539" xr:uid="{289D727C-C137-41B8-9C5D-ED39CE26373F}">
       <formula1>=IF(M539&lt;&gt;"",INDIRECT(VLOOKUP(M539,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M540" xr:uid="{63D79D8D-89EC-4894-8D23-2F555E7ACA70}">
+    <dataValidation type="list" sqref="M540" xr:uid="{DA401BEF-2310-4DD8-BF28-BF753B55E171}">
       <formula1>=IF(L540&lt;&gt;"",INDIRECT(VLOOKUP(L540,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N540" xr:uid="{75A6E206-67FF-4C3E-9004-C00BB46AE659}">
+    <dataValidation type="list" sqref="N540" xr:uid="{CF1F1616-0A5C-46FF-94D5-22A7F5DDFF14}">
       <formula1>=IF(M540&lt;&gt;"",INDIRECT(VLOOKUP(M540,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M541" xr:uid="{B8E6B591-8B6E-4EF6-808F-553311866797}">
+    <dataValidation type="list" sqref="M541" xr:uid="{6A1BEC88-44B6-4460-80AD-FC972EB4BA31}">
       <formula1>=IF(L541&lt;&gt;"",INDIRECT(VLOOKUP(L541,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N541" xr:uid="{CB06659C-1B51-4A26-A42D-C702FFA75D9E}">
+    <dataValidation type="list" sqref="N541" xr:uid="{66DFB34A-70B0-482A-A67F-6917F556787A}">
       <formula1>=IF(M541&lt;&gt;"",INDIRECT(VLOOKUP(M541,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M542" xr:uid="{B241C03F-E265-4614-B716-8CF6CB60F626}">
+    <dataValidation type="list" sqref="M542" xr:uid="{EBDDC28A-F0ED-46E8-9C2F-0405A7389DF3}">
       <formula1>=IF(L542&lt;&gt;"",INDIRECT(VLOOKUP(L542,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N542" xr:uid="{C2610B36-93BB-4099-AE32-FF878883B68C}">
+    <dataValidation type="list" sqref="N542" xr:uid="{BECE1D0F-F716-46D0-A725-6AA25EF5F541}">
       <formula1>=IF(M542&lt;&gt;"",INDIRECT(VLOOKUP(M542,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M543" xr:uid="{9DCBC55A-DF6F-4537-BE15-E47595252047}">
+    <dataValidation type="list" sqref="M543" xr:uid="{85D55AA6-56A1-49F7-BF64-2FBDD324F24A}">
       <formula1>=IF(L543&lt;&gt;"",INDIRECT(VLOOKUP(L543,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N543" xr:uid="{A1EBF633-1A2C-4DD9-9351-5A193DBB3B7A}">
+    <dataValidation type="list" sqref="N543" xr:uid="{2F879274-EE5E-4710-9D61-15C426FA54B9}">
       <formula1>=IF(M543&lt;&gt;"",INDIRECT(VLOOKUP(M543,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M544" xr:uid="{2D69A107-5136-46CA-9C47-7CD492331545}">
+    <dataValidation type="list" sqref="M544" xr:uid="{B80F93B6-1F32-4E62-8F95-495FB2FDA34B}">
       <formula1>=IF(L544&lt;&gt;"",INDIRECT(VLOOKUP(L544,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N544" xr:uid="{CFDF4CD0-19B5-494E-AC2F-2E08F69D76BF}">
+    <dataValidation type="list" sqref="N544" xr:uid="{9B65F163-059E-4FFF-876A-8DE0C50A4531}">
       <formula1>=IF(M544&lt;&gt;"",INDIRECT(VLOOKUP(M544,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M545" xr:uid="{B9AD6F71-BE70-492B-8BBE-3D39137E4708}">
+    <dataValidation type="list" sqref="M545" xr:uid="{9BB5B5F9-5F7F-4258-B2CD-D7A2F8F92D38}">
       <formula1>=IF(L545&lt;&gt;"",INDIRECT(VLOOKUP(L545,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N545" xr:uid="{1D398068-EEDC-4FA8-A1AC-1D763A7CE33E}">
+    <dataValidation type="list" sqref="N545" xr:uid="{7AC39809-8E85-49C2-9D34-9F8DDFFB5751}">
       <formula1>=IF(M545&lt;&gt;"",INDIRECT(VLOOKUP(M545,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M546" xr:uid="{68FDDC51-21FD-4043-BE32-D60C334DE8C6}">
+    <dataValidation type="list" sqref="M546" xr:uid="{D4A43BFD-4746-404E-9253-CE03CC839C11}">
       <formula1>=IF(L546&lt;&gt;"",INDIRECT(VLOOKUP(L546,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N546" xr:uid="{B8961FA1-666C-4F95-A6D5-37AE2D7850D4}">
+    <dataValidation type="list" sqref="N546" xr:uid="{3571FF90-46AC-44B5-A48B-1DAEB7D9BBCF}">
       <formula1>=IF(M546&lt;&gt;"",INDIRECT(VLOOKUP(M546,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M547" xr:uid="{92C717F1-A833-4A5B-A5A8-7617B50CB2D5}">
+    <dataValidation type="list" sqref="M547" xr:uid="{B73047E6-80CC-4783-9ADC-227B3FB39A01}">
       <formula1>=IF(L547&lt;&gt;"",INDIRECT(VLOOKUP(L547,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N547" xr:uid="{F71924C8-729F-400F-90A0-9B5D4E8BED8E}">
+    <dataValidation type="list" sqref="N547" xr:uid="{ECC6E742-9641-4BF3-9CBB-73ED1BE7B160}">
       <formula1>=IF(M547&lt;&gt;"",INDIRECT(VLOOKUP(M547,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M548" xr:uid="{5D7F44E3-74F9-4EB6-942C-922799100FA2}">
+    <dataValidation type="list" sqref="M548" xr:uid="{A1F552B7-0079-4F50-ACDB-78F46AC4D3E3}">
       <formula1>=IF(L548&lt;&gt;"",INDIRECT(VLOOKUP(L548,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N548" xr:uid="{8FBC91E6-241A-41BC-9B8B-62CE9FEFE4A0}">
+    <dataValidation type="list" sqref="N548" xr:uid="{046385D7-E95B-4729-A3C2-060249743B25}">
       <formula1>=IF(M548&lt;&gt;"",INDIRECT(VLOOKUP(M548,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M549" xr:uid="{8552464C-EE1E-45D6-B391-00B8A46D6CA6}">
+    <dataValidation type="list" sqref="M549" xr:uid="{4E1ED35B-3265-4DF7-ACED-BF22041D7F41}">
       <formula1>=IF(L549&lt;&gt;"",INDIRECT(VLOOKUP(L549,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N549" xr:uid="{BB949BDE-9D7D-4AAA-BC71-D262110217E6}">
+    <dataValidation type="list" sqref="N549" xr:uid="{874D5FC5-ECF2-4BA5-9ABB-D38058B91756}">
       <formula1>=IF(M549&lt;&gt;"",INDIRECT(VLOOKUP(M549,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M550" xr:uid="{DAF59178-BC97-484D-93B0-2036F4DEA22B}">
+    <dataValidation type="list" sqref="M550" xr:uid="{4FCBF62D-29EE-4D76-9065-8BC6F65EDF66}">
       <formula1>=IF(L550&lt;&gt;"",INDIRECT(VLOOKUP(L550,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N550" xr:uid="{54C40262-888D-428F-8260-7D091A765DFB}">
+    <dataValidation type="list" sqref="N550" xr:uid="{BA0A4B98-4273-4318-B10C-3597AC01CF57}">
       <formula1>=IF(M550&lt;&gt;"",INDIRECT(VLOOKUP(M550,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M551" xr:uid="{CF070DD3-C80C-4025-94E1-4679C987678E}">
+    <dataValidation type="list" sqref="M551" xr:uid="{00382745-0E2E-445E-8962-BB9E310D4886}">
       <formula1>=IF(L551&lt;&gt;"",INDIRECT(VLOOKUP(L551,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N551" xr:uid="{2B552908-9850-4012-AF23-67D0C7476F73}">
+    <dataValidation type="list" sqref="N551" xr:uid="{9BAB2244-ED67-49BF-AC99-FC348873EE67}">
       <formula1>=IF(M551&lt;&gt;"",INDIRECT(VLOOKUP(M551,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M552" xr:uid="{A215326B-3748-4A1A-A981-05D1E7909810}">
+    <dataValidation type="list" sqref="M552" xr:uid="{FDB6737F-F556-449A-BBB5-49F0A3D7FE15}">
       <formula1>=IF(L552&lt;&gt;"",INDIRECT(VLOOKUP(L552,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N552" xr:uid="{15EE4CEC-48A8-47BD-A825-B35ECC55B318}">
+    <dataValidation type="list" sqref="N552" xr:uid="{1A349DBE-3E96-41CB-B149-B51FF6B8151E}">
       <formula1>=IF(M552&lt;&gt;"",INDIRECT(VLOOKUP(M552,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M553" xr:uid="{54A1CF9C-C833-4E00-9E54-41761AF78431}">
+    <dataValidation type="list" sqref="M553" xr:uid="{4EE4A3EE-293C-4BC1-B455-26D9701C7EE7}">
       <formula1>=IF(L553&lt;&gt;"",INDIRECT(VLOOKUP(L553,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N553" xr:uid="{EDB3B5B9-4EC2-447C-A307-9354F7C1073F}">
+    <dataValidation type="list" sqref="N553" xr:uid="{A71F2D88-B74D-442D-BDE5-566D076E74F3}">
       <formula1>=IF(M553&lt;&gt;"",INDIRECT(VLOOKUP(M553,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M554" xr:uid="{009078C0-81FB-4DA0-9A68-5EA8105F9183}">
+    <dataValidation type="list" sqref="M554" xr:uid="{46C1ADB9-B36E-4F62-A0E5-EFDCA3666938}">
       <formula1>=IF(L554&lt;&gt;"",INDIRECT(VLOOKUP(L554,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N554" xr:uid="{B044960F-D5D9-45CE-98AB-880530D7E1A7}">
+    <dataValidation type="list" sqref="N554" xr:uid="{C47309FE-693B-4486-86B7-0D7AEFCBE4F7}">
       <formula1>=IF(M554&lt;&gt;"",INDIRECT(VLOOKUP(M554,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M555" xr:uid="{7944207E-6780-4085-A89A-72129410EDC7}">
+    <dataValidation type="list" sqref="M555" xr:uid="{53FFD2E8-775D-41AA-9A61-891A97C4FC4E}">
       <formula1>=IF(L555&lt;&gt;"",INDIRECT(VLOOKUP(L555,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N555" xr:uid="{4035008D-B538-4AD1-8297-00F7F923681D}">
+    <dataValidation type="list" sqref="N555" xr:uid="{76C9A0F4-E6F9-4331-B6A1-BC7083598E9F}">
       <formula1>=IF(M555&lt;&gt;"",INDIRECT(VLOOKUP(M555,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M556" xr:uid="{93D1FFD6-08FB-4246-9FD0-8EF7422F7480}">
+    <dataValidation type="list" sqref="M556" xr:uid="{79C504B1-E59D-4DDB-B210-D9341F65D9EC}">
       <formula1>=IF(L556&lt;&gt;"",INDIRECT(VLOOKUP(L556,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N556" xr:uid="{247C0704-AEC9-424A-98ED-F0EC021F8548}">
+    <dataValidation type="list" sqref="N556" xr:uid="{0CBC01CD-DC60-4623-8D6F-7478967D0409}">
       <formula1>=IF(M556&lt;&gt;"",INDIRECT(VLOOKUP(M556,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M557" xr:uid="{7A79CC00-1A9C-41FE-8915-BF10723705E4}">
+    <dataValidation type="list" sqref="M557" xr:uid="{98B2BFAD-2937-4FB7-9491-A3CBD6441F50}">
       <formula1>=IF(L557&lt;&gt;"",INDIRECT(VLOOKUP(L557,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N557" xr:uid="{A520E3DC-4A2E-45EB-AFED-CB2D5D252AF2}">
+    <dataValidation type="list" sqref="N557" xr:uid="{8FE75EA3-0083-4204-A2B9-8357C5A99780}">
       <formula1>=IF(M557&lt;&gt;"",INDIRECT(VLOOKUP(M557,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M558" xr:uid="{3D00BE09-83D6-4CED-87FA-359F7F018BE6}">
+    <dataValidation type="list" sqref="M558" xr:uid="{D613CB13-7255-4BA5-8A79-9CC6BA6DCA99}">
       <formula1>=IF(L558&lt;&gt;"",INDIRECT(VLOOKUP(L558,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N558" xr:uid="{F494BE75-504A-4451-BD1F-DBDAFB153AEB}">
+    <dataValidation type="list" sqref="N558" xr:uid="{D97FAB83-622B-4B36-896B-AA774F991D13}">
       <formula1>=IF(M558&lt;&gt;"",INDIRECT(VLOOKUP(M558,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M559" xr:uid="{7426D7ED-388B-49AA-8A69-D0E8E55661E5}">
+    <dataValidation type="list" sqref="M559" xr:uid="{809FC481-2851-403A-B079-A3EFA419F1F2}">
       <formula1>=IF(L559&lt;&gt;"",INDIRECT(VLOOKUP(L559,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N559" xr:uid="{9CDBB44E-A3FC-4078-A730-321BE315300D}">
+    <dataValidation type="list" sqref="N559" xr:uid="{28A29A1C-039E-4AE8-9E75-EF43529A801D}">
       <formula1>=IF(M559&lt;&gt;"",INDIRECT(VLOOKUP(M559,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M560" xr:uid="{799468E0-1D73-4196-90E5-1DD140BADCC5}">
+    <dataValidation type="list" sqref="M560" xr:uid="{4515DCAA-37E5-463C-923B-E96909265985}">
       <formula1>=IF(L560&lt;&gt;"",INDIRECT(VLOOKUP(L560,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N560" xr:uid="{6EFC4343-32C9-4730-9C45-A3B5A1A10DC0}">
+    <dataValidation type="list" sqref="N560" xr:uid="{823A8805-9560-483B-AEDC-A93B7531996D}">
       <formula1>=IF(M560&lt;&gt;"",INDIRECT(VLOOKUP(M560,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M561" xr:uid="{C2361C55-8F64-4F56-B43F-A6460CDBF1E2}">
+    <dataValidation type="list" sqref="M561" xr:uid="{650C65E6-B63B-4B90-BB13-4BE526B0DE0A}">
       <formula1>=IF(L561&lt;&gt;"",INDIRECT(VLOOKUP(L561,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N561" xr:uid="{A96DAAA2-5762-4335-9656-101925D2DEC2}">
+    <dataValidation type="list" sqref="N561" xr:uid="{58120DAE-81DA-4124-B222-92F113FA3C56}">
       <formula1>=IF(M561&lt;&gt;"",INDIRECT(VLOOKUP(M561,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M562" xr:uid="{6C0AB2DE-917A-4EC0-80C7-C3200FE4CA58}">
+    <dataValidation type="list" sqref="M562" xr:uid="{5A4AF038-6172-4270-8533-49ACCAA3B53A}">
       <formula1>=IF(L562&lt;&gt;"",INDIRECT(VLOOKUP(L562,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N562" xr:uid="{E7B18CA5-E0EA-48EC-90FB-E77DD13DA032}">
+    <dataValidation type="list" sqref="N562" xr:uid="{98C3B749-8722-4974-93A7-79232128A937}">
       <formula1>=IF(M562&lt;&gt;"",INDIRECT(VLOOKUP(M562,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M563" xr:uid="{E49A552E-DD2A-4371-A98C-A20AF2A37A6E}">
+    <dataValidation type="list" sqref="M563" xr:uid="{1307FAF0-BED9-4D79-A346-C207EDBC6F30}">
       <formula1>=IF(L563&lt;&gt;"",INDIRECT(VLOOKUP(L563,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N563" xr:uid="{7BEA601F-91B0-4C80-ABF3-2FD6C98D3A2C}">
+    <dataValidation type="list" sqref="N563" xr:uid="{1B577CCC-5C48-4F98-9500-A3391C1E268B}">
       <formula1>=IF(M563&lt;&gt;"",INDIRECT(VLOOKUP(M563,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M564" xr:uid="{F5F620E7-64C9-431A-ABFC-516BDB18E7C8}">
+    <dataValidation type="list" sqref="M564" xr:uid="{DB5E9542-1DF8-4FDC-A6B3-C7EAB8345DC8}">
       <formula1>=IF(L564&lt;&gt;"",INDIRECT(VLOOKUP(L564,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N564" xr:uid="{F3AB8F3F-D59E-4266-A05D-9DDF5672157E}">
+    <dataValidation type="list" sqref="N564" xr:uid="{FDE717E2-E5FC-45DF-BBB5-A49E7888F067}">
       <formula1>=IF(M564&lt;&gt;"",INDIRECT(VLOOKUP(M564,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M565" xr:uid="{933478A4-0B62-4A91-B4D3-281E72A873C8}">
+    <dataValidation type="list" sqref="M565" xr:uid="{FB0ADEF6-99D3-48D6-B71F-5AFC1BF3C612}">
       <formula1>=IF(L565&lt;&gt;"",INDIRECT(VLOOKUP(L565,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N565" xr:uid="{F887B7EA-6A7F-4D23-8948-66B8B5408366}">
+    <dataValidation type="list" sqref="N565" xr:uid="{DAD739C5-84F6-4D23-8346-CDC291F247BE}">
       <formula1>=IF(M565&lt;&gt;"",INDIRECT(VLOOKUP(M565,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M566" xr:uid="{52FFD986-0ABF-4D71-9B11-7F184ED8E4BA}">
+    <dataValidation type="list" sqref="M566" xr:uid="{6AF114E7-972B-4E35-957F-1DC2E1AA97FA}">
       <formula1>=IF(L566&lt;&gt;"",INDIRECT(VLOOKUP(L566,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N566" xr:uid="{93953F59-33EF-4DB7-85B3-8528339487EA}">
+    <dataValidation type="list" sqref="N566" xr:uid="{AED88DBE-64D3-41DB-83ED-F3926DE81569}">
       <formula1>=IF(M566&lt;&gt;"",INDIRECT(VLOOKUP(M566,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M567" xr:uid="{E800749F-11AF-4C18-9514-D9C4C9775645}">
+    <dataValidation type="list" sqref="M567" xr:uid="{30744531-F6B3-43FA-A87C-98CAEBB8568B}">
       <formula1>=IF(L567&lt;&gt;"",INDIRECT(VLOOKUP(L567,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N567" xr:uid="{117A27BE-658D-419F-963A-3B405CA72AF5}">
+    <dataValidation type="list" sqref="N567" xr:uid="{3983C565-664D-43A0-B476-0EA2CCEEB573}">
       <formula1>=IF(M567&lt;&gt;"",INDIRECT(VLOOKUP(M567,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M568" xr:uid="{57B9ABB5-3F5A-4132-A664-9D0D1A789079}">
+    <dataValidation type="list" sqref="M568" xr:uid="{A01093C2-6384-4112-981C-2FC46A9F85C3}">
       <formula1>=IF(L568&lt;&gt;"",INDIRECT(VLOOKUP(L568,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N568" xr:uid="{A2176237-47B3-42B4-A261-532CB5D31AF0}">
+    <dataValidation type="list" sqref="N568" xr:uid="{164BCB1D-913B-42CA-A75D-EBAC95759D6F}">
       <formula1>=IF(M568&lt;&gt;"",INDIRECT(VLOOKUP(M568,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M569" xr:uid="{8F4B02CE-EE61-4B0B-954D-6B1ED9D48960}">
+    <dataValidation type="list" sqref="M569" xr:uid="{43646B41-3645-4903-8F98-C61B05A79F64}">
       <formula1>=IF(L569&lt;&gt;"",INDIRECT(VLOOKUP(L569,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N569" xr:uid="{E0430334-85A4-454C-BCA7-91E73E6D0D63}">
+    <dataValidation type="list" sqref="N569" xr:uid="{BAD35BFD-699A-4E65-A428-885DE47AC044}">
       <formula1>=IF(M569&lt;&gt;"",INDIRECT(VLOOKUP(M569,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M570" xr:uid="{34204099-AA8F-4E60-B4A7-55F9FA48475B}">
+    <dataValidation type="list" sqref="M570" xr:uid="{D79355DE-9F39-42F0-9F00-00A3537CD790}">
       <formula1>=IF(L570&lt;&gt;"",INDIRECT(VLOOKUP(L570,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N570" xr:uid="{2359D8EB-347F-4F2F-8A38-E92A142A725C}">
+    <dataValidation type="list" sqref="N570" xr:uid="{F58772BA-051F-4996-8487-B264FA77AE10}">
       <formula1>=IF(M570&lt;&gt;"",INDIRECT(VLOOKUP(M570,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M571" xr:uid="{6D7F37AC-F15D-4C60-B5DC-B040D7D25E2C}">
+    <dataValidation type="list" sqref="M571" xr:uid="{50901BF9-249D-4C9F-98A7-9A4499E31806}">
       <formula1>=IF(L571&lt;&gt;"",INDIRECT(VLOOKUP(L571,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N571" xr:uid="{649CE33E-B703-48CB-BA76-C3C6176CED22}">
+    <dataValidation type="list" sqref="N571" xr:uid="{2CA82AFE-1098-49C9-8165-A9A42DB22831}">
       <formula1>=IF(M571&lt;&gt;"",INDIRECT(VLOOKUP(M571,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M572" xr:uid="{4D0282A0-3332-4089-96A1-C13AA19836F6}">
+    <dataValidation type="list" sqref="M572" xr:uid="{1DD5D434-B488-4F8A-9DEE-303627320D56}">
       <formula1>=IF(L572&lt;&gt;"",INDIRECT(VLOOKUP(L572,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N572" xr:uid="{26F0066E-2F97-4561-85B8-B203D8375EBB}">
+    <dataValidation type="list" sqref="N572" xr:uid="{A2F288C0-B003-4828-9E22-5CC997B93B7E}">
       <formula1>=IF(M572&lt;&gt;"",INDIRECT(VLOOKUP(M572,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M573" xr:uid="{487D100D-CB5C-4168-933C-06CD40336037}">
+    <dataValidation type="list" sqref="M573" xr:uid="{BF625C83-B9B6-4801-ADC6-B9D9FD3B3C57}">
       <formula1>=IF(L573&lt;&gt;"",INDIRECT(VLOOKUP(L573,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N573" xr:uid="{D740AD24-AE1B-4F8B-A101-7C42AD2200A6}">
+    <dataValidation type="list" sqref="N573" xr:uid="{82F475B6-143A-4736-A494-24452B01862A}">
       <formula1>=IF(M573&lt;&gt;"",INDIRECT(VLOOKUP(M573,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M574" xr:uid="{81A0854C-46CA-42C7-84EE-F1A06DC14457}">
+    <dataValidation type="list" sqref="M574" xr:uid="{8D4EA534-E2CF-4DEA-B47E-960CFD1E31F0}">
       <formula1>=IF(L574&lt;&gt;"",INDIRECT(VLOOKUP(L574,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N574" xr:uid="{F0FDF072-4E70-45E4-B564-BAF9115D6994}">
+    <dataValidation type="list" sqref="N574" xr:uid="{DACEA593-7BA3-4F44-A702-DCA0F41680F0}">
       <formula1>=IF(M574&lt;&gt;"",INDIRECT(VLOOKUP(M574,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M575" xr:uid="{D27FB8C1-B892-44D8-8E5F-64A80CBF025E}">
+    <dataValidation type="list" sqref="M575" xr:uid="{B35FBBDF-4CEE-49B0-AEDC-EE9DBE425740}">
       <formula1>=IF(L575&lt;&gt;"",INDIRECT(VLOOKUP(L575,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N575" xr:uid="{BF0C7042-055F-42CD-8788-97B580847CD2}">
+    <dataValidation type="list" sqref="N575" xr:uid="{0C391305-6650-4CE1-A73B-7CA7A03B9D20}">
       <formula1>=IF(M575&lt;&gt;"",INDIRECT(VLOOKUP(M575,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M576" xr:uid="{4CF30AEE-B82C-4AF7-AB0C-F4FCD24E397B}">
+    <dataValidation type="list" sqref="M576" xr:uid="{63C77DBD-2A83-4368-BD4C-935826311C2A}">
       <formula1>=IF(L576&lt;&gt;"",INDIRECT(VLOOKUP(L576,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N576" xr:uid="{2CA03FC1-1853-4A53-8100-43090F0009A6}">
+    <dataValidation type="list" sqref="N576" xr:uid="{8C1B2A5D-C23D-45E1-8C89-DD3821DE6467}">
       <formula1>=IF(M576&lt;&gt;"",INDIRECT(VLOOKUP(M576,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M577" xr:uid="{4924FEB3-9C14-4FA6-A72D-3D5350AA7DFD}">
+    <dataValidation type="list" sqref="M577" xr:uid="{795AAD8D-770B-401F-BDE6-D1B885D6BDAD}">
       <formula1>=IF(L577&lt;&gt;"",INDIRECT(VLOOKUP(L577,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N577" xr:uid="{CAD976B2-A4C9-406B-BCCF-2F702C0205C0}">
+    <dataValidation type="list" sqref="N577" xr:uid="{3E9B0FFC-02DA-4181-92C0-86059662E7BE}">
       <formula1>=IF(M577&lt;&gt;"",INDIRECT(VLOOKUP(M577,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M578" xr:uid="{C9B1C069-DAC5-47E9-96C1-9AB99A558F01}">
+    <dataValidation type="list" sqref="M578" xr:uid="{0F74802D-98A6-47F9-BB73-5B1F4E5CD8B3}">
       <formula1>=IF(L578&lt;&gt;"",INDIRECT(VLOOKUP(L578,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N578" xr:uid="{27EB73B7-97A6-40D1-80CA-342A3DCA54E4}">
+    <dataValidation type="list" sqref="N578" xr:uid="{4A2AF2AC-2173-4698-A12A-396628A3764C}">
       <formula1>=IF(M578&lt;&gt;"",INDIRECT(VLOOKUP(M578,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M579" xr:uid="{FB256581-8E90-4879-B5BF-D33A50E4ADD9}">
+    <dataValidation type="list" sqref="M579" xr:uid="{0ECE55F3-B981-40A2-8D4F-D5F133B2F641}">
       <formula1>=IF(L579&lt;&gt;"",INDIRECT(VLOOKUP(L579,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N579" xr:uid="{707CC1FF-2264-4750-BD4F-24C1BE811A2A}">
+    <dataValidation type="list" sqref="N579" xr:uid="{A6440AEC-4D36-47F2-A145-FCF5FBC79E23}">
       <formula1>=IF(M579&lt;&gt;"",INDIRECT(VLOOKUP(M579,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M580" xr:uid="{7920459B-5BF2-4D1F-8C78-3F06C2B4A113}">
+    <dataValidation type="list" sqref="M580" xr:uid="{970D7580-3477-4B66-8CD1-2B525D30C03E}">
       <formula1>=IF(L580&lt;&gt;"",INDIRECT(VLOOKUP(L580,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N580" xr:uid="{619E22A2-EFCC-4242-8CD1-0FD15D637A52}">
+    <dataValidation type="list" sqref="N580" xr:uid="{7CED5EF7-DF06-4893-A787-6D528CC4ECB3}">
       <formula1>=IF(M580&lt;&gt;"",INDIRECT(VLOOKUP(M580,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M581" xr:uid="{E75B3FA5-C5C3-40F4-8D44-096F9E5020CB}">
+    <dataValidation type="list" sqref="M581" xr:uid="{7F3F089E-D3E1-4206-9734-6A21B7CCD3CE}">
       <formula1>=IF(L581&lt;&gt;"",INDIRECT(VLOOKUP(L581,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N581" xr:uid="{5AE833E9-7FC3-442F-B04E-B6E67045CE5D}">
+    <dataValidation type="list" sqref="N581" xr:uid="{56805516-B52F-4B8C-A3B9-FE4B10C27853}">
       <formula1>=IF(M581&lt;&gt;"",INDIRECT(VLOOKUP(M581,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M582" xr:uid="{3A9D5B38-0A0F-46E5-A415-67CD30EE34D1}">
+    <dataValidation type="list" sqref="M582" xr:uid="{6E85F02D-2816-4685-A08B-E84A320DAA44}">
       <formula1>=IF(L582&lt;&gt;"",INDIRECT(VLOOKUP(L582,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N582" xr:uid="{B458EEEA-8AC9-420E-834D-FF54B0C61DF1}">
+    <dataValidation type="list" sqref="N582" xr:uid="{A5704320-A0F7-4856-9AF4-2FFC605619EA}">
       <formula1>=IF(M582&lt;&gt;"",INDIRECT(VLOOKUP(M582,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M583" xr:uid="{08C1176C-0802-47DA-8EA3-55CEE193B8B0}">
+    <dataValidation type="list" sqref="M583" xr:uid="{D66E0B9A-FDD5-4914-B415-34E5A46F33E9}">
       <formula1>=IF(L583&lt;&gt;"",INDIRECT(VLOOKUP(L583,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N583" xr:uid="{669330A6-12F4-48F0-84A3-2396D47141D0}">
+    <dataValidation type="list" sqref="N583" xr:uid="{25B96ED0-BBC3-4FA5-B063-FFC970F19831}">
       <formula1>=IF(M583&lt;&gt;"",INDIRECT(VLOOKUP(M583,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M584" xr:uid="{20D85F0A-5EBF-4B5C-BC99-0891D52793D2}">
+    <dataValidation type="list" sqref="M584" xr:uid="{9B4E1D2F-E700-44D0-A12E-9B51809F9CDE}">
       <formula1>=IF(L584&lt;&gt;"",INDIRECT(VLOOKUP(L584,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N584" xr:uid="{4B088160-9AD0-4D17-9DE0-20E15C57B5AC}">
+    <dataValidation type="list" sqref="N584" xr:uid="{3BDAB3BF-F0CC-4B7F-9832-98C036528F2B}">
       <formula1>=IF(M584&lt;&gt;"",INDIRECT(VLOOKUP(M584,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M585" xr:uid="{4D37AE03-795B-4D44-A6DA-F0FF7F807D66}">
+    <dataValidation type="list" sqref="M585" xr:uid="{231BCF2E-6CEC-41D9-8F46-8A983E3F9E79}">
       <formula1>=IF(L585&lt;&gt;"",INDIRECT(VLOOKUP(L585,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N585" xr:uid="{AFE1EC7C-6B73-4F51-A964-DFFF02695F9A}">
+    <dataValidation type="list" sqref="N585" xr:uid="{C7A616C0-54E3-4805-9A99-5BA43174E2EE}">
       <formula1>=IF(M585&lt;&gt;"",INDIRECT(VLOOKUP(M585,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M586" xr:uid="{AB67999F-C456-43A9-AE89-246098178090}">
+    <dataValidation type="list" sqref="M586" xr:uid="{FF1E436E-3397-4D6D-B3BB-B59534140ACD}">
       <formula1>=IF(L586&lt;&gt;"",INDIRECT(VLOOKUP(L586,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N586" xr:uid="{5C499B50-8A0D-47C8-A31C-BD54A8F8AC2E}">
+    <dataValidation type="list" sqref="N586" xr:uid="{9BB927DD-E944-45EA-A965-0552A3388AEE}">
       <formula1>=IF(M586&lt;&gt;"",INDIRECT(VLOOKUP(M586,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M587" xr:uid="{2DD9CEEB-292F-405C-B23D-0188434817F4}">
+    <dataValidation type="list" sqref="M587" xr:uid="{8ECB2F28-60D1-43D6-9D12-6CAF74D3DC26}">
       <formula1>=IF(L587&lt;&gt;"",INDIRECT(VLOOKUP(L587,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N587" xr:uid="{FC36E309-549F-480D-A441-50DE84836633}">
+    <dataValidation type="list" sqref="N587" xr:uid="{B326FB29-6484-48B5-8300-42D8B534409E}">
       <formula1>=IF(M587&lt;&gt;"",INDIRECT(VLOOKUP(M587,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M588" xr:uid="{FE5FA298-1482-4A3D-9CBC-381179463C58}">
+    <dataValidation type="list" sqref="M588" xr:uid="{89E2E7E3-DCA1-4A74-9DB7-CB8E3CED8333}">
       <formula1>=IF(L588&lt;&gt;"",INDIRECT(VLOOKUP(L588,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N588" xr:uid="{A2FE9838-5D99-4826-888B-7D17446D76CC}">
+    <dataValidation type="list" sqref="N588" xr:uid="{4A62BD63-D056-44D7-9F64-15C0AEA47CFD}">
       <formula1>=IF(M588&lt;&gt;"",INDIRECT(VLOOKUP(M588,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M589" xr:uid="{1FDCC8D3-D3EB-44BB-8BB2-61AAEA4A01AA}">
+    <dataValidation type="list" sqref="M589" xr:uid="{62F7D232-424D-41E9-9CE5-CA44749055F2}">
       <formula1>=IF(L589&lt;&gt;"",INDIRECT(VLOOKUP(L589,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N589" xr:uid="{899353B1-5204-4E42-8039-94477364FC84}">
+    <dataValidation type="list" sqref="N589" xr:uid="{FBFD5632-1785-4B9B-9500-DF93ED32A05A}">
       <formula1>=IF(M589&lt;&gt;"",INDIRECT(VLOOKUP(M589,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M590" xr:uid="{BAE8F459-1A75-4996-A70F-0465A3547C86}">
+    <dataValidation type="list" sqref="M590" xr:uid="{743F9FFD-67AF-4023-BEC0-C410488F4847}">
       <formula1>=IF(L590&lt;&gt;"",INDIRECT(VLOOKUP(L590,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N590" xr:uid="{AAA03E71-4456-4AB3-A4DC-198FBBD90A42}">
+    <dataValidation type="list" sqref="N590" xr:uid="{EC34E569-32C5-496B-BC03-B86719E0E6C4}">
       <formula1>=IF(M590&lt;&gt;"",INDIRECT(VLOOKUP(M590,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M591" xr:uid="{9E1603E1-F739-471E-84B0-BBCE610CBD0B}">
+    <dataValidation type="list" sqref="M591" xr:uid="{E08D5C34-466E-4728-B6B0-D9BD5C8F3B8C}">
       <formula1>=IF(L591&lt;&gt;"",INDIRECT(VLOOKUP(L591,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N591" xr:uid="{30C54B1B-B61E-4730-93F5-FB9DAEA8C2A3}">
+    <dataValidation type="list" sqref="N591" xr:uid="{91E308B9-962A-45AB-A708-94D160E1D222}">
       <formula1>=IF(M591&lt;&gt;"",INDIRECT(VLOOKUP(M591,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M592" xr:uid="{09759CD9-B47C-404A-B74D-093728F3CF4E}">
+    <dataValidation type="list" sqref="M592" xr:uid="{7009993F-06DE-4786-94DA-1BE9AC52DA30}">
       <formula1>=IF(L592&lt;&gt;"",INDIRECT(VLOOKUP(L592,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N592" xr:uid="{7A6A9F91-C964-49BB-8812-F385D181962A}">
+    <dataValidation type="list" sqref="N592" xr:uid="{DB14A5DB-928F-4884-B936-D2191D66D730}">
       <formula1>=IF(M592&lt;&gt;"",INDIRECT(VLOOKUP(M592,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M593" xr:uid="{978BE52F-1897-40EA-9458-F7C742D13297}">
+    <dataValidation type="list" sqref="M593" xr:uid="{F22404E7-B5B4-4212-AB86-64CA4C0B4C13}">
       <formula1>=IF(L593&lt;&gt;"",INDIRECT(VLOOKUP(L593,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N593" xr:uid="{C8511E29-7252-4232-8234-7ADDD5A5924C}">
+    <dataValidation type="list" sqref="N593" xr:uid="{93E8F5A2-7A66-4052-9A56-95EF17AA8988}">
       <formula1>=IF(M593&lt;&gt;"",INDIRECT(VLOOKUP(M593,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M594" xr:uid="{4EE8D107-948E-47C4-82BE-1CD69F758E8F}">
+    <dataValidation type="list" sqref="M594" xr:uid="{5C97F1CA-8C7D-4C1E-BDA2-7CDED365CAEC}">
       <formula1>=IF(L594&lt;&gt;"",INDIRECT(VLOOKUP(L594,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N594" xr:uid="{5FB5972D-4569-441C-8F96-4A3A20080575}">
+    <dataValidation type="list" sqref="N594" xr:uid="{8162B9E0-C107-495E-BB50-7C825EA584EF}">
       <formula1>=IF(M594&lt;&gt;"",INDIRECT(VLOOKUP(M594,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M595" xr:uid="{2C7D863B-97EA-40A8-8D9B-434EDF132043}">
+    <dataValidation type="list" sqref="M595" xr:uid="{6A4866CE-01EC-475A-8206-0ACC57DF70F0}">
       <formula1>=IF(L595&lt;&gt;"",INDIRECT(VLOOKUP(L595,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N595" xr:uid="{0E7CCC88-3375-4FCF-803D-D1923CC0A50A}">
+    <dataValidation type="list" sqref="N595" xr:uid="{487BBDFE-3E13-400B-80B6-9CC5781257D1}">
       <formula1>=IF(M595&lt;&gt;"",INDIRECT(VLOOKUP(M595,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M596" xr:uid="{757C1FB1-3A1F-4B5F-9F77-8EBF3708F4A7}">
+    <dataValidation type="list" sqref="M596" xr:uid="{F4ACF2B8-4681-4B53-9F46-F3630178CA59}">
       <formula1>=IF(L596&lt;&gt;"",INDIRECT(VLOOKUP(L596,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N596" xr:uid="{D6BA3399-4F32-4D52-98F1-9AEF81D8CAC4}">
+    <dataValidation type="list" sqref="N596" xr:uid="{3F67745F-E407-4D66-8C5A-0A346D431C43}">
       <formula1>=IF(M596&lt;&gt;"",INDIRECT(VLOOKUP(M596,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M597" xr:uid="{53A8DD7D-B27D-4F43-B904-AE785C61F5BC}">
+    <dataValidation type="list" sqref="M597" xr:uid="{B3F0F5C4-3A8D-4C9B-9E4A-4102DEDD1757}">
       <formula1>=IF(L597&lt;&gt;"",INDIRECT(VLOOKUP(L597,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N597" xr:uid="{711BB7A6-99DD-4EDC-B0B4-89FDD0EF2E0D}">
+    <dataValidation type="list" sqref="N597" xr:uid="{399E7485-3BCF-4E9B-9275-093FDFC40FBC}">
       <formula1>=IF(M597&lt;&gt;"",INDIRECT(VLOOKUP(M597,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M598" xr:uid="{E02DE6F2-98C5-4140-9C49-5D9A991AC160}">
+    <dataValidation type="list" sqref="M598" xr:uid="{89F5EC98-0B01-406C-BB62-337F1AC65B66}">
       <formula1>=IF(L598&lt;&gt;"",INDIRECT(VLOOKUP(L598,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N598" xr:uid="{179DF0E0-428D-4E45-A17B-26BA0EC366BE}">
+    <dataValidation type="list" sqref="N598" xr:uid="{37EF267D-3D61-46EE-ADDA-5232CDB4E90D}">
       <formula1>=IF(M598&lt;&gt;"",INDIRECT(VLOOKUP(M598,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M599" xr:uid="{209DB548-5ADE-4A82-AE1D-3C74BF2F8E3F}">
+    <dataValidation type="list" sqref="M599" xr:uid="{0FCF5567-E033-4C2D-B801-16B49C1EDF0B}">
       <formula1>=IF(L599&lt;&gt;"",INDIRECT(VLOOKUP(L599,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N599" xr:uid="{913D43DC-2AA1-40FC-8FC6-E2CDAE11FC43}">
+    <dataValidation type="list" sqref="N599" xr:uid="{4853BF29-557D-415A-AF24-72498AB40B6A}">
       <formula1>=IF(M599&lt;&gt;"",INDIRECT(VLOOKUP(M599,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M600" xr:uid="{EBFC7D1D-ABF5-4212-9BC6-151862BF1784}">
+    <dataValidation type="list" sqref="M600" xr:uid="{E1C8F9F3-A7C1-41AB-97FD-E315C21BD842}">
       <formula1>=IF(L600&lt;&gt;"",INDIRECT(VLOOKUP(L600,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N600" xr:uid="{391D9C64-4D37-498E-97E5-229043CEF737}">
+    <dataValidation type="list" sqref="N600" xr:uid="{3238101C-0394-46F2-882C-C4A1D05E0124}">
       <formula1>=IF(M600&lt;&gt;"",INDIRECT(VLOOKUP(M600,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M601" xr:uid="{6C9B97EE-CBAA-4555-A318-0F32814FF796}">
+    <dataValidation type="list" sqref="M601" xr:uid="{CA42F14E-4116-48B4-8B37-230D9C067163}">
       <formula1>=IF(L601&lt;&gt;"",INDIRECT(VLOOKUP(L601,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N601" xr:uid="{A660D522-39B2-4D93-8B09-E94381160B9D}">
+    <dataValidation type="list" sqref="N601" xr:uid="{D63AE96F-B9A0-4150-A105-6BA3AF18AD62}">
       <formula1>=IF(M601&lt;&gt;"",INDIRECT(VLOOKUP(M601,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M602" xr:uid="{1D3B397C-5289-41CA-8B76-1255EF6D7DD3}">
+    <dataValidation type="list" sqref="M602" xr:uid="{A1CE13F2-DC75-4E39-818F-17B2584F9C99}">
       <formula1>=IF(L602&lt;&gt;"",INDIRECT(VLOOKUP(L602,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N602" xr:uid="{59AD11BC-6C68-4B7C-A402-A1FA0DED871A}">
+    <dataValidation type="list" sqref="N602" xr:uid="{C44FDFC3-042A-4458-A3BC-063C09752C86}">
       <formula1>=IF(M602&lt;&gt;"",INDIRECT(VLOOKUP(M602,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M603" xr:uid="{40A031C3-52F1-4BFB-A7B6-B83DCAF65D7F}">
+    <dataValidation type="list" sqref="M603" xr:uid="{207AE704-E6E8-460E-832A-F6E1EA674736}">
       <formula1>=IF(L603&lt;&gt;"",INDIRECT(VLOOKUP(L603,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N603" xr:uid="{D15037A3-72DE-44A8-8DC1-2196D0F1C3B7}">
+    <dataValidation type="list" sqref="N603" xr:uid="{EAE0F361-1D3D-408F-9765-9ACF443D2B25}">
       <formula1>=IF(M603&lt;&gt;"",INDIRECT(VLOOKUP(M603,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M604" xr:uid="{EA48875D-383E-40D5-BE3F-C888D6720EB6}">
+    <dataValidation type="list" sqref="M604" xr:uid="{B4499EA0-5901-4EAB-AC4D-7564D1D7C42B}">
       <formula1>=IF(L604&lt;&gt;"",INDIRECT(VLOOKUP(L604,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N604" xr:uid="{833CFA0C-4731-4935-97A4-A71FF43D21D4}">
+    <dataValidation type="list" sqref="N604" xr:uid="{22A074D7-C9B7-47BA-A4A5-92DF58345F33}">
       <formula1>=IF(M604&lt;&gt;"",INDIRECT(VLOOKUP(M604,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M605" xr:uid="{00657629-D137-46C4-A2F3-14FD98A95E71}">
+    <dataValidation type="list" sqref="M605" xr:uid="{E773B47F-BF06-4DF0-8EEF-C79C2DABD837}">
       <formula1>=IF(L605&lt;&gt;"",INDIRECT(VLOOKUP(L605,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N605" xr:uid="{371790BC-CB36-49BC-A792-D89C82724C5F}">
+    <dataValidation type="list" sqref="N605" xr:uid="{29D75672-46BB-49EF-B5F5-CD91CF452E86}">
       <formula1>=IF(M605&lt;&gt;"",INDIRECT(VLOOKUP(M605,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M606" xr:uid="{F1AC7A03-0260-4094-B0D8-0A87C9F34FB1}">
+    <dataValidation type="list" sqref="M606" xr:uid="{FCE1EA49-5A41-439F-8862-337A8B1AB927}">
       <formula1>=IF(L606&lt;&gt;"",INDIRECT(VLOOKUP(L606,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N606" xr:uid="{924C215B-7AE9-4456-9D02-966D0DD1E571}">
+    <dataValidation type="list" sqref="N606" xr:uid="{3ACBD3C2-2943-46A9-B96B-87B9B8F276AE}">
       <formula1>=IF(M606&lt;&gt;"",INDIRECT(VLOOKUP(M606,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M607" xr:uid="{ABF33DD1-4928-401F-9BDC-4F3DE213CB25}">
+    <dataValidation type="list" sqref="M607" xr:uid="{538EBEF6-8D75-47D0-A4F8-DB3D1497B8F1}">
       <formula1>=IF(L607&lt;&gt;"",INDIRECT(VLOOKUP(L607,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N607" xr:uid="{D897686D-6617-4F49-8C3F-3BE2DE3AAB5D}">
+    <dataValidation type="list" sqref="N607" xr:uid="{A4D6736A-2310-4001-91F3-42079889E10F}">
       <formula1>=IF(M607&lt;&gt;"",INDIRECT(VLOOKUP(M607,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M608" xr:uid="{18B5DA4E-89C0-478B-9EF7-424CE0E5A90E}">
+    <dataValidation type="list" sqref="M608" xr:uid="{C53A800D-97A2-4698-BC9E-B30AD2EA3F00}">
       <formula1>=IF(L608&lt;&gt;"",INDIRECT(VLOOKUP(L608,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N608" xr:uid="{4000AE1C-E8B8-4EEA-8E07-2C8847FCFC59}">
+    <dataValidation type="list" sqref="N608" xr:uid="{82CE2BFC-2A2F-4A1F-9E6C-2009BC07479C}">
       <formula1>=IF(M608&lt;&gt;"",INDIRECT(VLOOKUP(M608,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M609" xr:uid="{19D12294-6E08-4632-BC9A-22ABCEAE0B09}">
+    <dataValidation type="list" sqref="M609" xr:uid="{539427CD-96CE-491D-8B62-F8E7AAEBEB11}">
       <formula1>=IF(L609&lt;&gt;"",INDIRECT(VLOOKUP(L609,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N609" xr:uid="{CDD50D75-49AB-4900-9BA5-67EE987C3EA0}">
+    <dataValidation type="list" sqref="N609" xr:uid="{AE971208-0743-41D7-822E-E4D62F6DAA19}">
       <formula1>=IF(M609&lt;&gt;"",INDIRECT(VLOOKUP(M609,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M610" xr:uid="{04FB6688-C119-40FE-9BBA-88D1B4507F25}">
+    <dataValidation type="list" sqref="M610" xr:uid="{99B267B3-B6F2-4F6A-AAAE-91C1452DE69A}">
       <formula1>=IF(L610&lt;&gt;"",INDIRECT(VLOOKUP(L610,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N610" xr:uid="{C48A97D8-B442-46C7-A24A-F1018757C411}">
+    <dataValidation type="list" sqref="N610" xr:uid="{89FEE778-9314-4CA0-89DD-C83B981B1D83}">
       <formula1>=IF(M610&lt;&gt;"",INDIRECT(VLOOKUP(M610,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M611" xr:uid="{53C00F7B-E9C6-49D5-9AF1-2CC7986D9CA0}">
+    <dataValidation type="list" sqref="M611" xr:uid="{D77BD2F8-4CD0-4ED1-8D1B-DCC7578C94A2}">
       <formula1>=IF(L611&lt;&gt;"",INDIRECT(VLOOKUP(L611,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N611" xr:uid="{50262BFA-9EF4-4F1F-8A2C-AA7D188E431C}">
+    <dataValidation type="list" sqref="N611" xr:uid="{B88BC370-AF52-4D8F-A7A6-35D08E6AA8A8}">
       <formula1>=IF(M611&lt;&gt;"",INDIRECT(VLOOKUP(M611,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M612" xr:uid="{B679996F-3514-4051-9F99-96934FF9DDAE}">
+    <dataValidation type="list" sqref="M612" xr:uid="{353187A5-45B0-480C-945C-9A197217E12E}">
       <formula1>=IF(L612&lt;&gt;"",INDIRECT(VLOOKUP(L612,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N612" xr:uid="{9BDEE6B0-BDF4-4EEA-BF0E-BF13D60EE1C8}">
+    <dataValidation type="list" sqref="N612" xr:uid="{0224ADD2-4A8A-4CF0-879C-987D39F999AF}">
       <formula1>=IF(M612&lt;&gt;"",INDIRECT(VLOOKUP(M612,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M613" xr:uid="{50C08A51-A80B-4D90-B484-4DB90F4FC2F7}">
+    <dataValidation type="list" sqref="M613" xr:uid="{E8BDFAC2-3803-489A-9386-18F599B81FEE}">
       <formula1>=IF(L613&lt;&gt;"",INDIRECT(VLOOKUP(L613,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N613" xr:uid="{2E36573F-68B9-4480-A1DD-96AE93649B94}">
+    <dataValidation type="list" sqref="N613" xr:uid="{AB413D95-2ECB-49F0-B9FF-51C2204E852A}">
       <formula1>=IF(M613&lt;&gt;"",INDIRECT(VLOOKUP(M613,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M614" xr:uid="{0BAE98D0-7030-4F62-A77F-0408B739DB20}">
+    <dataValidation type="list" sqref="M614" xr:uid="{618C3E58-738F-4F74-8C16-583312A3AD73}">
       <formula1>=IF(L614&lt;&gt;"",INDIRECT(VLOOKUP(L614,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N614" xr:uid="{7D17D9E1-737A-4309-B754-20C353E45DD0}">
+    <dataValidation type="list" sqref="N614" xr:uid="{C1583E56-A44D-4756-813F-5DA6ABF6DA1E}">
       <formula1>=IF(M614&lt;&gt;"",INDIRECT(VLOOKUP(M614,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M615" xr:uid="{64EC749C-BF6D-4843-BE60-90DC3FDEBD0D}">
+    <dataValidation type="list" sqref="M615" xr:uid="{993E8D28-0407-4776-98FB-60F214701D2D}">
       <formula1>=IF(L615&lt;&gt;"",INDIRECT(VLOOKUP(L615,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N615" xr:uid="{AB2C23E0-591B-4122-8A95-6C84C10CF125}">
+    <dataValidation type="list" sqref="N615" xr:uid="{BF7658FF-19A2-43B3-AF4A-10933777A5C9}">
       <formula1>=IF(M615&lt;&gt;"",INDIRECT(VLOOKUP(M615,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M616" xr:uid="{8E695563-F0B9-4A13-A7BF-4622C2D272E4}">
+    <dataValidation type="list" sqref="M616" xr:uid="{E49ECD4E-DA8B-4EAB-9271-CD48DCD614CC}">
       <formula1>=IF(L616&lt;&gt;"",INDIRECT(VLOOKUP(L616,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N616" xr:uid="{EACDF4BA-0302-4520-81C2-EDFD8DEC6A79}">
+    <dataValidation type="list" sqref="N616" xr:uid="{65CD4674-32E7-4710-84AB-F304F974A1B2}">
       <formula1>=IF(M616&lt;&gt;"",INDIRECT(VLOOKUP(M616,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M617" xr:uid="{4620E1DB-6FF3-4027-8738-68927AC29CD7}">
+    <dataValidation type="list" sqref="M617" xr:uid="{6A9B5F26-4C6A-4620-A3E0-87E5A7913383}">
       <formula1>=IF(L617&lt;&gt;"",INDIRECT(VLOOKUP(L617,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N617" xr:uid="{6F0497D7-1677-426D-A539-DA0F25986C33}">
+    <dataValidation type="list" sqref="N617" xr:uid="{0C8EAC92-DC06-420F-8BE9-2752CF59DC70}">
       <formula1>=IF(M617&lt;&gt;"",INDIRECT(VLOOKUP(M617,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M618" xr:uid="{201BCE5D-DCFD-424F-A28A-8C648211C6C5}">
+    <dataValidation type="list" sqref="M618" xr:uid="{15FAB0FE-0B99-4B67-A939-033015E3DD1C}">
       <formula1>=IF(L618&lt;&gt;"",INDIRECT(VLOOKUP(L618,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N618" xr:uid="{6FC665CC-4611-4A3D-9E4E-1220EFD411A5}">
+    <dataValidation type="list" sqref="N618" xr:uid="{E5A35B69-1637-4382-B832-B5AD820D50E7}">
       <formula1>=IF(M618&lt;&gt;"",INDIRECT(VLOOKUP(M618,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M619" xr:uid="{DEBD3871-CFF0-48AB-A940-945B22B0C821}">
+    <dataValidation type="list" sqref="M619" xr:uid="{66D83568-1059-41CA-8BF9-36A5A4EDE425}">
       <formula1>=IF(L619&lt;&gt;"",INDIRECT(VLOOKUP(L619,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N619" xr:uid="{8A4E3AC0-6D99-4604-937A-52C05D8B3FEB}">
+    <dataValidation type="list" sqref="N619" xr:uid="{B772883C-4A7B-4458-A959-50AA46A41A2D}">
       <formula1>=IF(M619&lt;&gt;"",INDIRECT(VLOOKUP(M619,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M620" xr:uid="{46550F84-6051-4A4D-B16E-49B67CE67CFE}">
+    <dataValidation type="list" sqref="M620" xr:uid="{89FE28D8-A805-4952-A958-E6789386C418}">
       <formula1>=IF(L620&lt;&gt;"",INDIRECT(VLOOKUP(L620,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N620" xr:uid="{3C9B2F65-B099-45C0-A5F1-6309648F519A}">
+    <dataValidation type="list" sqref="N620" xr:uid="{EDFEA116-F005-4EE8-9914-856975D917ED}">
       <formula1>=IF(M620&lt;&gt;"",INDIRECT(VLOOKUP(M620,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M621" xr:uid="{FF33DAC1-5E5D-408E-B87E-07A703EE9503}">
+    <dataValidation type="list" sqref="M621" xr:uid="{E279E887-8A58-47FE-97FD-97439CA1EA09}">
       <formula1>=IF(L621&lt;&gt;"",INDIRECT(VLOOKUP(L621,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N621" xr:uid="{FC8983F9-808B-45BF-9BEE-7E1EA4347A51}">
+    <dataValidation type="list" sqref="N621" xr:uid="{A6852F2E-E246-4464-A0F8-9EE6A4FAB29A}">
       <formula1>=IF(M621&lt;&gt;"",INDIRECT(VLOOKUP(M621,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M622" xr:uid="{3972C628-D21E-4F4D-BBF4-DA807F785A42}">
+    <dataValidation type="list" sqref="M622" xr:uid="{14447FC0-8783-414C-8DF8-ACEF901A258D}">
       <formula1>=IF(L622&lt;&gt;"",INDIRECT(VLOOKUP(L622,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N622" xr:uid="{5B50D82F-5DAA-4604-914D-1910344A34ED}">
+    <dataValidation type="list" sqref="N622" xr:uid="{4EBF194C-D92C-4289-8218-BB1D2DCB3500}">
       <formula1>=IF(M622&lt;&gt;"",INDIRECT(VLOOKUP(M622,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M623" xr:uid="{D0A16404-839C-428E-9175-E5EFD0CAC88A}">
+    <dataValidation type="list" sqref="M623" xr:uid="{2AAB7A10-98F9-49D4-82C7-E1E6994453BB}">
       <formula1>=IF(L623&lt;&gt;"",INDIRECT(VLOOKUP(L623,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N623" xr:uid="{B7178D0D-A6F2-4E98-A83C-78B5D553031C}">
+    <dataValidation type="list" sqref="N623" xr:uid="{0D30AF87-894C-435F-8B22-D97C178C154E}">
       <formula1>=IF(M623&lt;&gt;"",INDIRECT(VLOOKUP(M623,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M624" xr:uid="{74BEDF70-6BAB-4DEE-B2F9-F32AF8F1EAC8}">
+    <dataValidation type="list" sqref="M624" xr:uid="{A2C97C15-5D05-4420-836A-E0CCD77CB269}">
       <formula1>=IF(L624&lt;&gt;"",INDIRECT(VLOOKUP(L624,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N624" xr:uid="{03F94EA1-5A19-4DDE-904D-A255D50EC0D5}">
+    <dataValidation type="list" sqref="N624" xr:uid="{E4EC9BD8-F65C-4D3E-8E2E-D6C86166128D}">
       <formula1>=IF(M624&lt;&gt;"",INDIRECT(VLOOKUP(M624,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M625" xr:uid="{3FA4306B-4DC1-4EFE-85F2-B70B14935A56}">
+    <dataValidation type="list" sqref="M625" xr:uid="{4809EF9C-A6EB-4D21-A71F-2B8402BE3581}">
       <formula1>=IF(L625&lt;&gt;"",INDIRECT(VLOOKUP(L625,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N625" xr:uid="{1599A060-DCCA-40FE-A4EE-8405F309A2A7}">
+    <dataValidation type="list" sqref="N625" xr:uid="{E31520DC-EFAC-4259-AB7C-FB4AE8D398AB}">
       <formula1>=IF(M625&lt;&gt;"",INDIRECT(VLOOKUP(M625,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M626" xr:uid="{4FDF63F9-F8A9-4C94-BF2B-1EB9259B3749}">
+    <dataValidation type="list" sqref="M626" xr:uid="{9ACCE2DF-7E64-4DEC-AE08-359E54EAC05A}">
       <formula1>=IF(L626&lt;&gt;"",INDIRECT(VLOOKUP(L626,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N626" xr:uid="{C7C60472-854C-4870-B4BC-02979C0C9A2F}">
+    <dataValidation type="list" sqref="N626" xr:uid="{0188F297-59AE-4B91-AC49-55F051EB23F8}">
       <formula1>=IF(M626&lt;&gt;"",INDIRECT(VLOOKUP(M626,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M627" xr:uid="{D6839A25-BD52-4065-B1C5-5AAE9631C9EB}">
+    <dataValidation type="list" sqref="M627" xr:uid="{64E6AB96-483F-4EFB-85AE-1E8E6551792D}">
       <formula1>=IF(L627&lt;&gt;"",INDIRECT(VLOOKUP(L627,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N627" xr:uid="{DDF238F8-AB6C-40F1-A59F-D996A89E9C87}">
+    <dataValidation type="list" sqref="N627" xr:uid="{C8158153-D457-4144-9998-2A2C4D7B0E58}">
       <formula1>=IF(M627&lt;&gt;"",INDIRECT(VLOOKUP(M627,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M628" xr:uid="{567CB46C-F2CD-4524-880C-92B58620A113}">
+    <dataValidation type="list" sqref="M628" xr:uid="{A7E2CAC2-D964-4396-A525-497FF115F0B4}">
       <formula1>=IF(L628&lt;&gt;"",INDIRECT(VLOOKUP(L628,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N628" xr:uid="{5B020C3C-93A8-4CF3-903B-19A8CF7F08D7}">
+    <dataValidation type="list" sqref="N628" xr:uid="{29C89D70-EC29-433D-BD22-E47A4C0F50C8}">
       <formula1>=IF(M628&lt;&gt;"",INDIRECT(VLOOKUP(M628,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M629" xr:uid="{6F0A7332-53F7-4DF0-A2EB-CC7F9632F683}">
+    <dataValidation type="list" sqref="M629" xr:uid="{40B50244-75B4-4A0B-A4B9-222184260C9F}">
       <formula1>=IF(L629&lt;&gt;"",INDIRECT(VLOOKUP(L629,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N629" xr:uid="{C131C97A-1021-454F-9245-F09913A5C1DE}">
+    <dataValidation type="list" sqref="N629" xr:uid="{D2485F10-65D9-4CA7-8CE0-9D6EC6CB1330}">
       <formula1>=IF(M629&lt;&gt;"",INDIRECT(VLOOKUP(M629,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M630" xr:uid="{79D52EE8-F1F8-4BB3-846F-E5D353655C2D}">
+    <dataValidation type="list" sqref="M630" xr:uid="{A898CDDF-AFC3-48F8-B60C-2D46E5D79611}">
       <formula1>=IF(L630&lt;&gt;"",INDIRECT(VLOOKUP(L630,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N630" xr:uid="{D30D0B70-6676-4746-A911-AA0B71055EDE}">
+    <dataValidation type="list" sqref="N630" xr:uid="{C57DC6B8-8193-438E-92A6-C126629774B3}">
       <formula1>=IF(M630&lt;&gt;"",INDIRECT(VLOOKUP(M630,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M631" xr:uid="{C970FFDA-3989-4696-8D94-ED2E446E2C96}">
+    <dataValidation type="list" sqref="M631" xr:uid="{2971A483-3CB3-4FA4-ABD2-8FF4486E849F}">
       <formula1>=IF(L631&lt;&gt;"",INDIRECT(VLOOKUP(L631,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N631" xr:uid="{8E73E9A8-5350-4F60-9D06-9BFC58E10470}">
+    <dataValidation type="list" sqref="N631" xr:uid="{440A7949-33D4-4173-8564-43447B592A62}">
       <formula1>=IF(M631&lt;&gt;"",INDIRECT(VLOOKUP(M631,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M632" xr:uid="{FA3715AC-E77A-45F9-BF71-330C1D70D3E0}">
+    <dataValidation type="list" sqref="M632" xr:uid="{A7657E04-C13E-4E7C-89A7-690088F7FD8C}">
       <formula1>=IF(L632&lt;&gt;"",INDIRECT(VLOOKUP(L632,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N632" xr:uid="{99F7E3FF-0948-4AD6-A3C7-0974792FAE05}">
+    <dataValidation type="list" sqref="N632" xr:uid="{649A6BCA-B2AA-4AFE-A732-EB6D187689BD}">
       <formula1>=IF(M632&lt;&gt;"",INDIRECT(VLOOKUP(M632,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M633" xr:uid="{22D11D15-507D-40A9-8090-5DD9C7CFD700}">
+    <dataValidation type="list" sqref="M633" xr:uid="{A6DC0C22-DF2D-4E08-9BFF-F0786C0A2D54}">
       <formula1>=IF(L633&lt;&gt;"",INDIRECT(VLOOKUP(L633,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N633" xr:uid="{E49BFD7E-C161-4C22-B8A8-A9B65842C4BF}">
+    <dataValidation type="list" sqref="N633" xr:uid="{624CDD73-1E39-4E0E-B26E-EEA5A055E6B4}">
       <formula1>=IF(M633&lt;&gt;"",INDIRECT(VLOOKUP(M633,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M634" xr:uid="{DD5BABA0-57F3-434D-B840-DC9FFE96F7AB}">
+    <dataValidation type="list" sqref="M634" xr:uid="{40B041F3-D8C4-42C9-A693-8DB37FF707BF}">
       <formula1>=IF(L634&lt;&gt;"",INDIRECT(VLOOKUP(L634,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N634" xr:uid="{503297BD-B9B7-4C57-9F78-174CBD987322}">
+    <dataValidation type="list" sqref="N634" xr:uid="{51C68DC5-0576-48DF-B7B8-65FE52906A73}">
       <formula1>=IF(M634&lt;&gt;"",INDIRECT(VLOOKUP(M634,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M635" xr:uid="{8959721A-9495-476E-8143-442F2529ED1B}">
+    <dataValidation type="list" sqref="M635" xr:uid="{279AB58A-2766-42E9-82E8-C172F9694DFA}">
       <formula1>=IF(L635&lt;&gt;"",INDIRECT(VLOOKUP(L635,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N635" xr:uid="{5EF6BA37-EC88-441A-8B04-4134A640B078}">
+    <dataValidation type="list" sqref="N635" xr:uid="{3F872765-F249-43E6-9586-7776825DF555}">
       <formula1>=IF(M635&lt;&gt;"",INDIRECT(VLOOKUP(M635,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M636" xr:uid="{57C80DE3-68B1-40AD-BA8E-7A85FF805981}">
+    <dataValidation type="list" sqref="M636" xr:uid="{F6091C23-0CCD-4418-88D7-6F409DCEDAB4}">
       <formula1>=IF(L636&lt;&gt;"",INDIRECT(VLOOKUP(L636,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N636" xr:uid="{4097BB70-01E7-49E7-81AC-4AF846002403}">
+    <dataValidation type="list" sqref="N636" xr:uid="{DC5A6A38-9043-4AD0-B72F-214BC3566B5A}">
       <formula1>=IF(M636&lt;&gt;"",INDIRECT(VLOOKUP(M636,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M637" xr:uid="{4A3A8E8D-55B6-4DEA-9635-5193DF5639B5}">
+    <dataValidation type="list" sqref="M637" xr:uid="{EEF826DA-94D3-4E3A-93E2-7D9E4AA465D2}">
       <formula1>=IF(L637&lt;&gt;"",INDIRECT(VLOOKUP(L637,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N637" xr:uid="{29DC5C87-C4F8-48BB-91E1-1220888F4FEE}">
+    <dataValidation type="list" sqref="N637" xr:uid="{5F7D81A1-E5EA-4215-A87E-66F6E099F037}">
       <formula1>=IF(M637&lt;&gt;"",INDIRECT(VLOOKUP(M637,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M638" xr:uid="{570EB391-CF40-4FA3-BA66-53EFD89FBAFD}">
+    <dataValidation type="list" sqref="M638" xr:uid="{B89B3185-4C6B-4B89-B32E-44923D12C873}">
       <formula1>=IF(L638&lt;&gt;"",INDIRECT(VLOOKUP(L638,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N638" xr:uid="{0C95D954-A724-423C-9901-55A85939E314}">
+    <dataValidation type="list" sqref="N638" xr:uid="{CDA1ED20-9D35-4DFE-A88D-1527F129BD28}">
       <formula1>=IF(M638&lt;&gt;"",INDIRECT(VLOOKUP(M638,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M639" xr:uid="{7D125FEF-A02D-4312-8F6A-BDD3551AF8D1}">
+    <dataValidation type="list" sqref="M639" xr:uid="{05966775-A5F0-4712-919A-5268A7FCB2A6}">
       <formula1>=IF(L639&lt;&gt;"",INDIRECT(VLOOKUP(L639,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N639" xr:uid="{5BEEBE26-ADD8-4665-BDBD-3A7EA75E4E1A}">
+    <dataValidation type="list" sqref="N639" xr:uid="{05BF0818-3559-41F9-B516-7234F2550950}">
       <formula1>=IF(M639&lt;&gt;"",INDIRECT(VLOOKUP(M639,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M640" xr:uid="{C0491C19-C3AE-4DC2-9323-57A810D235DC}">
+    <dataValidation type="list" sqref="M640" xr:uid="{CC4E85E1-C01A-47F0-9FA3-C3406D196433}">
       <formula1>=IF(L640&lt;&gt;"",INDIRECT(VLOOKUP(L640,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N640" xr:uid="{B0498B3D-3EDF-48A5-BC8E-4DD9B57F6C00}">
+    <dataValidation type="list" sqref="N640" xr:uid="{560287C0-D2E9-426B-B7FE-F33A32579434}">
       <formula1>=IF(M640&lt;&gt;"",INDIRECT(VLOOKUP(M640,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M641" xr:uid="{C00D36E6-6C6B-481E-ADE4-D3D9D50401D9}">
+    <dataValidation type="list" sqref="M641" xr:uid="{3DE8E5E8-37A8-48DC-81A6-17C76304C41D}">
       <formula1>=IF(L641&lt;&gt;"",INDIRECT(VLOOKUP(L641,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N641" xr:uid="{2B8311B1-E379-4D5A-8D2F-1931AD8277E2}">
+    <dataValidation type="list" sqref="N641" xr:uid="{3CFCCF7D-B2EA-40D4-A2BC-6D13A943CBE2}">
       <formula1>=IF(M641&lt;&gt;"",INDIRECT(VLOOKUP(M641,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M642" xr:uid="{8F830F4D-CA54-4552-B4B5-353449D7B124}">
+    <dataValidation type="list" sqref="M642" xr:uid="{C573C6B8-9D1F-4DBF-917A-A0AEF680170C}">
       <formula1>=IF(L642&lt;&gt;"",INDIRECT(VLOOKUP(L642,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N642" xr:uid="{A5DA6D4D-AA4E-4504-8CFA-D653AE320BB5}">
+    <dataValidation type="list" sqref="N642" xr:uid="{C79E1FB4-B243-4A4C-BB91-F386535569C5}">
       <formula1>=IF(M642&lt;&gt;"",INDIRECT(VLOOKUP(M642,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M643" xr:uid="{18AC78CF-0F9C-4286-9535-07840E1EB976}">
+    <dataValidation type="list" sqref="M643" xr:uid="{9562CF19-FCEA-49EF-B859-1CA877227E99}">
       <formula1>=IF(L643&lt;&gt;"",INDIRECT(VLOOKUP(L643,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N643" xr:uid="{8250C41C-A1F2-4DC9-86A2-C850A8E5CFD5}">
+    <dataValidation type="list" sqref="N643" xr:uid="{49FEDC9F-F8AF-4ACB-958D-811300FDE239}">
       <formula1>=IF(M643&lt;&gt;"",INDIRECT(VLOOKUP(M643,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M644" xr:uid="{DEC5E9D5-6DFC-48FC-8CFE-83A00B134396}">
+    <dataValidation type="list" sqref="M644" xr:uid="{13B90A58-B244-45D5-8F55-6AF7824BF84D}">
       <formula1>=IF(L644&lt;&gt;"",INDIRECT(VLOOKUP(L644,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N644" xr:uid="{F5DF70B3-3E80-48FC-9070-9516EA788FF5}">
+    <dataValidation type="list" sqref="N644" xr:uid="{40E2E904-3916-4238-BACF-F64A037A0C11}">
       <formula1>=IF(M644&lt;&gt;"",INDIRECT(VLOOKUP(M644,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M645" xr:uid="{A0AE0F29-A7A9-4C75-B2C6-3BC1E96E9BFE}">
+    <dataValidation type="list" sqref="M645" xr:uid="{952F7445-46DC-453F-9E32-3AEA64BC2B55}">
       <formula1>=IF(L645&lt;&gt;"",INDIRECT(VLOOKUP(L645,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N645" xr:uid="{454A549F-904F-4EE7-9D4B-4928D4FB23EB}">
+    <dataValidation type="list" sqref="N645" xr:uid="{25574CDD-7D76-4528-AC3E-C9D1A45FECDC}">
       <formula1>=IF(M645&lt;&gt;"",INDIRECT(VLOOKUP(M645,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M646" xr:uid="{3FEAE040-14D3-4C7B-8E9C-F0CA629E0973}">
+    <dataValidation type="list" sqref="M646" xr:uid="{E171FFEF-D898-4F89-B67A-AB2222EFA439}">
       <formula1>=IF(L646&lt;&gt;"",INDIRECT(VLOOKUP(L646,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N646" xr:uid="{1539EBA1-A0E1-4FDA-A775-D9560D83D8B1}">
+    <dataValidation type="list" sqref="N646" xr:uid="{492068F9-84DF-4D4F-AA17-014EEDB25120}">
       <formula1>=IF(M646&lt;&gt;"",INDIRECT(VLOOKUP(M646,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M647" xr:uid="{D81D7038-659A-4B78-A815-2C3B103C0D7C}">
+    <dataValidation type="list" sqref="M647" xr:uid="{B939F997-3F3B-486D-82BF-0E91218B3145}">
       <formula1>=IF(L647&lt;&gt;"",INDIRECT(VLOOKUP(L647,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N647" xr:uid="{91F69AF1-465C-4C16-A3AF-0C83EB49C08B}">
+    <dataValidation type="list" sqref="N647" xr:uid="{9DC3A5C8-66A1-4BAE-B7FD-FF02E9B60832}">
       <formula1>=IF(M647&lt;&gt;"",INDIRECT(VLOOKUP(M647,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M648" xr:uid="{C9448505-A8CE-4494-9DD8-D2F9A1008346}">
+    <dataValidation type="list" sqref="M648" xr:uid="{E9E96E4E-2EF9-43DB-9B8A-FDC9F1086AF9}">
       <formula1>=IF(L648&lt;&gt;"",INDIRECT(VLOOKUP(L648,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N648" xr:uid="{42EC2B80-D5F6-4B12-BF3B-C2053AF83533}">
+    <dataValidation type="list" sqref="N648" xr:uid="{29E914F3-0A68-4C44-B257-4B1336A928E9}">
       <formula1>=IF(M648&lt;&gt;"",INDIRECT(VLOOKUP(M648,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M649" xr:uid="{94C7100D-B341-4338-993A-403325F2A216}">
+    <dataValidation type="list" sqref="M649" xr:uid="{C4F2FF2B-CA48-4691-9573-D5CF7E24A08B}">
       <formula1>=IF(L649&lt;&gt;"",INDIRECT(VLOOKUP(L649,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N649" xr:uid="{AE5440E4-3622-47E0-91BC-DB784C8C50FE}">
+    <dataValidation type="list" sqref="N649" xr:uid="{66F65790-7C3B-48D7-B853-3C6594C08052}">
       <formula1>=IF(M649&lt;&gt;"",INDIRECT(VLOOKUP(M649,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M650" xr:uid="{F3B7616E-88FD-4BF4-BBC2-D8C2175BA954}">
+    <dataValidation type="list" sqref="M650" xr:uid="{1B89B6BC-1512-4753-97A8-8F2F5F63CB86}">
       <formula1>=IF(L650&lt;&gt;"",INDIRECT(VLOOKUP(L650,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N650" xr:uid="{B3E6FF6F-646A-4C86-805B-16C0EF98F801}">
+    <dataValidation type="list" sqref="N650" xr:uid="{2F7E1917-5140-47C3-AA56-4A42F5D64FD5}">
       <formula1>=IF(M650&lt;&gt;"",INDIRECT(VLOOKUP(M650,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M651" xr:uid="{773F985F-E888-4212-9A43-E9F5B56327D3}">
+    <dataValidation type="list" sqref="M651" xr:uid="{C3AC2B38-834C-48ED-9035-13C191E5839D}">
       <formula1>=IF(L651&lt;&gt;"",INDIRECT(VLOOKUP(L651,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N651" xr:uid="{874965BE-828A-49E8-B057-45CF83D5557E}">
+    <dataValidation type="list" sqref="N651" xr:uid="{B4019972-CEC9-4241-8EE5-F4FA13DB4D11}">
       <formula1>=IF(M651&lt;&gt;"",INDIRECT(VLOOKUP(M651,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M652" xr:uid="{E7ED369C-337A-4F52-BE9B-5BA347D5C4BF}">
+    <dataValidation type="list" sqref="M652" xr:uid="{4BB7AD04-0DCE-4336-9E15-D78434F06B39}">
       <formula1>=IF(L652&lt;&gt;"",INDIRECT(VLOOKUP(L652,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N652" xr:uid="{36D7C6CC-91CD-4872-BB37-CAF574F21C4D}">
+    <dataValidation type="list" sqref="N652" xr:uid="{024E5DCA-9DF0-45E2-BD4C-13A9A9DDD92F}">
       <formula1>=IF(M652&lt;&gt;"",INDIRECT(VLOOKUP(M652,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M653" xr:uid="{83EAE5D1-EA1F-4291-965D-601691BA594D}">
+    <dataValidation type="list" sqref="M653" xr:uid="{2DF46D44-E051-41C5-8E55-4392F62B8DB8}">
       <formula1>=IF(L653&lt;&gt;"",INDIRECT(VLOOKUP(L653,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N653" xr:uid="{8FEDF216-E579-486D-9ADE-269D761015EE}">
+    <dataValidation type="list" sqref="N653" xr:uid="{55F619F7-8D3E-41C8-B221-CD4306B3CF98}">
       <formula1>=IF(M653&lt;&gt;"",INDIRECT(VLOOKUP(M653,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M654" xr:uid="{0CAF04CC-646B-4BC2-9610-9EC0F3967B28}">
+    <dataValidation type="list" sqref="M654" xr:uid="{C444ACE8-DD8A-4F45-AD0F-67666F176FB7}">
       <formula1>=IF(L654&lt;&gt;"",INDIRECT(VLOOKUP(L654,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N654" xr:uid="{9DCE510F-70B9-4186-9ED7-2FC54E196E68}">
+    <dataValidation type="list" sqref="N654" xr:uid="{AE961645-BF88-4C6B-8EA1-6563B5BD0F52}">
       <formula1>=IF(M654&lt;&gt;"",INDIRECT(VLOOKUP(M654,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M655" xr:uid="{B0A9848E-0BC6-4AB4-A5F8-AE5F7556BD67}">
+    <dataValidation type="list" sqref="M655" xr:uid="{D412436A-1094-4FD1-A7A8-1E0FECF96CB7}">
       <formula1>=IF(L655&lt;&gt;"",INDIRECT(VLOOKUP(L655,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N655" xr:uid="{23C4FA7F-AA30-4518-A352-305C30201D25}">
+    <dataValidation type="list" sqref="N655" xr:uid="{9EC2FFE8-AAF4-4314-A6AA-84A374D6CE24}">
       <formula1>=IF(M655&lt;&gt;"",INDIRECT(VLOOKUP(M655,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M656" xr:uid="{9CEA7DF8-F379-4AFF-AEFA-7A388C0EBF9E}">
+    <dataValidation type="list" sqref="M656" xr:uid="{AD099A69-F916-484D-8E51-923DEBEA1F17}">
       <formula1>=IF(L656&lt;&gt;"",INDIRECT(VLOOKUP(L656,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N656" xr:uid="{BA189FBF-3CC2-41C9-ADD2-F4FFBF3C11C3}">
+    <dataValidation type="list" sqref="N656" xr:uid="{E6BF9633-3304-4459-8D3A-A66B3FC92D7E}">
       <formula1>=IF(M656&lt;&gt;"",INDIRECT(VLOOKUP(M656,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M657" xr:uid="{4BCA5620-2D01-42B4-9CCC-F7833FCB5D5A}">
+    <dataValidation type="list" sqref="M657" xr:uid="{6DA93C7A-F682-4E43-AB5C-66BB4E8703CC}">
       <formula1>=IF(L657&lt;&gt;"",INDIRECT(VLOOKUP(L657,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N657" xr:uid="{DE9B54C4-9C09-497A-9D1C-C6267FF90CFB}">
+    <dataValidation type="list" sqref="N657" xr:uid="{EF801888-B6FB-4952-8586-6336F54F60C4}">
       <formula1>=IF(M657&lt;&gt;"",INDIRECT(VLOOKUP(M657,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M658" xr:uid="{F0EEC9F0-873E-4727-8C79-F9C462C40324}">
+    <dataValidation type="list" sqref="M658" xr:uid="{F539B1FA-9E68-4C02-A184-4CB88F0B71AA}">
       <formula1>=IF(L658&lt;&gt;"",INDIRECT(VLOOKUP(L658,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N658" xr:uid="{FC55770D-B51C-410D-B7F8-CA5EB9FC869B}">
+    <dataValidation type="list" sqref="N658" xr:uid="{7E974802-0A1E-40F2-9416-94F542F638D0}">
       <formula1>=IF(M658&lt;&gt;"",INDIRECT(VLOOKUP(M658,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M659" xr:uid="{D03BA3D6-E223-4194-9745-85A352FBC470}">
+    <dataValidation type="list" sqref="M659" xr:uid="{0D82C521-21E5-4DE0-A98A-3D93576260A3}">
       <formula1>=IF(L659&lt;&gt;"",INDIRECT(VLOOKUP(L659,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N659" xr:uid="{635B393C-3B96-4577-AF60-4BFD940450E6}">
+    <dataValidation type="list" sqref="N659" xr:uid="{02A74232-8C48-4ADC-80FC-C029F5B80193}">
       <formula1>=IF(M659&lt;&gt;"",INDIRECT(VLOOKUP(M659,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M660" xr:uid="{2FF22ED3-198B-4C32-ABD0-262F7FD0710D}">
+    <dataValidation type="list" sqref="M660" xr:uid="{5553D31D-2C6B-4FAE-B2D5-F9C9EFA704AA}">
       <formula1>=IF(L660&lt;&gt;"",INDIRECT(VLOOKUP(L660,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N660" xr:uid="{A3389307-87A5-404D-9CBF-047CC2C94F9A}">
+    <dataValidation type="list" sqref="N660" xr:uid="{A8BDEC54-F9EF-4B12-8F67-32E6BBF3A424}">
       <formula1>=IF(M660&lt;&gt;"",INDIRECT(VLOOKUP(M660,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M661" xr:uid="{DB81CF0C-0D85-49A3-9CF5-14E49F87639E}">
+    <dataValidation type="list" sqref="M661" xr:uid="{861B4BB7-09B1-49E9-A697-521A63DDE7E4}">
       <formula1>=IF(L661&lt;&gt;"",INDIRECT(VLOOKUP(L661,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N661" xr:uid="{B52AC1C6-32EA-4AE7-96EE-F99D60B794E8}">
+    <dataValidation type="list" sqref="N661" xr:uid="{538F052D-1659-4143-9C30-EA7E2E8D5CB0}">
       <formula1>=IF(M661&lt;&gt;"",INDIRECT(VLOOKUP(M661,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M662" xr:uid="{42575F80-D845-4F6A-81CD-7F5B107799F3}">
+    <dataValidation type="list" sqref="M662" xr:uid="{930001FD-E168-442E-921E-19A7BB7D02BC}">
       <formula1>=IF(L662&lt;&gt;"",INDIRECT(VLOOKUP(L662,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N662" xr:uid="{D3541F7F-5FAB-49AB-A3ED-056E12C62D3D}">
+    <dataValidation type="list" sqref="N662" xr:uid="{327A0962-2D1C-45C7-A777-37CF2CAFE66B}">
       <formula1>=IF(M662&lt;&gt;"",INDIRECT(VLOOKUP(M662,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M663" xr:uid="{44D1B406-4945-44E1-990F-073814EF9FFE}">
+    <dataValidation type="list" sqref="M663" xr:uid="{BC97394B-7E1E-4B5B-A1C4-30C0F6348CDB}">
       <formula1>=IF(L663&lt;&gt;"",INDIRECT(VLOOKUP(L663,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N663" xr:uid="{62AEC098-550D-495E-A7F6-5444D006568A}">
+    <dataValidation type="list" sqref="N663" xr:uid="{FC284397-B9A3-47D7-9D83-9EBB909A8A8D}">
       <formula1>=IF(M663&lt;&gt;"",INDIRECT(VLOOKUP(M663,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M664" xr:uid="{324FF9C8-4463-4422-87D9-50D65D88895D}">
+    <dataValidation type="list" sqref="M664" xr:uid="{7419B394-3376-430E-A7E5-CF60C0006C03}">
       <formula1>=IF(L664&lt;&gt;"",INDIRECT(VLOOKUP(L664,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N664" xr:uid="{CC7CB39A-CB1A-4639-8E9F-ED918E2CC774}">
+    <dataValidation type="list" sqref="N664" xr:uid="{14A58E74-AA75-42BF-B192-23AE8B3357EA}">
       <formula1>=IF(M664&lt;&gt;"",INDIRECT(VLOOKUP(M664,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M665" xr:uid="{FB81FEDB-A7BC-4236-A43F-DA8E37D081E9}">
+    <dataValidation type="list" sqref="M665" xr:uid="{F02E07D7-DEE3-4E28-A4D1-368539FDFF11}">
       <formula1>=IF(L665&lt;&gt;"",INDIRECT(VLOOKUP(L665,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N665" xr:uid="{DD0DEDDA-AF5D-4A46-997E-DB8D28518F2A}">
+    <dataValidation type="list" sqref="N665" xr:uid="{DF8DE581-AB8A-4214-8742-DA0B6CF1B854}">
       <formula1>=IF(M665&lt;&gt;"",INDIRECT(VLOOKUP(M665,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M666" xr:uid="{297237CF-3DE1-4F35-B201-18C770388892}">
+    <dataValidation type="list" sqref="M666" xr:uid="{0317A850-D0CC-4AE4-A4A0-FA74FD9D799C}">
       <formula1>=IF(L666&lt;&gt;"",INDIRECT(VLOOKUP(L666,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N666" xr:uid="{8E2A17E3-91FE-4D19-8484-1AE2D96FA457}">
+    <dataValidation type="list" sqref="N666" xr:uid="{A9072A36-3ABE-4789-B846-3EA9B5A067BC}">
       <formula1>=IF(M666&lt;&gt;"",INDIRECT(VLOOKUP(M666,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M667" xr:uid="{B21901DE-85C9-4F3D-9BF3-23501AC440E4}">
+    <dataValidation type="list" sqref="M667" xr:uid="{2CAFFFC4-CEA4-4C49-87D3-B3A0F512E02C}">
       <formula1>=IF(L667&lt;&gt;"",INDIRECT(VLOOKUP(L667,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N667" xr:uid="{C1F56E8B-3E60-467F-996C-EB81FE1E32DB}">
+    <dataValidation type="list" sqref="N667" xr:uid="{2E6DA971-3F1F-4AF4-A928-0D1B2948303D}">
       <formula1>=IF(M667&lt;&gt;"",INDIRECT(VLOOKUP(M667,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M668" xr:uid="{F1FE771A-32E2-429C-8AD0-D6642005C9FD}">
+    <dataValidation type="list" sqref="M668" xr:uid="{78EED2D7-595C-45BA-A747-3CDCD5551E62}">
       <formula1>=IF(L668&lt;&gt;"",INDIRECT(VLOOKUP(L668,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N668" xr:uid="{73434753-C0AD-49FE-AEAA-00C2CA5851DB}">
+    <dataValidation type="list" sqref="N668" xr:uid="{4B060AE5-4C67-4E65-A73B-D15C258AA86E}">
       <formula1>=IF(M668&lt;&gt;"",INDIRECT(VLOOKUP(M668,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M669" xr:uid="{DB6594D5-D9FF-455E-8AC8-189FE5C9E6E8}">
+    <dataValidation type="list" sqref="M669" xr:uid="{6E69BEB2-925E-4FD2-B311-44D3D4554C65}">
       <formula1>=IF(L669&lt;&gt;"",INDIRECT(VLOOKUP(L669,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N669" xr:uid="{7CC0EBAC-A9A4-45F7-8357-395C56BCC84A}">
+    <dataValidation type="list" sqref="N669" xr:uid="{D3B7B368-2851-4AB8-97F1-2381B03F7012}">
       <formula1>=IF(M669&lt;&gt;"",INDIRECT(VLOOKUP(M669,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M670" xr:uid="{82A53DBF-2AB7-40F4-BA86-004D5013042F}">
+    <dataValidation type="list" sqref="M670" xr:uid="{30D65038-7B54-4E20-8E85-7D1A24636D58}">
       <formula1>=IF(L670&lt;&gt;"",INDIRECT(VLOOKUP(L670,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N670" xr:uid="{8CB52EBC-248D-4DDD-800C-7F944239EC75}">
+    <dataValidation type="list" sqref="N670" xr:uid="{49234D6E-915E-4BBA-8783-7D323DDBD348}">
       <formula1>=IF(M670&lt;&gt;"",INDIRECT(VLOOKUP(M670,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M671" xr:uid="{D0BC4E71-8B72-4AE4-B805-BF384341ED61}">
+    <dataValidation type="list" sqref="M671" xr:uid="{39B80017-EA9F-403B-A481-1B05EAD119AB}">
       <formula1>=IF(L671&lt;&gt;"",INDIRECT(VLOOKUP(L671,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N671" xr:uid="{BDE17FFB-E98D-42C8-B9B2-7DE1507E9FEF}">
+    <dataValidation type="list" sqref="N671" xr:uid="{8D00B047-55B3-4B70-9438-09B874585754}">
       <formula1>=IF(M671&lt;&gt;"",INDIRECT(VLOOKUP(M671,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M672" xr:uid="{32B7D714-3A58-4EC3-A2C3-7BCFEAF14836}">
+    <dataValidation type="list" sqref="M672" xr:uid="{C9347244-ABED-4F47-BA19-6FA35B0ADE87}">
       <formula1>=IF(L672&lt;&gt;"",INDIRECT(VLOOKUP(L672,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N672" xr:uid="{3909CCA3-C133-4A05-9EF0-5E1CB8CFEFC5}">
+    <dataValidation type="list" sqref="N672" xr:uid="{81078336-0D74-410F-9393-A738C5E5B4CC}">
       <formula1>=IF(M672&lt;&gt;"",INDIRECT(VLOOKUP(M672,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M673" xr:uid="{0519F2C8-127C-40F2-BEC6-FB3032CB1E26}">
+    <dataValidation type="list" sqref="M673" xr:uid="{D75E544A-22FF-4A7D-820E-196AAF9FEA91}">
       <formula1>=IF(L673&lt;&gt;"",INDIRECT(VLOOKUP(L673,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N673" xr:uid="{6A4DA362-1F24-419F-B717-8F81950C1914}">
+    <dataValidation type="list" sqref="N673" xr:uid="{75DA9520-0F6F-436C-AAA8-5FC951F2D644}">
       <formula1>=IF(M673&lt;&gt;"",INDIRECT(VLOOKUP(M673,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M674" xr:uid="{E45186CE-B22D-4846-B495-E7F9B7BB864E}">
+    <dataValidation type="list" sqref="M674" xr:uid="{C8911018-AE5A-4DDC-A2E9-BD4B157DFF39}">
       <formula1>=IF(L674&lt;&gt;"",INDIRECT(VLOOKUP(L674,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N674" xr:uid="{FB2B0473-2ECE-41F0-BCB8-BCDB229510B2}">
+    <dataValidation type="list" sqref="N674" xr:uid="{73323827-6E99-4B2F-9B65-20158B910B65}">
       <formula1>=IF(M674&lt;&gt;"",INDIRECT(VLOOKUP(M674,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M675" xr:uid="{76B9F522-5808-406C-85C4-76A087BDECDD}">
+    <dataValidation type="list" sqref="M675" xr:uid="{1C92E1D7-6AEE-4417-A7BC-650FFF982521}">
       <formula1>=IF(L675&lt;&gt;"",INDIRECT(VLOOKUP(L675,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N675" xr:uid="{2D41EABB-768B-4BFF-9D09-C7922338143F}">
+    <dataValidation type="list" sqref="N675" xr:uid="{4933EAC3-D42F-4DA9-B5C5-07152D35FC6C}">
       <formula1>=IF(M675&lt;&gt;"",INDIRECT(VLOOKUP(M675,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M676" xr:uid="{CDE85DDC-B93A-4905-B2AD-B8CF3FB3785E}">
+    <dataValidation type="list" sqref="M676" xr:uid="{4B52F640-0609-4426-BAF1-59D301E7BEE3}">
       <formula1>=IF(L676&lt;&gt;"",INDIRECT(VLOOKUP(L676,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N676" xr:uid="{FA75F357-3F63-4BF1-A399-B1AD72894E92}">
+    <dataValidation type="list" sqref="N676" xr:uid="{BC3C793E-7442-444C-986E-BE84A3F3F986}">
       <formula1>=IF(M676&lt;&gt;"",INDIRECT(VLOOKUP(M676,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M677" xr:uid="{7107FAA7-22FA-464D-AB70-A0D7AD22E10F}">
+    <dataValidation type="list" sqref="M677" xr:uid="{1239F105-28B0-45D5-9C63-87C52E4E7E3E}">
       <formula1>=IF(L677&lt;&gt;"",INDIRECT(VLOOKUP(L677,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N677" xr:uid="{552E2577-6B6B-4223-A4E3-F72DE6AC52D6}">
+    <dataValidation type="list" sqref="N677" xr:uid="{DBC59488-4CA1-452E-9A66-AFD1E9D6A42B}">
       <formula1>=IF(M677&lt;&gt;"",INDIRECT(VLOOKUP(M677,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M678" xr:uid="{13B1FDDF-4918-4825-83B7-121D1BEED13C}">
+    <dataValidation type="list" sqref="M678" xr:uid="{518629FA-D981-424E-BAD7-A4CA93A363D1}">
       <formula1>=IF(L678&lt;&gt;"",INDIRECT(VLOOKUP(L678,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N678" xr:uid="{29010ECA-139B-46B5-A060-1D334C3E98BF}">
+    <dataValidation type="list" sqref="N678" xr:uid="{6AD328AE-1ED7-40BA-B79F-050F423BA5C1}">
       <formula1>=IF(M678&lt;&gt;"",INDIRECT(VLOOKUP(M678,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M679" xr:uid="{338A849C-F898-432A-91CB-44FE34AD76B0}">
+    <dataValidation type="list" sqref="M679" xr:uid="{C62463DD-4484-4169-8E18-A45549954494}">
       <formula1>=IF(L679&lt;&gt;"",INDIRECT(VLOOKUP(L679,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N679" xr:uid="{50C1028C-4D7D-4B3D-8ED3-B7AFC8840636}">
+    <dataValidation type="list" sqref="N679" xr:uid="{04323600-B557-42DE-B001-BCC1134E5C73}">
       <formula1>=IF(M679&lt;&gt;"",INDIRECT(VLOOKUP(M679,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M680" xr:uid="{789722CD-F69A-4330-937C-3572BC652B57}">
+    <dataValidation type="list" sqref="M680" xr:uid="{18F9F308-CE8A-4197-9598-875B12E92BE7}">
       <formula1>=IF(L680&lt;&gt;"",INDIRECT(VLOOKUP(L680,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N680" xr:uid="{ED5455A6-B22D-4902-9370-63DDE5CB4E4E}">
+    <dataValidation type="list" sqref="N680" xr:uid="{6D337D08-B593-44BC-BFD6-633793381940}">
       <formula1>=IF(M680&lt;&gt;"",INDIRECT(VLOOKUP(M680,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M681" xr:uid="{3BF3DFBB-FE54-4708-AED0-553EDDF3BD06}">
+    <dataValidation type="list" sqref="M681" xr:uid="{EA6F4939-864E-44EC-B374-B4FDF2E7F669}">
       <formula1>=IF(L681&lt;&gt;"",INDIRECT(VLOOKUP(L681,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N681" xr:uid="{63579340-EEE5-485B-85CD-B8047BB07A12}">
+    <dataValidation type="list" sqref="N681" xr:uid="{CDDF9C69-1DE7-46B6-8544-F126F32ED3F0}">
       <formula1>=IF(M681&lt;&gt;"",INDIRECT(VLOOKUP(M681,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M682" xr:uid="{40D682E7-2FA2-4230-BB1B-8FDDF792B401}">
+    <dataValidation type="list" sqref="M682" xr:uid="{72B6E5EE-14CC-4297-B10D-706280C1B90C}">
       <formula1>=IF(L682&lt;&gt;"",INDIRECT(VLOOKUP(L682,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N682" xr:uid="{363969C2-93DB-45C4-88EC-EDADA735F17A}">
+    <dataValidation type="list" sqref="N682" xr:uid="{BDDF232E-F94E-402D-96A5-C1EA6F3AAC50}">
       <formula1>=IF(M682&lt;&gt;"",INDIRECT(VLOOKUP(M682,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M683" xr:uid="{EDD072E6-520B-4F16-A4BD-B510BAB67545}">
+    <dataValidation type="list" sqref="M683" xr:uid="{E1866C57-2F74-4616-8A74-779DBB82C56E}">
       <formula1>=IF(L683&lt;&gt;"",INDIRECT(VLOOKUP(L683,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N683" xr:uid="{2E710D35-FE55-4355-B228-5B92B01EBDD3}">
+    <dataValidation type="list" sqref="N683" xr:uid="{46F67AA0-8BF5-4FD6-95EE-B936B7B5E970}">
       <formula1>=IF(M683&lt;&gt;"",INDIRECT(VLOOKUP(M683,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M684" xr:uid="{9082ACD5-ED59-41F4-A477-B22B457F0CF5}">
+    <dataValidation type="list" sqref="M684" xr:uid="{FCF715C9-B164-459D-BDC0-14AC63793F44}">
       <formula1>=IF(L684&lt;&gt;"",INDIRECT(VLOOKUP(L684,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N684" xr:uid="{A678F383-01CB-4058-A534-CC24D92D955B}">
+    <dataValidation type="list" sqref="N684" xr:uid="{2E3201C0-5E1A-45D9-9A0A-B4AF56DF4366}">
       <formula1>=IF(M684&lt;&gt;"",INDIRECT(VLOOKUP(M684,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M685" xr:uid="{4D612263-65F7-4FB1-AA83-D425FB219E81}">
+    <dataValidation type="list" sqref="M685" xr:uid="{7285CC92-0350-42D8-9ACF-6583E9D1438D}">
       <formula1>=IF(L685&lt;&gt;"",INDIRECT(VLOOKUP(L685,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N685" xr:uid="{6F9913DD-08B2-4410-8E44-F1E0DA6EC310}">
+    <dataValidation type="list" sqref="N685" xr:uid="{00304DC1-D23A-47C8-9A33-66B7D1D7B869}">
       <formula1>=IF(M685&lt;&gt;"",INDIRECT(VLOOKUP(M685,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M686" xr:uid="{116B9A7A-D4B2-47A1-AFBF-C396C710E819}">
+    <dataValidation type="list" sqref="M686" xr:uid="{AA0161DF-946B-4CF2-833E-22BA45A4A810}">
       <formula1>=IF(L686&lt;&gt;"",INDIRECT(VLOOKUP(L686,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N686" xr:uid="{FB43807D-B521-4C3A-8E97-E947C156BA83}">
+    <dataValidation type="list" sqref="N686" xr:uid="{9050FF63-204C-4653-8ABC-DDE03EA0EAC9}">
       <formula1>=IF(M686&lt;&gt;"",INDIRECT(VLOOKUP(M686,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M687" xr:uid="{3CD00897-7E91-408B-8D10-5053D64D1F51}">
+    <dataValidation type="list" sqref="M687" xr:uid="{5C070B14-366A-4FBF-B456-4CF80FF1CBDF}">
       <formula1>=IF(L687&lt;&gt;"",INDIRECT(VLOOKUP(L687,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N687" xr:uid="{41230DE3-F80C-4099-A6DA-77770198C7F3}">
+    <dataValidation type="list" sqref="N687" xr:uid="{D2F129E0-738D-46B0-BCE9-FFC28B2B1AEC}">
       <formula1>=IF(M687&lt;&gt;"",INDIRECT(VLOOKUP(M687,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M688" xr:uid="{9BC52EB8-6EAE-48FD-A514-93B8EAD5B363}">
+    <dataValidation type="list" sqref="M688" xr:uid="{3A2F18B6-9D62-49B5-A83E-547BD5CBA561}">
       <formula1>=IF(L688&lt;&gt;"",INDIRECT(VLOOKUP(L688,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N688" xr:uid="{9A549152-012F-47BE-A112-67775AC02BE3}">
+    <dataValidation type="list" sqref="N688" xr:uid="{10DC1112-7305-4AB5-AC75-BF3281A63AE7}">
       <formula1>=IF(M688&lt;&gt;"",INDIRECT(VLOOKUP(M688,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M689" xr:uid="{1B304389-0030-4B64-9D3E-1395B20F0BA6}">
+    <dataValidation type="list" sqref="M689" xr:uid="{C08DB9A1-908C-48F7-8F46-0576DEF75078}">
       <formula1>=IF(L689&lt;&gt;"",INDIRECT(VLOOKUP(L689,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N689" xr:uid="{198C15F4-8E2A-4EBD-A0A5-951AF68A4806}">
+    <dataValidation type="list" sqref="N689" xr:uid="{B612CF96-425B-443C-B392-8B24B671BB05}">
       <formula1>=IF(M689&lt;&gt;"",INDIRECT(VLOOKUP(M689,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M690" xr:uid="{B6A61635-32C8-4C2A-A7CB-078A0C8A9BA5}">
+    <dataValidation type="list" sqref="M690" xr:uid="{69D5A0DD-272A-42C0-8DEF-CCC8CAD2798D}">
       <formula1>=IF(L690&lt;&gt;"",INDIRECT(VLOOKUP(L690,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N690" xr:uid="{82016BC2-1E8C-4E7D-BD4F-7E4A3B5BDF14}">
+    <dataValidation type="list" sqref="N690" xr:uid="{D89C39C3-9C34-4FEC-99FA-6FD6F35DD2C0}">
       <formula1>=IF(M690&lt;&gt;"",INDIRECT(VLOOKUP(M690,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M691" xr:uid="{E5A00235-CE24-4281-A717-A938B100838F}">
+    <dataValidation type="list" sqref="M691" xr:uid="{05E7EDD5-72DB-4783-A9BA-04DA4E70844E}">
       <formula1>=IF(L691&lt;&gt;"",INDIRECT(VLOOKUP(L691,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N691" xr:uid="{FAE996DE-1B62-44A0-8233-F8F36A9C1E0D}">
+    <dataValidation type="list" sqref="N691" xr:uid="{CBFBCFD0-1A30-4042-985A-06AB8057D921}">
       <formula1>=IF(M691&lt;&gt;"",INDIRECT(VLOOKUP(M691,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M692" xr:uid="{F90F8E5F-ACEF-4B07-A8AC-396813EB8203}">
+    <dataValidation type="list" sqref="M692" xr:uid="{551F9964-9347-45BA-AFB9-ADCC3DB64FD5}">
       <formula1>=IF(L692&lt;&gt;"",INDIRECT(VLOOKUP(L692,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N692" xr:uid="{156814C7-0F33-46B1-BA13-B5939CF33CB0}">
+    <dataValidation type="list" sqref="N692" xr:uid="{8D368EB3-754B-4DD5-8958-03ABA6A558F6}">
       <formula1>=IF(M692&lt;&gt;"",INDIRECT(VLOOKUP(M692,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M693" xr:uid="{DD6388C1-87CA-4F5D-8C58-97942AEC3ED8}">
+    <dataValidation type="list" sqref="M693" xr:uid="{9120354A-4BBE-4A3B-B796-BDA4793FECDE}">
       <formula1>=IF(L693&lt;&gt;"",INDIRECT(VLOOKUP(L693,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N693" xr:uid="{9059CF1F-E0BD-4B16-95CA-49F55C1B84F6}">
+    <dataValidation type="list" sqref="N693" xr:uid="{3669BD83-DFD1-4A5C-9D7A-420856446BD0}">
       <formula1>=IF(M693&lt;&gt;"",INDIRECT(VLOOKUP(M693,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M694" xr:uid="{972D366E-8A3F-4E5F-9F0B-ABCB4B82B52D}">
+    <dataValidation type="list" sqref="M694" xr:uid="{BA5FD3C1-38F4-4014-B701-DC6956BC92D2}">
       <formula1>=IF(L694&lt;&gt;"",INDIRECT(VLOOKUP(L694,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N694" xr:uid="{4457E967-ADC8-488C-80CD-5BBF723B24DC}">
+    <dataValidation type="list" sqref="N694" xr:uid="{C7C48E0F-1114-414C-9365-98823A1C4344}">
       <formula1>=IF(M694&lt;&gt;"",INDIRECT(VLOOKUP(M694,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M695" xr:uid="{7B01DF7E-CEB7-4260-9563-71C8E95C2655}">
+    <dataValidation type="list" sqref="M695" xr:uid="{CD26A4D1-DE7D-4B1D-A809-8928BDED694C}">
       <formula1>=IF(L695&lt;&gt;"",INDIRECT(VLOOKUP(L695,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N695" xr:uid="{2F1ED3F1-234F-4AFD-9BB1-EDFAF4F38BC7}">
+    <dataValidation type="list" sqref="N695" xr:uid="{BF9AD187-8232-47A9-8439-BFD12C1138F1}">
       <formula1>=IF(M695&lt;&gt;"",INDIRECT(VLOOKUP(M695,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M696" xr:uid="{3AB23604-6781-491F-A4D9-01694C9137EA}">
+    <dataValidation type="list" sqref="M696" xr:uid="{40BB0B3F-0528-4EAF-863B-B45FC22C28BB}">
       <formula1>=IF(L696&lt;&gt;"",INDIRECT(VLOOKUP(L696,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N696" xr:uid="{E44E4D74-82CA-434C-B40C-61541DB9D2FD}">
+    <dataValidation type="list" sqref="N696" xr:uid="{C810450C-7536-46E7-AF25-41D1B26BF825}">
       <formula1>=IF(M696&lt;&gt;"",INDIRECT(VLOOKUP(M696,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M697" xr:uid="{C30397AA-5CA7-45C4-83B3-7730689ECB51}">
+    <dataValidation type="list" sqref="M697" xr:uid="{84897DB7-CF05-4766-8DF9-F4A5D2D45409}">
       <formula1>=IF(L697&lt;&gt;"",INDIRECT(VLOOKUP(L697,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N697" xr:uid="{8F4CFA99-4256-4B40-B612-418567B51D79}">
+    <dataValidation type="list" sqref="N697" xr:uid="{7159B075-630D-4FB0-A3BA-50F4361EC4E5}">
       <formula1>=IF(M697&lt;&gt;"",INDIRECT(VLOOKUP(M697,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M698" xr:uid="{81A01119-687E-4A28-BCEA-6FC492EBB202}">
+    <dataValidation type="list" sqref="M698" xr:uid="{530579E7-E2DB-4BEA-BDEF-7D5A7074FE19}">
       <formula1>=IF(L698&lt;&gt;"",INDIRECT(VLOOKUP(L698,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N698" xr:uid="{187916C7-7745-41F1-BEC1-2FE19C89F550}">
+    <dataValidation type="list" sqref="N698" xr:uid="{3129419F-6949-4A2C-BACC-34C1FF6A8323}">
       <formula1>=IF(M698&lt;&gt;"",INDIRECT(VLOOKUP(M698,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M699" xr:uid="{C4FFE70D-3847-4E01-BE16-775B9D67878F}">
+    <dataValidation type="list" sqref="M699" xr:uid="{2FEA3695-58DE-44DC-B40F-C0268447B2BB}">
       <formula1>=IF(L699&lt;&gt;"",INDIRECT(VLOOKUP(L699,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N699" xr:uid="{03743123-1F6B-4637-AC42-255988B2D4B1}">
+    <dataValidation type="list" sqref="N699" xr:uid="{31065859-8B24-440C-B2EA-E9069B3D180E}">
       <formula1>=IF(M699&lt;&gt;"",INDIRECT(VLOOKUP(M699,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M700" xr:uid="{282C394A-C45A-4942-ADA0-F8904B137B7E}">
+    <dataValidation type="list" sqref="M700" xr:uid="{B410F4B5-E24D-4E69-86CE-6CFBDF0383DD}">
       <formula1>=IF(L700&lt;&gt;"",INDIRECT(VLOOKUP(L700,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N700" xr:uid="{CBA28E7B-1C96-4388-97F7-03933FBA3AC5}">
+    <dataValidation type="list" sqref="N700" xr:uid="{9B398ACF-3DB6-4319-A6E8-21C7F3CF5868}">
       <formula1>=IF(M700&lt;&gt;"",INDIRECT(VLOOKUP(M700,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M701" xr:uid="{9CF547A9-0131-4C93-81DF-1F729A00C316}">
+    <dataValidation type="list" sqref="M701" xr:uid="{7AE429D8-4113-42A2-ACAF-EBAA9A847643}">
       <formula1>=IF(L701&lt;&gt;"",INDIRECT(VLOOKUP(L701,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N701" xr:uid="{6EF709B3-26F7-4155-AE92-D48D239C9015}">
+    <dataValidation type="list" sqref="N701" xr:uid="{42839356-25C0-4586-983E-AF68E617A733}">
       <formula1>=IF(M701&lt;&gt;"",INDIRECT(VLOOKUP(M701,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M702" xr:uid="{79A9D24D-C4A7-46E5-B605-8EC048D95E1B}">
+    <dataValidation type="list" sqref="M702" xr:uid="{03179F27-CD5C-4F58-AE0B-3C8394F48C96}">
       <formula1>=IF(L702&lt;&gt;"",INDIRECT(VLOOKUP(L702,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N702" xr:uid="{5663475B-B020-40D4-B0A3-5A05B5E8C25A}">
+    <dataValidation type="list" sqref="N702" xr:uid="{CE6314A1-7EDE-4F85-B9B0-A9E67D5A5CF1}">
       <formula1>=IF(M702&lt;&gt;"",INDIRECT(VLOOKUP(M702,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M703" xr:uid="{68CF10F3-664E-4870-BAC8-F474320A4B46}">
+    <dataValidation type="list" sqref="M703" xr:uid="{19D1EAEC-C260-4E3E-8CB5-35AF841D0038}">
       <formula1>=IF(L703&lt;&gt;"",INDIRECT(VLOOKUP(L703,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N703" xr:uid="{30B791A0-1F78-4C32-813F-689F8BA17899}">
+    <dataValidation type="list" sqref="N703" xr:uid="{D08A7C1F-74CD-46BD-9758-BC9E7C655D38}">
       <formula1>=IF(M703&lt;&gt;"",INDIRECT(VLOOKUP(M703,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M704" xr:uid="{710925B7-F001-4166-ABEC-084F82798D41}">
+    <dataValidation type="list" sqref="M704" xr:uid="{E8861C94-03C6-4109-B34A-7C3854C36B21}">
       <formula1>=IF(L704&lt;&gt;"",INDIRECT(VLOOKUP(L704,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N704" xr:uid="{A1ABD129-A5A5-4574-9EC3-A5FF94C54E3B}">
+    <dataValidation type="list" sqref="N704" xr:uid="{ED0EE069-0DD0-4F8B-AD7E-87DE25EF8E88}">
       <formula1>=IF(M704&lt;&gt;"",INDIRECT(VLOOKUP(M704,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M705" xr:uid="{FF2849A9-B116-4A9C-8284-4C8B4A7DE418}">
+    <dataValidation type="list" sqref="M705" xr:uid="{2E42752E-3B28-495D-BAA1-B8EF84E5D832}">
       <formula1>=IF(L705&lt;&gt;"",INDIRECT(VLOOKUP(L705,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N705" xr:uid="{6FDDE2E5-EDE7-4344-B525-529DD717004B}">
+    <dataValidation type="list" sqref="N705" xr:uid="{9ACD28C1-25EB-4330-90F6-67F770FF61C6}">
       <formula1>=IF(M705&lt;&gt;"",INDIRECT(VLOOKUP(M705,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M706" xr:uid="{1897D48C-D61D-474D-8A07-9041D88940AE}">
+    <dataValidation type="list" sqref="M706" xr:uid="{5D7A3A4F-1162-4301-AA47-634FF3478A8B}">
       <formula1>=IF(L706&lt;&gt;"",INDIRECT(VLOOKUP(L706,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N706" xr:uid="{BDA75CFC-5C98-4169-8B94-648F8B3A8762}">
+    <dataValidation type="list" sqref="N706" xr:uid="{AB735AD3-56E8-4AD3-97C7-9D7989B5B760}">
       <formula1>=IF(M706&lt;&gt;"",INDIRECT(VLOOKUP(M706,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M707" xr:uid="{AB1BF6D6-0125-4124-9509-AC2D60F33ED2}">
+    <dataValidation type="list" sqref="M707" xr:uid="{E4EE3129-1959-48D2-AC11-F697BEB932F6}">
       <formula1>=IF(L707&lt;&gt;"",INDIRECT(VLOOKUP(L707,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N707" xr:uid="{444889C5-B4FC-43B0-8C12-495BDB039F84}">
+    <dataValidation type="list" sqref="N707" xr:uid="{26A1BE18-4C38-4148-8F2F-0C81BD8571FE}">
       <formula1>=IF(M707&lt;&gt;"",INDIRECT(VLOOKUP(M707,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M708" xr:uid="{415737F9-DE4F-4A72-8A95-4BA351C8199C}">
+    <dataValidation type="list" sqref="M708" xr:uid="{46C29FB9-65B8-4687-BBC4-7AD8BA0AAACB}">
       <formula1>=IF(L708&lt;&gt;"",INDIRECT(VLOOKUP(L708,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N708" xr:uid="{A4B8C358-8FBC-4090-8AD7-AD92AFE1B636}">
+    <dataValidation type="list" sqref="N708" xr:uid="{80B925F2-7805-4B95-8896-CA0F81C9CA05}">
       <formula1>=IF(M708&lt;&gt;"",INDIRECT(VLOOKUP(M708,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M709" xr:uid="{A9A73992-A547-4627-B626-52088102BBC3}">
+    <dataValidation type="list" sqref="M709" xr:uid="{D00C66F9-1EDD-4D17-800D-BE9466F78616}">
       <formula1>=IF(L709&lt;&gt;"",INDIRECT(VLOOKUP(L709,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N709" xr:uid="{F2944116-E7B9-4606-8CC2-DFD62DBA0E09}">
+    <dataValidation type="list" sqref="N709" xr:uid="{ABB9B6B8-134E-4D8B-835E-F3B1111D9B62}">
       <formula1>=IF(M709&lt;&gt;"",INDIRECT(VLOOKUP(M709,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M710" xr:uid="{890BF19E-F2E4-4EDC-BB1A-A511D863326A}">
+    <dataValidation type="list" sqref="M710" xr:uid="{C4ABDE2A-BC07-4AAC-94EA-BA49DDDCA42D}">
       <formula1>=IF(L710&lt;&gt;"",INDIRECT(VLOOKUP(L710,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N710" xr:uid="{D65574B1-BF84-4A2D-B74E-8715C9B1B4D1}">
+    <dataValidation type="list" sqref="N710" xr:uid="{3F2413E8-4462-4A21-A29F-3454847FF5EA}">
       <formula1>=IF(M710&lt;&gt;"",INDIRECT(VLOOKUP(M710,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M711" xr:uid="{D34BF7A4-AA7A-430A-B291-648CE45D2B30}">
+    <dataValidation type="list" sqref="M711" xr:uid="{2D124447-8BDD-4122-B4CB-303F0C4EFD23}">
       <formula1>=IF(L711&lt;&gt;"",INDIRECT(VLOOKUP(L711,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N711" xr:uid="{A61E976E-B27C-468F-96CC-D24E4E3DB369}">
+    <dataValidation type="list" sqref="N711" xr:uid="{E0B93BF5-C0D5-42FE-AAD0-118EB54F7849}">
       <formula1>=IF(M711&lt;&gt;"",INDIRECT(VLOOKUP(M711,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M712" xr:uid="{2B5AFA95-B063-42EE-BA4C-6E39D04A1008}">
+    <dataValidation type="list" sqref="M712" xr:uid="{C7B940C6-4877-44E2-8401-DF01A8B86F12}">
       <formula1>=IF(L712&lt;&gt;"",INDIRECT(VLOOKUP(L712,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N712" xr:uid="{62FE01A2-5D9B-43FF-8F85-19216CF6D5AA}">
+    <dataValidation type="list" sqref="N712" xr:uid="{4D2F1B02-48F3-4063-85BB-82B183114D54}">
       <formula1>=IF(M712&lt;&gt;"",INDIRECT(VLOOKUP(M712,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M713" xr:uid="{E8CF6AC3-DA7E-4205-B779-2BCFAF1E846E}">
+    <dataValidation type="list" sqref="M713" xr:uid="{EA9A297D-8455-44E1-954E-C4244AF49C4F}">
       <formula1>=IF(L713&lt;&gt;"",INDIRECT(VLOOKUP(L713,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N713" xr:uid="{706B3C60-B4C6-456C-9AA7-64CF89DF7319}">
+    <dataValidation type="list" sqref="N713" xr:uid="{17FB0908-BC28-4436-A7B0-2A4AC5F18FAE}">
       <formula1>=IF(M713&lt;&gt;"",INDIRECT(VLOOKUP(M713,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M714" xr:uid="{28CECF8C-8142-42F5-A54A-8A247EAE4A68}">
+    <dataValidation type="list" sqref="M714" xr:uid="{36218201-3312-4257-A6DA-03B2BF15781C}">
       <formula1>=IF(L714&lt;&gt;"",INDIRECT(VLOOKUP(L714,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N714" xr:uid="{BC7B5D3E-C1B9-4DAA-BE11-E6300A3487C3}">
+    <dataValidation type="list" sqref="N714" xr:uid="{B052D2CD-E7B0-445E-A4A5-F838175679E6}">
       <formula1>=IF(M714&lt;&gt;"",INDIRECT(VLOOKUP(M714,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M715" xr:uid="{2A25F644-5AFC-46A7-9EEC-584EEF11339C}">
+    <dataValidation type="list" sqref="M715" xr:uid="{D4F48AD7-0AC1-4B6A-80C4-2C5612E5A435}">
       <formula1>=IF(L715&lt;&gt;"",INDIRECT(VLOOKUP(L715,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N715" xr:uid="{DDE5A2B1-BFE0-48F6-AF88-D51FF173F56C}">
+    <dataValidation type="list" sqref="N715" xr:uid="{E3A04C86-E2D8-4B07-B3D7-9F69AF9E12AF}">
       <formula1>=IF(M715&lt;&gt;"",INDIRECT(VLOOKUP(M715,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M716" xr:uid="{B2E78046-F2DA-4B6D-AF90-32BFC19345AA}">
+    <dataValidation type="list" sqref="M716" xr:uid="{BC4F860B-2E8C-45E5-9883-C7BBA55FC72E}">
       <formula1>=IF(L716&lt;&gt;"",INDIRECT(VLOOKUP(L716,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N716" xr:uid="{B240D00E-E670-4611-B76D-A2293973026D}">
+    <dataValidation type="list" sqref="N716" xr:uid="{DEA309DF-035A-4158-A9B0-E64E95273675}">
       <formula1>=IF(M716&lt;&gt;"",INDIRECT(VLOOKUP(M716,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M717" xr:uid="{F4244FBD-0783-4C86-93F5-C5E4385EA619}">
+    <dataValidation type="list" sqref="M717" xr:uid="{34B7BD85-17B2-4089-905B-7910E14C9767}">
       <formula1>=IF(L717&lt;&gt;"",INDIRECT(VLOOKUP(L717,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N717" xr:uid="{DD178337-09B4-43C7-AE85-09EA36EAA31B}">
+    <dataValidation type="list" sqref="N717" xr:uid="{120D35B1-3B6B-4580-98BD-58A6923A50AF}">
       <formula1>=IF(M717&lt;&gt;"",INDIRECT(VLOOKUP(M717,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M718" xr:uid="{A5712B32-7966-4E8E-87C2-7B3B01820C4F}">
+    <dataValidation type="list" sqref="M718" xr:uid="{E9F73078-7117-477D-9314-C92807848867}">
       <formula1>=IF(L718&lt;&gt;"",INDIRECT(VLOOKUP(L718,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N718" xr:uid="{D4C970B9-4215-42F1-85EE-8DF7DECF044E}">
+    <dataValidation type="list" sqref="N718" xr:uid="{48517A46-FC34-4616-8089-1A02DC6A983E}">
       <formula1>=IF(M718&lt;&gt;"",INDIRECT(VLOOKUP(M718,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M719" xr:uid="{18E018BC-8C31-493A-86B4-B7B518FEB24F}">
+    <dataValidation type="list" sqref="M719" xr:uid="{B9A7F6A8-D818-4932-B4DE-FCC3009E9D5C}">
       <formula1>=IF(L719&lt;&gt;"",INDIRECT(VLOOKUP(L719,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N719" xr:uid="{AD87E618-E948-43BB-8471-EFFA68969582}">
+    <dataValidation type="list" sqref="N719" xr:uid="{692C9FD4-C3B7-47B4-BA61-5DD83FB51794}">
       <formula1>=IF(M719&lt;&gt;"",INDIRECT(VLOOKUP(M719,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M720" xr:uid="{6E130D8D-DC35-4953-81B0-9EAFE22B17B8}">
+    <dataValidation type="list" sqref="M720" xr:uid="{4B61EAD5-934C-4718-A178-4F3F40CF322C}">
       <formula1>=IF(L720&lt;&gt;"",INDIRECT(VLOOKUP(L720,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N720" xr:uid="{13F4E5D0-3237-4924-B72A-980A05CD34FC}">
+    <dataValidation type="list" sqref="N720" xr:uid="{B4DFECA7-5C90-4FB3-AEEF-AB9E81B60B31}">
       <formula1>=IF(M720&lt;&gt;"",INDIRECT(VLOOKUP(M720,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M721" xr:uid="{BEAE277E-2350-4965-B636-8599B444606E}">
+    <dataValidation type="list" sqref="M721" xr:uid="{E3E952EC-7DE1-4554-ACB7-C43F2744B009}">
       <formula1>=IF(L721&lt;&gt;"",INDIRECT(VLOOKUP(L721,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N721" xr:uid="{FB93DBF0-8913-454D-85FE-0E2C671BB331}">
+    <dataValidation type="list" sqref="N721" xr:uid="{4C340FE2-624D-428F-9584-8393E9FABE6B}">
       <formula1>=IF(M721&lt;&gt;"",INDIRECT(VLOOKUP(M721,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M722" xr:uid="{86119DC7-C9E5-464E-B050-C6643BBB75DC}">
+    <dataValidation type="list" sqref="M722" xr:uid="{65B66AA4-2DE4-4FF0-8440-C470649F473D}">
       <formula1>=IF(L722&lt;&gt;"",INDIRECT(VLOOKUP(L722,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N722" xr:uid="{F2D6F177-F92D-4C64-A3B0-5708A85C6626}">
+    <dataValidation type="list" sqref="N722" xr:uid="{37524A58-188D-4C95-A8C5-8D6A778FDB38}">
       <formula1>=IF(M722&lt;&gt;"",INDIRECT(VLOOKUP(M722,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M723" xr:uid="{67819CA0-AB31-47CA-826B-D3707FA14ED3}">
+    <dataValidation type="list" sqref="M723" xr:uid="{36A50C8E-B334-4F9B-922D-5B395DAB7738}">
       <formula1>=IF(L723&lt;&gt;"",INDIRECT(VLOOKUP(L723,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N723" xr:uid="{999B6844-B4C6-4061-9D4A-2635767CCC8F}">
+    <dataValidation type="list" sqref="N723" xr:uid="{3DA58EE3-4A01-4BD0-B818-263619E4DAC0}">
       <formula1>=IF(M723&lt;&gt;"",INDIRECT(VLOOKUP(M723,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M724" xr:uid="{F8291934-E416-44CA-9161-8BCE750AF3BB}">
+    <dataValidation type="list" sqref="M724" xr:uid="{54AB92E4-B29E-42E6-A2CE-794458099337}">
       <formula1>=IF(L724&lt;&gt;"",INDIRECT(VLOOKUP(L724,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N724" xr:uid="{08A7D048-4EED-48A5-BEDF-A91F068D4427}">
+    <dataValidation type="list" sqref="N724" xr:uid="{E8D078CF-3709-488E-A42C-0C67892AF60B}">
       <formula1>=IF(M724&lt;&gt;"",INDIRECT(VLOOKUP(M724,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M725" xr:uid="{BC7B1233-A98E-4765-9DC9-7BE3CB2A30B0}">
+    <dataValidation type="list" sqref="M725" xr:uid="{C0860FF8-B0BE-42BE-B405-7F0A63E73BEC}">
       <formula1>=IF(L725&lt;&gt;"",INDIRECT(VLOOKUP(L725,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N725" xr:uid="{9E326A03-BC7D-49AE-94A6-6BE12F6A5CAD}">
+    <dataValidation type="list" sqref="N725" xr:uid="{1428B3FC-8C12-42F9-B79C-4F6549AC3D8A}">
       <formula1>=IF(M725&lt;&gt;"",INDIRECT(VLOOKUP(M725,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M726" xr:uid="{BBD2677A-3FA8-4D10-AA69-78013E805499}">
+    <dataValidation type="list" sqref="M726" xr:uid="{02898DB1-D81B-4545-86DF-0CDAC500C6D5}">
       <formula1>=IF(L726&lt;&gt;"",INDIRECT(VLOOKUP(L726,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N726" xr:uid="{C80C6382-CF6A-4136-AB61-8C7BC9B3F69E}">
+    <dataValidation type="list" sqref="N726" xr:uid="{D21D663E-CBF3-46B3-948C-9E7F6616D8E3}">
       <formula1>=IF(M726&lt;&gt;"",INDIRECT(VLOOKUP(M726,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M727" xr:uid="{E99BB22C-EEF0-41AC-B41D-91012CCF1534}">
+    <dataValidation type="list" sqref="M727" xr:uid="{182DD69B-7403-4448-AC07-19D230EA9DBD}">
       <formula1>=IF(L727&lt;&gt;"",INDIRECT(VLOOKUP(L727,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N727" xr:uid="{D4E40278-D4BB-4C21-914A-C4F34D92A6BE}">
+    <dataValidation type="list" sqref="N727" xr:uid="{63DEA756-30A7-4746-BFF1-77E4B4940A49}">
       <formula1>=IF(M727&lt;&gt;"",INDIRECT(VLOOKUP(M727,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M728" xr:uid="{5CDF8421-E62E-47E9-ADF0-750196C694DE}">
+    <dataValidation type="list" sqref="M728" xr:uid="{F6CA77E7-D568-4FBC-816B-10F11A88814E}">
       <formula1>=IF(L728&lt;&gt;"",INDIRECT(VLOOKUP(L728,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N728" xr:uid="{45D31EE9-BA09-48A0-83AD-53E40688A345}">
+    <dataValidation type="list" sqref="N728" xr:uid="{7FBCB53F-EC4A-441E-9224-59433E4BACAA}">
       <formula1>=IF(M728&lt;&gt;"",INDIRECT(VLOOKUP(M728,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M729" xr:uid="{493D347F-0D3D-4C47-909E-7B04E70861A6}">
+    <dataValidation type="list" sqref="M729" xr:uid="{CD6DF988-F662-4F28-87D6-93B5B9049FB7}">
       <formula1>=IF(L729&lt;&gt;"",INDIRECT(VLOOKUP(L729,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N729" xr:uid="{D529C4D3-13B6-4D93-881D-E1D85198B60A}">
+    <dataValidation type="list" sqref="N729" xr:uid="{EC0742CC-5797-4EA7-9B2E-E4BE38ADA840}">
       <formula1>=IF(M729&lt;&gt;"",INDIRECT(VLOOKUP(M729,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M730" xr:uid="{BB287AC9-D5BF-4452-A0DF-11DBC1CD30D8}">
+    <dataValidation type="list" sqref="M730" xr:uid="{AEAB6C21-798A-45E3-82DA-2B8548A4A2A8}">
       <formula1>=IF(L730&lt;&gt;"",INDIRECT(VLOOKUP(L730,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N730" xr:uid="{ECAA8A01-72C0-47DF-968E-4D725BAAA91E}">
+    <dataValidation type="list" sqref="N730" xr:uid="{02ADCCD4-95D8-4CBD-B291-4D07B5933C93}">
       <formula1>=IF(M730&lt;&gt;"",INDIRECT(VLOOKUP(M730,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M731" xr:uid="{179BBA85-4C08-4FED-B012-255BA3C4FE8C}">
+    <dataValidation type="list" sqref="M731" xr:uid="{C124B12A-7E83-4E04-ABC9-9B2AF15F79A4}">
       <formula1>=IF(L731&lt;&gt;"",INDIRECT(VLOOKUP(L731,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N731" xr:uid="{47751213-A192-4FB1-825A-D8A9947CDD41}">
+    <dataValidation type="list" sqref="N731" xr:uid="{506920AC-3836-4455-8A8A-3436D2978B25}">
       <formula1>=IF(M731&lt;&gt;"",INDIRECT(VLOOKUP(M731,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M732" xr:uid="{0E37D8A9-DA6B-444B-8D57-57D680554799}">
+    <dataValidation type="list" sqref="M732" xr:uid="{6970FD58-F108-4E31-902B-41A09120A418}">
       <formula1>=IF(L732&lt;&gt;"",INDIRECT(VLOOKUP(L732,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N732" xr:uid="{22B5EB29-0270-48C6-82FE-F05E41B81964}">
+    <dataValidation type="list" sqref="N732" xr:uid="{6699B5DA-BF81-47E0-BC43-21DBC5683982}">
       <formula1>=IF(M732&lt;&gt;"",INDIRECT(VLOOKUP(M732,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M733" xr:uid="{7F460EA5-AED7-4C73-9A3C-2D88DD74D6B5}">
+    <dataValidation type="list" sqref="M733" xr:uid="{8956386B-9D42-4658-A396-421688BEBBDD}">
       <formula1>=IF(L733&lt;&gt;"",INDIRECT(VLOOKUP(L733,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N733" xr:uid="{3FCE78F6-D61D-4AF3-A787-50356BF543EF}">
+    <dataValidation type="list" sqref="N733" xr:uid="{AEAF681D-6634-4F29-AFB6-F823E3C14319}">
       <formula1>=IF(M733&lt;&gt;"",INDIRECT(VLOOKUP(M733,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M734" xr:uid="{1C7D5864-FA46-4286-B3A5-5593DFE4A15D}">
+    <dataValidation type="list" sqref="M734" xr:uid="{24401E89-4901-4160-A447-9805E4180900}">
       <formula1>=IF(L734&lt;&gt;"",INDIRECT(VLOOKUP(L734,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N734" xr:uid="{8CA5BB16-16EE-492A-B343-A703C3C5E543}">
+    <dataValidation type="list" sqref="N734" xr:uid="{DADEC8AC-F01E-4FE6-84E0-26F87376A324}">
       <formula1>=IF(M734&lt;&gt;"",INDIRECT(VLOOKUP(M734,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M735" xr:uid="{BF2339B2-99CB-4AA7-A07A-05BFCD3241BC}">
+    <dataValidation type="list" sqref="M735" xr:uid="{4A86E9B6-A416-4AE1-9CAF-372419D4FAA6}">
       <formula1>=IF(L735&lt;&gt;"",INDIRECT(VLOOKUP(L735,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N735" xr:uid="{EC5466EA-DED4-444E-83F3-3B3F92E29F58}">
+    <dataValidation type="list" sqref="N735" xr:uid="{8EBD4E2C-1154-40B9-9F61-CEF6AD8E8482}">
       <formula1>=IF(M735&lt;&gt;"",INDIRECT(VLOOKUP(M735,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M736" xr:uid="{9F74F3FE-B9E8-4E07-AABC-7E86A76E59CA}">
+    <dataValidation type="list" sqref="M736" xr:uid="{EF28F0ED-5CC4-4A8B-97EA-2CE78B0400D6}">
       <formula1>=IF(L736&lt;&gt;"",INDIRECT(VLOOKUP(L736,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N736" xr:uid="{E3F12F86-A7D2-4740-AFA0-A5B344E90D04}">
+    <dataValidation type="list" sqref="N736" xr:uid="{D4BB460E-4242-4DC8-8FB8-B0B10D6BF704}">
       <formula1>=IF(M736&lt;&gt;"",INDIRECT(VLOOKUP(M736,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M737" xr:uid="{E24F34D7-22A3-463D-B7FD-CA9B3E7EBB85}">
+    <dataValidation type="list" sqref="M737" xr:uid="{78974135-3821-4955-B812-61A4358BA8E4}">
       <formula1>=IF(L737&lt;&gt;"",INDIRECT(VLOOKUP(L737,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N737" xr:uid="{3EFB1800-87E2-430E-A784-10DE34FCB765}">
+    <dataValidation type="list" sqref="N737" xr:uid="{11C7AEF1-063D-4FFF-80D5-AFB13EED086F}">
       <formula1>=IF(M737&lt;&gt;"",INDIRECT(VLOOKUP(M737,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M738" xr:uid="{F841C346-F212-4F80-94D7-D206062B316B}">
+    <dataValidation type="list" sqref="M738" xr:uid="{7DF5C8DE-8567-4141-82B6-2BF93CABF1F5}">
       <formula1>=IF(L738&lt;&gt;"",INDIRECT(VLOOKUP(L738,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N738" xr:uid="{67088AAD-FE19-4D52-A83E-89453CD5CFBD}">
+    <dataValidation type="list" sqref="N738" xr:uid="{0B94214A-0174-43CE-BE89-DE4ED59B7DC2}">
       <formula1>=IF(M738&lt;&gt;"",INDIRECT(VLOOKUP(M738,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M739" xr:uid="{1287CD2F-2EB7-41EA-8784-6F73E04F9E64}">
+    <dataValidation type="list" sqref="M739" xr:uid="{BA213CA6-C7F8-4F63-9B51-DECADABFE51B}">
       <formula1>=IF(L739&lt;&gt;"",INDIRECT(VLOOKUP(L739,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N739" xr:uid="{664270EF-C963-4CAF-88E9-7494EA2C9111}">
+    <dataValidation type="list" sqref="N739" xr:uid="{7C6C1377-EAAA-4E76-988C-D969EF2F913A}">
       <formula1>=IF(M739&lt;&gt;"",INDIRECT(VLOOKUP(M739,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M740" xr:uid="{55F18881-5D88-4911-ADB6-7F027C00B15B}">
+    <dataValidation type="list" sqref="M740" xr:uid="{FA4C47CC-B211-4493-952F-9B6756C6ABB8}">
       <formula1>=IF(L740&lt;&gt;"",INDIRECT(VLOOKUP(L740,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N740" xr:uid="{6122807F-1E21-4E24-A927-2660F8CA5CAD}">
+    <dataValidation type="list" sqref="N740" xr:uid="{ACDB3CC6-025A-4A0F-AA0B-51E4DA2E4021}">
       <formula1>=IF(M740&lt;&gt;"",INDIRECT(VLOOKUP(M740,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M741" xr:uid="{9C5969CF-B3BA-4C63-BDCE-889444FB20E4}">
+    <dataValidation type="list" sqref="M741" xr:uid="{A591C9C5-A3EA-443D-8096-561028FD7A39}">
       <formula1>=IF(L741&lt;&gt;"",INDIRECT(VLOOKUP(L741,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N741" xr:uid="{CBE5C23A-0AA1-4A0D-B5EC-E53C945CC1F9}">
+    <dataValidation type="list" sqref="N741" xr:uid="{429BBCC7-172A-4000-81D2-E151855FB022}">
       <formula1>=IF(M741&lt;&gt;"",INDIRECT(VLOOKUP(M741,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M742" xr:uid="{EE24B2F9-D613-467A-A464-6CB1FA0F855F}">
+    <dataValidation type="list" sqref="M742" xr:uid="{FCDBA2AD-9783-49DA-AFF3-210CD60026EC}">
       <formula1>=IF(L742&lt;&gt;"",INDIRECT(VLOOKUP(L742,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N742" xr:uid="{3D2EB59B-DDA8-4C1C-94BD-65561E3C4FDE}">
+    <dataValidation type="list" sqref="N742" xr:uid="{B835C526-92B4-4226-ADF2-6C11B27A7E51}">
       <formula1>=IF(M742&lt;&gt;"",INDIRECT(VLOOKUP(M742,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M743" xr:uid="{12CB0985-FA61-4999-B2B2-70587BB25730}">
+    <dataValidation type="list" sqref="M743" xr:uid="{9C1F9134-FA01-4443-BD45-6B947A216D50}">
       <formula1>=IF(L743&lt;&gt;"",INDIRECT(VLOOKUP(L743,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N743" xr:uid="{1D7FE307-4AFA-48EE-BB94-B86F1F4107FC}">
+    <dataValidation type="list" sqref="N743" xr:uid="{D65198C8-719E-4518-BC09-3B6531C95043}">
       <formula1>=IF(M743&lt;&gt;"",INDIRECT(VLOOKUP(M743,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M744" xr:uid="{FA2D3932-A437-47CD-A642-6279DA9A4E7C}">
+    <dataValidation type="list" sqref="M744" xr:uid="{80BE6C09-00BC-4A4A-B1D6-932C3976CA2F}">
       <formula1>=IF(L744&lt;&gt;"",INDIRECT(VLOOKUP(L744,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N744" xr:uid="{34BB4AE9-5763-4B2A-997D-EC57E11D414E}">
+    <dataValidation type="list" sqref="N744" xr:uid="{C631519E-1CD5-4E5B-BC86-957EE84C0642}">
       <formula1>=IF(M744&lt;&gt;"",INDIRECT(VLOOKUP(M744,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M745" xr:uid="{73E88BA5-8F3F-4E42-B696-8FE829E31099}">
+    <dataValidation type="list" sqref="M745" xr:uid="{6F6CA637-1016-43E0-BB50-8B7F59432403}">
       <formula1>=IF(L745&lt;&gt;"",INDIRECT(VLOOKUP(L745,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N745" xr:uid="{166AC94C-8C81-4234-8904-B2B4FE163B0E}">
+    <dataValidation type="list" sqref="N745" xr:uid="{21E916C0-01D2-4DB5-823C-9F987424F3F0}">
       <formula1>=IF(M745&lt;&gt;"",INDIRECT(VLOOKUP(M745,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M746" xr:uid="{3799BA03-8AE8-47E0-9B0F-55D94B5CEB41}">
+    <dataValidation type="list" sqref="M746" xr:uid="{BD7B4841-90FC-4DBF-BA87-8028CA97F5BA}">
       <formula1>=IF(L746&lt;&gt;"",INDIRECT(VLOOKUP(L746,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N746" xr:uid="{ED3D799C-83E0-47A7-8E80-5E86E1FF7A23}">
+    <dataValidation type="list" sqref="N746" xr:uid="{FB0E805B-D486-464D-83DC-B518F44B2C78}">
       <formula1>=IF(M746&lt;&gt;"",INDIRECT(VLOOKUP(M746,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M747" xr:uid="{BA9BB675-C4D5-44C6-8A7D-BA560E31331E}">
+    <dataValidation type="list" sqref="M747" xr:uid="{DA4F2587-26C3-4527-AE3A-C89FDB8D74B0}">
       <formula1>=IF(L747&lt;&gt;"",INDIRECT(VLOOKUP(L747,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N747" xr:uid="{DDB1DC5D-F9E8-43F7-910C-BBC9ACFE2FE3}">
+    <dataValidation type="list" sqref="N747" xr:uid="{1F2F46A2-F6E4-4522-95ED-1A1F60023776}">
       <formula1>=IF(M747&lt;&gt;"",INDIRECT(VLOOKUP(M747,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M748" xr:uid="{7560DE82-CB17-462D-A55B-A870527365E2}">
+    <dataValidation type="list" sqref="M748" xr:uid="{12ADD459-CCE1-4361-B1BE-DAFFB4671758}">
       <formula1>=IF(L748&lt;&gt;"",INDIRECT(VLOOKUP(L748,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N748" xr:uid="{B5EB6D51-1A68-4DA1-BAE7-53BDDE86A86F}">
+    <dataValidation type="list" sqref="N748" xr:uid="{425912D4-EBDD-473C-BDA2-E050607FBD47}">
       <formula1>=IF(M748&lt;&gt;"",INDIRECT(VLOOKUP(M748,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M749" xr:uid="{49E002D5-9C87-4CA0-905B-B342A13D8E6C}">
+    <dataValidation type="list" sqref="M749" xr:uid="{12EB90FD-7982-41AF-98E2-A9C450E0EDC3}">
       <formula1>=IF(L749&lt;&gt;"",INDIRECT(VLOOKUP(L749,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N749" xr:uid="{69075E1A-B34A-4E04-9FD0-D598ED75F7DC}">
+    <dataValidation type="list" sqref="N749" xr:uid="{3C551838-D4F2-47FB-89F5-E1B16004B1B0}">
       <formula1>=IF(M749&lt;&gt;"",INDIRECT(VLOOKUP(M749,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M750" xr:uid="{88D468E6-F425-4D3C-AA90-BCD6B6CBB156}">
+    <dataValidation type="list" sqref="M750" xr:uid="{A73FC48D-C2F9-4E82-A7E1-EDCD9B4D0F40}">
       <formula1>=IF(L750&lt;&gt;"",INDIRECT(VLOOKUP(L750,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N750" xr:uid="{84830C2C-3FE6-4C49-84C2-803C602EA8EB}">
+    <dataValidation type="list" sqref="N750" xr:uid="{F2A8160A-5E76-4428-899A-88AE46D4592C}">
       <formula1>=IF(M750&lt;&gt;"",INDIRECT(VLOOKUP(M750,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M751" xr:uid="{0E52382A-31AD-4834-B520-956C2F314766}">
+    <dataValidation type="list" sqref="M751" xr:uid="{B437B64B-1908-4DF1-8161-4FD534DF276D}">
       <formula1>=IF(L751&lt;&gt;"",INDIRECT(VLOOKUP(L751,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N751" xr:uid="{43FBBA98-5084-4772-9779-7F6AE110D49D}">
+    <dataValidation type="list" sqref="N751" xr:uid="{E0447118-4DF3-41B2-8193-ECFD44EB051D}">
       <formula1>=IF(M751&lt;&gt;"",INDIRECT(VLOOKUP(M751,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M752" xr:uid="{82D61295-E7E5-42FD-B51F-3D9A9EB069E6}">
+    <dataValidation type="list" sqref="M752" xr:uid="{F8859F19-B1B3-4344-B32A-2D44969E23BA}">
       <formula1>=IF(L752&lt;&gt;"",INDIRECT(VLOOKUP(L752,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N752" xr:uid="{929F7812-CDAB-43E6-8804-E8AA856AFE91}">
+    <dataValidation type="list" sqref="N752" xr:uid="{22416641-C9F6-4276-8B0D-3F87C055061D}">
       <formula1>=IF(M752&lt;&gt;"",INDIRECT(VLOOKUP(M752,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M753" xr:uid="{73818607-5B04-458E-9EE7-0F313B0026C4}">
+    <dataValidation type="list" sqref="M753" xr:uid="{BEAFECE5-250F-41F1-826E-84339C72880B}">
       <formula1>=IF(L753&lt;&gt;"",INDIRECT(VLOOKUP(L753,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N753" xr:uid="{7C33D15F-745A-46D4-9633-DFEE468D5E2B}">
+    <dataValidation type="list" sqref="N753" xr:uid="{189192E1-03D9-422D-B6A1-BABFE31432A8}">
       <formula1>=IF(M753&lt;&gt;"",INDIRECT(VLOOKUP(M753,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M754" xr:uid="{E8E7356A-A479-4198-BCA6-5C8AC235A692}">
+    <dataValidation type="list" sqref="M754" xr:uid="{A86BB3CC-744D-4EC5-8BD5-03B4E738695A}">
       <formula1>=IF(L754&lt;&gt;"",INDIRECT(VLOOKUP(L754,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N754" xr:uid="{12FBF27E-3038-4BBA-8E7A-B19A04D0AD2B}">
+    <dataValidation type="list" sqref="N754" xr:uid="{4FD26472-4D72-48A0-9F20-C46DCCB19A7A}">
       <formula1>=IF(M754&lt;&gt;"",INDIRECT(VLOOKUP(M754,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M755" xr:uid="{BB9AB679-1134-4B96-8B70-81B3D4CDDE66}">
+    <dataValidation type="list" sqref="M755" xr:uid="{0BEC3C96-0424-4B28-865A-C2644062C8EC}">
       <formula1>=IF(L755&lt;&gt;"",INDIRECT(VLOOKUP(L755,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N755" xr:uid="{FAF7A4B7-6F49-4C63-A39D-9ABD7257C18D}">
+    <dataValidation type="list" sqref="N755" xr:uid="{19112C85-9B37-4F53-8B7D-3A8769D61E9B}">
       <formula1>=IF(M755&lt;&gt;"",INDIRECT(VLOOKUP(M755,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M756" xr:uid="{514EE221-8134-40DB-BF7E-054CC6804361}">
+    <dataValidation type="list" sqref="M756" xr:uid="{7F804D3C-BEFB-4B9E-8F88-34BEF270C972}">
       <formula1>=IF(L756&lt;&gt;"",INDIRECT(VLOOKUP(L756,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N756" xr:uid="{9C3FE927-53A0-41E1-BA74-E8DF9AB8955F}">
+    <dataValidation type="list" sqref="N756" xr:uid="{4ECDC0F8-C1DF-4E60-86BC-480EFE350CB0}">
       <formula1>=IF(M756&lt;&gt;"",INDIRECT(VLOOKUP(M756,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M757" xr:uid="{183E5087-AFFE-4CF5-BA92-7CDD40F43061}">
+    <dataValidation type="list" sqref="M757" xr:uid="{FE50D307-6A5D-4092-928E-6CE1B68660CD}">
       <formula1>=IF(L757&lt;&gt;"",INDIRECT(VLOOKUP(L757,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N757" xr:uid="{BD1F3BD1-D926-4FB5-A82D-9D05B849E8C2}">
+    <dataValidation type="list" sqref="N757" xr:uid="{3F06D779-B478-4574-B3BE-634B6C2B1003}">
       <formula1>=IF(M757&lt;&gt;"",INDIRECT(VLOOKUP(M757,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M758" xr:uid="{366D93D8-8180-433F-A0E5-23D9CB22B2AD}">
+    <dataValidation type="list" sqref="M758" xr:uid="{D09E0992-3E2C-4F5F-9463-7E1C555D9B09}">
       <formula1>=IF(L758&lt;&gt;"",INDIRECT(VLOOKUP(L758,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N758" xr:uid="{BCBEC358-FBBF-46EF-AA02-C4F94147C9EB}">
+    <dataValidation type="list" sqref="N758" xr:uid="{7D7F24C0-4EB8-4417-8D6A-8F9895EFFEEC}">
       <formula1>=IF(M758&lt;&gt;"",INDIRECT(VLOOKUP(M758,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M759" xr:uid="{AB317ED0-0E2A-4BC2-AF07-E9441F4A457E}">
+    <dataValidation type="list" sqref="M759" xr:uid="{4ED4A0D3-C7EA-4A57-97A4-B9DBB7579853}">
       <formula1>=IF(L759&lt;&gt;"",INDIRECT(VLOOKUP(L759,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N759" xr:uid="{65FF8838-BE41-485B-8ABE-9B3380D3F42B}">
+    <dataValidation type="list" sqref="N759" xr:uid="{EED464BF-2A4A-4E7F-AC71-E9CACBBE91E2}">
       <formula1>=IF(M759&lt;&gt;"",INDIRECT(VLOOKUP(M759,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M760" xr:uid="{89EE0C02-9B88-4549-B240-F4D5DC590C9F}">
+    <dataValidation type="list" sqref="M760" xr:uid="{55E37241-978D-46D9-9E8F-CA308479514E}">
       <formula1>=IF(L760&lt;&gt;"",INDIRECT(VLOOKUP(L760,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N760" xr:uid="{A3F87758-5160-4517-800F-DA71E930F956}">
+    <dataValidation type="list" sqref="N760" xr:uid="{54CCD301-F2C9-4501-A02F-F42940C7274A}">
       <formula1>=IF(M760&lt;&gt;"",INDIRECT(VLOOKUP(M760,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M761" xr:uid="{D3B1DC6E-9E65-4B49-82B2-ABFB8298BBB7}">
+    <dataValidation type="list" sqref="M761" xr:uid="{1436329B-70F1-4809-84F8-40BC81805962}">
       <formula1>=IF(L761&lt;&gt;"",INDIRECT(VLOOKUP(L761,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N761" xr:uid="{B0C23335-3A89-4936-BC9E-238DDB06132B}">
+    <dataValidation type="list" sqref="N761" xr:uid="{C5D262A3-D2F5-4CE4-92FA-AD0CC9355DDF}">
       <formula1>=IF(M761&lt;&gt;"",INDIRECT(VLOOKUP(M761,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M762" xr:uid="{084FA401-FD24-4EB6-966F-BFB2F3FE0075}">
+    <dataValidation type="list" sqref="M762" xr:uid="{69C93E89-BD61-4525-82CA-36DCD9B8A8BC}">
       <formula1>=IF(L762&lt;&gt;"",INDIRECT(VLOOKUP(L762,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N762" xr:uid="{DD73C567-38E0-4BAE-B648-0A71A5D30084}">
+    <dataValidation type="list" sqref="N762" xr:uid="{82BC37D5-4109-4313-B398-EDE69C466974}">
       <formula1>=IF(M762&lt;&gt;"",INDIRECT(VLOOKUP(M762,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M763" xr:uid="{431B5084-2795-427B-94EE-A653F2180A30}">
+    <dataValidation type="list" sqref="M763" xr:uid="{704ABC04-BB8A-4200-AAE1-6B4675F72382}">
       <formula1>=IF(L763&lt;&gt;"",INDIRECT(VLOOKUP(L763,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N763" xr:uid="{2E04F929-C3F4-40B5-B573-33C961635AD7}">
+    <dataValidation type="list" sqref="N763" xr:uid="{4C72E698-15F6-4476-80DA-C21F0F516B4D}">
       <formula1>=IF(M763&lt;&gt;"",INDIRECT(VLOOKUP(M763,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M764" xr:uid="{B6A4A68D-49E6-4CE6-B78A-733B662FCB91}">
+    <dataValidation type="list" sqref="M764" xr:uid="{FFA0B6E3-3C34-47C9-8578-D70B1B0F4ED3}">
       <formula1>=IF(L764&lt;&gt;"",INDIRECT(VLOOKUP(L764,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N764" xr:uid="{9B6D01CB-379D-4E31-972D-3F0DABF4C567}">
+    <dataValidation type="list" sqref="N764" xr:uid="{37CC1578-F0C3-44F6-AB38-0EF7FDA77E8B}">
       <formula1>=IF(M764&lt;&gt;"",INDIRECT(VLOOKUP(M764,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M765" xr:uid="{068F4E41-589A-41D0-B7B5-BBE63385F7D8}">
+    <dataValidation type="list" sqref="M765" xr:uid="{D138221A-04EC-4382-B87D-B46EE7ADDC91}">
       <formula1>=IF(L765&lt;&gt;"",INDIRECT(VLOOKUP(L765,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N765" xr:uid="{BEBE67A7-351D-493A-9D60-229995110F6D}">
+    <dataValidation type="list" sqref="N765" xr:uid="{109BD291-8EEC-461D-B552-6A3257884494}">
       <formula1>=IF(M765&lt;&gt;"",INDIRECT(VLOOKUP(M765,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M766" xr:uid="{F69BFC52-04D9-442F-9FDB-324F2D53C896}">
+    <dataValidation type="list" sqref="M766" xr:uid="{B4978670-F8D1-4B76-A971-E02FD77D0F00}">
       <formula1>=IF(L766&lt;&gt;"",INDIRECT(VLOOKUP(L766,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N766" xr:uid="{8AEAE706-FD7C-4B64-B722-BBA9E09C166E}">
+    <dataValidation type="list" sqref="N766" xr:uid="{3F7BC9D3-757B-40AC-96A0-D82EE10E9619}">
       <formula1>=IF(M766&lt;&gt;"",INDIRECT(VLOOKUP(M766,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M767" xr:uid="{3D7AFD76-76CA-4171-9A71-AA3779959723}">
+    <dataValidation type="list" sqref="M767" xr:uid="{66062A1A-0522-4E51-89C3-D2CFBCD091EC}">
       <formula1>=IF(L767&lt;&gt;"",INDIRECT(VLOOKUP(L767,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N767" xr:uid="{80C0DC8F-EA5C-46F2-A779-57BC5ED8FB60}">
+    <dataValidation type="list" sqref="N767" xr:uid="{FDC628B4-4E63-44CE-939F-575E30E307C2}">
       <formula1>=IF(M767&lt;&gt;"",INDIRECT(VLOOKUP(M767,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M768" xr:uid="{E7CD4984-2012-4D20-A8B0-7B58AD7E9212}">
+    <dataValidation type="list" sqref="M768" xr:uid="{DFA78C4C-A7D0-4CFB-B4E4-8759D3DC101E}">
       <formula1>=IF(L768&lt;&gt;"",INDIRECT(VLOOKUP(L768,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N768" xr:uid="{0698CF29-998E-4022-AC91-8A4641463EF2}">
+    <dataValidation type="list" sqref="N768" xr:uid="{3701CE1E-3DF1-4B44-AA01-FB2E65F7336D}">
       <formula1>=IF(M768&lt;&gt;"",INDIRECT(VLOOKUP(M768,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M769" xr:uid="{EEF3BA0A-1A98-491C-B1C3-E38E4E0DC217}">
+    <dataValidation type="list" sqref="M769" xr:uid="{51F04509-3DAB-4FA3-B717-A864AE932016}">
       <formula1>=IF(L769&lt;&gt;"",INDIRECT(VLOOKUP(L769,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N769" xr:uid="{7BB6EE5B-5F86-4C2B-B641-832C8D07DAA0}">
+    <dataValidation type="list" sqref="N769" xr:uid="{6C62D944-6DC2-45E9-B721-45E6D923F974}">
       <formula1>=IF(M769&lt;&gt;"",INDIRECT(VLOOKUP(M769,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M770" xr:uid="{2CA92AB1-39E3-4397-B7B0-1305D9D71B6F}">
+    <dataValidation type="list" sqref="M770" xr:uid="{70FD8032-65EA-434A-BD67-9AB62F32C2F6}">
       <formula1>=IF(L770&lt;&gt;"",INDIRECT(VLOOKUP(L770,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N770" xr:uid="{DDF4F2E4-99A7-4F37-8F27-8F7ACCCB5559}">
+    <dataValidation type="list" sqref="N770" xr:uid="{54B24546-E2F3-45FF-9E56-79024F10417A}">
       <formula1>=IF(M770&lt;&gt;"",INDIRECT(VLOOKUP(M770,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M771" xr:uid="{5BA1D489-8802-4350-A230-CF38040F88BB}">
+    <dataValidation type="list" sqref="M771" xr:uid="{EC19D218-B94C-4F21-8591-EEB099FAE988}">
       <formula1>=IF(L771&lt;&gt;"",INDIRECT(VLOOKUP(L771,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N771" xr:uid="{A6A27AD4-9406-4A90-AB9F-4F65AAD4C0B6}">
+    <dataValidation type="list" sqref="N771" xr:uid="{C71E874B-6C96-4E41-B0ED-E70FD1894067}">
       <formula1>=IF(M771&lt;&gt;"",INDIRECT(VLOOKUP(M771,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M772" xr:uid="{C1D8E1B8-6261-47AD-B472-286A3E59C77D}">
+    <dataValidation type="list" sqref="M772" xr:uid="{B0FAFFB0-C7D8-43D7-B02B-5B5FD86AD93E}">
       <formula1>=IF(L772&lt;&gt;"",INDIRECT(VLOOKUP(L772,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N772" xr:uid="{E16DF21E-D666-4BCE-9D4D-1E59BF5A5017}">
+    <dataValidation type="list" sqref="N772" xr:uid="{EAEDE33A-1F8A-4D13-A847-AC9A891BDAD2}">
       <formula1>=IF(M772&lt;&gt;"",INDIRECT(VLOOKUP(M772,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M773" xr:uid="{9480E085-C3AB-4A16-B320-E0ECA7C72B16}">
+    <dataValidation type="list" sqref="M773" xr:uid="{D7BBD9F5-7FB9-4A58-9734-4367FBA1245F}">
       <formula1>=IF(L773&lt;&gt;"",INDIRECT(VLOOKUP(L773,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N773" xr:uid="{FA8E42CA-2F65-4AA8-947B-12C3140D949F}">
+    <dataValidation type="list" sqref="N773" xr:uid="{D6E22322-3E9A-411C-802E-9296DF7EBF14}">
       <formula1>=IF(M773&lt;&gt;"",INDIRECT(VLOOKUP(M773,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M774" xr:uid="{2E120742-286B-4A43-939A-D4F0D3B8E022}">
+    <dataValidation type="list" sqref="M774" xr:uid="{3A26C15A-55E9-434B-8AC1-2769D9167610}">
       <formula1>=IF(L774&lt;&gt;"",INDIRECT(VLOOKUP(L774,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N774" xr:uid="{53DE1D1F-A30F-43ED-A23F-3401841A138E}">
+    <dataValidation type="list" sqref="N774" xr:uid="{E90CE0DD-2ACC-407E-9A48-E813CF3ED3A8}">
       <formula1>=IF(M774&lt;&gt;"",INDIRECT(VLOOKUP(M774,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M775" xr:uid="{8D731EBF-F77F-4F4D-85A3-3586B1A4DF52}">
+    <dataValidation type="list" sqref="M775" xr:uid="{E337F393-6E22-4B98-9B2D-6805464E66F2}">
       <formula1>=IF(L775&lt;&gt;"",INDIRECT(VLOOKUP(L775,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N775" xr:uid="{EECAED06-CD0A-4871-8669-737D8B459F9D}">
+    <dataValidation type="list" sqref="N775" xr:uid="{5257BB81-DE72-4123-A5A1-8BB9AC6E9668}">
       <formula1>=IF(M775&lt;&gt;"",INDIRECT(VLOOKUP(M775,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M776" xr:uid="{EED00214-41C0-4AE9-A010-E37364531BF0}">
+    <dataValidation type="list" sqref="M776" xr:uid="{3F97C68A-AAC3-49A1-834B-8B4E1177B474}">
       <formula1>=IF(L776&lt;&gt;"",INDIRECT(VLOOKUP(L776,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N776" xr:uid="{8E379C90-073E-4951-BF83-691DA0FA288C}">
+    <dataValidation type="list" sqref="N776" xr:uid="{4519359B-BE7A-486B-9CC0-F3691C2AE9F0}">
       <formula1>=IF(M776&lt;&gt;"",INDIRECT(VLOOKUP(M776,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M777" xr:uid="{20A07850-0714-4184-9DF6-F08436C1EA4B}">
+    <dataValidation type="list" sqref="M777" xr:uid="{BB559C17-25B4-4C93-A038-60F8DDA5D5E0}">
       <formula1>=IF(L777&lt;&gt;"",INDIRECT(VLOOKUP(L777,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N777" xr:uid="{2FD95165-E29B-4874-BB9A-9EA68B900B4B}">
+    <dataValidation type="list" sqref="N777" xr:uid="{C8935AD2-771A-46C6-8D24-A8B72969C970}">
       <formula1>=IF(M777&lt;&gt;"",INDIRECT(VLOOKUP(M777,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M778" xr:uid="{5DF3FFA7-21BA-417C-A7A8-6F3486296547}">
+    <dataValidation type="list" sqref="M778" xr:uid="{3F471C9C-F546-44C5-AC26-483D3C5C1920}">
       <formula1>=IF(L778&lt;&gt;"",INDIRECT(VLOOKUP(L778,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N778" xr:uid="{B0D4A7FC-F4CA-4FEE-AC2C-8722FC8D30D9}">
+    <dataValidation type="list" sqref="N778" xr:uid="{EAC36838-6AEA-4CC1-A32F-A0F41E81DCE9}">
       <formula1>=IF(M778&lt;&gt;"",INDIRECT(VLOOKUP(M778,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M779" xr:uid="{C77EEE0D-3B58-4CD1-9202-B776AA9E5E6A}">
+    <dataValidation type="list" sqref="M779" xr:uid="{DB70B290-D5E4-497E-BA70-DF7172EB6C3A}">
       <formula1>=IF(L779&lt;&gt;"",INDIRECT(VLOOKUP(L779,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N779" xr:uid="{18861054-8D06-4B93-BC67-6F9D06CD83F1}">
+    <dataValidation type="list" sqref="N779" xr:uid="{A313E4C1-A13D-49BB-930B-911491DEDECA}">
       <formula1>=IF(M779&lt;&gt;"",INDIRECT(VLOOKUP(M779,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M780" xr:uid="{B447D624-BEB1-4C2D-AC60-FABA2DBAF6E8}">
+    <dataValidation type="list" sqref="M780" xr:uid="{2047973B-17C7-40EE-B262-849F3792BB14}">
       <formula1>=IF(L780&lt;&gt;"",INDIRECT(VLOOKUP(L780,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N780" xr:uid="{AFC4AA42-1268-4876-972F-97BB03B897BD}">
+    <dataValidation type="list" sqref="N780" xr:uid="{77D643E4-DB7D-4E3C-90C6-99013928E4EF}">
       <formula1>=IF(M780&lt;&gt;"",INDIRECT(VLOOKUP(M780,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M781" xr:uid="{A9899760-7430-4B43-9B8D-601BFA75F124}">
+    <dataValidation type="list" sqref="M781" xr:uid="{45E051BE-46A4-4356-92BF-4993ECD0EE36}">
       <formula1>=IF(L781&lt;&gt;"",INDIRECT(VLOOKUP(L781,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N781" xr:uid="{0DEDD98A-CBF3-4B4F-B620-E03A6447D618}">
+    <dataValidation type="list" sqref="N781" xr:uid="{D1951DB9-4208-400C-B269-E3355AC6C032}">
       <formula1>=IF(M781&lt;&gt;"",INDIRECT(VLOOKUP(M781,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M782" xr:uid="{57413854-64F6-43B6-A180-E25A9FC905C4}">
+    <dataValidation type="list" sqref="M782" xr:uid="{92515E0A-ADC1-4734-9A4B-32F359B4FE18}">
       <formula1>=IF(L782&lt;&gt;"",INDIRECT(VLOOKUP(L782,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N782" xr:uid="{1205B6B9-EF33-4889-BF0F-9E779A920C36}">
+    <dataValidation type="list" sqref="N782" xr:uid="{2FB73A10-C555-419C-B3C7-B0DA7AAE15C9}">
       <formula1>=IF(M782&lt;&gt;"",INDIRECT(VLOOKUP(M782,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M783" xr:uid="{DD6157FA-527A-4172-8F56-112F78901B66}">
+    <dataValidation type="list" sqref="M783" xr:uid="{789CBF41-0DD4-4D93-BBAC-A9044F4A4CED}">
       <formula1>=IF(L783&lt;&gt;"",INDIRECT(VLOOKUP(L783,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N783" xr:uid="{33F80415-DE63-416F-9FA3-566DA7CCDD50}">
+    <dataValidation type="list" sqref="N783" xr:uid="{B24FE1BE-D591-44C1-A3A8-64AAFEBEC6B9}">
       <formula1>=IF(M783&lt;&gt;"",INDIRECT(VLOOKUP(M783,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M784" xr:uid="{3333ABBD-F96D-45D0-9630-BE8AAAA9CD8D}">
+    <dataValidation type="list" sqref="M784" xr:uid="{508D81F3-344C-4701-B17B-7E48713991A1}">
       <formula1>=IF(L784&lt;&gt;"",INDIRECT(VLOOKUP(L784,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N784" xr:uid="{CB86D521-3D0F-4658-BC5E-A2CFF483680F}">
+    <dataValidation type="list" sqref="N784" xr:uid="{AF810F0F-0C33-438E-A461-2BE8A1F35083}">
       <formula1>=IF(M784&lt;&gt;"",INDIRECT(VLOOKUP(M784,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M785" xr:uid="{307B60F7-30B8-4F47-83F3-18FBAC8078F0}">
+    <dataValidation type="list" sqref="M785" xr:uid="{C52B8E74-343C-4C52-9346-AD1D0FEFB01B}">
       <formula1>=IF(L785&lt;&gt;"",INDIRECT(VLOOKUP(L785,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N785" xr:uid="{4A1110B8-2525-43B6-B09C-CFD5324B5294}">
+    <dataValidation type="list" sqref="N785" xr:uid="{5BD11F57-959A-4949-BE6D-9BE380D16820}">
       <formula1>=IF(M785&lt;&gt;"",INDIRECT(VLOOKUP(M785,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M786" xr:uid="{D356450B-188F-461B-BA56-4796F67DCD23}">
+    <dataValidation type="list" sqref="M786" xr:uid="{FC4E4A47-8706-4F06-8B1D-26ABA9877B63}">
       <formula1>=IF(L786&lt;&gt;"",INDIRECT(VLOOKUP(L786,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N786" xr:uid="{06025234-3734-44AE-AD58-009B7249339C}">
+    <dataValidation type="list" sqref="N786" xr:uid="{F248B174-41D3-4976-995C-8047730BC6DC}">
       <formula1>=IF(M786&lt;&gt;"",INDIRECT(VLOOKUP(M786,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M787" xr:uid="{E5BA9CB9-A0C9-4A2A-96B6-B99A009411A7}">
+    <dataValidation type="list" sqref="M787" xr:uid="{B0A0C06D-C7ED-4D48-BEB7-5013CC37D533}">
       <formula1>=IF(L787&lt;&gt;"",INDIRECT(VLOOKUP(L787,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N787" xr:uid="{B3F09E55-D4C8-4185-A3CC-85442B9AB234}">
+    <dataValidation type="list" sqref="N787" xr:uid="{120152FD-98B3-4AB3-9356-417CE76682EC}">
       <formula1>=IF(M787&lt;&gt;"",INDIRECT(VLOOKUP(M787,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M788" xr:uid="{A5A37DD6-78F7-4D69-9E4A-C57C0D2CF11A}">
+    <dataValidation type="list" sqref="M788" xr:uid="{0BC85473-5AFF-40C2-A7AA-8C73F92747C0}">
       <formula1>=IF(L788&lt;&gt;"",INDIRECT(VLOOKUP(L788,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N788" xr:uid="{164F5EF0-FE3F-4151-A329-3A343EC25109}">
+    <dataValidation type="list" sqref="N788" xr:uid="{37BD0844-7BDA-4802-8486-A3BFA4106348}">
       <formula1>=IF(M788&lt;&gt;"",INDIRECT(VLOOKUP(M788,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M789" xr:uid="{F4C7BDB7-23A6-4DE3-AA76-781442B5174E}">
+    <dataValidation type="list" sqref="M789" xr:uid="{8AA68A8C-79BC-4088-97E2-3241DE32078C}">
       <formula1>=IF(L789&lt;&gt;"",INDIRECT(VLOOKUP(L789,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N789" xr:uid="{3325735A-BB74-4F0A-B473-706980E7247A}">
+    <dataValidation type="list" sqref="N789" xr:uid="{7FC84026-15AF-4DA7-B961-525BB6EAE61B}">
       <formula1>=IF(M789&lt;&gt;"",INDIRECT(VLOOKUP(M789,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M790" xr:uid="{9231E8B2-8356-41E4-A608-8AAEB130DC8F}">
+    <dataValidation type="list" sqref="M790" xr:uid="{1F145862-8116-48FF-9CB6-8DB24C3960FC}">
       <formula1>=IF(L790&lt;&gt;"",INDIRECT(VLOOKUP(L790,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N790" xr:uid="{CA2ED2CD-FC71-4FAB-A207-E8CA14FC0317}">
+    <dataValidation type="list" sqref="N790" xr:uid="{DA46F5D3-F9F1-488E-86D3-188460F4C50E}">
       <formula1>=IF(M790&lt;&gt;"",INDIRECT(VLOOKUP(M790,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M791" xr:uid="{DED5DCE6-F70B-4EA9-B936-646AA9A27FBD}">
+    <dataValidation type="list" sqref="M791" xr:uid="{E80CCF9E-F07C-417F-85BB-471B1CCA92A3}">
       <formula1>=IF(L791&lt;&gt;"",INDIRECT(VLOOKUP(L791,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N791" xr:uid="{C2D6B7C3-F72C-4E11-934A-4A817656BC08}">
+    <dataValidation type="list" sqref="N791" xr:uid="{B067BDA9-4CAF-4869-BF47-6A1D5D5FEFFC}">
       <formula1>=IF(M791&lt;&gt;"",INDIRECT(VLOOKUP(M791,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M792" xr:uid="{D70770B9-69E0-4572-8F62-621444ADCF80}">
+    <dataValidation type="list" sqref="M792" xr:uid="{D7BE81BE-4AFF-4A11-97FA-26D2E4E2B82B}">
       <formula1>=IF(L792&lt;&gt;"",INDIRECT(VLOOKUP(L792,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N792" xr:uid="{077CD9CA-017D-4277-8992-8550D55268D5}">
+    <dataValidation type="list" sqref="N792" xr:uid="{ED043F87-A99C-4324-9322-00B115994FEA}">
       <formula1>=IF(M792&lt;&gt;"",INDIRECT(VLOOKUP(M792,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M793" xr:uid="{40CABD4B-FA3E-493E-957B-9B7FD1C7AA0E}">
+    <dataValidation type="list" sqref="M793" xr:uid="{B1EB8B94-D1C7-44EB-84A5-2F86690B1CB7}">
       <formula1>=IF(L793&lt;&gt;"",INDIRECT(VLOOKUP(L793,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N793" xr:uid="{D0A33772-231D-4C9D-8633-56C7A378D9AB}">
+    <dataValidation type="list" sqref="N793" xr:uid="{E44FBD45-70FF-412C-A4B9-66C044334199}">
       <formula1>=IF(M793&lt;&gt;"",INDIRECT(VLOOKUP(M793,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M794" xr:uid="{967759A2-7B86-4651-96B4-E360B3E73922}">
+    <dataValidation type="list" sqref="M794" xr:uid="{D402AA6F-8C02-4840-9E79-62D59C2E2A58}">
       <formula1>=IF(L794&lt;&gt;"",INDIRECT(VLOOKUP(L794,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N794" xr:uid="{F174215C-5E65-449F-9064-71BF145B8DA6}">
+    <dataValidation type="list" sqref="N794" xr:uid="{D089C51A-9027-4F74-BEE3-F9B9C60CA05E}">
       <formula1>=IF(M794&lt;&gt;"",INDIRECT(VLOOKUP(M794,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M795" xr:uid="{9584834A-CEA4-4024-92E0-C6A16CA53712}">
+    <dataValidation type="list" sqref="M795" xr:uid="{7DB2C337-8475-43AD-9222-14564F6E3DD4}">
       <formula1>=IF(L795&lt;&gt;"",INDIRECT(VLOOKUP(L795,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N795" xr:uid="{6CA16763-8BA2-458C-8040-EC327C34C263}">
+    <dataValidation type="list" sqref="N795" xr:uid="{F63E7CDF-C043-4E76-9C60-88F93605D9C2}">
       <formula1>=IF(M795&lt;&gt;"",INDIRECT(VLOOKUP(M795,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M796" xr:uid="{102ABDEF-CA7F-41F3-8CFB-DBCE4B23308E}">
+    <dataValidation type="list" sqref="M796" xr:uid="{7279B9D0-E6BA-46BC-A437-B3978121C59A}">
       <formula1>=IF(L796&lt;&gt;"",INDIRECT(VLOOKUP(L796,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N796" xr:uid="{9309E0DD-545A-4E43-BA3F-775079B27A7A}">
+    <dataValidation type="list" sqref="N796" xr:uid="{8842813C-2A05-463C-8D3C-B3765A6381FD}">
       <formula1>=IF(M796&lt;&gt;"",INDIRECT(VLOOKUP(M796,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M797" xr:uid="{1188C680-0742-49FD-A18F-7B0CF2C96F0D}">
+    <dataValidation type="list" sqref="M797" xr:uid="{37B0CB44-AF29-49E9-B0EF-D7641D78FC12}">
       <formula1>=IF(L797&lt;&gt;"",INDIRECT(VLOOKUP(L797,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N797" xr:uid="{B34528FA-73BA-4997-8333-B410EDF0434B}">
+    <dataValidation type="list" sqref="N797" xr:uid="{77F1926F-0294-4071-B373-D09534D176B0}">
       <formula1>=IF(M797&lt;&gt;"",INDIRECT(VLOOKUP(M797,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M798" xr:uid="{0F207573-E676-41DA-ABD5-E3FF5B6E73C6}">
+    <dataValidation type="list" sqref="M798" xr:uid="{AF76E158-5158-4291-A7F9-326596C84AE2}">
       <formula1>=IF(L798&lt;&gt;"",INDIRECT(VLOOKUP(L798,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N798" xr:uid="{EBE8DE86-B9E8-49ED-A28F-5AA5479039E4}">
+    <dataValidation type="list" sqref="N798" xr:uid="{5A06FE90-0407-4C56-B785-D78556657717}">
       <formula1>=IF(M798&lt;&gt;"",INDIRECT(VLOOKUP(M798,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M799" xr:uid="{D27261CF-7BF2-473A-A58D-32B07299EF48}">
+    <dataValidation type="list" sqref="M799" xr:uid="{0E4E3C0D-2703-4748-B88F-03E1EC2B3CC5}">
       <formula1>=IF(L799&lt;&gt;"",INDIRECT(VLOOKUP(L799,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N799" xr:uid="{0E4C6E75-EA1B-43D9-BB9A-6FC4DADC2003}">
+    <dataValidation type="list" sqref="N799" xr:uid="{8C90B4C2-1DB0-4E88-B9EB-F4343EC82C43}">
       <formula1>=IF(M799&lt;&gt;"",INDIRECT(VLOOKUP(M799,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M800" xr:uid="{CFCE5D70-DEAF-4A43-8104-6E2B02911427}">
+    <dataValidation type="list" sqref="M800" xr:uid="{E0EBD512-DC4D-4218-9848-C557419B22B6}">
       <formula1>=IF(L800&lt;&gt;"",INDIRECT(VLOOKUP(L800,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N800" xr:uid="{BD5420AF-66D5-4208-9C69-1930CD814A90}">
+    <dataValidation type="list" sqref="N800" xr:uid="{14383CE7-728E-4CD6-A8D3-F7ADA97EDB12}">
       <formula1>=IF(M800&lt;&gt;"",INDIRECT(VLOOKUP(M800,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M801" xr:uid="{2F7ADC72-103D-4867-846D-22BE9CFEFBFE}">
+    <dataValidation type="list" sqref="M801" xr:uid="{865EE6A6-8D2D-423F-92B8-03BEA83F3456}">
       <formula1>=IF(L801&lt;&gt;"",INDIRECT(VLOOKUP(L801,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N801" xr:uid="{CC466AE2-C96D-4287-B79D-14A7C4E4D66A}">
+    <dataValidation type="list" sqref="N801" xr:uid="{DC0F1356-0BB6-4E67-A27A-A0E49DF8B277}">
       <formula1>=IF(M801&lt;&gt;"",INDIRECT(VLOOKUP(M801,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M802" xr:uid="{D6185522-E0CF-464E-A50D-760B7B33AA22}">
+    <dataValidation type="list" sqref="M802" xr:uid="{768AB32F-2159-4F01-928A-7882388E2831}">
       <formula1>=IF(L802&lt;&gt;"",INDIRECT(VLOOKUP(L802,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N802" xr:uid="{DC56CC9E-B9D2-4619-98C8-279EB5C70144}">
+    <dataValidation type="list" sqref="N802" xr:uid="{8D14B5E2-0197-4BDE-AF6A-5513A687F9B3}">
       <formula1>=IF(M802&lt;&gt;"",INDIRECT(VLOOKUP(M802,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M803" xr:uid="{F1ED9915-2C6B-43F0-8453-103608520492}">
+    <dataValidation type="list" sqref="M803" xr:uid="{74DEEB9D-D611-4094-B814-67F293025439}">
       <formula1>=IF(L803&lt;&gt;"",INDIRECT(VLOOKUP(L803,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N803" xr:uid="{C648C328-9823-4EDF-A9BB-4FA45DC6507C}">
+    <dataValidation type="list" sqref="N803" xr:uid="{8B9038DC-EF29-4618-B145-3BB4C7AFDDF0}">
       <formula1>=IF(M803&lt;&gt;"",INDIRECT(VLOOKUP(M803,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M804" xr:uid="{ECC2EFB7-29BE-4AE6-9815-37DE2CDAE6BE}">
+    <dataValidation type="list" sqref="M804" xr:uid="{084DDE2A-2C7C-4628-965C-0AD17AAC1E01}">
       <formula1>=IF(L804&lt;&gt;"",INDIRECT(VLOOKUP(L804,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N804" xr:uid="{0DFF5495-A103-44DC-B990-A5EBA982ED02}">
+    <dataValidation type="list" sqref="N804" xr:uid="{4FEB1357-36D5-4FD1-9BD2-4B90960B22E2}">
       <formula1>=IF(M804&lt;&gt;"",INDIRECT(VLOOKUP(M804,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M805" xr:uid="{43574417-73AA-4B7A-A6B9-27C87091B60A}">
+    <dataValidation type="list" sqref="M805" xr:uid="{D2A83088-4C7E-48AF-AEAF-FFE7E2FBB5FE}">
       <formula1>=IF(L805&lt;&gt;"",INDIRECT(VLOOKUP(L805,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N805" xr:uid="{264E21CF-C570-4961-BF8E-663D68020CC4}">
+    <dataValidation type="list" sqref="N805" xr:uid="{03402C5C-C4BA-401A-9FBD-6378D91B51BE}">
       <formula1>=IF(M805&lt;&gt;"",INDIRECT(VLOOKUP(M805,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M806" xr:uid="{191F32BB-7485-4948-A4EB-54D22A27E0D1}">
+    <dataValidation type="list" sqref="M806" xr:uid="{0D2713F3-DC2A-4B8D-8155-59A2171AB19B}">
       <formula1>=IF(L806&lt;&gt;"",INDIRECT(VLOOKUP(L806,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N806" xr:uid="{24ED1D6A-EFB6-4AB7-91B6-BABC3EB84E8D}">
+    <dataValidation type="list" sqref="N806" xr:uid="{8E464E06-57F1-4DAB-B81E-FEA9E51D6823}">
       <formula1>=IF(M806&lt;&gt;"",INDIRECT(VLOOKUP(M806,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M807" xr:uid="{9AA5F3E1-5C4E-463A-8F62-9DE492B1031C}">
+    <dataValidation type="list" sqref="M807" xr:uid="{235B08A4-45F9-4ED9-8C70-05007CAA8E1B}">
       <formula1>=IF(L807&lt;&gt;"",INDIRECT(VLOOKUP(L807,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N807" xr:uid="{6DCE1E38-91AE-4AC7-8782-487F52CBF448}">
+    <dataValidation type="list" sqref="N807" xr:uid="{897DCAC0-1CAF-4B01-9E2C-07C3D96BCDC6}">
       <formula1>=IF(M807&lt;&gt;"",INDIRECT(VLOOKUP(M807,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M808" xr:uid="{AD7F226E-1018-44AF-800F-2734C74E06FC}">
+    <dataValidation type="list" sqref="M808" xr:uid="{D65357D1-A20B-43C9-B811-40915BEBEEEF}">
       <formula1>=IF(L808&lt;&gt;"",INDIRECT(VLOOKUP(L808,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N808" xr:uid="{2AD9B526-70D6-4C4B-B916-6A176AA8A676}">
+    <dataValidation type="list" sqref="N808" xr:uid="{C26C3A96-F527-496F-BA13-153C31ECFD20}">
       <formula1>=IF(M808&lt;&gt;"",INDIRECT(VLOOKUP(M808,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M809" xr:uid="{FCCE57E1-1EA9-4A1B-B2C6-883F40C936D8}">
+    <dataValidation type="list" sqref="M809" xr:uid="{1696E89F-500B-468D-8AA5-810CC657DE3E}">
       <formula1>=IF(L809&lt;&gt;"",INDIRECT(VLOOKUP(L809,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N809" xr:uid="{95E947F4-4D10-4E75-920D-A9633F72A5E5}">
+    <dataValidation type="list" sqref="N809" xr:uid="{08D338F5-073C-44C2-9DBC-DB595290A101}">
       <formula1>=IF(M809&lt;&gt;"",INDIRECT(VLOOKUP(M809,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M810" xr:uid="{0E74767D-2F96-46FF-8106-578B335F6C30}">
+    <dataValidation type="list" sqref="M810" xr:uid="{CD929DD7-54B7-4F3B-89FA-6CFD8C4D55CF}">
       <formula1>=IF(L810&lt;&gt;"",INDIRECT(VLOOKUP(L810,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N810" xr:uid="{E1534F92-1C7D-4647-ACA9-7596921F06F5}">
+    <dataValidation type="list" sqref="N810" xr:uid="{0A21F4DD-F840-452F-8A9A-820FF481F699}">
       <formula1>=IF(M810&lt;&gt;"",INDIRECT(VLOOKUP(M810,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M811" xr:uid="{FB50D782-8BBB-4A4F-B11D-B802192629F2}">
+    <dataValidation type="list" sqref="M811" xr:uid="{A06BA3B6-0D9C-44FA-A0FB-4BEAD69EF10C}">
       <formula1>=IF(L811&lt;&gt;"",INDIRECT(VLOOKUP(L811,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N811" xr:uid="{7F9041BF-AE6C-4755-B538-7AAAC39EFCB2}">
+    <dataValidation type="list" sqref="N811" xr:uid="{EC6A0415-E2E7-4DA2-A751-0A39B1514E1D}">
       <formula1>=IF(M811&lt;&gt;"",INDIRECT(VLOOKUP(M811,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M812" xr:uid="{6FA883CE-A186-4A42-8906-AC21C3C2AAD9}">
+    <dataValidation type="list" sqref="M812" xr:uid="{18EF8113-9D98-4D72-B861-9DD0CF4D8B39}">
       <formula1>=IF(L812&lt;&gt;"",INDIRECT(VLOOKUP(L812,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N812" xr:uid="{71581B79-2E82-48B0-897B-F6D79D07848F}">
+    <dataValidation type="list" sqref="N812" xr:uid="{EFF5B129-E034-41AA-A788-5F6A252359F2}">
       <formula1>=IF(M812&lt;&gt;"",INDIRECT(VLOOKUP(M812,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M813" xr:uid="{EC9B8566-5F09-43B4-B2A1-9D38E5AC4467}">
+    <dataValidation type="list" sqref="M813" xr:uid="{92212476-63F5-47CC-8266-2B7F7FC49B65}">
       <formula1>=IF(L813&lt;&gt;"",INDIRECT(VLOOKUP(L813,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N813" xr:uid="{C0A21188-3EE4-4FF7-8581-4B897FE89AB2}">
+    <dataValidation type="list" sqref="N813" xr:uid="{8885F034-7F31-4769-923C-EE6EC35D3B5F}">
       <formula1>=IF(M813&lt;&gt;"",INDIRECT(VLOOKUP(M813,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M814" xr:uid="{53B60DCC-1EBA-417A-861F-96792B59CCFA}">
+    <dataValidation type="list" sqref="M814" xr:uid="{9AA64F87-C72D-4F9A-A7AC-F32013ACB7FC}">
       <formula1>=IF(L814&lt;&gt;"",INDIRECT(VLOOKUP(L814,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N814" xr:uid="{41309CD8-F198-4195-B371-F41C286F0E52}">
+    <dataValidation type="list" sqref="N814" xr:uid="{64C3B5A0-7EB0-4AA0-8875-6E0A25261178}">
       <formula1>=IF(M814&lt;&gt;"",INDIRECT(VLOOKUP(M814,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M815" xr:uid="{D8C07FDD-6D1F-41C7-AACF-05F35EBC7A9E}">
+    <dataValidation type="list" sqref="M815" xr:uid="{9A2BF676-B939-490C-BD94-253C7A952FE4}">
       <formula1>=IF(L815&lt;&gt;"",INDIRECT(VLOOKUP(L815,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N815" xr:uid="{DE80F65E-0E66-4CD9-8DE0-27D67D9C4ACC}">
+    <dataValidation type="list" sqref="N815" xr:uid="{2ECE355F-3CD6-4BCB-9377-90E19025A041}">
       <formula1>=IF(M815&lt;&gt;"",INDIRECT(VLOOKUP(M815,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M816" xr:uid="{2E32DC13-13FF-4D5C-BCF5-E368DD461E99}">
+    <dataValidation type="list" sqref="M816" xr:uid="{F1F7A68B-F27F-43E4-AAE0-41F0887DCA1A}">
       <formula1>=IF(L816&lt;&gt;"",INDIRECT(VLOOKUP(L816,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N816" xr:uid="{0F74F85A-DF76-40B7-841F-4D6135319718}">
+    <dataValidation type="list" sqref="N816" xr:uid="{86E604EE-3377-41D4-9416-FAD4711B08DD}">
       <formula1>=IF(M816&lt;&gt;"",INDIRECT(VLOOKUP(M816,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M817" xr:uid="{09E085D7-8B03-4C64-A190-1FDFD79AE6E3}">
+    <dataValidation type="list" sqref="M817" xr:uid="{60AEB098-12D0-4E89-9D1E-A288DAC84E84}">
       <formula1>=IF(L817&lt;&gt;"",INDIRECT(VLOOKUP(L817,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N817" xr:uid="{3CB9FE6D-7BEB-44B9-90E5-A9E7CFE538D9}">
+    <dataValidation type="list" sqref="N817" xr:uid="{B2658873-AD64-433D-A61D-A5FEF88D7A30}">
       <formula1>=IF(M817&lt;&gt;"",INDIRECT(VLOOKUP(M817,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M818" xr:uid="{5A8607E2-9242-44C6-9D90-203215CDB4CB}">
+    <dataValidation type="list" sqref="M818" xr:uid="{26F13D28-0A0C-4ECA-9FE9-EBC61B36BE63}">
       <formula1>=IF(L818&lt;&gt;"",INDIRECT(VLOOKUP(L818,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N818" xr:uid="{0E97E2DE-995C-4845-879B-E9EFEF56CF87}">
+    <dataValidation type="list" sqref="N818" xr:uid="{C28106ED-AE1D-48C6-9424-803641D0AE17}">
       <formula1>=IF(M818&lt;&gt;"",INDIRECT(VLOOKUP(M818,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M819" xr:uid="{167BDCB8-0D2B-4803-BD4C-70C8CDAA4121}">
+    <dataValidation type="list" sqref="M819" xr:uid="{C8F2F160-1FE3-4668-97A5-6D35E2D3527A}">
       <formula1>=IF(L819&lt;&gt;"",INDIRECT(VLOOKUP(L819,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N819" xr:uid="{3C67AD26-AC35-48A1-8FBB-AD6AB6312EB9}">
+    <dataValidation type="list" sqref="N819" xr:uid="{28C9656C-46AF-492F-A9F5-2601ED46C455}">
       <formula1>=IF(M819&lt;&gt;"",INDIRECT(VLOOKUP(M819,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M820" xr:uid="{058E1BC9-7B4D-453C-BE72-E1C0FF5EE8EC}">
+    <dataValidation type="list" sqref="M820" xr:uid="{B51F2A52-BE29-4D20-ACD3-E648CC93441C}">
       <formula1>=IF(L820&lt;&gt;"",INDIRECT(VLOOKUP(L820,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N820" xr:uid="{911D19FB-D21A-415E-9CC7-40BC558061CE}">
+    <dataValidation type="list" sqref="N820" xr:uid="{6BC63EA7-94F8-4644-92A9-28F7850185A3}">
       <formula1>=IF(M820&lt;&gt;"",INDIRECT(VLOOKUP(M820,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M821" xr:uid="{1E466775-FE9C-4AC8-BD06-FADFBCC246E7}">
+    <dataValidation type="list" sqref="M821" xr:uid="{87FB479E-EF42-475D-8F75-320137379A3C}">
       <formula1>=IF(L821&lt;&gt;"",INDIRECT(VLOOKUP(L821,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N821" xr:uid="{7EA18694-F4EC-46AC-AD38-E63C78FCFB79}">
+    <dataValidation type="list" sqref="N821" xr:uid="{2BAD7E78-938A-4C5A-9AF7-251256C5CF08}">
       <formula1>=IF(M821&lt;&gt;"",INDIRECT(VLOOKUP(M821,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M822" xr:uid="{CFEBA6AC-91F5-4FA2-B2F4-9CBFBA2A3CC3}">
+    <dataValidation type="list" sqref="M822" xr:uid="{81B093E7-504C-4610-801D-EAE18C20243F}">
       <formula1>=IF(L822&lt;&gt;"",INDIRECT(VLOOKUP(L822,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N822" xr:uid="{BEC9FC97-AE56-402C-9C25-633184A5B320}">
+    <dataValidation type="list" sqref="N822" xr:uid="{8AD7054B-5D90-496C-9113-22A211E4F09A}">
       <formula1>=IF(M822&lt;&gt;"",INDIRECT(VLOOKUP(M822,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M823" xr:uid="{9DC39AB9-B44B-4A63-890E-CD9809C1B525}">
+    <dataValidation type="list" sqref="M823" xr:uid="{78073CDD-F35A-4DFF-81D5-619A4913A005}">
       <formula1>=IF(L823&lt;&gt;"",INDIRECT(VLOOKUP(L823,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N823" xr:uid="{30CBDA42-F4D6-42D0-AA79-692827AA558D}">
+    <dataValidation type="list" sqref="N823" xr:uid="{5DF84FE0-8506-485A-B625-3738C82F7835}">
       <formula1>=IF(M823&lt;&gt;"",INDIRECT(VLOOKUP(M823,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M824" xr:uid="{10034A4D-B880-4E62-BA7F-F01A30F90CE0}">
+    <dataValidation type="list" sqref="M824" xr:uid="{B32B167E-C966-4A1C-A0EC-A9181F9D835F}">
       <formula1>=IF(L824&lt;&gt;"",INDIRECT(VLOOKUP(L824,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N824" xr:uid="{A1B31764-302C-4C6E-8B81-6A92EA795B14}">
+    <dataValidation type="list" sqref="N824" xr:uid="{4BDFF48C-0492-40DD-ADCB-00F9BD731A7A}">
       <formula1>=IF(M824&lt;&gt;"",INDIRECT(VLOOKUP(M824,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M825" xr:uid="{D18A6FA3-A94E-4542-8E92-12B993A7FEC8}">
+    <dataValidation type="list" sqref="M825" xr:uid="{3E43B11F-2717-49CC-B26A-AEFC30AB2625}">
       <formula1>=IF(L825&lt;&gt;"",INDIRECT(VLOOKUP(L825,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N825" xr:uid="{57428A41-4254-417B-938E-01A17DBC19D3}">
+    <dataValidation type="list" sqref="N825" xr:uid="{F0ADEB09-699C-4F76-ADD7-2E4979F2634D}">
       <formula1>=IF(M825&lt;&gt;"",INDIRECT(VLOOKUP(M825,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M826" xr:uid="{59EF3251-59CB-4688-8843-C4E65285A073}">
+    <dataValidation type="list" sqref="M826" xr:uid="{D58667B9-A7CF-42E7-8DCE-865312A0E814}">
       <formula1>=IF(L826&lt;&gt;"",INDIRECT(VLOOKUP(L826,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N826" xr:uid="{34985EDF-92A5-48F6-95F8-7E26FD1F1C19}">
+    <dataValidation type="list" sqref="N826" xr:uid="{E756276B-4725-408E-B01B-25D4A764FBE9}">
       <formula1>=IF(M826&lt;&gt;"",INDIRECT(VLOOKUP(M826,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M827" xr:uid="{5A7BD25F-4B59-4C84-9B9D-16E96363A14A}">
+    <dataValidation type="list" sqref="M827" xr:uid="{6B9DC05F-79BE-4342-B816-5DA87897F8EC}">
       <formula1>=IF(L827&lt;&gt;"",INDIRECT(VLOOKUP(L827,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N827" xr:uid="{017D09B1-A9A7-4E96-B2FE-7A2F224244D9}">
+    <dataValidation type="list" sqref="N827" xr:uid="{298DBB08-FDDA-4456-927B-54E40061811E}">
       <formula1>=IF(M827&lt;&gt;"",INDIRECT(VLOOKUP(M827,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M828" xr:uid="{5DC0F0E4-22F8-40FF-B94C-7E8186DB8884}">
+    <dataValidation type="list" sqref="M828" xr:uid="{A1D1E12E-98F7-42DE-B728-3FF716F2EB28}">
       <formula1>=IF(L828&lt;&gt;"",INDIRECT(VLOOKUP(L828,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N828" xr:uid="{CCDCE59E-74CD-412C-9493-5037AA680E6C}">
+    <dataValidation type="list" sqref="N828" xr:uid="{5F41D6E8-E3EC-4190-8E0C-0909C23FA4AE}">
       <formula1>=IF(M828&lt;&gt;"",INDIRECT(VLOOKUP(M828,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M829" xr:uid="{4F0BF65A-7AA7-4A47-96EC-5AED629F3B3F}">
+    <dataValidation type="list" sqref="M829" xr:uid="{FBB4A8E4-AACD-4EC4-B958-315F602DEFDA}">
       <formula1>=IF(L829&lt;&gt;"",INDIRECT(VLOOKUP(L829,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N829" xr:uid="{AA919E56-6F66-4B85-BAE5-4285AEA20834}">
+    <dataValidation type="list" sqref="N829" xr:uid="{7A0CD60D-5784-41E7-A04B-4EF26FFEFA94}">
       <formula1>=IF(M829&lt;&gt;"",INDIRECT(VLOOKUP(M829,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M830" xr:uid="{2BC399BA-4D63-49ED-A17B-B02E99EC15BC}">
+    <dataValidation type="list" sqref="M830" xr:uid="{5F36C56C-E689-48E5-ADC8-96BDD33FA948}">
       <formula1>=IF(L830&lt;&gt;"",INDIRECT(VLOOKUP(L830,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N830" xr:uid="{A1336D3B-1FE2-4C45-9F7F-1EAF7F7E250B}">
+    <dataValidation type="list" sqref="N830" xr:uid="{884BC448-4BBD-4454-8A0B-231E0FC246C0}">
       <formula1>=IF(M830&lt;&gt;"",INDIRECT(VLOOKUP(M830,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M831" xr:uid="{77A6238D-68EA-4AA9-AEEA-C47D88F969D7}">
+    <dataValidation type="list" sqref="M831" xr:uid="{417E4B18-15FC-4F18-951A-BC10628F8FC7}">
       <formula1>=IF(L831&lt;&gt;"",INDIRECT(VLOOKUP(L831,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N831" xr:uid="{8E7C6779-DC54-4F4D-9630-427DA77FF2CB}">
+    <dataValidation type="list" sqref="N831" xr:uid="{272D9D69-1F35-49B1-9DDA-3C614F439038}">
       <formula1>=IF(M831&lt;&gt;"",INDIRECT(VLOOKUP(M831,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M832" xr:uid="{A1E28159-977F-462F-ACD9-A25790BC13E0}">
+    <dataValidation type="list" sqref="M832" xr:uid="{D15C7590-C470-4078-A9C9-38AC154FB2B2}">
       <formula1>=IF(L832&lt;&gt;"",INDIRECT(VLOOKUP(L832,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N832" xr:uid="{4CCDBB2A-4963-4712-98F1-D057F5F654D3}">
+    <dataValidation type="list" sqref="N832" xr:uid="{EAF882D7-54D6-4706-91D4-C568EA4051C2}">
       <formula1>=IF(M832&lt;&gt;"",INDIRECT(VLOOKUP(M832,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M833" xr:uid="{B74AEABB-96CF-486C-B845-E9722D3175D1}">
+    <dataValidation type="list" sqref="M833" xr:uid="{BD60B8B2-2486-45C1-8AF3-1C6D1A923518}">
       <formula1>=IF(L833&lt;&gt;"",INDIRECT(VLOOKUP(L833,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N833" xr:uid="{54EC870C-C41D-4FD1-A938-C102517FF4DF}">
+    <dataValidation type="list" sqref="N833" xr:uid="{13B412D8-087E-42B9-B2E8-429ABA4362B1}">
       <formula1>=IF(M833&lt;&gt;"",INDIRECT(VLOOKUP(M833,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M834" xr:uid="{CBDB53C3-EC51-403A-8D7D-32EBA39AF7C8}">
+    <dataValidation type="list" sqref="M834" xr:uid="{B6086FFE-5643-4F6B-8667-709090468339}">
       <formula1>=IF(L834&lt;&gt;"",INDIRECT(VLOOKUP(L834,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N834" xr:uid="{1061F69D-F234-4EF1-99AD-C8BA30CB19BA}">
+    <dataValidation type="list" sqref="N834" xr:uid="{0FE9119B-ED12-4B41-A858-A5E7FE59EF2E}">
       <formula1>=IF(M834&lt;&gt;"",INDIRECT(VLOOKUP(M834,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M835" xr:uid="{DBC22200-0E26-4062-87F6-0666F728E9EF}">
+    <dataValidation type="list" sqref="M835" xr:uid="{B8D45622-2A9A-448C-A38B-BB4B5C8FC3BB}">
       <formula1>=IF(L835&lt;&gt;"",INDIRECT(VLOOKUP(L835,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N835" xr:uid="{71252EB2-271E-4A9F-9FE1-A2949439C9C0}">
+    <dataValidation type="list" sqref="N835" xr:uid="{6474CAB5-343E-4410-8BCB-292A96F3D8B0}">
       <formula1>=IF(M835&lt;&gt;"",INDIRECT(VLOOKUP(M835,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M836" xr:uid="{76B721E1-766F-4927-8493-2333C442D12A}">
+    <dataValidation type="list" sqref="M836" xr:uid="{AB5D1F1B-0B26-4BBA-A970-CAABB6486A9E}">
       <formula1>=IF(L836&lt;&gt;"",INDIRECT(VLOOKUP(L836,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N836" xr:uid="{3D562616-BE04-4FA1-BBE5-12E8469FF361}">
+    <dataValidation type="list" sqref="N836" xr:uid="{148C6C8A-7023-461F-B4EC-C5915FA0CB66}">
       <formula1>=IF(M836&lt;&gt;"",INDIRECT(VLOOKUP(M836,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M837" xr:uid="{AFEFA24B-E13E-4E3E-9227-5D0B11C21B07}">
+    <dataValidation type="list" sqref="M837" xr:uid="{904EC9DF-969B-41F8-8F53-2D1DF93F4CC7}">
       <formula1>=IF(L837&lt;&gt;"",INDIRECT(VLOOKUP(L837,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N837" xr:uid="{238DB95D-7FD4-4F32-97F0-98381672C5A3}">
+    <dataValidation type="list" sqref="N837" xr:uid="{73F9FB62-CD33-4B8B-8DD3-F994BA83602C}">
       <formula1>=IF(M837&lt;&gt;"",INDIRECT(VLOOKUP(M837,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M838" xr:uid="{B3F18E72-FF2F-402A-8D54-FCA8934BBF8B}">
+    <dataValidation type="list" sqref="M838" xr:uid="{F0AC0818-F253-4363-BA57-2A17BEF32BA1}">
       <formula1>=IF(L838&lt;&gt;"",INDIRECT(VLOOKUP(L838,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N838" xr:uid="{74BF0AAB-4159-4B42-A359-8DC886843A99}">
+    <dataValidation type="list" sqref="N838" xr:uid="{CDCBB004-416A-4536-90BE-FBE34A292B2F}">
       <formula1>=IF(M838&lt;&gt;"",INDIRECT(VLOOKUP(M838,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M839" xr:uid="{E18B1EA0-7B68-405E-8F13-809EB9E3B495}">
+    <dataValidation type="list" sqref="M839" xr:uid="{67063DB3-A6F8-4468-A9E5-6CF09A2ED5FF}">
       <formula1>=IF(L839&lt;&gt;"",INDIRECT(VLOOKUP(L839,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N839" xr:uid="{DCD83B1C-20E6-4C57-BEED-77F9AC4CDD45}">
+    <dataValidation type="list" sqref="N839" xr:uid="{C43A8F58-3FB0-443C-821A-CFE72DE26FC2}">
       <formula1>=IF(M839&lt;&gt;"",INDIRECT(VLOOKUP(M839,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M840" xr:uid="{6D01BA41-EC67-43D9-9E24-F22CF19F8C59}">
+    <dataValidation type="list" sqref="M840" xr:uid="{75590AED-7BFE-4344-A947-18C2B47DEFF0}">
       <formula1>=IF(L840&lt;&gt;"",INDIRECT(VLOOKUP(L840,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N840" xr:uid="{9F160551-3420-48CE-8D56-9FF30D51BFB2}">
+    <dataValidation type="list" sqref="N840" xr:uid="{B26F9CFF-CFD6-4299-B328-3B54B339DE4C}">
       <formula1>=IF(M840&lt;&gt;"",INDIRECT(VLOOKUP(M840,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M841" xr:uid="{DC500CEF-2B55-46B8-BDBA-3E68C90A0676}">
+    <dataValidation type="list" sqref="M841" xr:uid="{8EFC4763-44A5-40A5-A6D5-AE735A3E5F9D}">
       <formula1>=IF(L841&lt;&gt;"",INDIRECT(VLOOKUP(L841,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N841" xr:uid="{5841FFAE-B90A-4552-BD7A-318894AD4DA3}">
+    <dataValidation type="list" sqref="N841" xr:uid="{FF055DF9-3708-4213-A858-FC738A98847F}">
       <formula1>=IF(M841&lt;&gt;"",INDIRECT(VLOOKUP(M841,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M842" xr:uid="{854DF330-6849-45F5-8A2D-8B44462797AB}">
+    <dataValidation type="list" sqref="M842" xr:uid="{6CEBC088-FD90-4C44-B5D3-E4C5F864E172}">
       <formula1>=IF(L842&lt;&gt;"",INDIRECT(VLOOKUP(L842,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N842" xr:uid="{321F8226-CEFB-427E-9162-0EEDCF08B436}">
+    <dataValidation type="list" sqref="N842" xr:uid="{E91E7F35-6FA7-4B20-9C6C-A184E51E0C57}">
       <formula1>=IF(M842&lt;&gt;"",INDIRECT(VLOOKUP(M842,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M843" xr:uid="{3D9D3445-B38E-4DE5-A04C-2B29EBF98F10}">
+    <dataValidation type="list" sqref="M843" xr:uid="{F6E58495-DE8A-4E3D-9B4E-D6BC844177AE}">
       <formula1>=IF(L843&lt;&gt;"",INDIRECT(VLOOKUP(L843,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N843" xr:uid="{A425DE6B-2F7E-4BD6-BBE4-2D11689A5AA6}">
+    <dataValidation type="list" sqref="N843" xr:uid="{770DA3DD-273D-4A28-905D-3D45E7D3F141}">
       <formula1>=IF(M843&lt;&gt;"",INDIRECT(VLOOKUP(M843,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M844" xr:uid="{D70D1194-A2E4-4EAA-A060-85FC95943005}">
+    <dataValidation type="list" sqref="M844" xr:uid="{7B6EF42C-ABF4-484F-B49C-40515F784404}">
       <formula1>=IF(L844&lt;&gt;"",INDIRECT(VLOOKUP(L844,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N844" xr:uid="{49E2F2BD-A5F6-4C74-90B2-41F275480105}">
+    <dataValidation type="list" sqref="N844" xr:uid="{F043A253-34D6-43ED-B451-69C6FBE87FE9}">
       <formula1>=IF(M844&lt;&gt;"",INDIRECT(VLOOKUP(M844,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M845" xr:uid="{9ECA2EAC-6EA5-4358-8B29-442033CF247B}">
+    <dataValidation type="list" sqref="M845" xr:uid="{54F54582-AD84-4549-848C-9C57C73D39F5}">
       <formula1>=IF(L845&lt;&gt;"",INDIRECT(VLOOKUP(L845,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N845" xr:uid="{885B26F7-20A7-4C14-AFF7-E3DFDD07B013}">
+    <dataValidation type="list" sqref="N845" xr:uid="{88C07720-BE05-46B9-A7E3-83349B51508F}">
       <formula1>=IF(M845&lt;&gt;"",INDIRECT(VLOOKUP(M845,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M846" xr:uid="{C6EC38A5-27BB-4443-8910-D1061B826226}">
+    <dataValidation type="list" sqref="M846" xr:uid="{3AE4D899-607D-4197-AA67-EDDCE49EA176}">
       <formula1>=IF(L846&lt;&gt;"",INDIRECT(VLOOKUP(L846,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N846" xr:uid="{967923AD-8265-4C8A-85AE-F1AEBE6E2CBD}">
+    <dataValidation type="list" sqref="N846" xr:uid="{D773BC15-DC03-4B15-AEC8-C72768243FF3}">
       <formula1>=IF(M846&lt;&gt;"",INDIRECT(VLOOKUP(M846,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M847" xr:uid="{7894C493-7258-4DDA-9600-FB18C74D9FCD}">
+    <dataValidation type="list" sqref="M847" xr:uid="{5FDE9B7A-B907-4025-9D08-2F3549CF213A}">
       <formula1>=IF(L847&lt;&gt;"",INDIRECT(VLOOKUP(L847,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N847" xr:uid="{3A5700C4-63C3-4CB5-A400-74FD102AC5A6}">
+    <dataValidation type="list" sqref="N847" xr:uid="{BD7B0E4F-FE9A-4FFF-9608-FB525D8978EA}">
       <formula1>=IF(M847&lt;&gt;"",INDIRECT(VLOOKUP(M847,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M848" xr:uid="{C06046A3-AF37-41F0-9417-72564B16DE34}">
+    <dataValidation type="list" sqref="M848" xr:uid="{02F7DDAA-0169-4D6C-B7F4-1D4EC0E2D800}">
       <formula1>=IF(L848&lt;&gt;"",INDIRECT(VLOOKUP(L848,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N848" xr:uid="{6BD79782-06CF-4190-AABB-94F1B2096FB4}">
+    <dataValidation type="list" sqref="N848" xr:uid="{68BD1FCB-4B14-4CFB-A227-76199B5A6902}">
       <formula1>=IF(M848&lt;&gt;"",INDIRECT(VLOOKUP(M848,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M849" xr:uid="{C6605454-C212-4F6E-A146-E83037BC464C}">
+    <dataValidation type="list" sqref="M849" xr:uid="{FFBE54EE-59EB-49DA-8B00-D89299AA2A62}">
       <formula1>=IF(L849&lt;&gt;"",INDIRECT(VLOOKUP(L849,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N849" xr:uid="{B212F426-3514-4526-8EDE-4395CEA251BE}">
+    <dataValidation type="list" sqref="N849" xr:uid="{AC1EE11E-68F7-4D09-8053-E842F68100A8}">
       <formula1>=IF(M849&lt;&gt;"",INDIRECT(VLOOKUP(M849,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M850" xr:uid="{CA21EF95-C86B-4A79-BFF8-A314FF19F49C}">
+    <dataValidation type="list" sqref="M850" xr:uid="{63532808-D6B3-4128-97A3-13AEBF7F5F03}">
       <formula1>=IF(L850&lt;&gt;"",INDIRECT(VLOOKUP(L850,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N850" xr:uid="{BFF088DC-0FBB-4F5F-AF77-B1602A3AA9ED}">
+    <dataValidation type="list" sqref="N850" xr:uid="{EBC86866-4295-424F-8067-65D245C08AA8}">
       <formula1>=IF(M850&lt;&gt;"",INDIRECT(VLOOKUP(M850,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M851" xr:uid="{298A1BDE-8C82-46E5-A8AB-57A92D715A25}">
+    <dataValidation type="list" sqref="M851" xr:uid="{097793B6-7F4B-4B14-A43F-AE5AE7320CCF}">
       <formula1>=IF(L851&lt;&gt;"",INDIRECT(VLOOKUP(L851,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N851" xr:uid="{FFFA6FAD-87EE-4CC2-AC28-15885AF9D3AF}">
+    <dataValidation type="list" sqref="N851" xr:uid="{2E51CAEB-9322-4ADC-80B5-F0A7A422C619}">
       <formula1>=IF(M851&lt;&gt;"",INDIRECT(VLOOKUP(M851,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M852" xr:uid="{8D2797CB-DED5-428D-B303-D41635099951}">
+    <dataValidation type="list" sqref="M852" xr:uid="{3D42B9B7-C7C9-49B1-BEA4-3AED78008EB2}">
       <formula1>=IF(L852&lt;&gt;"",INDIRECT(VLOOKUP(L852,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N852" xr:uid="{79DA303E-02B4-4F54-A8C9-ADCD85E27AA3}">
+    <dataValidation type="list" sqref="N852" xr:uid="{61C31CD4-4D99-4645-9291-77EDADA089BB}">
       <formula1>=IF(M852&lt;&gt;"",INDIRECT(VLOOKUP(M852,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M853" xr:uid="{3059C227-A4AD-4138-B87B-6BA0FA8CB11A}">
+    <dataValidation type="list" sqref="M853" xr:uid="{8B2441AF-42AE-4107-A6A6-A01C05324A63}">
       <formula1>=IF(L853&lt;&gt;"",INDIRECT(VLOOKUP(L853,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N853" xr:uid="{13FA69CB-5B1A-4AE9-A7FC-0621C29FBBCD}">
+    <dataValidation type="list" sqref="N853" xr:uid="{12F407BB-02DB-4BE7-B4BA-8E68AC1275B6}">
       <formula1>=IF(M853&lt;&gt;"",INDIRECT(VLOOKUP(M853,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M854" xr:uid="{2997A806-F754-40A2-85E5-4CEF66F77C67}">
+    <dataValidation type="list" sqref="M854" xr:uid="{20CD4378-C66B-4F11-9676-5B898A17127C}">
       <formula1>=IF(L854&lt;&gt;"",INDIRECT(VLOOKUP(L854,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N854" xr:uid="{2F357365-FCF7-4A35-99E4-B40EE0643A09}">
+    <dataValidation type="list" sqref="N854" xr:uid="{549983A1-835E-4594-9F7B-2502E0061D26}">
       <formula1>=IF(M854&lt;&gt;"",INDIRECT(VLOOKUP(M854,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M855" xr:uid="{7675840D-8598-4D06-A28D-F9A3A4832EBF}">
+    <dataValidation type="list" sqref="M855" xr:uid="{531169B3-8A52-4431-B0EE-376D47019D6F}">
       <formula1>=IF(L855&lt;&gt;"",INDIRECT(VLOOKUP(L855,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N855" xr:uid="{01028F1C-1516-4A2B-A8F2-BC9C08DCADD6}">
+    <dataValidation type="list" sqref="N855" xr:uid="{17925249-2FF1-4AC4-9804-C231FC9F8986}">
       <formula1>=IF(M855&lt;&gt;"",INDIRECT(VLOOKUP(M855,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M856" xr:uid="{F0A71E33-B362-4E71-A43F-F811DA604993}">
+    <dataValidation type="list" sqref="M856" xr:uid="{3C3F4865-0DB9-4952-82D5-F57151A6B1A4}">
       <formula1>=IF(L856&lt;&gt;"",INDIRECT(VLOOKUP(L856,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N856" xr:uid="{5F88924E-A898-4C3B-9D00-F37F000A0D53}">
+    <dataValidation type="list" sqref="N856" xr:uid="{E59E4948-48EB-4727-A3FB-112C0A8553C9}">
       <formula1>=IF(M856&lt;&gt;"",INDIRECT(VLOOKUP(M856,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M857" xr:uid="{46B166A3-88CE-40BC-AB6B-3E0B413451B6}">
+    <dataValidation type="list" sqref="M857" xr:uid="{49EC6CEB-A212-4664-A84C-98DAB5B68C7F}">
       <formula1>=IF(L857&lt;&gt;"",INDIRECT(VLOOKUP(L857,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N857" xr:uid="{6E666B91-BE0A-4325-B642-2E21B39DC2FE}">
+    <dataValidation type="list" sqref="N857" xr:uid="{4A7BA380-33BF-441F-ADE0-93D8954D725E}">
       <formula1>=IF(M857&lt;&gt;"",INDIRECT(VLOOKUP(M857,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M858" xr:uid="{5954091F-49C5-48E5-9EC8-B0F89AB39F24}">
+    <dataValidation type="list" sqref="M858" xr:uid="{063093C4-B17B-47F0-A52F-39020B19E999}">
       <formula1>=IF(L858&lt;&gt;"",INDIRECT(VLOOKUP(L858,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N858" xr:uid="{066C0CD8-7EB5-4CC3-903B-B398231E71CE}">
+    <dataValidation type="list" sqref="N858" xr:uid="{A2FD6D0C-2551-4C39-BE13-BD2DF47E1995}">
       <formula1>=IF(M858&lt;&gt;"",INDIRECT(VLOOKUP(M858,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M859" xr:uid="{A282973A-351A-4359-ABC7-1BF9E72D8C2A}">
+    <dataValidation type="list" sqref="M859" xr:uid="{E4CCCDAD-AEDE-4768-8196-B557B58A61E2}">
       <formula1>=IF(L859&lt;&gt;"",INDIRECT(VLOOKUP(L859,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N859" xr:uid="{9951289C-40C2-4916-92EE-1A7CA78EF462}">
+    <dataValidation type="list" sqref="N859" xr:uid="{ECBAC46C-79E0-4E29-B7D1-9403DB7B6B76}">
       <formula1>=IF(M859&lt;&gt;"",INDIRECT(VLOOKUP(M859,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M860" xr:uid="{8AEA9C73-BB29-4CDC-B1E8-9742F5D785E6}">
+    <dataValidation type="list" sqref="M860" xr:uid="{3DEC4D02-205D-4791-9844-050621C5D703}">
       <formula1>=IF(L860&lt;&gt;"",INDIRECT(VLOOKUP(L860,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N860" xr:uid="{0B0EB4E5-B9A0-454D-B1D6-D70A537A3C71}">
+    <dataValidation type="list" sqref="N860" xr:uid="{568F58AC-3E8A-4CFA-AB6C-DAEDA4F2530C}">
       <formula1>=IF(M860&lt;&gt;"",INDIRECT(VLOOKUP(M860,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M861" xr:uid="{E4CCF46C-92B5-4577-AA93-5B4112307CFF}">
+    <dataValidation type="list" sqref="M861" xr:uid="{5F2AB6D9-7C40-477A-B580-9D99406F218B}">
       <formula1>=IF(L861&lt;&gt;"",INDIRECT(VLOOKUP(L861,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N861" xr:uid="{557D0472-2A74-4CF8-9746-E6602B1F5E88}">
+    <dataValidation type="list" sqref="N861" xr:uid="{48687C71-47EC-436E-A01E-90CDB0ACE9B7}">
       <formula1>=IF(M861&lt;&gt;"",INDIRECT(VLOOKUP(M861,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M862" xr:uid="{20E1EFC7-0358-41DE-B85A-54C490335AF3}">
+    <dataValidation type="list" sqref="M862" xr:uid="{2ACA970D-09FA-43B5-9A14-C89449E6EC10}">
       <formula1>=IF(L862&lt;&gt;"",INDIRECT(VLOOKUP(L862,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N862" xr:uid="{CF89B104-B620-4215-9330-D85D7AAA2233}">
+    <dataValidation type="list" sqref="N862" xr:uid="{CAD12FC3-DAD1-45BA-AB5B-EEBC9B55D4FA}">
       <formula1>=IF(M862&lt;&gt;"",INDIRECT(VLOOKUP(M862,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M863" xr:uid="{A9F42D76-A885-4002-81FA-063549C10955}">
+    <dataValidation type="list" sqref="M863" xr:uid="{7AF49EEF-C3B0-464D-8ED8-DE17EEF7F4D0}">
       <formula1>=IF(L863&lt;&gt;"",INDIRECT(VLOOKUP(L863,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N863" xr:uid="{5D3343A7-3C0B-46AF-807A-9C368BB28608}">
+    <dataValidation type="list" sqref="N863" xr:uid="{953F4A3F-3C5A-42E8-9818-505A7AC4695D}">
       <formula1>=IF(M863&lt;&gt;"",INDIRECT(VLOOKUP(M863,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M864" xr:uid="{A862280E-C39E-4251-B94D-261495ED3673}">
+    <dataValidation type="list" sqref="M864" xr:uid="{AF0BC518-3F0D-4A5A-AE87-1736E76D8C19}">
       <formula1>=IF(L864&lt;&gt;"",INDIRECT(VLOOKUP(L864,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N864" xr:uid="{4987D715-A584-4DC8-83EF-4435EF12063C}">
+    <dataValidation type="list" sqref="N864" xr:uid="{1DE2E766-431E-46F0-8297-9815B6D4492D}">
       <formula1>=IF(M864&lt;&gt;"",INDIRECT(VLOOKUP(M864,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M865" xr:uid="{28F8A8CD-7738-4BCD-8256-F205E2EC1B2F}">
+    <dataValidation type="list" sqref="M865" xr:uid="{25154E5C-AA3F-4570-955C-0B034CA1A299}">
       <formula1>=IF(L865&lt;&gt;"",INDIRECT(VLOOKUP(L865,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N865" xr:uid="{C8CF722A-363B-4B02-ADB4-A9580683390B}">
+    <dataValidation type="list" sqref="N865" xr:uid="{8F7EA09D-3802-4E76-83F3-4B4D2B042993}">
       <formula1>=IF(M865&lt;&gt;"",INDIRECT(VLOOKUP(M865,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M866" xr:uid="{D8E0EF74-58C0-405B-BA00-DEA9594B0B08}">
+    <dataValidation type="list" sqref="M866" xr:uid="{AEDA9C2C-F1E1-496F-94D6-46CB24DD5FF3}">
       <formula1>=IF(L866&lt;&gt;"",INDIRECT(VLOOKUP(L866,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N866" xr:uid="{21FE8C50-2779-4816-B374-854655CAE0F1}">
+    <dataValidation type="list" sqref="N866" xr:uid="{38D404DC-5AF2-44D0-934C-8BB77A82F4CB}">
       <formula1>=IF(M866&lt;&gt;"",INDIRECT(VLOOKUP(M866,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M867" xr:uid="{8AC418D7-2C4F-409E-99E0-65D475CD53CF}">
+    <dataValidation type="list" sqref="M867" xr:uid="{AFB05736-1817-4339-B278-828878225EB7}">
       <formula1>=IF(L867&lt;&gt;"",INDIRECT(VLOOKUP(L867,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N867" xr:uid="{E92B19F5-47F0-473E-BA24-124FB7C568E4}">
+    <dataValidation type="list" sqref="N867" xr:uid="{4A87548E-108D-43A8-9346-6724FAD19A31}">
       <formula1>=IF(M867&lt;&gt;"",INDIRECT(VLOOKUP(M867,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M868" xr:uid="{C0CAD5B2-BF3D-4262-BCE9-04088DFC5654}">
+    <dataValidation type="list" sqref="M868" xr:uid="{3318F5FB-35C1-4B35-89BF-3BB12D78E17D}">
       <formula1>=IF(L868&lt;&gt;"",INDIRECT(VLOOKUP(L868,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N868" xr:uid="{48363458-A358-446C-BCFE-A899FAB960E4}">
+    <dataValidation type="list" sqref="N868" xr:uid="{C2DD41D1-5188-48DC-ADD7-2B3C4D8A9592}">
       <formula1>=IF(M868&lt;&gt;"",INDIRECT(VLOOKUP(M868,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M869" xr:uid="{B15487C5-EF50-4F27-9092-F85CCD5BBCB6}">
+    <dataValidation type="list" sqref="M869" xr:uid="{479FD960-EDBF-46C2-972A-F4E8FF82DDBB}">
       <formula1>=IF(L869&lt;&gt;"",INDIRECT(VLOOKUP(L869,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N869" xr:uid="{43117056-33AB-40C0-BBD2-6FF80F07F55C}">
+    <dataValidation type="list" sqref="N869" xr:uid="{A600AE9B-857D-4364-B582-A79BCE0FADB6}">
       <formula1>=IF(M869&lt;&gt;"",INDIRECT(VLOOKUP(M869,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M870" xr:uid="{561F7065-E235-4DAC-AB4C-0587AE2BE991}">
+    <dataValidation type="list" sqref="M870" xr:uid="{B23F76BE-B108-4582-98BE-9A2795F11984}">
       <formula1>=IF(L870&lt;&gt;"",INDIRECT(VLOOKUP(L870,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N870" xr:uid="{6F13577B-7DB6-4375-A1CE-77E795331131}">
+    <dataValidation type="list" sqref="N870" xr:uid="{F485320F-84F4-4AA0-9C5E-8F3A2DA4ECAC}">
       <formula1>=IF(M870&lt;&gt;"",INDIRECT(VLOOKUP(M870,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M871" xr:uid="{BA4E2E7E-072D-465A-AA82-D3D51CE6A742}">
+    <dataValidation type="list" sqref="M871" xr:uid="{293769AB-0DD7-4A7E-8A8D-9F9653347955}">
       <formula1>=IF(L871&lt;&gt;"",INDIRECT(VLOOKUP(L871,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N871" xr:uid="{9F3A108D-257F-4881-8B1E-16569D819179}">
+    <dataValidation type="list" sqref="N871" xr:uid="{50D7BFFD-CCE3-4A09-9C3E-5E378526A768}">
       <formula1>=IF(M871&lt;&gt;"",INDIRECT(VLOOKUP(M871,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M872" xr:uid="{3C607D5A-D2C9-4A9E-9342-7689C1B2EE2F}">
+    <dataValidation type="list" sqref="M872" xr:uid="{7225C826-FB14-4598-BBF6-C7F0964991FB}">
       <formula1>=IF(L872&lt;&gt;"",INDIRECT(VLOOKUP(L872,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N872" xr:uid="{9684401B-8B47-4F32-A096-9740E9DC06F5}">
+    <dataValidation type="list" sqref="N872" xr:uid="{8FF2D297-08D0-46D4-95E5-849DC70A07BF}">
       <formula1>=IF(M872&lt;&gt;"",INDIRECT(VLOOKUP(M872,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M873" xr:uid="{EC990234-0537-41A7-92B5-0066B78F297E}">
+    <dataValidation type="list" sqref="M873" xr:uid="{67547470-A3CA-4607-BFB3-60A06A5193DA}">
       <formula1>=IF(L873&lt;&gt;"",INDIRECT(VLOOKUP(L873,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N873" xr:uid="{4D372029-D8C2-4F3B-BB65-7BABA1931930}">
+    <dataValidation type="list" sqref="N873" xr:uid="{C3607811-6493-4396-BFCC-55B1C0B765D0}">
       <formula1>=IF(M873&lt;&gt;"",INDIRECT(VLOOKUP(M873,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M874" xr:uid="{C7A2AD61-8697-4D4E-805A-11E7AD499082}">
+    <dataValidation type="list" sqref="M874" xr:uid="{C11E6048-3544-47FE-95C2-4D59810058AC}">
       <formula1>=IF(L874&lt;&gt;"",INDIRECT(VLOOKUP(L874,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N874" xr:uid="{0D81A981-4CF9-434C-8A47-242795445260}">
+    <dataValidation type="list" sqref="N874" xr:uid="{F0F4A9CF-4EF9-4324-BAC0-0212357CEB1C}">
       <formula1>=IF(M874&lt;&gt;"",INDIRECT(VLOOKUP(M874,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M875" xr:uid="{E878953B-5EE6-4DB0-BAAA-AA05206CEE54}">
+    <dataValidation type="list" sqref="M875" xr:uid="{FD39A1B6-BA86-4666-8563-30D874E718D5}">
       <formula1>=IF(L875&lt;&gt;"",INDIRECT(VLOOKUP(L875,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N875" xr:uid="{18FB335A-BED5-47E2-AB8C-EABE6B5DE086}">
+    <dataValidation type="list" sqref="N875" xr:uid="{B81CC9BD-F32C-482B-A5C2-7220BB1DD411}">
       <formula1>=IF(M875&lt;&gt;"",INDIRECT(VLOOKUP(M875,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M876" xr:uid="{A878A14C-817C-4E47-8556-2D89BFC91C33}">
+    <dataValidation type="list" sqref="M876" xr:uid="{D9590C04-63AB-491D-B239-14611ADED75A}">
       <formula1>=IF(L876&lt;&gt;"",INDIRECT(VLOOKUP(L876,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N876" xr:uid="{C692B639-7171-4079-854F-7AE897A6E1C1}">
+    <dataValidation type="list" sqref="N876" xr:uid="{6F042B57-EE72-4548-ABE1-296E2F8C6233}">
       <formula1>=IF(M876&lt;&gt;"",INDIRECT(VLOOKUP(M876,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M877" xr:uid="{108DF8E2-507F-4B65-9E8D-B5CCE60A32C0}">
+    <dataValidation type="list" sqref="M877" xr:uid="{E6DB0678-A0A3-4BF8-A35B-A5DA38C11AB1}">
       <formula1>=IF(L877&lt;&gt;"",INDIRECT(VLOOKUP(L877,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N877" xr:uid="{247EEE17-7F49-483A-8690-378A28EA555B}">
+    <dataValidation type="list" sqref="N877" xr:uid="{CB46E3C7-F366-46FD-B595-15B38456325D}">
       <formula1>=IF(M877&lt;&gt;"",INDIRECT(VLOOKUP(M877,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M878" xr:uid="{66C43174-E25A-49A9-87C7-E27339332573}">
+    <dataValidation type="list" sqref="M878" xr:uid="{7E811D29-7376-4143-838E-72F54FAAD769}">
       <formula1>=IF(L878&lt;&gt;"",INDIRECT(VLOOKUP(L878,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N878" xr:uid="{AB43E51A-1382-435D-B4CE-B5F7A31A6C65}">
+    <dataValidation type="list" sqref="N878" xr:uid="{B0700538-89F8-40BC-954D-AD7E878FE73F}">
       <formula1>=IF(M878&lt;&gt;"",INDIRECT(VLOOKUP(M878,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M879" xr:uid="{844BE130-A8DE-49DE-A588-0A4A631BD383}">
+    <dataValidation type="list" sqref="M879" xr:uid="{ED63755A-03A0-4AE5-984C-B500404FE9D8}">
       <formula1>=IF(L879&lt;&gt;"",INDIRECT(VLOOKUP(L879,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N879" xr:uid="{2C6448FA-774C-4E10-8BE6-35E2D47C0269}">
+    <dataValidation type="list" sqref="N879" xr:uid="{6A7E1BA1-17C4-4098-815B-45BAA06116F2}">
       <formula1>=IF(M879&lt;&gt;"",INDIRECT(VLOOKUP(M879,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M880" xr:uid="{5A42F5F7-4709-478F-AFD5-4DBA42E6123A}">
+    <dataValidation type="list" sqref="M880" xr:uid="{5F67AE91-5F27-4EE6-820E-DA79B6C59D29}">
       <formula1>=IF(L880&lt;&gt;"",INDIRECT(VLOOKUP(L880,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N880" xr:uid="{2CCA60D3-6029-496E-8839-584027302DE0}">
+    <dataValidation type="list" sqref="N880" xr:uid="{486C3EE3-6D37-4B09-9974-E38945A81704}">
       <formula1>=IF(M880&lt;&gt;"",INDIRECT(VLOOKUP(M880,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M881" xr:uid="{3AE7FB6E-BFFA-4DC9-8FEA-E9676C6A14C9}">
+    <dataValidation type="list" sqref="M881" xr:uid="{3F21B6CA-33C2-4177-9C56-9CEAA7B64007}">
       <formula1>=IF(L881&lt;&gt;"",INDIRECT(VLOOKUP(L881,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N881" xr:uid="{6186C8E9-9953-47CA-B95A-A99208553BAB}">
+    <dataValidation type="list" sqref="N881" xr:uid="{469EA9A4-1471-4F3A-BD95-9DA1923286E0}">
       <formula1>=IF(M881&lt;&gt;"",INDIRECT(VLOOKUP(M881,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M882" xr:uid="{B5D15B4F-6792-44A5-92A7-3F5C3846CB5D}">
+    <dataValidation type="list" sqref="M882" xr:uid="{43CE6EE8-D6EC-495C-BCC1-6071CDF0E1AD}">
       <formula1>=IF(L882&lt;&gt;"",INDIRECT(VLOOKUP(L882,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N882" xr:uid="{13B1276B-B27B-4D99-A75A-5953F3B5044C}">
+    <dataValidation type="list" sqref="N882" xr:uid="{B32384A3-41F3-4D09-B33B-B46D1494D073}">
       <formula1>=IF(M882&lt;&gt;"",INDIRECT(VLOOKUP(M882,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M883" xr:uid="{E6CE35D9-B762-4D61-9234-E0E432F7AED3}">
+    <dataValidation type="list" sqref="M883" xr:uid="{61F24B25-7428-4A70-B4B0-2F58508ED2F8}">
       <formula1>=IF(L883&lt;&gt;"",INDIRECT(VLOOKUP(L883,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N883" xr:uid="{192779A4-14F1-4F87-AC3D-E5C64A96AC56}">
+    <dataValidation type="list" sqref="N883" xr:uid="{D3AA8831-9C8E-4468-A446-603A3FB41113}">
       <formula1>=IF(M883&lt;&gt;"",INDIRECT(VLOOKUP(M883,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M884" xr:uid="{DFC8FAC8-2AAA-4143-9A68-C386D5071D2A}">
+    <dataValidation type="list" sqref="M884" xr:uid="{C9C3FAE5-EBF4-4757-882B-189A748254F6}">
       <formula1>=IF(L884&lt;&gt;"",INDIRECT(VLOOKUP(L884,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N884" xr:uid="{C85C686C-5072-4FD0-8BDA-E6083A37808F}">
+    <dataValidation type="list" sqref="N884" xr:uid="{25332080-81CB-497A-8683-FA5230D775E8}">
       <formula1>=IF(M884&lt;&gt;"",INDIRECT(VLOOKUP(M884,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M885" xr:uid="{CDEEE7AE-176A-43DA-9B09-8B66BBEB1B58}">
+    <dataValidation type="list" sqref="M885" xr:uid="{D96138EF-FE21-489F-BACC-BB8209B569D4}">
       <formula1>=IF(L885&lt;&gt;"",INDIRECT(VLOOKUP(L885,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N885" xr:uid="{3E343F07-4DDF-4104-8E53-CD4760B56A5B}">
+    <dataValidation type="list" sqref="N885" xr:uid="{530BF5F4-E6C1-4AB4-860C-3BD9718EB6FE}">
       <formula1>=IF(M885&lt;&gt;"",INDIRECT(VLOOKUP(M885,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M886" xr:uid="{FD18FB75-7054-46DD-859E-4ED0A597BCE9}">
+    <dataValidation type="list" sqref="M886" xr:uid="{D4D4AFFA-213E-41D0-840F-0B34334CDEA7}">
       <formula1>=IF(L886&lt;&gt;"",INDIRECT(VLOOKUP(L886,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N886" xr:uid="{F0C06155-4E9F-4810-A5ED-8A606C115F24}">
+    <dataValidation type="list" sqref="N886" xr:uid="{3A45FA3B-BC00-454C-BBF8-B7187F726B9D}">
       <formula1>=IF(M886&lt;&gt;"",INDIRECT(VLOOKUP(M886,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M887" xr:uid="{8820DCDA-D960-4DAE-B36D-D32808362189}">
+    <dataValidation type="list" sqref="M887" xr:uid="{99CF43A2-2416-4A7F-B158-036850D3AF2C}">
       <formula1>=IF(L887&lt;&gt;"",INDIRECT(VLOOKUP(L887,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N887" xr:uid="{044C1492-628D-468D-AEDE-344619D3975E}">
+    <dataValidation type="list" sqref="N887" xr:uid="{1E55432A-83A4-48F8-AC60-02731F2636ED}">
       <formula1>=IF(M887&lt;&gt;"",INDIRECT(VLOOKUP(M887,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M888" xr:uid="{5F0F0178-BE9A-4EF0-9009-CD31CCE02BF4}">
+    <dataValidation type="list" sqref="M888" xr:uid="{EE218ECE-1C1A-4376-BB97-4EB9DE6207DA}">
       <formula1>=IF(L888&lt;&gt;"",INDIRECT(VLOOKUP(L888,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N888" xr:uid="{F51EA604-9B2B-4644-A08F-2C448F246B6D}">
+    <dataValidation type="list" sqref="N888" xr:uid="{77EDECAB-3C89-4659-AEC9-BF9DA8DA2435}">
       <formula1>=IF(M888&lt;&gt;"",INDIRECT(VLOOKUP(M888,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M889" xr:uid="{1AB948C9-0EFF-4FE0-B20D-076AFC027B5C}">
+    <dataValidation type="list" sqref="M889" xr:uid="{5DA0CD52-3E05-4808-82B7-2EEEEA8AC08A}">
       <formula1>=IF(L889&lt;&gt;"",INDIRECT(VLOOKUP(L889,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N889" xr:uid="{F3481E02-5590-4F64-BC11-06E2C6C3D71D}">
+    <dataValidation type="list" sqref="N889" xr:uid="{0C307255-42C9-4AFD-9C62-7BB4334ECE71}">
       <formula1>=IF(M889&lt;&gt;"",INDIRECT(VLOOKUP(M889,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M890" xr:uid="{876D4034-2141-4FEF-8BA4-B059AFCCE8ED}">
+    <dataValidation type="list" sqref="M890" xr:uid="{1132C053-A551-42AD-9619-E4AE7B2A4066}">
       <formula1>=IF(L890&lt;&gt;"",INDIRECT(VLOOKUP(L890,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N890" xr:uid="{6EEC271C-1728-4C0E-97AE-94CD47C39763}">
+    <dataValidation type="list" sqref="N890" xr:uid="{B0788873-94BC-4E92-9DBC-039846BCDDAC}">
       <formula1>=IF(M890&lt;&gt;"",INDIRECT(VLOOKUP(M890,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M891" xr:uid="{4764E021-236F-496E-859A-B1B178BA7E33}">
+    <dataValidation type="list" sqref="M891" xr:uid="{42B71728-D97B-47B8-9DE7-6597971B2159}">
       <formula1>=IF(L891&lt;&gt;"",INDIRECT(VLOOKUP(L891,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N891" xr:uid="{A39E45FB-5796-4EFE-BC70-DF5A0CECFC7E}">
+    <dataValidation type="list" sqref="N891" xr:uid="{9F67E270-860B-4797-BC54-2F85F0B29A1D}">
       <formula1>=IF(M891&lt;&gt;"",INDIRECT(VLOOKUP(M891,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M892" xr:uid="{1CF5BBA7-D637-41B7-A318-D5D3193EE1E0}">
+    <dataValidation type="list" sqref="M892" xr:uid="{73E94712-5483-4F9B-8071-003F9E134689}">
       <formula1>=IF(L892&lt;&gt;"",INDIRECT(VLOOKUP(L892,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N892" xr:uid="{B4824E9B-BD51-4C9B-9E5D-083D540664A0}">
+    <dataValidation type="list" sqref="N892" xr:uid="{E959C37F-1D0C-4C79-B219-6F1296C90B4F}">
       <formula1>=IF(M892&lt;&gt;"",INDIRECT(VLOOKUP(M892,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M893" xr:uid="{99F3C92F-CEAF-46A8-AC87-98B74C72277B}">
+    <dataValidation type="list" sqref="M893" xr:uid="{D08E9193-9FBA-47DA-A08F-17696D624D76}">
       <formula1>=IF(L893&lt;&gt;"",INDIRECT(VLOOKUP(L893,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N893" xr:uid="{D129AABC-3030-49B1-A657-307C84F8F450}">
+    <dataValidation type="list" sqref="N893" xr:uid="{525E8E8D-EBC6-4F93-BE27-C6097E4A888E}">
       <formula1>=IF(M893&lt;&gt;"",INDIRECT(VLOOKUP(M893,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M894" xr:uid="{45506EFF-4BE4-4260-A6D6-C7613E81F043}">
+    <dataValidation type="list" sqref="M894" xr:uid="{876621B3-0960-48B3-B2E4-4E35120F8563}">
       <formula1>=IF(L894&lt;&gt;"",INDIRECT(VLOOKUP(L894,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N894" xr:uid="{330DA9D3-889D-422B-9D4E-3E832C179C1C}">
+    <dataValidation type="list" sqref="N894" xr:uid="{A38D4EF4-21C3-415F-AF2B-CDB837022C05}">
       <formula1>=IF(M894&lt;&gt;"",INDIRECT(VLOOKUP(M894,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M895" xr:uid="{77F788E9-37B7-41FE-92E8-E26CFEAB7012}">
+    <dataValidation type="list" sqref="M895" xr:uid="{3B55933D-1D6D-408D-A613-359F34CCAD64}">
       <formula1>=IF(L895&lt;&gt;"",INDIRECT(VLOOKUP(L895,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N895" xr:uid="{FB259A32-7851-4E99-B05E-3557A6958B45}">
+    <dataValidation type="list" sqref="N895" xr:uid="{668D4998-AB16-4A90-8C02-91D2852A7A15}">
       <formula1>=IF(M895&lt;&gt;"",INDIRECT(VLOOKUP(M895,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M896" xr:uid="{70651011-FF6A-4B20-9ACF-8D68A1AD7218}">
+    <dataValidation type="list" sqref="M896" xr:uid="{B813E1AE-F14D-4720-B71C-5BE219379B49}">
       <formula1>=IF(L896&lt;&gt;"",INDIRECT(VLOOKUP(L896,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N896" xr:uid="{7D68684B-0814-4324-9336-ABA6057C6776}">
+    <dataValidation type="list" sqref="N896" xr:uid="{8508226E-C529-41B7-A19B-1775C9B4D23A}">
       <formula1>=IF(M896&lt;&gt;"",INDIRECT(VLOOKUP(M896,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M897" xr:uid="{5AC94B66-1EC4-439B-97B6-07798CC09CB9}">
+    <dataValidation type="list" sqref="M897" xr:uid="{597ABF31-65D0-4F42-84E0-7A3C3CF6359D}">
       <formula1>=IF(L897&lt;&gt;"",INDIRECT(VLOOKUP(L897,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N897" xr:uid="{C2443B53-8FCE-47F4-BB60-360891BC22E0}">
+    <dataValidation type="list" sqref="N897" xr:uid="{14A2D422-0346-4676-85BD-9DA955DF5847}">
       <formula1>=IF(M897&lt;&gt;"",INDIRECT(VLOOKUP(M897,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M898" xr:uid="{DFF165C9-A81D-4CB6-B4E8-46A1A855DC99}">
+    <dataValidation type="list" sqref="M898" xr:uid="{56085686-1368-4909-B534-4EFEA8B109A4}">
       <formula1>=IF(L898&lt;&gt;"",INDIRECT(VLOOKUP(L898,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N898" xr:uid="{41E7B6A6-D078-4D8C-9A57-9308BB02F64A}">
+    <dataValidation type="list" sqref="N898" xr:uid="{13BB0E9E-4531-45C5-B28D-3681ABB2528E}">
       <formula1>=IF(M898&lt;&gt;"",INDIRECT(VLOOKUP(M898,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M899" xr:uid="{95713859-1729-40DC-A496-6B98F741E7BA}">
+    <dataValidation type="list" sqref="M899" xr:uid="{9E117B61-55EB-4F5C-9FA4-B943328688D7}">
       <formula1>=IF(L899&lt;&gt;"",INDIRECT(VLOOKUP(L899,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N899" xr:uid="{2147967C-91EC-4B38-B59A-E7727154DF00}">
+    <dataValidation type="list" sqref="N899" xr:uid="{BB5D6657-BC28-486E-8086-429197AC2FEB}">
       <formula1>=IF(M899&lt;&gt;"",INDIRECT(VLOOKUP(M899,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M900" xr:uid="{0053AE4B-C114-4947-B69D-F8F27DA05354}">
+    <dataValidation type="list" sqref="M900" xr:uid="{6163AF6F-CEDD-46D5-999A-6E48C153666E}">
       <formula1>=IF(L900&lt;&gt;"",INDIRECT(VLOOKUP(L900,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N900" xr:uid="{DB6001DB-1F79-4F4E-8F3C-E7BA78CAF9A9}">
+    <dataValidation type="list" sqref="N900" xr:uid="{3661C0FA-6FEB-402A-8F94-E0B9526E7815}">
       <formula1>=IF(M900&lt;&gt;"",INDIRECT(VLOOKUP(M900,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M901" xr:uid="{76DD081D-67E0-4952-A3D0-DC2179661F36}">
+    <dataValidation type="list" sqref="M901" xr:uid="{93E266E2-C8F1-4DEF-89D0-7B0F9F8DCE64}">
       <formula1>=IF(L901&lt;&gt;"",INDIRECT(VLOOKUP(L901,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N901" xr:uid="{2E2DDC01-C6C6-432B-B1C4-3A58DB3CDA8F}">
+    <dataValidation type="list" sqref="N901" xr:uid="{1D591578-0D08-4FC8-9945-6B40AD4330C6}">
       <formula1>=IF(M901&lt;&gt;"",INDIRECT(VLOOKUP(M901,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M902" xr:uid="{BD36A3FF-F567-4E6B-BE08-5F7A4A7EA11F}">
+    <dataValidation type="list" sqref="M902" xr:uid="{7EFA35AC-5A15-4831-A76A-59FAC39557D2}">
       <formula1>=IF(L902&lt;&gt;"",INDIRECT(VLOOKUP(L902,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N902" xr:uid="{9B9BC6FE-71FB-41DA-91FF-A6BBCD3A371C}">
+    <dataValidation type="list" sqref="N902" xr:uid="{09DB1A00-F8B4-471A-85D0-9FC87938EB46}">
       <formula1>=IF(M902&lt;&gt;"",INDIRECT(VLOOKUP(M902,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M903" xr:uid="{8F6E42CC-33D6-4497-BA5B-5AD504700383}">
+    <dataValidation type="list" sqref="M903" xr:uid="{F15CECBF-83D3-48DE-A8C0-8604DC3A1AC9}">
       <formula1>=IF(L903&lt;&gt;"",INDIRECT(VLOOKUP(L903,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N903" xr:uid="{8E404BDF-0477-441C-BE53-31D71BF5805E}">
+    <dataValidation type="list" sqref="N903" xr:uid="{EADFDC6A-D878-4E61-AD50-46075AC85E1E}">
       <formula1>=IF(M903&lt;&gt;"",INDIRECT(VLOOKUP(M903,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M904" xr:uid="{27705E3A-32EB-45FD-A21B-E0006BA83ACB}">
+    <dataValidation type="list" sqref="M904" xr:uid="{6781F0AA-7E7F-44E5-9ACF-B810311C651B}">
       <formula1>=IF(L904&lt;&gt;"",INDIRECT(VLOOKUP(L904,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N904" xr:uid="{0F64DEFB-372F-41B5-AE42-B949566F83EF}">
+    <dataValidation type="list" sqref="N904" xr:uid="{7722AC72-3288-4C19-8CA3-71EAD6DB87AD}">
       <formula1>=IF(M904&lt;&gt;"",INDIRECT(VLOOKUP(M904,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M905" xr:uid="{9BB8116F-B116-4BF2-B876-62964492CF24}">
+    <dataValidation type="list" sqref="M905" xr:uid="{D87EDA6C-9DBF-4D99-ADDA-6E8B559D9089}">
       <formula1>=IF(L905&lt;&gt;"",INDIRECT(VLOOKUP(L905,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N905" xr:uid="{665D80AE-9C69-4C11-BAAE-5CAF2B1AC64F}">
+    <dataValidation type="list" sqref="N905" xr:uid="{59353D5A-26F8-45E6-AC77-6A8C5F3F637C}">
       <formula1>=IF(M905&lt;&gt;"",INDIRECT(VLOOKUP(M905,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M906" xr:uid="{8F7B4071-8F5B-4CA1-83F9-4F0DE5DAF718}">
+    <dataValidation type="list" sqref="M906" xr:uid="{769E1D3C-7D66-4C50-8B82-F8BE55E7A2CF}">
       <formula1>=IF(L906&lt;&gt;"",INDIRECT(VLOOKUP(L906,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N906" xr:uid="{CE933A83-9F87-43FD-A3AA-C6EF4CA8EDB5}">
+    <dataValidation type="list" sqref="N906" xr:uid="{7AA8265E-19FA-4BE7-9E14-A3E9279333AF}">
       <formula1>=IF(M906&lt;&gt;"",INDIRECT(VLOOKUP(M906,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M907" xr:uid="{BCB35366-0073-4268-A511-2B69302D3DA3}">
+    <dataValidation type="list" sqref="M907" xr:uid="{E86636F4-B022-41EB-925A-0A7F73C51C80}">
       <formula1>=IF(L907&lt;&gt;"",INDIRECT(VLOOKUP(L907,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N907" xr:uid="{378AF3D5-8C46-446D-AA4E-C594088E80BF}">
+    <dataValidation type="list" sqref="N907" xr:uid="{1C9360A4-904C-481F-BF54-711967F2E957}">
       <formula1>=IF(M907&lt;&gt;"",INDIRECT(VLOOKUP(M907,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M908" xr:uid="{899D805C-9FEC-4600-938F-64B7F6FA29C8}">
+    <dataValidation type="list" sqref="M908" xr:uid="{6D683C2B-C6C6-4DC6-80AF-0C788081ADC2}">
       <formula1>=IF(L908&lt;&gt;"",INDIRECT(VLOOKUP(L908,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N908" xr:uid="{45361EBC-08E8-4E62-BE08-BE4667879403}">
+    <dataValidation type="list" sqref="N908" xr:uid="{D0B1ECEF-E831-444D-9332-2AC3A4F63F4B}">
       <formula1>=IF(M908&lt;&gt;"",INDIRECT(VLOOKUP(M908,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M909" xr:uid="{B0EF35F1-943E-4237-9006-2DD5ED534852}">
+    <dataValidation type="list" sqref="M909" xr:uid="{B101CCD7-1B38-404F-BF44-402A688FA639}">
       <formula1>=IF(L909&lt;&gt;"",INDIRECT(VLOOKUP(L909,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N909" xr:uid="{C2E95A16-0D10-43E1-AAF9-58B8078401F4}">
+    <dataValidation type="list" sqref="N909" xr:uid="{0A5079AF-37BB-4881-8EF1-06A9EDD4476C}">
       <formula1>=IF(M909&lt;&gt;"",INDIRECT(VLOOKUP(M909,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M910" xr:uid="{D57AC5CE-A9F4-4FBC-8EB6-BDD13DBEA580}">
+    <dataValidation type="list" sqref="M910" xr:uid="{376EA182-63CE-4669-9E22-01A2E9D35009}">
       <formula1>=IF(L910&lt;&gt;"",INDIRECT(VLOOKUP(L910,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N910" xr:uid="{9C18BA57-CB58-4F6D-8BA2-DCA0FFDD9E98}">
+    <dataValidation type="list" sqref="N910" xr:uid="{685E47CD-F83C-4D7A-A18A-3A846ED8AD8D}">
       <formula1>=IF(M910&lt;&gt;"",INDIRECT(VLOOKUP(M910,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M911" xr:uid="{5A0B8C7A-2ADE-4D68-AE4C-7D8EDD9CAA5B}">
+    <dataValidation type="list" sqref="M911" xr:uid="{93F2533F-8322-4E31-A75E-4F9EA7E7DB0A}">
       <formula1>=IF(L911&lt;&gt;"",INDIRECT(VLOOKUP(L911,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N911" xr:uid="{2252FB60-9F6A-4827-AF34-361FA9DABB74}">
+    <dataValidation type="list" sqref="N911" xr:uid="{36AD8A52-1BCC-48C7-8E82-6719E6EF2C29}">
       <formula1>=IF(M911&lt;&gt;"",INDIRECT(VLOOKUP(M911,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M912" xr:uid="{C97784E5-11F1-4C06-BF82-986427813D45}">
+    <dataValidation type="list" sqref="M912" xr:uid="{77874881-16F8-44C6-AB7C-DDE4E1F3A04D}">
       <formula1>=IF(L912&lt;&gt;"",INDIRECT(VLOOKUP(L912,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N912" xr:uid="{2948B493-3BD1-4F44-B5F8-63463AB76723}">
+    <dataValidation type="list" sqref="N912" xr:uid="{20D7DA69-5C25-49BD-A746-CC94BFD45D11}">
       <formula1>=IF(M912&lt;&gt;"",INDIRECT(VLOOKUP(M912,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M913" xr:uid="{589190CA-1EA8-44FB-8BF6-F30555F8A7D5}">
+    <dataValidation type="list" sqref="M913" xr:uid="{BE05ADA2-AB84-46D2-97DC-6D2E49CA3763}">
       <formula1>=IF(L913&lt;&gt;"",INDIRECT(VLOOKUP(L913,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N913" xr:uid="{EE89C768-74BC-4255-BC49-06CD808D0015}">
+    <dataValidation type="list" sqref="N913" xr:uid="{509611DC-8EAC-4EBD-B7C8-D9EDC6504B92}">
       <formula1>=IF(M913&lt;&gt;"",INDIRECT(VLOOKUP(M913,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M914" xr:uid="{1A6AF3B4-740B-4A7E-8DD0-35C2CE7B9B40}">
+    <dataValidation type="list" sqref="M914" xr:uid="{8D6DC717-4ADD-4CC0-B7A5-2B8D24B4AED2}">
       <formula1>=IF(L914&lt;&gt;"",INDIRECT(VLOOKUP(L914,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N914" xr:uid="{63CF6B8B-FDB0-467E-8235-51C41F2FF276}">
+    <dataValidation type="list" sqref="N914" xr:uid="{92C5A897-4BB6-4616-906A-C6B2EA1FAB6F}">
       <formula1>=IF(M914&lt;&gt;"",INDIRECT(VLOOKUP(M914,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M915" xr:uid="{3A18E457-3FD5-4717-9546-2DD2CB9C1644}">
+    <dataValidation type="list" sqref="M915" xr:uid="{C15D58C9-7641-41C1-8B5E-C45B9E83E1F6}">
       <formula1>=IF(L915&lt;&gt;"",INDIRECT(VLOOKUP(L915,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N915" xr:uid="{44E4BBC8-C2C5-4DD8-8B35-EA281B495791}">
+    <dataValidation type="list" sqref="N915" xr:uid="{39E2E768-D682-49B1-89ED-64B6E3BA28C7}">
       <formula1>=IF(M915&lt;&gt;"",INDIRECT(VLOOKUP(M915,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M916" xr:uid="{48316DB1-A9BC-4341-95F4-8DA4442E8AC3}">
+    <dataValidation type="list" sqref="M916" xr:uid="{F5B91F95-AEC7-475E-956B-09671F5C5310}">
       <formula1>=IF(L916&lt;&gt;"",INDIRECT(VLOOKUP(L916,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N916" xr:uid="{B7A0AF08-5D84-4AD4-B117-04F04687BCD1}">
+    <dataValidation type="list" sqref="N916" xr:uid="{B42DE1E3-17B1-42BA-8A89-D0EF1A58090B}">
       <formula1>=IF(M916&lt;&gt;"",INDIRECT(VLOOKUP(M916,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M917" xr:uid="{31DB4782-B253-4A54-8B5C-D39AEA5BC3A7}">
+    <dataValidation type="list" sqref="M917" xr:uid="{041B0ADC-AD92-45AC-A2A4-D175FBD5E523}">
       <formula1>=IF(L917&lt;&gt;"",INDIRECT(VLOOKUP(L917,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N917" xr:uid="{18BC6B97-5AD4-4FCF-A70E-559E54F8D802}">
+    <dataValidation type="list" sqref="N917" xr:uid="{FD639982-7C91-4760-A3D0-C03272D46A31}">
       <formula1>=IF(M917&lt;&gt;"",INDIRECT(VLOOKUP(M917,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M918" xr:uid="{210C727D-3472-4E4C-85C9-8F5AD57531F6}">
+    <dataValidation type="list" sqref="M918" xr:uid="{111524AA-21B2-4797-BC64-C73797489548}">
       <formula1>=IF(L918&lt;&gt;"",INDIRECT(VLOOKUP(L918,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N918" xr:uid="{2CB70F28-4F9C-4076-AB10-D78E0DB121CA}">
+    <dataValidation type="list" sqref="N918" xr:uid="{4A9B28E5-6843-4895-B6D7-90D5D215C46F}">
       <formula1>=IF(M918&lt;&gt;"",INDIRECT(VLOOKUP(M918,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M919" xr:uid="{24BE79C4-E376-4475-BF33-03D0A53A5ED7}">
+    <dataValidation type="list" sqref="M919" xr:uid="{B46A76E9-02B6-487A-B1D9-D25676BB899A}">
       <formula1>=IF(L919&lt;&gt;"",INDIRECT(VLOOKUP(L919,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N919" xr:uid="{81610C75-8E54-4870-8F7F-D23C88BE9A9D}">
+    <dataValidation type="list" sqref="N919" xr:uid="{7F616384-B26B-4398-9700-B8E0E0B1BB77}">
       <formula1>=IF(M919&lt;&gt;"",INDIRECT(VLOOKUP(M919,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M920" xr:uid="{790A4DD0-9913-42CC-A473-C1C3A38184C5}">
+    <dataValidation type="list" sqref="M920" xr:uid="{B1ADC793-C9F4-41F9-B4BD-97F34453B560}">
       <formula1>=IF(L920&lt;&gt;"",INDIRECT(VLOOKUP(L920,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N920" xr:uid="{81D83FD0-0880-4943-BA33-B1A4EB66896D}">
+    <dataValidation type="list" sqref="N920" xr:uid="{A2FCDE19-E548-480F-84AB-91186548BC92}">
       <formula1>=IF(M920&lt;&gt;"",INDIRECT(VLOOKUP(M920,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M921" xr:uid="{8B164276-A643-4AB0-B8F9-0EFB9259B084}">
+    <dataValidation type="list" sqref="M921" xr:uid="{9ED2DECF-D904-4541-AD56-00F925F78DD3}">
       <formula1>=IF(L921&lt;&gt;"",INDIRECT(VLOOKUP(L921,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N921" xr:uid="{F0A9D8C7-BCB7-4077-8F97-328039B99C5E}">
+    <dataValidation type="list" sqref="N921" xr:uid="{20A42FFD-82F6-4CBE-B81B-724EBF9FBCBA}">
       <formula1>=IF(M921&lt;&gt;"",INDIRECT(VLOOKUP(M921,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M922" xr:uid="{626E0DAC-EAA5-42BF-BD8B-50350B4B7993}">
+    <dataValidation type="list" sqref="M922" xr:uid="{68F0C8D2-8D97-457B-9001-AA3EF9173BBA}">
       <formula1>=IF(L922&lt;&gt;"",INDIRECT(VLOOKUP(L922,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N922" xr:uid="{AE00B57F-C8B3-4853-96F7-A1B27E6DCE0F}">
+    <dataValidation type="list" sqref="N922" xr:uid="{042B5DE7-7CAA-4116-9708-0635F9CF5627}">
       <formula1>=IF(M922&lt;&gt;"",INDIRECT(VLOOKUP(M922,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M923" xr:uid="{784DDEE2-165E-456D-BF76-BC6269DEFF29}">
+    <dataValidation type="list" sqref="M923" xr:uid="{AE12390E-9E7B-4910-B889-CD3CB6AA4796}">
       <formula1>=IF(L923&lt;&gt;"",INDIRECT(VLOOKUP(L923,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N923" xr:uid="{31154190-8FB0-4A52-B1A2-513DA62716C3}">
+    <dataValidation type="list" sqref="N923" xr:uid="{9271DA4F-533C-454D-9668-5C9F8F80CC26}">
       <formula1>=IF(M923&lt;&gt;"",INDIRECT(VLOOKUP(M923,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M924" xr:uid="{B73D6058-D73F-4C22-B540-B3C34A9D679F}">
+    <dataValidation type="list" sqref="M924" xr:uid="{51C1744B-29A7-481E-AB02-5FC982B0773B}">
       <formula1>=IF(L924&lt;&gt;"",INDIRECT(VLOOKUP(L924,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N924" xr:uid="{189AC8FE-4BCF-4167-B2EF-54BC205B416F}">
+    <dataValidation type="list" sqref="N924" xr:uid="{202F9847-0774-4542-AB84-37CE1174D887}">
       <formula1>=IF(M924&lt;&gt;"",INDIRECT(VLOOKUP(M924,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M925" xr:uid="{81E41180-BAA2-4F36-B1B6-E797A93E2C53}">
+    <dataValidation type="list" sqref="M925" xr:uid="{BF569DD1-165B-4B54-AE83-71FBA4BFBD3A}">
       <formula1>=IF(L925&lt;&gt;"",INDIRECT(VLOOKUP(L925,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N925" xr:uid="{2F7BC35B-8CF7-43F4-AF0B-46FEE3F90E8D}">
+    <dataValidation type="list" sqref="N925" xr:uid="{1085F2CD-13A9-4DD3-B80C-B10E9E66FF15}">
       <formula1>=IF(M925&lt;&gt;"",INDIRECT(VLOOKUP(M925,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M926" xr:uid="{EB0E1D27-4E73-44AC-92C7-3C03C694DBE7}">
+    <dataValidation type="list" sqref="M926" xr:uid="{13A58CE0-7499-405F-B96B-404458642DCE}">
       <formula1>=IF(L926&lt;&gt;"",INDIRECT(VLOOKUP(L926,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N926" xr:uid="{BDF88697-E6E5-4A38-B313-0EABA366DAB3}">
+    <dataValidation type="list" sqref="N926" xr:uid="{A606481F-5E5F-4F80-B1FD-9AFD0E9F8451}">
       <formula1>=IF(M926&lt;&gt;"",INDIRECT(VLOOKUP(M926,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M927" xr:uid="{B8E93A21-F7F3-4FDB-879A-FD8AA1F25B32}">
+    <dataValidation type="list" sqref="M927" xr:uid="{B25F87BA-B970-45B6-A8B1-758881BBACC5}">
       <formula1>=IF(L927&lt;&gt;"",INDIRECT(VLOOKUP(L927,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N927" xr:uid="{530A3E3B-0BF6-47CF-9F54-FC87E6610176}">
+    <dataValidation type="list" sqref="N927" xr:uid="{9FBBB87F-B5FA-4525-8EFF-605084D5DF9B}">
       <formula1>=IF(M927&lt;&gt;"",INDIRECT(VLOOKUP(M927,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M928" xr:uid="{8B43E0F2-8767-4D06-873F-B7EEE76194AF}">
+    <dataValidation type="list" sqref="M928" xr:uid="{50138A25-F993-4462-BD40-4286698A948C}">
       <formula1>=IF(L928&lt;&gt;"",INDIRECT(VLOOKUP(L928,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N928" xr:uid="{ADCA3E12-BED8-4DFC-B409-048E18D49D0D}">
+    <dataValidation type="list" sqref="N928" xr:uid="{7C5AC4C5-EF83-402A-8D40-53564B575505}">
       <formula1>=IF(M928&lt;&gt;"",INDIRECT(VLOOKUP(M928,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M929" xr:uid="{124C58EC-5656-4472-BF3F-7834BD4B90BD}">
+    <dataValidation type="list" sqref="M929" xr:uid="{0B2B5588-EF51-4B00-84B0-7EB59B04A606}">
       <formula1>=IF(L929&lt;&gt;"",INDIRECT(VLOOKUP(L929,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N929" xr:uid="{CC026A9C-84DB-4F73-A27C-3F47FB1BD800}">
+    <dataValidation type="list" sqref="N929" xr:uid="{E9001450-928E-42FD-A034-55716216F18F}">
       <formula1>=IF(M929&lt;&gt;"",INDIRECT(VLOOKUP(M929,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M930" xr:uid="{1BDB931E-787A-4C42-9A21-4DD92CF6984C}">
+    <dataValidation type="list" sqref="M930" xr:uid="{2E8B4BC2-301C-4A63-AD9A-443995AD17E4}">
       <formula1>=IF(L930&lt;&gt;"",INDIRECT(VLOOKUP(L930,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N930" xr:uid="{85E5EB10-DB80-404F-9406-D1F461608976}">
+    <dataValidation type="list" sqref="N930" xr:uid="{D2423C0C-DBBB-4F57-A8E3-DF472BBA0067}">
       <formula1>=IF(M930&lt;&gt;"",INDIRECT(VLOOKUP(M930,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M931" xr:uid="{690B85E6-5CBB-4604-A1E8-51F0B6B0FEFE}">
+    <dataValidation type="list" sqref="M931" xr:uid="{1C72F704-2652-4A3B-B389-733F7A7F832D}">
       <formula1>=IF(L931&lt;&gt;"",INDIRECT(VLOOKUP(L931,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N931" xr:uid="{817863CE-ECF1-4C8B-8FF1-DA3EC558D4DF}">
+    <dataValidation type="list" sqref="N931" xr:uid="{2EB37CF3-2AB8-49A2-83BC-B6635EA4882E}">
       <formula1>=IF(M931&lt;&gt;"",INDIRECT(VLOOKUP(M931,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M932" xr:uid="{37BAFBB2-C698-4DBA-817F-EB2C3A713B74}">
+    <dataValidation type="list" sqref="M932" xr:uid="{64C5E7B9-E7E7-4F88-ACC0-2384B7168C7D}">
       <formula1>=IF(L932&lt;&gt;"",INDIRECT(VLOOKUP(L932,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N932" xr:uid="{3B41DE06-EB59-4CE0-ABFD-526873EA53E6}">
+    <dataValidation type="list" sqref="N932" xr:uid="{DBA9E809-5F2E-4838-AF42-F9F28C21BF52}">
       <formula1>=IF(M932&lt;&gt;"",INDIRECT(VLOOKUP(M932,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M933" xr:uid="{76CBAC2E-0498-4187-B8CE-FD6239AE32F4}">
+    <dataValidation type="list" sqref="M933" xr:uid="{243B1810-7DD1-4A46-B7A9-875351401BE1}">
       <formula1>=IF(L933&lt;&gt;"",INDIRECT(VLOOKUP(L933,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N933" xr:uid="{9D8E0FE3-57B0-4D92-A5E0-334C7AE5E36E}">
+    <dataValidation type="list" sqref="N933" xr:uid="{45D77022-633D-4635-99D3-5E9167E65797}">
       <formula1>=IF(M933&lt;&gt;"",INDIRECT(VLOOKUP(M933,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M934" xr:uid="{AF83E273-1067-479C-BCBF-6A00C18C6A6A}">
+    <dataValidation type="list" sqref="M934" xr:uid="{B45AD50A-F9AB-4AEE-BA03-9DF81BD6D470}">
       <formula1>=IF(L934&lt;&gt;"",INDIRECT(VLOOKUP(L934,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N934" xr:uid="{F0A2A5ED-936A-4A04-9414-246D930A98E7}">
+    <dataValidation type="list" sqref="N934" xr:uid="{AF568488-D30D-49C2-8D94-0B72A96B149F}">
       <formula1>=IF(M934&lt;&gt;"",INDIRECT(VLOOKUP(M934,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M935" xr:uid="{446C174F-FE9C-4CB7-A6A4-5220C0628427}">
+    <dataValidation type="list" sqref="M935" xr:uid="{F01B8DF5-31ED-460C-94B6-1FA90C49441B}">
       <formula1>=IF(L935&lt;&gt;"",INDIRECT(VLOOKUP(L935,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N935" xr:uid="{FE5128BB-9D3C-4DD1-9BD6-0E8C401767A3}">
+    <dataValidation type="list" sqref="N935" xr:uid="{89DD1BB7-E106-47F9-BBCB-FE6850845979}">
       <formula1>=IF(M935&lt;&gt;"",INDIRECT(VLOOKUP(M935,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M936" xr:uid="{30CD959C-3EAE-4101-8CDC-EFBC4EC8AE1E}">
+    <dataValidation type="list" sqref="M936" xr:uid="{523371A9-953C-4225-9E5F-900E77C8ED9D}">
       <formula1>=IF(L936&lt;&gt;"",INDIRECT(VLOOKUP(L936,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N936" xr:uid="{83322A02-BEA2-45FD-955F-D77B5D470ED4}">
+    <dataValidation type="list" sqref="N936" xr:uid="{E1385E33-F126-4C45-8C9B-B119FAA2D6EB}">
       <formula1>=IF(M936&lt;&gt;"",INDIRECT(VLOOKUP(M936,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M937" xr:uid="{B572FA98-58FC-4E96-A228-12A36B5AD2FE}">
+    <dataValidation type="list" sqref="M937" xr:uid="{7F322816-0157-4E30-AF4B-9621AA8201AB}">
       <formula1>=IF(L937&lt;&gt;"",INDIRECT(VLOOKUP(L937,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N937" xr:uid="{BD0422A7-2D2D-42D9-93DF-729D8EE6F12B}">
+    <dataValidation type="list" sqref="N937" xr:uid="{925AB1C5-C222-462B-9A0D-BFDE5A852354}">
       <formula1>=IF(M937&lt;&gt;"",INDIRECT(VLOOKUP(M937,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M938" xr:uid="{4041566E-560D-4A40-9372-7783042698FE}">
+    <dataValidation type="list" sqref="M938" xr:uid="{7BFC5607-7410-494D-B567-55231733E3A3}">
       <formula1>=IF(L938&lt;&gt;"",INDIRECT(VLOOKUP(L938,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N938" xr:uid="{12E2A27E-8B51-4367-9918-0F903AA63517}">
+    <dataValidation type="list" sqref="N938" xr:uid="{BFB74CE2-8827-49A5-8D4C-3BB864281CEE}">
       <formula1>=IF(M938&lt;&gt;"",INDIRECT(VLOOKUP(M938,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M939" xr:uid="{27568215-7D50-41F6-A77E-E625FFD94CEC}">
+    <dataValidation type="list" sqref="M939" xr:uid="{F4798468-75AC-4AB0-8932-ABE11DA57E2E}">
       <formula1>=IF(L939&lt;&gt;"",INDIRECT(VLOOKUP(L939,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N939" xr:uid="{BE3C76C9-4455-44DF-8601-D6BB37746B8A}">
+    <dataValidation type="list" sqref="N939" xr:uid="{C019800C-20F3-49DD-BD28-453782DFF7BB}">
       <formula1>=IF(M939&lt;&gt;"",INDIRECT(VLOOKUP(M939,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M940" xr:uid="{2E1CA5E3-9ED0-4D09-92F0-EE0E4BD6215F}">
+    <dataValidation type="list" sqref="M940" xr:uid="{076D6261-A7BD-4859-8783-C1531ECA262B}">
       <formula1>=IF(L940&lt;&gt;"",INDIRECT(VLOOKUP(L940,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N940" xr:uid="{CD39D92E-0196-4D97-BF2F-7003A6551148}">
+    <dataValidation type="list" sqref="N940" xr:uid="{24367682-4C21-48B3-8502-311E3A639771}">
       <formula1>=IF(M940&lt;&gt;"",INDIRECT(VLOOKUP(M940,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M941" xr:uid="{8BAA0568-D2E7-46E3-9EE1-96E66D7BF36E}">
+    <dataValidation type="list" sqref="M941" xr:uid="{3553E142-C1E5-4487-8C5D-7E8B10132DB3}">
       <formula1>=IF(L941&lt;&gt;"",INDIRECT(VLOOKUP(L941,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N941" xr:uid="{40E83B51-0ADB-4D14-8294-01FCBEDFED84}">
+    <dataValidation type="list" sqref="N941" xr:uid="{D1E4C1DC-C787-43E4-B5A7-E3E6EDDF3DAF}">
       <formula1>=IF(M941&lt;&gt;"",INDIRECT(VLOOKUP(M941,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M942" xr:uid="{50D35556-A5CA-48B8-9153-5476BF53B506}">
+    <dataValidation type="list" sqref="M942" xr:uid="{33AC1E54-D5DE-4B59-BC3E-44BEC64BAA49}">
       <formula1>=IF(L942&lt;&gt;"",INDIRECT(VLOOKUP(L942,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N942" xr:uid="{C9A375BB-4BCC-4412-98BE-177A87747D3F}">
+    <dataValidation type="list" sqref="N942" xr:uid="{9D859E55-0C25-447D-BB61-E90EDD59C8D8}">
       <formula1>=IF(M942&lt;&gt;"",INDIRECT(VLOOKUP(M942,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M943" xr:uid="{57D3FADB-13F4-441E-BCA6-FE03486DB55E}">
+    <dataValidation type="list" sqref="M943" xr:uid="{8CB396CC-A68E-47AC-935C-65E256A6CFBC}">
       <formula1>=IF(L943&lt;&gt;"",INDIRECT(VLOOKUP(L943,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N943" xr:uid="{BB687731-B681-432E-B600-73CEBC5E5D1B}">
+    <dataValidation type="list" sqref="N943" xr:uid="{78E8FF38-BF11-4638-8B32-0659DF578F75}">
       <formula1>=IF(M943&lt;&gt;"",INDIRECT(VLOOKUP(M943,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M944" xr:uid="{7A303108-CE4B-42C9-BCBE-4CF148355E36}">
+    <dataValidation type="list" sqref="M944" xr:uid="{1A55CD0C-B2AE-4EA4-9493-C3780058A2D5}">
       <formula1>=IF(L944&lt;&gt;"",INDIRECT(VLOOKUP(L944,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N944" xr:uid="{CD907AD2-376A-42EE-A1CC-BB3A3D33E76E}">
+    <dataValidation type="list" sqref="N944" xr:uid="{EB56E5C6-9270-4D72-B962-9A5B88E10585}">
       <formula1>=IF(M944&lt;&gt;"",INDIRECT(VLOOKUP(M944,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M945" xr:uid="{1D9195E4-4EB5-4B0C-AC93-66C46AA942AA}">
+    <dataValidation type="list" sqref="M945" xr:uid="{61C7F043-0F3E-4069-B735-667805C3D2DD}">
       <formula1>=IF(L945&lt;&gt;"",INDIRECT(VLOOKUP(L945,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N945" xr:uid="{4392A9F2-5776-4B61-B8C1-3C21B2B2857F}">
+    <dataValidation type="list" sqref="N945" xr:uid="{4AB2B212-03FD-4187-884A-279D5226BB98}">
       <formula1>=IF(M945&lt;&gt;"",INDIRECT(VLOOKUP(M945,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M946" xr:uid="{C2CFE75D-5E60-4E4D-87C4-E160E940CF08}">
+    <dataValidation type="list" sqref="M946" xr:uid="{AA96D841-8434-4CAB-A43B-6F85F121588F}">
       <formula1>=IF(L946&lt;&gt;"",INDIRECT(VLOOKUP(L946,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N946" xr:uid="{A1EA3843-160B-4577-A6E9-DCB7278B71A6}">
+    <dataValidation type="list" sqref="N946" xr:uid="{8EC6D9DF-2BE4-49BB-B4DA-835D270A8EB1}">
       <formula1>=IF(M946&lt;&gt;"",INDIRECT(VLOOKUP(M946,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M947" xr:uid="{EB846AAE-26BF-454F-A07F-ABD6ADF6D7AB}">
+    <dataValidation type="list" sqref="M947" xr:uid="{9984BCF0-D057-46C9-AFA6-9DE38805D5BB}">
       <formula1>=IF(L947&lt;&gt;"",INDIRECT(VLOOKUP(L947,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N947" xr:uid="{FB02F887-A4EE-41F5-A62B-5F3861EC9E6B}">
+    <dataValidation type="list" sqref="N947" xr:uid="{A58ED9E4-7AA7-4DEF-9392-8F06762C5F18}">
       <formula1>=IF(M947&lt;&gt;"",INDIRECT(VLOOKUP(M947,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M948" xr:uid="{BBD41F0D-7B15-4A07-9BA9-A3B87E041A89}">
+    <dataValidation type="list" sqref="M948" xr:uid="{16936704-D4A0-4520-9E41-12518D55C036}">
       <formula1>=IF(L948&lt;&gt;"",INDIRECT(VLOOKUP(L948,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N948" xr:uid="{0CD45E2D-B187-4F92-8B31-9BBF7805EBF9}">
+    <dataValidation type="list" sqref="N948" xr:uid="{041FB473-78B5-43CF-910D-FDB231F80B00}">
       <formula1>=IF(M948&lt;&gt;"",INDIRECT(VLOOKUP(M948,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M949" xr:uid="{594EFF33-03B6-49F0-BDFF-B6B72366EA14}">
+    <dataValidation type="list" sqref="M949" xr:uid="{3116D263-BBBA-40C3-8FE2-CD236E10A180}">
       <formula1>=IF(L949&lt;&gt;"",INDIRECT(VLOOKUP(L949,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N949" xr:uid="{44CAA890-65EA-45BB-918A-D8FB2031A037}">
+    <dataValidation type="list" sqref="N949" xr:uid="{C90D74C3-1BB8-4BE4-ACAD-48496E578312}">
       <formula1>=IF(M949&lt;&gt;"",INDIRECT(VLOOKUP(M949,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M950" xr:uid="{C12946E6-AFCB-4DD8-BB1B-B6E11DCDF91A}">
+    <dataValidation type="list" sqref="M950" xr:uid="{B54742FE-7FCC-431A-9461-AD368BEB071D}">
       <formula1>=IF(L950&lt;&gt;"",INDIRECT(VLOOKUP(L950,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N950" xr:uid="{07C383A5-35D9-4890-A647-B66DD2FDAFA3}">
+    <dataValidation type="list" sqref="N950" xr:uid="{EE0486A5-FCDF-423F-A341-D2B9D0D4FD30}">
       <formula1>=IF(M950&lt;&gt;"",INDIRECT(VLOOKUP(M950,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M951" xr:uid="{B6AFA2C9-B378-459B-8432-4B425248629C}">
+    <dataValidation type="list" sqref="M951" xr:uid="{9207FA09-83D7-4788-B844-1C024D4337D4}">
       <formula1>=IF(L951&lt;&gt;"",INDIRECT(VLOOKUP(L951,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N951" xr:uid="{B68F82B5-F1A4-42B0-B6CC-58E8F08478DA}">
+    <dataValidation type="list" sqref="N951" xr:uid="{DA78A154-0C05-4B5B-BCA0-55343337D6F4}">
       <formula1>=IF(M951&lt;&gt;"",INDIRECT(VLOOKUP(M951,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M952" xr:uid="{B3C56570-60CA-47C1-8D17-25D07569FCE5}">
+    <dataValidation type="list" sqref="M952" xr:uid="{7E33920F-E2C2-4314-AAEA-4D2E5C2F1A4F}">
       <formula1>=IF(L952&lt;&gt;"",INDIRECT(VLOOKUP(L952,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N952" xr:uid="{9FC5D9C5-FDFC-4510-A92D-26979E67D17B}">
+    <dataValidation type="list" sqref="N952" xr:uid="{0A562894-DBA4-4EC9-AFB6-960EA8100C1B}">
       <formula1>=IF(M952&lt;&gt;"",INDIRECT(VLOOKUP(M952,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M953" xr:uid="{06092780-4F62-431C-8C98-5FA10C2C6506}">
+    <dataValidation type="list" sqref="M953" xr:uid="{F99DB7A1-0AC4-4E8A-A7DE-3BDFCF0D5D3E}">
       <formula1>=IF(L953&lt;&gt;"",INDIRECT(VLOOKUP(L953,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N953" xr:uid="{F0F89BCC-BB55-4572-ABF7-FA266D95F65C}">
+    <dataValidation type="list" sqref="N953" xr:uid="{C0675347-BC39-4139-8AF9-619B8C0BF9DE}">
       <formula1>=IF(M953&lt;&gt;"",INDIRECT(VLOOKUP(M953,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M954" xr:uid="{507F68F7-A77C-414A-87F9-A383879D931F}">
+    <dataValidation type="list" sqref="M954" xr:uid="{9697B89F-5A28-4DC6-A10A-BDF893D414E7}">
       <formula1>=IF(L954&lt;&gt;"",INDIRECT(VLOOKUP(L954,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N954" xr:uid="{BB39D1BA-BF42-41A5-8870-B56C3F0E7DAA}">
+    <dataValidation type="list" sqref="N954" xr:uid="{067E037C-97BC-40D9-AA7A-9D55A6F42E04}">
       <formula1>=IF(M954&lt;&gt;"",INDIRECT(VLOOKUP(M954,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M955" xr:uid="{B39056D3-40BA-4DCA-9095-FD5D35B97C22}">
+    <dataValidation type="list" sqref="M955" xr:uid="{F757B248-9F3A-4052-8885-AEE96FC9D326}">
       <formula1>=IF(L955&lt;&gt;"",INDIRECT(VLOOKUP(L955,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N955" xr:uid="{95F2942B-35D3-468D-8EAF-AE1EC21D9946}">
+    <dataValidation type="list" sqref="N955" xr:uid="{41DFC1A0-7C5B-483B-9063-60F8DA3E5147}">
       <formula1>=IF(M955&lt;&gt;"",INDIRECT(VLOOKUP(M955,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M956" xr:uid="{4FFFFB73-6AF2-46C5-AB42-445C5C6E68C4}">
+    <dataValidation type="list" sqref="M956" xr:uid="{C79A915A-CA95-435B-A6AF-E05C793DA136}">
       <formula1>=IF(L956&lt;&gt;"",INDIRECT(VLOOKUP(L956,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N956" xr:uid="{B7C6DC9F-6D49-4B58-9AE4-F55D2259A44B}">
+    <dataValidation type="list" sqref="N956" xr:uid="{5CF17BAD-4FC9-48D6-8F32-FE6101081584}">
       <formula1>=IF(M956&lt;&gt;"",INDIRECT(VLOOKUP(M956,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M957" xr:uid="{BB0F0DF2-80DF-4726-95AB-CD54D1675CDB}">
+    <dataValidation type="list" sqref="M957" xr:uid="{60C4192A-EF08-4364-887F-F2C45CE3572A}">
       <formula1>=IF(L957&lt;&gt;"",INDIRECT(VLOOKUP(L957,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N957" xr:uid="{8A5D3BE0-09F7-4864-BE2C-A1CF29861711}">
+    <dataValidation type="list" sqref="N957" xr:uid="{292E9ACB-D966-44A0-AF22-41B2BC5225AB}">
       <formula1>=IF(M957&lt;&gt;"",INDIRECT(VLOOKUP(M957,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M958" xr:uid="{C0598A19-71D3-4B35-BF94-549A4717EA3F}">
+    <dataValidation type="list" sqref="M958" xr:uid="{27FD38DD-80FD-4E11-BF04-6558D896C3AE}">
       <formula1>=IF(L958&lt;&gt;"",INDIRECT(VLOOKUP(L958,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N958" xr:uid="{D44D2D97-7263-4971-B9D0-910D760B99F7}">
+    <dataValidation type="list" sqref="N958" xr:uid="{65470073-3427-4D38-A475-5D7A97BAD583}">
       <formula1>=IF(M958&lt;&gt;"",INDIRECT(VLOOKUP(M958,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M959" xr:uid="{932D3652-3F3D-4D04-988A-297AD8F3E3F8}">
+    <dataValidation type="list" sqref="M959" xr:uid="{850E898D-F910-4175-BAB6-38BF8FDCEDC3}">
       <formula1>=IF(L959&lt;&gt;"",INDIRECT(VLOOKUP(L959,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N959" xr:uid="{00B2233D-1392-4E45-AE4D-01334F948A5A}">
+    <dataValidation type="list" sqref="N959" xr:uid="{F0058321-3600-43CE-8795-9567ECCBB60B}">
       <formula1>=IF(M959&lt;&gt;"",INDIRECT(VLOOKUP(M959,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M960" xr:uid="{1E7A1C52-74A3-46DE-B4A5-E304F8078E2A}">
+    <dataValidation type="list" sqref="M960" xr:uid="{AC6E9979-3D29-4008-84D1-1E6BCCCAD7FC}">
       <formula1>=IF(L960&lt;&gt;"",INDIRECT(VLOOKUP(L960,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N960" xr:uid="{EE991A3C-F003-41FB-90F6-6D269C408CFB}">
+    <dataValidation type="list" sqref="N960" xr:uid="{A2F95084-FC92-49E2-9325-CE95986ADF15}">
       <formula1>=IF(M960&lt;&gt;"",INDIRECT(VLOOKUP(M960,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M961" xr:uid="{C0C47421-C600-4260-9037-6FE5C80F20AB}">
+    <dataValidation type="list" sqref="M961" xr:uid="{475C790B-1534-456D-9527-1A0775973E3F}">
       <formula1>=IF(L961&lt;&gt;"",INDIRECT(VLOOKUP(L961,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N961" xr:uid="{180F56A0-C0F5-452C-970A-60051693486A}">
+    <dataValidation type="list" sqref="N961" xr:uid="{4382E291-5083-4182-B26D-05ABF7937A48}">
       <formula1>=IF(M961&lt;&gt;"",INDIRECT(VLOOKUP(M961,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M962" xr:uid="{B5CB0D67-E718-4FFF-9B0C-5F8D3BBC6491}">
+    <dataValidation type="list" sqref="M962" xr:uid="{A560C610-E1EB-4F58-A2F9-A7AA7EB0D13B}">
       <formula1>=IF(L962&lt;&gt;"",INDIRECT(VLOOKUP(L962,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N962" xr:uid="{034C9069-31BA-4E9A-8B87-40CEDDD9935F}">
+    <dataValidation type="list" sqref="N962" xr:uid="{8E08A4A6-ECA3-4B74-9DB2-69B62EBAE6D2}">
       <formula1>=IF(M962&lt;&gt;"",INDIRECT(VLOOKUP(M962,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M963" xr:uid="{7F363500-E39C-44ED-A773-34F7867D4DB2}">
+    <dataValidation type="list" sqref="M963" xr:uid="{53F83421-E8B3-400A-9D73-DA2339FB5E81}">
       <formula1>=IF(L963&lt;&gt;"",INDIRECT(VLOOKUP(L963,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N963" xr:uid="{D1B04A12-498F-4563-8168-E7AFC6945651}">
+    <dataValidation type="list" sqref="N963" xr:uid="{4D195148-2021-4D67-B165-E63076A9A58B}">
       <formula1>=IF(M963&lt;&gt;"",INDIRECT(VLOOKUP(M963,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M964" xr:uid="{F8ADE0E4-71BC-427C-9C6A-DD3AC7051EB9}">
+    <dataValidation type="list" sqref="M964" xr:uid="{32A9D157-80E7-4F35-A0F1-F7D106B58FD4}">
       <formula1>=IF(L964&lt;&gt;"",INDIRECT(VLOOKUP(L964,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N964" xr:uid="{C44903D5-CE8A-43E5-9C74-17DC91AEC8D2}">
+    <dataValidation type="list" sqref="N964" xr:uid="{50DD3FCC-26D6-499B-995C-B415F0ED9F7A}">
       <formula1>=IF(M964&lt;&gt;"",INDIRECT(VLOOKUP(M964,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M965" xr:uid="{75B86068-AA52-429D-ADFD-A5E0A1155D50}">
+    <dataValidation type="list" sqref="M965" xr:uid="{C071C223-2178-4149-8672-968198D6EA94}">
       <formula1>=IF(L965&lt;&gt;"",INDIRECT(VLOOKUP(L965,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N965" xr:uid="{4E6540A7-BB4E-4977-B316-7F4112CD31B4}">
+    <dataValidation type="list" sqref="N965" xr:uid="{8531F2E0-F1CC-4D8A-B3C7-37036710F222}">
       <formula1>=IF(M965&lt;&gt;"",INDIRECT(VLOOKUP(M965,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M966" xr:uid="{41C601B5-E78B-42B8-9757-D12FA759BCAC}">
+    <dataValidation type="list" sqref="M966" xr:uid="{09DB84EA-3118-41AE-AB92-6C4C38148F53}">
       <formula1>=IF(L966&lt;&gt;"",INDIRECT(VLOOKUP(L966,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N966" xr:uid="{D98110F6-AD3D-45EE-A10F-946F2CFD0C6C}">
+    <dataValidation type="list" sqref="N966" xr:uid="{728ECF23-CAA0-4A02-ABB1-4FFB6BA82FE1}">
       <formula1>=IF(M966&lt;&gt;"",INDIRECT(VLOOKUP(M966,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M967" xr:uid="{791B717D-EEBA-4DEB-BC3F-BF783DDF5D12}">
+    <dataValidation type="list" sqref="M967" xr:uid="{935B8943-4E20-49ED-9087-88A0AD7D252C}">
       <formula1>=IF(L967&lt;&gt;"",INDIRECT(VLOOKUP(L967,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N967" xr:uid="{ECABF466-0462-4DCF-87CC-EFFA6704DC23}">
+    <dataValidation type="list" sqref="N967" xr:uid="{793E57F4-57C1-49C2-8F7C-F946A6A703AD}">
       <formula1>=IF(M967&lt;&gt;"",INDIRECT(VLOOKUP(M967,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M968" xr:uid="{B4430418-8BD0-475C-9669-F397C3DFAE25}">
+    <dataValidation type="list" sqref="M968" xr:uid="{B68688BF-8A79-4ACB-BFDB-AA5D2FCBE106}">
       <formula1>=IF(L968&lt;&gt;"",INDIRECT(VLOOKUP(L968,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N968" xr:uid="{AAAD89AB-6C90-43B6-AF25-D0FC7D6D170C}">
+    <dataValidation type="list" sqref="N968" xr:uid="{C21C5EDB-46D1-4A31-A123-3E8CDAF8E29F}">
       <formula1>=IF(M968&lt;&gt;"",INDIRECT(VLOOKUP(M968,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M969" xr:uid="{8D98F0A4-6900-4BC1-A082-679ECCAA31DA}">
+    <dataValidation type="list" sqref="M969" xr:uid="{B4A429D5-9D73-4ACD-82A6-F90E1A86CAD1}">
       <formula1>=IF(L969&lt;&gt;"",INDIRECT(VLOOKUP(L969,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N969" xr:uid="{05368038-AEF2-44F4-911A-CFC199395396}">
+    <dataValidation type="list" sqref="N969" xr:uid="{F9131056-1EB5-49C0-A877-E564256EFC37}">
       <formula1>=IF(M969&lt;&gt;"",INDIRECT(VLOOKUP(M969,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M970" xr:uid="{8A695AFE-F42C-4137-B1E4-07131CF92A29}">
+    <dataValidation type="list" sqref="M970" xr:uid="{7214E80A-0562-4FD8-AC16-3CD3B38AFEF4}">
       <formula1>=IF(L970&lt;&gt;"",INDIRECT(VLOOKUP(L970,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N970" xr:uid="{D7104B1C-7988-403F-9B73-968469933241}">
+    <dataValidation type="list" sqref="N970" xr:uid="{178586C7-4507-45B0-ADE5-062F5ED4DD50}">
       <formula1>=IF(M970&lt;&gt;"",INDIRECT(VLOOKUP(M970,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M971" xr:uid="{E426F9FA-61AC-4F8B-AD8B-FBA183A2834B}">
+    <dataValidation type="list" sqref="M971" xr:uid="{C582F54B-EBFB-47E4-B092-CB9EEB304516}">
       <formula1>=IF(L971&lt;&gt;"",INDIRECT(VLOOKUP(L971,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N971" xr:uid="{866BAB7D-F7F6-4A6D-A235-B173EFFE335C}">
+    <dataValidation type="list" sqref="N971" xr:uid="{6D5DD2BF-C726-4933-8D0C-406458474F8A}">
       <formula1>=IF(M971&lt;&gt;"",INDIRECT(VLOOKUP(M971,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M972" xr:uid="{09521911-BBA9-4625-90A0-1F9737CC2CE1}">
+    <dataValidation type="list" sqref="M972" xr:uid="{22AF9A16-D1C0-4E66-AE53-FC9D50EAB963}">
       <formula1>=IF(L972&lt;&gt;"",INDIRECT(VLOOKUP(L972,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N972" xr:uid="{9351A2ED-54F6-439B-9974-1A7B74CBDEA8}">
+    <dataValidation type="list" sqref="N972" xr:uid="{8DB7E93C-9923-4C39-A3F8-370CBC58EBB1}">
       <formula1>=IF(M972&lt;&gt;"",INDIRECT(VLOOKUP(M972,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M973" xr:uid="{B8AD1B96-2221-40F5-B23B-1E9311FFE856}">
+    <dataValidation type="list" sqref="M973" xr:uid="{218B557D-E876-4819-93DA-0A591D7E7B90}">
       <formula1>=IF(L973&lt;&gt;"",INDIRECT(VLOOKUP(L973,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N973" xr:uid="{7FBE4E76-6913-432A-8009-7A2611933971}">
+    <dataValidation type="list" sqref="N973" xr:uid="{C1AE8542-A139-4FAE-AA59-BA0B30B96787}">
       <formula1>=IF(M973&lt;&gt;"",INDIRECT(VLOOKUP(M973,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M974" xr:uid="{D6321A06-3F39-433C-AF11-9044629FDD78}">
+    <dataValidation type="list" sqref="M974" xr:uid="{3329CFCC-89CE-4B67-AEA8-90B76D19DE6F}">
       <formula1>=IF(L974&lt;&gt;"",INDIRECT(VLOOKUP(L974,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N974" xr:uid="{73A79ECF-AB62-4400-9AC8-9D5A3E6D2F1C}">
+    <dataValidation type="list" sqref="N974" xr:uid="{906202A1-3B11-4D25-B9FC-C48232F9DF95}">
       <formula1>=IF(M974&lt;&gt;"",INDIRECT(VLOOKUP(M974,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M975" xr:uid="{382B9A14-8683-437D-A87F-114DAB96694B}">
+    <dataValidation type="list" sqref="M975" xr:uid="{EAD4CD5B-BF62-4CE2-9CC5-26DD7D78B09E}">
       <formula1>=IF(L975&lt;&gt;"",INDIRECT(VLOOKUP(L975,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N975" xr:uid="{E85E9AF3-BC38-4016-A0D6-D363F155AE25}">
+    <dataValidation type="list" sqref="N975" xr:uid="{B189514A-4107-4A11-8483-1313AA571027}">
       <formula1>=IF(M975&lt;&gt;"",INDIRECT(VLOOKUP(M975,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M976" xr:uid="{612DFC6F-E8F7-4C72-8394-93C33EA996DD}">
+    <dataValidation type="list" sqref="M976" xr:uid="{49866A08-1D1C-43BA-95E2-A5424B2AFC1F}">
       <formula1>=IF(L976&lt;&gt;"",INDIRECT(VLOOKUP(L976,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N976" xr:uid="{422EEFAD-B841-4B1D-A378-D4BA9B3943D4}">
+    <dataValidation type="list" sqref="N976" xr:uid="{B595E224-5B3F-4B50-AE3F-EC0FA01D3E36}">
       <formula1>=IF(M976&lt;&gt;"",INDIRECT(VLOOKUP(M976,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M977" xr:uid="{6BD9B251-84EB-47C5-A3AF-AD67D97A322D}">
+    <dataValidation type="list" sqref="M977" xr:uid="{A0D3C278-9D3B-4A33-BA9B-99D3B9A4E96B}">
       <formula1>=IF(L977&lt;&gt;"",INDIRECT(VLOOKUP(L977,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N977" xr:uid="{3DDBBF16-727D-4611-ACD0-D96E03304872}">
+    <dataValidation type="list" sqref="N977" xr:uid="{A60A87DA-0EE8-4CC8-80B7-A6E52209CE60}">
       <formula1>=IF(M977&lt;&gt;"",INDIRECT(VLOOKUP(M977,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M978" xr:uid="{4A25630F-F075-4D65-BF66-32ADA337F3DC}">
+    <dataValidation type="list" sqref="M978" xr:uid="{439A5987-A670-430D-AA2C-31A7A5CCAA1A}">
       <formula1>=IF(L978&lt;&gt;"",INDIRECT(VLOOKUP(L978,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N978" xr:uid="{B7FE2E0E-86FB-4F32-98B9-41946374AFBB}">
+    <dataValidation type="list" sqref="N978" xr:uid="{BD0B031D-8A86-447A-932C-F18159F7DB84}">
       <formula1>=IF(M978&lt;&gt;"",INDIRECT(VLOOKUP(M978,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M979" xr:uid="{5D0D63B4-407D-49F2-B4AE-054D5B183C73}">
+    <dataValidation type="list" sqref="M979" xr:uid="{654146BC-47F1-4F3B-8F03-84DF52B43671}">
       <formula1>=IF(L979&lt;&gt;"",INDIRECT(VLOOKUP(L979,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N979" xr:uid="{81BCA571-FE90-4E5E-86E0-17C5A5CB8D3B}">
+    <dataValidation type="list" sqref="N979" xr:uid="{618C8569-B58A-4E17-9910-2233F2BEBEF8}">
       <formula1>=IF(M979&lt;&gt;"",INDIRECT(VLOOKUP(M979,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M980" xr:uid="{EE9A953B-266C-466F-BD94-459CDC4A334B}">
+    <dataValidation type="list" sqref="M980" xr:uid="{A5DD76CA-F917-468F-AB19-CA0144A9A2A5}">
       <formula1>=IF(L980&lt;&gt;"",INDIRECT(VLOOKUP(L980,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N980" xr:uid="{61A9AD6D-4A98-420C-9056-A8D0F8EC5CDA}">
+    <dataValidation type="list" sqref="N980" xr:uid="{0BDCC50B-A1AE-4DA7-BFEA-80E173A26EC7}">
       <formula1>=IF(M980&lt;&gt;"",INDIRECT(VLOOKUP(M980,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M981" xr:uid="{AD305EE8-77E8-4370-B405-C26FC53D3C67}">
+    <dataValidation type="list" sqref="M981" xr:uid="{F16D14A7-930B-48CD-85CC-9ECA35F7B56F}">
       <formula1>=IF(L981&lt;&gt;"",INDIRECT(VLOOKUP(L981,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N981" xr:uid="{562BBC3A-BE7D-4293-9A1A-A88F2C5BEE91}">
+    <dataValidation type="list" sqref="N981" xr:uid="{A5EE58E7-2004-47B7-81E5-34A780199E38}">
       <formula1>=IF(M981&lt;&gt;"",INDIRECT(VLOOKUP(M981,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M982" xr:uid="{D1736657-613C-41C0-9996-687E341BFC3F}">
+    <dataValidation type="list" sqref="M982" xr:uid="{7552F5E3-2937-44FC-BEBF-64783D980678}">
       <formula1>=IF(L982&lt;&gt;"",INDIRECT(VLOOKUP(L982,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N982" xr:uid="{D3B9E94A-1427-4B33-85E6-77F29CFDC588}">
+    <dataValidation type="list" sqref="N982" xr:uid="{6B6D1EEE-1FAA-46F3-90B3-6A3CFE61BC9C}">
       <formula1>=IF(M982&lt;&gt;"",INDIRECT(VLOOKUP(M982,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M983" xr:uid="{74244A04-9F45-43FF-BF0A-7E3D60DADF39}">
+    <dataValidation type="list" sqref="M983" xr:uid="{420F121D-CBBA-4E9D-9F1A-837374B2102F}">
       <formula1>=IF(L983&lt;&gt;"",INDIRECT(VLOOKUP(L983,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N983" xr:uid="{8F39109C-6739-487E-8451-F51A1C47BFB2}">
+    <dataValidation type="list" sqref="N983" xr:uid="{E1139538-AC68-4F00-ADC9-091EB7A4C063}">
       <formula1>=IF(M983&lt;&gt;"",INDIRECT(VLOOKUP(M983,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M984" xr:uid="{D9FD1102-6A5A-4638-BC94-4874053BEAAB}">
+    <dataValidation type="list" sqref="M984" xr:uid="{FB0719B1-C067-4F70-BB73-37F4EDBEF59F}">
       <formula1>=IF(L984&lt;&gt;"",INDIRECT(VLOOKUP(L984,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N984" xr:uid="{3A3109A6-EA78-467E-A4FC-1AFA200CD7C8}">
+    <dataValidation type="list" sqref="N984" xr:uid="{BC67A2FA-8B4E-416B-A63C-6F12BF7A358E}">
       <formula1>=IF(M984&lt;&gt;"",INDIRECT(VLOOKUP(M984,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M985" xr:uid="{60F3051C-20D8-4AD0-A1A4-2309C1AFFEDA}">
+    <dataValidation type="list" sqref="M985" xr:uid="{C1121AF7-FACD-4AF3-9653-18E29082B3CF}">
       <formula1>=IF(L985&lt;&gt;"",INDIRECT(VLOOKUP(L985,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N985" xr:uid="{B250688D-52F5-466D-BD5E-FB43402EED99}">
+    <dataValidation type="list" sqref="N985" xr:uid="{DC990226-BCF3-468A-82D8-6525439E616D}">
       <formula1>=IF(M985&lt;&gt;"",INDIRECT(VLOOKUP(M985,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M986" xr:uid="{923184D7-28E9-443B-94F2-A13227C7B3E6}">
+    <dataValidation type="list" sqref="M986" xr:uid="{42E56859-A9FE-478F-95E8-CAC54A548595}">
       <formula1>=IF(L986&lt;&gt;"",INDIRECT(VLOOKUP(L986,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N986" xr:uid="{AA23A29D-A26B-4A2F-A560-F781A8608AA8}">
+    <dataValidation type="list" sqref="N986" xr:uid="{AC452957-CC69-49A6-BB20-6389C4974AAD}">
       <formula1>=IF(M986&lt;&gt;"",INDIRECT(VLOOKUP(M986,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M987" xr:uid="{428702F7-94A5-4107-ABB9-77C4BA8A33B1}">
+    <dataValidation type="list" sqref="M987" xr:uid="{2D0BD6FB-B6D1-4F71-8D4D-367F92EADDF1}">
       <formula1>=IF(L987&lt;&gt;"",INDIRECT(VLOOKUP(L987,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N987" xr:uid="{D99915A3-802D-4951-BD91-5FC6C1F8F1B1}">
+    <dataValidation type="list" sqref="N987" xr:uid="{1850B912-A5E3-4433-AAFD-67A8B622CB33}">
       <formula1>=IF(M987&lt;&gt;"",INDIRECT(VLOOKUP(M987,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M988" xr:uid="{174A86F4-298A-4059-B057-83462D7BEA8A}">
+    <dataValidation type="list" sqref="M988" xr:uid="{C2CD2F77-0572-46F1-A7D4-AEEEFD0BCBB1}">
       <formula1>=IF(L988&lt;&gt;"",INDIRECT(VLOOKUP(L988,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N988" xr:uid="{F4E128BD-9AD0-4784-A9D4-28231267282D}">
+    <dataValidation type="list" sqref="N988" xr:uid="{7A6C0295-300F-4975-89AF-479FC1E251C9}">
       <formula1>=IF(M988&lt;&gt;"",INDIRECT(VLOOKUP(M988,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M989" xr:uid="{084CD523-6A4B-4A14-835F-0235024D0DC8}">
+    <dataValidation type="list" sqref="M989" xr:uid="{02B60FA6-16E8-4EE7-B9BE-55B06B35A155}">
       <formula1>=IF(L989&lt;&gt;"",INDIRECT(VLOOKUP(L989,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N989" xr:uid="{8D5D5D13-383B-43FA-9110-AFB432630AE1}">
+    <dataValidation type="list" sqref="N989" xr:uid="{4FFA6CC5-5CFA-4645-AE2F-220FCC2F43E3}">
       <formula1>=IF(M989&lt;&gt;"",INDIRECT(VLOOKUP(M989,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M990" xr:uid="{75A8F1CD-28D3-4051-A3B6-8000B3B45842}">
+    <dataValidation type="list" sqref="M990" xr:uid="{871B96BC-656F-4107-89BA-FC2F45065230}">
       <formula1>=IF(L990&lt;&gt;"",INDIRECT(VLOOKUP(L990,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N990" xr:uid="{86E2EE6D-4308-4903-81ED-9CFF742FED93}">
+    <dataValidation type="list" sqref="N990" xr:uid="{7079E704-9DEC-44E3-852D-C5E8DA013340}">
       <formula1>=IF(M990&lt;&gt;"",INDIRECT(VLOOKUP(M990,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M991" xr:uid="{D55F9FF2-DF99-45FB-AF9C-ABEFAF167FD0}">
+    <dataValidation type="list" sqref="M991" xr:uid="{F50B9E6E-9591-4341-9FB7-231330E9B491}">
       <formula1>=IF(L991&lt;&gt;"",INDIRECT(VLOOKUP(L991,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N991" xr:uid="{D2F429AF-48EA-4E7A-959B-47DB296B2594}">
+    <dataValidation type="list" sqref="N991" xr:uid="{BE8BB2F4-387B-424D-BFD1-316E20CA334F}">
       <formula1>=IF(M991&lt;&gt;"",INDIRECT(VLOOKUP(M991,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M992" xr:uid="{CC14965D-BF16-4296-87D7-123FF748B94F}">
+    <dataValidation type="list" sqref="M992" xr:uid="{0FBC2110-AFCF-47CE-9D28-7F90FC69906C}">
       <formula1>=IF(L992&lt;&gt;"",INDIRECT(VLOOKUP(L992,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N992" xr:uid="{75C6A12E-A30B-4D95-ACA3-08E43BD0DD39}">
+    <dataValidation type="list" sqref="N992" xr:uid="{BBFF29DC-3863-46A6-840F-9839B72270B9}">
       <formula1>=IF(M992&lt;&gt;"",INDIRECT(VLOOKUP(M992,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M993" xr:uid="{5C657199-19C1-4AD8-A8B7-CF599BD0B193}">
+    <dataValidation type="list" sqref="M993" xr:uid="{1D10B8D1-AE81-454D-9683-0676F3FD6846}">
       <formula1>=IF(L993&lt;&gt;"",INDIRECT(VLOOKUP(L993,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N993" xr:uid="{712DF895-9330-473E-BB00-4C74727685F7}">
+    <dataValidation type="list" sqref="N993" xr:uid="{75AE8961-1745-457D-A46B-FA0264D459FF}">
       <formula1>=IF(M993&lt;&gt;"",INDIRECT(VLOOKUP(M993,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M994" xr:uid="{67267C98-FC2D-4507-9ED1-8068B93045C7}">
+    <dataValidation type="list" sqref="M994" xr:uid="{AF9F93D3-AA8B-4A39-9CE2-2C89FE241EB1}">
       <formula1>=IF(L994&lt;&gt;"",INDIRECT(VLOOKUP(L994,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N994" xr:uid="{571103A8-BD4D-482A-A67C-3C459AD3889E}">
+    <dataValidation type="list" sqref="N994" xr:uid="{6868CE93-4DC1-4F42-B0D1-42C7F2BAEAF2}">
       <formula1>=IF(M994&lt;&gt;"",INDIRECT(VLOOKUP(M994,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M995" xr:uid="{87E9ECFF-A98B-470B-9C79-255DC4BFBD8B}">
+    <dataValidation type="list" sqref="M995" xr:uid="{8AFDCE4E-8DD8-4144-B688-0F1C143A24E4}">
       <formula1>=IF(L995&lt;&gt;"",INDIRECT(VLOOKUP(L995,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N995" xr:uid="{F664118A-7474-4A13-B984-B9CE3D49D27E}">
+    <dataValidation type="list" sqref="N995" xr:uid="{0B0D38F1-247B-4F68-BAD5-EB98725706AC}">
       <formula1>=IF(M995&lt;&gt;"",INDIRECT(VLOOKUP(M995,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M996" xr:uid="{0BD44A8F-EE40-4B9F-9B76-B72DFA73AF5C}">
+    <dataValidation type="list" sqref="M996" xr:uid="{FFA655B4-05B6-409E-876E-732664ED2FD6}">
       <formula1>=IF(L996&lt;&gt;"",INDIRECT(VLOOKUP(L996,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N996" xr:uid="{9A5415C7-BC48-4A3E-9C80-1A63F57CC2AB}">
+    <dataValidation type="list" sqref="N996" xr:uid="{B5611659-A3EB-4800-A070-C7F06E0A5872}">
       <formula1>=IF(M996&lt;&gt;"",INDIRECT(VLOOKUP(M996,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M997" xr:uid="{17AA1905-21FC-4A22-8E98-7C1D8E2FBD7B}">
+    <dataValidation type="list" sqref="M997" xr:uid="{A8E1CFF9-9578-4888-80CD-6191EA17E39A}">
       <formula1>=IF(L997&lt;&gt;"",INDIRECT(VLOOKUP(L997,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N997" xr:uid="{CB2ADDA1-2D9C-433A-B266-E3B95CC53F45}">
+    <dataValidation type="list" sqref="N997" xr:uid="{D4807982-C41E-4A70-A311-9A0B73A3D3FA}">
       <formula1>=IF(M997&lt;&gt;"",INDIRECT(VLOOKUP(M997,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M998" xr:uid="{521C2E89-1853-436D-AFF1-EEE1CB7FE612}">
+    <dataValidation type="list" sqref="M998" xr:uid="{2997E743-B150-411F-9B50-2F9A2A3DCAB5}">
       <formula1>=IF(L998&lt;&gt;"",INDIRECT(VLOOKUP(L998,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N998" xr:uid="{6E17ADCC-1869-4C4A-A855-D10CF44420D4}">
+    <dataValidation type="list" sqref="N998" xr:uid="{5D045B42-9810-4DDC-811A-53FC586CDFCE}">
       <formula1>=IF(M998&lt;&gt;"",INDIRECT(VLOOKUP(M998,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M999" xr:uid="{031F7BA3-9086-49AD-9284-08A6E75A17A1}">
+    <dataValidation type="list" sqref="M999" xr:uid="{3520D58F-ADD8-4716-BC83-DF6A539A5C87}">
       <formula1>=IF(L999&lt;&gt;"",INDIRECT(VLOOKUP(L999,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N999" xr:uid="{ACEF4EF9-17BE-4549-B16A-CBDE04D2A36F}">
+    <dataValidation type="list" sqref="N999" xr:uid="{B01EA188-2FD4-4C57-A1F3-2B4E2AE01EA6}">
       <formula1>=IF(M999&lt;&gt;"",INDIRECT(VLOOKUP(M999,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M1000" xr:uid="{B634F4DC-D9FE-47BE-B816-65F77BB87E61}">
+    <dataValidation type="list" sqref="M1000" xr:uid="{04AD7B44-87F7-49A7-9F61-88E298E8A935}">
       <formula1>=IF(L1000&lt;&gt;"",INDIRECT(VLOOKUP(L1000,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N1000" xr:uid="{D84F7ABA-1565-45F1-A4D3-4C423420D514}">
+    <dataValidation type="list" sqref="N1000" xr:uid="{1926B5C2-93AD-452E-B4FE-B30CF306FC3C}">
       <formula1>=IF(M1000&lt;&gt;"",INDIRECT(VLOOKUP(M1000,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
   </dataValidations>

--- a/ImportExportExcellApi/Templates/HU_WORKING_BASE_Release.xlsx
+++ b/ImportExportExcellApi/Templates/HU_WORKING_BASE_Release.xlsx
@@ -1636,7 +1636,6 @@
       <c r="D6" s="7"/>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
       <c r="H6" s="7"/>
       <c r="I6" s="7"/>
       <c r="J6" s="7"/>
@@ -33486,5992 +33485,5992 @@
     <mergeCell ref="A1:R2"/>
   </mergeCells>
   <dataValidations count="1996">
-    <dataValidation type="list" sqref="B6:B1000" xr:uid="{183D964D-CF21-4B7C-9041-5FD02AC5ACEB}">
+    <dataValidation type="list" sqref="B6:B1000" xr:uid="{75265D2F-3C9A-478C-BF11-97B46C35D76F}">
       <formula1>=DanhSachCode</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="D6:D1000" xr:uid="{2EE997C7-2BE7-41C6-BACB-C70F9640BC4C}">
+    <dataValidation type="list" sqref="D6:D1000" xr:uid="{6D15D64E-4C25-495B-9EAD-7C37034F2D12}">
       <formula1>=DanhSachLoaiQuyetDinh</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="I6:I1000" xr:uid="{624023F4-49E4-4B55-B700-EA62D6D4C357}">
+    <dataValidation type="list" sqref="I6:I1000" xr:uid="{EEC9EA65-0608-41FA-A811-887259D40C37}">
       <formula1>=DanhSachPhongBan</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="J6:J1000" xr:uid="{D4FD8260-F288-4225-B5A5-74F3415C8A54}">
+    <dataValidation type="list" sqref="J6:J1000" xr:uid="{B31BCDE4-6D7A-4582-A3FB-75AFC34E4277}">
       <formula1>=DanhSachChucDanh</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="L6:L1000" xr:uid="{63EDD045-886E-4BA7-B426-4C29294D7E51}">
+    <dataValidation type="list" sqref="L6:L1000" xr:uid="{B0F30BD6-F436-418D-B1CC-D4D280D4C7A9}">
       <formula1>=ThangLuongList</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="P6:P1000" xr:uid="{0DC734FE-E934-419B-9CB2-E95BBA3A9EE8}">
+    <dataValidation type="list" sqref="P6:P1000" xr:uid="{7D94A37E-A9F1-4901-A30D-73AEAFBE8F28}">
       <formula1>=DanhSachCode</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M6" xr:uid="{445A1D93-3270-4476-A6A3-A7406CF8C926}">
+    <dataValidation type="list" sqref="M6" xr:uid="{743F2062-1B18-4EB7-859C-A2DBE9EC935C}">
       <formula1>=IF(L6&lt;&gt;"",INDIRECT(VLOOKUP(L6,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N6" xr:uid="{65BFF6D8-59AB-413F-BB83-A63C3FB7D12B}">
+    <dataValidation type="list" sqref="N6" xr:uid="{9A6E8E57-BF16-4470-A58A-03EF636262F7}">
       <formula1>=IF(M6&lt;&gt;"",INDIRECT(VLOOKUP(M6,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M7" xr:uid="{6B1283EB-D256-4913-AFAE-F5A9E9D7DA08}">
+    <dataValidation type="list" sqref="M7" xr:uid="{9307A655-5779-4BB1-A68C-F5E74AB5200E}">
       <formula1>=IF(L7&lt;&gt;"",INDIRECT(VLOOKUP(L7,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N7" xr:uid="{14C8E1FD-74DB-40A3-9B99-BCF97778F08B}">
+    <dataValidation type="list" sqref="N7" xr:uid="{28A3A72A-E020-4A22-B03F-F077C17A3030}">
       <formula1>=IF(M7&lt;&gt;"",INDIRECT(VLOOKUP(M7,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M8" xr:uid="{4F229F28-92F9-42B3-8A5B-FD89C888ABAD}">
+    <dataValidation type="list" sqref="M8" xr:uid="{55FD0DE6-7EEC-416E-9368-30F27DBD07CF}">
       <formula1>=IF(L8&lt;&gt;"",INDIRECT(VLOOKUP(L8,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N8" xr:uid="{596AF037-BB05-438A-B321-6EFC6DA9CAB9}">
+    <dataValidation type="list" sqref="N8" xr:uid="{31583A49-71E6-40BA-8F4B-191390E8F03D}">
       <formula1>=IF(M8&lt;&gt;"",INDIRECT(VLOOKUP(M8,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M9" xr:uid="{DC492924-9C66-4A61-A38F-0A0ED205528B}">
+    <dataValidation type="list" sqref="M9" xr:uid="{556F7373-FC34-4E0C-8A95-EE3D9A841BF1}">
       <formula1>=IF(L9&lt;&gt;"",INDIRECT(VLOOKUP(L9,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N9" xr:uid="{8CE8F3FA-2CDB-451D-BF05-2665F9CCD408}">
+    <dataValidation type="list" sqref="N9" xr:uid="{3C8EB7AE-E75F-4868-BCEA-2F731E83AC48}">
       <formula1>=IF(M9&lt;&gt;"",INDIRECT(VLOOKUP(M9,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M10" xr:uid="{DED2AC7F-B12A-448B-B517-BB4121FEEFE9}">
+    <dataValidation type="list" sqref="M10" xr:uid="{9B200C0D-2D15-4C50-97A8-B892A8B3501D}">
       <formula1>=IF(L10&lt;&gt;"",INDIRECT(VLOOKUP(L10,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N10" xr:uid="{BAADAD1A-7686-4EB5-BC8E-573459745F35}">
+    <dataValidation type="list" sqref="N10" xr:uid="{21A47000-EA21-4B14-B960-1E014EE8DD84}">
       <formula1>=IF(M10&lt;&gt;"",INDIRECT(VLOOKUP(M10,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M11" xr:uid="{9C70F32A-0CBE-47FA-ABE7-095648F7D619}">
+    <dataValidation type="list" sqref="M11" xr:uid="{672BCC74-496D-4F72-AC58-F84CB4A94118}">
       <formula1>=IF(L11&lt;&gt;"",INDIRECT(VLOOKUP(L11,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N11" xr:uid="{DE71F833-F656-4B72-828E-861CE4DFE9AE}">
+    <dataValidation type="list" sqref="N11" xr:uid="{4E4C4E9F-0228-4251-9F50-739C9AA99DF3}">
       <formula1>=IF(M11&lt;&gt;"",INDIRECT(VLOOKUP(M11,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M12" xr:uid="{C3121A63-5299-4BA8-8FA8-8E22DC7065AE}">
+    <dataValidation type="list" sqref="M12" xr:uid="{A2AC8384-520E-42B9-A8DF-12F260B264C1}">
       <formula1>=IF(L12&lt;&gt;"",INDIRECT(VLOOKUP(L12,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N12" xr:uid="{350F6CAE-6A42-46D6-B146-903184992623}">
+    <dataValidation type="list" sqref="N12" xr:uid="{C06E11A8-DE6F-4505-8E46-AF7D2B052D82}">
       <formula1>=IF(M12&lt;&gt;"",INDIRECT(VLOOKUP(M12,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M13" xr:uid="{5126571B-3D38-4691-8F14-B4AEE3F95D45}">
+    <dataValidation type="list" sqref="M13" xr:uid="{AF90A9FF-7AEF-4155-B967-00E4AE6E63ED}">
       <formula1>=IF(L13&lt;&gt;"",INDIRECT(VLOOKUP(L13,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N13" xr:uid="{7AFC839A-D83C-4BBF-9A8C-802B2601819C}">
+    <dataValidation type="list" sqref="N13" xr:uid="{32AD2CE5-FAC6-47E9-A5A0-51A552D484C8}">
       <formula1>=IF(M13&lt;&gt;"",INDIRECT(VLOOKUP(M13,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M14" xr:uid="{4F156309-DAF8-4E16-8A27-734526A9688F}">
+    <dataValidation type="list" sqref="M14" xr:uid="{B7A9B414-B37D-445D-9D88-E6EFF26B88AC}">
       <formula1>=IF(L14&lt;&gt;"",INDIRECT(VLOOKUP(L14,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N14" xr:uid="{56128A30-440F-4F0C-AC49-B8655C40E0D0}">
+    <dataValidation type="list" sqref="N14" xr:uid="{73ED9A53-79CE-4A8A-BAC0-05F525068F25}">
       <formula1>=IF(M14&lt;&gt;"",INDIRECT(VLOOKUP(M14,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M15" xr:uid="{ACC257B5-F5FF-42F6-B5B6-7F22DC019244}">
+    <dataValidation type="list" sqref="M15" xr:uid="{C1416ABF-3D60-472C-8189-F86DD68EDBE5}">
       <formula1>=IF(L15&lt;&gt;"",INDIRECT(VLOOKUP(L15,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N15" xr:uid="{8F2ABC8B-EA28-47A8-98D8-B9E7E8ADB436}">
+    <dataValidation type="list" sqref="N15" xr:uid="{4E3B5905-2334-4B10-A110-71E191EE79C8}">
       <formula1>=IF(M15&lt;&gt;"",INDIRECT(VLOOKUP(M15,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M16" xr:uid="{D636058B-248F-4675-AD1E-C7DD740499C2}">
+    <dataValidation type="list" sqref="M16" xr:uid="{28602A5B-7418-4BB5-A5FE-174AE69A7F05}">
       <formula1>=IF(L16&lt;&gt;"",INDIRECT(VLOOKUP(L16,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N16" xr:uid="{6F17783B-B8F1-42DC-BD93-F1B296E27875}">
+    <dataValidation type="list" sqref="N16" xr:uid="{47E658E4-2B40-4D2F-BBFD-6A7D066A70E0}">
       <formula1>=IF(M16&lt;&gt;"",INDIRECT(VLOOKUP(M16,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M17" xr:uid="{CC393835-EFBD-46E4-923A-B17B37606DE3}">
+    <dataValidation type="list" sqref="M17" xr:uid="{22756184-24E2-4333-8568-0B1202E07535}">
       <formula1>=IF(L17&lt;&gt;"",INDIRECT(VLOOKUP(L17,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N17" xr:uid="{4F10FA90-5B4F-478C-B593-EA4D07F11A45}">
+    <dataValidation type="list" sqref="N17" xr:uid="{43049FDA-AF66-4A0A-A224-3E6C25366CD9}">
       <formula1>=IF(M17&lt;&gt;"",INDIRECT(VLOOKUP(M17,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M18" xr:uid="{19A6C4EE-EE8B-45B4-8483-30D541E229B5}">
+    <dataValidation type="list" sqref="M18" xr:uid="{7380E9F2-2516-4688-A926-93C7F3FA82E3}">
       <formula1>=IF(L18&lt;&gt;"",INDIRECT(VLOOKUP(L18,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N18" xr:uid="{9C55549B-CCEA-44A4-B89E-304F872CC0FE}">
+    <dataValidation type="list" sqref="N18" xr:uid="{12B6A236-4DD6-45A7-B3A1-9CBE8AD3D5F6}">
       <formula1>=IF(M18&lt;&gt;"",INDIRECT(VLOOKUP(M18,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M19" xr:uid="{D205F6EA-C7FF-4E23-A763-525B598E58F2}">
+    <dataValidation type="list" sqref="M19" xr:uid="{731C7C07-532F-409A-A28C-E053CC65F6CC}">
       <formula1>=IF(L19&lt;&gt;"",INDIRECT(VLOOKUP(L19,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N19" xr:uid="{57984A1C-83A6-4621-A3B2-8DD5A01BA01B}">
+    <dataValidation type="list" sqref="N19" xr:uid="{6B133283-6B33-460C-8047-5506DFE30685}">
       <formula1>=IF(M19&lt;&gt;"",INDIRECT(VLOOKUP(M19,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M20" xr:uid="{8AABC37A-73D4-4FE9-9444-581AD0B1BC2D}">
+    <dataValidation type="list" sqref="M20" xr:uid="{74376745-C9D6-484F-9D2C-60B8F02FFE15}">
       <formula1>=IF(L20&lt;&gt;"",INDIRECT(VLOOKUP(L20,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N20" xr:uid="{65E2A2E7-BB0B-47BB-B4BC-F3B3A6E10D77}">
+    <dataValidation type="list" sqref="N20" xr:uid="{AF64561B-BCFD-43B4-8A19-C7E1F86A5DED}">
       <formula1>=IF(M20&lt;&gt;"",INDIRECT(VLOOKUP(M20,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M21" xr:uid="{4500621C-736C-4408-A401-3C69F592E0F4}">
+    <dataValidation type="list" sqref="M21" xr:uid="{9E01116F-ECB9-4712-BFC7-01C8F35AAADD}">
       <formula1>=IF(L21&lt;&gt;"",INDIRECT(VLOOKUP(L21,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N21" xr:uid="{9975E3F8-94E0-4FE8-BAEB-8A5DC2D34C05}">
+    <dataValidation type="list" sqref="N21" xr:uid="{0F824C06-3396-4570-A64C-7ED018A6D8EB}">
       <formula1>=IF(M21&lt;&gt;"",INDIRECT(VLOOKUP(M21,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M22" xr:uid="{114DC6E6-334B-4F59-AE85-136423D8A133}">
+    <dataValidation type="list" sqref="M22" xr:uid="{22153002-C8AB-4D41-98FA-812221B3CE3C}">
       <formula1>=IF(L22&lt;&gt;"",INDIRECT(VLOOKUP(L22,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N22" xr:uid="{DEDD2A85-E884-4114-A4E6-59A4D19A9845}">
+    <dataValidation type="list" sqref="N22" xr:uid="{2930FF28-20B0-4F44-A523-A320DE20B43D}">
       <formula1>=IF(M22&lt;&gt;"",INDIRECT(VLOOKUP(M22,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M23" xr:uid="{D69AD00A-F2F7-4713-9B4E-C10945A39C3E}">
+    <dataValidation type="list" sqref="M23" xr:uid="{43FA824A-1F5F-467A-9885-61B2405F7213}">
       <formula1>=IF(L23&lt;&gt;"",INDIRECT(VLOOKUP(L23,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N23" xr:uid="{2FB039AC-DCFB-476C-961A-091E05623D4B}">
+    <dataValidation type="list" sqref="N23" xr:uid="{3E6F2080-A825-43AB-8441-2B235F9E75E2}">
       <formula1>=IF(M23&lt;&gt;"",INDIRECT(VLOOKUP(M23,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M24" xr:uid="{115C2C21-2B0D-4031-B72B-C8F805978E96}">
+    <dataValidation type="list" sqref="M24" xr:uid="{9D6B6EAA-ADC7-45D5-B4C8-A557186C586C}">
       <formula1>=IF(L24&lt;&gt;"",INDIRECT(VLOOKUP(L24,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N24" xr:uid="{EEB50FA2-F954-41FD-B80C-6A6FAFFE4D25}">
+    <dataValidation type="list" sqref="N24" xr:uid="{7F878F2D-E720-4D30-A831-D2C58AC89124}">
       <formula1>=IF(M24&lt;&gt;"",INDIRECT(VLOOKUP(M24,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M25" xr:uid="{EA8F89BF-343E-46BF-A8E7-0223B3193345}">
+    <dataValidation type="list" sqref="M25" xr:uid="{66846943-6F77-4006-9C5D-D6F6E404943D}">
       <formula1>=IF(L25&lt;&gt;"",INDIRECT(VLOOKUP(L25,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N25" xr:uid="{4464EA55-4464-44BD-8F5A-97598B3D42A9}">
+    <dataValidation type="list" sqref="N25" xr:uid="{9908ABEF-7ABB-44B8-B170-1BB893DBBB41}">
       <formula1>=IF(M25&lt;&gt;"",INDIRECT(VLOOKUP(M25,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M26" xr:uid="{65ABDD01-03A4-4CFE-9E80-8998CEC91B97}">
+    <dataValidation type="list" sqref="M26" xr:uid="{8583B594-723F-47F4-84D0-5B00A3FF2F7C}">
       <formula1>=IF(L26&lt;&gt;"",INDIRECT(VLOOKUP(L26,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N26" xr:uid="{16629D83-D194-4C95-846C-20F48DBC6D39}">
+    <dataValidation type="list" sqref="N26" xr:uid="{F5E6F983-944A-4953-92B9-E6D0E40FC1C8}">
       <formula1>=IF(M26&lt;&gt;"",INDIRECT(VLOOKUP(M26,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M27" xr:uid="{5902F433-7140-4A29-A19B-853BF3D6374E}">
+    <dataValidation type="list" sqref="M27" xr:uid="{B30DD2C6-1185-4841-A0B2-4BD4B8E595D9}">
       <formula1>=IF(L27&lt;&gt;"",INDIRECT(VLOOKUP(L27,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N27" xr:uid="{B4B9AB13-A97F-44D8-9237-A77C61D56E59}">
+    <dataValidation type="list" sqref="N27" xr:uid="{D02357FF-8E70-4317-B8DC-D1F4FC1B8C47}">
       <formula1>=IF(M27&lt;&gt;"",INDIRECT(VLOOKUP(M27,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M28" xr:uid="{43E9BBD5-79D0-47ED-8846-C6C253F63F2D}">
+    <dataValidation type="list" sqref="M28" xr:uid="{B80CAAE8-BB5E-4159-BDC7-B6B4F38A0386}">
       <formula1>=IF(L28&lt;&gt;"",INDIRECT(VLOOKUP(L28,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N28" xr:uid="{9087FA39-AE5A-4684-BC09-E0C21E797DC8}">
+    <dataValidation type="list" sqref="N28" xr:uid="{99205A10-E330-43AE-92E8-935574BF5E0A}">
       <formula1>=IF(M28&lt;&gt;"",INDIRECT(VLOOKUP(M28,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M29" xr:uid="{32DD610E-2C20-4AB5-92CB-F8B075273061}">
+    <dataValidation type="list" sqref="M29" xr:uid="{152A2D3B-C86D-4FC6-8ED3-E78FF4BC6A1E}">
       <formula1>=IF(L29&lt;&gt;"",INDIRECT(VLOOKUP(L29,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N29" xr:uid="{BD009797-CB16-4147-B86A-3225466821D2}">
+    <dataValidation type="list" sqref="N29" xr:uid="{D8198A33-9434-43F8-B2E1-D152568D2B8F}">
       <formula1>=IF(M29&lt;&gt;"",INDIRECT(VLOOKUP(M29,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M30" xr:uid="{93645275-2B51-45E0-8B95-F7B87347403C}">
+    <dataValidation type="list" sqref="M30" xr:uid="{398CC339-F84F-4444-BF0E-75329B81C991}">
       <formula1>=IF(L30&lt;&gt;"",INDIRECT(VLOOKUP(L30,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N30" xr:uid="{468D2FB5-6D80-4C8A-A523-CE2D33AD816B}">
+    <dataValidation type="list" sqref="N30" xr:uid="{68F1B4BC-FD41-485C-A26C-9517C22895BE}">
       <formula1>=IF(M30&lt;&gt;"",INDIRECT(VLOOKUP(M30,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M31" xr:uid="{DBD29876-8314-495F-9E4D-285CB81F7FD8}">
+    <dataValidation type="list" sqref="M31" xr:uid="{70CA6E7C-0E1B-4954-85DC-083DCDA188D7}">
       <formula1>=IF(L31&lt;&gt;"",INDIRECT(VLOOKUP(L31,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N31" xr:uid="{01C32535-FB07-425F-B0D3-6F7DE2CDBBF2}">
+    <dataValidation type="list" sqref="N31" xr:uid="{97318338-2315-4C32-83D4-0F0E20657A4C}">
       <formula1>=IF(M31&lt;&gt;"",INDIRECT(VLOOKUP(M31,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M32" xr:uid="{AF968805-3E41-4D72-A5E5-3080001EF7A3}">
+    <dataValidation type="list" sqref="M32" xr:uid="{1D8194D2-6CBD-478F-BB5A-EB2BD06BFA2E}">
       <formula1>=IF(L32&lt;&gt;"",INDIRECT(VLOOKUP(L32,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N32" xr:uid="{4FAF62FE-9D89-466F-8DD2-318B14069F0B}">
+    <dataValidation type="list" sqref="N32" xr:uid="{1389C4C3-3763-453A-B667-3A8980308412}">
       <formula1>=IF(M32&lt;&gt;"",INDIRECT(VLOOKUP(M32,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M33" xr:uid="{2218F329-4C61-4929-ACF7-4652BA469B62}">
+    <dataValidation type="list" sqref="M33" xr:uid="{2BFC4AD1-4BF1-44F4-971A-903A3E87A64A}">
       <formula1>=IF(L33&lt;&gt;"",INDIRECT(VLOOKUP(L33,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N33" xr:uid="{954C034E-665A-4974-A6D8-6B984B766A4B}">
+    <dataValidation type="list" sqref="N33" xr:uid="{414A9635-D1BF-4A57-B817-3BC890F65548}">
       <formula1>=IF(M33&lt;&gt;"",INDIRECT(VLOOKUP(M33,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M34" xr:uid="{9516CE5C-AB26-4718-A75F-4ED7215AF66F}">
+    <dataValidation type="list" sqref="M34" xr:uid="{EC6AE861-B42D-411C-A936-9C686B5AF258}">
       <formula1>=IF(L34&lt;&gt;"",INDIRECT(VLOOKUP(L34,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N34" xr:uid="{F6F68E9D-A6A5-4D4B-81DD-F7743B1BD4D9}">
+    <dataValidation type="list" sqref="N34" xr:uid="{E100B2A7-05D9-4770-916D-BC2783126DE5}">
       <formula1>=IF(M34&lt;&gt;"",INDIRECT(VLOOKUP(M34,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M35" xr:uid="{C724C295-3E21-4996-B357-426C86B89062}">
+    <dataValidation type="list" sqref="M35" xr:uid="{D988425B-A01A-400E-B99E-5021F3C96CEE}">
       <formula1>=IF(L35&lt;&gt;"",INDIRECT(VLOOKUP(L35,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N35" xr:uid="{EE460055-26E0-472A-8E72-EA8FBB91DCB8}">
+    <dataValidation type="list" sqref="N35" xr:uid="{0B3FBC75-1BDF-45A8-B760-D0739A094B8D}">
       <formula1>=IF(M35&lt;&gt;"",INDIRECT(VLOOKUP(M35,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M36" xr:uid="{AFF55D88-3BBC-4F4A-B6C8-3FD5F8237A71}">
+    <dataValidation type="list" sqref="M36" xr:uid="{B7722222-5564-4AC8-A383-A44649196E3B}">
       <formula1>=IF(L36&lt;&gt;"",INDIRECT(VLOOKUP(L36,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N36" xr:uid="{8A7A155F-460F-4785-B03B-09D2EC24E288}">
+    <dataValidation type="list" sqref="N36" xr:uid="{9C9CFF7A-CC85-4513-ABE3-5C2501D9BA8B}">
       <formula1>=IF(M36&lt;&gt;"",INDIRECT(VLOOKUP(M36,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M37" xr:uid="{B0F91D17-F2B6-48FB-965B-189DB79EEB54}">
+    <dataValidation type="list" sqref="M37" xr:uid="{334391C0-B4B0-4939-BBDD-53D3429C4440}">
       <formula1>=IF(L37&lt;&gt;"",INDIRECT(VLOOKUP(L37,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N37" xr:uid="{4DF9D833-9429-45A0-80AD-7B918FC9D345}">
+    <dataValidation type="list" sqref="N37" xr:uid="{9108D71C-969C-4199-8ED7-FE9F12B0C621}">
       <formula1>=IF(M37&lt;&gt;"",INDIRECT(VLOOKUP(M37,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M38" xr:uid="{28B9826D-CE7F-4BBD-99B7-146C786BC072}">
+    <dataValidation type="list" sqref="M38" xr:uid="{A2EAB137-EF75-41C9-A839-6B444838AE63}">
       <formula1>=IF(L38&lt;&gt;"",INDIRECT(VLOOKUP(L38,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N38" xr:uid="{38BBD57B-89ED-4793-B9E3-241141930BC1}">
+    <dataValidation type="list" sqref="N38" xr:uid="{C3A47F9A-2148-4C63-80FC-4BCCE13C93D9}">
       <formula1>=IF(M38&lt;&gt;"",INDIRECT(VLOOKUP(M38,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M39" xr:uid="{951231FB-CB9C-46C2-8097-F32494612953}">
+    <dataValidation type="list" sqref="M39" xr:uid="{C8CCC356-14B6-4E7C-917B-27EFE587CE75}">
       <formula1>=IF(L39&lt;&gt;"",INDIRECT(VLOOKUP(L39,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N39" xr:uid="{11521C43-E449-42EF-91AD-69B9495614EB}">
+    <dataValidation type="list" sqref="N39" xr:uid="{9F62B170-1155-43C8-A9CC-49D12C56391D}">
       <formula1>=IF(M39&lt;&gt;"",INDIRECT(VLOOKUP(M39,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M40" xr:uid="{122BF1D5-EC8D-4EF2-AB06-6881FEFE7318}">
+    <dataValidation type="list" sqref="M40" xr:uid="{7D38D41F-9E09-4409-974F-26201A7DF84E}">
       <formula1>=IF(L40&lt;&gt;"",INDIRECT(VLOOKUP(L40,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N40" xr:uid="{AE237F3D-C055-4DAD-B615-9EA0BAF976A7}">
+    <dataValidation type="list" sqref="N40" xr:uid="{E54EF0C6-2009-4927-A4A1-097B889FA265}">
       <formula1>=IF(M40&lt;&gt;"",INDIRECT(VLOOKUP(M40,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M41" xr:uid="{63E69A2B-C6CC-4E78-A842-BF15754F17BE}">
+    <dataValidation type="list" sqref="M41" xr:uid="{9AA442CB-1CCC-4097-84E8-0FC19A534C1D}">
       <formula1>=IF(L41&lt;&gt;"",INDIRECT(VLOOKUP(L41,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N41" xr:uid="{0EDB8117-2B49-490B-9D74-8CCA164FEA17}">
+    <dataValidation type="list" sqref="N41" xr:uid="{09774392-AFC0-4D93-85FF-F27DAF1B8776}">
       <formula1>=IF(M41&lt;&gt;"",INDIRECT(VLOOKUP(M41,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M42" xr:uid="{CD36877A-2886-4190-9128-78777F55135C}">
+    <dataValidation type="list" sqref="M42" xr:uid="{72840077-476E-4C4F-B24D-37FC39E5E45C}">
       <formula1>=IF(L42&lt;&gt;"",INDIRECT(VLOOKUP(L42,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N42" xr:uid="{78603E37-F371-4F07-A562-951779796EF4}">
+    <dataValidation type="list" sqref="N42" xr:uid="{DC54B18B-C18F-4DC0-AD17-14481FD93A0F}">
       <formula1>=IF(M42&lt;&gt;"",INDIRECT(VLOOKUP(M42,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M43" xr:uid="{90CF2C65-4D7C-4673-8ED5-7CBB803F7976}">
+    <dataValidation type="list" sqref="M43" xr:uid="{8E1F6BA3-8643-4585-B64D-B6FF12293551}">
       <formula1>=IF(L43&lt;&gt;"",INDIRECT(VLOOKUP(L43,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N43" xr:uid="{2FA46E38-9637-4B19-AFAA-81C925932DE1}">
+    <dataValidation type="list" sqref="N43" xr:uid="{E87BFFE5-CFB0-4A9E-A7E7-773D21EBC485}">
       <formula1>=IF(M43&lt;&gt;"",INDIRECT(VLOOKUP(M43,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M44" xr:uid="{BACF42BC-BC5A-497D-82F6-B5DD665D4647}">
+    <dataValidation type="list" sqref="M44" xr:uid="{F1742A1C-978C-4DD6-8C50-475055D97F6C}">
       <formula1>=IF(L44&lt;&gt;"",INDIRECT(VLOOKUP(L44,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N44" xr:uid="{60D76308-AFA3-4DC2-AFFB-1BE545F49E5F}">
+    <dataValidation type="list" sqref="N44" xr:uid="{4DD9310D-EB8E-46F7-BBCC-322B13C61A7C}">
       <formula1>=IF(M44&lt;&gt;"",INDIRECT(VLOOKUP(M44,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M45" xr:uid="{A29B4A2E-1CEA-434A-A912-4F276E44FC87}">
+    <dataValidation type="list" sqref="M45" xr:uid="{D6E7CC9A-45DC-4CC4-96D7-971A5143E864}">
       <formula1>=IF(L45&lt;&gt;"",INDIRECT(VLOOKUP(L45,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N45" xr:uid="{3BC43F60-A896-4D23-AAE7-3348B4F0666C}">
+    <dataValidation type="list" sqref="N45" xr:uid="{058B376E-594A-49BB-8327-72F4FF9D3E49}">
       <formula1>=IF(M45&lt;&gt;"",INDIRECT(VLOOKUP(M45,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M46" xr:uid="{73E3ACC7-704F-463A-B25D-82C99ED17209}">
+    <dataValidation type="list" sqref="M46" xr:uid="{B3482ADC-30A3-41DE-A637-5B5C0B895E5F}">
       <formula1>=IF(L46&lt;&gt;"",INDIRECT(VLOOKUP(L46,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N46" xr:uid="{CEA0FAF8-1A68-4BEB-AE65-620C84DF44CE}">
+    <dataValidation type="list" sqref="N46" xr:uid="{2875CC08-C377-43D7-820B-0210BD65DACB}">
       <formula1>=IF(M46&lt;&gt;"",INDIRECT(VLOOKUP(M46,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M47" xr:uid="{E2FD1B08-CF3F-464E-BDE3-0CD89C42DCD5}">
+    <dataValidation type="list" sqref="M47" xr:uid="{C87D5279-8071-443A-9FB2-B0CB76E7BD72}">
       <formula1>=IF(L47&lt;&gt;"",INDIRECT(VLOOKUP(L47,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N47" xr:uid="{DC86D6A5-3663-4381-B615-35DFC494A6FE}">
+    <dataValidation type="list" sqref="N47" xr:uid="{E6332450-69C5-4C49-B04A-B65BE711AEC9}">
       <formula1>=IF(M47&lt;&gt;"",INDIRECT(VLOOKUP(M47,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M48" xr:uid="{2A8E7A9E-1A84-44BD-BF82-A273907BE2A6}">
+    <dataValidation type="list" sqref="M48" xr:uid="{646A78FB-5BB4-4347-AB98-7E4A4FE705E0}">
       <formula1>=IF(L48&lt;&gt;"",INDIRECT(VLOOKUP(L48,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N48" xr:uid="{36F3A12B-126E-4881-B0FE-48C7DA100A0C}">
+    <dataValidation type="list" sqref="N48" xr:uid="{79BD7D14-4723-4E7C-A505-6AD68D345885}">
       <formula1>=IF(M48&lt;&gt;"",INDIRECT(VLOOKUP(M48,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M49" xr:uid="{B9927365-7A98-4287-BB83-12772180AC28}">
+    <dataValidation type="list" sqref="M49" xr:uid="{2AB590FF-331E-4574-92F1-1ACC47F43A88}">
       <formula1>=IF(L49&lt;&gt;"",INDIRECT(VLOOKUP(L49,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N49" xr:uid="{89D01AE9-0025-439F-BBD3-956D042C4765}">
+    <dataValidation type="list" sqref="N49" xr:uid="{7F29EAA4-0873-49E1-A961-8C1C158D06F7}">
       <formula1>=IF(M49&lt;&gt;"",INDIRECT(VLOOKUP(M49,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M50" xr:uid="{B5A1AEB0-8F39-4A22-BEBC-8E3EFF1E6CBC}">
+    <dataValidation type="list" sqref="M50" xr:uid="{F7F183BF-AB9A-461B-BD4D-7A4526B20C8C}">
       <formula1>=IF(L50&lt;&gt;"",INDIRECT(VLOOKUP(L50,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N50" xr:uid="{C725468D-A8FF-4D16-AD4B-935E89A88D93}">
+    <dataValidation type="list" sqref="N50" xr:uid="{FBFB128C-9CF7-4EE2-83E7-33D3E6272F34}">
       <formula1>=IF(M50&lt;&gt;"",INDIRECT(VLOOKUP(M50,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M51" xr:uid="{60A15773-C50C-4341-BDED-4B5D49F36960}">
+    <dataValidation type="list" sqref="M51" xr:uid="{F676A796-49A6-4859-93F1-9CBE243B42B9}">
       <formula1>=IF(L51&lt;&gt;"",INDIRECT(VLOOKUP(L51,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N51" xr:uid="{1B42C6E5-F5C2-4E88-B3F5-56B33F23D4D3}">
+    <dataValidation type="list" sqref="N51" xr:uid="{F67DD791-E272-4DEB-8491-2C64AC3EEFCC}">
       <formula1>=IF(M51&lt;&gt;"",INDIRECT(VLOOKUP(M51,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M52" xr:uid="{6F6679BA-2273-4ACA-8FF5-0FCBF334F7CC}">
+    <dataValidation type="list" sqref="M52" xr:uid="{8E6C8905-A0DA-4451-A7F0-77AAE8E51670}">
       <formula1>=IF(L52&lt;&gt;"",INDIRECT(VLOOKUP(L52,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N52" xr:uid="{F7DF70DF-9744-467F-B0F5-00F15BBF4C48}">
+    <dataValidation type="list" sqref="N52" xr:uid="{C4445BBF-8897-467C-B4DD-098F1F467D69}">
       <formula1>=IF(M52&lt;&gt;"",INDIRECT(VLOOKUP(M52,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M53" xr:uid="{CEC60A18-56AE-484B-A975-77FA1C381C7E}">
+    <dataValidation type="list" sqref="M53" xr:uid="{025D35D0-3432-470D-8688-E17DCE9C0AD3}">
       <formula1>=IF(L53&lt;&gt;"",INDIRECT(VLOOKUP(L53,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N53" xr:uid="{817D3DA7-E0DE-498B-BD3F-61B30BB5DA9E}">
+    <dataValidation type="list" sqref="N53" xr:uid="{A61612F7-4C40-40C2-84C6-416AE6FEAC16}">
       <formula1>=IF(M53&lt;&gt;"",INDIRECT(VLOOKUP(M53,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M54" xr:uid="{B7CBF283-48EB-44BF-80BF-80086CE63365}">
+    <dataValidation type="list" sqref="M54" xr:uid="{52D9422D-9AB4-454E-B2E3-E17C3266E806}">
       <formula1>=IF(L54&lt;&gt;"",INDIRECT(VLOOKUP(L54,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N54" xr:uid="{E4995DD3-E6ED-4D11-95A2-4FC52E12F32D}">
+    <dataValidation type="list" sqref="N54" xr:uid="{E32D8346-D333-4609-8E51-F19EE9739E44}">
       <formula1>=IF(M54&lt;&gt;"",INDIRECT(VLOOKUP(M54,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M55" xr:uid="{E8F60022-9019-4D02-AD55-FC1A3FE53B2A}">
+    <dataValidation type="list" sqref="M55" xr:uid="{C9EED16D-AD60-4B8A-BF66-88D6ACBACA6D}">
       <formula1>=IF(L55&lt;&gt;"",INDIRECT(VLOOKUP(L55,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N55" xr:uid="{EEB35BCD-6CF0-4733-B313-1183F69442CA}">
+    <dataValidation type="list" sqref="N55" xr:uid="{67924E0E-02D0-45C0-BD1E-23C38FCC473F}">
       <formula1>=IF(M55&lt;&gt;"",INDIRECT(VLOOKUP(M55,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M56" xr:uid="{36522A15-316C-4623-B36C-5BFE7A99C1EC}">
+    <dataValidation type="list" sqref="M56" xr:uid="{C1C97A6A-1B39-47B7-8892-E573E129343B}">
       <formula1>=IF(L56&lt;&gt;"",INDIRECT(VLOOKUP(L56,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N56" xr:uid="{D0767713-7A83-4CA8-A801-60B4EA7BFEF8}">
+    <dataValidation type="list" sqref="N56" xr:uid="{6C594F3F-8985-4288-BEAC-30FDA26BB354}">
       <formula1>=IF(M56&lt;&gt;"",INDIRECT(VLOOKUP(M56,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M57" xr:uid="{F6C89D68-64BD-4551-A661-AD851D74D454}">
+    <dataValidation type="list" sqref="M57" xr:uid="{8C6827D6-46F3-438A-B445-B3857A69F006}">
       <formula1>=IF(L57&lt;&gt;"",INDIRECT(VLOOKUP(L57,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N57" xr:uid="{7287D977-674B-4A79-8F3A-89ADB3DDB4BF}">
+    <dataValidation type="list" sqref="N57" xr:uid="{AF52A2D4-8298-47BD-B055-E2AB1CC4F1F1}">
       <formula1>=IF(M57&lt;&gt;"",INDIRECT(VLOOKUP(M57,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M58" xr:uid="{19940524-883F-40CA-A7E4-8F69E05D9236}">
+    <dataValidation type="list" sqref="M58" xr:uid="{0A757C47-DF72-49FB-853E-2911FFEE197C}">
       <formula1>=IF(L58&lt;&gt;"",INDIRECT(VLOOKUP(L58,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N58" xr:uid="{C881441A-BC1F-4055-BC1E-78C6DB7AD108}">
+    <dataValidation type="list" sqref="N58" xr:uid="{82247B13-E9D8-4B61-96C6-8BF34A85E34F}">
       <formula1>=IF(M58&lt;&gt;"",INDIRECT(VLOOKUP(M58,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M59" xr:uid="{9A1A89BA-2C5F-455C-8601-C88813CA37D1}">
+    <dataValidation type="list" sqref="M59" xr:uid="{8AF33EF9-4BCC-4F3E-AEFC-1736F55DFEDB}">
       <formula1>=IF(L59&lt;&gt;"",INDIRECT(VLOOKUP(L59,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N59" xr:uid="{627A8613-819C-472D-9515-B8E49802B0C2}">
+    <dataValidation type="list" sqref="N59" xr:uid="{A1EE052C-96CE-4B42-8207-469D7EF20001}">
       <formula1>=IF(M59&lt;&gt;"",INDIRECT(VLOOKUP(M59,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M60" xr:uid="{8E7FE6A7-7EB1-494D-A1D7-ED741B39EBFC}">
+    <dataValidation type="list" sqref="M60" xr:uid="{E2A52421-DFD5-4F71-AF58-DDA4E59D2676}">
       <formula1>=IF(L60&lt;&gt;"",INDIRECT(VLOOKUP(L60,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N60" xr:uid="{5FF75E5E-A43C-48D0-843E-578D76AF26AA}">
+    <dataValidation type="list" sqref="N60" xr:uid="{DF6B800E-450C-45E3-8BDE-CF1CFB54EAC9}">
       <formula1>=IF(M60&lt;&gt;"",INDIRECT(VLOOKUP(M60,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M61" xr:uid="{21A67CC3-882E-4312-A743-C6A815936E02}">
+    <dataValidation type="list" sqref="M61" xr:uid="{6574D916-AB15-4113-B493-E084451034F8}">
       <formula1>=IF(L61&lt;&gt;"",INDIRECT(VLOOKUP(L61,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N61" xr:uid="{0ED9807A-B267-46F7-8948-95C4D2F03D1F}">
+    <dataValidation type="list" sqref="N61" xr:uid="{979C4D1F-D9B2-4A65-95F9-1F13DCE3FE5B}">
       <formula1>=IF(M61&lt;&gt;"",INDIRECT(VLOOKUP(M61,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M62" xr:uid="{124A63D7-2D5B-46F3-8701-DE5085CDDEE7}">
+    <dataValidation type="list" sqref="M62" xr:uid="{3D6A0D2D-316B-415D-962A-2945A6C59106}">
       <formula1>=IF(L62&lt;&gt;"",INDIRECT(VLOOKUP(L62,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N62" xr:uid="{B33CA4AF-2D00-44C5-B909-14549C43B6C2}">
+    <dataValidation type="list" sqref="N62" xr:uid="{3CC7AADF-0A60-40FF-A5BC-67EEE2717835}">
       <formula1>=IF(M62&lt;&gt;"",INDIRECT(VLOOKUP(M62,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M63" xr:uid="{C17593F5-0005-4AB5-8DD2-364B9532F8F8}">
+    <dataValidation type="list" sqref="M63" xr:uid="{2D380C6D-2F87-4308-A087-C83777C63EB8}">
       <formula1>=IF(L63&lt;&gt;"",INDIRECT(VLOOKUP(L63,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N63" xr:uid="{FEFEAD1F-234E-43F0-BBC9-91826C3C45E2}">
+    <dataValidation type="list" sqref="N63" xr:uid="{C33378F3-F880-4191-A852-C1CD99E2273E}">
       <formula1>=IF(M63&lt;&gt;"",INDIRECT(VLOOKUP(M63,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M64" xr:uid="{BA0EDD2D-EFC7-4010-B04F-C6FFE722BB53}">
+    <dataValidation type="list" sqref="M64" xr:uid="{618795E5-0FD5-4872-A25B-351BDAA41C75}">
       <formula1>=IF(L64&lt;&gt;"",INDIRECT(VLOOKUP(L64,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N64" xr:uid="{FDB916FD-B13C-4A52-8109-E511D26963FE}">
+    <dataValidation type="list" sqref="N64" xr:uid="{B742D97E-CD35-498E-BA95-66F2E7DA8BEF}">
       <formula1>=IF(M64&lt;&gt;"",INDIRECT(VLOOKUP(M64,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M65" xr:uid="{2BFB3688-D172-48EB-B9A1-A682EF4D2C2E}">
+    <dataValidation type="list" sqref="M65" xr:uid="{06C3D699-7DCE-48FA-B75C-65332007C5E6}">
       <formula1>=IF(L65&lt;&gt;"",INDIRECT(VLOOKUP(L65,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N65" xr:uid="{F9611368-4C5D-4C2F-8400-B98564C024D5}">
+    <dataValidation type="list" sqref="N65" xr:uid="{2CD7D871-0618-4416-891C-CF69064ACFE8}">
       <formula1>=IF(M65&lt;&gt;"",INDIRECT(VLOOKUP(M65,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M66" xr:uid="{27F8A4AE-9B1E-4E00-94C8-ED77CA906762}">
+    <dataValidation type="list" sqref="M66" xr:uid="{7802832B-319E-4B4B-927E-871516E41FAB}">
       <formula1>=IF(L66&lt;&gt;"",INDIRECT(VLOOKUP(L66,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N66" xr:uid="{FA72D0E5-F40A-4780-B17C-CC84316E5A36}">
+    <dataValidation type="list" sqref="N66" xr:uid="{D79E7F4C-9242-425E-9994-934CBBA5A70B}">
       <formula1>=IF(M66&lt;&gt;"",INDIRECT(VLOOKUP(M66,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M67" xr:uid="{26770B6A-EE64-48E2-8D46-C06744CEEE4D}">
+    <dataValidation type="list" sqref="M67" xr:uid="{4ECA7A2F-618F-4CD3-8992-EEEA8175FB7B}">
       <formula1>=IF(L67&lt;&gt;"",INDIRECT(VLOOKUP(L67,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N67" xr:uid="{36B1D887-742B-4C87-A1CA-9251A4FD7506}">
+    <dataValidation type="list" sqref="N67" xr:uid="{C194272E-7880-419F-BDD2-60CD6126D291}">
       <formula1>=IF(M67&lt;&gt;"",INDIRECT(VLOOKUP(M67,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M68" xr:uid="{06FAB561-9A82-4BDF-B119-1BE54C229D8F}">
+    <dataValidation type="list" sqref="M68" xr:uid="{5C497880-DB6B-41E7-A17C-FD6F41A2D2B9}">
       <formula1>=IF(L68&lt;&gt;"",INDIRECT(VLOOKUP(L68,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N68" xr:uid="{3EA0AD43-CB87-43B7-847E-22FBF56B4B77}">
+    <dataValidation type="list" sqref="N68" xr:uid="{E08BC3A9-AE3A-4F40-90A4-9B2FB3465E1E}">
       <formula1>=IF(M68&lt;&gt;"",INDIRECT(VLOOKUP(M68,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M69" xr:uid="{53D321B5-9F15-4C8E-909A-4D109509BEB9}">
+    <dataValidation type="list" sqref="M69" xr:uid="{A2017E80-C54C-43E3-88AF-771787A1DB22}">
       <formula1>=IF(L69&lt;&gt;"",INDIRECT(VLOOKUP(L69,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N69" xr:uid="{68919276-32EC-4545-98C2-B19245A6BCDF}">
+    <dataValidation type="list" sqref="N69" xr:uid="{49D2BA7F-3118-4686-904F-CCC153079018}">
       <formula1>=IF(M69&lt;&gt;"",INDIRECT(VLOOKUP(M69,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M70" xr:uid="{77B15AF4-35AA-45E2-BB7C-2D06C92D5059}">
+    <dataValidation type="list" sqref="M70" xr:uid="{AED63CF9-1124-4D91-998A-DA5F318CCF6B}">
       <formula1>=IF(L70&lt;&gt;"",INDIRECT(VLOOKUP(L70,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N70" xr:uid="{D18C381F-675D-4383-BFC7-6DBDD8ECE24A}">
+    <dataValidation type="list" sqref="N70" xr:uid="{2F5A7164-BBDA-46E7-9138-E5C4C896E413}">
       <formula1>=IF(M70&lt;&gt;"",INDIRECT(VLOOKUP(M70,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M71" xr:uid="{F0A61632-CA3D-47E2-8A66-89DF3B23CAC5}">
+    <dataValidation type="list" sqref="M71" xr:uid="{4E30BE65-3966-47A8-964B-1C983D6FE304}">
       <formula1>=IF(L71&lt;&gt;"",INDIRECT(VLOOKUP(L71,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N71" xr:uid="{942CBD9A-7DC6-4146-A95E-F1BAD7544F0F}">
+    <dataValidation type="list" sqref="N71" xr:uid="{FAE299BB-325B-4254-B557-9F150AD2F3E9}">
       <formula1>=IF(M71&lt;&gt;"",INDIRECT(VLOOKUP(M71,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M72" xr:uid="{FE3D5123-8AD4-40E7-9524-7F862E7181DD}">
+    <dataValidation type="list" sqref="M72" xr:uid="{F9A1BEAE-E466-4E85-A69B-E5E32278C291}">
       <formula1>=IF(L72&lt;&gt;"",INDIRECT(VLOOKUP(L72,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N72" xr:uid="{EB306A01-A794-4450-A912-5C0A1A296153}">
+    <dataValidation type="list" sqref="N72" xr:uid="{EB6F2BD4-95AC-406B-8810-5823374586C6}">
       <formula1>=IF(M72&lt;&gt;"",INDIRECT(VLOOKUP(M72,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M73" xr:uid="{84AD3A1C-DFE6-4302-A278-A74BF023B186}">
+    <dataValidation type="list" sqref="M73" xr:uid="{2947B47A-2CD5-4C98-A035-D1CA08270CAE}">
       <formula1>=IF(L73&lt;&gt;"",INDIRECT(VLOOKUP(L73,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N73" xr:uid="{41A66315-6AB4-4E16-BE08-07E5C10032A4}">
+    <dataValidation type="list" sqref="N73" xr:uid="{F6663B43-50CA-4691-B510-39D43BB54F4B}">
       <formula1>=IF(M73&lt;&gt;"",INDIRECT(VLOOKUP(M73,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M74" xr:uid="{85117A2D-4C67-4891-B3FF-18697E87903E}">
+    <dataValidation type="list" sqref="M74" xr:uid="{27E8AC52-7B5A-4471-B82E-9E8B9420956A}">
       <formula1>=IF(L74&lt;&gt;"",INDIRECT(VLOOKUP(L74,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N74" xr:uid="{6A94EC14-7C98-41B4-9DA8-0C62B51C763D}">
+    <dataValidation type="list" sqref="N74" xr:uid="{6E25A0DB-016D-495E-BA29-3A58DEA5611E}">
       <formula1>=IF(M74&lt;&gt;"",INDIRECT(VLOOKUP(M74,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M75" xr:uid="{4055EF1D-555F-40AD-9BD6-E39327B530A5}">
+    <dataValidation type="list" sqref="M75" xr:uid="{88802CE2-80EC-4086-9B5E-1E7545EBA669}">
       <formula1>=IF(L75&lt;&gt;"",INDIRECT(VLOOKUP(L75,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N75" xr:uid="{6075063B-112E-4599-9E56-D2BD0194196A}">
+    <dataValidation type="list" sqref="N75" xr:uid="{4D46D532-164B-4B6D-B905-CCCE26527CAC}">
       <formula1>=IF(M75&lt;&gt;"",INDIRECT(VLOOKUP(M75,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M76" xr:uid="{805C91B1-2CA1-4915-B142-10AC5DCFB413}">
+    <dataValidation type="list" sqref="M76" xr:uid="{CBDE9792-1B59-4CB0-8C94-29EDADA174D6}">
       <formula1>=IF(L76&lt;&gt;"",INDIRECT(VLOOKUP(L76,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N76" xr:uid="{02C6C368-7B82-4415-8B7B-6559AEE54FC4}">
+    <dataValidation type="list" sqref="N76" xr:uid="{D8A44ADC-110E-444D-AB60-5273A7C324BD}">
       <formula1>=IF(M76&lt;&gt;"",INDIRECT(VLOOKUP(M76,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M77" xr:uid="{D7877A9F-3BB7-4C96-8194-8B138F0066BA}">
+    <dataValidation type="list" sqref="M77" xr:uid="{FE187C17-C126-4232-AF59-A554A9F6F562}">
       <formula1>=IF(L77&lt;&gt;"",INDIRECT(VLOOKUP(L77,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N77" xr:uid="{7D2032F0-E138-4082-83C0-1AD9BF2E8D0C}">
+    <dataValidation type="list" sqref="N77" xr:uid="{5586AF08-CB40-4A6D-883B-D577D9119790}">
       <formula1>=IF(M77&lt;&gt;"",INDIRECT(VLOOKUP(M77,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M78" xr:uid="{95C5FD1B-6B59-444F-98B0-BB735393AFC9}">
+    <dataValidation type="list" sqref="M78" xr:uid="{29A1592E-4429-438C-B917-336D7F04AD1A}">
       <formula1>=IF(L78&lt;&gt;"",INDIRECT(VLOOKUP(L78,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N78" xr:uid="{9C8432BF-7202-4D43-B4F1-0882401BF2C6}">
+    <dataValidation type="list" sqref="N78" xr:uid="{C58BBF51-68B4-405E-9AE8-39F5D6838FE7}">
       <formula1>=IF(M78&lt;&gt;"",INDIRECT(VLOOKUP(M78,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M79" xr:uid="{0646AE1D-8073-49B7-83FB-F1FAD69C8F35}">
+    <dataValidation type="list" sqref="M79" xr:uid="{375B8183-E420-4B9F-BF30-B12BD18E94CD}">
       <formula1>=IF(L79&lt;&gt;"",INDIRECT(VLOOKUP(L79,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N79" xr:uid="{BC760E8D-0D2A-4FC0-9E3B-3CAC678F7428}">
+    <dataValidation type="list" sqref="N79" xr:uid="{78029853-AE9E-4E69-ABB2-E0B63DF8A742}">
       <formula1>=IF(M79&lt;&gt;"",INDIRECT(VLOOKUP(M79,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M80" xr:uid="{BE83C5F1-E003-4707-9E69-A12D3DD57B34}">
+    <dataValidation type="list" sqref="M80" xr:uid="{A2786073-CAC7-46E8-9B4A-53D76CDE59F6}">
       <formula1>=IF(L80&lt;&gt;"",INDIRECT(VLOOKUP(L80,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N80" xr:uid="{65A1FFFA-9D66-4AA5-B5BF-A999198CDD19}">
+    <dataValidation type="list" sqref="N80" xr:uid="{84780E1B-FF6B-4D02-920D-C9BE7BC532F9}">
       <formula1>=IF(M80&lt;&gt;"",INDIRECT(VLOOKUP(M80,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M81" xr:uid="{28660974-2093-41FC-B9B5-75FA9BD00F81}">
+    <dataValidation type="list" sqref="M81" xr:uid="{94477EF1-DABE-414C-ADBC-4B549FCA97EB}">
       <formula1>=IF(L81&lt;&gt;"",INDIRECT(VLOOKUP(L81,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N81" xr:uid="{322C97CC-AD36-4CA2-B05B-400DE47D1185}">
+    <dataValidation type="list" sqref="N81" xr:uid="{E246FED5-7D9B-42E8-B8FA-DA2ACAC40533}">
       <formula1>=IF(M81&lt;&gt;"",INDIRECT(VLOOKUP(M81,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M82" xr:uid="{998F431D-CA04-40F6-A4EE-AB32DF1FB6EF}">
+    <dataValidation type="list" sqref="M82" xr:uid="{2186426C-E16E-4F36-ABA0-77454918DCE3}">
       <formula1>=IF(L82&lt;&gt;"",INDIRECT(VLOOKUP(L82,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N82" xr:uid="{511822EA-3B77-4C0C-9B12-B8628E732FA0}">
+    <dataValidation type="list" sqref="N82" xr:uid="{9F27CA44-67A3-48D9-AB62-00FF997C0264}">
       <formula1>=IF(M82&lt;&gt;"",INDIRECT(VLOOKUP(M82,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M83" xr:uid="{2F5B502D-078E-4F0D-B781-D860B8B6FB93}">
+    <dataValidation type="list" sqref="M83" xr:uid="{B18D46DD-C4BA-4CDA-815E-D642FDF70D59}">
       <formula1>=IF(L83&lt;&gt;"",INDIRECT(VLOOKUP(L83,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N83" xr:uid="{ED4FEFB1-2D65-4128-831D-D41756DFD3C9}">
+    <dataValidation type="list" sqref="N83" xr:uid="{5DA6DDB3-3D77-49B5-B649-A7F6DC77BB0F}">
       <formula1>=IF(M83&lt;&gt;"",INDIRECT(VLOOKUP(M83,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M84" xr:uid="{D710A604-6C2F-4F53-99CB-59CFDD18D9BA}">
+    <dataValidation type="list" sqref="M84" xr:uid="{8FDDE213-C211-4C3C-B130-26A21C01AFFE}">
       <formula1>=IF(L84&lt;&gt;"",INDIRECT(VLOOKUP(L84,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N84" xr:uid="{EB1ACFCC-10F7-40AC-AF1E-C67D157E5288}">
+    <dataValidation type="list" sqref="N84" xr:uid="{BE921E9C-47C7-4A3C-9999-D30B32768AE4}">
       <formula1>=IF(M84&lt;&gt;"",INDIRECT(VLOOKUP(M84,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M85" xr:uid="{A1AC73E0-1C4B-4A5C-A5BF-3DCD6500F353}">
+    <dataValidation type="list" sqref="M85" xr:uid="{5207C77C-C0D8-4BAB-A528-3B2A10BDA41C}">
       <formula1>=IF(L85&lt;&gt;"",INDIRECT(VLOOKUP(L85,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N85" xr:uid="{1426DA52-74D1-41D2-87C8-6A3788B809F7}">
+    <dataValidation type="list" sqref="N85" xr:uid="{11549CF5-9AF2-41E7-AF4D-3F2198165BBD}">
       <formula1>=IF(M85&lt;&gt;"",INDIRECT(VLOOKUP(M85,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M86" xr:uid="{51FE8F3D-966F-4A97-B67A-D73EC40FA0B4}">
+    <dataValidation type="list" sqref="M86" xr:uid="{313A37AD-4C39-4753-BD9C-78A4ED91391D}">
       <formula1>=IF(L86&lt;&gt;"",INDIRECT(VLOOKUP(L86,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N86" xr:uid="{19F2598B-6135-4EAD-9FBF-4ED7E0B5F9ED}">
+    <dataValidation type="list" sqref="N86" xr:uid="{15DCE614-5094-4CAD-A2E0-973E3D5723AB}">
       <formula1>=IF(M86&lt;&gt;"",INDIRECT(VLOOKUP(M86,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M87" xr:uid="{5D79B5A6-A3CB-4E4E-BCEC-312CD0C4EB75}">
+    <dataValidation type="list" sqref="M87" xr:uid="{93C11F28-ED5D-4F99-BC5D-BD68ACD15A7F}">
       <formula1>=IF(L87&lt;&gt;"",INDIRECT(VLOOKUP(L87,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N87" xr:uid="{4A290D23-2CFC-42DA-A911-2EB3B09EA693}">
+    <dataValidation type="list" sqref="N87" xr:uid="{908950C5-508B-4393-8A82-671454D0F68F}">
       <formula1>=IF(M87&lt;&gt;"",INDIRECT(VLOOKUP(M87,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M88" xr:uid="{9C904DF4-E12E-480A-BFDA-AE1B05EB222C}">
+    <dataValidation type="list" sqref="M88" xr:uid="{AFA528D4-AB9F-408D-A5DD-E6482453A457}">
       <formula1>=IF(L88&lt;&gt;"",INDIRECT(VLOOKUP(L88,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N88" xr:uid="{F52D25EC-6E31-4048-83C6-E149B15DD867}">
+    <dataValidation type="list" sqref="N88" xr:uid="{D23038CF-0806-4903-8A59-1E80CFEF80E8}">
       <formula1>=IF(M88&lt;&gt;"",INDIRECT(VLOOKUP(M88,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M89" xr:uid="{7C820D21-8636-4239-96F6-1FE06A94AB67}">
+    <dataValidation type="list" sqref="M89" xr:uid="{90686643-04B8-4B71-8C48-8FBA0A9189F2}">
       <formula1>=IF(L89&lt;&gt;"",INDIRECT(VLOOKUP(L89,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N89" xr:uid="{6F08276E-8B17-4A76-8B1A-D3C2D78477FE}">
+    <dataValidation type="list" sqref="N89" xr:uid="{5A6D99B3-9CC6-4BAC-A115-DF98578AEC2D}">
       <formula1>=IF(M89&lt;&gt;"",INDIRECT(VLOOKUP(M89,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M90" xr:uid="{03323B3F-BE92-46E3-BD57-3A9B801EAD44}">
+    <dataValidation type="list" sqref="M90" xr:uid="{F8F68CA0-FB3C-40AC-8B49-823F31CB7F6D}">
       <formula1>=IF(L90&lt;&gt;"",INDIRECT(VLOOKUP(L90,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N90" xr:uid="{6780889B-BC5D-4057-BE07-42E16E371293}">
+    <dataValidation type="list" sqref="N90" xr:uid="{FE245F57-2ADF-41DE-8483-E0F4BBE70FF0}">
       <formula1>=IF(M90&lt;&gt;"",INDIRECT(VLOOKUP(M90,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M91" xr:uid="{81E25C36-9814-43C3-AA28-BFABA26531F2}">
+    <dataValidation type="list" sqref="M91" xr:uid="{990FF675-9D25-42D9-950B-36A7EDBF0050}">
       <formula1>=IF(L91&lt;&gt;"",INDIRECT(VLOOKUP(L91,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N91" xr:uid="{2B8907CD-858A-4499-9918-D3A15CB11E48}">
+    <dataValidation type="list" sqref="N91" xr:uid="{5F8F4559-4C55-4C91-91F9-CE8FBB8841F9}">
       <formula1>=IF(M91&lt;&gt;"",INDIRECT(VLOOKUP(M91,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M92" xr:uid="{B88B7C35-EFC8-4ADC-98CC-2237D597755F}">
+    <dataValidation type="list" sqref="M92" xr:uid="{EBA35926-9948-456C-A9F2-38727054468D}">
       <formula1>=IF(L92&lt;&gt;"",INDIRECT(VLOOKUP(L92,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N92" xr:uid="{8198B19A-38AC-4E28-A3AF-07E0D784E10E}">
+    <dataValidation type="list" sqref="N92" xr:uid="{09B4F16E-05BC-4EAA-B146-130BB7FF8631}">
       <formula1>=IF(M92&lt;&gt;"",INDIRECT(VLOOKUP(M92,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M93" xr:uid="{8CD4500F-686C-4157-B1DA-83DD3F489CDA}">
+    <dataValidation type="list" sqref="M93" xr:uid="{0580F74B-EF42-4933-998F-C7B6AC70C75B}">
       <formula1>=IF(L93&lt;&gt;"",INDIRECT(VLOOKUP(L93,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N93" xr:uid="{512F5347-514F-4BD5-BD85-2C040F749F51}">
+    <dataValidation type="list" sqref="N93" xr:uid="{57306C3A-3985-42E9-8577-A2DF9A511660}">
       <formula1>=IF(M93&lt;&gt;"",INDIRECT(VLOOKUP(M93,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M94" xr:uid="{FFCF7163-85D0-4569-9217-5A91EB2EA9C3}">
+    <dataValidation type="list" sqref="M94" xr:uid="{43850FF3-5D16-4731-AED7-592772AF21AC}">
       <formula1>=IF(L94&lt;&gt;"",INDIRECT(VLOOKUP(L94,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N94" xr:uid="{6116D6D5-9AD5-41CC-8AA3-D399E82C1AC0}">
+    <dataValidation type="list" sqref="N94" xr:uid="{5C739F7F-D3E1-42A4-9B49-3E9B97DE78C4}">
       <formula1>=IF(M94&lt;&gt;"",INDIRECT(VLOOKUP(M94,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M95" xr:uid="{F2BF63C8-C5D1-417B-8C08-55D26DBE9E04}">
+    <dataValidation type="list" sqref="M95" xr:uid="{E381237F-68BB-4B13-96BB-3E848C7A81E3}">
       <formula1>=IF(L95&lt;&gt;"",INDIRECT(VLOOKUP(L95,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N95" xr:uid="{EE0B95C6-2C00-487D-8B45-E1AE322F9704}">
+    <dataValidation type="list" sqref="N95" xr:uid="{147FCDF8-2DE2-400D-9604-1B6AD96FBA95}">
       <formula1>=IF(M95&lt;&gt;"",INDIRECT(VLOOKUP(M95,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M96" xr:uid="{B9CD18CA-84BD-48CF-9292-986EB5211ADC}">
+    <dataValidation type="list" sqref="M96" xr:uid="{0B52F383-4F12-4CEE-9B13-CEB266D50AA3}">
       <formula1>=IF(L96&lt;&gt;"",INDIRECT(VLOOKUP(L96,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N96" xr:uid="{E5A91648-D9F5-42C8-9EFC-6075176B804A}">
+    <dataValidation type="list" sqref="N96" xr:uid="{0EE9203F-01C4-4D0A-8596-06B9DBC9AF33}">
       <formula1>=IF(M96&lt;&gt;"",INDIRECT(VLOOKUP(M96,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M97" xr:uid="{2154DDF6-FFA9-46DA-A138-D3F9C6507853}">
+    <dataValidation type="list" sqref="M97" xr:uid="{0352D03C-C2CE-4EF5-B340-9F36EAB35726}">
       <formula1>=IF(L97&lt;&gt;"",INDIRECT(VLOOKUP(L97,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N97" xr:uid="{59D8500F-EE1F-4F8F-8F18-5B635211FA71}">
+    <dataValidation type="list" sqref="N97" xr:uid="{11B09E28-8A53-4E92-BEA5-AF0B2D6777F1}">
       <formula1>=IF(M97&lt;&gt;"",INDIRECT(VLOOKUP(M97,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M98" xr:uid="{BE2BE0B2-7988-4C42-957A-189CFDCA288D}">
+    <dataValidation type="list" sqref="M98" xr:uid="{886D543B-C433-4292-A29C-9A41FE35F62C}">
       <formula1>=IF(L98&lt;&gt;"",INDIRECT(VLOOKUP(L98,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N98" xr:uid="{641C2FCB-51F4-4A3A-AF31-AF7E48D4F7D2}">
+    <dataValidation type="list" sqref="N98" xr:uid="{5D5FAD2D-BB37-4882-AB72-C1F780E8A817}">
       <formula1>=IF(M98&lt;&gt;"",INDIRECT(VLOOKUP(M98,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M99" xr:uid="{D1AF9BD0-C2E8-4609-BBC7-26D90EF85395}">
+    <dataValidation type="list" sqref="M99" xr:uid="{03567459-BAD9-4484-A0F5-57557B6F3431}">
       <formula1>=IF(L99&lt;&gt;"",INDIRECT(VLOOKUP(L99,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N99" xr:uid="{B6201BD7-8E42-417B-B4AB-9B1ED458E047}">
+    <dataValidation type="list" sqref="N99" xr:uid="{7FDA11D7-B5C3-403E-9A51-634C07968B95}">
       <formula1>=IF(M99&lt;&gt;"",INDIRECT(VLOOKUP(M99,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M100" xr:uid="{35D04D55-638E-48B7-8234-A145DB6E7790}">
+    <dataValidation type="list" sqref="M100" xr:uid="{AF82A34B-7538-4ED9-8DE8-268AC0EC73F2}">
       <formula1>=IF(L100&lt;&gt;"",INDIRECT(VLOOKUP(L100,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N100" xr:uid="{7EC63F77-B93C-475A-B2A1-415865FF293E}">
+    <dataValidation type="list" sqref="N100" xr:uid="{F07A62EC-A13E-4D01-81BD-35D87464D81E}">
       <formula1>=IF(M100&lt;&gt;"",INDIRECT(VLOOKUP(M100,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M101" xr:uid="{5B539496-3543-4155-871F-C5430B4EE13A}">
+    <dataValidation type="list" sqref="M101" xr:uid="{BE5AC6FC-584D-49F8-90BC-B77B49B5E99F}">
       <formula1>=IF(L101&lt;&gt;"",INDIRECT(VLOOKUP(L101,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N101" xr:uid="{3F57669C-43A2-4482-96A3-08FE228028CF}">
+    <dataValidation type="list" sqref="N101" xr:uid="{019D71F3-31A1-49DA-B964-51F1506B0924}">
       <formula1>=IF(M101&lt;&gt;"",INDIRECT(VLOOKUP(M101,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M102" xr:uid="{0694D293-36B0-497A-8A89-5B550C7A1DA0}">
+    <dataValidation type="list" sqref="M102" xr:uid="{CAB9641D-115F-4109-A662-6C609DF57936}">
       <formula1>=IF(L102&lt;&gt;"",INDIRECT(VLOOKUP(L102,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N102" xr:uid="{EA28BD43-1E73-45A7-BACF-0D3DED2E4027}">
+    <dataValidation type="list" sqref="N102" xr:uid="{F629769E-0374-4121-80AD-F6213023F9E3}">
       <formula1>=IF(M102&lt;&gt;"",INDIRECT(VLOOKUP(M102,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M103" xr:uid="{65D23985-C8C5-44A9-BDE3-664D6F33EB3D}">
+    <dataValidation type="list" sqref="M103" xr:uid="{7FC22BED-7E1C-4B61-AB5F-58B65BDA93DA}">
       <formula1>=IF(L103&lt;&gt;"",INDIRECT(VLOOKUP(L103,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N103" xr:uid="{84B9D54E-4AD9-4E13-BEA5-100CFCB147A2}">
+    <dataValidation type="list" sqref="N103" xr:uid="{C63D6D05-951D-4BE9-BFD2-D1801BFECD83}">
       <formula1>=IF(M103&lt;&gt;"",INDIRECT(VLOOKUP(M103,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M104" xr:uid="{5939CBD2-75BF-4D1B-942A-90D55AF8FFEE}">
+    <dataValidation type="list" sqref="M104" xr:uid="{ECE2904D-21B1-4ABC-9D64-A3FFD3B7CF98}">
       <formula1>=IF(L104&lt;&gt;"",INDIRECT(VLOOKUP(L104,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N104" xr:uid="{5BC36732-D9E9-4F4A-B506-F5163F678ED1}">
+    <dataValidation type="list" sqref="N104" xr:uid="{401C1744-BA99-4DE3-BE60-BCFB53543BE3}">
       <formula1>=IF(M104&lt;&gt;"",INDIRECT(VLOOKUP(M104,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M105" xr:uid="{17F5AEC8-A982-4937-8F47-50FEA8107D79}">
+    <dataValidation type="list" sqref="M105" xr:uid="{59B357EE-5A0A-429E-BDD5-02C01C05196C}">
       <formula1>=IF(L105&lt;&gt;"",INDIRECT(VLOOKUP(L105,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N105" xr:uid="{DA1BFA1F-418F-4BFD-9CD6-CD8C99BEE17C}">
+    <dataValidation type="list" sqref="N105" xr:uid="{133147D3-D5C3-4D20-8F00-103FDFD2C06D}">
       <formula1>=IF(M105&lt;&gt;"",INDIRECT(VLOOKUP(M105,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M106" xr:uid="{6BC074C3-AE0E-4D26-85C0-D575AA9075F8}">
+    <dataValidation type="list" sqref="M106" xr:uid="{9021F3B4-CEA3-4BBB-BF92-2B65180B30A8}">
       <formula1>=IF(L106&lt;&gt;"",INDIRECT(VLOOKUP(L106,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N106" xr:uid="{205A8D39-B775-4682-92D5-15DB3829A086}">
+    <dataValidation type="list" sqref="N106" xr:uid="{0DDE968F-BB16-444B-9A61-90BA5A11EB47}">
       <formula1>=IF(M106&lt;&gt;"",INDIRECT(VLOOKUP(M106,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M107" xr:uid="{3039B64D-DD79-476E-9CE2-02BE7A1E3A91}">
+    <dataValidation type="list" sqref="M107" xr:uid="{11258D40-14A5-4E4B-B844-C62F9B6D5113}">
       <formula1>=IF(L107&lt;&gt;"",INDIRECT(VLOOKUP(L107,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N107" xr:uid="{2795EB06-89B2-4AAB-BCBB-25D896D6CA68}">
+    <dataValidation type="list" sqref="N107" xr:uid="{2FF847C0-13FC-4624-A8D3-2972D718713D}">
       <formula1>=IF(M107&lt;&gt;"",INDIRECT(VLOOKUP(M107,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M108" xr:uid="{00BCB357-4D67-43FB-99C0-0CE4F6B0B26E}">
+    <dataValidation type="list" sqref="M108" xr:uid="{82518F65-86C5-4AE9-B026-EEB12FBFB8A5}">
       <formula1>=IF(L108&lt;&gt;"",INDIRECT(VLOOKUP(L108,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N108" xr:uid="{2BB650C5-578F-4E54-821C-05205C3EA2B4}">
+    <dataValidation type="list" sqref="N108" xr:uid="{E432B94D-869C-4AEC-B7E5-D8398D17FEB8}">
       <formula1>=IF(M108&lt;&gt;"",INDIRECT(VLOOKUP(M108,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M109" xr:uid="{27308770-1B6F-4938-965C-645E157CE562}">
+    <dataValidation type="list" sqref="M109" xr:uid="{3EDF25A2-D5A0-4D05-8CB6-D85D48A31D20}">
       <formula1>=IF(L109&lt;&gt;"",INDIRECT(VLOOKUP(L109,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N109" xr:uid="{5326452E-0566-4459-A81E-2BA3B5DA7783}">
+    <dataValidation type="list" sqref="N109" xr:uid="{EA293E48-0ED7-4E99-A891-E26D996E1745}">
       <formula1>=IF(M109&lt;&gt;"",INDIRECT(VLOOKUP(M109,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M110" xr:uid="{492C2B62-0454-40D3-BFDC-E05DDEF48AB1}">
+    <dataValidation type="list" sqref="M110" xr:uid="{ABBAE76E-884E-4BF8-961A-F9A70B0D69DF}">
       <formula1>=IF(L110&lt;&gt;"",INDIRECT(VLOOKUP(L110,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N110" xr:uid="{F5561376-C0E8-4047-94B1-4D4FA09CCA59}">
+    <dataValidation type="list" sqref="N110" xr:uid="{59A289A5-7B28-4AF1-AA5D-436E515FF98C}">
       <formula1>=IF(M110&lt;&gt;"",INDIRECT(VLOOKUP(M110,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M111" xr:uid="{6537941A-9629-41D7-8382-5EC4CEF870CB}">
+    <dataValidation type="list" sqref="M111" xr:uid="{F843D4A0-E1C0-430F-975B-742B9E2CFC21}">
       <formula1>=IF(L111&lt;&gt;"",INDIRECT(VLOOKUP(L111,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N111" xr:uid="{87562DBE-AA51-4FC6-B201-AB9787F21E37}">
+    <dataValidation type="list" sqref="N111" xr:uid="{1ED8FA3E-DD52-4EE9-9260-041E5CF0FD83}">
       <formula1>=IF(M111&lt;&gt;"",INDIRECT(VLOOKUP(M111,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M112" xr:uid="{5FDF8509-41ED-4324-A535-80CF219435C8}">
+    <dataValidation type="list" sqref="M112" xr:uid="{BF9CE27D-D98E-4462-8778-26E027CF1CFF}">
       <formula1>=IF(L112&lt;&gt;"",INDIRECT(VLOOKUP(L112,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N112" xr:uid="{E3559E13-D0AA-4395-AA94-1965575E5BB9}">
+    <dataValidation type="list" sqref="N112" xr:uid="{C2D2207D-28F5-46AC-ACDE-4A940D1988ED}">
       <formula1>=IF(M112&lt;&gt;"",INDIRECT(VLOOKUP(M112,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M113" xr:uid="{4DE17FFD-F776-4070-B0BD-6D0BC80B7EC7}">
+    <dataValidation type="list" sqref="M113" xr:uid="{9EB3CD51-CE1F-4D60-8928-6739D20F6929}">
       <formula1>=IF(L113&lt;&gt;"",INDIRECT(VLOOKUP(L113,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N113" xr:uid="{E1F2B553-AE38-43BF-B127-DFB7871F4914}">
+    <dataValidation type="list" sqref="N113" xr:uid="{2E82FD3B-7A6D-4856-AEE2-F44A3CB321BC}">
       <formula1>=IF(M113&lt;&gt;"",INDIRECT(VLOOKUP(M113,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M114" xr:uid="{5FB99E4D-701B-49C3-9960-A9546304554A}">
+    <dataValidation type="list" sqref="M114" xr:uid="{07B9CF62-488F-401F-B605-A5C5DEDF11C0}">
       <formula1>=IF(L114&lt;&gt;"",INDIRECT(VLOOKUP(L114,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N114" xr:uid="{8F995BF1-23A7-474F-B6C0-43CFF02D6E00}">
+    <dataValidation type="list" sqref="N114" xr:uid="{C2B96BC4-6B9B-4629-824D-9766EC82A230}">
       <formula1>=IF(M114&lt;&gt;"",INDIRECT(VLOOKUP(M114,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M115" xr:uid="{87C9531D-236A-47C8-8408-26E241ED4637}">
+    <dataValidation type="list" sqref="M115" xr:uid="{31849C59-48CE-4E41-B7CC-A41C0F563A09}">
       <formula1>=IF(L115&lt;&gt;"",INDIRECT(VLOOKUP(L115,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N115" xr:uid="{0A8B2950-4840-4B13-A026-4BD0B244A2F5}">
+    <dataValidation type="list" sqref="N115" xr:uid="{2B79B1CA-ED33-4B28-B8C9-BA5F934CC2F2}">
       <formula1>=IF(M115&lt;&gt;"",INDIRECT(VLOOKUP(M115,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M116" xr:uid="{2A37EA9E-0571-4864-8DED-95A2E608B47A}">
+    <dataValidation type="list" sqref="M116" xr:uid="{55B710BD-22E7-464E-ABDA-66CAE6CAB88D}">
       <formula1>=IF(L116&lt;&gt;"",INDIRECT(VLOOKUP(L116,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N116" xr:uid="{59BB793C-79CE-4A96-BEE7-C1713E73C55B}">
+    <dataValidation type="list" sqref="N116" xr:uid="{C992C156-80E8-4078-9165-50A8566C284B}">
       <formula1>=IF(M116&lt;&gt;"",INDIRECT(VLOOKUP(M116,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M117" xr:uid="{61D33F77-ACA1-4795-9E09-EA756B255672}">
+    <dataValidation type="list" sqref="M117" xr:uid="{BB673198-55C3-4801-AF23-E2858D0368A1}">
       <formula1>=IF(L117&lt;&gt;"",INDIRECT(VLOOKUP(L117,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N117" xr:uid="{C03F6256-D18C-4FD0-83E6-15AD44AD11F8}">
+    <dataValidation type="list" sqref="N117" xr:uid="{0ED3EE87-C3BF-415A-A8ED-6FE20A91A158}">
       <formula1>=IF(M117&lt;&gt;"",INDIRECT(VLOOKUP(M117,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M118" xr:uid="{5C76C2B3-A93D-409B-95DB-EB88CF433566}">
+    <dataValidation type="list" sqref="M118" xr:uid="{33A79C97-6348-40F9-9404-D1CA06819408}">
       <formula1>=IF(L118&lt;&gt;"",INDIRECT(VLOOKUP(L118,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N118" xr:uid="{77E714F1-9585-4B25-86C3-ACA83285A707}">
+    <dataValidation type="list" sqref="N118" xr:uid="{17741A7E-1F71-42DF-845F-6A148EA130C0}">
       <formula1>=IF(M118&lt;&gt;"",INDIRECT(VLOOKUP(M118,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M119" xr:uid="{102D96FA-A747-49A1-A5BB-833863D763AD}">
+    <dataValidation type="list" sqref="M119" xr:uid="{45AEDC51-2725-4C3A-94AC-A974B5328BA1}">
       <formula1>=IF(L119&lt;&gt;"",INDIRECT(VLOOKUP(L119,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N119" xr:uid="{D23B9F57-A673-4387-9B94-F11D6ADDEBDF}">
+    <dataValidation type="list" sqref="N119" xr:uid="{6F38A3CB-787C-43C3-A89C-146AF1CE399D}">
       <formula1>=IF(M119&lt;&gt;"",INDIRECT(VLOOKUP(M119,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M120" xr:uid="{527ACF85-65DB-4297-BA90-493DD5FDD74D}">
+    <dataValidation type="list" sqref="M120" xr:uid="{FF2F7EC7-E804-4DB1-A8A8-465C1AE536E1}">
       <formula1>=IF(L120&lt;&gt;"",INDIRECT(VLOOKUP(L120,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N120" xr:uid="{6C89DCEE-E0B9-4522-8B87-0DF5D8C7F29E}">
+    <dataValidation type="list" sqref="N120" xr:uid="{DD00410D-D177-423B-9CA9-50295D81A032}">
       <formula1>=IF(M120&lt;&gt;"",INDIRECT(VLOOKUP(M120,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M121" xr:uid="{7286EE78-8978-46F7-AE78-8B6C505997DC}">
+    <dataValidation type="list" sqref="M121" xr:uid="{84F235CD-F82D-4F3C-B9E0-39451C997782}">
       <formula1>=IF(L121&lt;&gt;"",INDIRECT(VLOOKUP(L121,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N121" xr:uid="{CA87554F-C13D-4C23-8415-BAC55AF42C31}">
+    <dataValidation type="list" sqref="N121" xr:uid="{78CC3D37-9EC1-42D1-B78B-2BCD07666557}">
       <formula1>=IF(M121&lt;&gt;"",INDIRECT(VLOOKUP(M121,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M122" xr:uid="{84F51637-F148-4B63-AF73-ADBFCAFCBFF3}">
+    <dataValidation type="list" sqref="M122" xr:uid="{6F1FFA47-735C-4F5F-9F5A-06465CA217FB}">
       <formula1>=IF(L122&lt;&gt;"",INDIRECT(VLOOKUP(L122,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N122" xr:uid="{C7BFA58D-24C0-49B1-802D-1612CCB9B851}">
+    <dataValidation type="list" sqref="N122" xr:uid="{CAD73FA8-B287-41C9-9826-6ED5C9DD9F2D}">
       <formula1>=IF(M122&lt;&gt;"",INDIRECT(VLOOKUP(M122,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M123" xr:uid="{F631FB44-5D2A-4820-B27B-B4013DF6A6CB}">
+    <dataValidation type="list" sqref="M123" xr:uid="{F816DDA1-1285-44EF-8E55-0B7B7837985B}">
       <formula1>=IF(L123&lt;&gt;"",INDIRECT(VLOOKUP(L123,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N123" xr:uid="{62A71F6C-2734-4A41-ACAA-8FD97E391001}">
+    <dataValidation type="list" sqref="N123" xr:uid="{81E86CF5-F3F8-4D68-AE5C-4B9381A7D69F}">
       <formula1>=IF(M123&lt;&gt;"",INDIRECT(VLOOKUP(M123,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M124" xr:uid="{167202B1-EFE2-44D1-AE4B-1B420E4D7C41}">
+    <dataValidation type="list" sqref="M124" xr:uid="{31D61917-3DBD-43A2-8A67-63D39F89EFEB}">
       <formula1>=IF(L124&lt;&gt;"",INDIRECT(VLOOKUP(L124,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N124" xr:uid="{09D2A024-D066-45AF-B46F-E38DC4F5761F}">
+    <dataValidation type="list" sqref="N124" xr:uid="{7E2A9257-D6EC-4B20-B32E-8B4F088326D9}">
       <formula1>=IF(M124&lt;&gt;"",INDIRECT(VLOOKUP(M124,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M125" xr:uid="{2172D972-D769-4C8C-BD41-FEF9BB785683}">
+    <dataValidation type="list" sqref="M125" xr:uid="{76ECFAE4-D2DC-45A0-8B0D-1D1FFE3CBB44}">
       <formula1>=IF(L125&lt;&gt;"",INDIRECT(VLOOKUP(L125,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N125" xr:uid="{3337CE72-90D6-4B9A-97C6-B35E95868AF2}">
+    <dataValidation type="list" sqref="N125" xr:uid="{01FC187E-78C5-4B1C-875B-327B2DD2EF35}">
       <formula1>=IF(M125&lt;&gt;"",INDIRECT(VLOOKUP(M125,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M126" xr:uid="{DADBDE7A-4D87-4ECD-99D1-D0CD9E50800B}">
+    <dataValidation type="list" sqref="M126" xr:uid="{AF8BDFBD-8BCD-4C9C-800A-1BAE412EDFFE}">
       <formula1>=IF(L126&lt;&gt;"",INDIRECT(VLOOKUP(L126,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N126" xr:uid="{F74DD38C-7DE9-4B44-9A5F-C88B2129DAA8}">
+    <dataValidation type="list" sqref="N126" xr:uid="{6B925E02-A515-41C3-B6C0-18FF01403653}">
       <formula1>=IF(M126&lt;&gt;"",INDIRECT(VLOOKUP(M126,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M127" xr:uid="{79CA90D4-CFB7-4EDE-9E48-5293C2102CCD}">
+    <dataValidation type="list" sqref="M127" xr:uid="{A9C78712-86E6-424B-983E-0362DD15EAFD}">
       <formula1>=IF(L127&lt;&gt;"",INDIRECT(VLOOKUP(L127,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N127" xr:uid="{D4837843-EC13-4E20-871F-B48F7C997837}">
+    <dataValidation type="list" sqref="N127" xr:uid="{F124876C-C1EC-4AD2-8920-E75C9684FEE5}">
       <formula1>=IF(M127&lt;&gt;"",INDIRECT(VLOOKUP(M127,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M128" xr:uid="{1A8E2115-8A86-47FE-B1C7-EB325BC68749}">
+    <dataValidation type="list" sqref="M128" xr:uid="{5228B4EC-1F02-4E65-9AF7-9D911AF2890F}">
       <formula1>=IF(L128&lt;&gt;"",INDIRECT(VLOOKUP(L128,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N128" xr:uid="{E52FF7F6-CA6B-4835-ABFF-E63F2D68F9A2}">
+    <dataValidation type="list" sqref="N128" xr:uid="{B5AECE86-0FFE-4FDB-8FB0-088B63A408C4}">
       <formula1>=IF(M128&lt;&gt;"",INDIRECT(VLOOKUP(M128,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M129" xr:uid="{FC54E392-497B-44FA-A1D4-13CA7FA22315}">
+    <dataValidation type="list" sqref="M129" xr:uid="{C5BAD787-1835-408F-94CF-40F8418CC224}">
       <formula1>=IF(L129&lt;&gt;"",INDIRECT(VLOOKUP(L129,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N129" xr:uid="{F2EDD658-01D3-424A-A352-4A3A1BC0D41F}">
+    <dataValidation type="list" sqref="N129" xr:uid="{8CDDFB31-1DC7-45DC-83BF-836F333C8BA2}">
       <formula1>=IF(M129&lt;&gt;"",INDIRECT(VLOOKUP(M129,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M130" xr:uid="{52F2498B-EE82-406E-8AC5-1B39C28A3B01}">
+    <dataValidation type="list" sqref="M130" xr:uid="{21B11C05-166C-43C8-8505-35A5A11649BA}">
       <formula1>=IF(L130&lt;&gt;"",INDIRECT(VLOOKUP(L130,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N130" xr:uid="{05A4CCD2-DF02-4823-9466-6F6677641518}">
+    <dataValidation type="list" sqref="N130" xr:uid="{81AA054F-71C4-48B1-A9DE-56E13B7BD9DC}">
       <formula1>=IF(M130&lt;&gt;"",INDIRECT(VLOOKUP(M130,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M131" xr:uid="{0DA31C18-6D7B-4B4A-957C-1F6A9CB5B6A1}">
+    <dataValidation type="list" sqref="M131" xr:uid="{CBA12ADD-FDD3-4EC6-9179-5D2BA5A3E954}">
       <formula1>=IF(L131&lt;&gt;"",INDIRECT(VLOOKUP(L131,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N131" xr:uid="{47F9DB6C-48FA-4D3D-8114-F2780B7B2EE2}">
+    <dataValidation type="list" sqref="N131" xr:uid="{5A21736A-8B2E-4155-AC05-EEED87C1AFD8}">
       <formula1>=IF(M131&lt;&gt;"",INDIRECT(VLOOKUP(M131,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M132" xr:uid="{7826BA41-49DF-4CB0-9757-5407A5F98CD5}">
+    <dataValidation type="list" sqref="M132" xr:uid="{AA2B9794-8D61-4D41-A993-1BA759894063}">
       <formula1>=IF(L132&lt;&gt;"",INDIRECT(VLOOKUP(L132,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N132" xr:uid="{D7DF29CF-D974-4BEE-A806-B57C632A3F81}">
+    <dataValidation type="list" sqref="N132" xr:uid="{10CCD20F-B5A3-470D-8312-053C6116DD64}">
       <formula1>=IF(M132&lt;&gt;"",INDIRECT(VLOOKUP(M132,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M133" xr:uid="{E47B7709-3492-4B4A-BF5C-8004155AC1EB}">
+    <dataValidation type="list" sqref="M133" xr:uid="{8B548BE7-FC88-4E09-A283-FD48281F0600}">
       <formula1>=IF(L133&lt;&gt;"",INDIRECT(VLOOKUP(L133,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N133" xr:uid="{A8FBD095-54EC-4E6B-9244-805231A9555C}">
+    <dataValidation type="list" sqref="N133" xr:uid="{BE9011EB-E382-4146-A5ED-DD0FC78D68FC}">
       <formula1>=IF(M133&lt;&gt;"",INDIRECT(VLOOKUP(M133,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M134" xr:uid="{5EF403B5-4745-4B9A-9ECA-5C917567AAB5}">
+    <dataValidation type="list" sqref="M134" xr:uid="{D6413342-8A8E-4B0D-89C5-FD777678B0CD}">
       <formula1>=IF(L134&lt;&gt;"",INDIRECT(VLOOKUP(L134,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N134" xr:uid="{BB0F7C5B-0229-4A2C-A15D-09BBE91651EF}">
+    <dataValidation type="list" sqref="N134" xr:uid="{296C6019-BE61-4AE9-A4AF-11823CFDD2EE}">
       <formula1>=IF(M134&lt;&gt;"",INDIRECT(VLOOKUP(M134,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M135" xr:uid="{C427E0ED-432C-42CD-972B-3150033F3E4E}">
+    <dataValidation type="list" sqref="M135" xr:uid="{17D8C37A-78FD-4E54-BA9E-25B0B5DD5612}">
       <formula1>=IF(L135&lt;&gt;"",INDIRECT(VLOOKUP(L135,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N135" xr:uid="{62D5936C-AF99-40D3-B0A2-6C77725816C8}">
+    <dataValidation type="list" sqref="N135" xr:uid="{F9D882CF-1634-49B2-B030-3590AE015F77}">
       <formula1>=IF(M135&lt;&gt;"",INDIRECT(VLOOKUP(M135,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M136" xr:uid="{C586C7EA-B2AD-4688-828E-1A8C04A6ACFE}">
+    <dataValidation type="list" sqref="M136" xr:uid="{3ECF6F64-33BE-4BA1-B215-1CD7E4FECAE0}">
       <formula1>=IF(L136&lt;&gt;"",INDIRECT(VLOOKUP(L136,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N136" xr:uid="{7D066C14-D2B9-41CF-ADD2-7D756046DA0A}">
+    <dataValidation type="list" sqref="N136" xr:uid="{81D7D2B5-EE01-43F8-AEDD-8386001D3696}">
       <formula1>=IF(M136&lt;&gt;"",INDIRECT(VLOOKUP(M136,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M137" xr:uid="{09493624-BAA0-49F3-AFB0-7E5969B1FBFD}">
+    <dataValidation type="list" sqref="M137" xr:uid="{B7888269-D182-468B-9AD1-D85EA9DB7FFA}">
       <formula1>=IF(L137&lt;&gt;"",INDIRECT(VLOOKUP(L137,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N137" xr:uid="{79346421-9F7D-494B-A7B3-543E8E1C3BAC}">
+    <dataValidation type="list" sqref="N137" xr:uid="{0746ED4B-6D1A-42F1-9BC1-B0ADD2717779}">
       <formula1>=IF(M137&lt;&gt;"",INDIRECT(VLOOKUP(M137,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M138" xr:uid="{EE544577-2D3A-46A8-9756-B8DD294C158F}">
+    <dataValidation type="list" sqref="M138" xr:uid="{5CA59839-F0F7-4931-8FA5-B49FBF5A9906}">
       <formula1>=IF(L138&lt;&gt;"",INDIRECT(VLOOKUP(L138,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N138" xr:uid="{16CE4321-E292-460B-8E6F-F014059F55DC}">
+    <dataValidation type="list" sqref="N138" xr:uid="{FCE30A2F-33D9-43C3-B361-2879EE9AA5A6}">
       <formula1>=IF(M138&lt;&gt;"",INDIRECT(VLOOKUP(M138,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M139" xr:uid="{5C5A1623-2AFC-456B-94C2-F664D7DBF7AE}">
+    <dataValidation type="list" sqref="M139" xr:uid="{DAB6529E-213E-4834-87A8-F4ECD3AED26D}">
       <formula1>=IF(L139&lt;&gt;"",INDIRECT(VLOOKUP(L139,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N139" xr:uid="{89A7DE52-3346-490D-B199-BE683B6C004B}">
+    <dataValidation type="list" sqref="N139" xr:uid="{7A165C50-B7D5-472A-B7EF-1D650E7FC09B}">
       <formula1>=IF(M139&lt;&gt;"",INDIRECT(VLOOKUP(M139,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M140" xr:uid="{9679E787-3E9C-442F-9532-59726D8482E7}">
+    <dataValidation type="list" sqref="M140" xr:uid="{3870ACB7-19BE-447D-8C81-3B80648FB491}">
       <formula1>=IF(L140&lt;&gt;"",INDIRECT(VLOOKUP(L140,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N140" xr:uid="{E0E0F892-BD09-463E-BCA8-A2CBAC7A1E34}">
+    <dataValidation type="list" sqref="N140" xr:uid="{E2C4F9D3-B68F-4228-AF23-55FBAC37AD7C}">
       <formula1>=IF(M140&lt;&gt;"",INDIRECT(VLOOKUP(M140,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M141" xr:uid="{FABA7A31-D9E2-4984-874D-E6F5A7685307}">
+    <dataValidation type="list" sqref="M141" xr:uid="{D775DE38-D50F-4893-A75B-9677340070E7}">
       <formula1>=IF(L141&lt;&gt;"",INDIRECT(VLOOKUP(L141,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N141" xr:uid="{7B520515-87EA-4303-BD90-154EFC23C2DE}">
+    <dataValidation type="list" sqref="N141" xr:uid="{A86B90E0-CCC6-4EDE-BCBC-78292A669FC3}">
       <formula1>=IF(M141&lt;&gt;"",INDIRECT(VLOOKUP(M141,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M142" xr:uid="{77628AD4-43BC-4DB3-8CD9-26449C2946C0}">
+    <dataValidation type="list" sqref="M142" xr:uid="{90768B47-DFD5-43E2-AEA6-646F47FCDCB1}">
       <formula1>=IF(L142&lt;&gt;"",INDIRECT(VLOOKUP(L142,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N142" xr:uid="{E04923AE-34B7-4833-9F59-BEBAE4D048AC}">
+    <dataValidation type="list" sqref="N142" xr:uid="{82547203-8DD7-48BD-BD49-47D3728E27B3}">
       <formula1>=IF(M142&lt;&gt;"",INDIRECT(VLOOKUP(M142,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M143" xr:uid="{CFEC14BC-C68D-4890-BEB9-C662EADF0C63}">
+    <dataValidation type="list" sqref="M143" xr:uid="{36EAC2E2-8862-44EE-99F4-D9B7E2D5231B}">
       <formula1>=IF(L143&lt;&gt;"",INDIRECT(VLOOKUP(L143,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N143" xr:uid="{376AAF7C-1AC9-4864-894D-1A0F384006BC}">
+    <dataValidation type="list" sqref="N143" xr:uid="{6C3AE50E-3E5A-4423-A91F-B85BA46C4876}">
       <formula1>=IF(M143&lt;&gt;"",INDIRECT(VLOOKUP(M143,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M144" xr:uid="{FD3CAEB6-24B0-41C5-B388-8140536660E4}">
+    <dataValidation type="list" sqref="M144" xr:uid="{4663DC8D-C3D3-418C-9CE8-F9088DE9BA85}">
       <formula1>=IF(L144&lt;&gt;"",INDIRECT(VLOOKUP(L144,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N144" xr:uid="{13815AFF-14C7-4DB6-9A67-F89D716A8801}">
+    <dataValidation type="list" sqref="N144" xr:uid="{75F92666-1267-4672-BBEA-EDE5D7061FD5}">
       <formula1>=IF(M144&lt;&gt;"",INDIRECT(VLOOKUP(M144,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M145" xr:uid="{EAB86181-B73A-459F-81A0-5D8E4D1CB093}">
+    <dataValidation type="list" sqref="M145" xr:uid="{FB57E1CD-AFA2-497A-A305-C119352EAA86}">
       <formula1>=IF(L145&lt;&gt;"",INDIRECT(VLOOKUP(L145,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N145" xr:uid="{823A8563-4496-42E8-B2F2-B5B5C5B651A2}">
+    <dataValidation type="list" sqref="N145" xr:uid="{F7DC8A8D-392E-4A9A-B241-76E6CB9D6239}">
       <formula1>=IF(M145&lt;&gt;"",INDIRECT(VLOOKUP(M145,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M146" xr:uid="{93B6EA9E-330C-40B5-9DB7-E9A99334CC32}">
+    <dataValidation type="list" sqref="M146" xr:uid="{EF64743D-92AB-43E6-B45C-80059E202A34}">
       <formula1>=IF(L146&lt;&gt;"",INDIRECT(VLOOKUP(L146,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N146" xr:uid="{87386A7A-CB3A-40AF-B7FC-5672A6C0597F}">
+    <dataValidation type="list" sqref="N146" xr:uid="{ACE13B61-5715-42C4-81C5-EAC2E057516A}">
       <formula1>=IF(M146&lt;&gt;"",INDIRECT(VLOOKUP(M146,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M147" xr:uid="{B3B4BC00-F0EF-4D6C-819B-9337F27D73BC}">
+    <dataValidation type="list" sqref="M147" xr:uid="{A1602BDC-0463-45DE-A8B7-87E7012C9517}">
       <formula1>=IF(L147&lt;&gt;"",INDIRECT(VLOOKUP(L147,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N147" xr:uid="{6B1ED579-6554-4B40-858B-3E5F476EB80B}">
+    <dataValidation type="list" sqref="N147" xr:uid="{1FC0BCE6-24DB-4327-A23B-F915A4D64669}">
       <formula1>=IF(M147&lt;&gt;"",INDIRECT(VLOOKUP(M147,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M148" xr:uid="{A9C06D86-C511-47DB-B251-ED0508E9CA17}">
+    <dataValidation type="list" sqref="M148" xr:uid="{22BF1492-9B86-4FD0-A5B4-EF6CD316F2A3}">
       <formula1>=IF(L148&lt;&gt;"",INDIRECT(VLOOKUP(L148,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N148" xr:uid="{0083C108-154C-4A85-BDF4-E9D3F1C65013}">
+    <dataValidation type="list" sqref="N148" xr:uid="{1585594E-1706-4F25-B2C3-3C77C7961425}">
       <formula1>=IF(M148&lt;&gt;"",INDIRECT(VLOOKUP(M148,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M149" xr:uid="{9FF5B716-B258-4BB1-A6E0-079C9457F6DE}">
+    <dataValidation type="list" sqref="M149" xr:uid="{B5AE0AE7-7819-45C0-9A13-2E577BFF2E9E}">
       <formula1>=IF(L149&lt;&gt;"",INDIRECT(VLOOKUP(L149,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N149" xr:uid="{6FDA6F57-B9E6-4B0C-BD74-85AD9682882F}">
+    <dataValidation type="list" sqref="N149" xr:uid="{3EC2E6BB-2408-43D9-A3F8-ECFD1E99742C}">
       <formula1>=IF(M149&lt;&gt;"",INDIRECT(VLOOKUP(M149,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M150" xr:uid="{093113C5-2560-4251-B17D-369C3C86C3E6}">
+    <dataValidation type="list" sqref="M150" xr:uid="{CE4E471A-0EBD-45A0-93B8-4D518F08D14F}">
       <formula1>=IF(L150&lt;&gt;"",INDIRECT(VLOOKUP(L150,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N150" xr:uid="{AA2D00FE-BBAB-4A9D-82AD-68DAB64B2138}">
+    <dataValidation type="list" sqref="N150" xr:uid="{35B3846C-E694-4102-93E8-E61B26415B37}">
       <formula1>=IF(M150&lt;&gt;"",INDIRECT(VLOOKUP(M150,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M151" xr:uid="{08EB7184-5684-4B44-8AD6-CF2535BB8496}">
+    <dataValidation type="list" sqref="M151" xr:uid="{5F747B76-2641-4858-8664-505251A156F0}">
       <formula1>=IF(L151&lt;&gt;"",INDIRECT(VLOOKUP(L151,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N151" xr:uid="{ADE84815-913D-4A3B-A11D-E14126065CCF}">
+    <dataValidation type="list" sqref="N151" xr:uid="{FAF21A4A-DCA0-45BE-BB8D-C940893E1328}">
       <formula1>=IF(M151&lt;&gt;"",INDIRECT(VLOOKUP(M151,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M152" xr:uid="{90761829-06BE-453C-AA77-5D1D734DDE67}">
+    <dataValidation type="list" sqref="M152" xr:uid="{7286D150-6B30-4D88-84F9-A7656C1375B6}">
       <formula1>=IF(L152&lt;&gt;"",INDIRECT(VLOOKUP(L152,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N152" xr:uid="{97F2AB3C-E6E7-480F-9B95-F325FECE2CD7}">
+    <dataValidation type="list" sqref="N152" xr:uid="{86FC049A-622A-4BED-86C2-EA4770FF8F01}">
       <formula1>=IF(M152&lt;&gt;"",INDIRECT(VLOOKUP(M152,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M153" xr:uid="{0120F668-06FF-4515-ACAE-F8746A7DED39}">
+    <dataValidation type="list" sqref="M153" xr:uid="{3D382CFF-95C5-4448-AF19-F016F56FAF95}">
       <formula1>=IF(L153&lt;&gt;"",INDIRECT(VLOOKUP(L153,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N153" xr:uid="{475EAC62-F46D-44CD-97CD-F7025C63239F}">
+    <dataValidation type="list" sqref="N153" xr:uid="{81006F51-DB17-49EC-95A9-E61E5D3E1A16}">
       <formula1>=IF(M153&lt;&gt;"",INDIRECT(VLOOKUP(M153,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M154" xr:uid="{36669EB4-F6D6-475B-A124-FEF71EB41981}">
+    <dataValidation type="list" sqref="M154" xr:uid="{C60B2A03-BA95-48F1-8871-8412010497DC}">
       <formula1>=IF(L154&lt;&gt;"",INDIRECT(VLOOKUP(L154,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N154" xr:uid="{3BA83D1A-D5F3-4C41-8F07-03C040099D34}">
+    <dataValidation type="list" sqref="N154" xr:uid="{02B6E67E-E12C-468C-9B21-965229E4264C}">
       <formula1>=IF(M154&lt;&gt;"",INDIRECT(VLOOKUP(M154,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M155" xr:uid="{A588A565-3737-4790-AAF0-0D5D3A48CB9A}">
+    <dataValidation type="list" sqref="M155" xr:uid="{A3D1803D-C4EC-447A-AF7E-EA1A698E1CD8}">
       <formula1>=IF(L155&lt;&gt;"",INDIRECT(VLOOKUP(L155,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N155" xr:uid="{F8F6DCEC-8930-4839-9239-4C38484980B9}">
+    <dataValidation type="list" sqref="N155" xr:uid="{484DEC4D-6C45-4588-AB01-50EEBD826597}">
       <formula1>=IF(M155&lt;&gt;"",INDIRECT(VLOOKUP(M155,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M156" xr:uid="{B9661033-561D-4089-B821-9B631E434878}">
+    <dataValidation type="list" sqref="M156" xr:uid="{1B4D0A25-E295-4C05-A761-78A306E15BFB}">
       <formula1>=IF(L156&lt;&gt;"",INDIRECT(VLOOKUP(L156,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N156" xr:uid="{1B2F62B8-E243-4F90-B2CB-88EA0AB533B0}">
+    <dataValidation type="list" sqref="N156" xr:uid="{0EFF0A5D-BD11-45B6-B0A1-579969CFC054}">
       <formula1>=IF(M156&lt;&gt;"",INDIRECT(VLOOKUP(M156,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M157" xr:uid="{B8A25F45-19C5-458E-87CB-7226B5BA91D6}">
+    <dataValidation type="list" sqref="M157" xr:uid="{0ECE603E-5FB1-4642-AE66-5D6C589BB300}">
       <formula1>=IF(L157&lt;&gt;"",INDIRECT(VLOOKUP(L157,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N157" xr:uid="{9FF5FF50-7743-47FF-B74D-BA6C6953C2D6}">
+    <dataValidation type="list" sqref="N157" xr:uid="{A89C9413-C38E-45F9-B265-480F4B28BEF5}">
       <formula1>=IF(M157&lt;&gt;"",INDIRECT(VLOOKUP(M157,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M158" xr:uid="{BD10391B-41E6-45AB-9536-ACAC68BF3C80}">
+    <dataValidation type="list" sqref="M158" xr:uid="{B6AEE0CA-6841-4132-AFFD-E74D52A7CF43}">
       <formula1>=IF(L158&lt;&gt;"",INDIRECT(VLOOKUP(L158,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N158" xr:uid="{5D1645FE-C2E4-495D-A207-767BD5D0F653}">
+    <dataValidation type="list" sqref="N158" xr:uid="{412B6B83-86AE-4F95-B8EF-0C7AA1DD68EB}">
       <formula1>=IF(M158&lt;&gt;"",INDIRECT(VLOOKUP(M158,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M159" xr:uid="{E83C5B4F-69D2-4470-919C-24DBB739C1E0}">
+    <dataValidation type="list" sqref="M159" xr:uid="{56B69FC5-B66E-48DF-97A1-E7339412FA64}">
       <formula1>=IF(L159&lt;&gt;"",INDIRECT(VLOOKUP(L159,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N159" xr:uid="{2F456BBC-1584-4860-90B2-C2BC3C5C2595}">
+    <dataValidation type="list" sqref="N159" xr:uid="{4BD0E27E-0957-4C77-9B67-F47A1FC31F56}">
       <formula1>=IF(M159&lt;&gt;"",INDIRECT(VLOOKUP(M159,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M160" xr:uid="{7D478A40-F9DC-4D77-8E6B-B937920AC4E1}">
+    <dataValidation type="list" sqref="M160" xr:uid="{9FDB1371-3EE5-42A2-A15A-5AAA85CCA598}">
       <formula1>=IF(L160&lt;&gt;"",INDIRECT(VLOOKUP(L160,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N160" xr:uid="{03D84719-431F-4A2F-B8C7-F3489CF7B6A1}">
+    <dataValidation type="list" sqref="N160" xr:uid="{5CBEA94D-70C9-40F6-B388-F9980EE4F264}">
       <formula1>=IF(M160&lt;&gt;"",INDIRECT(VLOOKUP(M160,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M161" xr:uid="{6DD00D70-86F4-4BFF-86EB-0977D5A8C80B}">
+    <dataValidation type="list" sqref="M161" xr:uid="{86A2F87B-C391-4729-936E-C4CCF36712E5}">
       <formula1>=IF(L161&lt;&gt;"",INDIRECT(VLOOKUP(L161,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N161" xr:uid="{06B434F4-DAB5-4393-9E9F-DFB2DB23E8D3}">
+    <dataValidation type="list" sqref="N161" xr:uid="{0F282069-7EAF-4F1A-B5E4-BE9AE2B30AA5}">
       <formula1>=IF(M161&lt;&gt;"",INDIRECT(VLOOKUP(M161,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M162" xr:uid="{5BD554AD-72FB-4513-B5D0-5DAE20482197}">
+    <dataValidation type="list" sqref="M162" xr:uid="{4ED148BD-D9F6-4B66-9D6D-FD4F8B124AFB}">
       <formula1>=IF(L162&lt;&gt;"",INDIRECT(VLOOKUP(L162,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N162" xr:uid="{75F80953-35F1-4F2A-A3C1-FFA4BA7F52E6}">
+    <dataValidation type="list" sqref="N162" xr:uid="{8988C05E-B6E8-41A1-9317-48A2FA325F28}">
       <formula1>=IF(M162&lt;&gt;"",INDIRECT(VLOOKUP(M162,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M163" xr:uid="{F3A74BC1-30CD-4E88-9A44-4DC4BB59239C}">
+    <dataValidation type="list" sqref="M163" xr:uid="{AC0CECC8-94AC-4BA7-9AFE-A1360CB0C626}">
       <formula1>=IF(L163&lt;&gt;"",INDIRECT(VLOOKUP(L163,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N163" xr:uid="{E52A0A48-B7ED-4707-A56E-BCB61581BC9F}">
+    <dataValidation type="list" sqref="N163" xr:uid="{E4DFC810-B227-43A6-892C-0E52A2E43C03}">
       <formula1>=IF(M163&lt;&gt;"",INDIRECT(VLOOKUP(M163,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M164" xr:uid="{7115245E-613A-4BDE-AC81-3B154975135E}">
+    <dataValidation type="list" sqref="M164" xr:uid="{3E020AA5-A03E-4A93-8043-2C0353AA9554}">
       <formula1>=IF(L164&lt;&gt;"",INDIRECT(VLOOKUP(L164,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N164" xr:uid="{9745A79A-175B-4996-809A-BB463B82A20B}">
+    <dataValidation type="list" sqref="N164" xr:uid="{14133CB8-C24B-478D-B904-51093F9A5751}">
       <formula1>=IF(M164&lt;&gt;"",INDIRECT(VLOOKUP(M164,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M165" xr:uid="{85D9D80C-97FC-4FA8-A415-59A8F5471C97}">
+    <dataValidation type="list" sqref="M165" xr:uid="{6B5D5A2C-ECDC-4F6E-9CC2-52EAA8AB230B}">
       <formula1>=IF(L165&lt;&gt;"",INDIRECT(VLOOKUP(L165,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N165" xr:uid="{31906289-EC3C-455F-9DB5-B24329144D8C}">
+    <dataValidation type="list" sqref="N165" xr:uid="{02F3B41B-DF1E-4F36-A0B7-D792185A9494}">
       <formula1>=IF(M165&lt;&gt;"",INDIRECT(VLOOKUP(M165,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M166" xr:uid="{0F0D17E7-1DED-406E-9538-E5281CB16E65}">
+    <dataValidation type="list" sqref="M166" xr:uid="{5C9EFBCF-79F7-42DF-AC46-CE4B89D31070}">
       <formula1>=IF(L166&lt;&gt;"",INDIRECT(VLOOKUP(L166,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N166" xr:uid="{42BD3915-A042-40FA-AAFC-992A1274A906}">
+    <dataValidation type="list" sqref="N166" xr:uid="{57A27386-0F6E-4843-9C21-8E1559E89BCF}">
       <formula1>=IF(M166&lt;&gt;"",INDIRECT(VLOOKUP(M166,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M167" xr:uid="{2D2B5F58-32E0-4655-8FC7-4BDA51784063}">
+    <dataValidation type="list" sqref="M167" xr:uid="{6C7C8759-E4D2-4B0D-860B-DA776DC6E73F}">
       <formula1>=IF(L167&lt;&gt;"",INDIRECT(VLOOKUP(L167,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N167" xr:uid="{69012F7A-06CF-4326-B18E-B9E1ED767E91}">
+    <dataValidation type="list" sqref="N167" xr:uid="{7018E153-0984-4C79-82DF-8046AE4F6B65}">
       <formula1>=IF(M167&lt;&gt;"",INDIRECT(VLOOKUP(M167,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M168" xr:uid="{674A7196-ED0F-44F7-9F05-ACE9655FF371}">
+    <dataValidation type="list" sqref="M168" xr:uid="{110B916D-6F59-4A72-B44B-E6FA9F32E785}">
       <formula1>=IF(L168&lt;&gt;"",INDIRECT(VLOOKUP(L168,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N168" xr:uid="{8F910EBB-ABC7-499C-AA72-D7291AC987B6}">
+    <dataValidation type="list" sqref="N168" xr:uid="{6721963B-4BD0-47F1-A63C-703690CBC424}">
       <formula1>=IF(M168&lt;&gt;"",INDIRECT(VLOOKUP(M168,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M169" xr:uid="{9C3E1844-8F45-41BD-9FD3-8F21ECA9FC73}">
+    <dataValidation type="list" sqref="M169" xr:uid="{4DAA2E69-3C1F-4E4A-ADC2-F886B3D35831}">
       <formula1>=IF(L169&lt;&gt;"",INDIRECT(VLOOKUP(L169,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N169" xr:uid="{20C2D4BE-B715-4586-BCB9-C141F83F38C7}">
+    <dataValidation type="list" sqref="N169" xr:uid="{1CD48354-F4D3-4651-8482-F62F3766CEEB}">
       <formula1>=IF(M169&lt;&gt;"",INDIRECT(VLOOKUP(M169,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M170" xr:uid="{25275127-F44E-4CAA-ADD3-F41B9BE89688}">
+    <dataValidation type="list" sqref="M170" xr:uid="{23EE4E3A-E54C-4379-81DE-7035A5E1FDC4}">
       <formula1>=IF(L170&lt;&gt;"",INDIRECT(VLOOKUP(L170,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N170" xr:uid="{F3D2119E-D756-4512-9744-1F6CA1DD6451}">
+    <dataValidation type="list" sqref="N170" xr:uid="{6C005F4F-A5F1-4CAC-84A3-2714C5DD08CC}">
       <formula1>=IF(M170&lt;&gt;"",INDIRECT(VLOOKUP(M170,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M171" xr:uid="{76C65C99-06A8-4F84-BF73-49FBCEF40304}">
+    <dataValidation type="list" sqref="M171" xr:uid="{0AB555C7-9073-4030-A80F-C8C731A0C74A}">
       <formula1>=IF(L171&lt;&gt;"",INDIRECT(VLOOKUP(L171,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N171" xr:uid="{BBAF01BC-A6A0-4428-9517-CA1BD45C1D2E}">
+    <dataValidation type="list" sqref="N171" xr:uid="{EBDBEF10-20D8-4EB5-B473-C0E267AAE0CA}">
       <formula1>=IF(M171&lt;&gt;"",INDIRECT(VLOOKUP(M171,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M172" xr:uid="{80CED641-512B-476E-A1BD-8CEF3F868EAA}">
+    <dataValidation type="list" sqref="M172" xr:uid="{39563D0B-C583-4E2D-84E5-8347DDE755E4}">
       <formula1>=IF(L172&lt;&gt;"",INDIRECT(VLOOKUP(L172,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N172" xr:uid="{0D4B58E1-FBB9-41BE-AF6F-E22645FB7C54}">
+    <dataValidation type="list" sqref="N172" xr:uid="{69DA2F34-AC10-4E61-B3B1-3BBB5366A78C}">
       <formula1>=IF(M172&lt;&gt;"",INDIRECT(VLOOKUP(M172,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M173" xr:uid="{9EE11E5D-66B6-4929-995F-E0CB5C2545F7}">
+    <dataValidation type="list" sqref="M173" xr:uid="{DF4797DA-C7F0-4451-9E86-58F48FE0DEC2}">
       <formula1>=IF(L173&lt;&gt;"",INDIRECT(VLOOKUP(L173,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N173" xr:uid="{23DD652C-9884-4123-B126-3555ECCF2DAD}">
+    <dataValidation type="list" sqref="N173" xr:uid="{492476D8-33E3-4017-9E26-6C2FB46D7156}">
       <formula1>=IF(M173&lt;&gt;"",INDIRECT(VLOOKUP(M173,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M174" xr:uid="{AEE3A5CF-54D0-4514-AB89-26AE5820CD20}">
+    <dataValidation type="list" sqref="M174" xr:uid="{640C5B4C-044F-455D-A0F5-26FE0D6C283A}">
       <formula1>=IF(L174&lt;&gt;"",INDIRECT(VLOOKUP(L174,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N174" xr:uid="{A1425CBC-9E1B-4253-9B00-D086A086FA4F}">
+    <dataValidation type="list" sqref="N174" xr:uid="{937D2FDB-2E34-4902-AB54-7953FB1F2BE1}">
       <formula1>=IF(M174&lt;&gt;"",INDIRECT(VLOOKUP(M174,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M175" xr:uid="{060CDF51-21EC-4909-AE86-D1B777F04A42}">
+    <dataValidation type="list" sqref="M175" xr:uid="{61531395-93C6-49A0-92E5-44FDCF999EEC}">
       <formula1>=IF(L175&lt;&gt;"",INDIRECT(VLOOKUP(L175,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N175" xr:uid="{4E693E16-6AD2-43EB-B431-2FB384D291B9}">
+    <dataValidation type="list" sqref="N175" xr:uid="{C5BA5618-EA9B-4C3B-9B9A-187410236DE6}">
       <formula1>=IF(M175&lt;&gt;"",INDIRECT(VLOOKUP(M175,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M176" xr:uid="{DD7A6AE2-8856-496C-93D2-007DAB7A996D}">
+    <dataValidation type="list" sqref="M176" xr:uid="{D3E4C667-3985-47B8-9D8A-4C03E6F35355}">
       <formula1>=IF(L176&lt;&gt;"",INDIRECT(VLOOKUP(L176,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N176" xr:uid="{AA12D547-9D5A-4B7E-9D37-9BAF46A15FF9}">
+    <dataValidation type="list" sqref="N176" xr:uid="{FA868440-98AB-4D9E-ADCE-04E5CA4CB925}">
       <formula1>=IF(M176&lt;&gt;"",INDIRECT(VLOOKUP(M176,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M177" xr:uid="{9246B401-3668-4860-8E39-BFA8C933F831}">
+    <dataValidation type="list" sqref="M177" xr:uid="{9DDD236C-2277-490C-BFD0-7713C6076524}">
       <formula1>=IF(L177&lt;&gt;"",INDIRECT(VLOOKUP(L177,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N177" xr:uid="{593970D3-F779-43CD-A8D1-D383F277A6EB}">
+    <dataValidation type="list" sqref="N177" xr:uid="{51EE643B-9F65-4D5F-B1F7-823DB4F8FF74}">
       <formula1>=IF(M177&lt;&gt;"",INDIRECT(VLOOKUP(M177,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M178" xr:uid="{CB775AF7-61AA-4F61-9109-EE2911F1094F}">
+    <dataValidation type="list" sqref="M178" xr:uid="{CB13601B-13F0-4396-A547-8B0D9FF2864A}">
       <formula1>=IF(L178&lt;&gt;"",INDIRECT(VLOOKUP(L178,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N178" xr:uid="{D94E13A4-3E1C-492D-AE7D-F688B8058DC3}">
+    <dataValidation type="list" sqref="N178" xr:uid="{E44D41A9-A3C0-4F65-AFBC-C40B96077899}">
       <formula1>=IF(M178&lt;&gt;"",INDIRECT(VLOOKUP(M178,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M179" xr:uid="{29064BF9-02FE-4261-8FD8-C4A191F52C28}">
+    <dataValidation type="list" sqref="M179" xr:uid="{D4364DD1-06C2-4974-9210-0E698134F945}">
       <formula1>=IF(L179&lt;&gt;"",INDIRECT(VLOOKUP(L179,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N179" xr:uid="{7ADCA1FD-2EB5-425E-B4E8-DD1E2C47C5BA}">
+    <dataValidation type="list" sqref="N179" xr:uid="{3F7A51BE-DAF7-466C-AC86-0D0441E410E9}">
       <formula1>=IF(M179&lt;&gt;"",INDIRECT(VLOOKUP(M179,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M180" xr:uid="{B0569034-EEDD-469B-8B85-B28FC9999D5E}">
+    <dataValidation type="list" sqref="M180" xr:uid="{47368CE4-8FD8-4FF0-95DF-1468F4DAB9A2}">
       <formula1>=IF(L180&lt;&gt;"",INDIRECT(VLOOKUP(L180,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N180" xr:uid="{4CE8BE22-BC66-4A17-A3DB-96ED1510AA93}">
+    <dataValidation type="list" sqref="N180" xr:uid="{899EA161-D2E6-4A77-83E5-86E12F33C183}">
       <formula1>=IF(M180&lt;&gt;"",INDIRECT(VLOOKUP(M180,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M181" xr:uid="{7DC451AD-25DA-4849-8AD4-965C3D77A1ED}">
+    <dataValidation type="list" sqref="M181" xr:uid="{602F8ACB-2A82-433D-9537-342C49CC2D14}">
       <formula1>=IF(L181&lt;&gt;"",INDIRECT(VLOOKUP(L181,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N181" xr:uid="{38C4E8C0-848F-4F81-A533-9137DB844362}">
+    <dataValidation type="list" sqref="N181" xr:uid="{A7319131-986C-4DA0-9004-C06A9E81DCB4}">
       <formula1>=IF(M181&lt;&gt;"",INDIRECT(VLOOKUP(M181,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M182" xr:uid="{8E627522-6882-4CAF-9751-6FE5DE1F54EB}">
+    <dataValidation type="list" sqref="M182" xr:uid="{3BDA38DC-341C-4379-A79C-025E49D05424}">
       <formula1>=IF(L182&lt;&gt;"",INDIRECT(VLOOKUP(L182,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N182" xr:uid="{9B66119E-20C0-457C-9E1F-73382BFAC910}">
+    <dataValidation type="list" sqref="N182" xr:uid="{53B18812-39E4-4F4E-BA08-20A485C23246}">
       <formula1>=IF(M182&lt;&gt;"",INDIRECT(VLOOKUP(M182,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M183" xr:uid="{F2407284-7663-4774-A766-9BB754C26D17}">
+    <dataValidation type="list" sqref="M183" xr:uid="{33E7FEE6-29F4-4300-BC04-99DBE0DACDC7}">
       <formula1>=IF(L183&lt;&gt;"",INDIRECT(VLOOKUP(L183,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N183" xr:uid="{2C35653D-5D36-4417-A491-E713749047FC}">
+    <dataValidation type="list" sqref="N183" xr:uid="{F45A581E-ACAB-4FE1-B003-140BE6E8F7EA}">
       <formula1>=IF(M183&lt;&gt;"",INDIRECT(VLOOKUP(M183,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M184" xr:uid="{4F88CE7E-C554-4F6B-B83E-DF52E7ADB191}">
+    <dataValidation type="list" sqref="M184" xr:uid="{792220CB-AFF8-40FC-83B1-277E5DE20478}">
       <formula1>=IF(L184&lt;&gt;"",INDIRECT(VLOOKUP(L184,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N184" xr:uid="{042C9BB2-323E-4510-AE6C-F82331BC9A79}">
+    <dataValidation type="list" sqref="N184" xr:uid="{AB11E553-9018-4162-BA71-A96FE511E36D}">
       <formula1>=IF(M184&lt;&gt;"",INDIRECT(VLOOKUP(M184,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M185" xr:uid="{5308DA34-9055-4943-B202-E59B2A14A57F}">
+    <dataValidation type="list" sqref="M185" xr:uid="{267DA1F5-A38D-490F-B611-8C8269837D3F}">
       <formula1>=IF(L185&lt;&gt;"",INDIRECT(VLOOKUP(L185,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N185" xr:uid="{6DE0899E-E317-4CDE-821E-41A477E53CBA}">
+    <dataValidation type="list" sqref="N185" xr:uid="{A41D6C09-D6C6-483B-A2E4-1F0D06D276D3}">
       <formula1>=IF(M185&lt;&gt;"",INDIRECT(VLOOKUP(M185,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M186" xr:uid="{90D89796-CCC5-462B-9C5B-01C219DAB024}">
+    <dataValidation type="list" sqref="M186" xr:uid="{987B42C9-5F05-40C4-9A84-CC747EBBD079}">
       <formula1>=IF(L186&lt;&gt;"",INDIRECT(VLOOKUP(L186,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N186" xr:uid="{402830A4-404F-47C7-9B36-D428924BFF10}">
+    <dataValidation type="list" sqref="N186" xr:uid="{C48374F4-76E1-47CB-84DC-74AE1D0010D9}">
       <formula1>=IF(M186&lt;&gt;"",INDIRECT(VLOOKUP(M186,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M187" xr:uid="{D5F8C5FE-598D-480E-BE5E-AEE42478C723}">
+    <dataValidation type="list" sqref="M187" xr:uid="{0A2E4144-797E-4966-B048-38268EBDBE19}">
       <formula1>=IF(L187&lt;&gt;"",INDIRECT(VLOOKUP(L187,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N187" xr:uid="{EA9DF7D4-23DD-4B3A-9EC3-5DC4AE84E165}">
+    <dataValidation type="list" sqref="N187" xr:uid="{6326DC9A-1B09-4A4E-9CE3-1EB288A96DEF}">
       <formula1>=IF(M187&lt;&gt;"",INDIRECT(VLOOKUP(M187,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M188" xr:uid="{BC54B994-DDBB-425E-BCE6-34099BBC4A0F}">
+    <dataValidation type="list" sqref="M188" xr:uid="{6B725E49-35A1-4A3C-9982-0F5C8DE10DDD}">
       <formula1>=IF(L188&lt;&gt;"",INDIRECT(VLOOKUP(L188,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N188" xr:uid="{46BB5337-B5F4-428A-9B3D-E4C7CB2B19DC}">
+    <dataValidation type="list" sqref="N188" xr:uid="{5E8B724B-C82F-47EB-8E39-A251D5A60325}">
       <formula1>=IF(M188&lt;&gt;"",INDIRECT(VLOOKUP(M188,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M189" xr:uid="{B89DC08B-0C35-4400-A04E-7B7AC53D47D1}">
+    <dataValidation type="list" sqref="M189" xr:uid="{3F80F367-8CF6-4753-B914-C3C79CF02E4A}">
       <formula1>=IF(L189&lt;&gt;"",INDIRECT(VLOOKUP(L189,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N189" xr:uid="{543D4CCB-01F0-4B69-AC69-0861B926860C}">
+    <dataValidation type="list" sqref="N189" xr:uid="{FA400DB8-237A-4F4B-85EA-87A28A836B9C}">
       <formula1>=IF(M189&lt;&gt;"",INDIRECT(VLOOKUP(M189,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M190" xr:uid="{C892FC94-CD27-49D5-AB01-A517DC30DC17}">
+    <dataValidation type="list" sqref="M190" xr:uid="{C1A2DA7E-21D7-4C14-B26E-CE4894906279}">
       <formula1>=IF(L190&lt;&gt;"",INDIRECT(VLOOKUP(L190,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N190" xr:uid="{C678355B-5FF8-48A3-A9A3-E84E2D2DFC8C}">
+    <dataValidation type="list" sqref="N190" xr:uid="{750D1AAB-BCE2-4541-AC2D-DBA601377F18}">
       <formula1>=IF(M190&lt;&gt;"",INDIRECT(VLOOKUP(M190,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M191" xr:uid="{267C1217-0A05-4832-AA4F-6C15874EFD6A}">
+    <dataValidation type="list" sqref="M191" xr:uid="{5999FCBC-AC57-470D-B999-0A95CD6652C8}">
       <formula1>=IF(L191&lt;&gt;"",INDIRECT(VLOOKUP(L191,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N191" xr:uid="{A962932C-C6E6-4118-AE81-F15EE1813011}">
+    <dataValidation type="list" sqref="N191" xr:uid="{73FAAF46-FDE1-4826-B05E-A332DCFC2039}">
       <formula1>=IF(M191&lt;&gt;"",INDIRECT(VLOOKUP(M191,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M192" xr:uid="{0EA11372-3610-43F6-B896-11DB8D8914BE}">
+    <dataValidation type="list" sqref="M192" xr:uid="{6854FF5E-D33B-4F65-A3FC-A504E36A4EB4}">
       <formula1>=IF(L192&lt;&gt;"",INDIRECT(VLOOKUP(L192,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N192" xr:uid="{C62F5780-8EF1-453A-A635-B3A7E8F04D40}">
+    <dataValidation type="list" sqref="N192" xr:uid="{8BB0BF5F-50DA-46EA-8719-F11E0E8DF4CE}">
       <formula1>=IF(M192&lt;&gt;"",INDIRECT(VLOOKUP(M192,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M193" xr:uid="{92654A5F-E12A-4DBB-8CA8-D94094D4D3E0}">
+    <dataValidation type="list" sqref="M193" xr:uid="{F30A52B6-7F68-4C3C-A484-69C5E753B0B5}">
       <formula1>=IF(L193&lt;&gt;"",INDIRECT(VLOOKUP(L193,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N193" xr:uid="{B2B35FDC-BE84-4920-B220-55819E3600CA}">
+    <dataValidation type="list" sqref="N193" xr:uid="{69E03394-6210-4C9C-8EF8-B60F98D74093}">
       <formula1>=IF(M193&lt;&gt;"",INDIRECT(VLOOKUP(M193,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M194" xr:uid="{E3012E50-1A70-4AC6-8125-A7D5B2394BAF}">
+    <dataValidation type="list" sqref="M194" xr:uid="{A9CF5E5D-FAEF-46E9-8999-9A3E0FF4C652}">
       <formula1>=IF(L194&lt;&gt;"",INDIRECT(VLOOKUP(L194,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N194" xr:uid="{9AD41338-C2E2-4E3D-96D4-7D4E0E0239DA}">
+    <dataValidation type="list" sqref="N194" xr:uid="{3468BD74-9836-4A77-943E-7B8B33F1BBCC}">
       <formula1>=IF(M194&lt;&gt;"",INDIRECT(VLOOKUP(M194,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M195" xr:uid="{C57022BB-84CB-4D96-9169-35436442840C}">
+    <dataValidation type="list" sqref="M195" xr:uid="{0A64AC85-2D41-47C0-A49A-5DEDD24F570C}">
       <formula1>=IF(L195&lt;&gt;"",INDIRECT(VLOOKUP(L195,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N195" xr:uid="{E7685C71-E48C-4582-B356-4FA433E891E9}">
+    <dataValidation type="list" sqref="N195" xr:uid="{8C04F5A5-15CC-4785-8EF1-A14A584E22BC}">
       <formula1>=IF(M195&lt;&gt;"",INDIRECT(VLOOKUP(M195,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M196" xr:uid="{849F07B6-A2C5-4417-8EF3-26BB13E9D2E1}">
+    <dataValidation type="list" sqref="M196" xr:uid="{3BAF5FFA-3F2B-434B-981A-444D82AF82FB}">
       <formula1>=IF(L196&lt;&gt;"",INDIRECT(VLOOKUP(L196,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N196" xr:uid="{C4DB8D8E-14DA-46CE-A3CA-30BB05FDCD1C}">
+    <dataValidation type="list" sqref="N196" xr:uid="{E947C282-FDE4-4D5F-80ED-0AA5F9CFBA95}">
       <formula1>=IF(M196&lt;&gt;"",INDIRECT(VLOOKUP(M196,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M197" xr:uid="{BA2DA054-0589-4122-A3BA-5D690B54A9BB}">
+    <dataValidation type="list" sqref="M197" xr:uid="{F7C6F384-69EE-406E-AFE7-17E0E8E3EE31}">
       <formula1>=IF(L197&lt;&gt;"",INDIRECT(VLOOKUP(L197,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N197" xr:uid="{6A5D5512-6A50-44A9-A1A9-BD0DF9B42FFA}">
+    <dataValidation type="list" sqref="N197" xr:uid="{EB8125BF-704D-4207-A0C7-68598AD03C03}">
       <formula1>=IF(M197&lt;&gt;"",INDIRECT(VLOOKUP(M197,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M198" xr:uid="{7A899002-0DFA-44DE-AE19-0025E198CA40}">
+    <dataValidation type="list" sqref="M198" xr:uid="{4F8A59BB-AB8D-4D31-A696-6A6925125AE7}">
       <formula1>=IF(L198&lt;&gt;"",INDIRECT(VLOOKUP(L198,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N198" xr:uid="{B3D707A2-9D76-4032-BA61-D05E27219A27}">
+    <dataValidation type="list" sqref="N198" xr:uid="{8BF1C6D7-5ACC-4A46-A062-0A8D7D112272}">
       <formula1>=IF(M198&lt;&gt;"",INDIRECT(VLOOKUP(M198,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M199" xr:uid="{E50F2EEC-687C-4931-84AF-71679ACE161A}">
+    <dataValidation type="list" sqref="M199" xr:uid="{F36D59CD-E027-4580-A34C-66B49C17E8FD}">
       <formula1>=IF(L199&lt;&gt;"",INDIRECT(VLOOKUP(L199,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N199" xr:uid="{DBE3F251-CA33-4772-BEF1-C39690EEA7CE}">
+    <dataValidation type="list" sqref="N199" xr:uid="{1AF89BC3-2482-482A-BDC6-8BD1F738F1A8}">
       <formula1>=IF(M199&lt;&gt;"",INDIRECT(VLOOKUP(M199,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M200" xr:uid="{2A78AA5C-7187-4DAF-9ADD-14F6A37A1B17}">
+    <dataValidation type="list" sqref="M200" xr:uid="{7F487DE4-B76F-4269-9559-8531937AB328}">
       <formula1>=IF(L200&lt;&gt;"",INDIRECT(VLOOKUP(L200,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N200" xr:uid="{3AC0F3E8-A7DE-40E5-A1C2-8918EEF534F7}">
+    <dataValidation type="list" sqref="N200" xr:uid="{AD7BC612-AC47-4D93-BE21-C01F099B528B}">
       <formula1>=IF(M200&lt;&gt;"",INDIRECT(VLOOKUP(M200,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M201" xr:uid="{94276A17-E724-4E0A-8919-DCD87D60E561}">
+    <dataValidation type="list" sqref="M201" xr:uid="{8600A391-F09E-49A1-A51C-613C1375D798}">
       <formula1>=IF(L201&lt;&gt;"",INDIRECT(VLOOKUP(L201,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N201" xr:uid="{E1D9838B-96F8-4C1E-AF79-14FE67B5CAF4}">
+    <dataValidation type="list" sqref="N201" xr:uid="{65BCA630-4750-462D-AEA3-2FB79AF82B8B}">
       <formula1>=IF(M201&lt;&gt;"",INDIRECT(VLOOKUP(M201,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M202" xr:uid="{9E566BB4-821D-4C72-B430-8A48EAFE3399}">
+    <dataValidation type="list" sqref="M202" xr:uid="{58692065-D064-40C4-9868-AE601FB5DF70}">
       <formula1>=IF(L202&lt;&gt;"",INDIRECT(VLOOKUP(L202,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N202" xr:uid="{D26A2D29-0361-47C8-AEFA-28BE5EB59722}">
+    <dataValidation type="list" sqref="N202" xr:uid="{8DA91C31-3498-4148-94EB-E4219B627620}">
       <formula1>=IF(M202&lt;&gt;"",INDIRECT(VLOOKUP(M202,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M203" xr:uid="{25DAE6A4-2BAD-42C4-8B72-D3CD771458B6}">
+    <dataValidation type="list" sqref="M203" xr:uid="{20AFA379-1E6B-41FB-B20E-A9FA214EFF51}">
       <formula1>=IF(L203&lt;&gt;"",INDIRECT(VLOOKUP(L203,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N203" xr:uid="{85200386-45BF-44DC-9315-7EC3355FD5C3}">
+    <dataValidation type="list" sqref="N203" xr:uid="{9A193703-45D2-4D9F-BD2F-CF54B96202D1}">
       <formula1>=IF(M203&lt;&gt;"",INDIRECT(VLOOKUP(M203,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M204" xr:uid="{505816DA-8799-4EB9-B9CD-49463995DAD2}">
+    <dataValidation type="list" sqref="M204" xr:uid="{E0D9FEA2-44E4-4381-907F-C23D31E3B60A}">
       <formula1>=IF(L204&lt;&gt;"",INDIRECT(VLOOKUP(L204,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N204" xr:uid="{D54B488F-8732-4E2A-A79D-97EA99984AA0}">
+    <dataValidation type="list" sqref="N204" xr:uid="{CAD5FC83-9F88-40C6-B089-E43235D984C4}">
       <formula1>=IF(M204&lt;&gt;"",INDIRECT(VLOOKUP(M204,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M205" xr:uid="{F9300926-BB63-4055-973F-FA31F879B6B4}">
+    <dataValidation type="list" sqref="M205" xr:uid="{4A099814-5066-449E-BBA1-BCC8A641421D}">
       <formula1>=IF(L205&lt;&gt;"",INDIRECT(VLOOKUP(L205,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N205" xr:uid="{E3C63E06-D874-4B46-A079-DD18428D93BA}">
+    <dataValidation type="list" sqref="N205" xr:uid="{C03B417F-D9EF-4276-98E5-F2C7CEA9B9E3}">
       <formula1>=IF(M205&lt;&gt;"",INDIRECT(VLOOKUP(M205,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M206" xr:uid="{B3DED1BA-CA1B-4597-B71E-F1FA5D84D791}">
+    <dataValidation type="list" sqref="M206" xr:uid="{01CA9C8C-AAD5-40D1-B221-91DED5B4626D}">
       <formula1>=IF(L206&lt;&gt;"",INDIRECT(VLOOKUP(L206,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N206" xr:uid="{FD1FD10F-DB45-43A2-A0F6-4D58F2C69763}">
+    <dataValidation type="list" sqref="N206" xr:uid="{93A2C86B-9A3C-43CD-9486-C09961FC9A22}">
       <formula1>=IF(M206&lt;&gt;"",INDIRECT(VLOOKUP(M206,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M207" xr:uid="{1A53AE75-D569-48BD-B7A2-99D074CEB7CC}">
+    <dataValidation type="list" sqref="M207" xr:uid="{09221355-7CAC-485D-B189-59642403677F}">
       <formula1>=IF(L207&lt;&gt;"",INDIRECT(VLOOKUP(L207,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N207" xr:uid="{8C8E422A-B0CC-4A7F-BB27-BC86E83B0278}">
+    <dataValidation type="list" sqref="N207" xr:uid="{366A1254-3EBB-4A2D-A8EC-A79F0F4AABF1}">
       <formula1>=IF(M207&lt;&gt;"",INDIRECT(VLOOKUP(M207,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M208" xr:uid="{06E80511-3F4E-4B6B-A181-6EA1D87A4CE6}">
+    <dataValidation type="list" sqref="M208" xr:uid="{16119060-EBDD-4327-9C2B-C9C6FDEE154F}">
       <formula1>=IF(L208&lt;&gt;"",INDIRECT(VLOOKUP(L208,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N208" xr:uid="{55D4B22E-CB13-40BB-BA2B-4461D62ACDAD}">
+    <dataValidation type="list" sqref="N208" xr:uid="{2CF3BB90-612E-4E98-B3FA-50DF63036CF7}">
       <formula1>=IF(M208&lt;&gt;"",INDIRECT(VLOOKUP(M208,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M209" xr:uid="{34695F97-B906-496C-A0E5-653270350F2B}">
+    <dataValidation type="list" sqref="M209" xr:uid="{C50F5F18-24C1-45A6-B893-DD467A254A33}">
       <formula1>=IF(L209&lt;&gt;"",INDIRECT(VLOOKUP(L209,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N209" xr:uid="{310F0849-C416-4391-B803-E3059358B149}">
+    <dataValidation type="list" sqref="N209" xr:uid="{23C32F41-814E-410B-832E-DAD63E3C4E3D}">
       <formula1>=IF(M209&lt;&gt;"",INDIRECT(VLOOKUP(M209,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M210" xr:uid="{C228CD3C-A7B6-4056-BAA2-4339197C250C}">
+    <dataValidation type="list" sqref="M210" xr:uid="{B1427E88-FAB0-4AD3-9104-3A6B747E5D5F}">
       <formula1>=IF(L210&lt;&gt;"",INDIRECT(VLOOKUP(L210,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N210" xr:uid="{7CB42359-089B-4AB3-9CC8-433A5A5E6D1D}">
+    <dataValidation type="list" sqref="N210" xr:uid="{A09158F6-D08D-4403-9940-205F25BC07C8}">
       <formula1>=IF(M210&lt;&gt;"",INDIRECT(VLOOKUP(M210,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M211" xr:uid="{D0DE5379-D6FB-446A-9591-CF7D02DFF61F}">
+    <dataValidation type="list" sqref="M211" xr:uid="{A45CBC3F-B507-49A0-9CA2-252A742D0CB6}">
       <formula1>=IF(L211&lt;&gt;"",INDIRECT(VLOOKUP(L211,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N211" xr:uid="{74CDFB9E-C5B8-40E4-80D3-072CA1376B95}">
+    <dataValidation type="list" sqref="N211" xr:uid="{BD6D5184-AB5D-429F-958A-FEA7BAA2254A}">
       <formula1>=IF(M211&lt;&gt;"",INDIRECT(VLOOKUP(M211,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M212" xr:uid="{003E78D6-F335-421E-8DF9-DA039FF3F53D}">
+    <dataValidation type="list" sqref="M212" xr:uid="{54812D98-728C-4854-8321-F924666F03DE}">
       <formula1>=IF(L212&lt;&gt;"",INDIRECT(VLOOKUP(L212,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N212" xr:uid="{72E1E37F-31EC-4389-8D65-3316E785BB9B}">
+    <dataValidation type="list" sqref="N212" xr:uid="{2F427A3A-9DCD-4030-8C16-92C2983C69CF}">
       <formula1>=IF(M212&lt;&gt;"",INDIRECT(VLOOKUP(M212,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M213" xr:uid="{36AA956B-8A57-46AD-8E79-B5B8A54D2E54}">
+    <dataValidation type="list" sqref="M213" xr:uid="{6C1651DC-04FD-4D32-A5A4-1A129E5CC410}">
       <formula1>=IF(L213&lt;&gt;"",INDIRECT(VLOOKUP(L213,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N213" xr:uid="{F85438EE-A19C-417D-B583-F276987E7BF6}">
+    <dataValidation type="list" sqref="N213" xr:uid="{26A75B61-6643-4D25-B4A3-CC4EF13D205B}">
       <formula1>=IF(M213&lt;&gt;"",INDIRECT(VLOOKUP(M213,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M214" xr:uid="{72F5CFCC-80B1-41A8-A076-598AB553AD50}">
+    <dataValidation type="list" sqref="M214" xr:uid="{4042E913-E22D-4C1F-9565-3459F79B25F5}">
       <formula1>=IF(L214&lt;&gt;"",INDIRECT(VLOOKUP(L214,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N214" xr:uid="{08F6D145-DC77-4313-9EB8-7A4B37173946}">
+    <dataValidation type="list" sqref="N214" xr:uid="{5F37D14F-0B62-4FB8-B521-DDC02EFADDB7}">
       <formula1>=IF(M214&lt;&gt;"",INDIRECT(VLOOKUP(M214,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M215" xr:uid="{37F25F3A-4383-4B71-9A85-586EA4774C22}">
+    <dataValidation type="list" sqref="M215" xr:uid="{0440E905-0EC1-46F1-857A-25A1AA97C8B5}">
       <formula1>=IF(L215&lt;&gt;"",INDIRECT(VLOOKUP(L215,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N215" xr:uid="{26F30151-2668-495F-9364-1C1203462804}">
+    <dataValidation type="list" sqref="N215" xr:uid="{681B075C-FCCC-4BCB-B0B6-43AEBE1C8FE0}">
       <formula1>=IF(M215&lt;&gt;"",INDIRECT(VLOOKUP(M215,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M216" xr:uid="{62B11299-2E00-4F68-B7A9-70E73BB7800D}">
+    <dataValidation type="list" sqref="M216" xr:uid="{89BE4C91-157A-478B-A3BF-7075C4239AF4}">
       <formula1>=IF(L216&lt;&gt;"",INDIRECT(VLOOKUP(L216,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N216" xr:uid="{6FA143DF-CEBA-417F-924B-639E9157CC54}">
+    <dataValidation type="list" sqref="N216" xr:uid="{8095054E-A788-4FF0-BA59-868494E78365}">
       <formula1>=IF(M216&lt;&gt;"",INDIRECT(VLOOKUP(M216,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M217" xr:uid="{3DA19AD6-D953-45C7-8CE0-7AF34A5EEA53}">
+    <dataValidation type="list" sqref="M217" xr:uid="{C6B4113D-0E83-4D9E-8871-F9B3087ED2A1}">
       <formula1>=IF(L217&lt;&gt;"",INDIRECT(VLOOKUP(L217,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N217" xr:uid="{A47A1C8A-4F5E-46F1-A12D-9D7E3B02411C}">
+    <dataValidation type="list" sqref="N217" xr:uid="{D833CFCD-1413-4609-AB88-EE63BB4B2BDC}">
       <formula1>=IF(M217&lt;&gt;"",INDIRECT(VLOOKUP(M217,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M218" xr:uid="{8F19B1F8-3384-45F3-A162-6D43C4BFE7AD}">
+    <dataValidation type="list" sqref="M218" xr:uid="{4B4ECF3F-A95B-443B-8BE9-F0D87D04637C}">
       <formula1>=IF(L218&lt;&gt;"",INDIRECT(VLOOKUP(L218,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N218" xr:uid="{F9AA91FA-D3CC-44E2-844D-5167D519B382}">
+    <dataValidation type="list" sqref="N218" xr:uid="{357864EA-80D0-4FF0-8DF9-0181313D3236}">
       <formula1>=IF(M218&lt;&gt;"",INDIRECT(VLOOKUP(M218,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M219" xr:uid="{27A252B4-211D-4749-BE3E-6284873A5E23}">
+    <dataValidation type="list" sqref="M219" xr:uid="{1D0E6DD7-EBC8-4E26-B9A9-B7AE7F5CE636}">
       <formula1>=IF(L219&lt;&gt;"",INDIRECT(VLOOKUP(L219,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N219" xr:uid="{8BD0E7C2-E49E-4E6F-AF8A-755F38E8253A}">
+    <dataValidation type="list" sqref="N219" xr:uid="{A3FC7155-B833-4C8E-AEE1-0C791A799C94}">
       <formula1>=IF(M219&lt;&gt;"",INDIRECT(VLOOKUP(M219,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M220" xr:uid="{E51A77EA-8807-4031-A3F8-26A44BD4BB4C}">
+    <dataValidation type="list" sqref="M220" xr:uid="{2EEEB5C7-B829-4278-AC84-F7084CB9C157}">
       <formula1>=IF(L220&lt;&gt;"",INDIRECT(VLOOKUP(L220,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N220" xr:uid="{5F62B48D-EB56-4F8E-B461-CF44152CE6E0}">
+    <dataValidation type="list" sqref="N220" xr:uid="{800DDBFE-52A2-4EA0-9A31-272D8F86C6AE}">
       <formula1>=IF(M220&lt;&gt;"",INDIRECT(VLOOKUP(M220,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M221" xr:uid="{DE24893F-E53E-421B-84C1-04E4AC6E8E9E}">
+    <dataValidation type="list" sqref="M221" xr:uid="{5005A8AF-4F5A-4C3D-B653-2B0D761551E9}">
       <formula1>=IF(L221&lt;&gt;"",INDIRECT(VLOOKUP(L221,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N221" xr:uid="{A9F17DA3-9157-4C70-97DE-8C930457CCE2}">
+    <dataValidation type="list" sqref="N221" xr:uid="{EE410B92-AD73-4661-BD0C-668732AEF7F1}">
       <formula1>=IF(M221&lt;&gt;"",INDIRECT(VLOOKUP(M221,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M222" xr:uid="{0196B1C8-448B-4A28-9C79-042B7968C355}">
+    <dataValidation type="list" sqref="M222" xr:uid="{E618F549-B916-4953-9610-9C0D2330D7E6}">
       <formula1>=IF(L222&lt;&gt;"",INDIRECT(VLOOKUP(L222,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N222" xr:uid="{DE38CB6D-EC73-479E-9C1B-CFC63573C223}">
+    <dataValidation type="list" sqref="N222" xr:uid="{0C9996BB-DAD8-4869-B128-3D10C08ACB89}">
       <formula1>=IF(M222&lt;&gt;"",INDIRECT(VLOOKUP(M222,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M223" xr:uid="{8621421F-9449-448B-8D41-42948C87D3AF}">
+    <dataValidation type="list" sqref="M223" xr:uid="{D26DC611-1236-4D37-AB00-687C7592D4D7}">
       <formula1>=IF(L223&lt;&gt;"",INDIRECT(VLOOKUP(L223,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N223" xr:uid="{85B92DEE-8941-4733-B44F-1DA35D49BAB8}">
+    <dataValidation type="list" sqref="N223" xr:uid="{860E0ECE-5E5E-4ADE-9D36-86174678AB07}">
       <formula1>=IF(M223&lt;&gt;"",INDIRECT(VLOOKUP(M223,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M224" xr:uid="{6128987E-1C50-4DFE-BFDB-62403E74116F}">
+    <dataValidation type="list" sqref="M224" xr:uid="{1FCC016A-A614-4E0C-8C3E-1936282985A4}">
       <formula1>=IF(L224&lt;&gt;"",INDIRECT(VLOOKUP(L224,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N224" xr:uid="{473F24D8-E919-44B8-AD05-E42D5B7D7B4D}">
+    <dataValidation type="list" sqref="N224" xr:uid="{34180832-A83D-4BDF-B620-A1B22A4CDC92}">
       <formula1>=IF(M224&lt;&gt;"",INDIRECT(VLOOKUP(M224,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M225" xr:uid="{E21513D1-AAE4-498E-8997-07641C8E6584}">
+    <dataValidation type="list" sqref="M225" xr:uid="{631035B6-BAB8-4895-92DE-6AF98F90DC3C}">
       <formula1>=IF(L225&lt;&gt;"",INDIRECT(VLOOKUP(L225,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N225" xr:uid="{982A566A-054D-45A6-A726-62C827A54875}">
+    <dataValidation type="list" sqref="N225" xr:uid="{391ED131-5CDA-44AC-80E2-BD5E54658648}">
       <formula1>=IF(M225&lt;&gt;"",INDIRECT(VLOOKUP(M225,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M226" xr:uid="{25C0736B-2D5C-403A-A0F4-33F013F29145}">
+    <dataValidation type="list" sqref="M226" xr:uid="{EEECD43E-F0D0-4991-8C2C-3E45B2765491}">
       <formula1>=IF(L226&lt;&gt;"",INDIRECT(VLOOKUP(L226,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N226" xr:uid="{9507CBA1-327C-41DC-A9F7-9DC53598B3B9}">
+    <dataValidation type="list" sqref="N226" xr:uid="{BF55FA7B-1C17-48BC-ABEC-D8648879E8A0}">
       <formula1>=IF(M226&lt;&gt;"",INDIRECT(VLOOKUP(M226,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M227" xr:uid="{D59C7D87-1764-4BD5-B2D0-7F516D61098F}">
+    <dataValidation type="list" sqref="M227" xr:uid="{07F5D286-AD48-40CF-BA44-9AAA75266AE8}">
       <formula1>=IF(L227&lt;&gt;"",INDIRECT(VLOOKUP(L227,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N227" xr:uid="{8F265D46-7D16-4BE7-9DB7-769BB82F3EFC}">
+    <dataValidation type="list" sqref="N227" xr:uid="{370B2E71-F38F-4C86-9C5D-9F72BD424612}">
       <formula1>=IF(M227&lt;&gt;"",INDIRECT(VLOOKUP(M227,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M228" xr:uid="{1BB43319-A2F8-45D7-B189-E5D908D06F4A}">
+    <dataValidation type="list" sqref="M228" xr:uid="{4410AE8E-C6D2-46DA-B140-7653CE6E84A2}">
       <formula1>=IF(L228&lt;&gt;"",INDIRECT(VLOOKUP(L228,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N228" xr:uid="{65682EFF-2098-4798-AE34-1F48263665D8}">
+    <dataValidation type="list" sqref="N228" xr:uid="{862120BF-2A0C-43DA-A807-779A2C3A6A0D}">
       <formula1>=IF(M228&lt;&gt;"",INDIRECT(VLOOKUP(M228,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M229" xr:uid="{5C8B0E89-3168-4006-A904-669A7BB7B31B}">
+    <dataValidation type="list" sqref="M229" xr:uid="{F3876D52-53E1-499C-AFDD-CBA41B42DE68}">
       <formula1>=IF(L229&lt;&gt;"",INDIRECT(VLOOKUP(L229,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N229" xr:uid="{0C7AC074-FA28-462E-8F6B-F59A49304962}">
+    <dataValidation type="list" sqref="N229" xr:uid="{DC1C539B-CF45-4EB5-ADE7-9052B77A3B35}">
       <formula1>=IF(M229&lt;&gt;"",INDIRECT(VLOOKUP(M229,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M230" xr:uid="{82F5F377-73B2-4573-A48F-4D38EA56E101}">
+    <dataValidation type="list" sqref="M230" xr:uid="{9226AACA-C8F8-4E9B-B884-A3FFC97D56AE}">
       <formula1>=IF(L230&lt;&gt;"",INDIRECT(VLOOKUP(L230,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N230" xr:uid="{567E75DA-97C5-4ECE-844D-7BC133822144}">
+    <dataValidation type="list" sqref="N230" xr:uid="{38A8F9A1-6E59-4F8B-977C-EDDE7B076C54}">
       <formula1>=IF(M230&lt;&gt;"",INDIRECT(VLOOKUP(M230,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M231" xr:uid="{D3DE5A41-C2DA-447A-BD25-373203CC4DE7}">
+    <dataValidation type="list" sqref="M231" xr:uid="{2683163D-D09D-48C4-8D86-0547BA19408D}">
       <formula1>=IF(L231&lt;&gt;"",INDIRECT(VLOOKUP(L231,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N231" xr:uid="{8AF564FC-68F4-4F1E-93DA-2C50BF7259D2}">
+    <dataValidation type="list" sqref="N231" xr:uid="{FD4F7717-AFE1-4A27-B8EB-E98940D3352F}">
       <formula1>=IF(M231&lt;&gt;"",INDIRECT(VLOOKUP(M231,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M232" xr:uid="{8CEC75CB-A83D-42F7-8FCB-DEB1D27E77CC}">
+    <dataValidation type="list" sqref="M232" xr:uid="{512D1F48-1F75-4E7E-AA82-56DE5EA8F219}">
       <formula1>=IF(L232&lt;&gt;"",INDIRECT(VLOOKUP(L232,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N232" xr:uid="{C0698478-2BB1-4EDF-8611-1A201132D8D8}">
+    <dataValidation type="list" sqref="N232" xr:uid="{4CC4D231-C68F-428A-B7BD-6FE2A18FAC9A}">
       <formula1>=IF(M232&lt;&gt;"",INDIRECT(VLOOKUP(M232,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M233" xr:uid="{72ED345C-B4F1-44CA-8520-80E03CEE80E2}">
+    <dataValidation type="list" sqref="M233" xr:uid="{C89011BF-C7E9-4978-8A49-F108D23A088B}">
       <formula1>=IF(L233&lt;&gt;"",INDIRECT(VLOOKUP(L233,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N233" xr:uid="{A6AC29D9-6E0A-42B3-98B3-2325C2E49DFB}">
+    <dataValidation type="list" sqref="N233" xr:uid="{0C693156-2FA5-4B8F-BB23-03BC02D85753}">
       <formula1>=IF(M233&lt;&gt;"",INDIRECT(VLOOKUP(M233,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M234" xr:uid="{FF6B32E6-C234-43BE-85D7-5BD9AA391B82}">
+    <dataValidation type="list" sqref="M234" xr:uid="{0390B92F-F9D6-4ACF-B1F3-27F803E52A63}">
       <formula1>=IF(L234&lt;&gt;"",INDIRECT(VLOOKUP(L234,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N234" xr:uid="{7C1E1FE0-F2BF-45C3-95B8-7BB46D8785C1}">
+    <dataValidation type="list" sqref="N234" xr:uid="{9A51A306-E080-41FC-A1F9-E7C539B8097B}">
       <formula1>=IF(M234&lt;&gt;"",INDIRECT(VLOOKUP(M234,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M235" xr:uid="{CE524655-BEA1-4255-81FD-B3112C586742}">
+    <dataValidation type="list" sqref="M235" xr:uid="{D4998929-E719-409D-80D7-C63BE81F85FE}">
       <formula1>=IF(L235&lt;&gt;"",INDIRECT(VLOOKUP(L235,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N235" xr:uid="{4A315B9E-0616-4A68-8542-B305DEDB5660}">
+    <dataValidation type="list" sqref="N235" xr:uid="{CD7383B0-11F5-4887-922D-93B66E208994}">
       <formula1>=IF(M235&lt;&gt;"",INDIRECT(VLOOKUP(M235,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M236" xr:uid="{89A70CA5-FA6D-4D18-A1F9-FEA2BF8C75C7}">
+    <dataValidation type="list" sqref="M236" xr:uid="{33BB5BDC-DC4F-4388-9195-5EC98784F0FB}">
       <formula1>=IF(L236&lt;&gt;"",INDIRECT(VLOOKUP(L236,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N236" xr:uid="{F4825143-3E2F-434E-AF92-90957837CA67}">
+    <dataValidation type="list" sqref="N236" xr:uid="{8E80B48D-0C17-4BD0-AEE2-BC011723CA79}">
       <formula1>=IF(M236&lt;&gt;"",INDIRECT(VLOOKUP(M236,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M237" xr:uid="{D2D5E071-A8A4-46AC-AF52-CC4DBC0FB73C}">
+    <dataValidation type="list" sqref="M237" xr:uid="{F83E7F08-44C1-4D43-BCE3-7F835BA58041}">
       <formula1>=IF(L237&lt;&gt;"",INDIRECT(VLOOKUP(L237,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N237" xr:uid="{57E19BAD-2059-4B25-8778-35D2376BB71A}">
+    <dataValidation type="list" sqref="N237" xr:uid="{AB6E2E96-3DA2-48EC-AE4C-1630BB584924}">
       <formula1>=IF(M237&lt;&gt;"",INDIRECT(VLOOKUP(M237,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M238" xr:uid="{AB520653-02CC-44AB-9EF5-7F66F9563A64}">
+    <dataValidation type="list" sqref="M238" xr:uid="{8FC9B3F9-0323-43B3-9BB8-85D8ABFF31BB}">
       <formula1>=IF(L238&lt;&gt;"",INDIRECT(VLOOKUP(L238,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N238" xr:uid="{BF942647-8CE7-4E33-A1CB-35E683FB48F8}">
+    <dataValidation type="list" sqref="N238" xr:uid="{53D180A8-E999-404F-8DAF-0EA91E6BDA44}">
       <formula1>=IF(M238&lt;&gt;"",INDIRECT(VLOOKUP(M238,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M239" xr:uid="{042F6BF3-E235-4021-AE3A-4C66E1D15C4D}">
+    <dataValidation type="list" sqref="M239" xr:uid="{4D92F7B5-131B-476B-8292-A01D04D5A132}">
       <formula1>=IF(L239&lt;&gt;"",INDIRECT(VLOOKUP(L239,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N239" xr:uid="{83404725-80F4-4BD0-858D-44DF711FE1BA}">
+    <dataValidation type="list" sqref="N239" xr:uid="{83E3ADCD-F595-49AA-8385-3156205D0C33}">
       <formula1>=IF(M239&lt;&gt;"",INDIRECT(VLOOKUP(M239,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M240" xr:uid="{A1B3AF31-EFAA-4016-90DA-CBFB05D2F962}">
+    <dataValidation type="list" sqref="M240" xr:uid="{076BC818-3E28-433E-ADA8-BF7358EE7688}">
       <formula1>=IF(L240&lt;&gt;"",INDIRECT(VLOOKUP(L240,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N240" xr:uid="{6EAD9736-AFB4-490B-BFB5-3183D8871999}">
+    <dataValidation type="list" sqref="N240" xr:uid="{8EC44608-82C5-401C-8E35-CE1BBF42DD1C}">
       <formula1>=IF(M240&lt;&gt;"",INDIRECT(VLOOKUP(M240,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M241" xr:uid="{2A2128D8-C5D4-46C6-8C0E-D20FC79CD193}">
+    <dataValidation type="list" sqref="M241" xr:uid="{48D0A982-B43F-4D84-9628-578ABE08B5F7}">
       <formula1>=IF(L241&lt;&gt;"",INDIRECT(VLOOKUP(L241,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N241" xr:uid="{611798C9-C0DE-4BB6-A71E-682DBDC411B8}">
+    <dataValidation type="list" sqref="N241" xr:uid="{9615A11D-B963-45CC-84D5-367BB869E5EF}">
       <formula1>=IF(M241&lt;&gt;"",INDIRECT(VLOOKUP(M241,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M242" xr:uid="{6E131C9A-ECE0-4FE4-8C3C-03D1AFB40A8D}">
+    <dataValidation type="list" sqref="M242" xr:uid="{5E841808-57B5-4E22-9392-49E0E91C53E3}">
       <formula1>=IF(L242&lt;&gt;"",INDIRECT(VLOOKUP(L242,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N242" xr:uid="{5A08ED91-8555-4422-BF32-9EFA21CF7DBC}">
+    <dataValidation type="list" sqref="N242" xr:uid="{05EDE20C-7B37-4E17-ABF6-D2D001BD2AD6}">
       <formula1>=IF(M242&lt;&gt;"",INDIRECT(VLOOKUP(M242,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M243" xr:uid="{162F5099-99D5-45E8-B964-B35A607B5788}">
+    <dataValidation type="list" sqref="M243" xr:uid="{43FAC472-AE92-45AD-9173-05C4C8133B22}">
       <formula1>=IF(L243&lt;&gt;"",INDIRECT(VLOOKUP(L243,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N243" xr:uid="{4F23D662-8D58-481A-9255-6F822BD08602}">
+    <dataValidation type="list" sqref="N243" xr:uid="{4F41F6FF-C2B7-4B39-B36B-49A5851A5021}">
       <formula1>=IF(M243&lt;&gt;"",INDIRECT(VLOOKUP(M243,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M244" xr:uid="{D13D0AED-654A-4CB3-AEB9-5AAA595363BE}">
+    <dataValidation type="list" sqref="M244" xr:uid="{CB301789-B445-4D77-A7FF-4952E8DC75F2}">
       <formula1>=IF(L244&lt;&gt;"",INDIRECT(VLOOKUP(L244,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N244" xr:uid="{33AE919D-9BAE-48B7-8DA3-642EB3431657}">
+    <dataValidation type="list" sqref="N244" xr:uid="{BDE1AA65-4E0C-4550-A748-B82AC45017D5}">
       <formula1>=IF(M244&lt;&gt;"",INDIRECT(VLOOKUP(M244,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M245" xr:uid="{099AD4A9-2E95-4015-95CC-258F692D2E17}">
+    <dataValidation type="list" sqref="M245" xr:uid="{F55BC2EB-9292-46EF-9A1E-D8C6436ECB86}">
       <formula1>=IF(L245&lt;&gt;"",INDIRECT(VLOOKUP(L245,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N245" xr:uid="{8D8319EA-1108-4D72-9CA9-B8343D4EA693}">
+    <dataValidation type="list" sqref="N245" xr:uid="{1E96B740-434D-4404-A884-8EC012DEB379}">
       <formula1>=IF(M245&lt;&gt;"",INDIRECT(VLOOKUP(M245,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M246" xr:uid="{44E491B3-6FDA-4C43-ABC4-F584B82EA2AD}">
+    <dataValidation type="list" sqref="M246" xr:uid="{AA0AB7DF-8E54-4EDA-925D-D0B90DAF9D74}">
       <formula1>=IF(L246&lt;&gt;"",INDIRECT(VLOOKUP(L246,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N246" xr:uid="{8BD72E10-15BD-485C-8E93-B748346577E8}">
+    <dataValidation type="list" sqref="N246" xr:uid="{CCAF7AF8-47D2-4880-82BE-B43D77373A2B}">
       <formula1>=IF(M246&lt;&gt;"",INDIRECT(VLOOKUP(M246,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M247" xr:uid="{BAC38B62-2D79-4562-BDFA-CA8EDE19719E}">
+    <dataValidation type="list" sqref="M247" xr:uid="{D63B2815-B770-4C68-B0F2-852D2231C627}">
       <formula1>=IF(L247&lt;&gt;"",INDIRECT(VLOOKUP(L247,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N247" xr:uid="{D76E4198-4AF8-49B9-ADC1-8A9F287D9159}">
+    <dataValidation type="list" sqref="N247" xr:uid="{9F9136B7-5FED-4FDF-BA08-8784547AACE7}">
       <formula1>=IF(M247&lt;&gt;"",INDIRECT(VLOOKUP(M247,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M248" xr:uid="{B6B29A42-A57A-4C61-B5E0-A22A161F521A}">
+    <dataValidation type="list" sqref="M248" xr:uid="{C9CBE3A4-8DE2-4752-9597-D4CBCA13B793}">
       <formula1>=IF(L248&lt;&gt;"",INDIRECT(VLOOKUP(L248,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N248" xr:uid="{A92B03E1-93A2-414E-9EC6-D6BCD0B6EED1}">
+    <dataValidation type="list" sqref="N248" xr:uid="{5291AB09-FC20-4FA1-B7BF-7B04CF2BC33E}">
       <formula1>=IF(M248&lt;&gt;"",INDIRECT(VLOOKUP(M248,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M249" xr:uid="{7C7DA6AB-AE18-4B54-AABB-D8E4197EB055}">
+    <dataValidation type="list" sqref="M249" xr:uid="{68A7B9A6-CA18-48C7-BA53-442B7A09865F}">
       <formula1>=IF(L249&lt;&gt;"",INDIRECT(VLOOKUP(L249,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N249" xr:uid="{B80D0138-FFB4-4304-ABA7-876574929DC3}">
+    <dataValidation type="list" sqref="N249" xr:uid="{7678D13A-97B4-41B7-971B-1815DC28EA66}">
       <formula1>=IF(M249&lt;&gt;"",INDIRECT(VLOOKUP(M249,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M250" xr:uid="{78775B13-661D-4226-B3F1-B60B53457BD3}">
+    <dataValidation type="list" sqref="M250" xr:uid="{2DBA01A1-C6A6-43B1-9699-872B5A4D2AB4}">
       <formula1>=IF(L250&lt;&gt;"",INDIRECT(VLOOKUP(L250,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N250" xr:uid="{7C19B41D-D53C-4A15-B596-00B99A288705}">
+    <dataValidation type="list" sqref="N250" xr:uid="{E472496E-EC24-433A-A3B6-2200BBB655CB}">
       <formula1>=IF(M250&lt;&gt;"",INDIRECT(VLOOKUP(M250,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M251" xr:uid="{A6F12D29-E661-49C3-A3C6-5BEEF1F5DB82}">
+    <dataValidation type="list" sqref="M251" xr:uid="{82898274-91E4-4A80-917C-F3235B7C17B5}">
       <formula1>=IF(L251&lt;&gt;"",INDIRECT(VLOOKUP(L251,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N251" xr:uid="{7A6751C4-1DA0-4245-8F74-BBEA767B327B}">
+    <dataValidation type="list" sqref="N251" xr:uid="{A989CF97-EAD3-4D69-A2DF-63A547FBEB4F}">
       <formula1>=IF(M251&lt;&gt;"",INDIRECT(VLOOKUP(M251,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M252" xr:uid="{1F3FF2B8-D2E6-4447-B04F-C4D75E377FFC}">
+    <dataValidation type="list" sqref="M252" xr:uid="{26203AAA-9FE0-4F26-A1BC-FE6FA267DFD8}">
       <formula1>=IF(L252&lt;&gt;"",INDIRECT(VLOOKUP(L252,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N252" xr:uid="{2DA51664-4CFF-4FB2-854C-0B597318A7A1}">
+    <dataValidation type="list" sqref="N252" xr:uid="{A019F58E-4816-4CB2-AAAF-BFF9825B206F}">
       <formula1>=IF(M252&lt;&gt;"",INDIRECT(VLOOKUP(M252,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M253" xr:uid="{6FC8C339-20A0-43F5-8846-5F5A1E0709E7}">
+    <dataValidation type="list" sqref="M253" xr:uid="{56AFAF68-4C63-4C67-B393-C1D404B350F1}">
       <formula1>=IF(L253&lt;&gt;"",INDIRECT(VLOOKUP(L253,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N253" xr:uid="{107C1D15-66FF-433E-9C3F-724A8D235B33}">
+    <dataValidation type="list" sqref="N253" xr:uid="{5CD5C5C7-6555-431B-85A1-2512A118AC27}">
       <formula1>=IF(M253&lt;&gt;"",INDIRECT(VLOOKUP(M253,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M254" xr:uid="{2F145F68-2492-48A5-AFF2-38C9397FC15B}">
+    <dataValidation type="list" sqref="M254" xr:uid="{A992CC0B-973A-496E-BF90-C4A26C47FD1A}">
       <formula1>=IF(L254&lt;&gt;"",INDIRECT(VLOOKUP(L254,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N254" xr:uid="{54144723-4EA6-45BD-9D03-240F821F1C17}">
+    <dataValidation type="list" sqref="N254" xr:uid="{5E14EF4C-7DA1-403D-99D9-C6F563352D9B}">
       <formula1>=IF(M254&lt;&gt;"",INDIRECT(VLOOKUP(M254,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M255" xr:uid="{15453C63-D55E-480C-B369-3F11005CD7D2}">
+    <dataValidation type="list" sqref="M255" xr:uid="{FEC31B97-1419-40CA-823B-1092A3FDD125}">
       <formula1>=IF(L255&lt;&gt;"",INDIRECT(VLOOKUP(L255,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N255" xr:uid="{0886CDE8-8782-4AF6-9F5F-8DEED7A471A5}">
+    <dataValidation type="list" sqref="N255" xr:uid="{D35DEC09-2CDD-404A-B554-32156E6EA9AA}">
       <formula1>=IF(M255&lt;&gt;"",INDIRECT(VLOOKUP(M255,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M256" xr:uid="{DAF4DF0C-39DF-465F-9835-ED2201B2EFF2}">
+    <dataValidation type="list" sqref="M256" xr:uid="{ACA3519A-3CB3-42C6-9A0E-C08D787EDEEC}">
       <formula1>=IF(L256&lt;&gt;"",INDIRECT(VLOOKUP(L256,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N256" xr:uid="{F573B888-5FBB-4CB2-9C3C-BCA7C0E42F1E}">
+    <dataValidation type="list" sqref="N256" xr:uid="{955D5785-43A2-43F8-A03D-B46C3C46632A}">
       <formula1>=IF(M256&lt;&gt;"",INDIRECT(VLOOKUP(M256,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M257" xr:uid="{2FB472FF-7DF3-400A-9301-315102C421E0}">
+    <dataValidation type="list" sqref="M257" xr:uid="{F1919D5F-02F7-48AE-BA21-9042CE4E2200}">
       <formula1>=IF(L257&lt;&gt;"",INDIRECT(VLOOKUP(L257,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N257" xr:uid="{FA08ED22-12E1-4EF5-B0F4-A62AD61E2BE4}">
+    <dataValidation type="list" sqref="N257" xr:uid="{B775D033-7130-47DE-A831-F4C204DF4CE5}">
       <formula1>=IF(M257&lt;&gt;"",INDIRECT(VLOOKUP(M257,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M258" xr:uid="{1256A62D-1CF7-41C4-AE77-693EA02BBF15}">
+    <dataValidation type="list" sqref="M258" xr:uid="{98C0058A-D8F4-4F6D-BC2C-FE85778C4BF8}">
       <formula1>=IF(L258&lt;&gt;"",INDIRECT(VLOOKUP(L258,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N258" xr:uid="{B68007A0-FDF9-4AAD-A88B-0C0FAC781E9B}">
+    <dataValidation type="list" sqref="N258" xr:uid="{BC574B50-AF0A-45EA-9C52-35465AE56197}">
       <formula1>=IF(M258&lt;&gt;"",INDIRECT(VLOOKUP(M258,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M259" xr:uid="{14FEB602-698E-4EBF-9F2E-9B5D270FC5B4}">
+    <dataValidation type="list" sqref="M259" xr:uid="{3D4130A1-C3A1-4C61-861A-7CE7EB75E52C}">
       <formula1>=IF(L259&lt;&gt;"",INDIRECT(VLOOKUP(L259,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N259" xr:uid="{94F11DE7-8C12-43AB-BAE1-F0DF49670BDD}">
+    <dataValidation type="list" sqref="N259" xr:uid="{B80652E8-8B64-4334-9E50-6771CBD54345}">
       <formula1>=IF(M259&lt;&gt;"",INDIRECT(VLOOKUP(M259,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M260" xr:uid="{E29DB746-9466-4248-A9CE-C4BC498900BB}">
+    <dataValidation type="list" sqref="M260" xr:uid="{E1E0931E-1010-4B0D-B919-1A92CC857A2E}">
       <formula1>=IF(L260&lt;&gt;"",INDIRECT(VLOOKUP(L260,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N260" xr:uid="{463A8A29-D944-454C-8AB8-D7790967FAF3}">
+    <dataValidation type="list" sqref="N260" xr:uid="{91D9D2E7-296D-45AD-ADB0-458AA12D036F}">
       <formula1>=IF(M260&lt;&gt;"",INDIRECT(VLOOKUP(M260,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M261" xr:uid="{75EA9437-59DE-4895-8345-065ABB8A9752}">
+    <dataValidation type="list" sqref="M261" xr:uid="{39BCB276-8E37-400E-BFA8-59E011DE3420}">
       <formula1>=IF(L261&lt;&gt;"",INDIRECT(VLOOKUP(L261,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N261" xr:uid="{CD20D9CC-7BB5-4A3F-9D95-DBD019854893}">
+    <dataValidation type="list" sqref="N261" xr:uid="{53706B58-6382-4B54-86E3-764A85FB8374}">
       <formula1>=IF(M261&lt;&gt;"",INDIRECT(VLOOKUP(M261,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M262" xr:uid="{5A7F0651-C78A-4D4D-9A3A-F3162997EAE1}">
+    <dataValidation type="list" sqref="M262" xr:uid="{529C4E0A-7D99-49ED-8FA7-E98E3FFEC65D}">
       <formula1>=IF(L262&lt;&gt;"",INDIRECT(VLOOKUP(L262,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N262" xr:uid="{DC281AF7-91FF-435A-9997-DE3AD437C73E}">
+    <dataValidation type="list" sqref="N262" xr:uid="{049021AC-83FE-4BA0-AB0B-126B38871853}">
       <formula1>=IF(M262&lt;&gt;"",INDIRECT(VLOOKUP(M262,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M263" xr:uid="{9A4C4FA2-9DFC-438B-AF70-54DFBF64AE92}">
+    <dataValidation type="list" sqref="M263" xr:uid="{8D59882A-8CEE-4572-9366-B91B7C5C1E7B}">
       <formula1>=IF(L263&lt;&gt;"",INDIRECT(VLOOKUP(L263,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N263" xr:uid="{F16FF8AC-FD9D-4FF3-BFFE-95067F1E3083}">
+    <dataValidation type="list" sqref="N263" xr:uid="{BFEC0C39-3245-4408-9C7A-462A3CCA7401}">
       <formula1>=IF(M263&lt;&gt;"",INDIRECT(VLOOKUP(M263,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M264" xr:uid="{1518D11F-3377-465A-82E8-BB52F263ABD2}">
+    <dataValidation type="list" sqref="M264" xr:uid="{2ABF342F-CFE8-43ED-A6E2-1AD9BC70907C}">
       <formula1>=IF(L264&lt;&gt;"",INDIRECT(VLOOKUP(L264,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N264" xr:uid="{7B0AEFEE-0C33-4395-8C0F-C7AC1B1B46AB}">
+    <dataValidation type="list" sqref="N264" xr:uid="{7015CC81-B98E-4EE7-8796-332736BFC6A7}">
       <formula1>=IF(M264&lt;&gt;"",INDIRECT(VLOOKUP(M264,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M265" xr:uid="{1EC753F8-9C49-4D70-89F3-6580ADC26C30}">
+    <dataValidation type="list" sqref="M265" xr:uid="{A5AC4864-0A62-4DE4-943E-CC3238A30A12}">
       <formula1>=IF(L265&lt;&gt;"",INDIRECT(VLOOKUP(L265,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N265" xr:uid="{0A980673-254E-42B9-B654-C261C0966877}">
+    <dataValidation type="list" sqref="N265" xr:uid="{59AC84C6-17B2-4F29-9D4D-8B58C7A059E7}">
       <formula1>=IF(M265&lt;&gt;"",INDIRECT(VLOOKUP(M265,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M266" xr:uid="{0CFCE7A9-397F-4F70-8733-7EAF067094BD}">
+    <dataValidation type="list" sqref="M266" xr:uid="{246FF6B3-1343-4CD3-816A-26A259A5A7C9}">
       <formula1>=IF(L266&lt;&gt;"",INDIRECT(VLOOKUP(L266,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N266" xr:uid="{0DA4F270-F6FB-448A-8813-9F3D189CFCE0}">
+    <dataValidation type="list" sqref="N266" xr:uid="{2B7E499E-9CA5-4B81-94E7-BC4B5DF682F0}">
       <formula1>=IF(M266&lt;&gt;"",INDIRECT(VLOOKUP(M266,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M267" xr:uid="{5F5EBBBD-3DCC-487A-B9EB-4BCE7E341B9C}">
+    <dataValidation type="list" sqref="M267" xr:uid="{180BFCB7-D50A-4B7F-BB60-27B69B89002C}">
       <formula1>=IF(L267&lt;&gt;"",INDIRECT(VLOOKUP(L267,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N267" xr:uid="{CA6D57C0-9454-483B-8446-8F191A050C98}">
+    <dataValidation type="list" sqref="N267" xr:uid="{B082D103-892D-43D5-9CE8-4B9997D6293D}">
       <formula1>=IF(M267&lt;&gt;"",INDIRECT(VLOOKUP(M267,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M268" xr:uid="{D7A99DC6-E270-4BD0-B7AA-C7BC919A419F}">
+    <dataValidation type="list" sqref="M268" xr:uid="{B844E12C-527D-4067-B896-9121347B0817}">
       <formula1>=IF(L268&lt;&gt;"",INDIRECT(VLOOKUP(L268,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N268" xr:uid="{A320B1B9-EC6B-49FD-85AB-2DFE8A499A6D}">
+    <dataValidation type="list" sqref="N268" xr:uid="{69C11765-F406-4224-9D27-6138D42BFDC2}">
       <formula1>=IF(M268&lt;&gt;"",INDIRECT(VLOOKUP(M268,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M269" xr:uid="{8F97665B-069F-4846-8269-5395E256804E}">
+    <dataValidation type="list" sqref="M269" xr:uid="{9B170B0B-B46F-473B-83F2-02E2952FF435}">
       <formula1>=IF(L269&lt;&gt;"",INDIRECT(VLOOKUP(L269,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N269" xr:uid="{DFFF1806-9191-48F3-A72B-F1F2CD27275F}">
+    <dataValidation type="list" sqref="N269" xr:uid="{3339C598-BF32-46AF-9BD5-166F44C65415}">
       <formula1>=IF(M269&lt;&gt;"",INDIRECT(VLOOKUP(M269,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M270" xr:uid="{38021D58-5A97-49DE-B317-14AB237254A4}">
+    <dataValidation type="list" sqref="M270" xr:uid="{49977F27-7D16-4428-9EF6-784E2C823611}">
       <formula1>=IF(L270&lt;&gt;"",INDIRECT(VLOOKUP(L270,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N270" xr:uid="{997B679B-11ED-4B91-84A9-5B623E208718}">
+    <dataValidation type="list" sqref="N270" xr:uid="{9E62FB84-1F26-48C8-8CFA-EDF2155C533E}">
       <formula1>=IF(M270&lt;&gt;"",INDIRECT(VLOOKUP(M270,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M271" xr:uid="{F7C7CEC6-05A6-463E-8954-2E77E521F592}">
+    <dataValidation type="list" sqref="M271" xr:uid="{F422AD5D-A07B-48A6-9655-E0CB8C21DE61}">
       <formula1>=IF(L271&lt;&gt;"",INDIRECT(VLOOKUP(L271,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N271" xr:uid="{B4B98A91-4D90-453E-B7EC-BE34061D4C1F}">
+    <dataValidation type="list" sqref="N271" xr:uid="{BCCE251D-8A15-4F87-86F4-6BD0D5776900}">
       <formula1>=IF(M271&lt;&gt;"",INDIRECT(VLOOKUP(M271,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M272" xr:uid="{E7DA30B5-74CC-4703-831A-CC68B18AA70C}">
+    <dataValidation type="list" sqref="M272" xr:uid="{98C567E7-D024-43B1-855C-141C91B123A5}">
       <formula1>=IF(L272&lt;&gt;"",INDIRECT(VLOOKUP(L272,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N272" xr:uid="{A25DEDF1-A003-4E62-BD59-AF53382D4B6F}">
+    <dataValidation type="list" sqref="N272" xr:uid="{C191D86D-A5FE-42A1-BF29-B88CE681C1A8}">
       <formula1>=IF(M272&lt;&gt;"",INDIRECT(VLOOKUP(M272,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M273" xr:uid="{DE9D1D34-A3BA-4DBC-8E31-3AE58D6F1A3A}">
+    <dataValidation type="list" sqref="M273" xr:uid="{7D8FEF68-FC6C-4513-A620-6AD286CE1AF2}">
       <formula1>=IF(L273&lt;&gt;"",INDIRECT(VLOOKUP(L273,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N273" xr:uid="{5DF7188A-9F94-43E8-A6A9-2300EF157EBB}">
+    <dataValidation type="list" sqref="N273" xr:uid="{C3FA7652-1EE8-4985-91EA-1A6F14B261C9}">
       <formula1>=IF(M273&lt;&gt;"",INDIRECT(VLOOKUP(M273,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M274" xr:uid="{F3FEDA53-A1DB-4B33-A4D8-71CC4852AB1D}">
+    <dataValidation type="list" sqref="M274" xr:uid="{A6273952-04B7-476B-9686-D27E870F456E}">
       <formula1>=IF(L274&lt;&gt;"",INDIRECT(VLOOKUP(L274,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N274" xr:uid="{4D6EC996-1EF6-4295-B904-1BA294C047C9}">
+    <dataValidation type="list" sqref="N274" xr:uid="{93DF3426-D0CE-4A17-B61F-D221C01CE5AF}">
       <formula1>=IF(M274&lt;&gt;"",INDIRECT(VLOOKUP(M274,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M275" xr:uid="{93D284F0-1023-4140-B28B-BB43B549EF63}">
+    <dataValidation type="list" sqref="M275" xr:uid="{75399C18-3CE8-45CB-8714-4A9CF0FE5437}">
       <formula1>=IF(L275&lt;&gt;"",INDIRECT(VLOOKUP(L275,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N275" xr:uid="{0BE6BD73-73F9-4A8A-BF87-115E3EE1B09D}">
+    <dataValidation type="list" sqref="N275" xr:uid="{EC2236C4-0C51-4AE1-AC4B-28CC8DF9BA66}">
       <formula1>=IF(M275&lt;&gt;"",INDIRECT(VLOOKUP(M275,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M276" xr:uid="{E94CCC1D-4836-4E59-9A5B-60B25E21D035}">
+    <dataValidation type="list" sqref="M276" xr:uid="{DA27DC00-6560-43FF-88F3-DD0D097E15F1}">
       <formula1>=IF(L276&lt;&gt;"",INDIRECT(VLOOKUP(L276,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N276" xr:uid="{CB524E61-2C61-4867-98D9-485F27D777BA}">
+    <dataValidation type="list" sqref="N276" xr:uid="{9FFBA281-6A38-4A76-97B6-706467EC5A14}">
       <formula1>=IF(M276&lt;&gt;"",INDIRECT(VLOOKUP(M276,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M277" xr:uid="{1C97C53A-1034-4360-9241-75FBA3249253}">
+    <dataValidation type="list" sqref="M277" xr:uid="{DC37A255-A2C6-4D87-BE72-22BD6B3768A6}">
       <formula1>=IF(L277&lt;&gt;"",INDIRECT(VLOOKUP(L277,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N277" xr:uid="{0DD75BEB-BC82-40CB-B47A-DC00C5F63C4E}">
+    <dataValidation type="list" sqref="N277" xr:uid="{B4B523D3-DA78-4172-82DC-DCA5AC1DECD3}">
       <formula1>=IF(M277&lt;&gt;"",INDIRECT(VLOOKUP(M277,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M278" xr:uid="{5F3287C6-3701-4AE1-AC55-84FE4B93F485}">
+    <dataValidation type="list" sqref="M278" xr:uid="{F4637350-ABFA-45B6-8BAB-7C644A65CFBC}">
       <formula1>=IF(L278&lt;&gt;"",INDIRECT(VLOOKUP(L278,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N278" xr:uid="{C255E130-6F4A-4103-820F-1B5968CD96E4}">
+    <dataValidation type="list" sqref="N278" xr:uid="{A42822AD-190F-4DF4-9137-8A3FFCF83389}">
       <formula1>=IF(M278&lt;&gt;"",INDIRECT(VLOOKUP(M278,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M279" xr:uid="{DED5EECE-E7BE-44B8-95F2-F43A084368AE}">
+    <dataValidation type="list" sqref="M279" xr:uid="{5DA5A14D-628B-4BAE-A7D4-7498E17FF7CA}">
       <formula1>=IF(L279&lt;&gt;"",INDIRECT(VLOOKUP(L279,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N279" xr:uid="{2558A5AD-4867-4194-99A5-93596B190618}">
+    <dataValidation type="list" sqref="N279" xr:uid="{9E66B123-6D0F-458A-A1EE-368DF84FCC87}">
       <formula1>=IF(M279&lt;&gt;"",INDIRECT(VLOOKUP(M279,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M280" xr:uid="{78BAFEDE-825B-4C6D-AA27-EEBCA72DFFBD}">
+    <dataValidation type="list" sqref="M280" xr:uid="{4BB4D065-9684-4C66-8ABB-8C89C1FEB740}">
       <formula1>=IF(L280&lt;&gt;"",INDIRECT(VLOOKUP(L280,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N280" xr:uid="{369D2C53-6F1C-4290-B1FB-31465875AA5B}">
+    <dataValidation type="list" sqref="N280" xr:uid="{81C346F3-9439-4A05-BDF4-2FB04E694C13}">
       <formula1>=IF(M280&lt;&gt;"",INDIRECT(VLOOKUP(M280,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M281" xr:uid="{4EC5FC62-0819-4CD9-A258-EAC4C8E10B57}">
+    <dataValidation type="list" sqref="M281" xr:uid="{BDC333F5-DCAB-4D8C-A95F-5C9E79C7A994}">
       <formula1>=IF(L281&lt;&gt;"",INDIRECT(VLOOKUP(L281,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N281" xr:uid="{9E1B296C-503C-4A3A-AB2B-C9FC1105F5DC}">
+    <dataValidation type="list" sqref="N281" xr:uid="{B2A30475-EA64-470D-98E2-68D51B6E2C16}">
       <formula1>=IF(M281&lt;&gt;"",INDIRECT(VLOOKUP(M281,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M282" xr:uid="{C35EAAAC-42BF-49F9-9009-BA2B33129598}">
+    <dataValidation type="list" sqref="M282" xr:uid="{0C5E983F-E7AD-4A1A-9D67-5FA03E742B72}">
       <formula1>=IF(L282&lt;&gt;"",INDIRECT(VLOOKUP(L282,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N282" xr:uid="{635F0C8D-5A3A-429C-A7DF-F8E7E68EEA24}">
+    <dataValidation type="list" sqref="N282" xr:uid="{3092DD07-4232-40AD-9B6E-F99D593AA7DB}">
       <formula1>=IF(M282&lt;&gt;"",INDIRECT(VLOOKUP(M282,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M283" xr:uid="{D8A9637E-F65B-4E0F-9D2E-58E4FDD47A61}">
+    <dataValidation type="list" sqref="M283" xr:uid="{F254B12A-C5C0-4177-AB0F-BCCD9537F8AE}">
       <formula1>=IF(L283&lt;&gt;"",INDIRECT(VLOOKUP(L283,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N283" xr:uid="{7B5FEEA5-37C3-47EF-915C-0A78878C2E59}">
+    <dataValidation type="list" sqref="N283" xr:uid="{518B767C-A5CD-40D3-A54F-A2266560F67D}">
       <formula1>=IF(M283&lt;&gt;"",INDIRECT(VLOOKUP(M283,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M284" xr:uid="{5D7EED97-A42B-4313-AB4F-F50719AE087B}">
+    <dataValidation type="list" sqref="M284" xr:uid="{3F828326-24EF-4900-9A06-64900EA10CE9}">
       <formula1>=IF(L284&lt;&gt;"",INDIRECT(VLOOKUP(L284,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N284" xr:uid="{A3EC6C97-190B-4DA9-9ACE-8861B2B28D6B}">
+    <dataValidation type="list" sqref="N284" xr:uid="{840BB3D0-BE99-4282-8349-17606B72A4AD}">
       <formula1>=IF(M284&lt;&gt;"",INDIRECT(VLOOKUP(M284,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M285" xr:uid="{4C2B29D5-1022-4513-B4C5-A14E9219EC7E}">
+    <dataValidation type="list" sqref="M285" xr:uid="{A8106A18-745F-4D98-B259-63ACA5AB7E37}">
       <formula1>=IF(L285&lt;&gt;"",INDIRECT(VLOOKUP(L285,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N285" xr:uid="{7D63C871-F8F0-4991-884F-7D7749EE1617}">
+    <dataValidation type="list" sqref="N285" xr:uid="{86666ACD-058C-4D66-99F5-849039836668}">
       <formula1>=IF(M285&lt;&gt;"",INDIRECT(VLOOKUP(M285,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M286" xr:uid="{BDE63FC4-2CFD-4755-9035-2649D53E9B62}">
+    <dataValidation type="list" sqref="M286" xr:uid="{A9D93B17-EFD7-4E67-93C2-5278206685DD}">
       <formula1>=IF(L286&lt;&gt;"",INDIRECT(VLOOKUP(L286,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N286" xr:uid="{E0F43EA1-C063-4215-9CF4-51C152C670B4}">
+    <dataValidation type="list" sqref="N286" xr:uid="{6E26A6F0-49AA-48A0-9378-776661B174FA}">
       <formula1>=IF(M286&lt;&gt;"",INDIRECT(VLOOKUP(M286,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M287" xr:uid="{956F1DF1-5061-4C8C-A091-91611B337C3F}">
+    <dataValidation type="list" sqref="M287" xr:uid="{EC5DB2BF-8869-460E-8244-8DFB6211EEA7}">
       <formula1>=IF(L287&lt;&gt;"",INDIRECT(VLOOKUP(L287,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N287" xr:uid="{8384F42E-C9B9-4397-B660-1023A2DE79DE}">
+    <dataValidation type="list" sqref="N287" xr:uid="{9F291DE4-7833-4A46-AB80-EA21BB85095A}">
       <formula1>=IF(M287&lt;&gt;"",INDIRECT(VLOOKUP(M287,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M288" xr:uid="{1D645A6E-5DD3-4047-B259-C56A9D10AE98}">
+    <dataValidation type="list" sqref="M288" xr:uid="{A1B53276-4437-48AF-99FE-E20E89FB00F0}">
       <formula1>=IF(L288&lt;&gt;"",INDIRECT(VLOOKUP(L288,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N288" xr:uid="{8EEB32FD-D3CE-412B-B1C1-F41401A64874}">
+    <dataValidation type="list" sqref="N288" xr:uid="{11D22194-8113-4504-97B3-09AEF65EBA3A}">
       <formula1>=IF(M288&lt;&gt;"",INDIRECT(VLOOKUP(M288,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M289" xr:uid="{C60FE1BF-E722-4A6D-A504-603EDC651C65}">
+    <dataValidation type="list" sqref="M289" xr:uid="{8D66F4F6-FF84-436E-9CF3-B5AFCC4EEF77}">
       <formula1>=IF(L289&lt;&gt;"",INDIRECT(VLOOKUP(L289,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N289" xr:uid="{F1745A72-56B9-47AD-B458-03B21C49CC4F}">
+    <dataValidation type="list" sqref="N289" xr:uid="{BFF2A06E-5B02-4C14-9C3A-8AD589D70C69}">
       <formula1>=IF(M289&lt;&gt;"",INDIRECT(VLOOKUP(M289,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M290" xr:uid="{637739F2-982C-4734-9EE8-11AC9F209F16}">
+    <dataValidation type="list" sqref="M290" xr:uid="{607A7F58-2790-4340-B996-D2D1F839E70D}">
       <formula1>=IF(L290&lt;&gt;"",INDIRECT(VLOOKUP(L290,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N290" xr:uid="{1B2F9B64-6A9B-4C01-9462-8E4B1759CE70}">
+    <dataValidation type="list" sqref="N290" xr:uid="{C7FF45BC-27C7-451E-9E1F-5465050676EE}">
       <formula1>=IF(M290&lt;&gt;"",INDIRECT(VLOOKUP(M290,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M291" xr:uid="{4796889E-EE05-4DFF-BEB2-72AB81B0D77F}">
+    <dataValidation type="list" sqref="M291" xr:uid="{460FC955-0DB3-483A-B9A6-68E167959C2C}">
       <formula1>=IF(L291&lt;&gt;"",INDIRECT(VLOOKUP(L291,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N291" xr:uid="{292443B8-ECF8-43A3-8D8A-B7D7DBC2A520}">
+    <dataValidation type="list" sqref="N291" xr:uid="{1731FA47-E648-445E-97DD-B71CF454B8A6}">
       <formula1>=IF(M291&lt;&gt;"",INDIRECT(VLOOKUP(M291,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M292" xr:uid="{BC0C70C1-731A-41ED-953F-9524AF666D56}">
+    <dataValidation type="list" sqref="M292" xr:uid="{43005CE4-A295-461A-8520-BC6189C73C69}">
       <formula1>=IF(L292&lt;&gt;"",INDIRECT(VLOOKUP(L292,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N292" xr:uid="{BDDAA876-85A7-410A-949A-794A2DBECB7E}">
+    <dataValidation type="list" sqref="N292" xr:uid="{EE7FCFB4-3CFF-417E-959F-7765AF96C83D}">
       <formula1>=IF(M292&lt;&gt;"",INDIRECT(VLOOKUP(M292,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M293" xr:uid="{46B20BF1-5C82-49DB-B9EC-059838CDA694}">
+    <dataValidation type="list" sqref="M293" xr:uid="{5B06E7BD-9A8C-4E8C-B05B-17B6A10FFAE1}">
       <formula1>=IF(L293&lt;&gt;"",INDIRECT(VLOOKUP(L293,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N293" xr:uid="{B6B933AB-3C65-40F2-83E7-76A51446516F}">
+    <dataValidation type="list" sqref="N293" xr:uid="{0F134DA8-44A6-403C-8BC8-862EAF58F492}">
       <formula1>=IF(M293&lt;&gt;"",INDIRECT(VLOOKUP(M293,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M294" xr:uid="{21A91D65-6B19-4D6A-A553-4628DC927DE5}">
+    <dataValidation type="list" sqref="M294" xr:uid="{6FFAE1D1-B0B2-4471-8ACC-5C9E41815FE1}">
       <formula1>=IF(L294&lt;&gt;"",INDIRECT(VLOOKUP(L294,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N294" xr:uid="{9F7AC2AA-9551-45FA-ACA0-31DF3497D0E5}">
+    <dataValidation type="list" sqref="N294" xr:uid="{E66E5FA2-E9ED-4557-90EF-0207CED8CCE5}">
       <formula1>=IF(M294&lt;&gt;"",INDIRECT(VLOOKUP(M294,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M295" xr:uid="{6A874541-A7EE-4891-9CD2-3E47DA956E88}">
+    <dataValidation type="list" sqref="M295" xr:uid="{D510B8A8-5D3A-4C83-8B02-712FBAA5AEB1}">
       <formula1>=IF(L295&lt;&gt;"",INDIRECT(VLOOKUP(L295,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N295" xr:uid="{3CB3EBF5-2852-4B82-841E-A9D7EC7CE25B}">
+    <dataValidation type="list" sqref="N295" xr:uid="{8C723048-9B37-485A-93BD-8F7761952E0D}">
       <formula1>=IF(M295&lt;&gt;"",INDIRECT(VLOOKUP(M295,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M296" xr:uid="{3E10A60E-DF39-4EAC-AA8D-C9FD24C6A5DE}">
+    <dataValidation type="list" sqref="M296" xr:uid="{5B6C2E55-FABA-43A3-B9EB-74D4BC630CBA}">
       <formula1>=IF(L296&lt;&gt;"",INDIRECT(VLOOKUP(L296,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N296" xr:uid="{3563D9B6-457E-423C-8616-64ADD9FA8460}">
+    <dataValidation type="list" sqref="N296" xr:uid="{51241140-5AA3-4DD5-B364-44F489585133}">
       <formula1>=IF(M296&lt;&gt;"",INDIRECT(VLOOKUP(M296,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M297" xr:uid="{EE5379D4-CF19-44A2-A13D-577439837158}">
+    <dataValidation type="list" sqref="M297" xr:uid="{E59D4E8A-530D-4026-9B80-98EFFF7036E0}">
       <formula1>=IF(L297&lt;&gt;"",INDIRECT(VLOOKUP(L297,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N297" xr:uid="{922A5149-7DB3-4967-9294-0183E1946678}">
+    <dataValidation type="list" sqref="N297" xr:uid="{90667F19-94FF-4D28-9D3C-99B2458BD1C0}">
       <formula1>=IF(M297&lt;&gt;"",INDIRECT(VLOOKUP(M297,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M298" xr:uid="{BB9C10EF-8F4E-49D8-8D6C-8A948C2318D2}">
+    <dataValidation type="list" sqref="M298" xr:uid="{B2CE0DD2-2C43-4420-9B92-AF67A87F5AFE}">
       <formula1>=IF(L298&lt;&gt;"",INDIRECT(VLOOKUP(L298,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N298" xr:uid="{F844E1F8-E868-4D6B-B8F5-4201FA8A2D75}">
+    <dataValidation type="list" sqref="N298" xr:uid="{BAC76D63-1148-488B-A78D-B95F74C9C662}">
       <formula1>=IF(M298&lt;&gt;"",INDIRECT(VLOOKUP(M298,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M299" xr:uid="{FB4558AE-3EE6-4D85-9A73-378F10B8CCAE}">
+    <dataValidation type="list" sqref="M299" xr:uid="{9543A070-871E-4924-993F-B0CB955231EF}">
       <formula1>=IF(L299&lt;&gt;"",INDIRECT(VLOOKUP(L299,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N299" xr:uid="{B988C94B-D29D-4CFA-81A6-17B80794D2C3}">
+    <dataValidation type="list" sqref="N299" xr:uid="{CF867515-5652-4D6F-906E-9FB7F9EAB1AC}">
       <formula1>=IF(M299&lt;&gt;"",INDIRECT(VLOOKUP(M299,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M300" xr:uid="{FD343BAA-2220-4F49-BA95-BFB1CE7062C9}">
+    <dataValidation type="list" sqref="M300" xr:uid="{1EF331BD-F302-4B48-8C33-86384B8302B6}">
       <formula1>=IF(L300&lt;&gt;"",INDIRECT(VLOOKUP(L300,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N300" xr:uid="{E90F1F13-249C-45E4-85DC-2AABABFAB2E7}">
+    <dataValidation type="list" sqref="N300" xr:uid="{914C78F8-5005-408B-A7D0-7C43BBE9657B}">
       <formula1>=IF(M300&lt;&gt;"",INDIRECT(VLOOKUP(M300,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M301" xr:uid="{BCFEFA5B-73B6-4F08-AC11-7BBA6C9AD085}">
+    <dataValidation type="list" sqref="M301" xr:uid="{3471FF1D-E984-44D4-A845-43E409CC5340}">
       <formula1>=IF(L301&lt;&gt;"",INDIRECT(VLOOKUP(L301,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N301" xr:uid="{9E0A1C13-4956-4B88-850D-976D5E2DC951}">
+    <dataValidation type="list" sqref="N301" xr:uid="{906C1C36-CF0E-4507-9DD1-F661903DD6F5}">
       <formula1>=IF(M301&lt;&gt;"",INDIRECT(VLOOKUP(M301,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M302" xr:uid="{69DA671C-8AC9-4B5A-BAA3-AF5DE3D683BC}">
+    <dataValidation type="list" sqref="M302" xr:uid="{FFDF1C75-FCCB-42B4-BE98-D00DCDE1734D}">
       <formula1>=IF(L302&lt;&gt;"",INDIRECT(VLOOKUP(L302,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N302" xr:uid="{0EF00D5E-8C04-48B5-B993-63243D640F01}">
+    <dataValidation type="list" sqref="N302" xr:uid="{6CC128C8-19EF-47B3-B5F3-B3D3A303686F}">
       <formula1>=IF(M302&lt;&gt;"",INDIRECT(VLOOKUP(M302,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M303" xr:uid="{6B41F4F8-800C-42AD-B6F1-7FEB6018F453}">
+    <dataValidation type="list" sqref="M303" xr:uid="{BFFB930A-09C2-406C-8E90-01B3185C081C}">
       <formula1>=IF(L303&lt;&gt;"",INDIRECT(VLOOKUP(L303,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N303" xr:uid="{DA8E3642-9702-4183-B48F-7EE62F1C27F6}">
+    <dataValidation type="list" sqref="N303" xr:uid="{DCC2B5F9-DB24-4280-9121-E3DBCD218B45}">
       <formula1>=IF(M303&lt;&gt;"",INDIRECT(VLOOKUP(M303,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M304" xr:uid="{BE6F8AC0-A375-487A-AD6D-5F72643E13C6}">
+    <dataValidation type="list" sqref="M304" xr:uid="{749A4D18-A8BD-4A66-A04A-ED49E4AF7D91}">
       <formula1>=IF(L304&lt;&gt;"",INDIRECT(VLOOKUP(L304,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N304" xr:uid="{E26F3650-2B4B-44D9-A612-44C269B62EEA}">
+    <dataValidation type="list" sqref="N304" xr:uid="{30C87FF7-BB72-487A-A461-9872F7021CF6}">
       <formula1>=IF(M304&lt;&gt;"",INDIRECT(VLOOKUP(M304,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M305" xr:uid="{61A7E6B3-3D62-4EDC-9DE8-5CED178E2E61}">
+    <dataValidation type="list" sqref="M305" xr:uid="{B3D60FF7-3D71-45B8-8A4A-E9D74A2A7C8B}">
       <formula1>=IF(L305&lt;&gt;"",INDIRECT(VLOOKUP(L305,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N305" xr:uid="{5666C2FD-1201-4307-B4D8-BAB2429570F8}">
+    <dataValidation type="list" sqref="N305" xr:uid="{4F1CE860-C067-45ED-8922-4D7604D7B481}">
       <formula1>=IF(M305&lt;&gt;"",INDIRECT(VLOOKUP(M305,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M306" xr:uid="{7D857B8A-E069-415D-B6D8-B628B08C659F}">
+    <dataValidation type="list" sqref="M306" xr:uid="{58D239F9-726E-4412-8906-60F511710A0F}">
       <formula1>=IF(L306&lt;&gt;"",INDIRECT(VLOOKUP(L306,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N306" xr:uid="{E7234D0E-54B5-4339-A41D-1DAE8CFC547D}">
+    <dataValidation type="list" sqref="N306" xr:uid="{D550FBDB-B488-42C8-B73F-FC8A665C94B7}">
       <formula1>=IF(M306&lt;&gt;"",INDIRECT(VLOOKUP(M306,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M307" xr:uid="{48A4B64F-EE37-4ED9-A46F-B8F5E7D2C9D4}">
+    <dataValidation type="list" sqref="M307" xr:uid="{53DDB99A-5679-43C3-B075-041C04CA07D6}">
       <formula1>=IF(L307&lt;&gt;"",INDIRECT(VLOOKUP(L307,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N307" xr:uid="{E5B7DE81-96E7-49F6-B5E3-BB029C5E8007}">
+    <dataValidation type="list" sqref="N307" xr:uid="{46698DE4-0867-410E-8607-CD5569BA8D02}">
       <formula1>=IF(M307&lt;&gt;"",INDIRECT(VLOOKUP(M307,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M308" xr:uid="{F8210A55-BB5B-48FA-93F5-6C2611E62234}">
+    <dataValidation type="list" sqref="M308" xr:uid="{834B5579-3A06-4EDB-BB2E-10680A2EADBB}">
       <formula1>=IF(L308&lt;&gt;"",INDIRECT(VLOOKUP(L308,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N308" xr:uid="{F8872A31-8593-46EE-8331-777B6E19C1CD}">
+    <dataValidation type="list" sqref="N308" xr:uid="{22ED8C74-60D4-455B-BC5A-E718F8E1188D}">
       <formula1>=IF(M308&lt;&gt;"",INDIRECT(VLOOKUP(M308,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M309" xr:uid="{E1B359EF-01B9-4700-8E9F-891FDE10AB06}">
+    <dataValidation type="list" sqref="M309" xr:uid="{E02EC392-912C-4DD0-922C-51C690446684}">
       <formula1>=IF(L309&lt;&gt;"",INDIRECT(VLOOKUP(L309,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N309" xr:uid="{9E8F201E-A148-446A-9BE2-A9E2E0DCAA9E}">
+    <dataValidation type="list" sqref="N309" xr:uid="{0B6FE01E-16DE-4664-87EE-696B2F051BD0}">
       <formula1>=IF(M309&lt;&gt;"",INDIRECT(VLOOKUP(M309,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M310" xr:uid="{0898350B-40D3-4CEC-B166-1BD6DD9C91C6}">
+    <dataValidation type="list" sqref="M310" xr:uid="{BABFC61A-82D5-4B63-998C-B16797E53DE2}">
       <formula1>=IF(L310&lt;&gt;"",INDIRECT(VLOOKUP(L310,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N310" xr:uid="{7C4BE710-6AC6-4D34-9F7E-6E8D62CF6BA6}">
+    <dataValidation type="list" sqref="N310" xr:uid="{2677BAAE-A51E-4977-A138-42D6E5B9B161}">
       <formula1>=IF(M310&lt;&gt;"",INDIRECT(VLOOKUP(M310,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M311" xr:uid="{F0C70385-7C80-4D37-A127-9BAFF07E7166}">
+    <dataValidation type="list" sqref="M311" xr:uid="{97EE2B59-CCCD-4A52-86D8-5BB1437E077F}">
       <formula1>=IF(L311&lt;&gt;"",INDIRECT(VLOOKUP(L311,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N311" xr:uid="{F58618C9-62D7-4EFB-B7B7-9B818B19D1BC}">
+    <dataValidation type="list" sqref="N311" xr:uid="{FC6F14CC-A9A9-4004-9968-FB51E73F67B1}">
       <formula1>=IF(M311&lt;&gt;"",INDIRECT(VLOOKUP(M311,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M312" xr:uid="{99A98BA9-1591-443F-875E-71769A11BE7E}">
+    <dataValidation type="list" sqref="M312" xr:uid="{D368A4DF-7574-42C6-8D48-526AFBA5E961}">
       <formula1>=IF(L312&lt;&gt;"",INDIRECT(VLOOKUP(L312,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N312" xr:uid="{7D47F8C5-CF85-44AF-8C95-392C683BC7D0}">
+    <dataValidation type="list" sqref="N312" xr:uid="{F5DE4A1B-EFE4-4901-9AC0-CD20EE0B5D15}">
       <formula1>=IF(M312&lt;&gt;"",INDIRECT(VLOOKUP(M312,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M313" xr:uid="{1F8E9BB1-73A2-42DC-B8A9-55F2A7864D26}">
+    <dataValidation type="list" sqref="M313" xr:uid="{6283C805-51E4-49B7-A274-1B8A229D3FDC}">
       <formula1>=IF(L313&lt;&gt;"",INDIRECT(VLOOKUP(L313,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N313" xr:uid="{51E1810D-03AE-46E3-AB27-84B52EC14BFF}">
+    <dataValidation type="list" sqref="N313" xr:uid="{1D08BCD1-8F22-448E-89B0-06302C1C31AA}">
       <formula1>=IF(M313&lt;&gt;"",INDIRECT(VLOOKUP(M313,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M314" xr:uid="{4FA1E6FE-EDBA-4F25-882B-E2C5DD614241}">
+    <dataValidation type="list" sqref="M314" xr:uid="{0E08D21B-E2EB-401F-8786-E522211B6A73}">
       <formula1>=IF(L314&lt;&gt;"",INDIRECT(VLOOKUP(L314,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N314" xr:uid="{2BD1F4D4-166F-41FB-9C09-C92EA057A31D}">
+    <dataValidation type="list" sqref="N314" xr:uid="{139F657B-9CA9-486D-88B4-02E80386C5E2}">
       <formula1>=IF(M314&lt;&gt;"",INDIRECT(VLOOKUP(M314,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M315" xr:uid="{C3A655AD-FB73-41F0-AC34-F8B227EC2CA6}">
+    <dataValidation type="list" sqref="M315" xr:uid="{CC016894-0BBC-4E8E-B8EF-9788DEE7CEAF}">
       <formula1>=IF(L315&lt;&gt;"",INDIRECT(VLOOKUP(L315,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N315" xr:uid="{53A665A5-474F-4F04-A4C0-E16862F69320}">
+    <dataValidation type="list" sqref="N315" xr:uid="{12AF3D80-EC3F-4F9D-A2D6-76CF7F2A9077}">
       <formula1>=IF(M315&lt;&gt;"",INDIRECT(VLOOKUP(M315,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M316" xr:uid="{F02C7B86-34C9-4FB7-94D2-CF279A8DAEDC}">
+    <dataValidation type="list" sqref="M316" xr:uid="{6F22DD64-F798-44CA-8B7C-68B6ADA937A4}">
       <formula1>=IF(L316&lt;&gt;"",INDIRECT(VLOOKUP(L316,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N316" xr:uid="{6EDFF03D-406F-403F-98AB-6A794414A198}">
+    <dataValidation type="list" sqref="N316" xr:uid="{7412D3A3-8EA4-438F-BF71-F9DEFF7DBA87}">
       <formula1>=IF(M316&lt;&gt;"",INDIRECT(VLOOKUP(M316,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M317" xr:uid="{FB0E12B8-1864-4ABA-8706-F43C49D9EBC2}">
+    <dataValidation type="list" sqref="M317" xr:uid="{E8103795-3BE6-47E2-90EB-B431CE1C71C7}">
       <formula1>=IF(L317&lt;&gt;"",INDIRECT(VLOOKUP(L317,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N317" xr:uid="{E4CE279C-F7AD-4A7A-AF5F-71C4111FC106}">
+    <dataValidation type="list" sqref="N317" xr:uid="{AC56DC6B-76FA-4FD3-8820-99E34FD94C95}">
       <formula1>=IF(M317&lt;&gt;"",INDIRECT(VLOOKUP(M317,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M318" xr:uid="{58AC1103-0555-47A0-81E7-FBFD403EC2AB}">
+    <dataValidation type="list" sqref="M318" xr:uid="{C06C9AF6-8F67-4593-8E1F-10BB5C864CAC}">
       <formula1>=IF(L318&lt;&gt;"",INDIRECT(VLOOKUP(L318,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N318" xr:uid="{6AB01C21-D96D-4CC0-AA0C-40F6499A9246}">
+    <dataValidation type="list" sqref="N318" xr:uid="{E6068998-5659-4441-9C6A-5DC82155223A}">
       <formula1>=IF(M318&lt;&gt;"",INDIRECT(VLOOKUP(M318,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M319" xr:uid="{D7B5C293-5510-464C-94F4-31A892D85B57}">
+    <dataValidation type="list" sqref="M319" xr:uid="{5E3A1D79-DB4E-481E-96F7-570AFFFC1CE8}">
       <formula1>=IF(L319&lt;&gt;"",INDIRECT(VLOOKUP(L319,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N319" xr:uid="{4ACBAC15-EA61-4BE3-8FC3-D0FE1996D297}">
+    <dataValidation type="list" sqref="N319" xr:uid="{B6045353-473E-48F1-AF6A-1E7D6D9528A8}">
       <formula1>=IF(M319&lt;&gt;"",INDIRECT(VLOOKUP(M319,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M320" xr:uid="{6F63F5D3-880F-4F97-9FFB-287239ABBA05}">
+    <dataValidation type="list" sqref="M320" xr:uid="{F51D6901-CEE1-4C61-89E6-DF4271E369A0}">
       <formula1>=IF(L320&lt;&gt;"",INDIRECT(VLOOKUP(L320,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N320" xr:uid="{13AF7632-628C-4A02-9355-276D69851BEC}">
+    <dataValidation type="list" sqref="N320" xr:uid="{27ADEB36-E4B4-4383-8CC7-E12D34805262}">
       <formula1>=IF(M320&lt;&gt;"",INDIRECT(VLOOKUP(M320,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M321" xr:uid="{19C16593-781F-4475-886C-E4528D8A241F}">
+    <dataValidation type="list" sqref="M321" xr:uid="{2EDEE83E-B521-4B8E-90D1-4C58A7590AC9}">
       <formula1>=IF(L321&lt;&gt;"",INDIRECT(VLOOKUP(L321,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N321" xr:uid="{052DFD2D-813E-4460-9BC3-350E7EE11120}">
+    <dataValidation type="list" sqref="N321" xr:uid="{DB1D14FC-C6A0-45AB-8CE7-2FED854A7C59}">
       <formula1>=IF(M321&lt;&gt;"",INDIRECT(VLOOKUP(M321,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M322" xr:uid="{225832DA-CE00-4859-ACE5-E775811533F9}">
+    <dataValidation type="list" sqref="M322" xr:uid="{7225A48B-F54F-47F3-B07E-FF526EDF42EE}">
       <formula1>=IF(L322&lt;&gt;"",INDIRECT(VLOOKUP(L322,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N322" xr:uid="{FE0E424A-D1FC-423F-B6B0-7147F7DADEB5}">
+    <dataValidation type="list" sqref="N322" xr:uid="{A3795398-EBD4-4FFD-9A57-2D387F54A3B9}">
       <formula1>=IF(M322&lt;&gt;"",INDIRECT(VLOOKUP(M322,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M323" xr:uid="{7482B98B-0A8D-4619-AC5C-90EDE4BF399E}">
+    <dataValidation type="list" sqref="M323" xr:uid="{CFC3EBA3-1360-4D84-AB16-31292853E56C}">
       <formula1>=IF(L323&lt;&gt;"",INDIRECT(VLOOKUP(L323,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N323" xr:uid="{54A6130D-0E4A-432F-8C4F-A2EFC6D8DE37}">
+    <dataValidation type="list" sqref="N323" xr:uid="{B0B387DA-B995-41F0-B8C8-5AE935E1E747}">
       <formula1>=IF(M323&lt;&gt;"",INDIRECT(VLOOKUP(M323,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M324" xr:uid="{D70C1EC4-91A3-4587-A0D0-88C932240B7D}">
+    <dataValidation type="list" sqref="M324" xr:uid="{DDAE98C8-3E7D-4263-8514-000FC885149E}">
       <formula1>=IF(L324&lt;&gt;"",INDIRECT(VLOOKUP(L324,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N324" xr:uid="{CB8758B0-F46D-4F5C-B425-B47382028424}">
+    <dataValidation type="list" sqref="N324" xr:uid="{7FCA4D31-2B14-4429-B85B-67EF3165C2A7}">
       <formula1>=IF(M324&lt;&gt;"",INDIRECT(VLOOKUP(M324,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M325" xr:uid="{EDB53BC6-F80D-4687-8671-9E491D2CD7AD}">
+    <dataValidation type="list" sqref="M325" xr:uid="{62E1189F-D1F8-4902-9080-37B895E48853}">
       <formula1>=IF(L325&lt;&gt;"",INDIRECT(VLOOKUP(L325,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N325" xr:uid="{5CA3B9E7-B7AA-4F1D-A881-175EED271DDD}">
+    <dataValidation type="list" sqref="N325" xr:uid="{E9D617BE-F55A-4249-848B-361D79A0371D}">
       <formula1>=IF(M325&lt;&gt;"",INDIRECT(VLOOKUP(M325,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M326" xr:uid="{2B1808A0-722B-4A2B-BF40-07E405A1C561}">
+    <dataValidation type="list" sqref="M326" xr:uid="{AC5A73B0-23AF-482E-8ECA-CBCBE4A99452}">
       <formula1>=IF(L326&lt;&gt;"",INDIRECT(VLOOKUP(L326,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N326" xr:uid="{1F60AD66-E810-4225-AFD4-8828D4C464C5}">
+    <dataValidation type="list" sqref="N326" xr:uid="{B03BB50A-F5D9-46EC-944E-3677F71D62B6}">
       <formula1>=IF(M326&lt;&gt;"",INDIRECT(VLOOKUP(M326,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M327" xr:uid="{5AA68EB3-B56F-4BBA-8148-6D7B3DE3FC75}">
+    <dataValidation type="list" sqref="M327" xr:uid="{5B71B5BB-9520-4179-BD30-04D488A847B8}">
       <formula1>=IF(L327&lt;&gt;"",INDIRECT(VLOOKUP(L327,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N327" xr:uid="{461E61C2-E296-43B7-A21E-EE058F5F20B4}">
+    <dataValidation type="list" sqref="N327" xr:uid="{AB1A32FE-9980-4234-AD3D-4B5BC1A8F679}">
       <formula1>=IF(M327&lt;&gt;"",INDIRECT(VLOOKUP(M327,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M328" xr:uid="{64783889-FB2D-40F7-8870-2208F90148A1}">
+    <dataValidation type="list" sqref="M328" xr:uid="{97849C6F-EC5E-4603-ACC8-C1A8A69CF00D}">
       <formula1>=IF(L328&lt;&gt;"",INDIRECT(VLOOKUP(L328,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N328" xr:uid="{839C5F50-52D6-4E93-BF8D-857E2211C585}">
+    <dataValidation type="list" sqref="N328" xr:uid="{797EDEC0-F931-4A79-8226-DB7E628015E6}">
       <formula1>=IF(M328&lt;&gt;"",INDIRECT(VLOOKUP(M328,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M329" xr:uid="{5E30CB1D-4997-4768-98C2-B5ED2D3721A2}">
+    <dataValidation type="list" sqref="M329" xr:uid="{01D89026-316F-4538-854A-7241F0651E2F}">
       <formula1>=IF(L329&lt;&gt;"",INDIRECT(VLOOKUP(L329,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N329" xr:uid="{218B5C88-3F03-4815-952A-F4794CEF02B9}">
+    <dataValidation type="list" sqref="N329" xr:uid="{0462A21D-93F5-48D7-9B23-39C3AC7A9ED5}">
       <formula1>=IF(M329&lt;&gt;"",INDIRECT(VLOOKUP(M329,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M330" xr:uid="{1F69F640-94F6-42C2-8A77-56D781B9546C}">
+    <dataValidation type="list" sqref="M330" xr:uid="{940673B0-3118-4B02-AF17-EC06A669D8C1}">
       <formula1>=IF(L330&lt;&gt;"",INDIRECT(VLOOKUP(L330,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N330" xr:uid="{1BF2BEFC-7716-431B-83DC-18D463CF1FD7}">
+    <dataValidation type="list" sqref="N330" xr:uid="{0B9E4835-CA89-4FED-9CAD-C10315E9C801}">
       <formula1>=IF(M330&lt;&gt;"",INDIRECT(VLOOKUP(M330,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M331" xr:uid="{5094B543-F077-4781-8B40-ED560603B5E9}">
+    <dataValidation type="list" sqref="M331" xr:uid="{8DF12241-70E2-4508-A3C8-EC9DF861CFED}">
       <formula1>=IF(L331&lt;&gt;"",INDIRECT(VLOOKUP(L331,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N331" xr:uid="{87F90438-063C-4A95-B3AF-8E2185A11DD4}">
+    <dataValidation type="list" sqref="N331" xr:uid="{1BE8DA61-BEB9-4C57-8EA9-33787A66C260}">
       <formula1>=IF(M331&lt;&gt;"",INDIRECT(VLOOKUP(M331,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M332" xr:uid="{316FDAC0-7F2C-497F-B139-447302502BDC}">
+    <dataValidation type="list" sqref="M332" xr:uid="{EA78BD88-31CE-41D1-9454-30F18CBAEC8E}">
       <formula1>=IF(L332&lt;&gt;"",INDIRECT(VLOOKUP(L332,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N332" xr:uid="{404ED91D-FCE1-4482-AE63-90BCD8BA1C62}">
+    <dataValidation type="list" sqref="N332" xr:uid="{4EAF060D-3C26-43EF-A12C-A8A5370EA66F}">
       <formula1>=IF(M332&lt;&gt;"",INDIRECT(VLOOKUP(M332,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M333" xr:uid="{6CC352F5-77A1-4833-9C30-324C4511FF1B}">
+    <dataValidation type="list" sqref="M333" xr:uid="{6D442EF9-B52C-4436-8D6A-A4162D20DCC6}">
       <formula1>=IF(L333&lt;&gt;"",INDIRECT(VLOOKUP(L333,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N333" xr:uid="{9CC5F320-FA43-4D34-8201-C1BAA3D94FF3}">
+    <dataValidation type="list" sqref="N333" xr:uid="{AB6F59F9-386A-4683-B5AC-1E1351E35E86}">
       <formula1>=IF(M333&lt;&gt;"",INDIRECT(VLOOKUP(M333,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M334" xr:uid="{B9F608FD-AC1C-487C-A344-63D49C45E9FC}">
+    <dataValidation type="list" sqref="M334" xr:uid="{FF3721BE-4F46-4262-9866-95877D36997E}">
       <formula1>=IF(L334&lt;&gt;"",INDIRECT(VLOOKUP(L334,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N334" xr:uid="{462BCFE0-E7C4-48C5-89A0-9453A643F961}">
+    <dataValidation type="list" sqref="N334" xr:uid="{67733296-CFE0-48CB-8B9F-533804AC2B64}">
       <formula1>=IF(M334&lt;&gt;"",INDIRECT(VLOOKUP(M334,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M335" xr:uid="{DC3851BF-8924-4AC8-BA49-DD363C0DA8A5}">
+    <dataValidation type="list" sqref="M335" xr:uid="{51B01C91-A1BA-4A16-A04D-FBFE5A9534D5}">
       <formula1>=IF(L335&lt;&gt;"",INDIRECT(VLOOKUP(L335,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N335" xr:uid="{3C73CACB-06D0-4CD6-8DD8-E24084C647BB}">
+    <dataValidation type="list" sqref="N335" xr:uid="{0B172E30-140B-437A-A159-9FF9AD919FE3}">
       <formula1>=IF(M335&lt;&gt;"",INDIRECT(VLOOKUP(M335,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M336" xr:uid="{7FD87BB1-A3F3-4344-9E1A-D3E6F8FAD6F8}">
+    <dataValidation type="list" sqref="M336" xr:uid="{616BC083-368A-47C0-AE8C-1750CD143D82}">
       <formula1>=IF(L336&lt;&gt;"",INDIRECT(VLOOKUP(L336,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N336" xr:uid="{D73C4C69-3530-4407-8AF9-1485FAD9DEE1}">
+    <dataValidation type="list" sqref="N336" xr:uid="{F76D095E-B603-45EC-A580-C186CF37E76D}">
       <formula1>=IF(M336&lt;&gt;"",INDIRECT(VLOOKUP(M336,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M337" xr:uid="{44F61A86-AE42-4D2A-87A3-CFAE4A3DF260}">
+    <dataValidation type="list" sqref="M337" xr:uid="{A95DD453-07FC-45C8-8107-4281E1F014F5}">
       <formula1>=IF(L337&lt;&gt;"",INDIRECT(VLOOKUP(L337,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N337" xr:uid="{4372B680-7F11-41E6-8ECE-3739F6ED6900}">
+    <dataValidation type="list" sqref="N337" xr:uid="{D222C533-5A76-4F00-976A-E1470E580E78}">
       <formula1>=IF(M337&lt;&gt;"",INDIRECT(VLOOKUP(M337,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M338" xr:uid="{A8D9AFB5-0AE3-4AB9-923B-30BFB26E2AFA}">
+    <dataValidation type="list" sqref="M338" xr:uid="{CD6A6458-BC38-4CB3-A6C1-CE480404C4A1}">
       <formula1>=IF(L338&lt;&gt;"",INDIRECT(VLOOKUP(L338,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N338" xr:uid="{C62CA265-1F06-47B7-BC4C-6609F04C5356}">
+    <dataValidation type="list" sqref="N338" xr:uid="{2B4DFA9F-A8D7-43D3-AD83-948FEE085596}">
       <formula1>=IF(M338&lt;&gt;"",INDIRECT(VLOOKUP(M338,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M339" xr:uid="{38577999-3FC3-4F42-A013-EBBC35398E61}">
+    <dataValidation type="list" sqref="M339" xr:uid="{C569992A-D2C0-4306-BC43-B1175E2C65CE}">
       <formula1>=IF(L339&lt;&gt;"",INDIRECT(VLOOKUP(L339,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N339" xr:uid="{577A0D04-756F-4DDB-B625-D16081FD2D14}">
+    <dataValidation type="list" sqref="N339" xr:uid="{55C96140-2055-44C1-AE68-6822D32B24D8}">
       <formula1>=IF(M339&lt;&gt;"",INDIRECT(VLOOKUP(M339,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M340" xr:uid="{0C9CADA4-4DD9-48B3-A255-602A49871B7D}">
+    <dataValidation type="list" sqref="M340" xr:uid="{601BA6A6-6109-468F-A7C4-41A5E3FEADD8}">
       <formula1>=IF(L340&lt;&gt;"",INDIRECT(VLOOKUP(L340,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N340" xr:uid="{97A0374E-49FE-405F-A957-4D0202B9D814}">
+    <dataValidation type="list" sqref="N340" xr:uid="{BC5E0913-04A7-4BA5-9DDA-67F230D9F464}">
       <formula1>=IF(M340&lt;&gt;"",INDIRECT(VLOOKUP(M340,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M341" xr:uid="{6E3B6403-0433-431A-9579-1C198C59ED96}">
+    <dataValidation type="list" sqref="M341" xr:uid="{7BDC5461-3EFE-49A9-8A93-61FF64E272AE}">
       <formula1>=IF(L341&lt;&gt;"",INDIRECT(VLOOKUP(L341,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N341" xr:uid="{A1B43F9A-5305-4C29-BA0F-C6C9269FA009}">
+    <dataValidation type="list" sqref="N341" xr:uid="{50CECB39-1198-47D2-A28B-D762B78A18CF}">
       <formula1>=IF(M341&lt;&gt;"",INDIRECT(VLOOKUP(M341,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M342" xr:uid="{6191A231-F044-4CB9-A3CF-4CA74C124C78}">
+    <dataValidation type="list" sqref="M342" xr:uid="{61D5D63D-C3F0-4BF4-9B68-56F1D93FFEE1}">
       <formula1>=IF(L342&lt;&gt;"",INDIRECT(VLOOKUP(L342,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N342" xr:uid="{DED6F900-74AA-4721-9A34-63850596DA1A}">
+    <dataValidation type="list" sqref="N342" xr:uid="{FEC71D7C-517A-4847-B8F6-593AF8A4DF06}">
       <formula1>=IF(M342&lt;&gt;"",INDIRECT(VLOOKUP(M342,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M343" xr:uid="{4952C526-8719-450E-944C-10E73239AE91}">
+    <dataValidation type="list" sqref="M343" xr:uid="{2142484A-9FFA-4D6D-BDE9-2170EB14C1B2}">
       <formula1>=IF(L343&lt;&gt;"",INDIRECT(VLOOKUP(L343,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N343" xr:uid="{035C273B-B9C2-46B2-A408-4EA9F47EA89C}">
+    <dataValidation type="list" sqref="N343" xr:uid="{F672086B-DA2C-49CE-A962-CF4376E1145B}">
       <formula1>=IF(M343&lt;&gt;"",INDIRECT(VLOOKUP(M343,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M344" xr:uid="{40D964B3-971C-4077-865A-5B696EF76CC8}">
+    <dataValidation type="list" sqref="M344" xr:uid="{235B818C-8671-42E8-AD0F-6045918B3C88}">
       <formula1>=IF(L344&lt;&gt;"",INDIRECT(VLOOKUP(L344,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N344" xr:uid="{7D3F6BBF-5CAB-4859-94E7-60B87BF0EB14}">
+    <dataValidation type="list" sqref="N344" xr:uid="{92BD0EF7-A7C8-4142-B461-0D8DCD066217}">
       <formula1>=IF(M344&lt;&gt;"",INDIRECT(VLOOKUP(M344,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M345" xr:uid="{7AC81228-6639-4D5A-9A12-C68653E1480C}">
+    <dataValidation type="list" sqref="M345" xr:uid="{00C00717-B7A3-433E-9AC3-3023082B420F}">
       <formula1>=IF(L345&lt;&gt;"",INDIRECT(VLOOKUP(L345,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N345" xr:uid="{5BCEA4A7-B32A-4B65-9402-02D94FC2EBC7}">
+    <dataValidation type="list" sqref="N345" xr:uid="{75E957FE-4299-4ABE-94D5-A78D184ED968}">
       <formula1>=IF(M345&lt;&gt;"",INDIRECT(VLOOKUP(M345,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M346" xr:uid="{34FB758C-530F-41AE-ADD4-D5F0A2543652}">
+    <dataValidation type="list" sqref="M346" xr:uid="{2143E67E-2A28-4B61-81B7-7770A4083077}">
       <formula1>=IF(L346&lt;&gt;"",INDIRECT(VLOOKUP(L346,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N346" xr:uid="{C502532C-707B-4F53-9E3F-2A19967EEB11}">
+    <dataValidation type="list" sqref="N346" xr:uid="{1FA023FA-6C08-4340-A287-80D11354580E}">
       <formula1>=IF(M346&lt;&gt;"",INDIRECT(VLOOKUP(M346,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M347" xr:uid="{9CB2460C-70F6-4B3E-B771-BB4A12E99EC0}">
+    <dataValidation type="list" sqref="M347" xr:uid="{EE211D5F-00B0-4DD5-9A5F-B09C56C73B8A}">
       <formula1>=IF(L347&lt;&gt;"",INDIRECT(VLOOKUP(L347,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N347" xr:uid="{5A068B1C-4560-41D0-A9F1-A71FDD3C778E}">
+    <dataValidation type="list" sqref="N347" xr:uid="{BCB0F3BA-8382-44DC-85DA-4935ECE44367}">
       <formula1>=IF(M347&lt;&gt;"",INDIRECT(VLOOKUP(M347,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M348" xr:uid="{A21189BE-E71E-42F2-8EBE-5B71BBF89C54}">
+    <dataValidation type="list" sqref="M348" xr:uid="{23F28435-38C8-4BC6-B15E-08C31F2B4A6A}">
       <formula1>=IF(L348&lt;&gt;"",INDIRECT(VLOOKUP(L348,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N348" xr:uid="{FEAC90D8-5F28-4CD4-B7B8-328666789230}">
+    <dataValidation type="list" sqref="N348" xr:uid="{E6DCEC5B-FF29-464E-BB1F-00EDAC2A2E3C}">
       <formula1>=IF(M348&lt;&gt;"",INDIRECT(VLOOKUP(M348,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M349" xr:uid="{C81FE709-028E-4939-A48A-F1170205FE7F}">
+    <dataValidation type="list" sqref="M349" xr:uid="{C5EBBF6E-18F6-462C-80CB-9C45FA48A2EB}">
       <formula1>=IF(L349&lt;&gt;"",INDIRECT(VLOOKUP(L349,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N349" xr:uid="{9DF25446-04F2-4BC4-B74F-2AEDA4E2A0E8}">
+    <dataValidation type="list" sqref="N349" xr:uid="{27338705-97F0-4485-B8A4-E37AF888B169}">
       <formula1>=IF(M349&lt;&gt;"",INDIRECT(VLOOKUP(M349,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M350" xr:uid="{9BF06012-A299-4155-909C-84FC551D6EB3}">
+    <dataValidation type="list" sqref="M350" xr:uid="{924C8DCC-6AF2-48E0-875A-F63C37D65902}">
       <formula1>=IF(L350&lt;&gt;"",INDIRECT(VLOOKUP(L350,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N350" xr:uid="{5210611D-5979-4605-8564-095FFF2EEB52}">
+    <dataValidation type="list" sqref="N350" xr:uid="{A158B72B-36D7-4592-B450-D9C5D6720DC1}">
       <formula1>=IF(M350&lt;&gt;"",INDIRECT(VLOOKUP(M350,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M351" xr:uid="{02D58A8A-FB96-4B78-8079-5390868F7EDA}">
+    <dataValidation type="list" sqref="M351" xr:uid="{0F7D6C27-4F84-455A-8EAC-9F6041ACDB03}">
       <formula1>=IF(L351&lt;&gt;"",INDIRECT(VLOOKUP(L351,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N351" xr:uid="{4C7CA9A6-E4D6-43A7-978A-85E231717D93}">
+    <dataValidation type="list" sqref="N351" xr:uid="{69EF4370-3E4D-4237-9F1A-17023DC0EF62}">
       <formula1>=IF(M351&lt;&gt;"",INDIRECT(VLOOKUP(M351,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M352" xr:uid="{E98BDAEF-799B-42EA-A2C1-DEFC2F27E6D4}">
+    <dataValidation type="list" sqref="M352" xr:uid="{7B6725BF-9F91-4E25-B623-7D7F9560BB37}">
       <formula1>=IF(L352&lt;&gt;"",INDIRECT(VLOOKUP(L352,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N352" xr:uid="{209F88F3-D1B3-41A6-AFB7-1CA1E8E50932}">
+    <dataValidation type="list" sqref="N352" xr:uid="{6240577A-CB16-45EE-80E8-A5772DF364E9}">
       <formula1>=IF(M352&lt;&gt;"",INDIRECT(VLOOKUP(M352,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M353" xr:uid="{4D5317E8-D5B7-454C-8227-A56E3302F1F0}">
+    <dataValidation type="list" sqref="M353" xr:uid="{32AA9212-19C0-476E-A9B2-DCB1C0375A34}">
       <formula1>=IF(L353&lt;&gt;"",INDIRECT(VLOOKUP(L353,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N353" xr:uid="{C3F56D06-5395-4DD7-A09B-23D7B2B4ACEF}">
+    <dataValidation type="list" sqref="N353" xr:uid="{0B285D9E-346A-4B12-83C8-BB262513D42E}">
       <formula1>=IF(M353&lt;&gt;"",INDIRECT(VLOOKUP(M353,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M354" xr:uid="{40776FB3-540F-434F-9DE3-75D9A5A469D9}">
+    <dataValidation type="list" sqref="M354" xr:uid="{7D3ED8DA-845F-4D20-B2C8-811297377D3E}">
       <formula1>=IF(L354&lt;&gt;"",INDIRECT(VLOOKUP(L354,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N354" xr:uid="{A47B9A37-091A-4F56-88AC-4A5428F6585C}">
+    <dataValidation type="list" sqref="N354" xr:uid="{4A3ABB19-F859-4A25-985C-8BEEEAD6C5AA}">
       <formula1>=IF(M354&lt;&gt;"",INDIRECT(VLOOKUP(M354,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M355" xr:uid="{6B751783-58BB-45FD-B259-77DF8F22DFD1}">
+    <dataValidation type="list" sqref="M355" xr:uid="{6F571823-6519-4B43-94F4-99B421615541}">
       <formula1>=IF(L355&lt;&gt;"",INDIRECT(VLOOKUP(L355,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N355" xr:uid="{8DB69C6E-7C22-49F8-8130-B73E3B3B891C}">
+    <dataValidation type="list" sqref="N355" xr:uid="{BD51B76F-B24F-4D32-83A6-075E803E08B8}">
       <formula1>=IF(M355&lt;&gt;"",INDIRECT(VLOOKUP(M355,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M356" xr:uid="{8442F979-1B21-42B8-8045-AD809EAABBCD}">
+    <dataValidation type="list" sqref="M356" xr:uid="{86F6CBC9-0628-46D6-A0A6-65970BAAE7BD}">
       <formula1>=IF(L356&lt;&gt;"",INDIRECT(VLOOKUP(L356,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N356" xr:uid="{8E8FC500-C3D0-426B-94DC-39F8238B5689}">
+    <dataValidation type="list" sqref="N356" xr:uid="{A17D3967-7A9C-4A09-B270-8E2B76F83C8E}">
       <formula1>=IF(M356&lt;&gt;"",INDIRECT(VLOOKUP(M356,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M357" xr:uid="{1409C9AF-4E11-4826-9D88-61CDEDBDF03F}">
+    <dataValidation type="list" sqref="M357" xr:uid="{09713CA2-6A5C-4F97-B90D-330BDFDE89D6}">
       <formula1>=IF(L357&lt;&gt;"",INDIRECT(VLOOKUP(L357,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N357" xr:uid="{7E9EEA41-AE38-4DA7-9AB8-2575296D92D6}">
+    <dataValidation type="list" sqref="N357" xr:uid="{70E3C5F5-2EFE-4D9D-A189-9A35EF9E5F34}">
       <formula1>=IF(M357&lt;&gt;"",INDIRECT(VLOOKUP(M357,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M358" xr:uid="{2E5CB641-6E79-467B-9CA7-000DA5C43AD9}">
+    <dataValidation type="list" sqref="M358" xr:uid="{0E8AB96D-223C-48A7-BAA8-1B1DB9B552AE}">
       <formula1>=IF(L358&lt;&gt;"",INDIRECT(VLOOKUP(L358,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N358" xr:uid="{485C79E2-7C68-4D05-8536-DA5F133B9C0B}">
+    <dataValidation type="list" sqref="N358" xr:uid="{D0A4364E-F319-4F76-B97C-C861342987FA}">
       <formula1>=IF(M358&lt;&gt;"",INDIRECT(VLOOKUP(M358,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M359" xr:uid="{7EE9E106-A109-415A-A40D-AFE6F0148C7E}">
+    <dataValidation type="list" sqref="M359" xr:uid="{1278C21F-C658-4A27-BC97-911CDED4B242}">
       <formula1>=IF(L359&lt;&gt;"",INDIRECT(VLOOKUP(L359,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N359" xr:uid="{F64C82A0-2864-4EE4-89CE-546B93E9EAB9}">
+    <dataValidation type="list" sqref="N359" xr:uid="{21BF19FA-04EF-4BEB-99C3-EB422FE97F52}">
       <formula1>=IF(M359&lt;&gt;"",INDIRECT(VLOOKUP(M359,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M360" xr:uid="{DD53077E-3C02-4802-957C-05C9ADE3D070}">
+    <dataValidation type="list" sqref="M360" xr:uid="{C5E4CE65-4695-4434-91B7-A00D00E42B98}">
       <formula1>=IF(L360&lt;&gt;"",INDIRECT(VLOOKUP(L360,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N360" xr:uid="{5D71E230-148C-4D82-96FA-07A4591833DF}">
+    <dataValidation type="list" sqref="N360" xr:uid="{E173810A-1487-450E-BAB2-6611DD95CC7D}">
       <formula1>=IF(M360&lt;&gt;"",INDIRECT(VLOOKUP(M360,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M361" xr:uid="{C3270214-C65E-4029-AF54-1E62F5F2AA7C}">
+    <dataValidation type="list" sqref="M361" xr:uid="{FA9D5332-A393-45D7-BA92-5EB30B8ED7AB}">
       <formula1>=IF(L361&lt;&gt;"",INDIRECT(VLOOKUP(L361,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N361" xr:uid="{743288D1-19B2-4EC8-BD94-E23F6A2FF599}">
+    <dataValidation type="list" sqref="N361" xr:uid="{FC049C49-3FEF-4B9F-B667-CE9DBE34B4AE}">
       <formula1>=IF(M361&lt;&gt;"",INDIRECT(VLOOKUP(M361,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M362" xr:uid="{9EDD622D-D521-4673-8A6A-F3D1BD11CD40}">
+    <dataValidation type="list" sqref="M362" xr:uid="{C9A2136A-4B40-416D-AB05-77FF3CE8A1EC}">
       <formula1>=IF(L362&lt;&gt;"",INDIRECT(VLOOKUP(L362,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N362" xr:uid="{4C577366-5655-4217-BF16-8A735C63B097}">
+    <dataValidation type="list" sqref="N362" xr:uid="{D277D473-2DDE-4D39-BE3D-2DA5F12C1081}">
       <formula1>=IF(M362&lt;&gt;"",INDIRECT(VLOOKUP(M362,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M363" xr:uid="{4CD93EAC-3AD4-4470-9775-4EBE1549BD65}">
+    <dataValidation type="list" sqref="M363" xr:uid="{C375B161-B0CB-474B-9CBE-5ACD504CEE44}">
       <formula1>=IF(L363&lt;&gt;"",INDIRECT(VLOOKUP(L363,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N363" xr:uid="{BEADD264-710F-4BF8-B9FB-AD155D53261B}">
+    <dataValidation type="list" sqref="N363" xr:uid="{AB3B8626-45EC-49D6-9C0D-65D29E6C50C4}">
       <formula1>=IF(M363&lt;&gt;"",INDIRECT(VLOOKUP(M363,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M364" xr:uid="{59E2D1FA-0A51-4CC9-A29B-FEA7069839B1}">
+    <dataValidation type="list" sqref="M364" xr:uid="{F8E0B377-3EE1-4C04-A76B-6C9BF8738BE0}">
       <formula1>=IF(L364&lt;&gt;"",INDIRECT(VLOOKUP(L364,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N364" xr:uid="{46C56889-6134-4C84-8FC1-C938C691245E}">
+    <dataValidation type="list" sqref="N364" xr:uid="{FE73CE0D-779A-4916-93D2-B254E6F0156F}">
       <formula1>=IF(M364&lt;&gt;"",INDIRECT(VLOOKUP(M364,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M365" xr:uid="{98A6E4B1-414F-4AB6-AC4E-6F11B6D6AD03}">
+    <dataValidation type="list" sqref="M365" xr:uid="{CC088378-C8AE-4C60-AEEA-6D44C4D520F6}">
       <formula1>=IF(L365&lt;&gt;"",INDIRECT(VLOOKUP(L365,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N365" xr:uid="{7CC075E8-F9F8-42BB-AD79-D9171E0A8C1B}">
+    <dataValidation type="list" sqref="N365" xr:uid="{B08013C3-1055-47CE-9B2C-B40810C04979}">
       <formula1>=IF(M365&lt;&gt;"",INDIRECT(VLOOKUP(M365,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M366" xr:uid="{4D984C57-A024-4387-A2DF-53AD871F5D27}">
+    <dataValidation type="list" sqref="M366" xr:uid="{CCC89D02-1271-4CFA-AFD7-45607210AEE4}">
       <formula1>=IF(L366&lt;&gt;"",INDIRECT(VLOOKUP(L366,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N366" xr:uid="{BE6DBCA4-103E-4729-BD6A-DC28A017B10F}">
+    <dataValidation type="list" sqref="N366" xr:uid="{4C3205BD-8A84-44E7-B183-0E571AF21161}">
       <formula1>=IF(M366&lt;&gt;"",INDIRECT(VLOOKUP(M366,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M367" xr:uid="{E41F7A48-3495-4439-B378-80C713E0C10F}">
+    <dataValidation type="list" sqref="M367" xr:uid="{4966AD42-6B6A-4A6F-9C2E-D803BB9C9B1D}">
       <formula1>=IF(L367&lt;&gt;"",INDIRECT(VLOOKUP(L367,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N367" xr:uid="{C019E3C1-83DF-4387-BE87-E1C01159BC71}">
+    <dataValidation type="list" sqref="N367" xr:uid="{3BDFF9A2-6289-48F9-9920-966C18CD6FB3}">
       <formula1>=IF(M367&lt;&gt;"",INDIRECT(VLOOKUP(M367,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M368" xr:uid="{38029374-79AA-4F70-9B04-06CF3A558220}">
+    <dataValidation type="list" sqref="M368" xr:uid="{8469D40B-3131-4854-8E2A-4835A6A585A9}">
       <formula1>=IF(L368&lt;&gt;"",INDIRECT(VLOOKUP(L368,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N368" xr:uid="{80136504-65C6-4391-8353-15A424C6B58D}">
+    <dataValidation type="list" sqref="N368" xr:uid="{003EE87C-AC88-41B5-9667-E0C881F0112F}">
       <formula1>=IF(M368&lt;&gt;"",INDIRECT(VLOOKUP(M368,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M369" xr:uid="{976D19E8-E2EF-4FE9-A883-00D9B1C7F483}">
+    <dataValidation type="list" sqref="M369" xr:uid="{54E9C069-6234-4B50-973D-DD33ECB01080}">
       <formula1>=IF(L369&lt;&gt;"",INDIRECT(VLOOKUP(L369,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N369" xr:uid="{B3E86F47-E2E4-4AD7-89BC-4FC1770E051F}">
+    <dataValidation type="list" sqref="N369" xr:uid="{5ADED4F8-8563-4D09-A7F8-F6E53197D0C2}">
       <formula1>=IF(M369&lt;&gt;"",INDIRECT(VLOOKUP(M369,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M370" xr:uid="{DC18C1D9-ED45-4905-ACAE-5841CA3CABFF}">
+    <dataValidation type="list" sqref="M370" xr:uid="{CCDC555D-EA22-4B0B-9133-4017D1FAFC8F}">
       <formula1>=IF(L370&lt;&gt;"",INDIRECT(VLOOKUP(L370,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N370" xr:uid="{49875AAF-A84B-4046-B154-5316C970BA23}">
+    <dataValidation type="list" sqref="N370" xr:uid="{13B9282D-E653-43C4-9AFE-8E4BE5650646}">
       <formula1>=IF(M370&lt;&gt;"",INDIRECT(VLOOKUP(M370,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M371" xr:uid="{6D9A00CA-08EB-4302-AAEE-5B46EC9B6114}">
+    <dataValidation type="list" sqref="M371" xr:uid="{457DFA3D-626A-442A-839A-DF6FA8852A98}">
       <formula1>=IF(L371&lt;&gt;"",INDIRECT(VLOOKUP(L371,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N371" xr:uid="{DF62BF80-C640-402A-94FA-624C353551A5}">
+    <dataValidation type="list" sqref="N371" xr:uid="{90DCF2F8-4715-45D1-AE43-4CE84E6A594E}">
       <formula1>=IF(M371&lt;&gt;"",INDIRECT(VLOOKUP(M371,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M372" xr:uid="{BC0C7332-66C0-4A8F-AFBD-254839463CFA}">
+    <dataValidation type="list" sqref="M372" xr:uid="{0059C3C4-8B7C-4982-922C-EFB382DC6B8A}">
       <formula1>=IF(L372&lt;&gt;"",INDIRECT(VLOOKUP(L372,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N372" xr:uid="{5B149184-62B6-4657-BFFA-71CC95D68306}">
+    <dataValidation type="list" sqref="N372" xr:uid="{A8F89FB3-E8A5-4952-9711-ED9BB6E63DDD}">
       <formula1>=IF(M372&lt;&gt;"",INDIRECT(VLOOKUP(M372,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M373" xr:uid="{7DC31AE4-DC85-443C-BEFD-0CDCDCCA68F6}">
+    <dataValidation type="list" sqref="M373" xr:uid="{669A5F55-A211-4BD0-BA8A-386F8B4D848F}">
       <formula1>=IF(L373&lt;&gt;"",INDIRECT(VLOOKUP(L373,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N373" xr:uid="{F00544EE-84EC-4E25-BC17-D98E32BA132D}">
+    <dataValidation type="list" sqref="N373" xr:uid="{F9CB1D45-14D5-4B8F-83FE-EE0ECC8BD5E6}">
       <formula1>=IF(M373&lt;&gt;"",INDIRECT(VLOOKUP(M373,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M374" xr:uid="{DEFEFF78-503A-4A85-B99B-B89BDFF6D2E4}">
+    <dataValidation type="list" sqref="M374" xr:uid="{D2B796C6-EEEF-49AD-85E6-73BDC4F38B2F}">
       <formula1>=IF(L374&lt;&gt;"",INDIRECT(VLOOKUP(L374,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N374" xr:uid="{ACD01551-77BA-4626-A9F6-E1FA93E3F1BD}">
+    <dataValidation type="list" sqref="N374" xr:uid="{B205585E-A058-4ADB-A25B-BEE9D802BE84}">
       <formula1>=IF(M374&lt;&gt;"",INDIRECT(VLOOKUP(M374,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M375" xr:uid="{56BBF29A-E87F-4BCC-A13B-4F0A8B9EF47D}">
+    <dataValidation type="list" sqref="M375" xr:uid="{FF196106-CFB0-46BF-94CE-6399E9AB5977}">
       <formula1>=IF(L375&lt;&gt;"",INDIRECT(VLOOKUP(L375,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N375" xr:uid="{4440D776-2360-4B11-BF51-A52E16BD64FB}">
+    <dataValidation type="list" sqref="N375" xr:uid="{269A5B3D-F1A9-46E6-9024-2FFCA3572719}">
       <formula1>=IF(M375&lt;&gt;"",INDIRECT(VLOOKUP(M375,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M376" xr:uid="{5ED6D803-792A-4F13-8107-4BB15724EE5F}">
+    <dataValidation type="list" sqref="M376" xr:uid="{A6E6FD3A-32B8-43AA-830E-8521F058C642}">
       <formula1>=IF(L376&lt;&gt;"",INDIRECT(VLOOKUP(L376,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N376" xr:uid="{5F6DBC04-52D7-44FB-833B-D898AC1AB93F}">
+    <dataValidation type="list" sqref="N376" xr:uid="{A34FF8BC-9452-42C7-ACD0-A5DB9EF78589}">
       <formula1>=IF(M376&lt;&gt;"",INDIRECT(VLOOKUP(M376,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M377" xr:uid="{7A9C08A4-9198-4042-9A14-1E5CC0408993}">
+    <dataValidation type="list" sqref="M377" xr:uid="{A63D2D2F-B107-422E-9C85-B6F80025B2A6}">
       <formula1>=IF(L377&lt;&gt;"",INDIRECT(VLOOKUP(L377,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N377" xr:uid="{83ED5637-0501-4D5E-A591-DA4EF81F600B}">
+    <dataValidation type="list" sqref="N377" xr:uid="{BAE8AFF3-96DB-468A-86DC-A09D56253174}">
       <formula1>=IF(M377&lt;&gt;"",INDIRECT(VLOOKUP(M377,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M378" xr:uid="{21574FA9-2DD4-4ECA-9D98-A0170F8C8580}">
+    <dataValidation type="list" sqref="M378" xr:uid="{3B701B33-5FB8-4F5D-BB59-88C318C69AFA}">
       <formula1>=IF(L378&lt;&gt;"",INDIRECT(VLOOKUP(L378,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N378" xr:uid="{0BD23514-75E1-44AC-AC3B-1DA20343D387}">
+    <dataValidation type="list" sqref="N378" xr:uid="{45C858A2-6C37-4A92-8E81-5FFF3EB47146}">
       <formula1>=IF(M378&lt;&gt;"",INDIRECT(VLOOKUP(M378,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M379" xr:uid="{1D955661-00EF-4497-8CC0-DD78FADBCCBE}">
+    <dataValidation type="list" sqref="M379" xr:uid="{65DE6250-3981-4617-8867-A3B6F86CE41D}">
       <formula1>=IF(L379&lt;&gt;"",INDIRECT(VLOOKUP(L379,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N379" xr:uid="{9051600A-4ADA-47C8-8C7C-DACAD052F907}">
+    <dataValidation type="list" sqref="N379" xr:uid="{799849D0-CAA7-4FC9-B3ED-D3A3B0D5C5C9}">
       <formula1>=IF(M379&lt;&gt;"",INDIRECT(VLOOKUP(M379,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M380" xr:uid="{45DD6C9F-C1F5-4406-A2FF-662299C00E9D}">
+    <dataValidation type="list" sqref="M380" xr:uid="{D1914DE8-5248-4BBD-AFE1-40CE9A0AD2BB}">
       <formula1>=IF(L380&lt;&gt;"",INDIRECT(VLOOKUP(L380,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N380" xr:uid="{D50A8153-A928-45C4-ABC0-87ED27E93295}">
+    <dataValidation type="list" sqref="N380" xr:uid="{D23DA842-9186-486A-A811-386925DAC897}">
       <formula1>=IF(M380&lt;&gt;"",INDIRECT(VLOOKUP(M380,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M381" xr:uid="{3312559A-E137-4673-ACA5-A759141F48E9}">
+    <dataValidation type="list" sqref="M381" xr:uid="{40DD2961-D7A4-4CCC-8338-5C4B409CDB12}">
       <formula1>=IF(L381&lt;&gt;"",INDIRECT(VLOOKUP(L381,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N381" xr:uid="{6EFFABAD-E089-4068-ABAC-1187BDF96A7C}">
+    <dataValidation type="list" sqref="N381" xr:uid="{433B655B-C438-4A40-B6C0-81F76AD4189E}">
       <formula1>=IF(M381&lt;&gt;"",INDIRECT(VLOOKUP(M381,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M382" xr:uid="{701AE994-807D-43D3-BD65-E7A138960183}">
+    <dataValidation type="list" sqref="M382" xr:uid="{C8872C00-0970-46AB-9E1E-F3D7B4446C22}">
       <formula1>=IF(L382&lt;&gt;"",INDIRECT(VLOOKUP(L382,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N382" xr:uid="{2276F55E-5563-4537-B363-12275996C6C7}">
+    <dataValidation type="list" sqref="N382" xr:uid="{A9F324A3-B2A2-43A9-8122-DCACB3E0C298}">
       <formula1>=IF(M382&lt;&gt;"",INDIRECT(VLOOKUP(M382,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M383" xr:uid="{71390691-E248-4F55-BE0A-7690B4372B6E}">
+    <dataValidation type="list" sqref="M383" xr:uid="{7F06DDF4-2211-463D-AF9F-173C8F1678ED}">
       <formula1>=IF(L383&lt;&gt;"",INDIRECT(VLOOKUP(L383,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N383" xr:uid="{1CB4BF22-3D3B-4906-8CFE-E55B374B8F7A}">
+    <dataValidation type="list" sqref="N383" xr:uid="{DCFA4057-5982-4BBF-A7BB-C818042F03C6}">
       <formula1>=IF(M383&lt;&gt;"",INDIRECT(VLOOKUP(M383,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M384" xr:uid="{79777C1D-5315-4985-97F0-9822A4E796F9}">
+    <dataValidation type="list" sqref="M384" xr:uid="{2CE46FB1-EFD8-4200-885A-14ADE7413F66}">
       <formula1>=IF(L384&lt;&gt;"",INDIRECT(VLOOKUP(L384,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N384" xr:uid="{225D9BF5-4FD2-4375-AAA3-DE6ECF827869}">
+    <dataValidation type="list" sqref="N384" xr:uid="{3AE78786-4B5F-4DA2-A1BE-32B92B50C9A4}">
       <formula1>=IF(M384&lt;&gt;"",INDIRECT(VLOOKUP(M384,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M385" xr:uid="{79042917-2A24-45B5-8D73-57FF6D87421D}">
+    <dataValidation type="list" sqref="M385" xr:uid="{D9655C9D-3002-4C10-B02A-EE1FFEF6BAE8}">
       <formula1>=IF(L385&lt;&gt;"",INDIRECT(VLOOKUP(L385,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N385" xr:uid="{1731E6C7-B99F-4733-9431-70798B3C8BA6}">
+    <dataValidation type="list" sqref="N385" xr:uid="{2C96C275-3DB3-4070-B03B-0F9A46EFA3AB}">
       <formula1>=IF(M385&lt;&gt;"",INDIRECT(VLOOKUP(M385,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M386" xr:uid="{7E7D81E2-7CFE-45DC-9937-937B4A26C177}">
+    <dataValidation type="list" sqref="M386" xr:uid="{814B78E1-0AA4-49F9-A972-81C1BED45182}">
       <formula1>=IF(L386&lt;&gt;"",INDIRECT(VLOOKUP(L386,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N386" xr:uid="{0F22A3E8-18B5-4A0D-8B8B-E289393427B1}">
+    <dataValidation type="list" sqref="N386" xr:uid="{59A48A69-DBEF-4C7B-9FF9-DB0736F836ED}">
       <formula1>=IF(M386&lt;&gt;"",INDIRECT(VLOOKUP(M386,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M387" xr:uid="{F2D26C29-8449-4B83-ADF6-366FA8FE821B}">
+    <dataValidation type="list" sqref="M387" xr:uid="{02A1FD94-1319-4C87-A747-B5E61A419534}">
       <formula1>=IF(L387&lt;&gt;"",INDIRECT(VLOOKUP(L387,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N387" xr:uid="{1D72BAC8-0DAD-4416-9490-F1754B746CA2}">
+    <dataValidation type="list" sqref="N387" xr:uid="{4086D1A8-F60D-4ED0-AB00-4545322D0AD1}">
       <formula1>=IF(M387&lt;&gt;"",INDIRECT(VLOOKUP(M387,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M388" xr:uid="{10897D46-56B5-4194-8BD3-F25281448C08}">
+    <dataValidation type="list" sqref="M388" xr:uid="{ED50C6BF-AF34-4595-AF53-189FDEFBECBB}">
       <formula1>=IF(L388&lt;&gt;"",INDIRECT(VLOOKUP(L388,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N388" xr:uid="{E6BE5AEC-C15E-4B4F-9BA5-6F18FFF2D4A4}">
+    <dataValidation type="list" sqref="N388" xr:uid="{44258B62-CEE9-40B7-9CDE-19648497C5C5}">
       <formula1>=IF(M388&lt;&gt;"",INDIRECT(VLOOKUP(M388,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M389" xr:uid="{933F4B3E-52EA-45A2-8CF9-E4A1B51BA0BA}">
+    <dataValidation type="list" sqref="M389" xr:uid="{5255D9B5-576F-4155-808B-844589E8D617}">
       <formula1>=IF(L389&lt;&gt;"",INDIRECT(VLOOKUP(L389,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N389" xr:uid="{DB340752-99BD-4A4B-A4B6-74B39E385C19}">
+    <dataValidation type="list" sqref="N389" xr:uid="{80125EB9-7E82-4376-8599-6746FA7B2CE8}">
       <formula1>=IF(M389&lt;&gt;"",INDIRECT(VLOOKUP(M389,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M390" xr:uid="{5512703D-2A26-41D9-98D6-F1CC093C0DCF}">
+    <dataValidation type="list" sqref="M390" xr:uid="{A3E0A318-B763-4BFC-BC92-4E06D0BBAA55}">
       <formula1>=IF(L390&lt;&gt;"",INDIRECT(VLOOKUP(L390,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N390" xr:uid="{3C8A7594-BB49-4EE1-8E99-A3A35FFDE51F}">
+    <dataValidation type="list" sqref="N390" xr:uid="{CD7E1EF4-DD9A-41E9-B682-49BBF5DB71D7}">
       <formula1>=IF(M390&lt;&gt;"",INDIRECT(VLOOKUP(M390,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M391" xr:uid="{FFA657D5-82F5-4B14-A2C2-43111BAA93B3}">
+    <dataValidation type="list" sqref="M391" xr:uid="{CED805F1-BF6C-4FBA-94E7-DB2839DC5FCC}">
       <formula1>=IF(L391&lt;&gt;"",INDIRECT(VLOOKUP(L391,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N391" xr:uid="{D40C4012-C391-44E9-B585-3F397043AC2E}">
+    <dataValidation type="list" sqref="N391" xr:uid="{F289EF85-B677-4072-BD4A-B8A9D924459F}">
       <formula1>=IF(M391&lt;&gt;"",INDIRECT(VLOOKUP(M391,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M392" xr:uid="{7F17292F-5FF0-4052-A623-56356179DBA1}">
+    <dataValidation type="list" sqref="M392" xr:uid="{3A177514-7DEC-4B94-A30F-4C0BC2D4BB0A}">
       <formula1>=IF(L392&lt;&gt;"",INDIRECT(VLOOKUP(L392,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N392" xr:uid="{3C4DB92F-3B97-40E4-BF0A-DB63823CDA96}">
+    <dataValidation type="list" sqref="N392" xr:uid="{BF40C012-9E7C-463C-8FD8-8BFF73E1DD10}">
       <formula1>=IF(M392&lt;&gt;"",INDIRECT(VLOOKUP(M392,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M393" xr:uid="{0BDE4506-66E5-4627-AC14-E333F7762E60}">
+    <dataValidation type="list" sqref="M393" xr:uid="{7C45A14B-EADF-486F-89D4-DF0FC1B1AF90}">
       <formula1>=IF(L393&lt;&gt;"",INDIRECT(VLOOKUP(L393,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N393" xr:uid="{809859B2-C39F-4D16-87CB-27E3A6C94B4A}">
+    <dataValidation type="list" sqref="N393" xr:uid="{4C165FE2-7171-4F1E-85D1-684C17433B9F}">
       <formula1>=IF(M393&lt;&gt;"",INDIRECT(VLOOKUP(M393,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M394" xr:uid="{04086CC9-D08D-45F6-A297-FFDCF94AC3C6}">
+    <dataValidation type="list" sqref="M394" xr:uid="{0C307BC4-A8D0-4CE9-80EE-449F970D4261}">
       <formula1>=IF(L394&lt;&gt;"",INDIRECT(VLOOKUP(L394,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N394" xr:uid="{90C9A03D-D471-4A7E-8578-B72320455D25}">
+    <dataValidation type="list" sqref="N394" xr:uid="{BE8378AA-2939-4757-B720-18DC57CC3C91}">
       <formula1>=IF(M394&lt;&gt;"",INDIRECT(VLOOKUP(M394,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M395" xr:uid="{0BD33945-0FFC-4EF0-AFE7-1CF4C6A49FF6}">
+    <dataValidation type="list" sqref="M395" xr:uid="{F755711E-C8C0-4033-BE21-2BEADF54DA6E}">
       <formula1>=IF(L395&lt;&gt;"",INDIRECT(VLOOKUP(L395,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N395" xr:uid="{9276A681-3F21-43DE-B2A7-7394C5D601AF}">
+    <dataValidation type="list" sqref="N395" xr:uid="{513111AA-0F60-4F94-94FA-77565655001C}">
       <formula1>=IF(M395&lt;&gt;"",INDIRECT(VLOOKUP(M395,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M396" xr:uid="{AF6CF385-FB29-4293-8822-A96C215AE2B6}">
+    <dataValidation type="list" sqref="M396" xr:uid="{2910404C-14A4-4328-827D-9C3333A21244}">
       <formula1>=IF(L396&lt;&gt;"",INDIRECT(VLOOKUP(L396,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N396" xr:uid="{07580F72-2A0A-4A14-8442-48297579CBB7}">
+    <dataValidation type="list" sqref="N396" xr:uid="{75753C4F-D9AE-48A8-A230-637F1FF2FB53}">
       <formula1>=IF(M396&lt;&gt;"",INDIRECT(VLOOKUP(M396,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M397" xr:uid="{A725A6E0-52EA-443D-B913-8A7052B5B193}">
+    <dataValidation type="list" sqref="M397" xr:uid="{993621C9-5602-46E1-87E9-CB985773D399}">
       <formula1>=IF(L397&lt;&gt;"",INDIRECT(VLOOKUP(L397,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N397" xr:uid="{47FF1636-4852-4BF9-8102-6CE73FF51E6C}">
+    <dataValidation type="list" sqref="N397" xr:uid="{96D5804E-D126-479B-893E-9FD9C6BC9153}">
       <formula1>=IF(M397&lt;&gt;"",INDIRECT(VLOOKUP(M397,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M398" xr:uid="{03D36D9D-D2A1-4DDD-8768-EDD90FC66179}">
+    <dataValidation type="list" sqref="M398" xr:uid="{D528838B-96B7-4034-8025-1B3E40D69C50}">
       <formula1>=IF(L398&lt;&gt;"",INDIRECT(VLOOKUP(L398,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N398" xr:uid="{0866681C-53FB-4C5B-B965-7D03DC6D68F1}">
+    <dataValidation type="list" sqref="N398" xr:uid="{457DDFF2-03C3-434F-AD19-362B86E86B3C}">
       <formula1>=IF(M398&lt;&gt;"",INDIRECT(VLOOKUP(M398,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M399" xr:uid="{02B6F223-0BDF-4530-9D61-E9BC46C3B58D}">
+    <dataValidation type="list" sqref="M399" xr:uid="{418B3E0F-ACEB-4DC2-A494-123F55095828}">
       <formula1>=IF(L399&lt;&gt;"",INDIRECT(VLOOKUP(L399,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N399" xr:uid="{BFEEF9BE-C1DB-436F-A2D1-AA37BF8A7304}">
+    <dataValidation type="list" sqref="N399" xr:uid="{CDF66B84-0DA8-4B9E-9B70-5985C5278299}">
       <formula1>=IF(M399&lt;&gt;"",INDIRECT(VLOOKUP(M399,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M400" xr:uid="{9A16E7BC-575A-44C1-AED9-CC3781D4AF73}">
+    <dataValidation type="list" sqref="M400" xr:uid="{C087D3E8-3C7D-47A5-9B6E-2D72C17D8808}">
       <formula1>=IF(L400&lt;&gt;"",INDIRECT(VLOOKUP(L400,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N400" xr:uid="{FEA1BEAD-C6E5-489E-8481-619649871306}">
+    <dataValidation type="list" sqref="N400" xr:uid="{5DC24E5C-9D27-4FC5-96C6-75B0D9156892}">
       <formula1>=IF(M400&lt;&gt;"",INDIRECT(VLOOKUP(M400,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M401" xr:uid="{EB337EE0-B5D7-4A87-B3D2-7C45377009F5}">
+    <dataValidation type="list" sqref="M401" xr:uid="{5C21B9C2-812E-47E0-A7B9-11B13E4D5C13}">
       <formula1>=IF(L401&lt;&gt;"",INDIRECT(VLOOKUP(L401,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N401" xr:uid="{E9DC307E-0C6E-4E98-8391-B20E0C53F400}">
+    <dataValidation type="list" sqref="N401" xr:uid="{2C7CA23D-AFF7-4A01-B2F4-2B61241E2B73}">
       <formula1>=IF(M401&lt;&gt;"",INDIRECT(VLOOKUP(M401,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M402" xr:uid="{5A2E54C8-3B86-4CFF-B405-2C7FA2FE8C12}">
+    <dataValidation type="list" sqref="M402" xr:uid="{F93CA85C-4CC6-47A7-9F07-E29426393293}">
       <formula1>=IF(L402&lt;&gt;"",INDIRECT(VLOOKUP(L402,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N402" xr:uid="{ACD42EFA-ABF2-4E5C-95C6-B28826541249}">
+    <dataValidation type="list" sqref="N402" xr:uid="{E5C11D1A-FAFB-49D1-8E62-A56A8E8CECEA}">
       <formula1>=IF(M402&lt;&gt;"",INDIRECT(VLOOKUP(M402,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M403" xr:uid="{30C00765-7F96-4BAB-B0A4-EA23A75B5398}">
+    <dataValidation type="list" sqref="M403" xr:uid="{F6A10F16-F2CE-4C31-8024-6DB2B53CE9A0}">
       <formula1>=IF(L403&lt;&gt;"",INDIRECT(VLOOKUP(L403,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N403" xr:uid="{DB13F331-14BC-477E-AB70-745823BBA71F}">
+    <dataValidation type="list" sqref="N403" xr:uid="{E9399AF4-746B-4DF9-908A-92D4853EEF28}">
       <formula1>=IF(M403&lt;&gt;"",INDIRECT(VLOOKUP(M403,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M404" xr:uid="{38C42CE6-0C9F-42B2-8BF8-B8A652C64311}">
+    <dataValidation type="list" sqref="M404" xr:uid="{FAAC172F-0F41-456F-9728-01687A83C0C1}">
       <formula1>=IF(L404&lt;&gt;"",INDIRECT(VLOOKUP(L404,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N404" xr:uid="{324EF5BE-5A9B-4F3D-9436-862FD193BE23}">
+    <dataValidation type="list" sqref="N404" xr:uid="{5FE9AF13-1A32-4E5D-A7C2-57F3C51E971F}">
       <formula1>=IF(M404&lt;&gt;"",INDIRECT(VLOOKUP(M404,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M405" xr:uid="{47F4A2CC-BDD4-4581-B5C0-5F62EA89962D}">
+    <dataValidation type="list" sqref="M405" xr:uid="{194370AC-418D-4295-97E0-56F3E04A8180}">
       <formula1>=IF(L405&lt;&gt;"",INDIRECT(VLOOKUP(L405,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N405" xr:uid="{CBEEDFEB-7D93-4A58-8032-DC5AB6CCFBB7}">
+    <dataValidation type="list" sqref="N405" xr:uid="{E41828AC-2A00-4B1D-AF27-BBF3C1F83E00}">
       <formula1>=IF(M405&lt;&gt;"",INDIRECT(VLOOKUP(M405,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M406" xr:uid="{47F83528-D777-4DF3-9AE2-03D2D1616501}">
+    <dataValidation type="list" sqref="M406" xr:uid="{BC8EA522-0317-44BC-BDF7-89643678E095}">
       <formula1>=IF(L406&lt;&gt;"",INDIRECT(VLOOKUP(L406,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N406" xr:uid="{10A77F37-80BC-4CCC-9B67-7966623C3946}">
+    <dataValidation type="list" sqref="N406" xr:uid="{18AE3CF8-2CAE-4E4E-B255-847F775297D5}">
       <formula1>=IF(M406&lt;&gt;"",INDIRECT(VLOOKUP(M406,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M407" xr:uid="{11C84746-3239-4305-A279-B76B8FC54940}">
+    <dataValidation type="list" sqref="M407" xr:uid="{2B03B89F-D3F9-493C-9F06-260CF3F2BDFD}">
       <formula1>=IF(L407&lt;&gt;"",INDIRECT(VLOOKUP(L407,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N407" xr:uid="{9327DEB8-ADBE-48E3-89A6-6707E58E317D}">
+    <dataValidation type="list" sqref="N407" xr:uid="{81F8B71D-AA7B-43DE-A73A-6C825E604FAD}">
       <formula1>=IF(M407&lt;&gt;"",INDIRECT(VLOOKUP(M407,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M408" xr:uid="{AE484DF7-976E-4125-B6F7-CA1125E0ED20}">
+    <dataValidation type="list" sqref="M408" xr:uid="{41B13CD3-C3A1-42D4-B5F9-F5315E280577}">
       <formula1>=IF(L408&lt;&gt;"",INDIRECT(VLOOKUP(L408,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N408" xr:uid="{90C73299-D482-4378-A1A0-31884747A14F}">
+    <dataValidation type="list" sqref="N408" xr:uid="{21CD3827-0C03-4969-A419-D182DCDB8048}">
       <formula1>=IF(M408&lt;&gt;"",INDIRECT(VLOOKUP(M408,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M409" xr:uid="{77C5362A-0DC2-44CC-B22D-69BBDDA86770}">
+    <dataValidation type="list" sqref="M409" xr:uid="{7AACADBD-6B05-43C2-846E-538CC10EFF4E}">
       <formula1>=IF(L409&lt;&gt;"",INDIRECT(VLOOKUP(L409,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N409" xr:uid="{79D71E24-BA8F-4852-ACE7-37EE53ED3431}">
+    <dataValidation type="list" sqref="N409" xr:uid="{0910CFEC-083C-468B-B3E4-FBBDF35D1A3C}">
       <formula1>=IF(M409&lt;&gt;"",INDIRECT(VLOOKUP(M409,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M410" xr:uid="{2FE43BBF-6579-441D-BCFA-B3D443AFF3A4}">
+    <dataValidation type="list" sqref="M410" xr:uid="{1C475934-111A-48B3-9768-BC5700871491}">
       <formula1>=IF(L410&lt;&gt;"",INDIRECT(VLOOKUP(L410,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N410" xr:uid="{EC6801F3-FDD3-483F-BE4B-5CFC50DD6C64}">
+    <dataValidation type="list" sqref="N410" xr:uid="{09C7AC58-3AC5-4744-A681-0D6015004024}">
       <formula1>=IF(M410&lt;&gt;"",INDIRECT(VLOOKUP(M410,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M411" xr:uid="{89AA8941-7CCE-4E92-B0DB-2AFFBD4A391D}">
+    <dataValidation type="list" sqref="M411" xr:uid="{A1F10D70-A0D5-41BC-93E4-E3084E5828AD}">
       <formula1>=IF(L411&lt;&gt;"",INDIRECT(VLOOKUP(L411,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N411" xr:uid="{344A798B-322D-42F4-8029-473D511DEE38}">
+    <dataValidation type="list" sqref="N411" xr:uid="{C05EFE71-5017-4406-8197-F319EF6F78D5}">
       <formula1>=IF(M411&lt;&gt;"",INDIRECT(VLOOKUP(M411,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M412" xr:uid="{BB6EE9D1-7924-4996-8D0B-85D2F8D72FAC}">
+    <dataValidation type="list" sqref="M412" xr:uid="{A78193AD-BD1A-4406-9CF0-6374ECAE75CD}">
       <formula1>=IF(L412&lt;&gt;"",INDIRECT(VLOOKUP(L412,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N412" xr:uid="{941B1C60-2D18-4D77-BC8D-8DEBC5044740}">
+    <dataValidation type="list" sqref="N412" xr:uid="{EF529615-6846-49AF-8717-27AA13F72D4C}">
       <formula1>=IF(M412&lt;&gt;"",INDIRECT(VLOOKUP(M412,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M413" xr:uid="{74285BAF-10B9-4DA3-90FF-A79F5494DC0F}">
+    <dataValidation type="list" sqref="M413" xr:uid="{45C2407E-09A8-4604-B325-E983F25B8C25}">
       <formula1>=IF(L413&lt;&gt;"",INDIRECT(VLOOKUP(L413,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N413" xr:uid="{EDCEED92-962A-4E32-A86D-1E389148DB73}">
+    <dataValidation type="list" sqref="N413" xr:uid="{97A93849-9473-4A88-9F51-583ECECE4509}">
       <formula1>=IF(M413&lt;&gt;"",INDIRECT(VLOOKUP(M413,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M414" xr:uid="{B7780880-A9A2-45FE-A8B0-D6E2BD64E0D3}">
+    <dataValidation type="list" sqref="M414" xr:uid="{2237AF37-914A-4658-9BAB-89BD4978CF71}">
       <formula1>=IF(L414&lt;&gt;"",INDIRECT(VLOOKUP(L414,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N414" xr:uid="{EDC55B72-6D82-4CBF-925B-D76ACEB3A017}">
+    <dataValidation type="list" sqref="N414" xr:uid="{25DC36FE-4AA8-45ED-AC3B-A5CC0391C4F0}">
       <formula1>=IF(M414&lt;&gt;"",INDIRECT(VLOOKUP(M414,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M415" xr:uid="{04810F6C-2E50-47DE-A2E6-FDF2DC73E141}">
+    <dataValidation type="list" sqref="M415" xr:uid="{A685BAE2-F7B1-483E-9D63-251C5ECA7AC7}">
       <formula1>=IF(L415&lt;&gt;"",INDIRECT(VLOOKUP(L415,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N415" xr:uid="{B30930B5-D6F4-4219-8444-D3AF7489B5A5}">
+    <dataValidation type="list" sqref="N415" xr:uid="{648D6405-5FCA-4CDE-9C0E-2CBC0E3CC3DF}">
       <formula1>=IF(M415&lt;&gt;"",INDIRECT(VLOOKUP(M415,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M416" xr:uid="{4FD298F0-B559-484C-94EA-459751B114A3}">
+    <dataValidation type="list" sqref="M416" xr:uid="{0E737C5B-986D-4EC9-8A69-9C8AF517A719}">
       <formula1>=IF(L416&lt;&gt;"",INDIRECT(VLOOKUP(L416,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N416" xr:uid="{345BC9F3-E31C-4829-8C4F-83CD84873876}">
+    <dataValidation type="list" sqref="N416" xr:uid="{4443B127-BE9B-4EF3-8255-FEBD42BEDD09}">
       <formula1>=IF(M416&lt;&gt;"",INDIRECT(VLOOKUP(M416,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M417" xr:uid="{C2FA63BD-E980-4EF6-B4D5-25FF9D52B5B5}">
+    <dataValidation type="list" sqref="M417" xr:uid="{654DA0EF-4A33-4476-BF68-B76529AE06A6}">
       <formula1>=IF(L417&lt;&gt;"",INDIRECT(VLOOKUP(L417,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N417" xr:uid="{4B0E8FBA-96DE-484C-8E32-B422F6F23343}">
+    <dataValidation type="list" sqref="N417" xr:uid="{6788E20C-C4B0-4B1F-B2DB-B54DDB5F4171}">
       <formula1>=IF(M417&lt;&gt;"",INDIRECT(VLOOKUP(M417,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M418" xr:uid="{4444C2BB-0655-4B13-8A68-D48C256187AE}">
+    <dataValidation type="list" sqref="M418" xr:uid="{88B8AE2D-FE60-4A71-8D03-E08B72D973D9}">
       <formula1>=IF(L418&lt;&gt;"",INDIRECT(VLOOKUP(L418,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N418" xr:uid="{2788121F-14B0-4095-871D-AA61D8DE271A}">
+    <dataValidation type="list" sqref="N418" xr:uid="{62EE4E67-F6B9-4446-9A1F-4F5C462AD9D2}">
       <formula1>=IF(M418&lt;&gt;"",INDIRECT(VLOOKUP(M418,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M419" xr:uid="{E61DBB7B-D2BB-4D87-89CB-9C23F66F7CF1}">
+    <dataValidation type="list" sqref="M419" xr:uid="{5E7DF15C-8B77-483A-ACF5-A72DFCC37740}">
       <formula1>=IF(L419&lt;&gt;"",INDIRECT(VLOOKUP(L419,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N419" xr:uid="{634547A7-22D4-4713-98F3-A7CB19B03155}">
+    <dataValidation type="list" sqref="N419" xr:uid="{15C98A3C-AC5C-4D7F-B33F-86AD9851084B}">
       <formula1>=IF(M419&lt;&gt;"",INDIRECT(VLOOKUP(M419,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M420" xr:uid="{214A9BEB-C5C4-429F-8704-320ACC9738B3}">
+    <dataValidation type="list" sqref="M420" xr:uid="{56E3675E-17F6-4B40-A1E7-D01CBF83D531}">
       <formula1>=IF(L420&lt;&gt;"",INDIRECT(VLOOKUP(L420,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N420" xr:uid="{58FF58A8-879B-49C7-B0D6-FD890B9B6D0A}">
+    <dataValidation type="list" sqref="N420" xr:uid="{5FD1E007-1904-44FD-9733-E62E9F35AFDA}">
       <formula1>=IF(M420&lt;&gt;"",INDIRECT(VLOOKUP(M420,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M421" xr:uid="{D5A18212-1C88-4339-A9A1-033371298117}">
+    <dataValidation type="list" sqref="M421" xr:uid="{35C2910C-DAFC-4C87-BE03-71A895D5BD73}">
       <formula1>=IF(L421&lt;&gt;"",INDIRECT(VLOOKUP(L421,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N421" xr:uid="{3DB02CB6-FA2D-40F9-A850-2A151485B572}">
+    <dataValidation type="list" sqref="N421" xr:uid="{E4B1A835-8358-4016-A07D-C4907FE16236}">
       <formula1>=IF(M421&lt;&gt;"",INDIRECT(VLOOKUP(M421,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M422" xr:uid="{E7B00C7F-5FA7-4A84-ABEC-B34012AD7C12}">
+    <dataValidation type="list" sqref="M422" xr:uid="{AC977B58-209B-424E-96EB-5FE495BCF754}">
       <formula1>=IF(L422&lt;&gt;"",INDIRECT(VLOOKUP(L422,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N422" xr:uid="{6623DB3A-84D1-417E-B778-A8B47612841A}">
+    <dataValidation type="list" sqref="N422" xr:uid="{77A428F4-E3A8-4DA8-A78B-9EB7B4698331}">
       <formula1>=IF(M422&lt;&gt;"",INDIRECT(VLOOKUP(M422,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M423" xr:uid="{AEC0AF32-6656-469A-A501-09CBA0AD0588}">
+    <dataValidation type="list" sqref="M423" xr:uid="{EA2B02EB-A456-4335-B171-9BA3A50CEE92}">
       <formula1>=IF(L423&lt;&gt;"",INDIRECT(VLOOKUP(L423,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N423" xr:uid="{2ACF9C67-E1E2-4E6D-BF9F-473D57FFAF9B}">
+    <dataValidation type="list" sqref="N423" xr:uid="{042143CD-4D63-4567-8947-9ACFD5700C6F}">
       <formula1>=IF(M423&lt;&gt;"",INDIRECT(VLOOKUP(M423,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M424" xr:uid="{4C1B0003-1402-47C9-8658-1EF10B927C25}">
+    <dataValidation type="list" sqref="M424" xr:uid="{196DCD24-5B94-4474-809D-A332F3804397}">
       <formula1>=IF(L424&lt;&gt;"",INDIRECT(VLOOKUP(L424,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N424" xr:uid="{DD345DC6-7EB5-4901-9D5A-6CFDB2768234}">
+    <dataValidation type="list" sqref="N424" xr:uid="{CBE0825A-64AA-487E-B7EC-BECCF0D69D54}">
       <formula1>=IF(M424&lt;&gt;"",INDIRECT(VLOOKUP(M424,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M425" xr:uid="{A0844BA8-C3F1-43EF-A38C-976B1EBB1E9F}">
+    <dataValidation type="list" sqref="M425" xr:uid="{6011B114-F126-442F-87BD-98350345EDA4}">
       <formula1>=IF(L425&lt;&gt;"",INDIRECT(VLOOKUP(L425,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N425" xr:uid="{92E05CD5-0F23-48AE-9CBD-43B658CDBE7F}">
+    <dataValidation type="list" sqref="N425" xr:uid="{E49EA0A9-EC5F-489D-A368-B7C01CD86FEF}">
       <formula1>=IF(M425&lt;&gt;"",INDIRECT(VLOOKUP(M425,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M426" xr:uid="{35FD5C2D-AC3F-4460-A3CE-5A39A3BC2C9F}">
+    <dataValidation type="list" sqref="M426" xr:uid="{A106B33F-CAA6-43C0-A118-BFBA44F465A6}">
       <formula1>=IF(L426&lt;&gt;"",INDIRECT(VLOOKUP(L426,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N426" xr:uid="{DA309792-B61D-4FF3-96DA-F5C7CE37EA2F}">
+    <dataValidation type="list" sqref="N426" xr:uid="{E320D744-42DC-4F35-A25D-360A70B23814}">
       <formula1>=IF(M426&lt;&gt;"",INDIRECT(VLOOKUP(M426,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M427" xr:uid="{8F601BE4-427D-4FE4-BB81-F1A1E6E5F14F}">
+    <dataValidation type="list" sqref="M427" xr:uid="{A887668C-CFB1-4E3C-9F48-8DE84280EA8E}">
       <formula1>=IF(L427&lt;&gt;"",INDIRECT(VLOOKUP(L427,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N427" xr:uid="{C708BE07-B0D7-49AE-91C1-608C9B115F61}">
+    <dataValidation type="list" sqref="N427" xr:uid="{AE206ED0-DE8D-414B-8E48-F734153A4E41}">
       <formula1>=IF(M427&lt;&gt;"",INDIRECT(VLOOKUP(M427,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M428" xr:uid="{60AE9770-2A6C-4C56-BB00-773FBE08B538}">
+    <dataValidation type="list" sqref="M428" xr:uid="{877B6352-406C-44C3-AE9D-84DF6EF326DE}">
       <formula1>=IF(L428&lt;&gt;"",INDIRECT(VLOOKUP(L428,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N428" xr:uid="{2BBF8C9B-E832-495E-989F-F37DBA0DF2FF}">
+    <dataValidation type="list" sqref="N428" xr:uid="{7CC78BE8-0732-4E70-BA80-94E9E583FD56}">
       <formula1>=IF(M428&lt;&gt;"",INDIRECT(VLOOKUP(M428,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M429" xr:uid="{2C353B19-0AEE-4CFC-8986-B9B52CB2629C}">
+    <dataValidation type="list" sqref="M429" xr:uid="{B3B1593A-27C2-4E89-9AC2-E25977A0848E}">
       <formula1>=IF(L429&lt;&gt;"",INDIRECT(VLOOKUP(L429,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N429" xr:uid="{CEF9FB38-F5E0-4250-8571-208E52BFBBC5}">
+    <dataValidation type="list" sqref="N429" xr:uid="{010A274F-8918-4D7A-9C69-268C21686A4C}">
       <formula1>=IF(M429&lt;&gt;"",INDIRECT(VLOOKUP(M429,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M430" xr:uid="{54E5D172-20CE-41C7-97D3-D3E9E71456A3}">
+    <dataValidation type="list" sqref="M430" xr:uid="{9C962EC4-B6A9-4DA6-83E2-5CAAD083E1BE}">
       <formula1>=IF(L430&lt;&gt;"",INDIRECT(VLOOKUP(L430,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N430" xr:uid="{E24F0514-EFB1-4A76-BA7D-4551B845A158}">
+    <dataValidation type="list" sqref="N430" xr:uid="{7B065F09-40B6-4069-819C-459F3368CC37}">
       <formula1>=IF(M430&lt;&gt;"",INDIRECT(VLOOKUP(M430,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M431" xr:uid="{4C068565-D2AB-44C2-A6A9-0249035BDDBC}">
+    <dataValidation type="list" sqref="M431" xr:uid="{F88853C4-AF94-46F8-B2D4-6245714919EF}">
       <formula1>=IF(L431&lt;&gt;"",INDIRECT(VLOOKUP(L431,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N431" xr:uid="{529FB3EB-4648-49A3-A177-D0D6A1209549}">
+    <dataValidation type="list" sqref="N431" xr:uid="{28F5F7E5-3158-4269-8E04-63996F57FD0C}">
       <formula1>=IF(M431&lt;&gt;"",INDIRECT(VLOOKUP(M431,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M432" xr:uid="{5B0DA41A-055B-4793-9C2F-C2C66340BB30}">
+    <dataValidation type="list" sqref="M432" xr:uid="{B168468E-6222-4C8E-BBEA-133E0B4C692C}">
       <formula1>=IF(L432&lt;&gt;"",INDIRECT(VLOOKUP(L432,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N432" xr:uid="{29250303-CA0D-40C3-84F4-D8EC6B3703D9}">
+    <dataValidation type="list" sqref="N432" xr:uid="{7BB31456-E19A-44E1-8A52-D1E01EDC8DD3}">
       <formula1>=IF(M432&lt;&gt;"",INDIRECT(VLOOKUP(M432,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M433" xr:uid="{EEEAA2C4-1DAA-4123-B3B9-40FD3206CF59}">
+    <dataValidation type="list" sqref="M433" xr:uid="{5621A142-D062-4F2B-9C90-6087DA7B8411}">
       <formula1>=IF(L433&lt;&gt;"",INDIRECT(VLOOKUP(L433,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N433" xr:uid="{A562F638-4C26-4F4F-8739-E6AE53B7E550}">
+    <dataValidation type="list" sqref="N433" xr:uid="{D8044851-8B1D-4DB5-9981-51DD0AD06EC6}">
       <formula1>=IF(M433&lt;&gt;"",INDIRECT(VLOOKUP(M433,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M434" xr:uid="{36E84E73-F3CF-4064-9488-A1E6528D0FD7}">
+    <dataValidation type="list" sqref="M434" xr:uid="{430AE5AF-E8E7-49E9-AFE6-804A773F078E}">
       <formula1>=IF(L434&lt;&gt;"",INDIRECT(VLOOKUP(L434,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N434" xr:uid="{44290B92-8647-43ED-AAAF-D125474F0010}">
+    <dataValidation type="list" sqref="N434" xr:uid="{97247260-06BC-41FD-9E6E-A40EADA81ED8}">
       <formula1>=IF(M434&lt;&gt;"",INDIRECT(VLOOKUP(M434,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M435" xr:uid="{68EE8E2B-02D9-4A68-9604-EAFE13FD5216}">
+    <dataValidation type="list" sqref="M435" xr:uid="{26A17BB5-7FF3-4522-8C57-8084FADBE837}">
       <formula1>=IF(L435&lt;&gt;"",INDIRECT(VLOOKUP(L435,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N435" xr:uid="{16CC78B8-DBFB-4208-AF4C-18430BF0503A}">
+    <dataValidation type="list" sqref="N435" xr:uid="{9FE3C5A9-B445-4760-93A2-7C941A507A19}">
       <formula1>=IF(M435&lt;&gt;"",INDIRECT(VLOOKUP(M435,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M436" xr:uid="{DDB7C889-C83A-41DA-B358-511EA333B810}">
+    <dataValidation type="list" sqref="M436" xr:uid="{36703FF4-89B3-4212-80D9-1BC98DC4381D}">
       <formula1>=IF(L436&lt;&gt;"",INDIRECT(VLOOKUP(L436,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N436" xr:uid="{CBB4C7DD-2804-4CDA-A31F-FA1CEB3F5E4F}">
+    <dataValidation type="list" sqref="N436" xr:uid="{46E5220F-45B0-4932-B229-BC5FE94065E4}">
       <formula1>=IF(M436&lt;&gt;"",INDIRECT(VLOOKUP(M436,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M437" xr:uid="{6A9B2703-4F7E-46E2-B67F-D0A22719083B}">
+    <dataValidation type="list" sqref="M437" xr:uid="{83FC505B-CFEA-4719-A545-1666F2FC3C2F}">
       <formula1>=IF(L437&lt;&gt;"",INDIRECT(VLOOKUP(L437,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N437" xr:uid="{26DFB509-8467-423E-B8BB-F008034737D3}">
+    <dataValidation type="list" sqref="N437" xr:uid="{1BF4463D-CB35-433D-9FE5-A5C4888D1EC3}">
       <formula1>=IF(M437&lt;&gt;"",INDIRECT(VLOOKUP(M437,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M438" xr:uid="{5AA87B05-CC62-451D-9053-374DCF02535B}">
+    <dataValidation type="list" sqref="M438" xr:uid="{29AFC1DB-781F-419B-9198-439FA33B2885}">
       <formula1>=IF(L438&lt;&gt;"",INDIRECT(VLOOKUP(L438,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N438" xr:uid="{A3B2D715-46FE-42E8-9633-B113D436A7A6}">
+    <dataValidation type="list" sqref="N438" xr:uid="{FEC95058-A59B-4BA0-BC63-5E231BB9917D}">
       <formula1>=IF(M438&lt;&gt;"",INDIRECT(VLOOKUP(M438,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M439" xr:uid="{22C74E97-9B3A-43F1-BC6D-7549E3922CD8}">
+    <dataValidation type="list" sqref="M439" xr:uid="{D33FC39F-4F7B-40B0-A958-6F0CF6A16A5D}">
       <formula1>=IF(L439&lt;&gt;"",INDIRECT(VLOOKUP(L439,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N439" xr:uid="{E08C7851-B182-4944-9A80-94A7171D114D}">
+    <dataValidation type="list" sqref="N439" xr:uid="{8DBBE460-44A9-47B5-B4A9-0CE3B5039434}">
       <formula1>=IF(M439&lt;&gt;"",INDIRECT(VLOOKUP(M439,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M440" xr:uid="{EB1E213E-34DF-4541-8928-9E8B19684FC0}">
+    <dataValidation type="list" sqref="M440" xr:uid="{9510D04C-46CB-4700-85B3-D7F3B97DC5D4}">
       <formula1>=IF(L440&lt;&gt;"",INDIRECT(VLOOKUP(L440,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N440" xr:uid="{215FE6E7-2268-4D99-A094-8E412D030F66}">
+    <dataValidation type="list" sqref="N440" xr:uid="{6068088C-2410-4883-82D0-30AAFFFC0593}">
       <formula1>=IF(M440&lt;&gt;"",INDIRECT(VLOOKUP(M440,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M441" xr:uid="{6DE8C46A-A28B-40BF-BDEC-8E776DC8B17D}">
+    <dataValidation type="list" sqref="M441" xr:uid="{041837B4-1956-4ACB-ADB4-21E620B002FE}">
       <formula1>=IF(L441&lt;&gt;"",INDIRECT(VLOOKUP(L441,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N441" xr:uid="{99C5D275-EA65-4175-BE6C-AC73BE44E48C}">
+    <dataValidation type="list" sqref="N441" xr:uid="{1254252D-9BAC-4556-9DF6-3BFC6CAF3823}">
       <formula1>=IF(M441&lt;&gt;"",INDIRECT(VLOOKUP(M441,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M442" xr:uid="{EA5CDFDA-60CE-4E0B-88B4-949C773FDA1C}">
+    <dataValidation type="list" sqref="M442" xr:uid="{2FAE5FB2-82AD-4DCA-ABEE-241C37D77CCC}">
       <formula1>=IF(L442&lt;&gt;"",INDIRECT(VLOOKUP(L442,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N442" xr:uid="{7DA254F4-CD99-4B39-A448-576D8FC9B112}">
+    <dataValidation type="list" sqref="N442" xr:uid="{354029D8-CAAA-48DB-9D31-B33C7E011AFD}">
       <formula1>=IF(M442&lt;&gt;"",INDIRECT(VLOOKUP(M442,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M443" xr:uid="{CFBED6AE-CEEB-46B2-90E3-8353B16D375C}">
+    <dataValidation type="list" sqref="M443" xr:uid="{27CAB746-331F-42FF-87A7-2AC204D2C7A0}">
       <formula1>=IF(L443&lt;&gt;"",INDIRECT(VLOOKUP(L443,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N443" xr:uid="{6B4B4B3D-D20A-42A2-BE31-7191D68FCF1C}">
+    <dataValidation type="list" sqref="N443" xr:uid="{AD086E18-F8D7-4D0A-A901-F22A2405B05A}">
       <formula1>=IF(M443&lt;&gt;"",INDIRECT(VLOOKUP(M443,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M444" xr:uid="{4D51D707-93F4-43F5-9CE5-174BE6B39FE1}">
+    <dataValidation type="list" sqref="M444" xr:uid="{6BE88381-1144-4FAC-B16D-4A61E6240624}">
       <formula1>=IF(L444&lt;&gt;"",INDIRECT(VLOOKUP(L444,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N444" xr:uid="{61EFD5FC-45B2-4095-B460-206E29FD1FC7}">
+    <dataValidation type="list" sqref="N444" xr:uid="{D48423BD-AAFD-4932-81B1-C34400A98140}">
       <formula1>=IF(M444&lt;&gt;"",INDIRECT(VLOOKUP(M444,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M445" xr:uid="{FA0647A1-8C56-4077-9BE8-A75245EE8DCB}">
+    <dataValidation type="list" sqref="M445" xr:uid="{20754940-8E56-415E-8106-AB3FE1448515}">
       <formula1>=IF(L445&lt;&gt;"",INDIRECT(VLOOKUP(L445,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N445" xr:uid="{AA880E94-4C4B-440F-BAFC-1F62CBF321EC}">
+    <dataValidation type="list" sqref="N445" xr:uid="{AEB74533-8147-4C35-9DDD-A8534D3A6AE0}">
       <formula1>=IF(M445&lt;&gt;"",INDIRECT(VLOOKUP(M445,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M446" xr:uid="{1B7F474A-7BDF-43B8-9EA4-EFC4A2719F86}">
+    <dataValidation type="list" sqref="M446" xr:uid="{0281EE99-CF04-47A7-8E08-A3C9B88CD439}">
       <formula1>=IF(L446&lt;&gt;"",INDIRECT(VLOOKUP(L446,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N446" xr:uid="{832F28F9-24A5-46EA-8116-FBE61579CC83}">
+    <dataValidation type="list" sqref="N446" xr:uid="{0C85972E-1FD5-4266-AD28-E553D072D5A3}">
       <formula1>=IF(M446&lt;&gt;"",INDIRECT(VLOOKUP(M446,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M447" xr:uid="{547C6A7A-288C-4BE1-9C4B-E001E185F208}">
+    <dataValidation type="list" sqref="M447" xr:uid="{ACF1F799-A6DB-4996-8E71-A946C8FD5085}">
       <formula1>=IF(L447&lt;&gt;"",INDIRECT(VLOOKUP(L447,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N447" xr:uid="{364C5674-34C9-4540-94EF-FAC7E26D9C6E}">
+    <dataValidation type="list" sqref="N447" xr:uid="{0BE13AF0-1CDD-4C92-B03C-B9D5E0563132}">
       <formula1>=IF(M447&lt;&gt;"",INDIRECT(VLOOKUP(M447,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M448" xr:uid="{7028D3D8-8152-4C23-953B-5EC309CDF2AB}">
+    <dataValidation type="list" sqref="M448" xr:uid="{BCBCD50C-57CD-4D0A-9786-04CF791BFA62}">
       <formula1>=IF(L448&lt;&gt;"",INDIRECT(VLOOKUP(L448,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N448" xr:uid="{955E9921-A194-4694-BAFE-D332AC9A0752}">
+    <dataValidation type="list" sqref="N448" xr:uid="{10409F95-7B13-4185-BDBD-B2FB39CA292A}">
       <formula1>=IF(M448&lt;&gt;"",INDIRECT(VLOOKUP(M448,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M449" xr:uid="{F61C5094-3FCC-4E36-9424-1A0E6C7248D1}">
+    <dataValidation type="list" sqref="M449" xr:uid="{51297392-B1FD-4DC2-92C9-E3456F6C1A84}">
       <formula1>=IF(L449&lt;&gt;"",INDIRECT(VLOOKUP(L449,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N449" xr:uid="{D2DE721A-F464-45A5-9EEF-F1851CCD393F}">
+    <dataValidation type="list" sqref="N449" xr:uid="{CD17E0F7-BFF5-4367-BB24-9F409DBD94A2}">
       <formula1>=IF(M449&lt;&gt;"",INDIRECT(VLOOKUP(M449,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M450" xr:uid="{743A16D3-5251-47E2-A22F-9885F3BFAFB1}">
+    <dataValidation type="list" sqref="M450" xr:uid="{4E39DFCC-EE4F-4EBE-8AE2-5B71C59133BB}">
       <formula1>=IF(L450&lt;&gt;"",INDIRECT(VLOOKUP(L450,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N450" xr:uid="{5471FA98-904A-4ECA-96C9-DBA947AAA290}">
+    <dataValidation type="list" sqref="N450" xr:uid="{A395EFCB-D77D-4FF8-A211-DFE7330879E1}">
       <formula1>=IF(M450&lt;&gt;"",INDIRECT(VLOOKUP(M450,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M451" xr:uid="{9D712BE0-59E0-4385-B767-9A7EBA596BCB}">
+    <dataValidation type="list" sqref="M451" xr:uid="{887DD1AE-180D-4114-8996-91513FF9DDEC}">
       <formula1>=IF(L451&lt;&gt;"",INDIRECT(VLOOKUP(L451,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N451" xr:uid="{8220C14C-3CFD-4F21-B428-7B037053C963}">
+    <dataValidation type="list" sqref="N451" xr:uid="{C48FE478-2D54-4FA7-B174-82CE618E6116}">
       <formula1>=IF(M451&lt;&gt;"",INDIRECT(VLOOKUP(M451,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M452" xr:uid="{5C4DDF61-E4F7-454A-92E8-2453ED927EE0}">
+    <dataValidation type="list" sqref="M452" xr:uid="{73E27750-A907-40FE-BB26-500764D8AA68}">
       <formula1>=IF(L452&lt;&gt;"",INDIRECT(VLOOKUP(L452,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N452" xr:uid="{3C176C2B-2656-4AAC-A3EE-053C6F381761}">
+    <dataValidation type="list" sqref="N452" xr:uid="{8307C4E1-6A33-4AAF-BCA3-24747AED471E}">
       <formula1>=IF(M452&lt;&gt;"",INDIRECT(VLOOKUP(M452,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M453" xr:uid="{C49CC693-BB14-4718-AA57-A5FB84E40E05}">
+    <dataValidation type="list" sqref="M453" xr:uid="{5FFDF808-3438-4307-8C6E-1F2C181EE72A}">
       <formula1>=IF(L453&lt;&gt;"",INDIRECT(VLOOKUP(L453,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N453" xr:uid="{E5B123B5-3123-4D14-8D56-6872623EA0D9}">
+    <dataValidation type="list" sqref="N453" xr:uid="{3E84FD33-F4C6-4949-BC2A-62768A4E6B2D}">
       <formula1>=IF(M453&lt;&gt;"",INDIRECT(VLOOKUP(M453,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M454" xr:uid="{5FA4F6EE-DEB9-4672-9349-6F50C98120E5}">
+    <dataValidation type="list" sqref="M454" xr:uid="{65164374-A27A-41DE-B100-770A8D243A40}">
       <formula1>=IF(L454&lt;&gt;"",INDIRECT(VLOOKUP(L454,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N454" xr:uid="{9734FBAA-22C7-4738-945A-C6040D297E8B}">
+    <dataValidation type="list" sqref="N454" xr:uid="{1960A7FD-A930-44BC-A878-BBD5C56A6C99}">
       <formula1>=IF(M454&lt;&gt;"",INDIRECT(VLOOKUP(M454,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M455" xr:uid="{A55C2619-63CD-41F9-8040-38455F4E76ED}">
+    <dataValidation type="list" sqref="M455" xr:uid="{B19F01DD-65D3-4AB4-9C3D-D45F937F3E3E}">
       <formula1>=IF(L455&lt;&gt;"",INDIRECT(VLOOKUP(L455,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N455" xr:uid="{A049CA87-0F84-4338-A23C-F3E53ABDAE72}">
+    <dataValidation type="list" sqref="N455" xr:uid="{E6D5A0FF-C4A8-4663-BEB3-3E104DD76214}">
       <formula1>=IF(M455&lt;&gt;"",INDIRECT(VLOOKUP(M455,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M456" xr:uid="{A7DB136C-D81A-4AED-92FD-2369C80CD3E8}">
+    <dataValidation type="list" sqref="M456" xr:uid="{E3938ECE-8EE4-48A0-8F24-1BDB571D2A00}">
       <formula1>=IF(L456&lt;&gt;"",INDIRECT(VLOOKUP(L456,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N456" xr:uid="{B15F63DD-515C-4A43-A6C6-9FCD7515D7C2}">
+    <dataValidation type="list" sqref="N456" xr:uid="{B7DE515D-DF10-40A8-911C-B0D4D87EB826}">
       <formula1>=IF(M456&lt;&gt;"",INDIRECT(VLOOKUP(M456,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M457" xr:uid="{781782DC-7B1C-4558-97DB-93FCE217C078}">
+    <dataValidation type="list" sqref="M457" xr:uid="{A63F0EE3-D135-40D1-A524-DAE09848384A}">
       <formula1>=IF(L457&lt;&gt;"",INDIRECT(VLOOKUP(L457,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N457" xr:uid="{14A536FB-EA90-4618-902B-C2FA630C5F8D}">
+    <dataValidation type="list" sqref="N457" xr:uid="{5B38E961-531E-453F-85AB-018549C9F89D}">
       <formula1>=IF(M457&lt;&gt;"",INDIRECT(VLOOKUP(M457,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M458" xr:uid="{38F26B02-3506-4CD1-ADFD-14B266A619F4}">
+    <dataValidation type="list" sqref="M458" xr:uid="{648DEC78-FB7B-4BDF-811B-FE9F132DED29}">
       <formula1>=IF(L458&lt;&gt;"",INDIRECT(VLOOKUP(L458,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N458" xr:uid="{A9093268-7AA9-4546-95FC-AE90DCE8072D}">
+    <dataValidation type="list" sqref="N458" xr:uid="{05F7180E-E38F-488D-86C7-23E6FEDD9366}">
       <formula1>=IF(M458&lt;&gt;"",INDIRECT(VLOOKUP(M458,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M459" xr:uid="{4B651802-2893-43E4-B69F-9FFAF0624B40}">
+    <dataValidation type="list" sqref="M459" xr:uid="{3B875361-7C2E-4270-87D2-4BC1A5AD355A}">
       <formula1>=IF(L459&lt;&gt;"",INDIRECT(VLOOKUP(L459,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N459" xr:uid="{5EE5E1B3-6BDF-4B90-AF8B-632324460DFF}">
+    <dataValidation type="list" sqref="N459" xr:uid="{664722EF-AABD-423A-8412-A6385A4FC1C1}">
       <formula1>=IF(M459&lt;&gt;"",INDIRECT(VLOOKUP(M459,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M460" xr:uid="{A21C0D60-1DCD-4EA8-B3F5-6A3643E68099}">
+    <dataValidation type="list" sqref="M460" xr:uid="{289CDD6C-9A9A-40FC-95E3-4A813E67834C}">
       <formula1>=IF(L460&lt;&gt;"",INDIRECT(VLOOKUP(L460,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N460" xr:uid="{EA44B163-5CBF-4695-8092-F3608A0F6475}">
+    <dataValidation type="list" sqref="N460" xr:uid="{824C779C-EA3F-4C99-AF77-F48EE087A5EC}">
       <formula1>=IF(M460&lt;&gt;"",INDIRECT(VLOOKUP(M460,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M461" xr:uid="{35340B80-127F-4023-A898-3A9FD648051A}">
+    <dataValidation type="list" sqref="M461" xr:uid="{5A32D4E6-7B18-4C06-A4CF-CE46B177D4CF}">
       <formula1>=IF(L461&lt;&gt;"",INDIRECT(VLOOKUP(L461,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N461" xr:uid="{F1C09409-8D95-41A3-A8AB-60773C45C0F3}">
+    <dataValidation type="list" sqref="N461" xr:uid="{8D78AD93-7D23-4FE8-BCB7-BA99DC44EF4D}">
       <formula1>=IF(M461&lt;&gt;"",INDIRECT(VLOOKUP(M461,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M462" xr:uid="{26F3C855-6612-4B67-B85D-3BBBC52395EA}">
+    <dataValidation type="list" sqref="M462" xr:uid="{A188D203-493F-4FF2-9566-8BEC20666C99}">
       <formula1>=IF(L462&lt;&gt;"",INDIRECT(VLOOKUP(L462,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N462" xr:uid="{874BE26B-2ADF-4086-97C0-B46CF755B9D7}">
+    <dataValidation type="list" sqref="N462" xr:uid="{550BD342-A8F2-4ABD-8B8D-258875147E55}">
       <formula1>=IF(M462&lt;&gt;"",INDIRECT(VLOOKUP(M462,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M463" xr:uid="{207190C8-850B-45F8-B211-877110351DA5}">
+    <dataValidation type="list" sqref="M463" xr:uid="{8EE896AC-7C38-4D58-8B74-821A6E5CC3A0}">
       <formula1>=IF(L463&lt;&gt;"",INDIRECT(VLOOKUP(L463,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N463" xr:uid="{8ACA5D64-99D4-4567-AC0A-964C1D64A4E9}">
+    <dataValidation type="list" sqref="N463" xr:uid="{2A230083-C36C-4CE6-81A8-58928DC35273}">
       <formula1>=IF(M463&lt;&gt;"",INDIRECT(VLOOKUP(M463,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M464" xr:uid="{15B2E896-1D92-4CE1-965B-DDED5CF28077}">
+    <dataValidation type="list" sqref="M464" xr:uid="{3A1D407C-A35A-4580-858B-3699B0F96619}">
       <formula1>=IF(L464&lt;&gt;"",INDIRECT(VLOOKUP(L464,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N464" xr:uid="{E660260D-B5EC-4B52-A252-F2D3CBBAE45C}">
+    <dataValidation type="list" sqref="N464" xr:uid="{183271BE-C055-4673-B84C-A23495B50E78}">
       <formula1>=IF(M464&lt;&gt;"",INDIRECT(VLOOKUP(M464,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M465" xr:uid="{9E49442D-AFBF-4422-8C85-B4D7C89D6836}">
+    <dataValidation type="list" sqref="M465" xr:uid="{8B8AA890-B4D1-428C-B2EC-19ACFBC370A8}">
       <formula1>=IF(L465&lt;&gt;"",INDIRECT(VLOOKUP(L465,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N465" xr:uid="{2AF6D974-F61E-42C5-B569-916FB0B326DD}">
+    <dataValidation type="list" sqref="N465" xr:uid="{4168D765-B3D8-4909-ADB3-2EF28884F3CC}">
       <formula1>=IF(M465&lt;&gt;"",INDIRECT(VLOOKUP(M465,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M466" xr:uid="{ED1B0AC3-26F2-4E4E-B4D7-8297D009BB20}">
+    <dataValidation type="list" sqref="M466" xr:uid="{696DAC5F-D07C-4C11-AA94-302EFE4546BC}">
       <formula1>=IF(L466&lt;&gt;"",INDIRECT(VLOOKUP(L466,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N466" xr:uid="{7DA0E2FF-A024-43A9-B8BA-EA6C26036A26}">
+    <dataValidation type="list" sqref="N466" xr:uid="{F589C36B-C427-4E86-A692-F5D6C99E38AE}">
       <formula1>=IF(M466&lt;&gt;"",INDIRECT(VLOOKUP(M466,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M467" xr:uid="{880AF979-8CBA-4198-AE03-5811558AAFD9}">
+    <dataValidation type="list" sqref="M467" xr:uid="{82798D91-B3E5-43B5-B905-86DC50D4F2B3}">
       <formula1>=IF(L467&lt;&gt;"",INDIRECT(VLOOKUP(L467,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N467" xr:uid="{DE1160B5-7487-45F1-A3A1-521D8CD39B34}">
+    <dataValidation type="list" sqref="N467" xr:uid="{DD92F440-DBF6-4477-A175-9224FA58D982}">
       <formula1>=IF(M467&lt;&gt;"",INDIRECT(VLOOKUP(M467,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M468" xr:uid="{EC78C4A9-8A59-4986-8F7C-BFD7183AA637}">
+    <dataValidation type="list" sqref="M468" xr:uid="{3FEC02F8-7829-434E-AD20-11FD59C1906A}">
       <formula1>=IF(L468&lt;&gt;"",INDIRECT(VLOOKUP(L468,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N468" xr:uid="{20080894-FC0B-401E-86B1-BE71915BBFC9}">
+    <dataValidation type="list" sqref="N468" xr:uid="{1F22859A-995D-4AC6-89AA-EB746B410450}">
       <formula1>=IF(M468&lt;&gt;"",INDIRECT(VLOOKUP(M468,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M469" xr:uid="{5C2450BF-CE01-408E-A0B5-9464F3A6DD7F}">
+    <dataValidation type="list" sqref="M469" xr:uid="{B14A80E9-A3BE-4299-AE7B-F238A2AA6F85}">
       <formula1>=IF(L469&lt;&gt;"",INDIRECT(VLOOKUP(L469,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N469" xr:uid="{EEBEE72F-77FE-44D7-ADCF-DE18FAFDF98D}">
+    <dataValidation type="list" sqref="N469" xr:uid="{71461867-95D9-495B-A7A4-B9B990E23D2C}">
       <formula1>=IF(M469&lt;&gt;"",INDIRECT(VLOOKUP(M469,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M470" xr:uid="{A09460CA-90FC-4226-AFF1-4D006D4F754F}">
+    <dataValidation type="list" sqref="M470" xr:uid="{15C56E85-B594-45E1-A291-5E9FC4B4807A}">
       <formula1>=IF(L470&lt;&gt;"",INDIRECT(VLOOKUP(L470,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N470" xr:uid="{700B6710-F914-4D46-8897-DB8BA9630BAC}">
+    <dataValidation type="list" sqref="N470" xr:uid="{DE4434A2-2C18-4137-BDC9-819ED3DF82B8}">
       <formula1>=IF(M470&lt;&gt;"",INDIRECT(VLOOKUP(M470,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M471" xr:uid="{6C7EDF59-560E-4943-B41C-3DC931C2F57C}">
+    <dataValidation type="list" sqref="M471" xr:uid="{0E2D0BFD-1FFD-41B0-A2FD-3B0549330834}">
       <formula1>=IF(L471&lt;&gt;"",INDIRECT(VLOOKUP(L471,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N471" xr:uid="{5D76C8FF-59E3-469D-BADD-C99DB984C9E9}">
+    <dataValidation type="list" sqref="N471" xr:uid="{096938B8-408F-464C-B8FC-601042003212}">
       <formula1>=IF(M471&lt;&gt;"",INDIRECT(VLOOKUP(M471,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M472" xr:uid="{14B0F45F-8756-418B-8A0B-A87D06CB4C3A}">
+    <dataValidation type="list" sqref="M472" xr:uid="{CE716D8B-0AA8-4F7A-9FB5-D0A7326EFEE2}">
       <formula1>=IF(L472&lt;&gt;"",INDIRECT(VLOOKUP(L472,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N472" xr:uid="{5D956100-CDCB-44DC-B7A9-694CDDFF252D}">
+    <dataValidation type="list" sqref="N472" xr:uid="{5F0F0E5B-CC3C-47DF-A385-E35008B7904E}">
       <formula1>=IF(M472&lt;&gt;"",INDIRECT(VLOOKUP(M472,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M473" xr:uid="{A8425AAB-C347-43C4-B1EF-04971560D988}">
+    <dataValidation type="list" sqref="M473" xr:uid="{D0F90AB9-EFBA-4B3A-9B78-F3F9811AA87D}">
       <formula1>=IF(L473&lt;&gt;"",INDIRECT(VLOOKUP(L473,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N473" xr:uid="{C17560BC-02A9-4F5F-A0CF-7E3D823EE16A}">
+    <dataValidation type="list" sqref="N473" xr:uid="{3EA4E40A-D1EB-4A1E-A050-29AF70C317BD}">
       <formula1>=IF(M473&lt;&gt;"",INDIRECT(VLOOKUP(M473,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M474" xr:uid="{B64A180B-E109-43C9-8F75-EE6DCC796807}">
+    <dataValidation type="list" sqref="M474" xr:uid="{4B2E467F-F472-4112-8677-29071DE5333D}">
       <formula1>=IF(L474&lt;&gt;"",INDIRECT(VLOOKUP(L474,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N474" xr:uid="{E7A627F5-4EA0-467C-88D0-383632AD15CF}">
+    <dataValidation type="list" sqref="N474" xr:uid="{DE8CD622-6EF3-4A56-8553-EBDE87F3066F}">
       <formula1>=IF(M474&lt;&gt;"",INDIRECT(VLOOKUP(M474,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M475" xr:uid="{49602236-4FB4-45CE-AAD3-7B0748B771E3}">
+    <dataValidation type="list" sqref="M475" xr:uid="{FBBFAA67-95DE-40FE-9ECC-9BB4E9BF91A3}">
       <formula1>=IF(L475&lt;&gt;"",INDIRECT(VLOOKUP(L475,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N475" xr:uid="{3AF59123-D6D1-4101-ABDA-9748D7F09890}">
+    <dataValidation type="list" sqref="N475" xr:uid="{C93AFBBA-5674-46E8-B4B7-14F83E7D30C1}">
       <formula1>=IF(M475&lt;&gt;"",INDIRECT(VLOOKUP(M475,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M476" xr:uid="{4E2F4878-04DC-4B2C-A1A8-4A1DBC6D3C9E}">
+    <dataValidation type="list" sqref="M476" xr:uid="{ADDFC588-B48B-4B46-9192-49970A97FC30}">
       <formula1>=IF(L476&lt;&gt;"",INDIRECT(VLOOKUP(L476,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N476" xr:uid="{5A622907-B314-44B0-B0F3-D21217146F47}">
+    <dataValidation type="list" sqref="N476" xr:uid="{2ECC61AE-E046-4EA4-ABBB-853000BD25C2}">
       <formula1>=IF(M476&lt;&gt;"",INDIRECT(VLOOKUP(M476,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M477" xr:uid="{D97CFCAA-F2F7-4923-AA20-E42908B9B68C}">
+    <dataValidation type="list" sqref="M477" xr:uid="{FF511774-8141-4B22-8A7C-606B04D45BDD}">
       <formula1>=IF(L477&lt;&gt;"",INDIRECT(VLOOKUP(L477,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N477" xr:uid="{F9BD948B-46C4-4372-892B-2FD5E985AF29}">
+    <dataValidation type="list" sqref="N477" xr:uid="{314D7E2B-32EA-4506-9AFD-7330CD9A8A43}">
       <formula1>=IF(M477&lt;&gt;"",INDIRECT(VLOOKUP(M477,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M478" xr:uid="{4C784875-F1F0-42C6-9999-48E93B5FF6B2}">
+    <dataValidation type="list" sqref="M478" xr:uid="{C120911D-BB26-4079-AFB1-529BAE48ED3C}">
       <formula1>=IF(L478&lt;&gt;"",INDIRECT(VLOOKUP(L478,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N478" xr:uid="{06FE86B6-90D2-4A7A-AC4F-AFEB9712CDD9}">
+    <dataValidation type="list" sqref="N478" xr:uid="{BD103EFB-AA06-42E0-A5AE-0D50C18A1CD8}">
       <formula1>=IF(M478&lt;&gt;"",INDIRECT(VLOOKUP(M478,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M479" xr:uid="{BD043B2C-ABBA-44BC-A1C4-7980E94E9B39}">
+    <dataValidation type="list" sqref="M479" xr:uid="{C31D256E-CC74-4BBC-9AD5-8C92CC0455B9}">
       <formula1>=IF(L479&lt;&gt;"",INDIRECT(VLOOKUP(L479,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N479" xr:uid="{7BB653C6-73A8-4F9E-B456-0EEF45AB2EEB}">
+    <dataValidation type="list" sqref="N479" xr:uid="{F567B97B-F07D-459C-903D-D66AA7EC42C6}">
       <formula1>=IF(M479&lt;&gt;"",INDIRECT(VLOOKUP(M479,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M480" xr:uid="{26CC42FD-09EA-4F51-9F47-81EA6F5A415B}">
+    <dataValidation type="list" sqref="M480" xr:uid="{990E348A-68F0-4E28-AC5D-E3186658F2CD}">
       <formula1>=IF(L480&lt;&gt;"",INDIRECT(VLOOKUP(L480,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N480" xr:uid="{5218DC02-C9D5-4226-90E6-DC86C408FDC6}">
+    <dataValidation type="list" sqref="N480" xr:uid="{97A608FA-BDB7-4FAF-8F78-825941294A4D}">
       <formula1>=IF(M480&lt;&gt;"",INDIRECT(VLOOKUP(M480,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M481" xr:uid="{0C22AADB-6691-45FA-956F-4E0E2CCB29F1}">
+    <dataValidation type="list" sqref="M481" xr:uid="{BD8CF5AC-E1D3-4477-A8F5-515B575A2CDF}">
       <formula1>=IF(L481&lt;&gt;"",INDIRECT(VLOOKUP(L481,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N481" xr:uid="{B2A28CAB-3EFC-4A42-9549-94168C8F347B}">
+    <dataValidation type="list" sqref="N481" xr:uid="{066F6F1E-2EAD-4FF7-8484-85E1A003555B}">
       <formula1>=IF(M481&lt;&gt;"",INDIRECT(VLOOKUP(M481,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M482" xr:uid="{3DD63821-B014-4F32-B1C2-114A91FFB5EA}">
+    <dataValidation type="list" sqref="M482" xr:uid="{F38810E2-99BC-4977-B5A3-FEABC1AF44E0}">
       <formula1>=IF(L482&lt;&gt;"",INDIRECT(VLOOKUP(L482,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N482" xr:uid="{0DD81732-CA84-4C90-9461-C0D645F1D3DD}">
+    <dataValidation type="list" sqref="N482" xr:uid="{07D33B4A-E479-40DD-8508-FE2EEC667ED7}">
       <formula1>=IF(M482&lt;&gt;"",INDIRECT(VLOOKUP(M482,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M483" xr:uid="{D273C950-8872-4304-AD45-A602FD6D184F}">
+    <dataValidation type="list" sqref="M483" xr:uid="{DB906A84-D9A6-4D9B-B578-70FD55B3575B}">
       <formula1>=IF(L483&lt;&gt;"",INDIRECT(VLOOKUP(L483,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N483" xr:uid="{6E7355B7-C815-438E-91FC-5731FBFF56DE}">
+    <dataValidation type="list" sqref="N483" xr:uid="{6FDCFF9F-13D9-43BE-92F7-AE82DB266799}">
       <formula1>=IF(M483&lt;&gt;"",INDIRECT(VLOOKUP(M483,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M484" xr:uid="{F28ED448-CAE2-42D6-83CB-A0E723B1D835}">
+    <dataValidation type="list" sqref="M484" xr:uid="{75FF48E2-88FF-4477-898E-4416C5F6E235}">
       <formula1>=IF(L484&lt;&gt;"",INDIRECT(VLOOKUP(L484,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N484" xr:uid="{B8D80E9B-A8D8-4931-A0BA-49E7A84FC7B3}">
+    <dataValidation type="list" sqref="N484" xr:uid="{BEA551E8-37AE-4CF5-9A06-D77351CBEB1A}">
       <formula1>=IF(M484&lt;&gt;"",INDIRECT(VLOOKUP(M484,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M485" xr:uid="{CBA0F120-3E5C-47D6-9C46-71B9D3B121E9}">
+    <dataValidation type="list" sqref="M485" xr:uid="{8CC5D95E-4E68-4315-8A71-18E2A46B75B9}">
       <formula1>=IF(L485&lt;&gt;"",INDIRECT(VLOOKUP(L485,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N485" xr:uid="{E5F97499-7EE4-47E2-95C8-7716CF29699B}">
+    <dataValidation type="list" sqref="N485" xr:uid="{F5F6EF19-DFBB-45EA-8B57-81D8974D8BB6}">
       <formula1>=IF(M485&lt;&gt;"",INDIRECT(VLOOKUP(M485,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M486" xr:uid="{E8E0ABF3-BF66-4F0E-8270-5306980CBE68}">
+    <dataValidation type="list" sqref="M486" xr:uid="{B2C909A5-94C0-4743-9F84-E2ACFE7509A3}">
       <formula1>=IF(L486&lt;&gt;"",INDIRECT(VLOOKUP(L486,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N486" xr:uid="{9F876C47-4444-4D33-920C-667DDA1E3D3D}">
+    <dataValidation type="list" sqref="N486" xr:uid="{564AA1FD-2DF8-4614-9057-3641B69F26E8}">
       <formula1>=IF(M486&lt;&gt;"",INDIRECT(VLOOKUP(M486,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M487" xr:uid="{D6059736-909B-441D-9DD0-AC1281671961}">
+    <dataValidation type="list" sqref="M487" xr:uid="{9AF6B54F-E587-4A29-A304-AB7C8BE74911}">
       <formula1>=IF(L487&lt;&gt;"",INDIRECT(VLOOKUP(L487,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N487" xr:uid="{113DC997-12CD-4508-8F9F-E874BD3FABB4}">
+    <dataValidation type="list" sqref="N487" xr:uid="{4C54BC82-F3C2-48AB-9E91-4C1F79B774E2}">
       <formula1>=IF(M487&lt;&gt;"",INDIRECT(VLOOKUP(M487,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M488" xr:uid="{E10FF1E6-E503-4FE1-8198-AB91FD4C2844}">
+    <dataValidation type="list" sqref="M488" xr:uid="{22DBB2D8-35FF-40CB-8D1C-BCF7E50B2A56}">
       <formula1>=IF(L488&lt;&gt;"",INDIRECT(VLOOKUP(L488,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N488" xr:uid="{77438DE6-94BC-4725-ADD0-98BFDD15F878}">
+    <dataValidation type="list" sqref="N488" xr:uid="{5BF383BB-5379-4B47-9B9E-F8470668AB7B}">
       <formula1>=IF(M488&lt;&gt;"",INDIRECT(VLOOKUP(M488,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M489" xr:uid="{CC488916-C2F8-40D1-93F2-CE1616D63887}">
+    <dataValidation type="list" sqref="M489" xr:uid="{44B59F3F-C0FB-4D74-BE88-15DDD018B818}">
       <formula1>=IF(L489&lt;&gt;"",INDIRECT(VLOOKUP(L489,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N489" xr:uid="{4CA6D0CC-5A14-4080-B968-353EF37329ED}">
+    <dataValidation type="list" sqref="N489" xr:uid="{7BE16630-71FE-42AC-83C0-B3C9E3826CE4}">
       <formula1>=IF(M489&lt;&gt;"",INDIRECT(VLOOKUP(M489,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M490" xr:uid="{5FFBD62C-6836-46F0-8FFF-A88BBCDD573D}">
+    <dataValidation type="list" sqref="M490" xr:uid="{E4EC5017-73D1-4D96-AFDB-B8D6F4D4E6CE}">
       <formula1>=IF(L490&lt;&gt;"",INDIRECT(VLOOKUP(L490,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N490" xr:uid="{834BBC45-196C-469E-A6F6-16A97246C42B}">
+    <dataValidation type="list" sqref="N490" xr:uid="{50222D99-19DD-4050-8B03-AE6F60D285F5}">
       <formula1>=IF(M490&lt;&gt;"",INDIRECT(VLOOKUP(M490,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M491" xr:uid="{33647C54-C96D-434A-B0EF-8570F915CA32}">
+    <dataValidation type="list" sqref="M491" xr:uid="{E1AE35E0-0348-425B-9A3C-B4F1FFC2957F}">
       <formula1>=IF(L491&lt;&gt;"",INDIRECT(VLOOKUP(L491,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N491" xr:uid="{F8251859-DA14-42A8-B784-07033414F642}">
+    <dataValidation type="list" sqref="N491" xr:uid="{298C3BD2-2E67-4946-BF7B-E839E8F52B98}">
       <formula1>=IF(M491&lt;&gt;"",INDIRECT(VLOOKUP(M491,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M492" xr:uid="{7C839245-0D7C-411B-9B60-524A18312759}">
+    <dataValidation type="list" sqref="M492" xr:uid="{4DEBE82F-C079-4809-A35B-EC93FE9319D8}">
       <formula1>=IF(L492&lt;&gt;"",INDIRECT(VLOOKUP(L492,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N492" xr:uid="{29D86E65-4F3B-4465-A627-13AD0E0E7A19}">
+    <dataValidation type="list" sqref="N492" xr:uid="{9923626E-B123-4AF2-B5E5-EACBBC2B5C15}">
       <formula1>=IF(M492&lt;&gt;"",INDIRECT(VLOOKUP(M492,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M493" xr:uid="{393D0D46-6B8B-4CE8-B829-00BA938B24E8}">
+    <dataValidation type="list" sqref="M493" xr:uid="{A5778D31-D4CF-4786-9F44-F6ADA6EE3461}">
       <formula1>=IF(L493&lt;&gt;"",INDIRECT(VLOOKUP(L493,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N493" xr:uid="{8E49245D-612C-4087-9360-231C964801C1}">
+    <dataValidation type="list" sqref="N493" xr:uid="{0ACD5337-8E50-4DFE-A334-E116643C2C1E}">
       <formula1>=IF(M493&lt;&gt;"",INDIRECT(VLOOKUP(M493,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M494" xr:uid="{E04D70CC-D03A-44D4-9B99-87E238273CD3}">
+    <dataValidation type="list" sqref="M494" xr:uid="{59504A9C-474E-4522-9769-4985A0B450E7}">
       <formula1>=IF(L494&lt;&gt;"",INDIRECT(VLOOKUP(L494,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N494" xr:uid="{21491583-2183-41CE-9B7D-7CF11E1DA686}">
+    <dataValidation type="list" sqref="N494" xr:uid="{55097C06-1FE1-46D6-9AC5-BC272B684788}">
       <formula1>=IF(M494&lt;&gt;"",INDIRECT(VLOOKUP(M494,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M495" xr:uid="{28948FF6-12D1-48C3-BDB9-CE9F699C625D}">
+    <dataValidation type="list" sqref="M495" xr:uid="{16D1DCAB-1C7A-492B-95D0-B010FD921F1D}">
       <formula1>=IF(L495&lt;&gt;"",INDIRECT(VLOOKUP(L495,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N495" xr:uid="{7ADA3E02-3629-4F35-A497-94AFD26EEB3E}">
+    <dataValidation type="list" sqref="N495" xr:uid="{8A4F9EE7-25F8-4BEB-AAAD-06C87CEA9C51}">
       <formula1>=IF(M495&lt;&gt;"",INDIRECT(VLOOKUP(M495,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M496" xr:uid="{64513DFB-DA96-4E50-86D4-42EA2D5D48AA}">
+    <dataValidation type="list" sqref="M496" xr:uid="{7E12DE59-5528-4BFD-A8A0-8EBB2F73CE98}">
       <formula1>=IF(L496&lt;&gt;"",INDIRECT(VLOOKUP(L496,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N496" xr:uid="{CF0FC8DF-EAA0-4881-975F-0644D8C836D4}">
+    <dataValidation type="list" sqref="N496" xr:uid="{086D613C-5A9E-45D3-9F21-3DAEE969803D}">
       <formula1>=IF(M496&lt;&gt;"",INDIRECT(VLOOKUP(M496,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M497" xr:uid="{8A94FEF2-A01C-489B-B58C-085DF074FACD}">
+    <dataValidation type="list" sqref="M497" xr:uid="{E5C41F61-2BE6-42CE-AF33-5E677D9CF351}">
       <formula1>=IF(L497&lt;&gt;"",INDIRECT(VLOOKUP(L497,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N497" xr:uid="{8412C7C0-2DC1-44A4-B293-841C7ACBBE5C}">
+    <dataValidation type="list" sqref="N497" xr:uid="{7A17DEBE-EC46-47F9-8505-518AB3091FF3}">
       <formula1>=IF(M497&lt;&gt;"",INDIRECT(VLOOKUP(M497,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M498" xr:uid="{646368DD-1529-4E75-92D7-E7D3087B7950}">
+    <dataValidation type="list" sqref="M498" xr:uid="{5B3D8C92-91F8-4246-93B4-186DC378FD91}">
       <formula1>=IF(L498&lt;&gt;"",INDIRECT(VLOOKUP(L498,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N498" xr:uid="{D680E756-9D59-4433-886E-73100880743C}">
+    <dataValidation type="list" sqref="N498" xr:uid="{0AA74A29-E5EE-4C6A-8B10-7F38C215AE2B}">
       <formula1>=IF(M498&lt;&gt;"",INDIRECT(VLOOKUP(M498,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M499" xr:uid="{3535D02C-2F55-4F92-B0A3-C710DF2BC27B}">
+    <dataValidation type="list" sqref="M499" xr:uid="{5FFE2F22-EB17-464A-A6BD-0EDEB1427841}">
       <formula1>=IF(L499&lt;&gt;"",INDIRECT(VLOOKUP(L499,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N499" xr:uid="{D98EE93F-53BE-4C9E-A3AD-55CE3E739C78}">
+    <dataValidation type="list" sqref="N499" xr:uid="{5FD4191B-F6F6-4D92-922D-7BB360647D13}">
       <formula1>=IF(M499&lt;&gt;"",INDIRECT(VLOOKUP(M499,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M500" xr:uid="{669E8CDB-5BB7-4A43-89AA-FF0717F4FC94}">
+    <dataValidation type="list" sqref="M500" xr:uid="{AB5B453C-6ADB-45AB-86B3-A3C798396C9A}">
       <formula1>=IF(L500&lt;&gt;"",INDIRECT(VLOOKUP(L500,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N500" xr:uid="{434521B2-9286-4E7E-B965-3044E044ADB4}">
+    <dataValidation type="list" sqref="N500" xr:uid="{51F832D0-062D-4F26-989E-0A9D0EE11FE9}">
       <formula1>=IF(M500&lt;&gt;"",INDIRECT(VLOOKUP(M500,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M501" xr:uid="{43214CCC-261F-4E4A-B0EE-78DC398DFDE0}">
+    <dataValidation type="list" sqref="M501" xr:uid="{E431481D-AB26-4F47-9538-1664435554F3}">
       <formula1>=IF(L501&lt;&gt;"",INDIRECT(VLOOKUP(L501,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N501" xr:uid="{9B5CB807-2C37-4F7F-870C-E8595346E5C4}">
+    <dataValidation type="list" sqref="N501" xr:uid="{161654E1-D144-4D27-B9B5-3F49FB9A3DF9}">
       <formula1>=IF(M501&lt;&gt;"",INDIRECT(VLOOKUP(M501,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M502" xr:uid="{20188ADE-41A4-473D-8E8D-AC90E3EC1C1F}">
+    <dataValidation type="list" sqref="M502" xr:uid="{F62E4768-657B-4B43-B438-50AB6EFDF918}">
       <formula1>=IF(L502&lt;&gt;"",INDIRECT(VLOOKUP(L502,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N502" xr:uid="{E6CB4200-B320-4086-B894-FDAD63287D44}">
+    <dataValidation type="list" sqref="N502" xr:uid="{DED235C8-8CA9-4BFE-AD77-97FBBB1E0988}">
       <formula1>=IF(M502&lt;&gt;"",INDIRECT(VLOOKUP(M502,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M503" xr:uid="{D9884491-697A-43DF-929D-38C7D3F3F9C8}">
+    <dataValidation type="list" sqref="M503" xr:uid="{7F05C88A-D60F-47E6-9A61-66FF580132BE}">
       <formula1>=IF(L503&lt;&gt;"",INDIRECT(VLOOKUP(L503,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N503" xr:uid="{3AADDA7D-F609-43AE-9135-737E8EB1CD0D}">
+    <dataValidation type="list" sqref="N503" xr:uid="{8D52C71C-B310-48C3-9126-551036F610D5}">
       <formula1>=IF(M503&lt;&gt;"",INDIRECT(VLOOKUP(M503,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M504" xr:uid="{65D0F5A9-1FD8-4613-AB1C-523892800954}">
+    <dataValidation type="list" sqref="M504" xr:uid="{2DB8A9C5-752E-4EDE-AB54-2EA27A257C40}">
       <formula1>=IF(L504&lt;&gt;"",INDIRECT(VLOOKUP(L504,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N504" xr:uid="{8046091E-CA2E-4FFE-BB73-C7335E8C9D59}">
+    <dataValidation type="list" sqref="N504" xr:uid="{4FF81160-81E7-4E56-971C-CD64847588B2}">
       <formula1>=IF(M504&lt;&gt;"",INDIRECT(VLOOKUP(M504,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M505" xr:uid="{057712D7-7051-40BC-A3FD-0E6571C9533C}">
+    <dataValidation type="list" sqref="M505" xr:uid="{5EAA9796-ECD4-4ABA-BB33-6625030CAF5F}">
       <formula1>=IF(L505&lt;&gt;"",INDIRECT(VLOOKUP(L505,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N505" xr:uid="{BE89C665-D331-4DA7-985D-5CC9CC63980D}">
+    <dataValidation type="list" sqref="N505" xr:uid="{A30A5463-04C7-4F12-A4DE-639E0D73954D}">
       <formula1>=IF(M505&lt;&gt;"",INDIRECT(VLOOKUP(M505,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M506" xr:uid="{F5CE0C03-93A3-4B5F-AD1E-AD432E155E85}">
+    <dataValidation type="list" sqref="M506" xr:uid="{48F529A5-019B-49C1-95D6-D94382679CEE}">
       <formula1>=IF(L506&lt;&gt;"",INDIRECT(VLOOKUP(L506,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N506" xr:uid="{0011A9CE-CF53-4F61-B3F1-845F8242BD7C}">
+    <dataValidation type="list" sqref="N506" xr:uid="{BF316C9B-D20D-47D1-B69B-D1EC3F4B1280}">
       <formula1>=IF(M506&lt;&gt;"",INDIRECT(VLOOKUP(M506,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M507" xr:uid="{8175E83B-C1B2-4D65-99EE-8D17F97DE0A7}">
+    <dataValidation type="list" sqref="M507" xr:uid="{FE980BE9-1B81-4E02-AACC-BE02521D26FF}">
       <formula1>=IF(L507&lt;&gt;"",INDIRECT(VLOOKUP(L507,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N507" xr:uid="{BE74E5CB-64D8-42D2-897C-44B24B12E63B}">
+    <dataValidation type="list" sqref="N507" xr:uid="{61ACB313-CCF8-449C-8D8C-6E1DB667A498}">
       <formula1>=IF(M507&lt;&gt;"",INDIRECT(VLOOKUP(M507,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M508" xr:uid="{6D54BF2E-9DF4-4FBC-B12B-5E5B54A647D3}">
+    <dataValidation type="list" sqref="M508" xr:uid="{C448E205-0988-4CB4-8BCE-464E2305239E}">
       <formula1>=IF(L508&lt;&gt;"",INDIRECT(VLOOKUP(L508,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N508" xr:uid="{CE3B8E7C-330C-4F9C-ABBD-2B28384A7D4C}">
+    <dataValidation type="list" sqref="N508" xr:uid="{AC1F7A61-B88F-4F05-BC29-64AE7F5112C0}">
       <formula1>=IF(M508&lt;&gt;"",INDIRECT(VLOOKUP(M508,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M509" xr:uid="{F1C2D0E0-7F05-491C-83B8-E96B5A8D6984}">
+    <dataValidation type="list" sqref="M509" xr:uid="{77F1F797-EA57-47C1-9590-901F01DD9FFC}">
       <formula1>=IF(L509&lt;&gt;"",INDIRECT(VLOOKUP(L509,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N509" xr:uid="{DC78142B-BBE5-40F0-9332-C9BB25073D00}">
+    <dataValidation type="list" sqref="N509" xr:uid="{25770055-6C45-4AA9-A6F3-16D32B4C55BD}">
       <formula1>=IF(M509&lt;&gt;"",INDIRECT(VLOOKUP(M509,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M510" xr:uid="{ABFF1D2E-B593-4951-A6D9-A4AD9C8DF6DC}">
+    <dataValidation type="list" sqref="M510" xr:uid="{0EA385DE-845E-4207-A229-3863B1CC684E}">
       <formula1>=IF(L510&lt;&gt;"",INDIRECT(VLOOKUP(L510,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N510" xr:uid="{E4AD0C47-68CE-4E01-92AE-5D2364077D6B}">
+    <dataValidation type="list" sqref="N510" xr:uid="{96A91E4D-67D8-4A7F-91A7-9BE7780BEF62}">
       <formula1>=IF(M510&lt;&gt;"",INDIRECT(VLOOKUP(M510,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M511" xr:uid="{71679CFA-641F-464A-913B-084A46437257}">
+    <dataValidation type="list" sqref="M511" xr:uid="{47FD5C26-B0B9-4EF4-B76B-A8CBE80FF46B}">
       <formula1>=IF(L511&lt;&gt;"",INDIRECT(VLOOKUP(L511,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N511" xr:uid="{7DBDD98C-6C50-485B-BBB4-434924D0A8EB}">
+    <dataValidation type="list" sqref="N511" xr:uid="{5374D8B8-A329-4B68-8F43-DCB2C2F550B0}">
       <formula1>=IF(M511&lt;&gt;"",INDIRECT(VLOOKUP(M511,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M512" xr:uid="{91186734-BD78-43E1-BF5D-6C226CBED40E}">
+    <dataValidation type="list" sqref="M512" xr:uid="{C337350E-F31B-4A03-A2AB-73AC8D33AA27}">
       <formula1>=IF(L512&lt;&gt;"",INDIRECT(VLOOKUP(L512,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N512" xr:uid="{A28E0ED6-7388-41A3-9F4F-D99C542DAEFB}">
+    <dataValidation type="list" sqref="N512" xr:uid="{F72C2CBF-2EDA-4905-87A1-D0C687BE166A}">
       <formula1>=IF(M512&lt;&gt;"",INDIRECT(VLOOKUP(M512,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M513" xr:uid="{8CBA2217-8904-4B98-9AF2-3AC8CB814910}">
+    <dataValidation type="list" sqref="M513" xr:uid="{29C7584B-F097-40ED-95A5-A327A3B9E286}">
       <formula1>=IF(L513&lt;&gt;"",INDIRECT(VLOOKUP(L513,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N513" xr:uid="{E9EBF84A-E7B9-4E62-B688-405D94319417}">
+    <dataValidation type="list" sqref="N513" xr:uid="{BC642C61-AC66-4EC2-B5D6-A2EADE9B944B}">
       <formula1>=IF(M513&lt;&gt;"",INDIRECT(VLOOKUP(M513,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M514" xr:uid="{6C8844CC-82BF-49A3-838C-3D6DDCE049B5}">
+    <dataValidation type="list" sqref="M514" xr:uid="{BA8D859F-AC12-4ED3-8002-5A220BF2B6B4}">
       <formula1>=IF(L514&lt;&gt;"",INDIRECT(VLOOKUP(L514,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N514" xr:uid="{92F43471-1AF8-44C9-BF09-4538174F5556}">
+    <dataValidation type="list" sqref="N514" xr:uid="{0CE009C2-BA0A-4AFD-A08F-8AFAFBEBC0DD}">
       <formula1>=IF(M514&lt;&gt;"",INDIRECT(VLOOKUP(M514,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M515" xr:uid="{0CCC2E85-0873-4D83-97E5-69D326D7E6F6}">
+    <dataValidation type="list" sqref="M515" xr:uid="{FF9F5EFD-53AC-477F-A7B1-9FE18B19585E}">
       <formula1>=IF(L515&lt;&gt;"",INDIRECT(VLOOKUP(L515,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N515" xr:uid="{ED1903C6-20A0-4AC6-A283-76C7C4F25190}">
+    <dataValidation type="list" sqref="N515" xr:uid="{1A3D77DA-2955-4862-BDDD-462B1F39EF8E}">
       <formula1>=IF(M515&lt;&gt;"",INDIRECT(VLOOKUP(M515,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M516" xr:uid="{85BC422B-CDCA-4380-8EAB-B3285E578A14}">
+    <dataValidation type="list" sqref="M516" xr:uid="{14B926F3-C751-4927-87DA-193DF8284E36}">
       <formula1>=IF(L516&lt;&gt;"",INDIRECT(VLOOKUP(L516,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N516" xr:uid="{B2C46DFA-0830-43D6-822D-4CAD3FEA2650}">
+    <dataValidation type="list" sqref="N516" xr:uid="{2B54AEC9-FF40-4176-98B4-52B27CCB308C}">
       <formula1>=IF(M516&lt;&gt;"",INDIRECT(VLOOKUP(M516,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M517" xr:uid="{32256930-630E-4D33-9E71-10F20ACC88BA}">
+    <dataValidation type="list" sqref="M517" xr:uid="{444E4F20-8EAC-40ED-886D-E140619ECF06}">
       <formula1>=IF(L517&lt;&gt;"",INDIRECT(VLOOKUP(L517,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N517" xr:uid="{E5836809-7062-41D2-A05A-0956B5791818}">
+    <dataValidation type="list" sqref="N517" xr:uid="{885D16C7-A59F-4BC5-8BA3-D9B7A1458D11}">
       <formula1>=IF(M517&lt;&gt;"",INDIRECT(VLOOKUP(M517,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M518" xr:uid="{336F62E4-6B02-422E-AC27-3B0AA1D8DFAC}">
+    <dataValidation type="list" sqref="M518" xr:uid="{A9D3FDE5-3D20-410F-952B-FB6DA4434660}">
       <formula1>=IF(L518&lt;&gt;"",INDIRECT(VLOOKUP(L518,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N518" xr:uid="{80E88F52-084C-43A1-B337-E7DB08FEC253}">
+    <dataValidation type="list" sqref="N518" xr:uid="{AFEB23ED-03B7-4EA0-8AF4-A65B9BBD7D73}">
       <formula1>=IF(M518&lt;&gt;"",INDIRECT(VLOOKUP(M518,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M519" xr:uid="{AA030EF2-90E3-4698-B0F5-655D8C05776E}">
+    <dataValidation type="list" sqref="M519" xr:uid="{EC630B6C-54FE-454A-9070-1F6AED0AAA17}">
       <formula1>=IF(L519&lt;&gt;"",INDIRECT(VLOOKUP(L519,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N519" xr:uid="{C4479DF0-A70E-44B4-80D4-E4C7B6951B00}">
+    <dataValidation type="list" sqref="N519" xr:uid="{24D9C14D-EA27-4C94-BA79-4AAE445C6E96}">
       <formula1>=IF(M519&lt;&gt;"",INDIRECT(VLOOKUP(M519,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M520" xr:uid="{EB7DCC89-2243-4454-AD06-743CA63EF43D}">
+    <dataValidation type="list" sqref="M520" xr:uid="{C5B55881-A93E-4EA2-B0E7-0AEBF66E153C}">
       <formula1>=IF(L520&lt;&gt;"",INDIRECT(VLOOKUP(L520,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N520" xr:uid="{43892C20-F149-4C44-9A28-B350CDFCFFA2}">
+    <dataValidation type="list" sqref="N520" xr:uid="{15A27F35-3F99-42F3-8668-2E732B0E145A}">
       <formula1>=IF(M520&lt;&gt;"",INDIRECT(VLOOKUP(M520,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M521" xr:uid="{97803B1F-8783-4B47-9A0C-BB4CE42EF2EF}">
+    <dataValidation type="list" sqref="M521" xr:uid="{1DB6F607-BBB8-4B90-BFB8-1EE95D0DF1AC}">
       <formula1>=IF(L521&lt;&gt;"",INDIRECT(VLOOKUP(L521,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N521" xr:uid="{3B118AC2-8DDE-4500-90C6-70C6EF9E4CD6}">
+    <dataValidation type="list" sqref="N521" xr:uid="{18C12FC7-E3DD-41C0-AA1D-C0B98A0BA64B}">
       <formula1>=IF(M521&lt;&gt;"",INDIRECT(VLOOKUP(M521,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M522" xr:uid="{F3E90986-5B25-414F-93B3-E6FFB83AB41D}">
+    <dataValidation type="list" sqref="M522" xr:uid="{C3DB9727-8BB5-4741-AF45-189DCC4ECBC1}">
       <formula1>=IF(L522&lt;&gt;"",INDIRECT(VLOOKUP(L522,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N522" xr:uid="{24FDA259-8280-434E-8986-1894C7A20CAE}">
+    <dataValidation type="list" sqref="N522" xr:uid="{B30173CE-2E0D-465F-B2F6-FD73016BD723}">
       <formula1>=IF(M522&lt;&gt;"",INDIRECT(VLOOKUP(M522,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M523" xr:uid="{12D8D161-3DFA-4F6E-9C85-A357A7907187}">
+    <dataValidation type="list" sqref="M523" xr:uid="{B5ED755B-8311-4D61-97F7-862F2008FC30}">
       <formula1>=IF(L523&lt;&gt;"",INDIRECT(VLOOKUP(L523,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N523" xr:uid="{532EA203-6B46-4CFA-AD04-80CDAF75A56C}">
+    <dataValidation type="list" sqref="N523" xr:uid="{BBD6F3FC-553B-4DA5-BF99-B58A1AF0EAF8}">
       <formula1>=IF(M523&lt;&gt;"",INDIRECT(VLOOKUP(M523,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M524" xr:uid="{FD1A7C31-DBD1-4F24-9670-CCC6BE6D52E2}">
+    <dataValidation type="list" sqref="M524" xr:uid="{98227A83-CC86-4E9B-B3D2-6837D337B097}">
       <formula1>=IF(L524&lt;&gt;"",INDIRECT(VLOOKUP(L524,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N524" xr:uid="{877DB845-25FF-417D-89D7-00991F6813A8}">
+    <dataValidation type="list" sqref="N524" xr:uid="{08D0C4CC-0080-4F3F-B55C-75AC7C8507D7}">
       <formula1>=IF(M524&lt;&gt;"",INDIRECT(VLOOKUP(M524,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M525" xr:uid="{A026DD38-DA53-4212-909D-32CB963F6B70}">
+    <dataValidation type="list" sqref="M525" xr:uid="{10E05FDD-F0C7-48A8-B013-87D427194BCD}">
       <formula1>=IF(L525&lt;&gt;"",INDIRECT(VLOOKUP(L525,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N525" xr:uid="{EECEC61A-CB5E-4DD9-A118-99DE580441AA}">
+    <dataValidation type="list" sqref="N525" xr:uid="{1615A67D-366A-4880-9703-111BFE7FA665}">
       <formula1>=IF(M525&lt;&gt;"",INDIRECT(VLOOKUP(M525,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M526" xr:uid="{312B00C4-77AD-4298-8DCB-C6E71BBE9BE2}">
+    <dataValidation type="list" sqref="M526" xr:uid="{10670201-34D8-4313-A7EB-BB66209612A4}">
       <formula1>=IF(L526&lt;&gt;"",INDIRECT(VLOOKUP(L526,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N526" xr:uid="{32E940C1-5FEF-4880-B9F5-F9882AA7F506}">
+    <dataValidation type="list" sqref="N526" xr:uid="{A1BFFB52-4ADD-4673-9C84-8703423FC01A}">
       <formula1>=IF(M526&lt;&gt;"",INDIRECT(VLOOKUP(M526,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M527" xr:uid="{557C5040-69BD-4DE8-B466-69AAF078D2D0}">
+    <dataValidation type="list" sqref="M527" xr:uid="{F0F3C843-5701-4916-87AA-3ABB02766363}">
       <formula1>=IF(L527&lt;&gt;"",INDIRECT(VLOOKUP(L527,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N527" xr:uid="{8BCA791D-4B6B-435A-BFDD-A37795695C73}">
+    <dataValidation type="list" sqref="N527" xr:uid="{31EBA332-329E-4A26-A235-935C0FAF8844}">
       <formula1>=IF(M527&lt;&gt;"",INDIRECT(VLOOKUP(M527,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M528" xr:uid="{981C5942-3634-4915-85A3-90E666FB0159}">
+    <dataValidation type="list" sqref="M528" xr:uid="{EE477648-4039-4E6C-8B13-22E82AB975CA}">
       <formula1>=IF(L528&lt;&gt;"",INDIRECT(VLOOKUP(L528,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N528" xr:uid="{7786654F-2FCE-4B19-B8DB-760B065011A0}">
+    <dataValidation type="list" sqref="N528" xr:uid="{BBF71CF2-B93C-4867-8C7B-687617DFB851}">
       <formula1>=IF(M528&lt;&gt;"",INDIRECT(VLOOKUP(M528,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M529" xr:uid="{DAA1AB7A-71F5-4530-9FE9-C8D4A5174A95}">
+    <dataValidation type="list" sqref="M529" xr:uid="{5D88E7E6-C57B-4601-9CDF-3C12F9491066}">
       <formula1>=IF(L529&lt;&gt;"",INDIRECT(VLOOKUP(L529,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N529" xr:uid="{CF8EC988-7D18-4C3E-9F3E-AC6CB5031924}">
+    <dataValidation type="list" sqref="N529" xr:uid="{1F78A032-F15A-46EA-A003-E2A8B2F34AEB}">
       <formula1>=IF(M529&lt;&gt;"",INDIRECT(VLOOKUP(M529,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M530" xr:uid="{D4F59440-F730-4252-8225-39C511E5CDE3}">
+    <dataValidation type="list" sqref="M530" xr:uid="{62D59E4F-69FD-44B3-8EC7-B96822C1628E}">
       <formula1>=IF(L530&lt;&gt;"",INDIRECT(VLOOKUP(L530,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N530" xr:uid="{4477AB5F-CD3A-46B3-880B-C610456DAF7A}">
+    <dataValidation type="list" sqref="N530" xr:uid="{559DA34F-98CB-4BB5-82B9-489B2B53E90A}">
       <formula1>=IF(M530&lt;&gt;"",INDIRECT(VLOOKUP(M530,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M531" xr:uid="{2EDE6BF0-E221-4D56-BF33-B0B765C525EF}">
+    <dataValidation type="list" sqref="M531" xr:uid="{890373E8-B5BD-4401-9494-60EBBEC0A529}">
       <formula1>=IF(L531&lt;&gt;"",INDIRECT(VLOOKUP(L531,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N531" xr:uid="{12D1D99C-4DAD-4571-AAF0-86D5C2EF3299}">
+    <dataValidation type="list" sqref="N531" xr:uid="{D2E01FDB-1EFB-4FBF-B49C-EF7407466069}">
       <formula1>=IF(M531&lt;&gt;"",INDIRECT(VLOOKUP(M531,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M532" xr:uid="{78DB65C2-FFD3-4AC6-A88D-D6DF9D4D7A88}">
+    <dataValidation type="list" sqref="M532" xr:uid="{0DB31ED6-BED4-4261-B8CF-C9D449547F7D}">
       <formula1>=IF(L532&lt;&gt;"",INDIRECT(VLOOKUP(L532,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N532" xr:uid="{DBCBF89A-E1A4-425B-87D4-EAB341842C51}">
+    <dataValidation type="list" sqref="N532" xr:uid="{A314E782-DBA3-41C3-BAE0-14B6FF84B35D}">
       <formula1>=IF(M532&lt;&gt;"",INDIRECT(VLOOKUP(M532,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M533" xr:uid="{4322420C-83B6-4B6D-82F0-92F652EE6BB3}">
+    <dataValidation type="list" sqref="M533" xr:uid="{65B20E7B-590D-4713-951B-2301DF21C053}">
       <formula1>=IF(L533&lt;&gt;"",INDIRECT(VLOOKUP(L533,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N533" xr:uid="{35ADA60B-855C-4262-B213-44C5B3820CE9}">
+    <dataValidation type="list" sqref="N533" xr:uid="{446FC541-1475-49D0-958A-6A4E6F52C647}">
       <formula1>=IF(M533&lt;&gt;"",INDIRECT(VLOOKUP(M533,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M534" xr:uid="{558798AD-BD54-489C-81FA-B0E0DBB38774}">
+    <dataValidation type="list" sqref="M534" xr:uid="{6804E42D-9D2B-48C3-B272-43D741D16858}">
       <formula1>=IF(L534&lt;&gt;"",INDIRECT(VLOOKUP(L534,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N534" xr:uid="{EE1AA8F4-50E3-47A4-B17D-B1418EA098EC}">
+    <dataValidation type="list" sqref="N534" xr:uid="{2F5354A4-6534-4B29-B69B-02D48433D133}">
       <formula1>=IF(M534&lt;&gt;"",INDIRECT(VLOOKUP(M534,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M535" xr:uid="{7B6E9C60-2179-4D55-B4DE-65854D5BA616}">
+    <dataValidation type="list" sqref="M535" xr:uid="{DDFE8610-F0CA-4B9C-A91C-6E19F353DF43}">
       <formula1>=IF(L535&lt;&gt;"",INDIRECT(VLOOKUP(L535,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N535" xr:uid="{16EF9CB4-A667-4FAB-AD0D-34ACC11B3DE4}">
+    <dataValidation type="list" sqref="N535" xr:uid="{0ABE8F89-9141-4CA5-B57D-A3457FD4E46F}">
       <formula1>=IF(M535&lt;&gt;"",INDIRECT(VLOOKUP(M535,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M536" xr:uid="{CDBA7FEB-8103-4906-B63C-D563947449C6}">
+    <dataValidation type="list" sqref="M536" xr:uid="{5B3018EA-A512-47D5-BF22-04C538E05E8E}">
       <formula1>=IF(L536&lt;&gt;"",INDIRECT(VLOOKUP(L536,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N536" xr:uid="{75B58FBE-353A-4431-B5D7-84B77D55D1D9}">
+    <dataValidation type="list" sqref="N536" xr:uid="{FDBC19F1-6351-4195-A982-4D1A8CE6A507}">
       <formula1>=IF(M536&lt;&gt;"",INDIRECT(VLOOKUP(M536,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M537" xr:uid="{5EE43541-B7B4-4C0A-96FF-88F738FA760E}">
+    <dataValidation type="list" sqref="M537" xr:uid="{C137C3AD-268A-4A3A-9F79-84CCDFC01057}">
       <formula1>=IF(L537&lt;&gt;"",INDIRECT(VLOOKUP(L537,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N537" xr:uid="{E91F3CFF-9F2B-4CCD-B4B4-52BCD2926CC9}">
+    <dataValidation type="list" sqref="N537" xr:uid="{1725F1AA-3D94-4E84-A151-CA24079309B4}">
       <formula1>=IF(M537&lt;&gt;"",INDIRECT(VLOOKUP(M537,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M538" xr:uid="{EA194EFF-F689-4CF6-A345-B389848784FE}">
+    <dataValidation type="list" sqref="M538" xr:uid="{332752B4-34F1-4AB8-A528-35B85B1259DC}">
       <formula1>=IF(L538&lt;&gt;"",INDIRECT(VLOOKUP(L538,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N538" xr:uid="{E338FF4F-3845-42A5-8024-0C60E2F4DB21}">
+    <dataValidation type="list" sqref="N538" xr:uid="{ACBC5FA8-4A50-410A-B180-F0F5C651F1F4}">
       <formula1>=IF(M538&lt;&gt;"",INDIRECT(VLOOKUP(M538,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M539" xr:uid="{70F3F9E7-8E89-4F58-9C86-9D8B2D9C2A5C}">
+    <dataValidation type="list" sqref="M539" xr:uid="{7ED407EF-A8FF-4504-B6D3-22E42A6D1C70}">
       <formula1>=IF(L539&lt;&gt;"",INDIRECT(VLOOKUP(L539,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N539" xr:uid="{7FD4ADF4-624B-4982-B85B-C700F6A783F2}">
+    <dataValidation type="list" sqref="N539" xr:uid="{4F1CB170-3412-4B58-8D93-6C3D69B73D35}">
       <formula1>=IF(M539&lt;&gt;"",INDIRECT(VLOOKUP(M539,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M540" xr:uid="{5A46AAD3-1368-4AB2-9A57-0C99BA4B2493}">
+    <dataValidation type="list" sqref="M540" xr:uid="{8C00206B-1EB2-4CA4-BC19-751DEF757D7C}">
       <formula1>=IF(L540&lt;&gt;"",INDIRECT(VLOOKUP(L540,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N540" xr:uid="{C0937F08-1540-4F0C-96CE-F25243E27399}">
+    <dataValidation type="list" sqref="N540" xr:uid="{10F2AFDF-8C11-4820-9938-76F6BDE25D64}">
       <formula1>=IF(M540&lt;&gt;"",INDIRECT(VLOOKUP(M540,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M541" xr:uid="{3D05E79F-D08A-4FE9-B141-9ACEFB21D9A5}">
+    <dataValidation type="list" sqref="M541" xr:uid="{582DBA75-3B6E-4E90-AA52-6F80659B392B}">
       <formula1>=IF(L541&lt;&gt;"",INDIRECT(VLOOKUP(L541,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N541" xr:uid="{D249F5E2-8440-4BF2-A5ED-A499D66ABFB5}">
+    <dataValidation type="list" sqref="N541" xr:uid="{262DD5F3-8EBC-4D5B-A862-157CC9BC13AF}">
       <formula1>=IF(M541&lt;&gt;"",INDIRECT(VLOOKUP(M541,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M542" xr:uid="{6BCE45AD-C721-467F-8757-719359749020}">
+    <dataValidation type="list" sqref="M542" xr:uid="{36EABF9B-54E7-40A0-8A4A-CAEE82BBDB67}">
       <formula1>=IF(L542&lt;&gt;"",INDIRECT(VLOOKUP(L542,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N542" xr:uid="{01F5C98C-C7E5-4DD7-806A-1491E79680E5}">
+    <dataValidation type="list" sqref="N542" xr:uid="{BFD6A0ED-E644-4095-A8DE-0322E086EF45}">
       <formula1>=IF(M542&lt;&gt;"",INDIRECT(VLOOKUP(M542,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M543" xr:uid="{1A260063-13D6-4DE2-A8DF-F5AEBB8AC0B9}">
+    <dataValidation type="list" sqref="M543" xr:uid="{76968E6C-25F2-47C0-BA41-B26BDC582787}">
       <formula1>=IF(L543&lt;&gt;"",INDIRECT(VLOOKUP(L543,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N543" xr:uid="{6650D844-BCC6-4074-8212-0D222169E0E1}">
+    <dataValidation type="list" sqref="N543" xr:uid="{E5F2FA04-F9EC-4453-9278-483308242C40}">
       <formula1>=IF(M543&lt;&gt;"",INDIRECT(VLOOKUP(M543,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M544" xr:uid="{D116E5DC-A34D-4FE1-8597-FD59596800BE}">
+    <dataValidation type="list" sqref="M544" xr:uid="{173832AE-703D-4552-B082-78452A80C0F6}">
       <formula1>=IF(L544&lt;&gt;"",INDIRECT(VLOOKUP(L544,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N544" xr:uid="{CCA8BD51-9374-4726-9D5F-57BB8801C567}">
+    <dataValidation type="list" sqref="N544" xr:uid="{3D944AC1-3F3A-4D57-9BC6-E8A7278EA131}">
       <formula1>=IF(M544&lt;&gt;"",INDIRECT(VLOOKUP(M544,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M545" xr:uid="{7A453BE0-1835-42BF-836B-E81FBD0EF7CC}">
+    <dataValidation type="list" sqref="M545" xr:uid="{39549491-90BA-40C5-B3B8-37A5B0AC92FD}">
       <formula1>=IF(L545&lt;&gt;"",INDIRECT(VLOOKUP(L545,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N545" xr:uid="{2B42F6A7-5829-4DA5-9CC9-0424F0BE21C0}">
+    <dataValidation type="list" sqref="N545" xr:uid="{F2BCF338-6DC4-4967-961A-CC13B22CF65F}">
       <formula1>=IF(M545&lt;&gt;"",INDIRECT(VLOOKUP(M545,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M546" xr:uid="{7E24C028-C683-474F-AEDA-DEE7141B95A8}">
+    <dataValidation type="list" sqref="M546" xr:uid="{3B6F8F56-FA17-4017-AA7F-DCB592BE8EFB}">
       <formula1>=IF(L546&lt;&gt;"",INDIRECT(VLOOKUP(L546,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N546" xr:uid="{09FDE476-0AD5-4BE7-92CF-6281B476322A}">
+    <dataValidation type="list" sqref="N546" xr:uid="{8DC1BA72-14E7-47FE-BACF-99183296AE5C}">
       <formula1>=IF(M546&lt;&gt;"",INDIRECT(VLOOKUP(M546,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M547" xr:uid="{0485047B-F5DD-49D3-ACC3-C72840EE6554}">
+    <dataValidation type="list" sqref="M547" xr:uid="{DE5DF63C-988D-432C-B2E1-621AA285E522}">
       <formula1>=IF(L547&lt;&gt;"",INDIRECT(VLOOKUP(L547,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N547" xr:uid="{74425924-6DC5-4D1F-B47C-B5F946CF0D46}">
+    <dataValidation type="list" sqref="N547" xr:uid="{6332BF99-30A6-4C9D-BEFF-3B449729D625}">
       <formula1>=IF(M547&lt;&gt;"",INDIRECT(VLOOKUP(M547,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M548" xr:uid="{D29F769C-C91D-4DFD-9846-1BA83CF106F2}">
+    <dataValidation type="list" sqref="M548" xr:uid="{B4AF9F90-C49E-4405-8E17-55D111598265}">
       <formula1>=IF(L548&lt;&gt;"",INDIRECT(VLOOKUP(L548,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N548" xr:uid="{6431EBF4-CFCC-46EB-BBCC-EE0C22C80366}">
+    <dataValidation type="list" sqref="N548" xr:uid="{D546B480-B655-4692-985A-477DEBDCE0E4}">
       <formula1>=IF(M548&lt;&gt;"",INDIRECT(VLOOKUP(M548,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M549" xr:uid="{E1C50FAE-F15A-45D1-B348-EA858A528FD8}">
+    <dataValidation type="list" sqref="M549" xr:uid="{84FE59C3-D6CA-426A-AC73-0A87BCD530EA}">
       <formula1>=IF(L549&lt;&gt;"",INDIRECT(VLOOKUP(L549,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N549" xr:uid="{26F88743-1244-40E4-A639-1E934A3A9966}">
+    <dataValidation type="list" sqref="N549" xr:uid="{51728E92-0B41-4055-9726-517944309845}">
       <formula1>=IF(M549&lt;&gt;"",INDIRECT(VLOOKUP(M549,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M550" xr:uid="{03079119-FDE4-48E6-AD4D-9D3BBBCDC3D8}">
+    <dataValidation type="list" sqref="M550" xr:uid="{4DB4A424-888E-400F-ACA2-37B7F2A1A17E}">
       <formula1>=IF(L550&lt;&gt;"",INDIRECT(VLOOKUP(L550,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N550" xr:uid="{FB1A4D43-98A1-4840-B401-C92B90DFEEC0}">
+    <dataValidation type="list" sqref="N550" xr:uid="{7E58AB79-D077-4DAF-BE7E-F67CAEED869B}">
       <formula1>=IF(M550&lt;&gt;"",INDIRECT(VLOOKUP(M550,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M551" xr:uid="{8F349213-7BCD-4969-B2C7-0BE8328067F4}">
+    <dataValidation type="list" sqref="M551" xr:uid="{69AA706C-FE7D-4F72-9B5D-029F1654AB4B}">
       <formula1>=IF(L551&lt;&gt;"",INDIRECT(VLOOKUP(L551,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N551" xr:uid="{943C35E2-D8F1-49BD-AF0B-A3AD74E5A6EF}">
+    <dataValidation type="list" sqref="N551" xr:uid="{0A960E9F-46CA-4BBA-9661-6DA1F11BDBC9}">
       <formula1>=IF(M551&lt;&gt;"",INDIRECT(VLOOKUP(M551,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M552" xr:uid="{6A04129F-6547-41E8-8CED-F9F950B01E74}">
+    <dataValidation type="list" sqref="M552" xr:uid="{882FC5A4-E736-4544-995E-7ABC33379EFA}">
       <formula1>=IF(L552&lt;&gt;"",INDIRECT(VLOOKUP(L552,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N552" xr:uid="{32870598-BE8E-4CD2-84E9-0C6EC65D23E3}">
+    <dataValidation type="list" sqref="N552" xr:uid="{C0F42A1E-D999-4D4D-BDB6-25A74B02F8F1}">
       <formula1>=IF(M552&lt;&gt;"",INDIRECT(VLOOKUP(M552,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M553" xr:uid="{74EC2C38-0094-41DA-9B49-E2765698E595}">
+    <dataValidation type="list" sqref="M553" xr:uid="{9B579A18-5E79-495B-8402-09079254D8E8}">
       <formula1>=IF(L553&lt;&gt;"",INDIRECT(VLOOKUP(L553,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N553" xr:uid="{3585F0FE-8544-4CF6-B2E0-48BDD3399717}">
+    <dataValidation type="list" sqref="N553" xr:uid="{3D8E37E1-1566-4BF9-8F17-787FDD1582EB}">
       <formula1>=IF(M553&lt;&gt;"",INDIRECT(VLOOKUP(M553,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M554" xr:uid="{BADDE5B2-A994-406D-870F-ED5DC061EF36}">
+    <dataValidation type="list" sqref="M554" xr:uid="{19BD5AE3-A439-46AA-BF12-FBBD27406089}">
       <formula1>=IF(L554&lt;&gt;"",INDIRECT(VLOOKUP(L554,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N554" xr:uid="{3277D2B4-2B2E-42BF-A9B0-0F58076CD4F1}">
+    <dataValidation type="list" sqref="N554" xr:uid="{5EBEBE2B-2BBE-49F7-A293-1D12450A9B28}">
       <formula1>=IF(M554&lt;&gt;"",INDIRECT(VLOOKUP(M554,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M555" xr:uid="{D145A12D-8D2A-492B-A45D-688B4F59327B}">
+    <dataValidation type="list" sqref="M555" xr:uid="{EEDB65B2-68B9-4356-8757-8F0EFADDAC64}">
       <formula1>=IF(L555&lt;&gt;"",INDIRECT(VLOOKUP(L555,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N555" xr:uid="{49AA6559-193A-4CE4-BC5F-9BB8B969C992}">
+    <dataValidation type="list" sqref="N555" xr:uid="{F015910C-B3D6-4A3E-A02D-D2F619CBCA92}">
       <formula1>=IF(M555&lt;&gt;"",INDIRECT(VLOOKUP(M555,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M556" xr:uid="{222FA7A6-690D-4903-AA48-EFF4774753B1}">
+    <dataValidation type="list" sqref="M556" xr:uid="{47A93616-3066-4866-93A4-5465A9510F8C}">
       <formula1>=IF(L556&lt;&gt;"",INDIRECT(VLOOKUP(L556,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N556" xr:uid="{DD457AFB-02EC-42B4-9CA5-A2BF163A3132}">
+    <dataValidation type="list" sqref="N556" xr:uid="{447CBF46-535A-4640-816E-D8796496BF84}">
       <formula1>=IF(M556&lt;&gt;"",INDIRECT(VLOOKUP(M556,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M557" xr:uid="{DFB5DC12-5A6F-49B7-AB8E-0E41C0C6E009}">
+    <dataValidation type="list" sqref="M557" xr:uid="{659FCAEC-94B5-4214-A217-C3488C5CC19E}">
       <formula1>=IF(L557&lt;&gt;"",INDIRECT(VLOOKUP(L557,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N557" xr:uid="{1DC99455-8AD1-4365-BA41-8B4899FE264C}">
+    <dataValidation type="list" sqref="N557" xr:uid="{23C366E9-85A7-4E45-8A27-1C6F92814A25}">
       <formula1>=IF(M557&lt;&gt;"",INDIRECT(VLOOKUP(M557,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M558" xr:uid="{7A9EC6BF-3576-43AE-B02A-8B04F349CC5A}">
+    <dataValidation type="list" sqref="M558" xr:uid="{E2CC8624-4F6F-49E8-B799-C7FB6EB7247B}">
       <formula1>=IF(L558&lt;&gt;"",INDIRECT(VLOOKUP(L558,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N558" xr:uid="{C8DD5EAF-CF54-42F7-B076-89CFD1A360F1}">
+    <dataValidation type="list" sqref="N558" xr:uid="{E415FD50-4863-4ACC-ACC9-F94C750D3483}">
       <formula1>=IF(M558&lt;&gt;"",INDIRECT(VLOOKUP(M558,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M559" xr:uid="{0D61978F-AE12-410C-862E-F1ACCB912C1B}">
+    <dataValidation type="list" sqref="M559" xr:uid="{F3556C5C-CD48-4441-8951-59DA7405811A}">
       <formula1>=IF(L559&lt;&gt;"",INDIRECT(VLOOKUP(L559,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N559" xr:uid="{D3D79082-104E-46A7-9D4A-50D5BB25E728}">
+    <dataValidation type="list" sqref="N559" xr:uid="{26DA73FB-AE6A-4CD4-9E00-21DACE7A6714}">
       <formula1>=IF(M559&lt;&gt;"",INDIRECT(VLOOKUP(M559,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M560" xr:uid="{C0E993AE-89FD-47D9-88C0-C833B9AF0852}">
+    <dataValidation type="list" sqref="M560" xr:uid="{38EBBAB8-DAC4-43AA-B2D7-E5E6FD3FE78B}">
       <formula1>=IF(L560&lt;&gt;"",INDIRECT(VLOOKUP(L560,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N560" xr:uid="{A7883E06-11B3-4780-A586-121D34212935}">
+    <dataValidation type="list" sqref="N560" xr:uid="{E4735939-FB75-491D-803A-7E19068C2BF7}">
       <formula1>=IF(M560&lt;&gt;"",INDIRECT(VLOOKUP(M560,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M561" xr:uid="{A2FEA928-CB49-489F-AA38-58BC87025E5D}">
+    <dataValidation type="list" sqref="M561" xr:uid="{635D4D02-8F0E-42B8-9520-B555D044A586}">
       <formula1>=IF(L561&lt;&gt;"",INDIRECT(VLOOKUP(L561,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N561" xr:uid="{3682D1F8-3996-40DF-8410-F7D7D92F6A01}">
+    <dataValidation type="list" sqref="N561" xr:uid="{EA977519-B4CB-4B70-AE55-FBA3B4FAFC47}">
       <formula1>=IF(M561&lt;&gt;"",INDIRECT(VLOOKUP(M561,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M562" xr:uid="{281A0887-AB50-48C7-8A0A-B661F32165E4}">
+    <dataValidation type="list" sqref="M562" xr:uid="{D02581F3-5F9D-4612-B2F6-2D87F581CEB7}">
       <formula1>=IF(L562&lt;&gt;"",INDIRECT(VLOOKUP(L562,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N562" xr:uid="{4148C216-893B-4E39-AC61-3BCB52CD7432}">
+    <dataValidation type="list" sqref="N562" xr:uid="{CC197355-92ED-4A56-BD36-64A3839B105C}">
       <formula1>=IF(M562&lt;&gt;"",INDIRECT(VLOOKUP(M562,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M563" xr:uid="{095F0779-4006-4B02-AEE9-8A0BF0F0696A}">
+    <dataValidation type="list" sqref="M563" xr:uid="{1183860A-7E88-4F05-9D81-DBD8C4D6060E}">
       <formula1>=IF(L563&lt;&gt;"",INDIRECT(VLOOKUP(L563,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N563" xr:uid="{E92F150A-41DA-4080-99FE-57B390EF3E75}">
+    <dataValidation type="list" sqref="N563" xr:uid="{BA566E92-E7A2-4676-A6F7-E76E3648950C}">
       <formula1>=IF(M563&lt;&gt;"",INDIRECT(VLOOKUP(M563,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M564" xr:uid="{397AB0DB-66F5-4C3E-B9F2-C37F2ECCB621}">
+    <dataValidation type="list" sqref="M564" xr:uid="{934DCAEB-03E4-47C7-8542-8D4819E28A2A}">
       <formula1>=IF(L564&lt;&gt;"",INDIRECT(VLOOKUP(L564,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N564" xr:uid="{D514C012-EB66-4466-9F00-95FBEE364A9D}">
+    <dataValidation type="list" sqref="N564" xr:uid="{977E8448-84D6-4D53-8BCA-72280C21235C}">
       <formula1>=IF(M564&lt;&gt;"",INDIRECT(VLOOKUP(M564,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M565" xr:uid="{4DFDA011-2CB1-4B10-9A32-657610D73626}">
+    <dataValidation type="list" sqref="M565" xr:uid="{A661B5E9-BF3B-4AA7-A89C-A9DA7B0EC5D6}">
       <formula1>=IF(L565&lt;&gt;"",INDIRECT(VLOOKUP(L565,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N565" xr:uid="{F96AE286-AA88-4E06-A776-BFFDCBF14600}">
+    <dataValidation type="list" sqref="N565" xr:uid="{84E71246-CB1B-4DCD-8FEA-4894AA81E92E}">
       <formula1>=IF(M565&lt;&gt;"",INDIRECT(VLOOKUP(M565,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M566" xr:uid="{37BA03E6-69D3-4C79-8504-7E951DAF042E}">
+    <dataValidation type="list" sqref="M566" xr:uid="{33BA8087-2D7F-4B08-AE40-423244BC7E4C}">
       <formula1>=IF(L566&lt;&gt;"",INDIRECT(VLOOKUP(L566,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N566" xr:uid="{51DB98BF-35EB-4BBC-90FC-90EB9669DFF3}">
+    <dataValidation type="list" sqref="N566" xr:uid="{F2758FBB-3EC9-4AA5-9808-AD09482EBB13}">
       <formula1>=IF(M566&lt;&gt;"",INDIRECT(VLOOKUP(M566,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M567" xr:uid="{E02BB33E-EF27-4E65-9E01-68CDA9797771}">
+    <dataValidation type="list" sqref="M567" xr:uid="{AD987D7C-A803-42C2-8D0C-92EB6B107A7A}">
       <formula1>=IF(L567&lt;&gt;"",INDIRECT(VLOOKUP(L567,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N567" xr:uid="{6E927D79-F748-4AAA-B475-BA5B297239B5}">
+    <dataValidation type="list" sqref="N567" xr:uid="{39179446-2598-4D38-9778-3BD84426A656}">
       <formula1>=IF(M567&lt;&gt;"",INDIRECT(VLOOKUP(M567,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M568" xr:uid="{77E2E5A4-6FB5-451E-A4BD-01147E88A29C}">
+    <dataValidation type="list" sqref="M568" xr:uid="{DEB41C32-20FA-4382-8AF3-8347D226D061}">
       <formula1>=IF(L568&lt;&gt;"",INDIRECT(VLOOKUP(L568,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N568" xr:uid="{977ECC74-7498-4172-B634-71A6FC4DB573}">
+    <dataValidation type="list" sqref="N568" xr:uid="{552D64A2-FF59-4544-A650-09A01398489D}">
       <formula1>=IF(M568&lt;&gt;"",INDIRECT(VLOOKUP(M568,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M569" xr:uid="{48B96986-88E6-497C-BA6C-F177DB976538}">
+    <dataValidation type="list" sqref="M569" xr:uid="{C8B087C4-B2D3-422E-ADFD-222195B3F10F}">
       <formula1>=IF(L569&lt;&gt;"",INDIRECT(VLOOKUP(L569,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N569" xr:uid="{5478E10A-0E35-4B25-8E70-A6944D83AE80}">
+    <dataValidation type="list" sqref="N569" xr:uid="{5E9F1F87-A3E4-4F21-9D88-505A41B73A89}">
       <formula1>=IF(M569&lt;&gt;"",INDIRECT(VLOOKUP(M569,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M570" xr:uid="{00686134-0BB5-44BE-A934-725973AAFB6D}">
+    <dataValidation type="list" sqref="M570" xr:uid="{581BCD56-AFBC-4503-AC27-2E22840CD6DD}">
       <formula1>=IF(L570&lt;&gt;"",INDIRECT(VLOOKUP(L570,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N570" xr:uid="{43637C5A-CE6A-40DF-B84A-B4368307A3CA}">
+    <dataValidation type="list" sqref="N570" xr:uid="{BE0E6EC3-CFF6-4D04-88EF-5B028D970371}">
       <formula1>=IF(M570&lt;&gt;"",INDIRECT(VLOOKUP(M570,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M571" xr:uid="{8F3BCD6E-7578-48E8-965F-D86C9DA75307}">
+    <dataValidation type="list" sqref="M571" xr:uid="{81A97D76-2D14-4A35-91D6-0BAFBA09F954}">
       <formula1>=IF(L571&lt;&gt;"",INDIRECT(VLOOKUP(L571,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N571" xr:uid="{95E7CAE9-5D3C-480A-ADFF-1961865B7172}">
+    <dataValidation type="list" sqref="N571" xr:uid="{1B14FE80-4A95-4E5E-B42F-928E0E144F77}">
       <formula1>=IF(M571&lt;&gt;"",INDIRECT(VLOOKUP(M571,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M572" xr:uid="{39C77D00-2BF0-472F-8C1B-B1E835B69F17}">
+    <dataValidation type="list" sqref="M572" xr:uid="{7E97E132-F65A-40E7-8CDD-FB72E2611E1F}">
       <formula1>=IF(L572&lt;&gt;"",INDIRECT(VLOOKUP(L572,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N572" xr:uid="{3B22FB81-375C-4C0E-BD07-CA7845F2E4B0}">
+    <dataValidation type="list" sqref="N572" xr:uid="{F9F678A6-F58A-4C82-A278-0B1CEC91C8A2}">
       <formula1>=IF(M572&lt;&gt;"",INDIRECT(VLOOKUP(M572,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M573" xr:uid="{9A1EB50C-C15C-4F72-BB33-8B2F663A5A5F}">
+    <dataValidation type="list" sqref="M573" xr:uid="{5EEB0A51-717D-481C-8187-7DC63F54A8AE}">
       <formula1>=IF(L573&lt;&gt;"",INDIRECT(VLOOKUP(L573,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N573" xr:uid="{C192F5C1-742B-403B-9A6B-ED0FA9C7BD4B}">
+    <dataValidation type="list" sqref="N573" xr:uid="{D240C035-F050-48AC-94A5-D8C8E5F6B6BC}">
       <formula1>=IF(M573&lt;&gt;"",INDIRECT(VLOOKUP(M573,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M574" xr:uid="{B6FEB31C-B64E-48C3-86FD-3CE074B67FE0}">
+    <dataValidation type="list" sqref="M574" xr:uid="{CDCBD3BC-9B21-45A6-9595-B9B64034EF82}">
       <formula1>=IF(L574&lt;&gt;"",INDIRECT(VLOOKUP(L574,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N574" xr:uid="{AD081D57-6F34-481E-8859-458CA216302A}">
+    <dataValidation type="list" sqref="N574" xr:uid="{F5CDCB64-F2EF-42CB-A6F4-F01D5845A87E}">
       <formula1>=IF(M574&lt;&gt;"",INDIRECT(VLOOKUP(M574,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M575" xr:uid="{87F7AA24-44E0-490C-9D4B-B7E4C8313AA6}">
+    <dataValidation type="list" sqref="M575" xr:uid="{FA0B9B27-E4E1-44B2-BE3E-E080501484CB}">
       <formula1>=IF(L575&lt;&gt;"",INDIRECT(VLOOKUP(L575,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N575" xr:uid="{C4D2C135-13DD-4CFB-AFE3-2BA8F13764D9}">
+    <dataValidation type="list" sqref="N575" xr:uid="{FA18CF8A-9AAB-465B-BB32-2A04D5D8DB08}">
       <formula1>=IF(M575&lt;&gt;"",INDIRECT(VLOOKUP(M575,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M576" xr:uid="{C4A78698-02B3-4764-8A2B-CAB86B0D180F}">
+    <dataValidation type="list" sqref="M576" xr:uid="{675FA04A-02A5-4948-A774-280D497BD9C2}">
       <formula1>=IF(L576&lt;&gt;"",INDIRECT(VLOOKUP(L576,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N576" xr:uid="{D89D180F-E0FA-4532-896F-87449B0453A3}">
+    <dataValidation type="list" sqref="N576" xr:uid="{4024FAC9-34CD-4E06-A53F-11EC55AD615B}">
       <formula1>=IF(M576&lt;&gt;"",INDIRECT(VLOOKUP(M576,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M577" xr:uid="{E41A5ADB-F08A-4BD9-A2EA-0AD1068D2BCD}">
+    <dataValidation type="list" sqref="M577" xr:uid="{5CA17111-C294-4E63-B3F0-4E0A7D0462E6}">
       <formula1>=IF(L577&lt;&gt;"",INDIRECT(VLOOKUP(L577,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N577" xr:uid="{FD42F8D7-A123-4E6B-A1CC-3163DC43D42E}">
+    <dataValidation type="list" sqref="N577" xr:uid="{D2B7B17D-CCEB-4096-BCB8-772BA3FBBEAB}">
       <formula1>=IF(M577&lt;&gt;"",INDIRECT(VLOOKUP(M577,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M578" xr:uid="{804BD5A8-AF38-406B-9DAC-5B75E401C3A6}">
+    <dataValidation type="list" sqref="M578" xr:uid="{732ED1BD-3AEB-4F95-B14B-A409E4B89ADD}">
       <formula1>=IF(L578&lt;&gt;"",INDIRECT(VLOOKUP(L578,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N578" xr:uid="{3178D1D3-3228-4DD2-A787-611AAA81EF8E}">
+    <dataValidation type="list" sqref="N578" xr:uid="{5D3CCFC7-ECA7-4DC3-ACCA-EF9B9F491A4E}">
       <formula1>=IF(M578&lt;&gt;"",INDIRECT(VLOOKUP(M578,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M579" xr:uid="{43809661-1B7C-4604-A9E8-C63EA3C364FE}">
+    <dataValidation type="list" sqref="M579" xr:uid="{0B51369E-DF1D-432F-92E7-F41F6101F60D}">
       <formula1>=IF(L579&lt;&gt;"",INDIRECT(VLOOKUP(L579,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N579" xr:uid="{6F18FE8B-72BD-47A5-AC72-83C4B0F646EB}">
+    <dataValidation type="list" sqref="N579" xr:uid="{6268240E-210E-4611-91A3-995E8234281B}">
       <formula1>=IF(M579&lt;&gt;"",INDIRECT(VLOOKUP(M579,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M580" xr:uid="{19D44677-EBD0-46B5-B395-EF89C6034FA8}">
+    <dataValidation type="list" sqref="M580" xr:uid="{4B085D4B-E88F-4BF9-9601-83B3AD7C021A}">
       <formula1>=IF(L580&lt;&gt;"",INDIRECT(VLOOKUP(L580,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N580" xr:uid="{0D373B75-59C5-4303-ABB4-BE8F38F4B66B}">
+    <dataValidation type="list" sqref="N580" xr:uid="{6C25AB3B-C412-418F-97FF-5D74D3B9A6CA}">
       <formula1>=IF(M580&lt;&gt;"",INDIRECT(VLOOKUP(M580,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M581" xr:uid="{984BD1C5-DE68-460F-835E-8858ACD6AE31}">
+    <dataValidation type="list" sqref="M581" xr:uid="{52490004-774F-4E78-9C2D-5F438855A1D9}">
       <formula1>=IF(L581&lt;&gt;"",INDIRECT(VLOOKUP(L581,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N581" xr:uid="{7214ABF8-9368-4CA7-9B5A-D572A36713D9}">
+    <dataValidation type="list" sqref="N581" xr:uid="{AE5F8F92-2C49-4BE8-8026-8D7662424C28}">
       <formula1>=IF(M581&lt;&gt;"",INDIRECT(VLOOKUP(M581,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M582" xr:uid="{613A86B4-8477-4E92-89A9-488F156F5686}">
+    <dataValidation type="list" sqref="M582" xr:uid="{19411B1A-18AE-4A87-9FAD-C7D5CB730ACE}">
       <formula1>=IF(L582&lt;&gt;"",INDIRECT(VLOOKUP(L582,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N582" xr:uid="{42A2F0D2-7C56-4AB2-8B8C-E97923A6AE38}">
+    <dataValidation type="list" sqref="N582" xr:uid="{F6304E8B-B512-4C2A-8103-E2FAF893795C}">
       <formula1>=IF(M582&lt;&gt;"",INDIRECT(VLOOKUP(M582,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M583" xr:uid="{B465DC9C-BA29-451D-973F-CED027D9B697}">
+    <dataValidation type="list" sqref="M583" xr:uid="{D682856D-4EFB-4E9C-B40C-75B764C5169E}">
       <formula1>=IF(L583&lt;&gt;"",INDIRECT(VLOOKUP(L583,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N583" xr:uid="{60F3C1F8-D3F5-4FC3-8ED0-DDAD2C5DC7D8}">
+    <dataValidation type="list" sqref="N583" xr:uid="{DACBFE54-3ACE-441F-BDDA-C5FDBDC1B749}">
       <formula1>=IF(M583&lt;&gt;"",INDIRECT(VLOOKUP(M583,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M584" xr:uid="{00E86132-59C5-4E02-9631-11936A710B82}">
+    <dataValidation type="list" sqref="M584" xr:uid="{7F0725B9-864C-48C0-9EB6-2EB4D9753EC7}">
       <formula1>=IF(L584&lt;&gt;"",INDIRECT(VLOOKUP(L584,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N584" xr:uid="{CB35A041-D5F5-45A6-A401-24154B3695F4}">
+    <dataValidation type="list" sqref="N584" xr:uid="{5C23ED5C-CBA0-4E46-97AC-EF68DD43199F}">
       <formula1>=IF(M584&lt;&gt;"",INDIRECT(VLOOKUP(M584,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M585" xr:uid="{6F792016-3568-4EAE-8294-E88CE27BA996}">
+    <dataValidation type="list" sqref="M585" xr:uid="{406B9EC9-A42F-4917-A0AA-6279F41C0659}">
       <formula1>=IF(L585&lt;&gt;"",INDIRECT(VLOOKUP(L585,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N585" xr:uid="{51F21A61-A398-4DF5-826D-081FCE421C51}">
+    <dataValidation type="list" sqref="N585" xr:uid="{32A8D3B3-0E93-4CBA-BAA2-BA7CE4CA227E}">
       <formula1>=IF(M585&lt;&gt;"",INDIRECT(VLOOKUP(M585,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M586" xr:uid="{92A96984-4E5A-460A-8EC5-1E940567196A}">
+    <dataValidation type="list" sqref="M586" xr:uid="{9230AA75-F62E-4F74-B34A-089AFCA2D636}">
       <formula1>=IF(L586&lt;&gt;"",INDIRECT(VLOOKUP(L586,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N586" xr:uid="{4E3838AB-FFFF-4C28-9DBC-4BAE0FE796CB}">
+    <dataValidation type="list" sqref="N586" xr:uid="{433D4E56-2CB7-4290-93D3-D81CD89B5810}">
       <formula1>=IF(M586&lt;&gt;"",INDIRECT(VLOOKUP(M586,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M587" xr:uid="{17FE41B8-84E5-4217-9861-6CDF8088A5C8}">
+    <dataValidation type="list" sqref="M587" xr:uid="{748745C4-F723-4A7F-A3B5-FE557E1A749A}">
       <formula1>=IF(L587&lt;&gt;"",INDIRECT(VLOOKUP(L587,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N587" xr:uid="{E9129836-B43F-447F-8262-2832147391BF}">
+    <dataValidation type="list" sqref="N587" xr:uid="{22BF765E-00AD-405E-ABA0-F8864B27D452}">
       <formula1>=IF(M587&lt;&gt;"",INDIRECT(VLOOKUP(M587,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M588" xr:uid="{1DCBA475-71DA-4300-8B45-4BD360DA28A4}">
+    <dataValidation type="list" sqref="M588" xr:uid="{E7969F84-862F-420C-BEBB-13D79369219C}">
       <formula1>=IF(L588&lt;&gt;"",INDIRECT(VLOOKUP(L588,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N588" xr:uid="{51A87698-DCCC-4B99-8DDA-59B69A1EE549}">
+    <dataValidation type="list" sqref="N588" xr:uid="{B3076C95-488F-4FB7-9583-5EFC9757ED4C}">
       <formula1>=IF(M588&lt;&gt;"",INDIRECT(VLOOKUP(M588,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M589" xr:uid="{2503C8E7-3361-41C9-AAA3-889761D15762}">
+    <dataValidation type="list" sqref="M589" xr:uid="{591903BD-03EC-4776-BA8B-AAF550585264}">
       <formula1>=IF(L589&lt;&gt;"",INDIRECT(VLOOKUP(L589,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N589" xr:uid="{7CBE3C44-630E-4C31-BBCC-95168F295675}">
+    <dataValidation type="list" sqref="N589" xr:uid="{5750C7BD-13D3-44A8-8E8A-6D75F4B981CC}">
       <formula1>=IF(M589&lt;&gt;"",INDIRECT(VLOOKUP(M589,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M590" xr:uid="{24738256-8D62-4092-9D01-0C953F9CE79C}">
+    <dataValidation type="list" sqref="M590" xr:uid="{65FFD36B-EC4D-414A-B2C9-45886F7CCCB2}">
       <formula1>=IF(L590&lt;&gt;"",INDIRECT(VLOOKUP(L590,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N590" xr:uid="{2F91B423-E754-4D4D-8B57-2947B2F9AA90}">
+    <dataValidation type="list" sqref="N590" xr:uid="{C67CA2D0-5F5B-4322-B2AC-9FFDDF51896E}">
       <formula1>=IF(M590&lt;&gt;"",INDIRECT(VLOOKUP(M590,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M591" xr:uid="{32B51209-2399-4055-8956-056CAE52CF0C}">
+    <dataValidation type="list" sqref="M591" xr:uid="{ABFCA6B4-5CDF-4BE8-9F63-77CDF44E842B}">
       <formula1>=IF(L591&lt;&gt;"",INDIRECT(VLOOKUP(L591,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N591" xr:uid="{0CF25B76-AEF0-4A96-9A30-28042D0D3CD1}">
+    <dataValidation type="list" sqref="N591" xr:uid="{FF1B8F01-A74C-4405-A76A-2B1CE85AA5DF}">
       <formula1>=IF(M591&lt;&gt;"",INDIRECT(VLOOKUP(M591,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M592" xr:uid="{0C21BF56-B4ED-479C-91D3-2016578BD528}">
+    <dataValidation type="list" sqref="M592" xr:uid="{3943D0B5-87C7-41D2-BF4A-F1F79559EBD5}">
       <formula1>=IF(L592&lt;&gt;"",INDIRECT(VLOOKUP(L592,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N592" xr:uid="{6F3B47A9-BC5A-4F09-A10D-2CC2240F61E6}">
+    <dataValidation type="list" sqref="N592" xr:uid="{414F35DF-0B9A-4535-948C-139386086345}">
       <formula1>=IF(M592&lt;&gt;"",INDIRECT(VLOOKUP(M592,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M593" xr:uid="{3665110A-0A3C-4F3C-B962-53CF7F0E90E2}">
+    <dataValidation type="list" sqref="M593" xr:uid="{F7F406E9-D885-4114-ABFF-24110C3ED717}">
       <formula1>=IF(L593&lt;&gt;"",INDIRECT(VLOOKUP(L593,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N593" xr:uid="{4EF5B5DB-2695-4690-BC2D-A4B054D0D6BB}">
+    <dataValidation type="list" sqref="N593" xr:uid="{CDF176F9-A71F-4AC7-BE1B-0F490B9F72FC}">
       <formula1>=IF(M593&lt;&gt;"",INDIRECT(VLOOKUP(M593,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M594" xr:uid="{3875DC11-2747-42FC-AD9B-34681698CD81}">
+    <dataValidation type="list" sqref="M594" xr:uid="{F386BFE7-7557-4314-B4B4-17ECFC6BFFEA}">
       <formula1>=IF(L594&lt;&gt;"",INDIRECT(VLOOKUP(L594,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N594" xr:uid="{F58B335C-53D1-4A1E-9D92-6E57747235F1}">
+    <dataValidation type="list" sqref="N594" xr:uid="{2F67A866-5F56-414D-A193-548EF7867E12}">
       <formula1>=IF(M594&lt;&gt;"",INDIRECT(VLOOKUP(M594,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M595" xr:uid="{9C7C1CE1-D074-457C-8DF1-77CAEB0B4C83}">
+    <dataValidation type="list" sqref="M595" xr:uid="{CC55687A-02A8-4744-A484-7CDD41C21C30}">
       <formula1>=IF(L595&lt;&gt;"",INDIRECT(VLOOKUP(L595,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N595" xr:uid="{86A4C25B-3EB1-44B1-A3AD-A1C9A167A678}">
+    <dataValidation type="list" sqref="N595" xr:uid="{7B52DDB7-7E77-453F-A7F0-46F8EBA91A64}">
       <formula1>=IF(M595&lt;&gt;"",INDIRECT(VLOOKUP(M595,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M596" xr:uid="{F251942D-47D9-4647-AE9A-478C7170437F}">
+    <dataValidation type="list" sqref="M596" xr:uid="{20B35B3D-A514-41D6-B690-FF989C822DA2}">
       <formula1>=IF(L596&lt;&gt;"",INDIRECT(VLOOKUP(L596,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N596" xr:uid="{BCBB7A17-DC64-473E-94B0-9EA64FED2D3C}">
+    <dataValidation type="list" sqref="N596" xr:uid="{AE71E253-C71B-4554-BAA6-BE31F0BBAD0F}">
       <formula1>=IF(M596&lt;&gt;"",INDIRECT(VLOOKUP(M596,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M597" xr:uid="{9D379DD8-45FC-410A-922D-A674771EEEA7}">
+    <dataValidation type="list" sqref="M597" xr:uid="{09C0AB18-570E-432A-AC0A-6D11371CB135}">
       <formula1>=IF(L597&lt;&gt;"",INDIRECT(VLOOKUP(L597,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N597" xr:uid="{BBBD5B36-DA56-4937-9986-D1EBB0935C36}">
+    <dataValidation type="list" sqref="N597" xr:uid="{F8721128-89F7-419B-B4AB-387D20CE54C9}">
       <formula1>=IF(M597&lt;&gt;"",INDIRECT(VLOOKUP(M597,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M598" xr:uid="{98C6CDFD-4E0E-496E-9C9C-87D94C16D634}">
+    <dataValidation type="list" sqref="M598" xr:uid="{63C435DA-81E2-4230-9140-97E5694C0BC2}">
       <formula1>=IF(L598&lt;&gt;"",INDIRECT(VLOOKUP(L598,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N598" xr:uid="{6A21BFE7-62C5-49A9-B52F-903E2C9D203D}">
+    <dataValidation type="list" sqref="N598" xr:uid="{22813961-C2C1-4C5C-A8E0-FAC77E46A740}">
       <formula1>=IF(M598&lt;&gt;"",INDIRECT(VLOOKUP(M598,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M599" xr:uid="{2BB0677C-5562-4053-B236-E6E327E8257E}">
+    <dataValidation type="list" sqref="M599" xr:uid="{9E423CCF-5473-44B4-BE2A-505F82B4AD94}">
       <formula1>=IF(L599&lt;&gt;"",INDIRECT(VLOOKUP(L599,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N599" xr:uid="{76F4079C-9050-40FC-90EF-A411218E4845}">
+    <dataValidation type="list" sqref="N599" xr:uid="{4F92A42E-BC58-49E5-88C7-148440065AE9}">
       <formula1>=IF(M599&lt;&gt;"",INDIRECT(VLOOKUP(M599,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M600" xr:uid="{3C6C178D-A3C1-4288-BCE5-AAC7696EDB01}">
+    <dataValidation type="list" sqref="M600" xr:uid="{F8548FA0-ECDE-4897-AB4B-C0A1209ACE1D}">
       <formula1>=IF(L600&lt;&gt;"",INDIRECT(VLOOKUP(L600,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N600" xr:uid="{B80DAE1F-76CA-42F6-9966-0D2371C10B8D}">
+    <dataValidation type="list" sqref="N600" xr:uid="{BBDAEAA7-F6A2-48F9-B6EB-F50339411E18}">
       <formula1>=IF(M600&lt;&gt;"",INDIRECT(VLOOKUP(M600,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M601" xr:uid="{8BE88F17-261B-408A-814A-F3AAF61BF12C}">
+    <dataValidation type="list" sqref="M601" xr:uid="{66A146E3-B194-4293-8912-8C16A0E72E83}">
       <formula1>=IF(L601&lt;&gt;"",INDIRECT(VLOOKUP(L601,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N601" xr:uid="{244ECC1D-5D3E-4306-82A0-A4798A7435CB}">
+    <dataValidation type="list" sqref="N601" xr:uid="{AD3B2DB4-9A58-4386-AA4C-83EFEA7509A4}">
       <formula1>=IF(M601&lt;&gt;"",INDIRECT(VLOOKUP(M601,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M602" xr:uid="{09141D2B-6460-48E2-9E10-03EF8631BB91}">
+    <dataValidation type="list" sqref="M602" xr:uid="{4FBFACED-E2D8-45CE-AFB4-5570B13169D1}">
       <formula1>=IF(L602&lt;&gt;"",INDIRECT(VLOOKUP(L602,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N602" xr:uid="{1A105828-CDF8-426A-8937-DAB67D0F459A}">
+    <dataValidation type="list" sqref="N602" xr:uid="{09671598-AB2A-49EF-AB48-C32DF341D94E}">
       <formula1>=IF(M602&lt;&gt;"",INDIRECT(VLOOKUP(M602,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M603" xr:uid="{111088D0-5DBA-4224-B88D-D9D1BC052FEA}">
+    <dataValidation type="list" sqref="M603" xr:uid="{2FDEE999-DCC3-4589-A8BE-E045B7DD4B5D}">
       <formula1>=IF(L603&lt;&gt;"",INDIRECT(VLOOKUP(L603,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N603" xr:uid="{13AC0526-A07D-4302-9D63-601BC094C617}">
+    <dataValidation type="list" sqref="N603" xr:uid="{B5958B13-45CA-4B7E-B02A-9FEA190DF704}">
       <formula1>=IF(M603&lt;&gt;"",INDIRECT(VLOOKUP(M603,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M604" xr:uid="{5C937CB6-09A8-46B1-B1D2-BE6EFE1C16D9}">
+    <dataValidation type="list" sqref="M604" xr:uid="{16C9DE74-04A9-49F6-8B35-451A30C54E09}">
       <formula1>=IF(L604&lt;&gt;"",INDIRECT(VLOOKUP(L604,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N604" xr:uid="{5A748F45-C45C-4DDC-AECF-BD320DA5D653}">
+    <dataValidation type="list" sqref="N604" xr:uid="{BB8ED4A6-5B23-460E-B96E-11E0565CCF97}">
       <formula1>=IF(M604&lt;&gt;"",INDIRECT(VLOOKUP(M604,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M605" xr:uid="{91F631F3-37CD-48D9-BF7D-3F1AAA428F80}">
+    <dataValidation type="list" sqref="M605" xr:uid="{D309BFC6-6276-4FC6-9074-6E940256397C}">
       <formula1>=IF(L605&lt;&gt;"",INDIRECT(VLOOKUP(L605,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N605" xr:uid="{79CBE1B8-7333-4B8F-8B77-CCBD73CEA982}">
+    <dataValidation type="list" sqref="N605" xr:uid="{C671E54D-0D45-45C5-ADC2-16F683AD78A2}">
       <formula1>=IF(M605&lt;&gt;"",INDIRECT(VLOOKUP(M605,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M606" xr:uid="{0810DD82-FDD1-45BD-8B32-DE4B2DA31C39}">
+    <dataValidation type="list" sqref="M606" xr:uid="{F9313CF1-D338-47C5-965D-4E0EF6193BDC}">
       <formula1>=IF(L606&lt;&gt;"",INDIRECT(VLOOKUP(L606,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N606" xr:uid="{8373FDC5-3FB3-40CE-8684-385217B40232}">
+    <dataValidation type="list" sqref="N606" xr:uid="{9A91FBAD-9928-489B-8DC0-2448E936AB8D}">
       <formula1>=IF(M606&lt;&gt;"",INDIRECT(VLOOKUP(M606,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M607" xr:uid="{DF018731-08E5-4C07-951E-4752C5D67B25}">
+    <dataValidation type="list" sqref="M607" xr:uid="{D1B77227-6B38-4DA8-91A5-F168A1A0E283}">
       <formula1>=IF(L607&lt;&gt;"",INDIRECT(VLOOKUP(L607,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N607" xr:uid="{EF299763-45CE-4F2A-95D2-79138781063B}">
+    <dataValidation type="list" sqref="N607" xr:uid="{6B7D0167-B0A0-4796-9280-8EE25C64422C}">
       <formula1>=IF(M607&lt;&gt;"",INDIRECT(VLOOKUP(M607,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M608" xr:uid="{F4B53CD6-E1F3-4075-82CC-90FDF90A5698}">
+    <dataValidation type="list" sqref="M608" xr:uid="{82E1FF6E-BADA-4A3A-A884-099F99B9C86A}">
       <formula1>=IF(L608&lt;&gt;"",INDIRECT(VLOOKUP(L608,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N608" xr:uid="{40DFA799-DD0F-44C2-8F4C-EBFCA8C4C725}">
+    <dataValidation type="list" sqref="N608" xr:uid="{9B65505D-3189-435B-9B03-1E52AB553861}">
       <formula1>=IF(M608&lt;&gt;"",INDIRECT(VLOOKUP(M608,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M609" xr:uid="{DA4A739A-872D-493F-90CD-CCA92C16955D}">
+    <dataValidation type="list" sqref="M609" xr:uid="{3EA92F6D-278F-4B26-8CBC-BA1B7B09CF2E}">
       <formula1>=IF(L609&lt;&gt;"",INDIRECT(VLOOKUP(L609,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N609" xr:uid="{C0249814-B13E-453F-9E2C-3D4B98BBEC1E}">
+    <dataValidation type="list" sqref="N609" xr:uid="{21443009-F3E8-4014-9BC2-148A71780775}">
       <formula1>=IF(M609&lt;&gt;"",INDIRECT(VLOOKUP(M609,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M610" xr:uid="{EABBD555-97AD-4135-B077-EF76A80E6326}">
+    <dataValidation type="list" sqref="M610" xr:uid="{7F18E33D-5E56-456F-B171-790EB12D8822}">
       <formula1>=IF(L610&lt;&gt;"",INDIRECT(VLOOKUP(L610,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N610" xr:uid="{E59EB0B9-950A-45BA-B707-91B73527D9A6}">
+    <dataValidation type="list" sqref="N610" xr:uid="{3DD4541A-9D33-45A5-9028-D15405F377DC}">
       <formula1>=IF(M610&lt;&gt;"",INDIRECT(VLOOKUP(M610,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M611" xr:uid="{7AFC697E-FAAC-4E49-AA34-7C0706F40DF0}">
+    <dataValidation type="list" sqref="M611" xr:uid="{FD1BCCE7-F529-4319-8FBE-8BBD7F0B05D6}">
       <formula1>=IF(L611&lt;&gt;"",INDIRECT(VLOOKUP(L611,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N611" xr:uid="{84E5D174-0BF4-4CB8-A932-C0C645333AAF}">
+    <dataValidation type="list" sqref="N611" xr:uid="{BDB2F9B5-84A4-4796-8153-6B86840BBCD3}">
       <formula1>=IF(M611&lt;&gt;"",INDIRECT(VLOOKUP(M611,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M612" xr:uid="{35939363-3B4C-4BF3-83B0-0DDF667611DF}">
+    <dataValidation type="list" sqref="M612" xr:uid="{567B4F04-D60A-40CF-B86C-7D1EE89C938B}">
       <formula1>=IF(L612&lt;&gt;"",INDIRECT(VLOOKUP(L612,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N612" xr:uid="{1B9939BA-FBDD-40F3-AF62-31B92AA1F6E0}">
+    <dataValidation type="list" sqref="N612" xr:uid="{77EF8CC6-F924-43C4-AD42-BA1EE644756F}">
       <formula1>=IF(M612&lt;&gt;"",INDIRECT(VLOOKUP(M612,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M613" xr:uid="{60281000-CBF6-459D-8941-B17E264141A6}">
+    <dataValidation type="list" sqref="M613" xr:uid="{CF1029C8-247E-4054-A0B0-E9EFF54584FD}">
       <formula1>=IF(L613&lt;&gt;"",INDIRECT(VLOOKUP(L613,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N613" xr:uid="{C28226BC-673F-4C01-B062-2046F97A85C3}">
+    <dataValidation type="list" sqref="N613" xr:uid="{C41EBB95-BC42-4604-A038-54E7DC441753}">
       <formula1>=IF(M613&lt;&gt;"",INDIRECT(VLOOKUP(M613,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M614" xr:uid="{EF95EFF0-EDB4-4F13-8752-A051B3268958}">
+    <dataValidation type="list" sqref="M614" xr:uid="{8BD9ABA7-B79E-45FA-A8B2-7E6AF1FD74D5}">
       <formula1>=IF(L614&lt;&gt;"",INDIRECT(VLOOKUP(L614,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N614" xr:uid="{4D9F6A80-4056-4428-8421-BBC570AFAB5C}">
+    <dataValidation type="list" sqref="N614" xr:uid="{4D2D57CC-C1F8-4205-8BC5-F0A547DEC1F5}">
       <formula1>=IF(M614&lt;&gt;"",INDIRECT(VLOOKUP(M614,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M615" xr:uid="{2F8020FB-A916-48E0-A4CE-CFAF3C02458B}">
+    <dataValidation type="list" sqref="M615" xr:uid="{EF69EA37-38F6-45BF-BDFE-08AD387D831A}">
       <formula1>=IF(L615&lt;&gt;"",INDIRECT(VLOOKUP(L615,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N615" xr:uid="{DE4FE49B-D580-4196-969C-AEC54E6AE107}">
+    <dataValidation type="list" sqref="N615" xr:uid="{CB0ADC87-CFB3-4106-A1B1-A253FD89A4E8}">
       <formula1>=IF(M615&lt;&gt;"",INDIRECT(VLOOKUP(M615,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M616" xr:uid="{9FBAA41E-9583-4866-A97A-C16BF603DFFC}">
+    <dataValidation type="list" sqref="M616" xr:uid="{7D264EB8-FE6C-4416-8CA6-FAC534C428F1}">
       <formula1>=IF(L616&lt;&gt;"",INDIRECT(VLOOKUP(L616,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N616" xr:uid="{E5BFAF35-105E-4529-BD11-9CDCF14AB030}">
+    <dataValidation type="list" sqref="N616" xr:uid="{98E00E32-8580-4481-B097-7B659EC71A98}">
       <formula1>=IF(M616&lt;&gt;"",INDIRECT(VLOOKUP(M616,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M617" xr:uid="{03BFB7C0-861F-413E-BFBB-C934BBD96502}">
+    <dataValidation type="list" sqref="M617" xr:uid="{0A1E3A82-2306-4FDE-A5B7-DF9E9B88589F}">
       <formula1>=IF(L617&lt;&gt;"",INDIRECT(VLOOKUP(L617,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N617" xr:uid="{89616D9F-4220-439D-AFBB-988F1A5B4FEB}">
+    <dataValidation type="list" sqref="N617" xr:uid="{8CC16F8A-E265-4C14-9B1C-057E67CA0930}">
       <formula1>=IF(M617&lt;&gt;"",INDIRECT(VLOOKUP(M617,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M618" xr:uid="{C0D2AF3B-8BC1-406C-8848-5322F0CEF860}">
+    <dataValidation type="list" sqref="M618" xr:uid="{AE99314F-C5A7-4A9B-A74B-D9CD2ABC601D}">
       <formula1>=IF(L618&lt;&gt;"",INDIRECT(VLOOKUP(L618,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N618" xr:uid="{1D1CC17E-50F5-4AB8-BA23-D1AB4F4041BE}">
+    <dataValidation type="list" sqref="N618" xr:uid="{55C204EC-23A4-421C-9417-CE4F7681E87D}">
       <formula1>=IF(M618&lt;&gt;"",INDIRECT(VLOOKUP(M618,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M619" xr:uid="{B6CF86BE-6BE7-495C-9184-808DEA48A51B}">
+    <dataValidation type="list" sqref="M619" xr:uid="{488A799E-28DA-4C16-A2BD-96BAE19AA5EE}">
       <formula1>=IF(L619&lt;&gt;"",INDIRECT(VLOOKUP(L619,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N619" xr:uid="{BDF1B0A0-A7B9-429C-9099-D432EB6868F9}">
+    <dataValidation type="list" sqref="N619" xr:uid="{1EB66169-AD73-46F9-9A4D-78BD861D62DE}">
       <formula1>=IF(M619&lt;&gt;"",INDIRECT(VLOOKUP(M619,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M620" xr:uid="{9827C77F-742C-4DE9-8C5D-6E3145900562}">
+    <dataValidation type="list" sqref="M620" xr:uid="{BE1AB9FB-9719-4321-863E-3CEDF7D7E1EF}">
       <formula1>=IF(L620&lt;&gt;"",INDIRECT(VLOOKUP(L620,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N620" xr:uid="{D4D329CA-40F1-4ABB-A3A9-892DD1D63930}">
+    <dataValidation type="list" sqref="N620" xr:uid="{41F6F546-E4B2-4C42-B9B1-06A884D1CD1B}">
       <formula1>=IF(M620&lt;&gt;"",INDIRECT(VLOOKUP(M620,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M621" xr:uid="{436E5C5D-0866-4760-9522-F508E34E5C0A}">
+    <dataValidation type="list" sqref="M621" xr:uid="{6EA513E1-2541-4CD4-A751-60349106DFAC}">
       <formula1>=IF(L621&lt;&gt;"",INDIRECT(VLOOKUP(L621,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N621" xr:uid="{83B52B88-D532-46CE-9822-CA63E0DB4061}">
+    <dataValidation type="list" sqref="N621" xr:uid="{9BB7ECA0-9CAB-496A-8197-4A674FF33157}">
       <formula1>=IF(M621&lt;&gt;"",INDIRECT(VLOOKUP(M621,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M622" xr:uid="{AD3633E1-96C6-4CCC-AC6E-0828E34C1A9E}">
+    <dataValidation type="list" sqref="M622" xr:uid="{2EFC1ECE-700F-4166-8671-AC5F2824DA24}">
       <formula1>=IF(L622&lt;&gt;"",INDIRECT(VLOOKUP(L622,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N622" xr:uid="{2C4C5722-2807-46AF-8E56-3641F75AEE23}">
+    <dataValidation type="list" sqref="N622" xr:uid="{4E61E5FA-4E49-46D8-86B3-B695F699999F}">
       <formula1>=IF(M622&lt;&gt;"",INDIRECT(VLOOKUP(M622,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M623" xr:uid="{11B2DAB1-6992-43EA-ACD7-18F72645511A}">
+    <dataValidation type="list" sqref="M623" xr:uid="{E5B7AF4F-7165-47CA-B1EF-1903596B3D00}">
       <formula1>=IF(L623&lt;&gt;"",INDIRECT(VLOOKUP(L623,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N623" xr:uid="{DB284E6F-F2CC-448C-9EA7-301A8E432789}">
+    <dataValidation type="list" sqref="N623" xr:uid="{8DC54054-7173-48F9-815E-744DBC5DCF8D}">
       <formula1>=IF(M623&lt;&gt;"",INDIRECT(VLOOKUP(M623,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M624" xr:uid="{28730660-801B-452C-9F3C-FC9278AB4991}">
+    <dataValidation type="list" sqref="M624" xr:uid="{B7D34C50-81B6-4E7C-989B-CAA1E36309D0}">
       <formula1>=IF(L624&lt;&gt;"",INDIRECT(VLOOKUP(L624,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N624" xr:uid="{0D61DBA3-EB23-4805-9FA0-F64353770875}">
+    <dataValidation type="list" sqref="N624" xr:uid="{33C72754-6B43-4315-98E0-38F37E3EE0D8}">
       <formula1>=IF(M624&lt;&gt;"",INDIRECT(VLOOKUP(M624,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M625" xr:uid="{28488598-8515-4E59-8DCE-C8A775909AC7}">
+    <dataValidation type="list" sqref="M625" xr:uid="{AE60715D-AD5A-496B-A5CE-45B2B8921525}">
       <formula1>=IF(L625&lt;&gt;"",INDIRECT(VLOOKUP(L625,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N625" xr:uid="{4A77073D-6A10-4FFF-B3A7-76162E522183}">
+    <dataValidation type="list" sqref="N625" xr:uid="{1BEF2ECF-E0A7-4682-B84A-41B177C942E8}">
       <formula1>=IF(M625&lt;&gt;"",INDIRECT(VLOOKUP(M625,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M626" xr:uid="{BBF1AC2B-1759-4342-9ECA-D5B19077A022}">
+    <dataValidation type="list" sqref="M626" xr:uid="{AAD60EA5-1084-4319-B1C1-81E03992FA23}">
       <formula1>=IF(L626&lt;&gt;"",INDIRECT(VLOOKUP(L626,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N626" xr:uid="{9DBAE685-52B5-43C1-A6E8-AAC46CF20775}">
+    <dataValidation type="list" sqref="N626" xr:uid="{D5FEB1AA-7825-499A-8219-C6265BFAA9C9}">
       <formula1>=IF(M626&lt;&gt;"",INDIRECT(VLOOKUP(M626,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M627" xr:uid="{3137445E-2ECF-481A-B095-A6AEA22C8E28}">
+    <dataValidation type="list" sqref="M627" xr:uid="{7BDA2C61-2940-450A-94A7-D945712D8500}">
       <formula1>=IF(L627&lt;&gt;"",INDIRECT(VLOOKUP(L627,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N627" xr:uid="{7CBCB4EC-FCEC-43BB-B4A2-20B75F057D5C}">
+    <dataValidation type="list" sqref="N627" xr:uid="{FBA20A99-FA25-4A5B-9DDA-8405DC665C50}">
       <formula1>=IF(M627&lt;&gt;"",INDIRECT(VLOOKUP(M627,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M628" xr:uid="{D8A275F7-2DBD-4F33-B9C1-10620E5CC17E}">
+    <dataValidation type="list" sqref="M628" xr:uid="{F22277DA-736E-4067-9858-65275E936A6A}">
       <formula1>=IF(L628&lt;&gt;"",INDIRECT(VLOOKUP(L628,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N628" xr:uid="{D0F736E5-0C93-44FB-8A45-EA08ABF744F7}">
+    <dataValidation type="list" sqref="N628" xr:uid="{26169BD9-257B-47C4-86D2-77E547757A04}">
       <formula1>=IF(M628&lt;&gt;"",INDIRECT(VLOOKUP(M628,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M629" xr:uid="{6ED9E8A8-16D9-4B9A-8C8F-89B966137BB9}">
+    <dataValidation type="list" sqref="M629" xr:uid="{EAD1706E-A2C3-47FF-9A4A-6C71FFA29593}">
       <formula1>=IF(L629&lt;&gt;"",INDIRECT(VLOOKUP(L629,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N629" xr:uid="{B2F2070C-50D1-4BFA-BF16-F830751F716C}">
+    <dataValidation type="list" sqref="N629" xr:uid="{7A1DFB27-4A1C-4CE0-B73B-205D8DF057B1}">
       <formula1>=IF(M629&lt;&gt;"",INDIRECT(VLOOKUP(M629,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M630" xr:uid="{4FB1CE97-1FD0-4A45-83AA-35670C5CACB4}">
+    <dataValidation type="list" sqref="M630" xr:uid="{308DBA8B-4795-48E3-A94E-CC8249CA5899}">
       <formula1>=IF(L630&lt;&gt;"",INDIRECT(VLOOKUP(L630,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N630" xr:uid="{68369628-16DE-4ECA-B554-5C8D27EE4A79}">
+    <dataValidation type="list" sqref="N630" xr:uid="{3DBC6E33-B2D5-47F5-A6F9-171431F782A5}">
       <formula1>=IF(M630&lt;&gt;"",INDIRECT(VLOOKUP(M630,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M631" xr:uid="{BF30BC89-74CB-4399-80BD-2F59AC8BDDE5}">
+    <dataValidation type="list" sqref="M631" xr:uid="{2C5BB9D1-29BD-41DC-B5BE-6D3A0257044B}">
       <formula1>=IF(L631&lt;&gt;"",INDIRECT(VLOOKUP(L631,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N631" xr:uid="{0BAF3A9B-3BDD-4A7A-AA45-457D848B01D4}">
+    <dataValidation type="list" sqref="N631" xr:uid="{674C75A7-792F-4AEE-AC0B-05808934DA70}">
       <formula1>=IF(M631&lt;&gt;"",INDIRECT(VLOOKUP(M631,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M632" xr:uid="{F097658F-921C-4106-A4AF-3DE1043E41DE}">
+    <dataValidation type="list" sqref="M632" xr:uid="{4A177EAF-D8E8-4DC3-9A77-BE0C1A2EA140}">
       <formula1>=IF(L632&lt;&gt;"",INDIRECT(VLOOKUP(L632,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N632" xr:uid="{BCEC97FA-6939-4C32-92A5-8E1C224ED4C1}">
+    <dataValidation type="list" sqref="N632" xr:uid="{3A07B3AB-0121-42FB-BF8A-56559CD345B8}">
       <formula1>=IF(M632&lt;&gt;"",INDIRECT(VLOOKUP(M632,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M633" xr:uid="{E4E794B2-D6E3-4A8F-9579-6D1A365064BB}">
+    <dataValidation type="list" sqref="M633" xr:uid="{8C19BC04-E57E-4320-8D78-8EDF136B7C4A}">
       <formula1>=IF(L633&lt;&gt;"",INDIRECT(VLOOKUP(L633,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N633" xr:uid="{06708CCD-2D26-49F8-BDEC-0F2382AAD2EA}">
+    <dataValidation type="list" sqref="N633" xr:uid="{72B2C387-C56C-4BDF-A3DB-03E0077EBF86}">
       <formula1>=IF(M633&lt;&gt;"",INDIRECT(VLOOKUP(M633,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M634" xr:uid="{280326EB-6A67-4FF3-A08D-031DC80D2A43}">
+    <dataValidation type="list" sqref="M634" xr:uid="{86B08B43-B899-472E-A2B9-8E17E44E8F22}">
       <formula1>=IF(L634&lt;&gt;"",INDIRECT(VLOOKUP(L634,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N634" xr:uid="{B5161F71-1A62-47D1-A633-D1F8D3F805E1}">
+    <dataValidation type="list" sqref="N634" xr:uid="{E9057B79-101C-4EC5-AA97-16BE67B321F6}">
       <formula1>=IF(M634&lt;&gt;"",INDIRECT(VLOOKUP(M634,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M635" xr:uid="{0F3A691F-7E5E-4075-8EE8-BC3C8336ED09}">
+    <dataValidation type="list" sqref="M635" xr:uid="{56BC9DF6-BFC1-4B96-8E22-4FC893606591}">
       <formula1>=IF(L635&lt;&gt;"",INDIRECT(VLOOKUP(L635,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N635" xr:uid="{49E9470A-D468-41EF-BEF9-92F8D6A19007}">
+    <dataValidation type="list" sqref="N635" xr:uid="{10DAF338-0ED8-4064-B3AB-0ED65552FCE2}">
       <formula1>=IF(M635&lt;&gt;"",INDIRECT(VLOOKUP(M635,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M636" xr:uid="{1E848D80-2D76-4A25-908E-FEECFFA0A187}">
+    <dataValidation type="list" sqref="M636" xr:uid="{9B59501C-E978-4B65-A36C-9ADDD37161D5}">
       <formula1>=IF(L636&lt;&gt;"",INDIRECT(VLOOKUP(L636,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N636" xr:uid="{CE12BE53-6AF2-4811-9113-2843568D16CE}">
+    <dataValidation type="list" sqref="N636" xr:uid="{9C0279B1-7EE2-40BA-8852-EE179A83DD3C}">
       <formula1>=IF(M636&lt;&gt;"",INDIRECT(VLOOKUP(M636,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M637" xr:uid="{51C4415C-8CBE-4DD7-80DF-D8785EF27F21}">
+    <dataValidation type="list" sqref="M637" xr:uid="{BBC434F6-56A5-4E87-9690-0D0BE4C877FD}">
       <formula1>=IF(L637&lt;&gt;"",INDIRECT(VLOOKUP(L637,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N637" xr:uid="{ADB78E26-4357-4C44-8A74-E676FAF151E8}">
+    <dataValidation type="list" sqref="N637" xr:uid="{1DE735AC-DCE1-4AC8-A348-4044164D16AD}">
       <formula1>=IF(M637&lt;&gt;"",INDIRECT(VLOOKUP(M637,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M638" xr:uid="{B5EF9F05-B5FF-4A5E-8120-04CAE06708D3}">
+    <dataValidation type="list" sqref="M638" xr:uid="{4941F736-1D14-45B0-9F36-7DCEB78B3FA0}">
       <formula1>=IF(L638&lt;&gt;"",INDIRECT(VLOOKUP(L638,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N638" xr:uid="{CB45CC0B-C824-41B7-B886-8D72973EA3B4}">
+    <dataValidation type="list" sqref="N638" xr:uid="{0C0CC643-A2ED-4939-9392-C765ED6FCFE5}">
       <formula1>=IF(M638&lt;&gt;"",INDIRECT(VLOOKUP(M638,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M639" xr:uid="{A32C890E-8698-4567-904D-77EEC3309641}">
+    <dataValidation type="list" sqref="M639" xr:uid="{86D809F6-1C0C-4D55-9CEC-2ADAE3A24433}">
       <formula1>=IF(L639&lt;&gt;"",INDIRECT(VLOOKUP(L639,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N639" xr:uid="{FE81CC8B-FC80-4A1C-AA3A-5BFD1AEFE8FF}">
+    <dataValidation type="list" sqref="N639" xr:uid="{085FE754-6F0F-4376-9B25-B7B3A49D3B55}">
       <formula1>=IF(M639&lt;&gt;"",INDIRECT(VLOOKUP(M639,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M640" xr:uid="{F606DFC0-51C0-4143-B9D3-F44080B1B904}">
+    <dataValidation type="list" sqref="M640" xr:uid="{BA69DD2A-5057-449A-A1D3-B74D09101025}">
       <formula1>=IF(L640&lt;&gt;"",INDIRECT(VLOOKUP(L640,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N640" xr:uid="{AB2D33AE-1240-49C9-8BCC-04F5C42A0825}">
+    <dataValidation type="list" sqref="N640" xr:uid="{6A385DC2-5C1C-4E76-A7BE-5ABDFCEC6CDB}">
       <formula1>=IF(M640&lt;&gt;"",INDIRECT(VLOOKUP(M640,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M641" xr:uid="{507C5C10-82ED-4CA8-8F69-4285B07D0373}">
+    <dataValidation type="list" sqref="M641" xr:uid="{764E7303-7941-4AB0-AC4F-F8C7F53FBE00}">
       <formula1>=IF(L641&lt;&gt;"",INDIRECT(VLOOKUP(L641,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N641" xr:uid="{A6985A79-97F0-4C4C-B4EE-13717B863C2F}">
+    <dataValidation type="list" sqref="N641" xr:uid="{DE83BDDC-99E9-48B0-9DB0-F600DFE48475}">
       <formula1>=IF(M641&lt;&gt;"",INDIRECT(VLOOKUP(M641,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M642" xr:uid="{6CB82507-1BC0-441C-8EC4-B720CF03344F}">
+    <dataValidation type="list" sqref="M642" xr:uid="{7FBC7FEB-6D5C-48B4-A807-1C321D8E9334}">
       <formula1>=IF(L642&lt;&gt;"",INDIRECT(VLOOKUP(L642,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N642" xr:uid="{7EFC40F7-AC6C-4E02-B2BE-DA147F151F1F}">
+    <dataValidation type="list" sqref="N642" xr:uid="{050E435D-B672-4AC2-9128-A4F33C904531}">
       <formula1>=IF(M642&lt;&gt;"",INDIRECT(VLOOKUP(M642,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M643" xr:uid="{D4D25BA5-CF57-43FF-B9ED-C2CAF8A779CF}">
+    <dataValidation type="list" sqref="M643" xr:uid="{0A88FA51-184C-4F96-9291-DD783742C38D}">
       <formula1>=IF(L643&lt;&gt;"",INDIRECT(VLOOKUP(L643,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N643" xr:uid="{7072EA5F-C3DE-4EE8-B889-D5BDCA1121B4}">
+    <dataValidation type="list" sqref="N643" xr:uid="{4C965AE5-F829-4A09-8124-F80A7A6FC592}">
       <formula1>=IF(M643&lt;&gt;"",INDIRECT(VLOOKUP(M643,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M644" xr:uid="{88A569FE-72BD-4104-90E9-63C0124E9845}">
+    <dataValidation type="list" sqref="M644" xr:uid="{33FB6E49-4FDD-4308-9794-2EDA5732B85E}">
       <formula1>=IF(L644&lt;&gt;"",INDIRECT(VLOOKUP(L644,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N644" xr:uid="{50881186-B118-4ABC-B328-55FC9495EF13}">
+    <dataValidation type="list" sqref="N644" xr:uid="{8252B756-B735-424E-857A-D2BE331CA6DA}">
       <formula1>=IF(M644&lt;&gt;"",INDIRECT(VLOOKUP(M644,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M645" xr:uid="{5C502938-4B06-4709-B06F-7B34264C8172}">
+    <dataValidation type="list" sqref="M645" xr:uid="{2B7E4F27-D35E-426E-B1D8-52952047BA11}">
       <formula1>=IF(L645&lt;&gt;"",INDIRECT(VLOOKUP(L645,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N645" xr:uid="{38B583BD-9235-4763-8B0E-C12C23571167}">
+    <dataValidation type="list" sqref="N645" xr:uid="{D4C75B87-4783-46C2-AAE1-003DAF3F1DDA}">
       <formula1>=IF(M645&lt;&gt;"",INDIRECT(VLOOKUP(M645,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M646" xr:uid="{792AA10C-48C4-488F-87FA-79EE8D2FA2D9}">
+    <dataValidation type="list" sqref="M646" xr:uid="{33899668-F9DA-4BCC-8387-6EF167C32BD1}">
       <formula1>=IF(L646&lt;&gt;"",INDIRECT(VLOOKUP(L646,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N646" xr:uid="{C426527F-4423-4BF6-A4E1-A7737624A072}">
+    <dataValidation type="list" sqref="N646" xr:uid="{F7E6A8F4-84AF-4896-ABDB-FC6B00D62DB8}">
       <formula1>=IF(M646&lt;&gt;"",INDIRECT(VLOOKUP(M646,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M647" xr:uid="{55AEAD13-BACD-4175-A383-0566DD372371}">
+    <dataValidation type="list" sqref="M647" xr:uid="{EE13B60B-8156-428C-9446-6ED1CA3360F9}">
       <formula1>=IF(L647&lt;&gt;"",INDIRECT(VLOOKUP(L647,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N647" xr:uid="{25203AC6-E080-497A-A848-2DBA6BA903B7}">
+    <dataValidation type="list" sqref="N647" xr:uid="{9990F7AC-AA93-4950-9056-645FC5BE31C8}">
       <formula1>=IF(M647&lt;&gt;"",INDIRECT(VLOOKUP(M647,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M648" xr:uid="{BD61C4A2-31FE-4786-A668-69F3A81ED2BF}">
+    <dataValidation type="list" sqref="M648" xr:uid="{C0996FF1-506A-4C60-A498-FEB9786239BD}">
       <formula1>=IF(L648&lt;&gt;"",INDIRECT(VLOOKUP(L648,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N648" xr:uid="{B0C93575-320D-48E5-BD51-9DDDB2295287}">
+    <dataValidation type="list" sqref="N648" xr:uid="{45F20F10-5AF8-4C89-84BC-3EB97D494F76}">
       <formula1>=IF(M648&lt;&gt;"",INDIRECT(VLOOKUP(M648,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M649" xr:uid="{6B387F1A-A973-47DC-82E1-063C05DB93F0}">
+    <dataValidation type="list" sqref="M649" xr:uid="{8246C24A-CBE7-4E28-84F3-1E67C298BC90}">
       <formula1>=IF(L649&lt;&gt;"",INDIRECT(VLOOKUP(L649,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N649" xr:uid="{F89D888C-6765-4AA6-B635-320FA6C6269F}">
+    <dataValidation type="list" sqref="N649" xr:uid="{2167B962-E1F2-4A77-B91D-EC23736D7A84}">
       <formula1>=IF(M649&lt;&gt;"",INDIRECT(VLOOKUP(M649,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M650" xr:uid="{C9619484-99FC-4C54-AC98-CF6BF26D1DFB}">
+    <dataValidation type="list" sqref="M650" xr:uid="{588BDF64-5FF7-4151-9418-E234D6F6FDBB}">
       <formula1>=IF(L650&lt;&gt;"",INDIRECT(VLOOKUP(L650,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N650" xr:uid="{B71C02D2-F7C7-4E68-B4F7-D76DD7DD454D}">
+    <dataValidation type="list" sqref="N650" xr:uid="{4A4A76CD-3DE7-4177-853F-44E70BE4B6E0}">
       <formula1>=IF(M650&lt;&gt;"",INDIRECT(VLOOKUP(M650,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M651" xr:uid="{C641BF1D-CF48-4181-9499-58AA77F8E791}">
+    <dataValidation type="list" sqref="M651" xr:uid="{CDFD9458-E53A-43CD-974E-3626E219BB90}">
       <formula1>=IF(L651&lt;&gt;"",INDIRECT(VLOOKUP(L651,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N651" xr:uid="{D38B3E32-7BDB-403B-B261-4146EF5907F4}">
+    <dataValidation type="list" sqref="N651" xr:uid="{EBA9C7A5-9183-4FF4-BA2D-A95AD0152ED2}">
       <formula1>=IF(M651&lt;&gt;"",INDIRECT(VLOOKUP(M651,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M652" xr:uid="{93891E45-9509-4C62-B3FE-021A725426F6}">
+    <dataValidation type="list" sqref="M652" xr:uid="{13BE3AB5-7A7D-4945-9952-BB6B710B40BA}">
       <formula1>=IF(L652&lt;&gt;"",INDIRECT(VLOOKUP(L652,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N652" xr:uid="{1B4788C3-3D2D-4992-9D7F-CD85F0E6C14A}">
+    <dataValidation type="list" sqref="N652" xr:uid="{6A524441-56B7-4CF0-ABA5-D415A4307ED8}">
       <formula1>=IF(M652&lt;&gt;"",INDIRECT(VLOOKUP(M652,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M653" xr:uid="{B70712CA-0354-4BBB-A83F-3BC9DC16B7D3}">
+    <dataValidation type="list" sqref="M653" xr:uid="{DFD0AECB-4782-443B-B970-A8C6E319CA40}">
       <formula1>=IF(L653&lt;&gt;"",INDIRECT(VLOOKUP(L653,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N653" xr:uid="{3D53BD70-7613-4BCB-8B9D-677C4CE041D9}">
+    <dataValidation type="list" sqref="N653" xr:uid="{96EE087A-315B-4DDF-8E06-9FEA2D2C8D80}">
       <formula1>=IF(M653&lt;&gt;"",INDIRECT(VLOOKUP(M653,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M654" xr:uid="{B2B91492-D6F4-4918-BA1C-9315EE8781A4}">
+    <dataValidation type="list" sqref="M654" xr:uid="{E7FAFC6A-5D7C-4C2C-A32F-4E027180EC55}">
       <formula1>=IF(L654&lt;&gt;"",INDIRECT(VLOOKUP(L654,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N654" xr:uid="{F7BBF6E5-A316-42C5-8DBC-B73382B91416}">
+    <dataValidation type="list" sqref="N654" xr:uid="{8D7F29AF-6F1F-4A9F-A7B7-5CF2345D1449}">
       <formula1>=IF(M654&lt;&gt;"",INDIRECT(VLOOKUP(M654,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M655" xr:uid="{1FA6CF41-3218-4323-A713-0A7C7B0B8A77}">
+    <dataValidation type="list" sqref="M655" xr:uid="{C8677095-D7E6-463D-BE9C-642DDD30B82F}">
       <formula1>=IF(L655&lt;&gt;"",INDIRECT(VLOOKUP(L655,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N655" xr:uid="{461F2ADB-6F17-436D-A5FE-517FB1325A50}">
+    <dataValidation type="list" sqref="N655" xr:uid="{4261F8E5-F50D-48DE-A404-21FB365671DD}">
       <formula1>=IF(M655&lt;&gt;"",INDIRECT(VLOOKUP(M655,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M656" xr:uid="{D05FAEF3-5D63-4AD3-BA0E-FDE56401CC5D}">
+    <dataValidation type="list" sqref="M656" xr:uid="{BB8B2DD5-0DB0-4A57-876B-03C325F1397D}">
       <formula1>=IF(L656&lt;&gt;"",INDIRECT(VLOOKUP(L656,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N656" xr:uid="{09F433E7-7DC6-42BF-B92B-01E4BF826329}">
+    <dataValidation type="list" sqref="N656" xr:uid="{DE616404-D825-44F6-9366-1A2D04DC6B7C}">
       <formula1>=IF(M656&lt;&gt;"",INDIRECT(VLOOKUP(M656,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M657" xr:uid="{916CB22B-C107-4A9F-99FD-EDA40988032A}">
+    <dataValidation type="list" sqref="M657" xr:uid="{02C7C2B3-6BF1-40DA-89B4-694F3D00FCD9}">
       <formula1>=IF(L657&lt;&gt;"",INDIRECT(VLOOKUP(L657,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N657" xr:uid="{44C0E9DF-8F40-443A-BA66-FE8970596E81}">
+    <dataValidation type="list" sqref="N657" xr:uid="{C11E4476-C6D3-4FEC-B7F4-F261F0B28D31}">
       <formula1>=IF(M657&lt;&gt;"",INDIRECT(VLOOKUP(M657,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M658" xr:uid="{8F286CFC-6DD9-4931-8C7A-02616386C2A8}">
+    <dataValidation type="list" sqref="M658" xr:uid="{682B8D5C-9710-4681-B2B9-1C68291554AB}">
       <formula1>=IF(L658&lt;&gt;"",INDIRECT(VLOOKUP(L658,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N658" xr:uid="{DC86F665-0EF0-4A74-94A3-2D1149FE7E72}">
+    <dataValidation type="list" sqref="N658" xr:uid="{FF1120DF-59F4-4B09-890C-3E920853CB93}">
       <formula1>=IF(M658&lt;&gt;"",INDIRECT(VLOOKUP(M658,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M659" xr:uid="{48432B80-8A0B-48A7-A679-3C3355A78260}">
+    <dataValidation type="list" sqref="M659" xr:uid="{1B97D5DF-B070-41DF-A656-58475D56714A}">
       <formula1>=IF(L659&lt;&gt;"",INDIRECT(VLOOKUP(L659,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N659" xr:uid="{79A8F5CC-8A58-41F6-8A40-0E80D0AFF9C3}">
+    <dataValidation type="list" sqref="N659" xr:uid="{CF206F24-06CE-4F53-BC77-A0CA506FC38A}">
       <formula1>=IF(M659&lt;&gt;"",INDIRECT(VLOOKUP(M659,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M660" xr:uid="{9BB0DF1E-5263-4B4E-878A-D32C0F58114B}">
+    <dataValidation type="list" sqref="M660" xr:uid="{8FCE0497-C2C9-487F-B69B-F34DD4835BCC}">
       <formula1>=IF(L660&lt;&gt;"",INDIRECT(VLOOKUP(L660,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N660" xr:uid="{2B928BC2-E1E0-4509-A95F-A0CF7E1987C6}">
+    <dataValidation type="list" sqref="N660" xr:uid="{D384E096-449D-4C73-A743-D492F074BE9B}">
       <formula1>=IF(M660&lt;&gt;"",INDIRECT(VLOOKUP(M660,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M661" xr:uid="{38A9E63E-9E1E-4736-A998-3D99B552F667}">
+    <dataValidation type="list" sqref="M661" xr:uid="{6E695A50-A280-4FD2-8CDF-AE3756F8D1DC}">
       <formula1>=IF(L661&lt;&gt;"",INDIRECT(VLOOKUP(L661,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N661" xr:uid="{9546FCD0-C7FB-44E1-8FA1-CAB6C066B390}">
+    <dataValidation type="list" sqref="N661" xr:uid="{8B938019-D664-4E98-BF0E-F2DDFFD01C18}">
       <formula1>=IF(M661&lt;&gt;"",INDIRECT(VLOOKUP(M661,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M662" xr:uid="{7F1B540A-4EB7-4311-9B33-9AA012F389AA}">
+    <dataValidation type="list" sqref="M662" xr:uid="{C5744C4B-CF57-4884-9DCC-C80AE74C37FD}">
       <formula1>=IF(L662&lt;&gt;"",INDIRECT(VLOOKUP(L662,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N662" xr:uid="{FD8B90C7-0A6F-4F8B-8127-E6E454FAD1A0}">
+    <dataValidation type="list" sqref="N662" xr:uid="{674D7C7C-5742-45D4-90F8-0CC3899C34F5}">
       <formula1>=IF(M662&lt;&gt;"",INDIRECT(VLOOKUP(M662,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M663" xr:uid="{5AD0B8A2-BD0C-4284-A0A7-6565F9D0A713}">
+    <dataValidation type="list" sqref="M663" xr:uid="{DC93706A-2F55-44BE-82A8-A64BB7057DDB}">
       <formula1>=IF(L663&lt;&gt;"",INDIRECT(VLOOKUP(L663,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N663" xr:uid="{739DE153-AC69-4B0F-B209-98E0E6C9BD80}">
+    <dataValidation type="list" sqref="N663" xr:uid="{A4CD59CD-0425-4D24-A4A7-7A2D5EA28A3C}">
       <formula1>=IF(M663&lt;&gt;"",INDIRECT(VLOOKUP(M663,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M664" xr:uid="{A2FA9B11-E1F2-4D0B-B997-EE7D76F0791A}">
+    <dataValidation type="list" sqref="M664" xr:uid="{01C7D575-C376-48C0-A6C0-3CFE9769A76C}">
       <formula1>=IF(L664&lt;&gt;"",INDIRECT(VLOOKUP(L664,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N664" xr:uid="{C0E07E55-DC17-4E7E-87F5-379AB2111F6F}">
+    <dataValidation type="list" sqref="N664" xr:uid="{D0199ED3-BBF7-4912-92DC-7BEF56BD01D0}">
       <formula1>=IF(M664&lt;&gt;"",INDIRECT(VLOOKUP(M664,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M665" xr:uid="{4B590A78-D79B-4A97-B173-2D07E8473627}">
+    <dataValidation type="list" sqref="M665" xr:uid="{8B63E71D-477D-4045-9E11-E960E259172D}">
       <formula1>=IF(L665&lt;&gt;"",INDIRECT(VLOOKUP(L665,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N665" xr:uid="{33622FC7-D321-4A0B-9191-B9245DE449B0}">
+    <dataValidation type="list" sqref="N665" xr:uid="{95431B86-EA3E-4446-98C1-90AE2C29E65C}">
       <formula1>=IF(M665&lt;&gt;"",INDIRECT(VLOOKUP(M665,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M666" xr:uid="{A33F913B-DC24-4902-BD38-B639DA757171}">
+    <dataValidation type="list" sqref="M666" xr:uid="{8226B850-F1CE-4F59-9A93-B0F9C857D035}">
       <formula1>=IF(L666&lt;&gt;"",INDIRECT(VLOOKUP(L666,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N666" xr:uid="{28BC729D-CA7B-4B73-9D45-A0793AFA3484}">
+    <dataValidation type="list" sqref="N666" xr:uid="{F7E2FB9E-2908-4ADA-AE75-F930804EC42F}">
       <formula1>=IF(M666&lt;&gt;"",INDIRECT(VLOOKUP(M666,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M667" xr:uid="{D315467F-E0DF-4D6F-A365-907692782618}">
+    <dataValidation type="list" sqref="M667" xr:uid="{7993CBAD-6D9A-4B2E-8DEC-9503C39232FA}">
       <formula1>=IF(L667&lt;&gt;"",INDIRECT(VLOOKUP(L667,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N667" xr:uid="{F4F56A04-303B-4C23-B452-12E9E964D0FA}">
+    <dataValidation type="list" sqref="N667" xr:uid="{505F7309-C1BA-486E-AE43-95B025FD60BA}">
       <formula1>=IF(M667&lt;&gt;"",INDIRECT(VLOOKUP(M667,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M668" xr:uid="{8E16DC0E-B907-4041-8E22-54FA79AF4DB7}">
+    <dataValidation type="list" sqref="M668" xr:uid="{EE8F966F-E861-43D7-95DA-AA65506C605F}">
       <formula1>=IF(L668&lt;&gt;"",INDIRECT(VLOOKUP(L668,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N668" xr:uid="{8C97015A-CEF3-4DEC-9C4C-6FEE29237FBD}">
+    <dataValidation type="list" sqref="N668" xr:uid="{4DE4E7D8-4AC1-4652-BF50-81059687D9CD}">
       <formula1>=IF(M668&lt;&gt;"",INDIRECT(VLOOKUP(M668,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M669" xr:uid="{CE2A8B94-7283-4242-A7FF-CC61B3DB1AC0}">
+    <dataValidation type="list" sqref="M669" xr:uid="{44C7D4B8-08C4-406A-9C2E-3B7E45CB5239}">
       <formula1>=IF(L669&lt;&gt;"",INDIRECT(VLOOKUP(L669,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N669" xr:uid="{C861FEDF-0957-4057-8076-F2659B04E42A}">
+    <dataValidation type="list" sqref="N669" xr:uid="{556D9A65-B9C4-41E2-9C88-4123B09AE501}">
       <formula1>=IF(M669&lt;&gt;"",INDIRECT(VLOOKUP(M669,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M670" xr:uid="{869E214D-0A73-4460-A133-8AF948D6BEA8}">
+    <dataValidation type="list" sqref="M670" xr:uid="{49197600-4B2A-47A3-8FE2-480AD026A0A8}">
       <formula1>=IF(L670&lt;&gt;"",INDIRECT(VLOOKUP(L670,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N670" xr:uid="{325E8A78-2CD8-42BF-A980-566D6B2F0B0B}">
+    <dataValidation type="list" sqref="N670" xr:uid="{AD795EF9-DA86-4F43-A2C3-0D59A63B3CA2}">
       <formula1>=IF(M670&lt;&gt;"",INDIRECT(VLOOKUP(M670,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M671" xr:uid="{1AF14F74-5561-4065-8131-EB39D288EE0F}">
+    <dataValidation type="list" sqref="M671" xr:uid="{16411C2A-C306-4EA7-B2C0-60F5727897E6}">
       <formula1>=IF(L671&lt;&gt;"",INDIRECT(VLOOKUP(L671,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N671" xr:uid="{D0EC7FAE-33A5-4931-9DDE-1F4E6DAE150D}">
+    <dataValidation type="list" sqref="N671" xr:uid="{C2A9F005-CF4D-45A3-85C3-BB60A39C659F}">
       <formula1>=IF(M671&lt;&gt;"",INDIRECT(VLOOKUP(M671,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M672" xr:uid="{452C3783-0A04-400D-AFCD-1E8B29BAFFC8}">
+    <dataValidation type="list" sqref="M672" xr:uid="{8061ECEF-B6CA-4972-B5DE-D349927A0DA9}">
       <formula1>=IF(L672&lt;&gt;"",INDIRECT(VLOOKUP(L672,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N672" xr:uid="{88AD0977-64AB-482E-A446-AC9EAB5896E0}">
+    <dataValidation type="list" sqref="N672" xr:uid="{11569CE3-2654-42FB-8DFD-8A5C2084DECC}">
       <formula1>=IF(M672&lt;&gt;"",INDIRECT(VLOOKUP(M672,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M673" xr:uid="{A0D511DB-D132-444C-81D3-9ECABBA8D07C}">
+    <dataValidation type="list" sqref="M673" xr:uid="{207A5960-204C-4BCE-B912-056A4A610051}">
       <formula1>=IF(L673&lt;&gt;"",INDIRECT(VLOOKUP(L673,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N673" xr:uid="{5995FA26-F099-464C-8058-F97A987B481B}">
+    <dataValidation type="list" sqref="N673" xr:uid="{5433DE15-E7E4-4F34-93B8-F16309D3CE37}">
       <formula1>=IF(M673&lt;&gt;"",INDIRECT(VLOOKUP(M673,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M674" xr:uid="{0422B75C-7365-42CD-BC3E-0BAFD98F7286}">
+    <dataValidation type="list" sqref="M674" xr:uid="{EA81DE8A-EB13-4812-A30F-0B95F7EE64E8}">
       <formula1>=IF(L674&lt;&gt;"",INDIRECT(VLOOKUP(L674,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N674" xr:uid="{A09CA631-4603-45E4-87F8-3BB6B8D28250}">
+    <dataValidation type="list" sqref="N674" xr:uid="{2EFAC7E5-8899-445C-BF8A-DC73468ADF98}">
       <formula1>=IF(M674&lt;&gt;"",INDIRECT(VLOOKUP(M674,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M675" xr:uid="{7385A005-D88D-4DC2-AE65-702F1CF478C2}">
+    <dataValidation type="list" sqref="M675" xr:uid="{61D19B96-5F3C-41C7-ABE6-095A2CBFF5FE}">
       <formula1>=IF(L675&lt;&gt;"",INDIRECT(VLOOKUP(L675,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N675" xr:uid="{5C2A586D-054D-4B22-8950-1FEB5562C908}">
+    <dataValidation type="list" sqref="N675" xr:uid="{5B775C97-D5F4-43BB-916A-EAFAE04F568F}">
       <formula1>=IF(M675&lt;&gt;"",INDIRECT(VLOOKUP(M675,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M676" xr:uid="{9CB2DE97-A22F-41B1-8DC7-E778214CAC69}">
+    <dataValidation type="list" sqref="M676" xr:uid="{0BD451D5-4822-4FAD-94DE-DA9E1965BB46}">
       <formula1>=IF(L676&lt;&gt;"",INDIRECT(VLOOKUP(L676,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N676" xr:uid="{515AFFF7-2254-495E-84AE-C859799F8B46}">
+    <dataValidation type="list" sqref="N676" xr:uid="{778B21AE-B894-4106-BE9E-0F121894E6FB}">
       <formula1>=IF(M676&lt;&gt;"",INDIRECT(VLOOKUP(M676,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M677" xr:uid="{90BDD20F-96A5-4715-9717-A5839C75B027}">
+    <dataValidation type="list" sqref="M677" xr:uid="{61E9DB4E-773D-45F3-AF4B-7EDB1A88C831}">
       <formula1>=IF(L677&lt;&gt;"",INDIRECT(VLOOKUP(L677,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N677" xr:uid="{99AD1C5B-92F0-4E8D-8FFC-30FA32BCF49A}">
+    <dataValidation type="list" sqref="N677" xr:uid="{1A95919B-A7CA-4509-A6B7-D63AAB9EB319}">
       <formula1>=IF(M677&lt;&gt;"",INDIRECT(VLOOKUP(M677,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M678" xr:uid="{4804357C-5815-43C6-B520-7B7945E0AE29}">
+    <dataValidation type="list" sqref="M678" xr:uid="{69E09FE5-0A92-4433-90B7-C2808268C0B1}">
       <formula1>=IF(L678&lt;&gt;"",INDIRECT(VLOOKUP(L678,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N678" xr:uid="{B4E36698-6442-4141-BDD1-C5AA55B683B8}">
+    <dataValidation type="list" sqref="N678" xr:uid="{08CED220-AFEB-4186-A905-2256EBCE2A1E}">
       <formula1>=IF(M678&lt;&gt;"",INDIRECT(VLOOKUP(M678,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M679" xr:uid="{D708DA1B-4369-4F5C-8DFF-9A8390812879}">
+    <dataValidation type="list" sqref="M679" xr:uid="{0005E01F-AF1E-431A-AEC5-79FC1908BCB7}">
       <formula1>=IF(L679&lt;&gt;"",INDIRECT(VLOOKUP(L679,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N679" xr:uid="{5BA10067-2AF1-431C-AA42-A67E8D39EC0B}">
+    <dataValidation type="list" sqref="N679" xr:uid="{91FBD291-16C7-45EE-BF82-B85AB5411E0B}">
       <formula1>=IF(M679&lt;&gt;"",INDIRECT(VLOOKUP(M679,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M680" xr:uid="{EC2EF894-8FC7-41F2-A378-74091EA85FA0}">
+    <dataValidation type="list" sqref="M680" xr:uid="{410DF301-23AB-4F72-805E-57372F2F1933}">
       <formula1>=IF(L680&lt;&gt;"",INDIRECT(VLOOKUP(L680,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N680" xr:uid="{086FFF38-036E-4883-AA2E-9F119CD4B1CD}">
+    <dataValidation type="list" sqref="N680" xr:uid="{38B013A7-6BD2-4673-8CDA-E73A2365371F}">
       <formula1>=IF(M680&lt;&gt;"",INDIRECT(VLOOKUP(M680,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M681" xr:uid="{1C77C320-ED40-497F-BA09-B14929E8950B}">
+    <dataValidation type="list" sqref="M681" xr:uid="{6A3BAA90-60EE-4050-B013-8DF676FF61B1}">
       <formula1>=IF(L681&lt;&gt;"",INDIRECT(VLOOKUP(L681,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N681" xr:uid="{FFCAE385-F9D6-4843-9392-82D8D3CA14BD}">
+    <dataValidation type="list" sqref="N681" xr:uid="{F9A3E67C-3503-4040-9BAE-EEAC6BDF76AC}">
       <formula1>=IF(M681&lt;&gt;"",INDIRECT(VLOOKUP(M681,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M682" xr:uid="{4E59A0C8-712E-4E09-9634-2C9638E17510}">
+    <dataValidation type="list" sqref="M682" xr:uid="{D71DAEE8-047A-43FB-A5AF-48FAC9A00C3E}">
       <formula1>=IF(L682&lt;&gt;"",INDIRECT(VLOOKUP(L682,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N682" xr:uid="{7187D280-7F18-45BD-98FA-439900543700}">
+    <dataValidation type="list" sqref="N682" xr:uid="{7ABC24C6-7A31-4ED1-BE07-06FEE3ED04E9}">
       <formula1>=IF(M682&lt;&gt;"",INDIRECT(VLOOKUP(M682,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M683" xr:uid="{E16751A8-87A0-47CD-9A81-202476CF5D40}">
+    <dataValidation type="list" sqref="M683" xr:uid="{BB1AF3C7-56BB-4895-AB2E-C9E1B43DE857}">
       <formula1>=IF(L683&lt;&gt;"",INDIRECT(VLOOKUP(L683,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N683" xr:uid="{A3DB285A-F180-439C-B58F-75DBBDEBAE4B}">
+    <dataValidation type="list" sqref="N683" xr:uid="{3D6A4F8A-82C6-46B4-BC1E-B111317B801E}">
       <formula1>=IF(M683&lt;&gt;"",INDIRECT(VLOOKUP(M683,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M684" xr:uid="{50EBA5DC-707B-4F3C-AD01-7A1607775F86}">
+    <dataValidation type="list" sqref="M684" xr:uid="{29EA5064-DC1D-4DAE-8FA1-57C6DC4B170A}">
       <formula1>=IF(L684&lt;&gt;"",INDIRECT(VLOOKUP(L684,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N684" xr:uid="{0E89EBA6-B072-4B2F-BB77-6DC1CE3B02A6}">
+    <dataValidation type="list" sqref="N684" xr:uid="{A22C2377-8659-4D2D-9F76-83D72F4AD40B}">
       <formula1>=IF(M684&lt;&gt;"",INDIRECT(VLOOKUP(M684,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M685" xr:uid="{181F96E5-EEE9-4634-836D-BCBB601694F4}">
+    <dataValidation type="list" sqref="M685" xr:uid="{C41EEAAF-9DE1-44EE-89B2-E636F980A7CD}">
       <formula1>=IF(L685&lt;&gt;"",INDIRECT(VLOOKUP(L685,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N685" xr:uid="{5AE3E19A-1D9E-4BC0-B907-0467682F68AF}">
+    <dataValidation type="list" sqref="N685" xr:uid="{99E3F181-AF9F-4D70-B712-7A86B13AEF91}">
       <formula1>=IF(M685&lt;&gt;"",INDIRECT(VLOOKUP(M685,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M686" xr:uid="{D3B74743-8890-4085-A706-788A5E0D3290}">
+    <dataValidation type="list" sqref="M686" xr:uid="{D2BDA36B-BBEB-4EAF-8107-EA461D376BA4}">
       <formula1>=IF(L686&lt;&gt;"",INDIRECT(VLOOKUP(L686,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N686" xr:uid="{79DB4056-101B-436D-BA6E-BF5EF1D818EA}">
+    <dataValidation type="list" sqref="N686" xr:uid="{F6426836-E24A-4517-8681-B659A2DC71B8}">
       <formula1>=IF(M686&lt;&gt;"",INDIRECT(VLOOKUP(M686,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M687" xr:uid="{407C0426-92B6-4F1C-941F-B2D26957B3F6}">
+    <dataValidation type="list" sqref="M687" xr:uid="{B6922EF9-6DE6-46C6-96A7-EAF3E8A76077}">
       <formula1>=IF(L687&lt;&gt;"",INDIRECT(VLOOKUP(L687,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N687" xr:uid="{C1B38942-EA77-4C5F-A11D-28DAFA3696E7}">
+    <dataValidation type="list" sqref="N687" xr:uid="{62CA19AA-6917-4EA3-A288-A1075A8C955F}">
       <formula1>=IF(M687&lt;&gt;"",INDIRECT(VLOOKUP(M687,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M688" xr:uid="{86E65587-7404-4E3C-889C-0B1621A25B2A}">
+    <dataValidation type="list" sqref="M688" xr:uid="{4CC22737-A303-4289-BA12-48FEB23587F8}">
       <formula1>=IF(L688&lt;&gt;"",INDIRECT(VLOOKUP(L688,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N688" xr:uid="{77D020CB-2029-4A83-B879-237692783366}">
+    <dataValidation type="list" sqref="N688" xr:uid="{D55A39A4-7468-4FE3-9797-85E9C22ED23E}">
       <formula1>=IF(M688&lt;&gt;"",INDIRECT(VLOOKUP(M688,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M689" xr:uid="{6F35B6E0-7001-4BE7-85AA-7A05AF814104}">
+    <dataValidation type="list" sqref="M689" xr:uid="{F7148104-6400-401C-8091-90318DEFD34F}">
       <formula1>=IF(L689&lt;&gt;"",INDIRECT(VLOOKUP(L689,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N689" xr:uid="{E696ED5A-BCE2-426E-900F-0CB831B1589A}">
+    <dataValidation type="list" sqref="N689" xr:uid="{3910B39F-499E-41A0-85EB-C19BE041CC14}">
       <formula1>=IF(M689&lt;&gt;"",INDIRECT(VLOOKUP(M689,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M690" xr:uid="{2E88C4BE-E8DE-4D32-B3F7-0BBDAA451BEF}">
+    <dataValidation type="list" sqref="M690" xr:uid="{8EAFBEE5-72A8-494B-AC0C-5AA8D92D661A}">
       <formula1>=IF(L690&lt;&gt;"",INDIRECT(VLOOKUP(L690,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N690" xr:uid="{2888B889-D057-4065-BE4A-8D917404C605}">
+    <dataValidation type="list" sqref="N690" xr:uid="{873796EB-7494-4F17-82C7-9919711AE539}">
       <formula1>=IF(M690&lt;&gt;"",INDIRECT(VLOOKUP(M690,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M691" xr:uid="{97F87C7C-8DA6-4742-B673-4153929CB9A3}">
+    <dataValidation type="list" sqref="M691" xr:uid="{A44B7BFB-44D9-4B22-B490-D9DC5786CF1D}">
       <formula1>=IF(L691&lt;&gt;"",INDIRECT(VLOOKUP(L691,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N691" xr:uid="{F851B418-C468-454F-A5F0-27C40B3D57C0}">
+    <dataValidation type="list" sqref="N691" xr:uid="{AB267D45-6D1B-4D48-896A-2DC45FD15E84}">
       <formula1>=IF(M691&lt;&gt;"",INDIRECT(VLOOKUP(M691,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M692" xr:uid="{ED65A5A7-9D38-4E23-A92A-6C1A593CE663}">
+    <dataValidation type="list" sqref="M692" xr:uid="{D5A09E75-73A6-4AEE-8029-0675BCF37311}">
       <formula1>=IF(L692&lt;&gt;"",INDIRECT(VLOOKUP(L692,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N692" xr:uid="{E1F50543-E8DF-478A-93F6-F03B0E2A4FCB}">
+    <dataValidation type="list" sqref="N692" xr:uid="{9633816F-9AD1-496D-ABFA-CE8EE1DCEFFA}">
       <formula1>=IF(M692&lt;&gt;"",INDIRECT(VLOOKUP(M692,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M693" xr:uid="{0DEE5179-9D72-4E75-A075-FC3543DB4013}">
+    <dataValidation type="list" sqref="M693" xr:uid="{09F88E28-5AF7-4C7D-8C9C-0C74F8154066}">
       <formula1>=IF(L693&lt;&gt;"",INDIRECT(VLOOKUP(L693,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N693" xr:uid="{7B73E2D8-FA00-4FB2-A00A-D9ED08209511}">
+    <dataValidation type="list" sqref="N693" xr:uid="{24174C41-A708-4CAF-BBE2-959FF9B39984}">
       <formula1>=IF(M693&lt;&gt;"",INDIRECT(VLOOKUP(M693,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M694" xr:uid="{4C1FFE48-97C3-4992-9551-18A88E84DB2D}">
+    <dataValidation type="list" sqref="M694" xr:uid="{7C13D300-3EA0-49FC-9BA1-7ECAFDB5D21B}">
       <formula1>=IF(L694&lt;&gt;"",INDIRECT(VLOOKUP(L694,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N694" xr:uid="{5472DB8E-5C3C-459A-9909-627EB5FA2CCA}">
+    <dataValidation type="list" sqref="N694" xr:uid="{421251AA-45A0-415E-A1EB-FAD2C9303A49}">
       <formula1>=IF(M694&lt;&gt;"",INDIRECT(VLOOKUP(M694,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M695" xr:uid="{F1C05808-EEB4-41C9-8991-2DC9AD4E1A3F}">
+    <dataValidation type="list" sqref="M695" xr:uid="{D4F4922A-3C5A-413A-B14E-AEF2FCA3159C}">
       <formula1>=IF(L695&lt;&gt;"",INDIRECT(VLOOKUP(L695,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N695" xr:uid="{D03BDAF9-1A56-4C6A-A0D6-DF6DDA45D9D3}">
+    <dataValidation type="list" sqref="N695" xr:uid="{971C03EF-43CE-47AC-A698-44178FECF95E}">
       <formula1>=IF(M695&lt;&gt;"",INDIRECT(VLOOKUP(M695,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M696" xr:uid="{3A041CBE-DAD6-4C49-A38D-CDF68DC81419}">
+    <dataValidation type="list" sqref="M696" xr:uid="{B06684BC-EB3E-4913-8E7F-C6B43F50E606}">
       <formula1>=IF(L696&lt;&gt;"",INDIRECT(VLOOKUP(L696,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N696" xr:uid="{18E9B1F4-0309-4711-9261-21FC1B2B636E}">
+    <dataValidation type="list" sqref="N696" xr:uid="{A3814799-FB58-4D5E-97BF-FB87FC354DF8}">
       <formula1>=IF(M696&lt;&gt;"",INDIRECT(VLOOKUP(M696,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M697" xr:uid="{03B25AE5-FC14-49D0-8AB5-B20BD3FEB222}">
+    <dataValidation type="list" sqref="M697" xr:uid="{9FE48DA4-A05D-4C43-A224-F73206C3E8E3}">
       <formula1>=IF(L697&lt;&gt;"",INDIRECT(VLOOKUP(L697,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N697" xr:uid="{D3207C3C-8537-42C6-A819-4ACD38A3A8E9}">
+    <dataValidation type="list" sqref="N697" xr:uid="{5B959F47-5A6B-4C2D-ACD9-A93DEBEC80CD}">
       <formula1>=IF(M697&lt;&gt;"",INDIRECT(VLOOKUP(M697,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M698" xr:uid="{9046A564-B2E8-4883-B5E7-3B431ADF329A}">
+    <dataValidation type="list" sqref="M698" xr:uid="{7BF31285-8C16-4CA4-9E58-23F8D9B6E24E}">
       <formula1>=IF(L698&lt;&gt;"",INDIRECT(VLOOKUP(L698,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N698" xr:uid="{D7CFB504-2129-4F0C-8308-0D42E1DD25A5}">
+    <dataValidation type="list" sqref="N698" xr:uid="{8B81EAA6-4E1F-4F13-984B-78997FE7E1FC}">
       <formula1>=IF(M698&lt;&gt;"",INDIRECT(VLOOKUP(M698,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M699" xr:uid="{A894DD68-0A7A-4EAC-B419-392AB528DE27}">
+    <dataValidation type="list" sqref="M699" xr:uid="{11EF0AF0-7D3D-47B8-808E-7DB56B5E88C4}">
       <formula1>=IF(L699&lt;&gt;"",INDIRECT(VLOOKUP(L699,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N699" xr:uid="{764D42FE-77E1-46FB-89B9-17910AECDFF1}">
+    <dataValidation type="list" sqref="N699" xr:uid="{FFCFF144-2A50-460D-9369-78E80344271F}">
       <formula1>=IF(M699&lt;&gt;"",INDIRECT(VLOOKUP(M699,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M700" xr:uid="{8F9A2939-9EC6-429A-BFE8-194BA5306E1E}">
+    <dataValidation type="list" sqref="M700" xr:uid="{8D207C77-08FB-41A3-A1D6-27F333F1DCE4}">
       <formula1>=IF(L700&lt;&gt;"",INDIRECT(VLOOKUP(L700,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N700" xr:uid="{CCE6BB6B-4426-45B1-A4A1-338A2D35CA6D}">
+    <dataValidation type="list" sqref="N700" xr:uid="{527AADDF-72BE-4544-83CF-1ED30DD4F089}">
       <formula1>=IF(M700&lt;&gt;"",INDIRECT(VLOOKUP(M700,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M701" xr:uid="{71CA9699-3197-4A5C-85FC-ECB1F2517A0C}">
+    <dataValidation type="list" sqref="M701" xr:uid="{25111886-53B5-40EF-8093-8F7BABB23D4A}">
       <formula1>=IF(L701&lt;&gt;"",INDIRECT(VLOOKUP(L701,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N701" xr:uid="{6F2EDBAE-152A-495B-83A6-9A120165D566}">
+    <dataValidation type="list" sqref="N701" xr:uid="{10D8644E-9AC5-4BC6-A019-C2AC457EAAB8}">
       <formula1>=IF(M701&lt;&gt;"",INDIRECT(VLOOKUP(M701,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M702" xr:uid="{CB4FEE5C-335E-437C-A2E5-3188CB218B71}">
+    <dataValidation type="list" sqref="M702" xr:uid="{CBCADC4E-14B0-4C71-B91F-7BD285E3D1D6}">
       <formula1>=IF(L702&lt;&gt;"",INDIRECT(VLOOKUP(L702,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N702" xr:uid="{52CE001A-0538-4B6E-ADE7-554349C3C279}">
+    <dataValidation type="list" sqref="N702" xr:uid="{1E634F64-1B02-48BC-8F98-C32B31F80871}">
       <formula1>=IF(M702&lt;&gt;"",INDIRECT(VLOOKUP(M702,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M703" xr:uid="{EF91311F-314F-4815-B4BE-B5395AE02FF4}">
+    <dataValidation type="list" sqref="M703" xr:uid="{DD071D5E-AC73-4E62-A3A3-E68B226D6A6E}">
       <formula1>=IF(L703&lt;&gt;"",INDIRECT(VLOOKUP(L703,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N703" xr:uid="{9933DE2B-15AD-4D1A-A6F7-3EC575A71517}">
+    <dataValidation type="list" sqref="N703" xr:uid="{78C06E6E-F008-488C-9259-AD3F13BACD61}">
       <formula1>=IF(M703&lt;&gt;"",INDIRECT(VLOOKUP(M703,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M704" xr:uid="{88DC2A1A-F16C-4C8F-8E3B-017EDCA4E5DC}">
+    <dataValidation type="list" sqref="M704" xr:uid="{3FC3C9EE-DA8A-4C19-9F68-FC248DD05FF2}">
       <formula1>=IF(L704&lt;&gt;"",INDIRECT(VLOOKUP(L704,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N704" xr:uid="{99492283-ED18-4174-8288-413A777197B8}">
+    <dataValidation type="list" sqref="N704" xr:uid="{43234CF1-C1D9-440E-9943-F7F382BCD037}">
       <formula1>=IF(M704&lt;&gt;"",INDIRECT(VLOOKUP(M704,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M705" xr:uid="{797BF2AC-2948-4F27-AD23-2B32313D0D5F}">
+    <dataValidation type="list" sqref="M705" xr:uid="{382730C6-9E7F-4059-9DD3-ADEEAD16D492}">
       <formula1>=IF(L705&lt;&gt;"",INDIRECT(VLOOKUP(L705,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N705" xr:uid="{B1B29CAF-CAA3-4B27-A442-788A1E1E877A}">
+    <dataValidation type="list" sqref="N705" xr:uid="{A257B7CF-A1E6-4B2D-BE30-FFF62550A1F7}">
       <formula1>=IF(M705&lt;&gt;"",INDIRECT(VLOOKUP(M705,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M706" xr:uid="{A0338241-E826-469D-B98C-BD52A19A1CAD}">
+    <dataValidation type="list" sqref="M706" xr:uid="{019B6382-672D-4A98-9898-B5AC838CDD11}">
       <formula1>=IF(L706&lt;&gt;"",INDIRECT(VLOOKUP(L706,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N706" xr:uid="{220DB706-FC39-4C15-8351-66C766E37944}">
+    <dataValidation type="list" sqref="N706" xr:uid="{72CE97C5-CED4-4BFE-8DE4-4F87F613FEC8}">
       <formula1>=IF(M706&lt;&gt;"",INDIRECT(VLOOKUP(M706,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M707" xr:uid="{AE3D27FB-43CF-4CBC-8E66-86A7918317B8}">
+    <dataValidation type="list" sqref="M707" xr:uid="{555A383C-F82B-4B2B-93F2-A1DCFCA57238}">
       <formula1>=IF(L707&lt;&gt;"",INDIRECT(VLOOKUP(L707,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N707" xr:uid="{632A5420-501A-48A6-9952-B60DB3357ADF}">
+    <dataValidation type="list" sqref="N707" xr:uid="{D92C5598-8966-4153-A237-3851283F4599}">
       <formula1>=IF(M707&lt;&gt;"",INDIRECT(VLOOKUP(M707,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M708" xr:uid="{F0DECE5B-81C2-43BA-A92B-33D8F76B3130}">
+    <dataValidation type="list" sqref="M708" xr:uid="{A8E32614-F681-4259-B575-680108D0ACEF}">
       <formula1>=IF(L708&lt;&gt;"",INDIRECT(VLOOKUP(L708,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N708" xr:uid="{C242ABF2-6BD5-4A25-9F27-071EF6396FD4}">
+    <dataValidation type="list" sqref="N708" xr:uid="{AFEA9AF3-2B71-495E-B50B-712F1C2D1438}">
       <formula1>=IF(M708&lt;&gt;"",INDIRECT(VLOOKUP(M708,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M709" xr:uid="{9513BD65-426F-4DF1-B4CB-BB26898E3349}">
+    <dataValidation type="list" sqref="M709" xr:uid="{4AFC47E5-A5B1-4DCD-8059-8243054CF8D7}">
       <formula1>=IF(L709&lt;&gt;"",INDIRECT(VLOOKUP(L709,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N709" xr:uid="{5CEE775E-AF9B-4ABB-A7FA-FF4A6D6D6562}">
+    <dataValidation type="list" sqref="N709" xr:uid="{9075E319-7B5F-4A10-8A1C-B9CCE0AF726E}">
       <formula1>=IF(M709&lt;&gt;"",INDIRECT(VLOOKUP(M709,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M710" xr:uid="{64E9E088-1681-4E51-BFC4-A6CDA22ADA96}">
+    <dataValidation type="list" sqref="M710" xr:uid="{5B3D7B83-F75A-4515-8856-5CDB27445718}">
       <formula1>=IF(L710&lt;&gt;"",INDIRECT(VLOOKUP(L710,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N710" xr:uid="{3D1268C0-236D-4BAF-8329-724D1A4DE0C0}">
+    <dataValidation type="list" sqref="N710" xr:uid="{35EC1A7C-C0B2-4217-B258-62EAE3E87551}">
       <formula1>=IF(M710&lt;&gt;"",INDIRECT(VLOOKUP(M710,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M711" xr:uid="{1E3606E5-584D-4FBB-86AF-EF64D370BF32}">
+    <dataValidation type="list" sqref="M711" xr:uid="{BD35C05F-B997-48F2-9113-800E946E2620}">
       <formula1>=IF(L711&lt;&gt;"",INDIRECT(VLOOKUP(L711,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N711" xr:uid="{1AA65B41-B062-4562-BE3F-EA682AEC5AFF}">
+    <dataValidation type="list" sqref="N711" xr:uid="{16336073-04F3-46F7-AEC2-2F0FDEE8748F}">
       <formula1>=IF(M711&lt;&gt;"",INDIRECT(VLOOKUP(M711,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M712" xr:uid="{0F206923-A24A-4646-8BEF-F7D7E41E8E18}">
+    <dataValidation type="list" sqref="M712" xr:uid="{B78F8C4F-5F04-4FD5-ADFE-CDF859D5B516}">
       <formula1>=IF(L712&lt;&gt;"",INDIRECT(VLOOKUP(L712,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N712" xr:uid="{C4D4B7A4-2D7D-4F34-9324-FB6067CAC6F0}">
+    <dataValidation type="list" sqref="N712" xr:uid="{455FC6DC-1D0F-4B5D-A4F8-D3F2ADC0B999}">
       <formula1>=IF(M712&lt;&gt;"",INDIRECT(VLOOKUP(M712,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M713" xr:uid="{70BE3239-B330-4BED-99A3-85D6AD9F9BEC}">
+    <dataValidation type="list" sqref="M713" xr:uid="{8BF36E50-1BE0-4187-8C0E-796B2C60CAE1}">
       <formula1>=IF(L713&lt;&gt;"",INDIRECT(VLOOKUP(L713,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N713" xr:uid="{E97DEA3C-D8CC-430A-B7B0-302BC7FE0FCE}">
+    <dataValidation type="list" sqref="N713" xr:uid="{4946AA90-BACF-41CF-997A-FEA2DDEFCD65}">
       <formula1>=IF(M713&lt;&gt;"",INDIRECT(VLOOKUP(M713,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M714" xr:uid="{689D1415-5187-4884-9DC6-4CA1C937A95D}">
+    <dataValidation type="list" sqref="M714" xr:uid="{174332DE-0EBC-428F-A7FB-74CFFD557AE7}">
       <formula1>=IF(L714&lt;&gt;"",INDIRECT(VLOOKUP(L714,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N714" xr:uid="{659B2608-6AF5-45E1-AC91-DAAD5D7499CA}">
+    <dataValidation type="list" sqref="N714" xr:uid="{BE8CA11F-3A78-4382-9733-FF525E6B80A6}">
       <formula1>=IF(M714&lt;&gt;"",INDIRECT(VLOOKUP(M714,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M715" xr:uid="{175A0F4D-B7D2-409D-9DDC-B5A5D21F8C88}">
+    <dataValidation type="list" sqref="M715" xr:uid="{FC7563C5-26CB-4D90-A9D4-0EF13E35892C}">
       <formula1>=IF(L715&lt;&gt;"",INDIRECT(VLOOKUP(L715,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N715" xr:uid="{6CBD2397-4542-4D19-AF54-90FF7FAC4F4A}">
+    <dataValidation type="list" sqref="N715" xr:uid="{AE8B6C59-A8A8-46C9-B7E2-337EE4246695}">
       <formula1>=IF(M715&lt;&gt;"",INDIRECT(VLOOKUP(M715,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M716" xr:uid="{86E8560E-C40D-486E-9C89-47AB0569451B}">
+    <dataValidation type="list" sqref="M716" xr:uid="{A75A7312-9825-4B60-AD8B-0654A49333C2}">
       <formula1>=IF(L716&lt;&gt;"",INDIRECT(VLOOKUP(L716,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N716" xr:uid="{D34E115C-FB93-46F2-948C-8C4AE671427A}">
+    <dataValidation type="list" sqref="N716" xr:uid="{92DA6080-70B8-4BD3-8A0C-4371E2D4B4E5}">
       <formula1>=IF(M716&lt;&gt;"",INDIRECT(VLOOKUP(M716,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M717" xr:uid="{AFAC58CC-0136-4190-9208-BEFBE5D1D71D}">
+    <dataValidation type="list" sqref="M717" xr:uid="{7DE7F780-51B0-4F88-8E93-6B83AC6FE816}">
       <formula1>=IF(L717&lt;&gt;"",INDIRECT(VLOOKUP(L717,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N717" xr:uid="{2AFEAE74-C7E0-4E79-8532-6D54C81CB875}">
+    <dataValidation type="list" sqref="N717" xr:uid="{1E432555-3952-4C7F-9BEF-BE2E040D4D2D}">
       <formula1>=IF(M717&lt;&gt;"",INDIRECT(VLOOKUP(M717,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M718" xr:uid="{6EAC13D1-BC75-4A4C-8372-B68F90DA6D37}">
+    <dataValidation type="list" sqref="M718" xr:uid="{F3A5FE4D-9591-4F96-8CB7-D6EA801A3E27}">
       <formula1>=IF(L718&lt;&gt;"",INDIRECT(VLOOKUP(L718,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N718" xr:uid="{E27FA86F-B89B-4538-A68B-CA68ACE49BF7}">
+    <dataValidation type="list" sqref="N718" xr:uid="{3EFF20F6-9DB5-4FFA-B67B-2E30E276313B}">
       <formula1>=IF(M718&lt;&gt;"",INDIRECT(VLOOKUP(M718,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M719" xr:uid="{E56D4B9E-9937-48F3-9B61-87C237717F89}">
+    <dataValidation type="list" sqref="M719" xr:uid="{3B5BFC80-E10E-408B-8098-5ECE6912A05F}">
       <formula1>=IF(L719&lt;&gt;"",INDIRECT(VLOOKUP(L719,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N719" xr:uid="{5D2F4413-CB44-44D6-AD4B-D43A79205E72}">
+    <dataValidation type="list" sqref="N719" xr:uid="{0DFB78E3-0975-4D1F-AB09-6895C62C735A}">
       <formula1>=IF(M719&lt;&gt;"",INDIRECT(VLOOKUP(M719,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M720" xr:uid="{10269B2E-88F9-4676-A688-97C9151409E5}">
+    <dataValidation type="list" sqref="M720" xr:uid="{18BB3ADA-DCDF-4560-8635-EA4872C68234}">
       <formula1>=IF(L720&lt;&gt;"",INDIRECT(VLOOKUP(L720,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N720" xr:uid="{E1778B9F-CE2B-4B4D-A7FF-2B40A707DB43}">
+    <dataValidation type="list" sqref="N720" xr:uid="{8CEE34A8-0CF0-46C4-A600-BDA1AC57D0D6}">
       <formula1>=IF(M720&lt;&gt;"",INDIRECT(VLOOKUP(M720,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M721" xr:uid="{DDA593EE-1348-48C8-8AE4-DBE355F83932}">
+    <dataValidation type="list" sqref="M721" xr:uid="{8ECDEA9B-9375-445C-BD37-EDD00857BA96}">
       <formula1>=IF(L721&lt;&gt;"",INDIRECT(VLOOKUP(L721,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N721" xr:uid="{F45F080B-E93D-482B-B073-2E0046491E38}">
+    <dataValidation type="list" sqref="N721" xr:uid="{7C79E81D-B7FD-4FA1-9323-B361F7DF3BD6}">
       <formula1>=IF(M721&lt;&gt;"",INDIRECT(VLOOKUP(M721,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M722" xr:uid="{3CA8D82E-1912-44D3-AF3F-672E0304BA43}">
+    <dataValidation type="list" sqref="M722" xr:uid="{74DC2F83-EAA8-4C1D-BCF6-7B80FD307F65}">
       <formula1>=IF(L722&lt;&gt;"",INDIRECT(VLOOKUP(L722,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N722" xr:uid="{80EAFE21-4F78-429A-BBE9-A269E5045560}">
+    <dataValidation type="list" sqref="N722" xr:uid="{A898668B-BCF2-49EF-9323-9D9A95626735}">
       <formula1>=IF(M722&lt;&gt;"",INDIRECT(VLOOKUP(M722,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M723" xr:uid="{730343EF-4ABE-47D2-A6D6-1381ED8B8623}">
+    <dataValidation type="list" sqref="M723" xr:uid="{EF2596FF-5DDF-4F51-B46A-7A878EDD56D8}">
       <formula1>=IF(L723&lt;&gt;"",INDIRECT(VLOOKUP(L723,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N723" xr:uid="{21C071AE-874F-49C0-AF9F-6D54D94D6ACF}">
+    <dataValidation type="list" sqref="N723" xr:uid="{165C56EC-867A-439F-A3AC-FF728A35490B}">
       <formula1>=IF(M723&lt;&gt;"",INDIRECT(VLOOKUP(M723,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M724" xr:uid="{4E2D46F4-C4E2-45CE-A0C7-1D1AC5C61AEE}">
+    <dataValidation type="list" sqref="M724" xr:uid="{6BAD022B-9761-45AE-BD44-B8BCF52AE983}">
       <formula1>=IF(L724&lt;&gt;"",INDIRECT(VLOOKUP(L724,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N724" xr:uid="{4B10C1E6-5329-4195-9485-855652FA71A9}">
+    <dataValidation type="list" sqref="N724" xr:uid="{B3713482-463D-4E2C-9F27-41938F5C26C1}">
       <formula1>=IF(M724&lt;&gt;"",INDIRECT(VLOOKUP(M724,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M725" xr:uid="{6AECAD75-139F-48BA-A518-482A8E9760F4}">
+    <dataValidation type="list" sqref="M725" xr:uid="{9DBFB699-102A-45CE-AA08-9A0C824CEAA6}">
       <formula1>=IF(L725&lt;&gt;"",INDIRECT(VLOOKUP(L725,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N725" xr:uid="{D2DC329A-578F-43D0-9DC2-DF0C410088E5}">
+    <dataValidation type="list" sqref="N725" xr:uid="{25358CFE-2CEE-44D9-8555-1231F5D05F1B}">
       <formula1>=IF(M725&lt;&gt;"",INDIRECT(VLOOKUP(M725,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M726" xr:uid="{D6B90F09-55BB-4B06-9B69-FD672ABC3EEA}">
+    <dataValidation type="list" sqref="M726" xr:uid="{2C91F31F-69B2-452F-B250-A93C2CCC7F2D}">
       <formula1>=IF(L726&lt;&gt;"",INDIRECT(VLOOKUP(L726,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N726" xr:uid="{DDF8908D-B5E2-4901-A5BC-B1BD8C02B3DF}">
+    <dataValidation type="list" sqref="N726" xr:uid="{549E3906-03BA-4A93-9F9B-B26F5BA059EB}">
       <formula1>=IF(M726&lt;&gt;"",INDIRECT(VLOOKUP(M726,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M727" xr:uid="{93C370A2-BB7D-4AD0-ACA5-C3F0F0ABFC37}">
+    <dataValidation type="list" sqref="M727" xr:uid="{99EC2822-CB30-4F88-94E2-01E36BF39D9B}">
       <formula1>=IF(L727&lt;&gt;"",INDIRECT(VLOOKUP(L727,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N727" xr:uid="{EA8DDB2E-05B7-47D9-A6B8-0ED6F33C11D5}">
+    <dataValidation type="list" sqref="N727" xr:uid="{5C40AF3D-C5BF-4C7E-BC75-98E4F6983D18}">
       <formula1>=IF(M727&lt;&gt;"",INDIRECT(VLOOKUP(M727,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M728" xr:uid="{162ED5E9-3BE5-4055-9413-2711B1539F71}">
+    <dataValidation type="list" sqref="M728" xr:uid="{0120348A-D051-46CA-8D24-92576F9864F4}">
       <formula1>=IF(L728&lt;&gt;"",INDIRECT(VLOOKUP(L728,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N728" xr:uid="{7E50D1BD-D5B4-46F6-9D7D-CAA254E80A86}">
+    <dataValidation type="list" sqref="N728" xr:uid="{7E2B9A3C-186C-4F5E-B063-D834BA6B5DCB}">
       <formula1>=IF(M728&lt;&gt;"",INDIRECT(VLOOKUP(M728,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M729" xr:uid="{C0248E12-2BA5-4F3C-BEB4-636F3F2AAEEF}">
+    <dataValidation type="list" sqref="M729" xr:uid="{37802EBE-3355-449E-BEA8-9EC0A1A66131}">
       <formula1>=IF(L729&lt;&gt;"",INDIRECT(VLOOKUP(L729,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N729" xr:uid="{0AC35CC6-C1FA-4399-9FD7-A7848E96E37E}">
+    <dataValidation type="list" sqref="N729" xr:uid="{16975BAC-8B46-44CB-92F5-D6DCCF4C0408}">
       <formula1>=IF(M729&lt;&gt;"",INDIRECT(VLOOKUP(M729,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M730" xr:uid="{5B385702-E195-4128-8D5A-209FF4E43FCB}">
+    <dataValidation type="list" sqref="M730" xr:uid="{0E8BC3DC-3184-4745-93C2-0D1907DEE3BD}">
       <formula1>=IF(L730&lt;&gt;"",INDIRECT(VLOOKUP(L730,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N730" xr:uid="{ED262CA0-AF0B-4956-A6CF-D95C8113C4A1}">
+    <dataValidation type="list" sqref="N730" xr:uid="{AC1D8EE9-B15F-491B-AEE2-07E4F2794C30}">
       <formula1>=IF(M730&lt;&gt;"",INDIRECT(VLOOKUP(M730,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M731" xr:uid="{618AC3D7-2291-4CC0-BC8C-FEFC4BD5BD98}">
+    <dataValidation type="list" sqref="M731" xr:uid="{1ACA80BB-41A9-4180-BFA3-52439A2D1190}">
       <formula1>=IF(L731&lt;&gt;"",INDIRECT(VLOOKUP(L731,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N731" xr:uid="{23C2F12B-1D5B-40AF-A3E0-B76AFD43E431}">
+    <dataValidation type="list" sqref="N731" xr:uid="{7CF720E9-1401-4DEA-AD8A-0344598FD686}">
       <formula1>=IF(M731&lt;&gt;"",INDIRECT(VLOOKUP(M731,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M732" xr:uid="{29520CDE-0723-44A5-B6B6-368D8CC6562E}">
+    <dataValidation type="list" sqref="M732" xr:uid="{2F2C3465-F86A-45F6-B9B2-1B3CA02F8FBF}">
       <formula1>=IF(L732&lt;&gt;"",INDIRECT(VLOOKUP(L732,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N732" xr:uid="{064757AE-5AD2-41F9-996C-916F7F46A91B}">
+    <dataValidation type="list" sqref="N732" xr:uid="{8A530A15-CEDE-4A6E-B272-92F4CA306EAB}">
       <formula1>=IF(M732&lt;&gt;"",INDIRECT(VLOOKUP(M732,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M733" xr:uid="{7A6D98ED-5E88-48AA-A63F-D9EDDCDF6966}">
+    <dataValidation type="list" sqref="M733" xr:uid="{3B612A2E-FCF7-4A44-8EB9-59453B628158}">
       <formula1>=IF(L733&lt;&gt;"",INDIRECT(VLOOKUP(L733,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N733" xr:uid="{3556DE51-2132-48C0-89B7-407D9A4A6086}">
+    <dataValidation type="list" sqref="N733" xr:uid="{E4D4D269-89AE-42D0-90E0-E4ED0C5F1C17}">
       <formula1>=IF(M733&lt;&gt;"",INDIRECT(VLOOKUP(M733,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M734" xr:uid="{B5234C51-E807-4624-8E30-E22F349AD2E2}">
+    <dataValidation type="list" sqref="M734" xr:uid="{2724E7D3-1D64-48DD-AF91-C03A7F9AD4ED}">
       <formula1>=IF(L734&lt;&gt;"",INDIRECT(VLOOKUP(L734,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N734" xr:uid="{2530FCCF-12E0-489B-89F9-CB4CA7420BDA}">
+    <dataValidation type="list" sqref="N734" xr:uid="{01C11768-615C-4AB7-BE91-D85B0B8A0631}">
       <formula1>=IF(M734&lt;&gt;"",INDIRECT(VLOOKUP(M734,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M735" xr:uid="{F7AD95CB-B4F1-40C8-BFD0-7708D467C426}">
+    <dataValidation type="list" sqref="M735" xr:uid="{0107FCEE-E9EB-4AC9-B078-DF481B770BB1}">
       <formula1>=IF(L735&lt;&gt;"",INDIRECT(VLOOKUP(L735,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N735" xr:uid="{1583156D-1121-4A2B-99F3-DD67E55056B1}">
+    <dataValidation type="list" sqref="N735" xr:uid="{DF89F94E-88EA-4876-A7C8-D932B75FB6AE}">
       <formula1>=IF(M735&lt;&gt;"",INDIRECT(VLOOKUP(M735,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M736" xr:uid="{0C56AB50-AC7C-49F7-8499-C66A67EA983A}">
+    <dataValidation type="list" sqref="M736" xr:uid="{1CC6D1BF-5197-4A51-A18E-9CC8D5F36B31}">
       <formula1>=IF(L736&lt;&gt;"",INDIRECT(VLOOKUP(L736,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N736" xr:uid="{B92DD06A-C595-4005-BB02-B2C185AB7473}">
+    <dataValidation type="list" sqref="N736" xr:uid="{A93DC3A7-8CA3-405C-A43C-B650AD330381}">
       <formula1>=IF(M736&lt;&gt;"",INDIRECT(VLOOKUP(M736,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M737" xr:uid="{9824D0B5-F1BC-43DD-9CAB-57CCBC4EA008}">
+    <dataValidation type="list" sqref="M737" xr:uid="{EF0E9BD5-0145-4915-98F9-885E2874F39D}">
       <formula1>=IF(L737&lt;&gt;"",INDIRECT(VLOOKUP(L737,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N737" xr:uid="{048E69BB-0C3B-4B26-883F-077AFD47540A}">
+    <dataValidation type="list" sqref="N737" xr:uid="{D4EB2623-5E34-479F-BCC3-B615942275B5}">
       <formula1>=IF(M737&lt;&gt;"",INDIRECT(VLOOKUP(M737,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M738" xr:uid="{EB04590C-DC2F-49F3-AEE7-7E45EB9E797A}">
+    <dataValidation type="list" sqref="M738" xr:uid="{AD4864D0-C08A-4673-A144-7EC21574138A}">
       <formula1>=IF(L738&lt;&gt;"",INDIRECT(VLOOKUP(L738,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N738" xr:uid="{051E3D1C-ADEE-4980-8159-CCD36EFAEE1B}">
+    <dataValidation type="list" sqref="N738" xr:uid="{151BAC88-D363-4112-A540-A97E99404CA3}">
       <formula1>=IF(M738&lt;&gt;"",INDIRECT(VLOOKUP(M738,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M739" xr:uid="{8747DF9D-224E-4173-8042-9E05B061692E}">
+    <dataValidation type="list" sqref="M739" xr:uid="{369FA65B-6264-43D0-B448-EDA7AE935B71}">
       <formula1>=IF(L739&lt;&gt;"",INDIRECT(VLOOKUP(L739,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N739" xr:uid="{08629967-0C2A-4520-85B5-0DD9576BF77D}">
+    <dataValidation type="list" sqref="N739" xr:uid="{A88D42F4-9852-40B1-8D80-01CC47FAE22B}">
       <formula1>=IF(M739&lt;&gt;"",INDIRECT(VLOOKUP(M739,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M740" xr:uid="{2584E662-19DB-46B7-9158-28C8EFAC2038}">
+    <dataValidation type="list" sqref="M740" xr:uid="{8584979B-7D4B-47C2-965D-2B8E00A86D48}">
       <formula1>=IF(L740&lt;&gt;"",INDIRECT(VLOOKUP(L740,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N740" xr:uid="{A9C57CE8-B238-4EA2-939C-ECC3B0E2DE02}">
+    <dataValidation type="list" sqref="N740" xr:uid="{7D9C2954-5912-4CD6-8449-2AE4B4130894}">
       <formula1>=IF(M740&lt;&gt;"",INDIRECT(VLOOKUP(M740,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M741" xr:uid="{47A6ED7E-38EB-4AA6-929F-922170C7041C}">
+    <dataValidation type="list" sqref="M741" xr:uid="{8471C8AD-024F-4461-B903-B887442715A4}">
       <formula1>=IF(L741&lt;&gt;"",INDIRECT(VLOOKUP(L741,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N741" xr:uid="{3C98B89A-2D1F-4395-AE05-EBEF0A9C4852}">
+    <dataValidation type="list" sqref="N741" xr:uid="{50B35333-6D6B-49A5-ACB0-58420E2C0B48}">
       <formula1>=IF(M741&lt;&gt;"",INDIRECT(VLOOKUP(M741,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M742" xr:uid="{D0CBC8C5-7A34-46E3-AB90-1197342FFFE1}">
+    <dataValidation type="list" sqref="M742" xr:uid="{6619822A-BCD9-461B-B7D4-1C8990DF2154}">
       <formula1>=IF(L742&lt;&gt;"",INDIRECT(VLOOKUP(L742,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N742" xr:uid="{BB432694-EC95-4ECA-9AF3-E8434E5206CF}">
+    <dataValidation type="list" sqref="N742" xr:uid="{FC7C07DE-7D98-45EA-B5E2-AE7F2656B4A0}">
       <formula1>=IF(M742&lt;&gt;"",INDIRECT(VLOOKUP(M742,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M743" xr:uid="{A2CE0589-A02D-4C69-A0D8-F5D9CC4A9C55}">
+    <dataValidation type="list" sqref="M743" xr:uid="{54D32BF9-E670-4CC3-86E5-99ED276FB632}">
       <formula1>=IF(L743&lt;&gt;"",INDIRECT(VLOOKUP(L743,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N743" xr:uid="{449801EC-9DD3-481A-9B1A-A9D3289855DB}">
+    <dataValidation type="list" sqref="N743" xr:uid="{226D9312-1E65-49D2-9772-7A3B1586DC69}">
       <formula1>=IF(M743&lt;&gt;"",INDIRECT(VLOOKUP(M743,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M744" xr:uid="{87173680-D402-4B6D-9B68-F57112DD020C}">
+    <dataValidation type="list" sqref="M744" xr:uid="{177F1D47-DB4A-420A-BCE7-11DC2981AD11}">
       <formula1>=IF(L744&lt;&gt;"",INDIRECT(VLOOKUP(L744,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N744" xr:uid="{3AD82C5B-3F57-407B-951B-DADC390A3721}">
+    <dataValidation type="list" sqref="N744" xr:uid="{2197423A-1754-41CD-98FE-707F4B880E04}">
       <formula1>=IF(M744&lt;&gt;"",INDIRECT(VLOOKUP(M744,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M745" xr:uid="{DF6F3748-FBD5-4CE5-A390-C0EF1E3B0C34}">
+    <dataValidation type="list" sqref="M745" xr:uid="{4CEBB9B9-940C-419D-8A49-CAAC81CF85AC}">
       <formula1>=IF(L745&lt;&gt;"",INDIRECT(VLOOKUP(L745,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N745" xr:uid="{10F85BAB-15EA-42CE-B0AF-6A15197ED304}">
+    <dataValidation type="list" sqref="N745" xr:uid="{BD3B7D1B-364D-4DF2-93D7-E8F81A5C3D42}">
       <formula1>=IF(M745&lt;&gt;"",INDIRECT(VLOOKUP(M745,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M746" xr:uid="{E9FB96BE-9482-481C-AD29-8E1130DCC9B5}">
+    <dataValidation type="list" sqref="M746" xr:uid="{A15638AD-1DC8-4612-90FD-832D23AAB37D}">
       <formula1>=IF(L746&lt;&gt;"",INDIRECT(VLOOKUP(L746,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N746" xr:uid="{DF1C286D-C5BA-4755-BE07-00A1BDF75435}">
+    <dataValidation type="list" sqref="N746" xr:uid="{8E4C4949-00B6-4625-84CF-4D8BC39827CC}">
       <formula1>=IF(M746&lt;&gt;"",INDIRECT(VLOOKUP(M746,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M747" xr:uid="{739614D1-4F80-4900-9C49-896D9D5FFD33}">
+    <dataValidation type="list" sqref="M747" xr:uid="{E6BE02E7-4049-4020-ABCB-39D77F1D40FE}">
       <formula1>=IF(L747&lt;&gt;"",INDIRECT(VLOOKUP(L747,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N747" xr:uid="{4430BF0E-25C6-40FC-8161-F2DDB9EAB41F}">
+    <dataValidation type="list" sqref="N747" xr:uid="{841D25C9-9308-47ED-A71A-01D0EDA923B8}">
       <formula1>=IF(M747&lt;&gt;"",INDIRECT(VLOOKUP(M747,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M748" xr:uid="{0A4F7FEA-1525-46D9-919A-0463F7D6D8A9}">
+    <dataValidation type="list" sqref="M748" xr:uid="{50CF3EDE-CC0D-4182-A433-68D8749DD2CE}">
       <formula1>=IF(L748&lt;&gt;"",INDIRECT(VLOOKUP(L748,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N748" xr:uid="{8643D38A-836A-466B-AF8C-FFAB49E1E0D6}">
+    <dataValidation type="list" sqref="N748" xr:uid="{0EA543FC-C815-427F-AC4C-9D11508EC7D0}">
       <formula1>=IF(M748&lt;&gt;"",INDIRECT(VLOOKUP(M748,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M749" xr:uid="{51CF8C12-577C-4BC6-A9EB-818D72428215}">
+    <dataValidation type="list" sqref="M749" xr:uid="{F821E6E6-10C0-42EB-8E9C-F3DEC5EC4331}">
       <formula1>=IF(L749&lt;&gt;"",INDIRECT(VLOOKUP(L749,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N749" xr:uid="{B651FCF8-AF8B-4A45-B403-33834B3E5CB3}">
+    <dataValidation type="list" sqref="N749" xr:uid="{A3041C88-B509-4CAD-AF7B-97BC4EB387A3}">
       <formula1>=IF(M749&lt;&gt;"",INDIRECT(VLOOKUP(M749,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M750" xr:uid="{097E2D48-6F6F-45F5-ACE9-A851E753CC7D}">
+    <dataValidation type="list" sqref="M750" xr:uid="{86C062D7-EB45-4846-A877-3E76FEFB5DD4}">
       <formula1>=IF(L750&lt;&gt;"",INDIRECT(VLOOKUP(L750,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N750" xr:uid="{5794A37C-591C-4312-B475-E2E5D9ECDAFB}">
+    <dataValidation type="list" sqref="N750" xr:uid="{8B5B5F07-F93F-4C57-B8DC-BDFDA6EA129F}">
       <formula1>=IF(M750&lt;&gt;"",INDIRECT(VLOOKUP(M750,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M751" xr:uid="{2A7D38AF-AAC8-47AB-BCD3-F6437D03DDAF}">
+    <dataValidation type="list" sqref="M751" xr:uid="{BE4886E4-D6F8-41A7-BB97-4FF366ECA543}">
       <formula1>=IF(L751&lt;&gt;"",INDIRECT(VLOOKUP(L751,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N751" xr:uid="{D4C8BEA1-9798-4B4F-A723-DCA273F341E9}">
+    <dataValidation type="list" sqref="N751" xr:uid="{8158EA78-3E05-48D7-B4FE-CE3F756D72BA}">
       <formula1>=IF(M751&lt;&gt;"",INDIRECT(VLOOKUP(M751,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M752" xr:uid="{8B132656-AF6D-45FF-A13E-8882A052EAF6}">
+    <dataValidation type="list" sqref="M752" xr:uid="{56C40498-D010-4E96-8906-3FA358D04784}">
       <formula1>=IF(L752&lt;&gt;"",INDIRECT(VLOOKUP(L752,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N752" xr:uid="{C795B96D-D743-46F8-AACF-6257E6A287D4}">
+    <dataValidation type="list" sqref="N752" xr:uid="{76B3D9D3-AB40-4D3A-A219-0ACFAF16A5E8}">
       <formula1>=IF(M752&lt;&gt;"",INDIRECT(VLOOKUP(M752,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M753" xr:uid="{3D4C43A2-9A74-4F21-A734-8E179642A194}">
+    <dataValidation type="list" sqref="M753" xr:uid="{48E71267-815B-40E3-AEF7-CD5B52771D13}">
       <formula1>=IF(L753&lt;&gt;"",INDIRECT(VLOOKUP(L753,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N753" xr:uid="{8C2CBC63-CF42-45BC-A254-B9DAF310455F}">
+    <dataValidation type="list" sqref="N753" xr:uid="{A0DC9FC3-5866-4BA1-AE5A-802CF7F2B2FB}">
       <formula1>=IF(M753&lt;&gt;"",INDIRECT(VLOOKUP(M753,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M754" xr:uid="{F17F057C-B1A5-4E48-88D2-B090670E03D1}">
+    <dataValidation type="list" sqref="M754" xr:uid="{0E3249F1-E7D5-4640-805C-5F3F6688783C}">
       <formula1>=IF(L754&lt;&gt;"",INDIRECT(VLOOKUP(L754,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N754" xr:uid="{9D0FCCDC-6075-4E4C-A492-32536B6B9E5D}">
+    <dataValidation type="list" sqref="N754" xr:uid="{56A5BE01-B70D-4E41-871F-4AD49DD61C57}">
       <formula1>=IF(M754&lt;&gt;"",INDIRECT(VLOOKUP(M754,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M755" xr:uid="{FB376C1A-C667-4ABF-9020-BCFE16A8D096}">
+    <dataValidation type="list" sqref="M755" xr:uid="{27DF8D7B-B651-41AC-A209-7EE9EC99673C}">
       <formula1>=IF(L755&lt;&gt;"",INDIRECT(VLOOKUP(L755,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N755" xr:uid="{23B0C10D-81CC-4526-A022-47A39B383288}">
+    <dataValidation type="list" sqref="N755" xr:uid="{1A3A2475-C904-4921-AE04-3E69E7A42EBA}">
       <formula1>=IF(M755&lt;&gt;"",INDIRECT(VLOOKUP(M755,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M756" xr:uid="{5D92BD78-EABF-4688-B21E-824A2B44F72B}">
+    <dataValidation type="list" sqref="M756" xr:uid="{8E540F49-101A-4C90-9625-7AB8D31A673D}">
       <formula1>=IF(L756&lt;&gt;"",INDIRECT(VLOOKUP(L756,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N756" xr:uid="{3A8091C2-9087-464F-8733-0375428E6996}">
+    <dataValidation type="list" sqref="N756" xr:uid="{02425F05-B93A-4181-B8B9-272BB554E947}">
       <formula1>=IF(M756&lt;&gt;"",INDIRECT(VLOOKUP(M756,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M757" xr:uid="{77D9C4A6-1A86-42A0-B71B-4FF21884B30B}">
+    <dataValidation type="list" sqref="M757" xr:uid="{279FE51C-EB26-47BD-A520-D610543840BC}">
       <formula1>=IF(L757&lt;&gt;"",INDIRECT(VLOOKUP(L757,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N757" xr:uid="{EB87116A-FAAA-495B-935C-A6D0AE16E464}">
+    <dataValidation type="list" sqref="N757" xr:uid="{0DE5B574-A383-4CC3-8F28-8D796D258C07}">
       <formula1>=IF(M757&lt;&gt;"",INDIRECT(VLOOKUP(M757,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M758" xr:uid="{B8F72638-1507-4156-9F45-F81BC6AF119C}">
+    <dataValidation type="list" sqref="M758" xr:uid="{E98380E2-3F0E-4D04-AC45-CE8AD7E9701B}">
       <formula1>=IF(L758&lt;&gt;"",INDIRECT(VLOOKUP(L758,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N758" xr:uid="{7D466AE7-7392-4BA1-876A-216CD38DEEB6}">
+    <dataValidation type="list" sqref="N758" xr:uid="{59CCB6F3-1605-4193-96E9-79039E229A1F}">
       <formula1>=IF(M758&lt;&gt;"",INDIRECT(VLOOKUP(M758,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M759" xr:uid="{63BDC690-50EB-4493-A9D8-6B72BCB127B4}">
+    <dataValidation type="list" sqref="M759" xr:uid="{1A33F95E-BB5C-4340-A9FB-1D36555D9C7A}">
       <formula1>=IF(L759&lt;&gt;"",INDIRECT(VLOOKUP(L759,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N759" xr:uid="{B2F9BF14-386F-4FE2-9572-FC87F8B57D11}">
+    <dataValidation type="list" sqref="N759" xr:uid="{830A81E6-E4F9-41A3-BDCE-0708C27629D6}">
       <formula1>=IF(M759&lt;&gt;"",INDIRECT(VLOOKUP(M759,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M760" xr:uid="{4FF2CEE9-ACE7-4039-909C-4691D1159B4E}">
+    <dataValidation type="list" sqref="M760" xr:uid="{06970C54-5136-41DA-80B6-F9F77975F537}">
       <formula1>=IF(L760&lt;&gt;"",INDIRECT(VLOOKUP(L760,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N760" xr:uid="{7BE82C4D-5D12-4A60-90E0-EB5F733719B2}">
+    <dataValidation type="list" sqref="N760" xr:uid="{69EB4A30-39DB-4D5D-8A8D-926717E08FEF}">
       <formula1>=IF(M760&lt;&gt;"",INDIRECT(VLOOKUP(M760,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M761" xr:uid="{E3BCCFCE-17B1-4920-8907-5AACFDDC37F6}">
+    <dataValidation type="list" sqref="M761" xr:uid="{920B5707-5C68-45B0-A64B-83E234FB7EEF}">
       <formula1>=IF(L761&lt;&gt;"",INDIRECT(VLOOKUP(L761,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N761" xr:uid="{EA71634F-39C8-44A5-B3C3-03E16BC156C4}">
+    <dataValidation type="list" sqref="N761" xr:uid="{CC3BF546-2D82-4396-8205-F5973AAAD413}">
       <formula1>=IF(M761&lt;&gt;"",INDIRECT(VLOOKUP(M761,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M762" xr:uid="{4A3F033F-1408-4AB0-B820-684CC527BE7B}">
+    <dataValidation type="list" sqref="M762" xr:uid="{283C0F66-B7F7-43FA-8881-0206C6C62CF2}">
       <formula1>=IF(L762&lt;&gt;"",INDIRECT(VLOOKUP(L762,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N762" xr:uid="{2237C1F1-EF86-4A86-B4C6-0EB2318B9C47}">
+    <dataValidation type="list" sqref="N762" xr:uid="{5B420F27-5825-4959-839E-D295BBF6BE2F}">
       <formula1>=IF(M762&lt;&gt;"",INDIRECT(VLOOKUP(M762,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M763" xr:uid="{7A2B3D58-98A5-45AC-BED0-83E4AA7CA865}">
+    <dataValidation type="list" sqref="M763" xr:uid="{94AD88A7-21F0-4366-8AF6-80C3AAF14D16}">
       <formula1>=IF(L763&lt;&gt;"",INDIRECT(VLOOKUP(L763,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N763" xr:uid="{7998677C-C7EE-4197-8F48-576EEADB9568}">
+    <dataValidation type="list" sqref="N763" xr:uid="{2E67EA68-D064-4F56-B8BE-AFE434EA2C8E}">
       <formula1>=IF(M763&lt;&gt;"",INDIRECT(VLOOKUP(M763,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M764" xr:uid="{307D434B-E555-40A4-8163-714A6C3A140D}">
+    <dataValidation type="list" sqref="M764" xr:uid="{CE2D81B3-D89E-4B9B-A444-81E9963001BC}">
       <formula1>=IF(L764&lt;&gt;"",INDIRECT(VLOOKUP(L764,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N764" xr:uid="{9C989F98-4AAB-4102-A79E-8AD58897D323}">
+    <dataValidation type="list" sqref="N764" xr:uid="{C19181FD-D06F-4004-AA52-1366BF857DBA}">
       <formula1>=IF(M764&lt;&gt;"",INDIRECT(VLOOKUP(M764,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M765" xr:uid="{BAD29011-A3DA-4961-AB91-E6B014DF93B4}">
+    <dataValidation type="list" sqref="M765" xr:uid="{525F682E-0709-4781-8E26-BA3B56F52661}">
       <formula1>=IF(L765&lt;&gt;"",INDIRECT(VLOOKUP(L765,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N765" xr:uid="{234F5207-4203-446A-8E17-04F0185B525F}">
+    <dataValidation type="list" sqref="N765" xr:uid="{B05A6B0C-04F2-4AAD-BB84-0E4642A61477}">
       <formula1>=IF(M765&lt;&gt;"",INDIRECT(VLOOKUP(M765,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M766" xr:uid="{C1F172D8-35EF-4EB9-9C50-7D52882901A2}">
+    <dataValidation type="list" sqref="M766" xr:uid="{7D5CB745-4271-4273-A00E-DCAD16E79A82}">
       <formula1>=IF(L766&lt;&gt;"",INDIRECT(VLOOKUP(L766,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N766" xr:uid="{DE7AC191-BFD7-46AD-BC4D-2177F71300C4}">
+    <dataValidation type="list" sqref="N766" xr:uid="{6A174291-52B7-47D3-B7BD-589CAA08DEAF}">
       <formula1>=IF(M766&lt;&gt;"",INDIRECT(VLOOKUP(M766,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M767" xr:uid="{B275D545-CAB6-4939-93C6-90A5A6E03654}">
+    <dataValidation type="list" sqref="M767" xr:uid="{D4B75A41-4424-4984-89AD-890FB72BE0AC}">
       <formula1>=IF(L767&lt;&gt;"",INDIRECT(VLOOKUP(L767,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N767" xr:uid="{2197D264-F658-4BDC-9722-DD64D28E18DF}">
+    <dataValidation type="list" sqref="N767" xr:uid="{FE0BB618-A432-4254-8C5F-39AC71BD3089}">
       <formula1>=IF(M767&lt;&gt;"",INDIRECT(VLOOKUP(M767,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M768" xr:uid="{7D0845E2-BFC9-4B2C-91A5-01AD1B4A9FE7}">
+    <dataValidation type="list" sqref="M768" xr:uid="{EFE791FA-0240-4EF5-BF22-C1344D63C6BF}">
       <formula1>=IF(L768&lt;&gt;"",INDIRECT(VLOOKUP(L768,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N768" xr:uid="{691E3714-1319-4079-B5C4-64341B8552DB}">
+    <dataValidation type="list" sqref="N768" xr:uid="{34229A8B-0FA5-4996-A95E-1ACE8ED045AE}">
       <formula1>=IF(M768&lt;&gt;"",INDIRECT(VLOOKUP(M768,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M769" xr:uid="{9D37A216-4029-47D7-A892-2BBC11B5790E}">
+    <dataValidation type="list" sqref="M769" xr:uid="{202B343B-6A56-43B1-8A96-4B1177CAE23C}">
       <formula1>=IF(L769&lt;&gt;"",INDIRECT(VLOOKUP(L769,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N769" xr:uid="{0C3A9592-A52B-4007-BCCE-F9F79B2FCF0C}">
+    <dataValidation type="list" sqref="N769" xr:uid="{2CA6830D-5AF1-434C-88BB-B0A60F66777E}">
       <formula1>=IF(M769&lt;&gt;"",INDIRECT(VLOOKUP(M769,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M770" xr:uid="{66018AF5-C873-4CD3-A916-5F3E7045F57D}">
+    <dataValidation type="list" sqref="M770" xr:uid="{C2E379B4-ED7E-4D23-8006-CCB029B8C437}">
       <formula1>=IF(L770&lt;&gt;"",INDIRECT(VLOOKUP(L770,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N770" xr:uid="{49869E58-E766-4054-8C25-B94464C645CE}">
+    <dataValidation type="list" sqref="N770" xr:uid="{F7198C75-728C-4E30-B6CF-3C95A337DFB6}">
       <formula1>=IF(M770&lt;&gt;"",INDIRECT(VLOOKUP(M770,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M771" xr:uid="{0D5437A0-C475-4560-8441-AD8BD82D5D19}">
+    <dataValidation type="list" sqref="M771" xr:uid="{0D151431-8015-4125-903A-7032FF8234CB}">
       <formula1>=IF(L771&lt;&gt;"",INDIRECT(VLOOKUP(L771,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N771" xr:uid="{45E3FF30-8A0A-43B2-9E64-032F874920AB}">
+    <dataValidation type="list" sqref="N771" xr:uid="{E54C18FB-1844-4549-B135-B2856166D73B}">
       <formula1>=IF(M771&lt;&gt;"",INDIRECT(VLOOKUP(M771,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M772" xr:uid="{B7559244-88A3-4CD9-80CB-7687DC093E71}">
+    <dataValidation type="list" sqref="M772" xr:uid="{021F4394-52CE-4160-BD4A-07A674B3E4D1}">
       <formula1>=IF(L772&lt;&gt;"",INDIRECT(VLOOKUP(L772,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N772" xr:uid="{0E9E319E-07E9-4BD6-8399-95E443889639}">
+    <dataValidation type="list" sqref="N772" xr:uid="{C9DC207F-D18A-49BB-9DC6-A88DEA20EE97}">
       <formula1>=IF(M772&lt;&gt;"",INDIRECT(VLOOKUP(M772,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M773" xr:uid="{DD03739A-9609-4993-82D1-935B78045F77}">
+    <dataValidation type="list" sqref="M773" xr:uid="{AAB6BF99-2DF6-40F1-9690-9A6B65D21968}">
       <formula1>=IF(L773&lt;&gt;"",INDIRECT(VLOOKUP(L773,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N773" xr:uid="{14DC60C6-022F-497F-BC11-5B0BFB7B035B}">
+    <dataValidation type="list" sqref="N773" xr:uid="{276E0768-F8D9-4255-BFCB-FF774C275934}">
       <formula1>=IF(M773&lt;&gt;"",INDIRECT(VLOOKUP(M773,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M774" xr:uid="{4D97494A-6379-45ED-ABB8-84E59F500D26}">
+    <dataValidation type="list" sqref="M774" xr:uid="{4D570315-67E9-45E6-B181-615AE33DD711}">
       <formula1>=IF(L774&lt;&gt;"",INDIRECT(VLOOKUP(L774,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N774" xr:uid="{07F6448D-F915-47D1-8C01-11917D03AAF4}">
+    <dataValidation type="list" sqref="N774" xr:uid="{E101DDC7-AC5C-4C2A-BC2D-FB17D2D785BC}">
       <formula1>=IF(M774&lt;&gt;"",INDIRECT(VLOOKUP(M774,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M775" xr:uid="{BB01C13E-1B4C-4275-9E5A-C4DF8ED0BEBC}">
+    <dataValidation type="list" sqref="M775" xr:uid="{36653127-0018-45C6-A32B-D2C708FF2994}">
       <formula1>=IF(L775&lt;&gt;"",INDIRECT(VLOOKUP(L775,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N775" xr:uid="{6330E870-A1E6-47C5-9F7F-EF8658669507}">
+    <dataValidation type="list" sqref="N775" xr:uid="{6BCB7AC8-4C55-4AA9-9636-582EF9CA35CF}">
       <formula1>=IF(M775&lt;&gt;"",INDIRECT(VLOOKUP(M775,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M776" xr:uid="{5605562B-7885-48CC-95D5-C632BA87B582}">
+    <dataValidation type="list" sqref="M776" xr:uid="{9D47E3D2-EF43-4D7F-B97F-01035ADC04BA}">
       <formula1>=IF(L776&lt;&gt;"",INDIRECT(VLOOKUP(L776,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N776" xr:uid="{4CD3BCD1-FD3B-42F0-A695-B9E0C1342403}">
+    <dataValidation type="list" sqref="N776" xr:uid="{024DE376-F168-4AE4-9796-1F561DF46F26}">
       <formula1>=IF(M776&lt;&gt;"",INDIRECT(VLOOKUP(M776,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M777" xr:uid="{E62F3033-0D86-4B4E-AB01-6225CCB9243F}">
+    <dataValidation type="list" sqref="M777" xr:uid="{8F03F318-E362-4D2E-9A3A-FE740E20D442}">
       <formula1>=IF(L777&lt;&gt;"",INDIRECT(VLOOKUP(L777,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N777" xr:uid="{DCEFE886-B476-4A2A-9D4A-F16352E128D0}">
+    <dataValidation type="list" sqref="N777" xr:uid="{80709AB6-A46A-478A-8A23-33A9E9E30B9F}">
       <formula1>=IF(M777&lt;&gt;"",INDIRECT(VLOOKUP(M777,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M778" xr:uid="{EA85EC30-BF1C-40C2-B737-041A9C950633}">
+    <dataValidation type="list" sqref="M778" xr:uid="{AD8BEDB7-79D6-4C68-9C31-F99AD95A20E0}">
       <formula1>=IF(L778&lt;&gt;"",INDIRECT(VLOOKUP(L778,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N778" xr:uid="{B40A3422-CBDE-4E5B-9E2D-9547650A20E3}">
+    <dataValidation type="list" sqref="N778" xr:uid="{DC647042-287E-4C64-B79D-481DE4EC0808}">
       <formula1>=IF(M778&lt;&gt;"",INDIRECT(VLOOKUP(M778,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M779" xr:uid="{767FCFE6-D945-4747-A70B-C92469105154}">
+    <dataValidation type="list" sqref="M779" xr:uid="{95C7FC42-0FE6-4209-849C-15BDB4DFD1AA}">
       <formula1>=IF(L779&lt;&gt;"",INDIRECT(VLOOKUP(L779,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N779" xr:uid="{3298B4C6-E394-4E9C-A14C-5B8F355B7C69}">
+    <dataValidation type="list" sqref="N779" xr:uid="{8D3CCE54-2590-4E89-A2D1-2B1285C629DD}">
       <formula1>=IF(M779&lt;&gt;"",INDIRECT(VLOOKUP(M779,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M780" xr:uid="{C134E614-6509-4C59-A861-950E66B568A4}">
+    <dataValidation type="list" sqref="M780" xr:uid="{041737F6-E9A7-4314-8260-66A7BDDE1C1E}">
       <formula1>=IF(L780&lt;&gt;"",INDIRECT(VLOOKUP(L780,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N780" xr:uid="{F62A7B70-C30F-453B-B137-67CA244432F7}">
+    <dataValidation type="list" sqref="N780" xr:uid="{8E6CC6E0-8C96-40A1-B443-E89FAB0F8D10}">
       <formula1>=IF(M780&lt;&gt;"",INDIRECT(VLOOKUP(M780,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M781" xr:uid="{2698BDE8-1578-4D90-BE39-8637D534E394}">
+    <dataValidation type="list" sqref="M781" xr:uid="{E4BB07DA-50D6-444D-81E5-4B08ACEE0717}">
       <formula1>=IF(L781&lt;&gt;"",INDIRECT(VLOOKUP(L781,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N781" xr:uid="{C0F9BE1A-B164-4159-A4C5-4926B92E4702}">
+    <dataValidation type="list" sqref="N781" xr:uid="{7E27C8FB-2686-48EF-848F-3240DD58E55C}">
       <formula1>=IF(M781&lt;&gt;"",INDIRECT(VLOOKUP(M781,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M782" xr:uid="{F0A84596-465E-4539-BAD3-0E9325F8DAA9}">
+    <dataValidation type="list" sqref="M782" xr:uid="{118A4DF8-24AA-4505-8B64-CBD138192A28}">
       <formula1>=IF(L782&lt;&gt;"",INDIRECT(VLOOKUP(L782,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N782" xr:uid="{FDDC4D9E-5CAE-4338-8A38-9724E794BC1E}">
+    <dataValidation type="list" sqref="N782" xr:uid="{2FC62194-35D3-41CF-9F1B-1F5A65D0B6DA}">
       <formula1>=IF(M782&lt;&gt;"",INDIRECT(VLOOKUP(M782,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M783" xr:uid="{05DC99C7-8BBF-48E7-A45B-DE47398E3AAB}">
+    <dataValidation type="list" sqref="M783" xr:uid="{879E430E-11A0-40D3-8D24-353640E39D6F}">
       <formula1>=IF(L783&lt;&gt;"",INDIRECT(VLOOKUP(L783,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N783" xr:uid="{A7437FC4-4BE5-4711-ACC0-53E0A11F7514}">
+    <dataValidation type="list" sqref="N783" xr:uid="{AA3EA758-9F35-4384-B40F-F1F5B88C0C81}">
       <formula1>=IF(M783&lt;&gt;"",INDIRECT(VLOOKUP(M783,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M784" xr:uid="{E4B2E150-33FD-4D87-BBE3-BAA425A300C1}">
+    <dataValidation type="list" sqref="M784" xr:uid="{166FF0A2-2ABF-4E91-BAA1-94377AED09F9}">
       <formula1>=IF(L784&lt;&gt;"",INDIRECT(VLOOKUP(L784,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N784" xr:uid="{6F29BD83-D799-4A22-BFE6-4AA70FDC633E}">
+    <dataValidation type="list" sqref="N784" xr:uid="{93E31975-FC9B-4CA4-BF36-771FABB5CAB6}">
       <formula1>=IF(M784&lt;&gt;"",INDIRECT(VLOOKUP(M784,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M785" xr:uid="{A26B6E55-00E3-4687-9B4B-97A2B22EB191}">
+    <dataValidation type="list" sqref="M785" xr:uid="{84F7553E-CF38-428C-9985-05FE1672BDA0}">
       <formula1>=IF(L785&lt;&gt;"",INDIRECT(VLOOKUP(L785,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N785" xr:uid="{132630AF-3C98-4EC9-AEBE-6E79F56CD111}">
+    <dataValidation type="list" sqref="N785" xr:uid="{95FE13F5-BB72-4086-BF71-833FDAA072C0}">
       <formula1>=IF(M785&lt;&gt;"",INDIRECT(VLOOKUP(M785,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M786" xr:uid="{E8AEC432-1EDA-4AD8-88FB-B95C7435CADF}">
+    <dataValidation type="list" sqref="M786" xr:uid="{71B0CCE3-D1E6-447F-B877-8FB8D3B8CF58}">
       <formula1>=IF(L786&lt;&gt;"",INDIRECT(VLOOKUP(L786,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N786" xr:uid="{B4DCEDC0-F2FA-497C-8BB2-4BFDB20EBED2}">
+    <dataValidation type="list" sqref="N786" xr:uid="{93BDC203-5117-4141-8E4B-02F43E796FA9}">
       <formula1>=IF(M786&lt;&gt;"",INDIRECT(VLOOKUP(M786,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M787" xr:uid="{7743C52B-A074-4D7D-B052-9629CF4FFAE5}">
+    <dataValidation type="list" sqref="M787" xr:uid="{753C6326-233F-4653-914E-E5748796FBD1}">
       <formula1>=IF(L787&lt;&gt;"",INDIRECT(VLOOKUP(L787,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N787" xr:uid="{31F4D55D-246C-40A1-87D0-B66074E2CC7F}">
+    <dataValidation type="list" sqref="N787" xr:uid="{3840024B-7BD1-44C7-9C4E-1AED5C79F2AE}">
       <formula1>=IF(M787&lt;&gt;"",INDIRECT(VLOOKUP(M787,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M788" xr:uid="{EC4281BA-DC16-48C4-86A2-B4678DED892D}">
+    <dataValidation type="list" sqref="M788" xr:uid="{39BFA85A-C4A8-4143-82C7-62CAD66A6655}">
       <formula1>=IF(L788&lt;&gt;"",INDIRECT(VLOOKUP(L788,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N788" xr:uid="{07AB9B3D-CFAC-46DB-932B-D5ABF9B293D6}">
+    <dataValidation type="list" sqref="N788" xr:uid="{3CEB111D-7F5C-44B1-90DE-0FFE7FBDFE5E}">
       <formula1>=IF(M788&lt;&gt;"",INDIRECT(VLOOKUP(M788,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M789" xr:uid="{77BE4376-4725-40F9-94CB-6737A13603C2}">
+    <dataValidation type="list" sqref="M789" xr:uid="{940E8BDE-D7E4-4EA1-A106-2B1E024E529C}">
       <formula1>=IF(L789&lt;&gt;"",INDIRECT(VLOOKUP(L789,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N789" xr:uid="{9219766E-82A7-4702-A2F3-2F8A0E24F9D4}">
+    <dataValidation type="list" sqref="N789" xr:uid="{15D774CB-3875-4409-8FE6-C527D41CECCE}">
       <formula1>=IF(M789&lt;&gt;"",INDIRECT(VLOOKUP(M789,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M790" xr:uid="{031BBC5C-6ADC-410C-8C51-3E9092B48EAF}">
+    <dataValidation type="list" sqref="M790" xr:uid="{BDF00253-1C3E-40A7-BC94-FA447D4A5BBD}">
       <formula1>=IF(L790&lt;&gt;"",INDIRECT(VLOOKUP(L790,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N790" xr:uid="{6E8AB591-E095-431A-A241-A874460A6092}">
+    <dataValidation type="list" sqref="N790" xr:uid="{A2E37387-7032-4493-9223-552A040184ED}">
       <formula1>=IF(M790&lt;&gt;"",INDIRECT(VLOOKUP(M790,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M791" xr:uid="{AB0C04FD-29F5-426C-B35E-C8CB6AC57789}">
+    <dataValidation type="list" sqref="M791" xr:uid="{7A6D9507-2083-41DE-8AC9-ACEE58890BE7}">
       <formula1>=IF(L791&lt;&gt;"",INDIRECT(VLOOKUP(L791,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N791" xr:uid="{391FCF08-6D8F-4CA5-880B-C11538AF655C}">
+    <dataValidation type="list" sqref="N791" xr:uid="{2EB06674-FAE7-4FDA-A658-1865D63B396B}">
       <formula1>=IF(M791&lt;&gt;"",INDIRECT(VLOOKUP(M791,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M792" xr:uid="{88E919DE-4492-4F89-BCD3-E227877698D3}">
+    <dataValidation type="list" sqref="M792" xr:uid="{F813F498-BF1A-47FF-A7C6-90360C2B4326}">
       <formula1>=IF(L792&lt;&gt;"",INDIRECT(VLOOKUP(L792,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N792" xr:uid="{CCF5B1FC-4926-4509-905D-C29183CFD993}">
+    <dataValidation type="list" sqref="N792" xr:uid="{C6219A4F-D030-4CD4-B4D3-D6893FB0A26A}">
       <formula1>=IF(M792&lt;&gt;"",INDIRECT(VLOOKUP(M792,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M793" xr:uid="{1879D5A9-99E9-45CF-ACDC-286A63E91E25}">
+    <dataValidation type="list" sqref="M793" xr:uid="{313CE4FD-C2FA-471E-9CDC-4D9ABEDF21D0}">
       <formula1>=IF(L793&lt;&gt;"",INDIRECT(VLOOKUP(L793,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N793" xr:uid="{56FB9B94-7988-4B22-B7D2-555180D7F0C8}">
+    <dataValidation type="list" sqref="N793" xr:uid="{6FDD720A-D80C-4B70-8F25-8A5142542652}">
       <formula1>=IF(M793&lt;&gt;"",INDIRECT(VLOOKUP(M793,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M794" xr:uid="{2FA0674A-D066-4AB3-A4B7-938B2D444079}">
+    <dataValidation type="list" sqref="M794" xr:uid="{8DBA4904-625A-433A-93F9-597B1845B444}">
       <formula1>=IF(L794&lt;&gt;"",INDIRECT(VLOOKUP(L794,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N794" xr:uid="{BEDABD06-2AA0-4282-9981-84F4ABD3C80F}">
+    <dataValidation type="list" sqref="N794" xr:uid="{3B8F00C0-A42E-4041-B347-D657064932AA}">
       <formula1>=IF(M794&lt;&gt;"",INDIRECT(VLOOKUP(M794,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M795" xr:uid="{C662D444-3135-44C4-9AD0-A13537C38F95}">
+    <dataValidation type="list" sqref="M795" xr:uid="{3227C2DB-856E-4BEA-A5A6-2775C6C1F310}">
       <formula1>=IF(L795&lt;&gt;"",INDIRECT(VLOOKUP(L795,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N795" xr:uid="{9D4E2254-1EAF-4892-BBC2-DB2BA9906AEC}">
+    <dataValidation type="list" sqref="N795" xr:uid="{0FE953B6-33BA-408B-8922-9A4283BB33ED}">
       <formula1>=IF(M795&lt;&gt;"",INDIRECT(VLOOKUP(M795,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M796" xr:uid="{EFA090F3-B198-4072-8D58-D569714C21E2}">
+    <dataValidation type="list" sqref="M796" xr:uid="{3704522A-9530-430E-9DD6-B6DEE80540E0}">
       <formula1>=IF(L796&lt;&gt;"",INDIRECT(VLOOKUP(L796,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N796" xr:uid="{1298C4C6-24E7-42CF-BA95-A847AE6245ED}">
+    <dataValidation type="list" sqref="N796" xr:uid="{BED9FFB9-863F-454A-80FE-2787B967B105}">
       <formula1>=IF(M796&lt;&gt;"",INDIRECT(VLOOKUP(M796,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M797" xr:uid="{65C29291-1825-4888-973B-CEAE3D0EC79B}">
+    <dataValidation type="list" sqref="M797" xr:uid="{910F3A1C-AC32-444B-8E98-11F56C0747E8}">
       <formula1>=IF(L797&lt;&gt;"",INDIRECT(VLOOKUP(L797,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N797" xr:uid="{36B5C3FE-B8BF-4BAF-8CAD-054B2BA98920}">
+    <dataValidation type="list" sqref="N797" xr:uid="{48387833-1F6A-4F7F-B2FD-D875072D8A16}">
       <formula1>=IF(M797&lt;&gt;"",INDIRECT(VLOOKUP(M797,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M798" xr:uid="{C8660EFB-654B-4222-B576-E9F14EBA6A39}">
+    <dataValidation type="list" sqref="M798" xr:uid="{97BAC581-DC16-4BB7-8C41-4B32A7969C16}">
       <formula1>=IF(L798&lt;&gt;"",INDIRECT(VLOOKUP(L798,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N798" xr:uid="{4A64F85F-41DB-47C0-8C75-D312D291126F}">
+    <dataValidation type="list" sqref="N798" xr:uid="{C7E88B7E-4D3E-43A6-AE6C-E01243929B72}">
       <formula1>=IF(M798&lt;&gt;"",INDIRECT(VLOOKUP(M798,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M799" xr:uid="{B596C6C0-809F-42B4-8DEB-C9092C7899BA}">
+    <dataValidation type="list" sqref="M799" xr:uid="{DBCB5F3D-F9F0-468E-8E47-30227874E333}">
       <formula1>=IF(L799&lt;&gt;"",INDIRECT(VLOOKUP(L799,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N799" xr:uid="{0E8ECC63-EAA0-495B-A8CD-13AEA0111DB6}">
+    <dataValidation type="list" sqref="N799" xr:uid="{65A9846D-30AB-4404-9693-72EF5B90FA0D}">
       <formula1>=IF(M799&lt;&gt;"",INDIRECT(VLOOKUP(M799,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M800" xr:uid="{03DC2270-5FF9-4D93-8A48-2CD52A257676}">
+    <dataValidation type="list" sqref="M800" xr:uid="{BAC672B5-F95C-4F23-B4D6-44AFC430CD53}">
       <formula1>=IF(L800&lt;&gt;"",INDIRECT(VLOOKUP(L800,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N800" xr:uid="{021D53D1-F3B5-4629-9906-538387CD8748}">
+    <dataValidation type="list" sqref="N800" xr:uid="{4D3EFAEC-8DCA-4F61-A78F-AB3BD3868200}">
       <formula1>=IF(M800&lt;&gt;"",INDIRECT(VLOOKUP(M800,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M801" xr:uid="{64C4ED2E-84E6-4C2E-945C-8422763C3979}">
+    <dataValidation type="list" sqref="M801" xr:uid="{EAE17333-58DB-4B6D-BA48-B6207B001739}">
       <formula1>=IF(L801&lt;&gt;"",INDIRECT(VLOOKUP(L801,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N801" xr:uid="{C3BA672E-75A4-4BFD-BD51-470F708A7A78}">
+    <dataValidation type="list" sqref="N801" xr:uid="{FE0F6D8D-CDEB-492A-8341-5F425443E5B8}">
       <formula1>=IF(M801&lt;&gt;"",INDIRECT(VLOOKUP(M801,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M802" xr:uid="{4B9936F2-4C68-4D9D-8DDB-DAA4C260F56A}">
+    <dataValidation type="list" sqref="M802" xr:uid="{01AC9DDA-3E2A-4E84-A3EF-66763FB7544A}">
       <formula1>=IF(L802&lt;&gt;"",INDIRECT(VLOOKUP(L802,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N802" xr:uid="{FBEEAB04-D771-4736-B50E-012FA18F3340}">
+    <dataValidation type="list" sqref="N802" xr:uid="{E84F3548-E6BB-4776-8C7F-E2690AF96EC1}">
       <formula1>=IF(M802&lt;&gt;"",INDIRECT(VLOOKUP(M802,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M803" xr:uid="{6582F361-3087-4567-B978-2B11C8CA5BE1}">
+    <dataValidation type="list" sqref="M803" xr:uid="{735D848D-7572-4762-A7CF-B4C64B1D0358}">
       <formula1>=IF(L803&lt;&gt;"",INDIRECT(VLOOKUP(L803,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N803" xr:uid="{97CC485D-2015-40A3-A96C-0C76BA44F079}">
+    <dataValidation type="list" sqref="N803" xr:uid="{1EA7ADD8-459A-44F6-B131-21F701D19F29}">
       <formula1>=IF(M803&lt;&gt;"",INDIRECT(VLOOKUP(M803,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M804" xr:uid="{33AD7B73-C1D1-427C-95AB-60A582982F48}">
+    <dataValidation type="list" sqref="M804" xr:uid="{2DADB09E-5648-4532-BE64-139A84802677}">
       <formula1>=IF(L804&lt;&gt;"",INDIRECT(VLOOKUP(L804,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N804" xr:uid="{65F0B549-F87F-47D7-B753-6DC05A114FC2}">
+    <dataValidation type="list" sqref="N804" xr:uid="{7250E56A-4339-4FB7-8F3B-CD535EAE7875}">
       <formula1>=IF(M804&lt;&gt;"",INDIRECT(VLOOKUP(M804,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M805" xr:uid="{C4D245EE-CEEF-466B-AEB2-02541EF71E0D}">
+    <dataValidation type="list" sqref="M805" xr:uid="{8AF9EA95-3B4C-49FB-BE3B-58431EDDE300}">
       <formula1>=IF(L805&lt;&gt;"",INDIRECT(VLOOKUP(L805,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N805" xr:uid="{37B822B9-5233-4873-AC27-9AC006FB3F53}">
+    <dataValidation type="list" sqref="N805" xr:uid="{5FE88E3E-C952-40C7-81C8-67550C7DEE2A}">
       <formula1>=IF(M805&lt;&gt;"",INDIRECT(VLOOKUP(M805,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M806" xr:uid="{DC0D6698-A78F-4058-9F07-2A45AD4D8530}">
+    <dataValidation type="list" sqref="M806" xr:uid="{93F77E87-021C-423E-80D5-0593DB11B327}">
       <formula1>=IF(L806&lt;&gt;"",INDIRECT(VLOOKUP(L806,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N806" xr:uid="{3DEB1891-EB5F-4FDA-AE8E-A24B1D746379}">
+    <dataValidation type="list" sqref="N806" xr:uid="{8DFD516E-792D-4A9F-9E2B-50769FCA8FE3}">
       <formula1>=IF(M806&lt;&gt;"",INDIRECT(VLOOKUP(M806,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M807" xr:uid="{D309E2A8-5C92-4DA1-8023-C6B9987180E9}">
+    <dataValidation type="list" sqref="M807" xr:uid="{8662D608-96DE-4B36-BB82-D69194F490E7}">
       <formula1>=IF(L807&lt;&gt;"",INDIRECT(VLOOKUP(L807,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N807" xr:uid="{12B770D2-A8A7-4CED-B613-8FC231EFD3BF}">
+    <dataValidation type="list" sqref="N807" xr:uid="{ED822FE1-3490-410B-B27A-C4FDF0A07E96}">
       <formula1>=IF(M807&lt;&gt;"",INDIRECT(VLOOKUP(M807,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M808" xr:uid="{DD6A8D90-1112-45CE-9405-A8BA2FAC8610}">
+    <dataValidation type="list" sqref="M808" xr:uid="{238797E9-0AA4-4891-956F-584C22CD0CCA}">
       <formula1>=IF(L808&lt;&gt;"",INDIRECT(VLOOKUP(L808,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N808" xr:uid="{F49C2E9F-2B77-4511-98C2-D21F2FC97CC8}">
+    <dataValidation type="list" sqref="N808" xr:uid="{F970033E-733D-4D2F-89E8-42BDF7F62B29}">
       <formula1>=IF(M808&lt;&gt;"",INDIRECT(VLOOKUP(M808,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M809" xr:uid="{2CF396C5-255C-4EDC-9A9B-3DE96272B58A}">
+    <dataValidation type="list" sqref="M809" xr:uid="{0261B8B2-C379-4CEB-A2F6-80DFE04938D1}">
       <formula1>=IF(L809&lt;&gt;"",INDIRECT(VLOOKUP(L809,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N809" xr:uid="{EF25641F-BB75-446D-86CB-79B8B984FEE2}">
+    <dataValidation type="list" sqref="N809" xr:uid="{167AB5B4-CE3A-4E5B-B694-4FBC576FA242}">
       <formula1>=IF(M809&lt;&gt;"",INDIRECT(VLOOKUP(M809,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M810" xr:uid="{EFF14B9B-E941-4FF1-BFC3-83E238D3163D}">
+    <dataValidation type="list" sqref="M810" xr:uid="{70F8FEF9-F034-4A21-B762-123248525F00}">
       <formula1>=IF(L810&lt;&gt;"",INDIRECT(VLOOKUP(L810,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N810" xr:uid="{C8B0D7E4-8D4B-4815-86DF-2E810222A646}">
+    <dataValidation type="list" sqref="N810" xr:uid="{A28FD4CA-A678-4523-A80C-CF7523A44860}">
       <formula1>=IF(M810&lt;&gt;"",INDIRECT(VLOOKUP(M810,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M811" xr:uid="{D960774A-692E-40D4-9E6C-3C2C870BFC7F}">
+    <dataValidation type="list" sqref="M811" xr:uid="{74363EC7-F333-46F9-920E-393CE875AD07}">
       <formula1>=IF(L811&lt;&gt;"",INDIRECT(VLOOKUP(L811,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N811" xr:uid="{F5AA225D-9E24-458A-BB61-BE8CA87F9A8C}">
+    <dataValidation type="list" sqref="N811" xr:uid="{AE4C3B61-B822-4786-8815-1E2D6646EF72}">
       <formula1>=IF(M811&lt;&gt;"",INDIRECT(VLOOKUP(M811,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M812" xr:uid="{24BC0C72-9636-4EE3-BAE2-4F2EBCAC6525}">
+    <dataValidation type="list" sqref="M812" xr:uid="{8D5E5BAA-A53C-492E-86E5-621C61893030}">
       <formula1>=IF(L812&lt;&gt;"",INDIRECT(VLOOKUP(L812,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N812" xr:uid="{BCDDB578-8E60-4708-97A0-D06600C4965F}">
+    <dataValidation type="list" sqref="N812" xr:uid="{1588E1F3-0E9E-45DC-A544-31A4C1864F9B}">
       <formula1>=IF(M812&lt;&gt;"",INDIRECT(VLOOKUP(M812,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M813" xr:uid="{3C9A3C48-59CA-4482-81E0-DD6BBE0A3D33}">
+    <dataValidation type="list" sqref="M813" xr:uid="{8297DAF7-95F6-4CEF-9022-28A604CA3CD8}">
       <formula1>=IF(L813&lt;&gt;"",INDIRECT(VLOOKUP(L813,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N813" xr:uid="{E2F29A74-2FCA-4FD0-899C-ED9F0793C6C5}">
+    <dataValidation type="list" sqref="N813" xr:uid="{9530A34E-2A17-4F9C-B869-D7C4C3E40D11}">
       <formula1>=IF(M813&lt;&gt;"",INDIRECT(VLOOKUP(M813,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M814" xr:uid="{2EF3957A-6962-446E-8CDE-92B0011557DF}">
+    <dataValidation type="list" sqref="M814" xr:uid="{9A7717D3-A1A7-48B5-AC89-D6822E87751A}">
       <formula1>=IF(L814&lt;&gt;"",INDIRECT(VLOOKUP(L814,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N814" xr:uid="{6AA38467-C05B-481A-BD5E-A4F492AF0B69}">
+    <dataValidation type="list" sqref="N814" xr:uid="{97013288-047D-4075-B71A-226B3D546129}">
       <formula1>=IF(M814&lt;&gt;"",INDIRECT(VLOOKUP(M814,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M815" xr:uid="{AE7177B8-FE12-4235-8AFD-C271C824F73B}">
+    <dataValidation type="list" sqref="M815" xr:uid="{210C9324-DDD6-456C-8C7B-16A11D4777F1}">
       <formula1>=IF(L815&lt;&gt;"",INDIRECT(VLOOKUP(L815,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N815" xr:uid="{E9C7EA98-E84D-48B9-B902-9885F7F3703A}">
+    <dataValidation type="list" sqref="N815" xr:uid="{D62EC7BC-EED7-41D9-8A35-66CF53335D3A}">
       <formula1>=IF(M815&lt;&gt;"",INDIRECT(VLOOKUP(M815,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M816" xr:uid="{52EC3E58-8329-4B30-A44A-74E57488341D}">
+    <dataValidation type="list" sqref="M816" xr:uid="{2A9453BD-2CCD-43CC-967F-3F4FEF6895F8}">
       <formula1>=IF(L816&lt;&gt;"",INDIRECT(VLOOKUP(L816,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N816" xr:uid="{5C312315-3CA5-4EE4-8443-C9975113559D}">
+    <dataValidation type="list" sqref="N816" xr:uid="{A4883CC2-E4D7-4A83-8474-B7BC77124335}">
       <formula1>=IF(M816&lt;&gt;"",INDIRECT(VLOOKUP(M816,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M817" xr:uid="{778BE42A-87DF-482D-B697-7C227AA65FD5}">
+    <dataValidation type="list" sqref="M817" xr:uid="{F27FAD19-19A4-4D3E-BE9E-7E9C189D907E}">
       <formula1>=IF(L817&lt;&gt;"",INDIRECT(VLOOKUP(L817,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N817" xr:uid="{E0957E1E-B935-4902-9D37-313ED7BD3323}">
+    <dataValidation type="list" sqref="N817" xr:uid="{9637D1E8-5D22-43B0-AB77-62B1D6C9E023}">
       <formula1>=IF(M817&lt;&gt;"",INDIRECT(VLOOKUP(M817,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M818" xr:uid="{3E48E0AC-9FFA-477F-99DF-2A2590BE5F30}">
+    <dataValidation type="list" sqref="M818" xr:uid="{27934CB9-2BAA-4F51-AC77-07989E083B9D}">
       <formula1>=IF(L818&lt;&gt;"",INDIRECT(VLOOKUP(L818,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N818" xr:uid="{80918F68-C401-4E23-A3C9-D857B3D549C8}">
+    <dataValidation type="list" sqref="N818" xr:uid="{8A4A4FFD-B127-4130-BC75-F94340F31C8D}">
       <formula1>=IF(M818&lt;&gt;"",INDIRECT(VLOOKUP(M818,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M819" xr:uid="{01FDF4C0-AACE-4956-80C5-3329C83DE490}">
+    <dataValidation type="list" sqref="M819" xr:uid="{A4F26143-D754-46B9-AC88-42E79BFD5A3C}">
       <formula1>=IF(L819&lt;&gt;"",INDIRECT(VLOOKUP(L819,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N819" xr:uid="{219DB593-CA68-40BA-95D5-FB7833119B87}">
+    <dataValidation type="list" sqref="N819" xr:uid="{5DC7493C-D6E5-4A7E-A955-31C85B4FC368}">
       <formula1>=IF(M819&lt;&gt;"",INDIRECT(VLOOKUP(M819,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M820" xr:uid="{997826F3-BC50-4AAA-877E-01FBBCE5954E}">
+    <dataValidation type="list" sqref="M820" xr:uid="{A362B4AD-5D68-486C-B0A5-D77C3F4092B5}">
       <formula1>=IF(L820&lt;&gt;"",INDIRECT(VLOOKUP(L820,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N820" xr:uid="{D5E5D94C-2D40-4D30-9E2F-267A75E3063B}">
+    <dataValidation type="list" sqref="N820" xr:uid="{7636F866-8A69-43C3-AC0A-EA1094F2C856}">
       <formula1>=IF(M820&lt;&gt;"",INDIRECT(VLOOKUP(M820,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M821" xr:uid="{B45FB9F3-37E3-499C-BA91-0797BC1B300F}">
+    <dataValidation type="list" sqref="M821" xr:uid="{ECD83C62-A363-413E-8A80-7F9132A25CC6}">
       <formula1>=IF(L821&lt;&gt;"",INDIRECT(VLOOKUP(L821,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N821" xr:uid="{724BFE21-5F5E-4451-AB81-B53985C0965B}">
+    <dataValidation type="list" sqref="N821" xr:uid="{2B51F74E-F3D7-4275-9F23-B8D708371EF8}">
       <formula1>=IF(M821&lt;&gt;"",INDIRECT(VLOOKUP(M821,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M822" xr:uid="{6A74085D-F3BD-4F2E-A412-0004EFF2B2EE}">
+    <dataValidation type="list" sqref="M822" xr:uid="{281986DA-D545-41B8-919E-A98608EE676D}">
       <formula1>=IF(L822&lt;&gt;"",INDIRECT(VLOOKUP(L822,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N822" xr:uid="{DC934430-6CA7-4C66-8DAF-BEF983B598EC}">
+    <dataValidation type="list" sqref="N822" xr:uid="{029D6CB0-4A1A-4F81-8D5C-12CFE776CF03}">
       <formula1>=IF(M822&lt;&gt;"",INDIRECT(VLOOKUP(M822,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M823" xr:uid="{6C27603A-ED4C-454C-8355-61553337E2D2}">
+    <dataValidation type="list" sqref="M823" xr:uid="{9B6322F2-99B7-48D5-997D-94383BA0FFF7}">
       <formula1>=IF(L823&lt;&gt;"",INDIRECT(VLOOKUP(L823,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N823" xr:uid="{ABFEB9FF-5C5C-415F-9A51-40D665892508}">
+    <dataValidation type="list" sqref="N823" xr:uid="{1AE9F9DF-79CB-48DC-AC0E-7263741EF6A0}">
       <formula1>=IF(M823&lt;&gt;"",INDIRECT(VLOOKUP(M823,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M824" xr:uid="{3852750E-3244-4DF8-8C88-C0B7FD4ABB86}">
+    <dataValidation type="list" sqref="M824" xr:uid="{B8B124E0-9AF1-4D35-8CA0-AA0918E16B51}">
       <formula1>=IF(L824&lt;&gt;"",INDIRECT(VLOOKUP(L824,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N824" xr:uid="{1A9E9EFC-1449-49A7-9AB6-CDCA31084173}">
+    <dataValidation type="list" sqref="N824" xr:uid="{3710D19F-7CBA-45C5-A989-2CA91A21E26E}">
       <formula1>=IF(M824&lt;&gt;"",INDIRECT(VLOOKUP(M824,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M825" xr:uid="{EB62C347-D765-4225-B686-BCD365DBD437}">
+    <dataValidation type="list" sqref="M825" xr:uid="{B5F743DE-A24F-4635-9222-491FABEB0675}">
       <formula1>=IF(L825&lt;&gt;"",INDIRECT(VLOOKUP(L825,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N825" xr:uid="{8EF19AAF-4E6D-4221-9B92-9E0E351FD92C}">
+    <dataValidation type="list" sqref="N825" xr:uid="{ABC69EEE-AC74-4AF3-BED1-325E6B5E6488}">
       <formula1>=IF(M825&lt;&gt;"",INDIRECT(VLOOKUP(M825,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M826" xr:uid="{AB10A777-52EE-41EA-9609-C6035000848B}">
+    <dataValidation type="list" sqref="M826" xr:uid="{1FABB7C6-EF39-4721-A1B5-0FDB8F5158E7}">
       <formula1>=IF(L826&lt;&gt;"",INDIRECT(VLOOKUP(L826,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N826" xr:uid="{1D91FFA5-C5A2-4D31-8374-85045BDF9E84}">
+    <dataValidation type="list" sqref="N826" xr:uid="{D2357350-1A35-4088-A678-E1E774A79F71}">
       <formula1>=IF(M826&lt;&gt;"",INDIRECT(VLOOKUP(M826,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M827" xr:uid="{967EB9BC-5DAE-43DA-8FC6-59B0090547F2}">
+    <dataValidation type="list" sqref="M827" xr:uid="{086CE2B9-7793-4423-8607-574C1853A9CD}">
       <formula1>=IF(L827&lt;&gt;"",INDIRECT(VLOOKUP(L827,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N827" xr:uid="{5580F77B-33B4-40F7-83A2-A3FFAB0B30C7}">
+    <dataValidation type="list" sqref="N827" xr:uid="{3C4F0C29-4F96-4991-B963-A86550CF9438}">
       <formula1>=IF(M827&lt;&gt;"",INDIRECT(VLOOKUP(M827,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M828" xr:uid="{4A3132EF-055B-4F06-AFE0-D8A7F1BC941B}">
+    <dataValidation type="list" sqref="M828" xr:uid="{DC877ED6-D537-417C-BE48-4A5F8B4BAF39}">
       <formula1>=IF(L828&lt;&gt;"",INDIRECT(VLOOKUP(L828,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N828" xr:uid="{D5B69C19-E982-4CEF-B53A-2BAFA24ED6F8}">
+    <dataValidation type="list" sqref="N828" xr:uid="{57A0B2CA-9928-4C04-8C62-923D92B4ED9F}">
       <formula1>=IF(M828&lt;&gt;"",INDIRECT(VLOOKUP(M828,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M829" xr:uid="{AAEBBCAE-1693-4F80-81B6-AFC422A32171}">
+    <dataValidation type="list" sqref="M829" xr:uid="{B6518B2C-B9F3-4764-8E47-E12C3905B4A5}">
       <formula1>=IF(L829&lt;&gt;"",INDIRECT(VLOOKUP(L829,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N829" xr:uid="{81F8FF35-F4B5-4918-838D-ABA41E62BD56}">
+    <dataValidation type="list" sqref="N829" xr:uid="{10B8264E-E741-4A1D-B315-8ED189B22CAD}">
       <formula1>=IF(M829&lt;&gt;"",INDIRECT(VLOOKUP(M829,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M830" xr:uid="{62B8EE5E-4645-4E22-8F7D-CCE9D854551C}">
+    <dataValidation type="list" sqref="M830" xr:uid="{51313527-A6BD-4256-B446-8F339752635C}">
       <formula1>=IF(L830&lt;&gt;"",INDIRECT(VLOOKUP(L830,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N830" xr:uid="{5D8A4D94-6209-4733-B7CE-64CE0D8738AF}">
+    <dataValidation type="list" sqref="N830" xr:uid="{54CE23EC-7A7C-469D-A6B4-78E8D2432D20}">
       <formula1>=IF(M830&lt;&gt;"",INDIRECT(VLOOKUP(M830,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M831" xr:uid="{C722CAC0-9816-42A1-A235-91EE4DDDBAF9}">
+    <dataValidation type="list" sqref="M831" xr:uid="{A7AA5FEE-8A53-4125-A4D4-3239C9715E0F}">
       <formula1>=IF(L831&lt;&gt;"",INDIRECT(VLOOKUP(L831,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N831" xr:uid="{67CFA060-ABBE-49A1-B17D-C41B9594C402}">
+    <dataValidation type="list" sqref="N831" xr:uid="{BC661AFB-B1D8-45E7-9CD3-6633C75D5C2D}">
       <formula1>=IF(M831&lt;&gt;"",INDIRECT(VLOOKUP(M831,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M832" xr:uid="{FA6A5043-D56F-45C4-BECC-D95ABA270A86}">
+    <dataValidation type="list" sqref="M832" xr:uid="{350A04A5-13B9-442B-8C97-20A9F703A9D7}">
       <formula1>=IF(L832&lt;&gt;"",INDIRECT(VLOOKUP(L832,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N832" xr:uid="{514D3560-BDCF-4742-9CC2-98C0B30AD769}">
+    <dataValidation type="list" sqref="N832" xr:uid="{45D508D5-2456-4F78-9CF8-F2EB8A960899}">
       <formula1>=IF(M832&lt;&gt;"",INDIRECT(VLOOKUP(M832,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M833" xr:uid="{90EEC173-A5BB-49EF-8DF5-9A52C77598AE}">
+    <dataValidation type="list" sqref="M833" xr:uid="{513C0652-BE4A-47FA-975C-DF941F71F45E}">
       <formula1>=IF(L833&lt;&gt;"",INDIRECT(VLOOKUP(L833,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N833" xr:uid="{4E2D9A37-A27A-456D-8615-2958BA5CF429}">
+    <dataValidation type="list" sqref="N833" xr:uid="{2301C6FE-A93B-436B-93E8-38F4296B511D}">
       <formula1>=IF(M833&lt;&gt;"",INDIRECT(VLOOKUP(M833,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M834" xr:uid="{6A50C70D-43C4-43AF-BF2D-82B8C815F9E8}">
+    <dataValidation type="list" sqref="M834" xr:uid="{8893676B-DD6F-4F10-A4F3-BF4886F34433}">
       <formula1>=IF(L834&lt;&gt;"",INDIRECT(VLOOKUP(L834,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N834" xr:uid="{100DEFF2-8BD6-481E-B9B6-4C5E79AFE259}">
+    <dataValidation type="list" sqref="N834" xr:uid="{F7F5E3B7-1551-40E3-BEB4-1D45C46A8A04}">
       <formula1>=IF(M834&lt;&gt;"",INDIRECT(VLOOKUP(M834,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M835" xr:uid="{AEA60843-85BF-43A0-8AAC-6C7BE57D93C8}">
+    <dataValidation type="list" sqref="M835" xr:uid="{7E746180-CB52-4650-9A93-7B0DDA6D684C}">
       <formula1>=IF(L835&lt;&gt;"",INDIRECT(VLOOKUP(L835,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N835" xr:uid="{DD6F315F-0B4D-42FB-8678-E83F94C8ABB1}">
+    <dataValidation type="list" sqref="N835" xr:uid="{2785D19F-FE1A-4679-BE2C-72CC5048E135}">
       <formula1>=IF(M835&lt;&gt;"",INDIRECT(VLOOKUP(M835,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M836" xr:uid="{B1B84FBB-15F9-4AAE-803C-E26738A1100C}">
+    <dataValidation type="list" sqref="M836" xr:uid="{51A382D0-69A6-46B3-9581-DDB2BEE2ACA6}">
       <formula1>=IF(L836&lt;&gt;"",INDIRECT(VLOOKUP(L836,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N836" xr:uid="{2DF34141-25CB-4778-B1D0-F7567F118F56}">
+    <dataValidation type="list" sqref="N836" xr:uid="{5A6715A9-88FB-422E-988C-23A86EBD024F}">
       <formula1>=IF(M836&lt;&gt;"",INDIRECT(VLOOKUP(M836,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M837" xr:uid="{2A6C62D8-5279-417E-8F25-EC2C7C478BF6}">
+    <dataValidation type="list" sqref="M837" xr:uid="{A56C2120-13CB-4521-BDE8-DFDB2705A080}">
       <formula1>=IF(L837&lt;&gt;"",INDIRECT(VLOOKUP(L837,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N837" xr:uid="{B39139CF-3D70-430C-B247-F19DD6E34C42}">
+    <dataValidation type="list" sqref="N837" xr:uid="{27E25B80-A821-45E8-A3C2-8CC66A4D329F}">
       <formula1>=IF(M837&lt;&gt;"",INDIRECT(VLOOKUP(M837,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M838" xr:uid="{4C74C768-982D-4D9F-AFB5-1329A10AB92F}">
+    <dataValidation type="list" sqref="M838" xr:uid="{CB9E6D2E-1768-4849-8D8A-5F95C90E84FE}">
       <formula1>=IF(L838&lt;&gt;"",INDIRECT(VLOOKUP(L838,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N838" xr:uid="{51A8D3FE-CA62-49A1-A555-4B1AD757B611}">
+    <dataValidation type="list" sqref="N838" xr:uid="{5D2C6A3A-2B6A-4A90-9D51-F34AE3D968F3}">
       <formula1>=IF(M838&lt;&gt;"",INDIRECT(VLOOKUP(M838,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M839" xr:uid="{D407E649-B568-42E8-9DDC-407609507C49}">
+    <dataValidation type="list" sqref="M839" xr:uid="{99DCE2C2-90E6-477D-9F5C-9A4E577B2FC0}">
       <formula1>=IF(L839&lt;&gt;"",INDIRECT(VLOOKUP(L839,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N839" xr:uid="{02F61EC9-FEA4-4CD8-99B6-3A7D8DEE66AD}">
+    <dataValidation type="list" sqref="N839" xr:uid="{65CC12D2-75F5-4330-BD99-E38012EE3D20}">
       <formula1>=IF(M839&lt;&gt;"",INDIRECT(VLOOKUP(M839,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M840" xr:uid="{74D6648C-7A8B-43DD-A298-9D34BEB68543}">
+    <dataValidation type="list" sqref="M840" xr:uid="{C5FC7414-7217-45B6-AA5F-909AFF67F4CC}">
       <formula1>=IF(L840&lt;&gt;"",INDIRECT(VLOOKUP(L840,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N840" xr:uid="{E12BDF5D-4F47-45DF-AA6F-17A136A0B857}">
+    <dataValidation type="list" sqref="N840" xr:uid="{51850B36-216A-4122-9993-29B9A62F7E96}">
       <formula1>=IF(M840&lt;&gt;"",INDIRECT(VLOOKUP(M840,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M841" xr:uid="{9D4350E6-E84B-4339-888D-0018F7DE839D}">
+    <dataValidation type="list" sqref="M841" xr:uid="{7A31CC96-3946-4630-B302-885402097F7A}">
       <formula1>=IF(L841&lt;&gt;"",INDIRECT(VLOOKUP(L841,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N841" xr:uid="{BBC23312-E611-476C-90D1-F87362B95A22}">
+    <dataValidation type="list" sqref="N841" xr:uid="{D535A818-0831-42B3-9433-A3CA56755569}">
       <formula1>=IF(M841&lt;&gt;"",INDIRECT(VLOOKUP(M841,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M842" xr:uid="{5AB8FF47-5D67-4447-A6D8-0265954563FF}">
+    <dataValidation type="list" sqref="M842" xr:uid="{EF922D74-A436-4BD6-B04D-013C1EB41FC9}">
       <formula1>=IF(L842&lt;&gt;"",INDIRECT(VLOOKUP(L842,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N842" xr:uid="{709587B7-327B-449B-AC94-83B9238A660E}">
+    <dataValidation type="list" sqref="N842" xr:uid="{87CC1FCC-6A03-4CBB-A021-62F234CA641A}">
       <formula1>=IF(M842&lt;&gt;"",INDIRECT(VLOOKUP(M842,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M843" xr:uid="{2C4BEBD2-C97F-4C53-A595-A4CA922FA374}">
+    <dataValidation type="list" sqref="M843" xr:uid="{6E6FACA1-4F2A-49AE-8A06-A72B879EA97E}">
       <formula1>=IF(L843&lt;&gt;"",INDIRECT(VLOOKUP(L843,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N843" xr:uid="{7F45B511-CEB4-4907-B510-8D61B7FF14AA}">
+    <dataValidation type="list" sqref="N843" xr:uid="{4E270103-6F32-412F-B77A-69C9FD6A5CD5}">
       <formula1>=IF(M843&lt;&gt;"",INDIRECT(VLOOKUP(M843,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M844" xr:uid="{1BBDCE71-4ABD-4D36-BB25-6377B5415165}">
+    <dataValidation type="list" sqref="M844" xr:uid="{39D98B2A-02DC-4046-8DD6-390C2FD256C4}">
       <formula1>=IF(L844&lt;&gt;"",INDIRECT(VLOOKUP(L844,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N844" xr:uid="{7B591229-6843-44E5-9333-37AFFF5FECE8}">
+    <dataValidation type="list" sqref="N844" xr:uid="{6392A718-1A0E-4268-8744-978C2C606473}">
       <formula1>=IF(M844&lt;&gt;"",INDIRECT(VLOOKUP(M844,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M845" xr:uid="{F89A0CEF-75D8-4E39-A648-058419B5A6EB}">
+    <dataValidation type="list" sqref="M845" xr:uid="{C5AB672C-EF1E-443B-9446-9C38324952CC}">
       <formula1>=IF(L845&lt;&gt;"",INDIRECT(VLOOKUP(L845,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N845" xr:uid="{DDF4BFDA-05FE-4D2B-9E6E-94000C7533DE}">
+    <dataValidation type="list" sqref="N845" xr:uid="{5BE54773-FBC7-4210-9E86-A9D4456E3635}">
       <formula1>=IF(M845&lt;&gt;"",INDIRECT(VLOOKUP(M845,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M846" xr:uid="{F6F19C3D-9B05-4F58-BA40-5242F1A8C8FB}">
+    <dataValidation type="list" sqref="M846" xr:uid="{2427C835-B3F2-41B5-8CF0-9CBE800F016F}">
       <formula1>=IF(L846&lt;&gt;"",INDIRECT(VLOOKUP(L846,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N846" xr:uid="{E5DB1B19-04A5-4C97-859C-C66FE3CEB87E}">
+    <dataValidation type="list" sqref="N846" xr:uid="{28BBCA3C-B315-4EC1-92FB-DD2710466B8B}">
       <formula1>=IF(M846&lt;&gt;"",INDIRECT(VLOOKUP(M846,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M847" xr:uid="{294A8965-741B-488A-9F83-6176165EC6DF}">
+    <dataValidation type="list" sqref="M847" xr:uid="{C9E3167E-AED4-4BD4-89F9-0E15BB0E6B40}">
       <formula1>=IF(L847&lt;&gt;"",INDIRECT(VLOOKUP(L847,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N847" xr:uid="{5AFCCE1A-D381-4B94-8DF1-143EBCB6AA19}">
+    <dataValidation type="list" sqref="N847" xr:uid="{9E279A25-B41A-4D68-B787-D6E9A72553A1}">
       <formula1>=IF(M847&lt;&gt;"",INDIRECT(VLOOKUP(M847,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M848" xr:uid="{BB2C50EE-082C-42A9-8B40-5B184FE3F75A}">
+    <dataValidation type="list" sqref="M848" xr:uid="{5FCB5375-7C35-43FF-A170-36E531453B5C}">
       <formula1>=IF(L848&lt;&gt;"",INDIRECT(VLOOKUP(L848,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N848" xr:uid="{1BD7BAB5-EFA4-42C7-8635-372942DFE26D}">
+    <dataValidation type="list" sqref="N848" xr:uid="{3D2ABD58-5DE7-4BF2-BD73-77A4EC88FBA6}">
       <formula1>=IF(M848&lt;&gt;"",INDIRECT(VLOOKUP(M848,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M849" xr:uid="{A74029CD-CE1F-4156-98A8-7C9E7A8A15B5}">
+    <dataValidation type="list" sqref="M849" xr:uid="{D082AA93-4EDD-478D-A4F4-428D45C58E8B}">
       <formula1>=IF(L849&lt;&gt;"",INDIRECT(VLOOKUP(L849,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N849" xr:uid="{75E99E1C-5211-42ED-9373-3D31FE198711}">
+    <dataValidation type="list" sqref="N849" xr:uid="{A4659A13-A305-4243-A655-A819BBC61A8E}">
       <formula1>=IF(M849&lt;&gt;"",INDIRECT(VLOOKUP(M849,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M850" xr:uid="{0C96E26A-AFD0-456D-99BB-7E87AB4D512A}">
+    <dataValidation type="list" sqref="M850" xr:uid="{E4646D9B-2807-42B0-B9CB-D218089ACFE0}">
       <formula1>=IF(L850&lt;&gt;"",INDIRECT(VLOOKUP(L850,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N850" xr:uid="{FD0FDE22-59DC-4BA4-B491-4123C9C3ADD4}">
+    <dataValidation type="list" sqref="N850" xr:uid="{BC2ABF3A-E59F-4A64-9566-1467955ACCE4}">
       <formula1>=IF(M850&lt;&gt;"",INDIRECT(VLOOKUP(M850,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M851" xr:uid="{CA7ECCAC-2430-4177-B5C3-5AC2D514AE6D}">
+    <dataValidation type="list" sqref="M851" xr:uid="{7F90F9CC-CB81-4E9B-AE06-3D73838A9DD0}">
       <formula1>=IF(L851&lt;&gt;"",INDIRECT(VLOOKUP(L851,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N851" xr:uid="{55BAEAB4-D157-4A66-BAFF-734EC816B377}">
+    <dataValidation type="list" sqref="N851" xr:uid="{76FAB719-56C4-4B7F-BC6C-B4B23D8E69B1}">
       <formula1>=IF(M851&lt;&gt;"",INDIRECT(VLOOKUP(M851,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M852" xr:uid="{21832D7D-13DF-4008-83D4-C6293DFB4C90}">
+    <dataValidation type="list" sqref="M852" xr:uid="{6E885FDD-71B3-45AE-A40E-3AA2BDCEFC53}">
       <formula1>=IF(L852&lt;&gt;"",INDIRECT(VLOOKUP(L852,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N852" xr:uid="{7A23D98E-38A0-4C17-9C78-A59A515BC11A}">
+    <dataValidation type="list" sqref="N852" xr:uid="{007AE2C7-68BD-4CDA-9801-2B4D7FC7B932}">
       <formula1>=IF(M852&lt;&gt;"",INDIRECT(VLOOKUP(M852,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M853" xr:uid="{A43D1AE0-19E7-4E48-AA5F-D60FBE6B5A50}">
+    <dataValidation type="list" sqref="M853" xr:uid="{01A96E19-0073-4525-9766-3B9EB797DFC8}">
       <formula1>=IF(L853&lt;&gt;"",INDIRECT(VLOOKUP(L853,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N853" xr:uid="{5FD1834D-BC82-44D8-AA25-FD51177E09C2}">
+    <dataValidation type="list" sqref="N853" xr:uid="{EB52A18B-DA49-4CAC-B401-3A2DC0719F8C}">
       <formula1>=IF(M853&lt;&gt;"",INDIRECT(VLOOKUP(M853,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M854" xr:uid="{0DA571ED-7FCD-47FF-8983-911296D77CF4}">
+    <dataValidation type="list" sqref="M854" xr:uid="{E1233DFD-CC40-4EB7-AF66-87D8CC507E37}">
       <formula1>=IF(L854&lt;&gt;"",INDIRECT(VLOOKUP(L854,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N854" xr:uid="{62F2243E-D0D1-46B6-8697-070957FCBF74}">
+    <dataValidation type="list" sqref="N854" xr:uid="{5316F17D-F798-4A29-AAA0-6AD180758B7B}">
       <formula1>=IF(M854&lt;&gt;"",INDIRECT(VLOOKUP(M854,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M855" xr:uid="{B17E65AA-D457-4E0B-9733-52B24F578EA4}">
+    <dataValidation type="list" sqref="M855" xr:uid="{BC828A00-D12E-4DB7-9ED3-11D1BCE8230E}">
       <formula1>=IF(L855&lt;&gt;"",INDIRECT(VLOOKUP(L855,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N855" xr:uid="{1CAF082F-7EF1-4E73-A4ED-62E50DD5B49E}">
+    <dataValidation type="list" sqref="N855" xr:uid="{25F44F85-8426-4597-9D98-5DEEBC85D1EF}">
       <formula1>=IF(M855&lt;&gt;"",INDIRECT(VLOOKUP(M855,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M856" xr:uid="{71884350-A6FE-4F59-88BB-684396F8A865}">
+    <dataValidation type="list" sqref="M856" xr:uid="{B2165D94-C367-4042-9963-A703E8EE912B}">
       <formula1>=IF(L856&lt;&gt;"",INDIRECT(VLOOKUP(L856,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N856" xr:uid="{EA272701-9A1D-442E-8D8D-2A82391BF096}">
+    <dataValidation type="list" sqref="N856" xr:uid="{40222962-A313-457A-B730-03781D739A08}">
       <formula1>=IF(M856&lt;&gt;"",INDIRECT(VLOOKUP(M856,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M857" xr:uid="{0564308B-9C62-40F3-B43C-6D34864095A2}">
+    <dataValidation type="list" sqref="M857" xr:uid="{2F14050E-8216-44A1-9919-F82D308AE6E4}">
       <formula1>=IF(L857&lt;&gt;"",INDIRECT(VLOOKUP(L857,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N857" xr:uid="{2E837504-9A7B-45C8-A629-8335BB975343}">
+    <dataValidation type="list" sqref="N857" xr:uid="{FABAAB0A-DF8B-4CD2-81B4-0BE8C81331A1}">
       <formula1>=IF(M857&lt;&gt;"",INDIRECT(VLOOKUP(M857,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M858" xr:uid="{ECD417F1-1B48-4F01-9D0B-387948687CFB}">
+    <dataValidation type="list" sqref="M858" xr:uid="{641E555C-3531-48ED-8992-37A0A84E50F4}">
       <formula1>=IF(L858&lt;&gt;"",INDIRECT(VLOOKUP(L858,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N858" xr:uid="{4C97E7C2-C66E-49B0-BA67-D7405795B06B}">
+    <dataValidation type="list" sqref="N858" xr:uid="{77742737-D8AE-46F6-9C55-1575C247ED68}">
       <formula1>=IF(M858&lt;&gt;"",INDIRECT(VLOOKUP(M858,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M859" xr:uid="{2B4D7CD8-695F-4F5B-B5BB-2DC9090CF1D7}">
+    <dataValidation type="list" sqref="M859" xr:uid="{729ADAC1-CFDC-462C-B40B-4163D182093C}">
       <formula1>=IF(L859&lt;&gt;"",INDIRECT(VLOOKUP(L859,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N859" xr:uid="{6D462489-D856-4EB4-B808-75DC9CD2DE70}">
+    <dataValidation type="list" sqref="N859" xr:uid="{DAFB52B2-32D8-4637-A30C-910BF98F03DF}">
       <formula1>=IF(M859&lt;&gt;"",INDIRECT(VLOOKUP(M859,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M860" xr:uid="{83CCB79B-6968-40C5-8F7C-F96EC1F9B5CE}">
+    <dataValidation type="list" sqref="M860" xr:uid="{D3B4282D-7673-448E-A6F1-A87BA6B474D5}">
       <formula1>=IF(L860&lt;&gt;"",INDIRECT(VLOOKUP(L860,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N860" xr:uid="{0CC76A37-8311-4D72-8F0D-F66CF2F4685D}">
+    <dataValidation type="list" sqref="N860" xr:uid="{E9F6C8F2-01C5-46F0-8A11-17265FC2AF2C}">
       <formula1>=IF(M860&lt;&gt;"",INDIRECT(VLOOKUP(M860,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M861" xr:uid="{198E07A8-4DD9-435B-816E-AE942268E345}">
+    <dataValidation type="list" sqref="M861" xr:uid="{FC898A86-A806-43E6-BFDD-634B3DB13786}">
       <formula1>=IF(L861&lt;&gt;"",INDIRECT(VLOOKUP(L861,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N861" xr:uid="{7FD94C4B-40CF-4AEE-B312-1002C6CD9579}">
+    <dataValidation type="list" sqref="N861" xr:uid="{FB5A8557-0065-4265-ABE5-9BAB62C93337}">
       <formula1>=IF(M861&lt;&gt;"",INDIRECT(VLOOKUP(M861,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M862" xr:uid="{C91823C1-3483-4EBB-A49B-5880B0D1131B}">
+    <dataValidation type="list" sqref="M862" xr:uid="{A62CA6FC-90C1-4F71-9160-1A76FF248F1C}">
       <formula1>=IF(L862&lt;&gt;"",INDIRECT(VLOOKUP(L862,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N862" xr:uid="{DE440AAD-0B09-4667-9506-FFC0A69CBD80}">
+    <dataValidation type="list" sqref="N862" xr:uid="{ECA001ED-2906-440D-9752-E0B2245FB0D5}">
       <formula1>=IF(M862&lt;&gt;"",INDIRECT(VLOOKUP(M862,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M863" xr:uid="{43964B6C-2698-4F9D-8BF2-837261304E34}">
+    <dataValidation type="list" sqref="M863" xr:uid="{40A98657-E113-496C-99F7-BC2BA738E17A}">
       <formula1>=IF(L863&lt;&gt;"",INDIRECT(VLOOKUP(L863,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N863" xr:uid="{10ABD271-282C-4C73-8171-B47C90CCC91F}">
+    <dataValidation type="list" sqref="N863" xr:uid="{7385CA58-889F-4A6E-9710-141EB5601100}">
       <formula1>=IF(M863&lt;&gt;"",INDIRECT(VLOOKUP(M863,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M864" xr:uid="{37DC3216-31E4-4792-97EE-3B288C8DDEB8}">
+    <dataValidation type="list" sqref="M864" xr:uid="{4E2BC572-E7A4-4522-9C3B-91EB6540C9B6}">
       <formula1>=IF(L864&lt;&gt;"",INDIRECT(VLOOKUP(L864,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N864" xr:uid="{5FA287A6-4C7E-4577-B923-948924E52F74}">
+    <dataValidation type="list" sqref="N864" xr:uid="{317C6A07-373D-4A52-A0DF-7DBB2C81C87C}">
       <formula1>=IF(M864&lt;&gt;"",INDIRECT(VLOOKUP(M864,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M865" xr:uid="{36E123CF-2DF7-478C-8595-D45138A0448A}">
+    <dataValidation type="list" sqref="M865" xr:uid="{DFA300F0-707E-4EFF-82FA-95C52B168FF8}">
       <formula1>=IF(L865&lt;&gt;"",INDIRECT(VLOOKUP(L865,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N865" xr:uid="{3492C3E3-4C56-4DBD-9DA0-ACC31A306BCC}">
+    <dataValidation type="list" sqref="N865" xr:uid="{3FDE8A52-339E-44C9-8FF7-D9FC9B012648}">
       <formula1>=IF(M865&lt;&gt;"",INDIRECT(VLOOKUP(M865,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M866" xr:uid="{FDAF3BC5-4225-443C-BE55-0386F1EDF865}">
+    <dataValidation type="list" sqref="M866" xr:uid="{248452FA-1B43-4424-9FA5-2A913D5AE82B}">
       <formula1>=IF(L866&lt;&gt;"",INDIRECT(VLOOKUP(L866,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N866" xr:uid="{D29841CC-976E-4563-BCDA-DFFDD36C481C}">
+    <dataValidation type="list" sqref="N866" xr:uid="{B13A9CD2-2924-438E-80D3-235B85327160}">
       <formula1>=IF(M866&lt;&gt;"",INDIRECT(VLOOKUP(M866,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M867" xr:uid="{9E5F8B6A-61E1-400C-8ACC-CDF9ADDA3CEB}">
+    <dataValidation type="list" sqref="M867" xr:uid="{2CF9C28E-CB4F-4E8F-8EC0-3B12BF6BB4A3}">
       <formula1>=IF(L867&lt;&gt;"",INDIRECT(VLOOKUP(L867,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N867" xr:uid="{63BF5DC3-ED2B-4640-9EDF-C09316C18463}">
+    <dataValidation type="list" sqref="N867" xr:uid="{BBB1489F-725B-4F6A-8224-7B6625C2D1A9}">
       <formula1>=IF(M867&lt;&gt;"",INDIRECT(VLOOKUP(M867,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M868" xr:uid="{9AE849DB-5184-4E37-973E-628783F7B4B6}">
+    <dataValidation type="list" sqref="M868" xr:uid="{4360E30C-8E82-4CA9-BC3C-FE954A713AAD}">
       <formula1>=IF(L868&lt;&gt;"",INDIRECT(VLOOKUP(L868,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N868" xr:uid="{B4B694FE-1168-46B2-ADD3-346CF277826C}">
+    <dataValidation type="list" sqref="N868" xr:uid="{72600C90-B9BD-4ECC-8A58-3B4DD06FD7E2}">
       <formula1>=IF(M868&lt;&gt;"",INDIRECT(VLOOKUP(M868,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M869" xr:uid="{00ADCA74-E609-4DA1-B6BE-D2E1746A60F9}">
+    <dataValidation type="list" sqref="M869" xr:uid="{21B9C290-3090-4B74-B4FC-896C55B024F3}">
       <formula1>=IF(L869&lt;&gt;"",INDIRECT(VLOOKUP(L869,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N869" xr:uid="{9FBB1D6C-E078-4F44-B695-15E5C72864E5}">
+    <dataValidation type="list" sqref="N869" xr:uid="{4ECF825C-C6A0-4D57-BAC8-C50388D9B75E}">
       <formula1>=IF(M869&lt;&gt;"",INDIRECT(VLOOKUP(M869,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M870" xr:uid="{E28870E2-AE6E-4E85-BC27-CD754B2833A4}">
+    <dataValidation type="list" sqref="M870" xr:uid="{BE21281D-7048-47E9-A15C-989FB31EBB40}">
       <formula1>=IF(L870&lt;&gt;"",INDIRECT(VLOOKUP(L870,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N870" xr:uid="{5D05D0D2-778C-4402-9A1F-B9C48A9B30CC}">
+    <dataValidation type="list" sqref="N870" xr:uid="{7BD6D25D-65FD-48DE-ABB4-FA0DDEBCD4D4}">
       <formula1>=IF(M870&lt;&gt;"",INDIRECT(VLOOKUP(M870,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M871" xr:uid="{E19C8E98-B75A-49EE-9FCC-2E3AAB3148C9}">
+    <dataValidation type="list" sqref="M871" xr:uid="{23785C9A-9DCA-47CC-8BF8-C7C45581C217}">
       <formula1>=IF(L871&lt;&gt;"",INDIRECT(VLOOKUP(L871,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N871" xr:uid="{917AAE88-CE75-471C-8FC4-35D93E9A6509}">
+    <dataValidation type="list" sqref="N871" xr:uid="{ADD9A077-ECB9-418C-BE07-A54A1EDEE609}">
       <formula1>=IF(M871&lt;&gt;"",INDIRECT(VLOOKUP(M871,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M872" xr:uid="{0776A2E3-D0EE-4F36-8432-E4B9D71568C6}">
+    <dataValidation type="list" sqref="M872" xr:uid="{0A8AC9C6-17B8-40D9-9B82-CA59E8CA3D66}">
       <formula1>=IF(L872&lt;&gt;"",INDIRECT(VLOOKUP(L872,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N872" xr:uid="{8CF2FBD7-7DCB-4ED9-BCB4-3E92900FAF89}">
+    <dataValidation type="list" sqref="N872" xr:uid="{40D74056-6473-4B51-9840-7DE6E3C0BAAB}">
       <formula1>=IF(M872&lt;&gt;"",INDIRECT(VLOOKUP(M872,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M873" xr:uid="{58626F35-C09C-4F65-9645-786F7928E72C}">
+    <dataValidation type="list" sqref="M873" xr:uid="{1700FAA1-F223-4170-9ADB-C0F25F0E12EC}">
       <formula1>=IF(L873&lt;&gt;"",INDIRECT(VLOOKUP(L873,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N873" xr:uid="{B5B9C585-BAAA-4A27-8310-C92982F463D0}">
+    <dataValidation type="list" sqref="N873" xr:uid="{F19CB4A8-EB6E-4B64-8AB4-A6857C2390D5}">
       <formula1>=IF(M873&lt;&gt;"",INDIRECT(VLOOKUP(M873,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M874" xr:uid="{5B9288BB-879D-48C3-BF89-55A34DA046E3}">
+    <dataValidation type="list" sqref="M874" xr:uid="{E35528C6-8A9B-4017-A2CF-10FA5ADC6D21}">
       <formula1>=IF(L874&lt;&gt;"",INDIRECT(VLOOKUP(L874,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N874" xr:uid="{2BA70A32-9FE0-470F-B879-E1A2760186EE}">
+    <dataValidation type="list" sqref="N874" xr:uid="{92551FA3-2B36-44F8-9884-4EA543151B7E}">
       <formula1>=IF(M874&lt;&gt;"",INDIRECT(VLOOKUP(M874,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M875" xr:uid="{B5A22B96-0AD4-4243-ADED-944889A06EC8}">
+    <dataValidation type="list" sqref="M875" xr:uid="{50306291-8888-49E8-9049-48C014B8E0FE}">
       <formula1>=IF(L875&lt;&gt;"",INDIRECT(VLOOKUP(L875,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N875" xr:uid="{9B5E6B8E-FA81-485F-A2D4-49917566EDD1}">
+    <dataValidation type="list" sqref="N875" xr:uid="{4868CD6E-DD78-4089-B76E-FBA4FFA97665}">
       <formula1>=IF(M875&lt;&gt;"",INDIRECT(VLOOKUP(M875,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M876" xr:uid="{6210063A-F040-47FD-9E6B-D2622F549BF1}">
+    <dataValidation type="list" sqref="M876" xr:uid="{C53FCA43-6182-4448-9D23-753E7061BE91}">
       <formula1>=IF(L876&lt;&gt;"",INDIRECT(VLOOKUP(L876,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N876" xr:uid="{2EB01E64-69F1-47B6-AADF-617BA0295E5A}">
+    <dataValidation type="list" sqref="N876" xr:uid="{BF6222BA-B75D-455B-AD29-61C26E01D0A9}">
       <formula1>=IF(M876&lt;&gt;"",INDIRECT(VLOOKUP(M876,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M877" xr:uid="{B93735D4-ABB5-4FC2-9285-CB7E9CB47193}">
+    <dataValidation type="list" sqref="M877" xr:uid="{3A0F809F-3E4D-40C9-8E0A-294BD469D580}">
       <formula1>=IF(L877&lt;&gt;"",INDIRECT(VLOOKUP(L877,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N877" xr:uid="{95F37827-15C0-44C6-B8BC-BDF077AEE824}">
+    <dataValidation type="list" sqref="N877" xr:uid="{A38ADA68-9BA9-4D42-B9B1-4717F26430C4}">
       <formula1>=IF(M877&lt;&gt;"",INDIRECT(VLOOKUP(M877,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M878" xr:uid="{1F4EE7B0-1B74-4EB5-8C74-A353FA99513D}">
+    <dataValidation type="list" sqref="M878" xr:uid="{204F056B-92EC-45C4-91E8-683FC8B303BE}">
       <formula1>=IF(L878&lt;&gt;"",INDIRECT(VLOOKUP(L878,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N878" xr:uid="{AC83CE00-FF55-4D0E-92ED-45131F50E8F3}">
+    <dataValidation type="list" sqref="N878" xr:uid="{A070B7A8-AB79-4169-89B3-0A2EC6ADE768}">
       <formula1>=IF(M878&lt;&gt;"",INDIRECT(VLOOKUP(M878,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M879" xr:uid="{B205B40E-3FCB-44E0-B8AA-CC2FEB830908}">
+    <dataValidation type="list" sqref="M879" xr:uid="{5C37CCBF-BA70-4539-8541-03D1F9EBEFB6}">
       <formula1>=IF(L879&lt;&gt;"",INDIRECT(VLOOKUP(L879,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N879" xr:uid="{A9987C02-0A69-440C-ACCD-D262FE824CE3}">
+    <dataValidation type="list" sqref="N879" xr:uid="{0CDA37EA-1254-49D7-BE47-E3642E942710}">
       <formula1>=IF(M879&lt;&gt;"",INDIRECT(VLOOKUP(M879,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M880" xr:uid="{7085973E-49DC-4DDF-942F-93FABE9D0ACD}">
+    <dataValidation type="list" sqref="M880" xr:uid="{1E427F52-9473-4E8F-829B-28B6263FD140}">
       <formula1>=IF(L880&lt;&gt;"",INDIRECT(VLOOKUP(L880,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N880" xr:uid="{74C55128-11FF-48DC-ADB8-C007B3D26D98}">
+    <dataValidation type="list" sqref="N880" xr:uid="{68FAD24E-53B2-4FD9-87BF-2AE34B2A43E0}">
       <formula1>=IF(M880&lt;&gt;"",INDIRECT(VLOOKUP(M880,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M881" xr:uid="{CAF33BBB-A10F-48AD-AE02-A381D25052FF}">
+    <dataValidation type="list" sqref="M881" xr:uid="{754AF753-41E8-4468-B0FC-6BD97FAC6878}">
       <formula1>=IF(L881&lt;&gt;"",INDIRECT(VLOOKUP(L881,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N881" xr:uid="{92F4C03D-F2BC-4A82-B2F0-A965874C9A92}">
+    <dataValidation type="list" sqref="N881" xr:uid="{0B5E050D-E501-4EC9-90D3-04197F557D2E}">
       <formula1>=IF(M881&lt;&gt;"",INDIRECT(VLOOKUP(M881,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M882" xr:uid="{634CD5E1-89D3-4825-92D4-0C133322AA84}">
+    <dataValidation type="list" sqref="M882" xr:uid="{8DD04FFF-C4D8-4942-B04E-50E7D198929A}">
       <formula1>=IF(L882&lt;&gt;"",INDIRECT(VLOOKUP(L882,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N882" xr:uid="{A4918058-C599-49FF-BDB0-CA67816E78BE}">
+    <dataValidation type="list" sqref="N882" xr:uid="{02F3CA27-5F46-44D4-B521-52D01745FCD3}">
       <formula1>=IF(M882&lt;&gt;"",INDIRECT(VLOOKUP(M882,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M883" xr:uid="{FFE2E70A-165B-4D9D-84C6-63FAD5F22562}">
+    <dataValidation type="list" sqref="M883" xr:uid="{69DF4DDE-4457-4CE7-81FF-C645EBE03C9F}">
       <formula1>=IF(L883&lt;&gt;"",INDIRECT(VLOOKUP(L883,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N883" xr:uid="{2205113F-2348-42A6-B464-B7C3B5D6D466}">
+    <dataValidation type="list" sqref="N883" xr:uid="{038EB2A4-C57A-4DCB-94D2-E68311336D11}">
       <formula1>=IF(M883&lt;&gt;"",INDIRECT(VLOOKUP(M883,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M884" xr:uid="{92C11869-B7C7-4260-ABF2-82FC26EC4592}">
+    <dataValidation type="list" sqref="M884" xr:uid="{A4FD9AA5-E32D-45A8-96E0-FE30FA68674A}">
       <formula1>=IF(L884&lt;&gt;"",INDIRECT(VLOOKUP(L884,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N884" xr:uid="{9BC0CF68-7B22-4E2D-B28E-B2CF37998F55}">
+    <dataValidation type="list" sqref="N884" xr:uid="{1D1214CC-E8E6-4C00-A397-07A7E1A70D45}">
       <formula1>=IF(M884&lt;&gt;"",INDIRECT(VLOOKUP(M884,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M885" xr:uid="{43402D67-1D80-43EB-8D91-430B37FF3BF3}">
+    <dataValidation type="list" sqref="M885" xr:uid="{F940E992-3B6B-4DF4-87DD-FD6707C27ED5}">
       <formula1>=IF(L885&lt;&gt;"",INDIRECT(VLOOKUP(L885,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N885" xr:uid="{CA96C6B0-6680-4B14-A496-57891AB2244F}">
+    <dataValidation type="list" sqref="N885" xr:uid="{5D71343F-BA7A-4158-8D50-BD191F511F59}">
       <formula1>=IF(M885&lt;&gt;"",INDIRECT(VLOOKUP(M885,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M886" xr:uid="{3D39493F-35BA-4999-8270-0531D3E6D050}">
+    <dataValidation type="list" sqref="M886" xr:uid="{E2D8D6BC-71B5-49E8-B0DC-9F1379270114}">
       <formula1>=IF(L886&lt;&gt;"",INDIRECT(VLOOKUP(L886,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N886" xr:uid="{F89AC0F8-36F0-4E91-A62B-A456C2179391}">
+    <dataValidation type="list" sqref="N886" xr:uid="{9686DA40-A69A-4D72-976D-21B1907FCB17}">
       <formula1>=IF(M886&lt;&gt;"",INDIRECT(VLOOKUP(M886,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M887" xr:uid="{D30B2738-4A05-4FA1-B729-C94FF5049535}">
+    <dataValidation type="list" sqref="M887" xr:uid="{28020D6F-5047-4071-9D70-2F5D6F88B2AE}">
       <formula1>=IF(L887&lt;&gt;"",INDIRECT(VLOOKUP(L887,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N887" xr:uid="{B3F94F47-2961-46D9-8BC0-053D8DFA7A70}">
+    <dataValidation type="list" sqref="N887" xr:uid="{D971E0A8-F9AC-49FE-8862-31204E055685}">
       <formula1>=IF(M887&lt;&gt;"",INDIRECT(VLOOKUP(M887,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M888" xr:uid="{775AE19E-8706-47FF-9EA5-611266ED94B6}">
+    <dataValidation type="list" sqref="M888" xr:uid="{2925334D-9F15-446C-889E-1A1417CD312B}">
       <formula1>=IF(L888&lt;&gt;"",INDIRECT(VLOOKUP(L888,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N888" xr:uid="{6722D4DB-86D5-4205-85BB-12C5CC8E0C9D}">
+    <dataValidation type="list" sqref="N888" xr:uid="{C7A36C4E-273B-4211-808F-DBBF252D188A}">
       <formula1>=IF(M888&lt;&gt;"",INDIRECT(VLOOKUP(M888,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M889" xr:uid="{7EAE27DB-C429-4D67-8AE5-63AF563A9DFB}">
+    <dataValidation type="list" sqref="M889" xr:uid="{3E108D80-A8B3-4BFB-AF3D-E6338EAA2E24}">
       <formula1>=IF(L889&lt;&gt;"",INDIRECT(VLOOKUP(L889,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N889" xr:uid="{D4FFA5F2-3DE0-4949-958A-6ADAFEC3C2DD}">
+    <dataValidation type="list" sqref="N889" xr:uid="{F2A9A216-9BA1-4F79-BBEB-C2CEE1A67485}">
       <formula1>=IF(M889&lt;&gt;"",INDIRECT(VLOOKUP(M889,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M890" xr:uid="{C2D5F5E9-CA8B-4E67-A84B-1D9D72FF69BD}">
+    <dataValidation type="list" sqref="M890" xr:uid="{0525005A-30A3-41DE-82B1-22292CFE5CA0}">
       <formula1>=IF(L890&lt;&gt;"",INDIRECT(VLOOKUP(L890,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N890" xr:uid="{15E17319-02E0-4E09-9D35-88E1671334F6}">
+    <dataValidation type="list" sqref="N890" xr:uid="{C6E6E799-21C8-4552-8042-4CE4465E97D5}">
       <formula1>=IF(M890&lt;&gt;"",INDIRECT(VLOOKUP(M890,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M891" xr:uid="{B0F9BE4F-DCDA-49BD-BBF7-F08393F0DFD6}">
+    <dataValidation type="list" sqref="M891" xr:uid="{AFE4F735-2D4E-490E-82B6-B9ACAAF5879D}">
       <formula1>=IF(L891&lt;&gt;"",INDIRECT(VLOOKUP(L891,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N891" xr:uid="{73FD3823-072E-439E-AF07-A2B13DE66D11}">
+    <dataValidation type="list" sqref="N891" xr:uid="{222E5FE4-56BB-439C-A0EC-6B6E2F7C9871}">
       <formula1>=IF(M891&lt;&gt;"",INDIRECT(VLOOKUP(M891,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M892" xr:uid="{26F3D8D4-63CB-4FA4-BC67-D7024095DADA}">
+    <dataValidation type="list" sqref="M892" xr:uid="{650DF9A9-D7D7-4422-AE37-196A1939C18F}">
       <formula1>=IF(L892&lt;&gt;"",INDIRECT(VLOOKUP(L892,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N892" xr:uid="{03162067-B69E-4A3B-8102-92671CE12A45}">
+    <dataValidation type="list" sqref="N892" xr:uid="{A4087F36-D71C-4AEC-9BE6-B93A7AA572BD}">
       <formula1>=IF(M892&lt;&gt;"",INDIRECT(VLOOKUP(M892,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M893" xr:uid="{9E5380B0-4A07-4E80-A53E-4D5FE08D4F05}">
+    <dataValidation type="list" sqref="M893" xr:uid="{417B4624-6E38-46AB-9A56-FBD6A3678D52}">
       <formula1>=IF(L893&lt;&gt;"",INDIRECT(VLOOKUP(L893,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N893" xr:uid="{9017BCCB-14AA-4C59-8FDD-3982FDEADBD4}">
+    <dataValidation type="list" sqref="N893" xr:uid="{59ADC711-AA5B-4A3A-9ED4-57A1DD064DAC}">
       <formula1>=IF(M893&lt;&gt;"",INDIRECT(VLOOKUP(M893,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M894" xr:uid="{2789514B-0058-4314-91A7-A7D6A14DEE22}">
+    <dataValidation type="list" sqref="M894" xr:uid="{B77AD019-59E8-44FA-93E7-28F1816F2DB5}">
       <formula1>=IF(L894&lt;&gt;"",INDIRECT(VLOOKUP(L894,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N894" xr:uid="{DDD95C90-D67B-4EDC-A989-9527BB63BE32}">
+    <dataValidation type="list" sqref="N894" xr:uid="{F3321B20-6F15-4B95-A6E6-A711F0130FEC}">
       <formula1>=IF(M894&lt;&gt;"",INDIRECT(VLOOKUP(M894,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M895" xr:uid="{63CF1184-1915-4AC9-8086-97139FC04575}">
+    <dataValidation type="list" sqref="M895" xr:uid="{2F35017D-3110-4F40-9BB3-90F4672D5622}">
       <formula1>=IF(L895&lt;&gt;"",INDIRECT(VLOOKUP(L895,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N895" xr:uid="{E3B1DE9A-6291-4CED-97EB-CA0F530D7B41}">
+    <dataValidation type="list" sqref="N895" xr:uid="{04A3D2C8-59BC-4C7C-ABC3-371FA20450FF}">
       <formula1>=IF(M895&lt;&gt;"",INDIRECT(VLOOKUP(M895,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M896" xr:uid="{BBB7B945-E18F-430C-ABCA-09BCE153276F}">
+    <dataValidation type="list" sqref="M896" xr:uid="{E444FDE3-30CC-42E2-9284-864523BD8367}">
       <formula1>=IF(L896&lt;&gt;"",INDIRECT(VLOOKUP(L896,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N896" xr:uid="{3A0E7880-4EAA-42D6-91D2-D29D96DBB379}">
+    <dataValidation type="list" sqref="N896" xr:uid="{E0C9D923-076B-4605-9181-A15A998C0E15}">
       <formula1>=IF(M896&lt;&gt;"",INDIRECT(VLOOKUP(M896,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M897" xr:uid="{23285DEC-318B-48FA-B3F8-7E7FDA975319}">
+    <dataValidation type="list" sqref="M897" xr:uid="{2F6B9475-C785-4899-B32F-74D439B39148}">
       <formula1>=IF(L897&lt;&gt;"",INDIRECT(VLOOKUP(L897,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N897" xr:uid="{9ADA4906-22D1-4314-9214-17BF102DE5A8}">
+    <dataValidation type="list" sqref="N897" xr:uid="{5C0EF8C2-8C90-4F25-97CD-727FCC16EC96}">
       <formula1>=IF(M897&lt;&gt;"",INDIRECT(VLOOKUP(M897,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M898" xr:uid="{0697D3A9-AD0A-4DA6-A379-EFF02538815F}">
+    <dataValidation type="list" sqref="M898" xr:uid="{A8312606-C660-4D13-90D8-952D06E57D0E}">
       <formula1>=IF(L898&lt;&gt;"",INDIRECT(VLOOKUP(L898,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N898" xr:uid="{1B40F1A7-F87A-4827-9035-D4639AE91089}">
+    <dataValidation type="list" sqref="N898" xr:uid="{75FFCB95-4737-4B4C-B35D-86280E6D7D71}">
       <formula1>=IF(M898&lt;&gt;"",INDIRECT(VLOOKUP(M898,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M899" xr:uid="{3BE28011-CFFB-4D08-BEBA-36E207F38C13}">
+    <dataValidation type="list" sqref="M899" xr:uid="{BD52C357-2343-4E25-9694-A5A588C43553}">
       <formula1>=IF(L899&lt;&gt;"",INDIRECT(VLOOKUP(L899,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N899" xr:uid="{DCE37707-A910-45F9-B14E-775FDC16F356}">
+    <dataValidation type="list" sqref="N899" xr:uid="{556EAF70-7E8D-47BB-9EC5-215DBFFA102C}">
       <formula1>=IF(M899&lt;&gt;"",INDIRECT(VLOOKUP(M899,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M900" xr:uid="{5706BA4C-530B-42E2-83BE-29CDF95E21F9}">
+    <dataValidation type="list" sqref="M900" xr:uid="{176E4C5B-7C57-4FE3-9A3A-A31D8EA28070}">
       <formula1>=IF(L900&lt;&gt;"",INDIRECT(VLOOKUP(L900,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N900" xr:uid="{D8ADC9AC-34A7-4200-8507-DF0791D77D4D}">
+    <dataValidation type="list" sqref="N900" xr:uid="{FA79257A-8873-491D-A303-4E0DF8C93A6F}">
       <formula1>=IF(M900&lt;&gt;"",INDIRECT(VLOOKUP(M900,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M901" xr:uid="{9875C1B2-E689-440C-BE56-4DEA31830F6E}">
+    <dataValidation type="list" sqref="M901" xr:uid="{E232DEEE-1339-49B3-BB2D-120A8E4EF48C}">
       <formula1>=IF(L901&lt;&gt;"",INDIRECT(VLOOKUP(L901,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N901" xr:uid="{911E603D-5E77-446D-BFB7-EB294C288C6A}">
+    <dataValidation type="list" sqref="N901" xr:uid="{28B99BCF-9BC6-44CB-A26F-C25B5CA74BF9}">
       <formula1>=IF(M901&lt;&gt;"",INDIRECT(VLOOKUP(M901,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M902" xr:uid="{6FE209AB-8E9D-4F66-8F99-1CB1CD26A292}">
+    <dataValidation type="list" sqref="M902" xr:uid="{313A3F26-45CA-4EA1-8B37-D8E67ADC34C3}">
       <formula1>=IF(L902&lt;&gt;"",INDIRECT(VLOOKUP(L902,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N902" xr:uid="{586C1902-CC09-431C-BDD2-3A8CA78F8D01}">
+    <dataValidation type="list" sqref="N902" xr:uid="{86863154-01BC-45BF-83C8-79F86682F049}">
       <formula1>=IF(M902&lt;&gt;"",INDIRECT(VLOOKUP(M902,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M903" xr:uid="{D691802D-D24C-42F6-BD6F-774DB0AC4B6F}">
+    <dataValidation type="list" sqref="M903" xr:uid="{0AAFBD22-3226-47FB-8720-7AA07370CE37}">
       <formula1>=IF(L903&lt;&gt;"",INDIRECT(VLOOKUP(L903,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N903" xr:uid="{5EFA2685-393B-443E-B7C5-820CBD64014E}">
+    <dataValidation type="list" sqref="N903" xr:uid="{7FD36B57-0236-4696-847E-9630C371756A}">
       <formula1>=IF(M903&lt;&gt;"",INDIRECT(VLOOKUP(M903,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M904" xr:uid="{2B972FA6-2EA2-4D20-9E2B-E897489AED31}">
+    <dataValidation type="list" sqref="M904" xr:uid="{C87D3B66-8AE5-4166-8CA2-5BD9C1E65945}">
       <formula1>=IF(L904&lt;&gt;"",INDIRECT(VLOOKUP(L904,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N904" xr:uid="{CC414B04-0FDF-4642-AEE4-C0B4CB52CECC}">
+    <dataValidation type="list" sqref="N904" xr:uid="{22A6A748-CFA3-41EE-8249-FB955AAECB2B}">
       <formula1>=IF(M904&lt;&gt;"",INDIRECT(VLOOKUP(M904,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M905" xr:uid="{8EB22E2D-40E0-4C0A-890B-81196CCD11A7}">
+    <dataValidation type="list" sqref="M905" xr:uid="{2824BFE9-1831-4C7E-A3D3-F29B0A51E8C1}">
       <formula1>=IF(L905&lt;&gt;"",INDIRECT(VLOOKUP(L905,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N905" xr:uid="{EE9DD324-F3CE-4D74-A3F1-D29FD63CF0D3}">
+    <dataValidation type="list" sqref="N905" xr:uid="{E18A3F77-9DA1-4E4D-BA56-75D9CB2CF191}">
       <formula1>=IF(M905&lt;&gt;"",INDIRECT(VLOOKUP(M905,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M906" xr:uid="{9596AD83-C5B2-49DA-AE89-00A5E9EC061E}">
+    <dataValidation type="list" sqref="M906" xr:uid="{F1D04BEF-C899-4917-9C8B-634FE6F87B51}">
       <formula1>=IF(L906&lt;&gt;"",INDIRECT(VLOOKUP(L906,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N906" xr:uid="{F7548DC6-B61B-4231-BE59-EFB73C1BA2C7}">
+    <dataValidation type="list" sqref="N906" xr:uid="{59C53E00-8842-409D-8699-D0B0558FF687}">
       <formula1>=IF(M906&lt;&gt;"",INDIRECT(VLOOKUP(M906,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M907" xr:uid="{37CB5925-E012-412D-959A-08791EE15B20}">
+    <dataValidation type="list" sqref="M907" xr:uid="{82E3890B-039F-4F8F-8034-6BA1575779B0}">
       <formula1>=IF(L907&lt;&gt;"",INDIRECT(VLOOKUP(L907,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N907" xr:uid="{40EE6234-9532-4AE9-BCE4-4999AF251E91}">
+    <dataValidation type="list" sqref="N907" xr:uid="{B43EE0B1-9CFA-400E-A579-851641F49B6B}">
       <formula1>=IF(M907&lt;&gt;"",INDIRECT(VLOOKUP(M907,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M908" xr:uid="{495F9FCE-D8A7-4D54-8ADF-B2A2A07B0D02}">
+    <dataValidation type="list" sqref="M908" xr:uid="{F6729247-9EFB-4858-B8C0-DA6CBC1C8BFA}">
       <formula1>=IF(L908&lt;&gt;"",INDIRECT(VLOOKUP(L908,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N908" xr:uid="{D130E8EF-C53D-4A80-ABBA-39BF9A8004A9}">
+    <dataValidation type="list" sqref="N908" xr:uid="{40F196CA-3E6D-4045-BEF8-63695677E009}">
       <formula1>=IF(M908&lt;&gt;"",INDIRECT(VLOOKUP(M908,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M909" xr:uid="{BF90748D-34C8-4A13-9600-20F3EDD4B296}">
+    <dataValidation type="list" sqref="M909" xr:uid="{28B4A617-041A-4C14-9F7E-3CFBA2E7547B}">
       <formula1>=IF(L909&lt;&gt;"",INDIRECT(VLOOKUP(L909,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N909" xr:uid="{33266CAB-5172-481A-92AB-0F64EFB33B52}">
+    <dataValidation type="list" sqref="N909" xr:uid="{D763F135-F0DB-4BC6-B2BD-F06D8C017C8E}">
       <formula1>=IF(M909&lt;&gt;"",INDIRECT(VLOOKUP(M909,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M910" xr:uid="{E447ACCD-610A-440C-BFF8-B16B5688C058}">
+    <dataValidation type="list" sqref="M910" xr:uid="{DDF45B62-83FF-47F8-B8B2-31DD1A0D9FFF}">
       <formula1>=IF(L910&lt;&gt;"",INDIRECT(VLOOKUP(L910,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N910" xr:uid="{7DAA7C4F-DF05-4E8A-BD77-22849A748DEA}">
+    <dataValidation type="list" sqref="N910" xr:uid="{94DDA248-0D44-4070-B05D-BB6A6D5E688B}">
       <formula1>=IF(M910&lt;&gt;"",INDIRECT(VLOOKUP(M910,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M911" xr:uid="{BA7842C8-A38B-4C80-8058-E125C4F4E3B5}">
+    <dataValidation type="list" sqref="M911" xr:uid="{139C9701-6039-4924-8F58-6EBD9AB39501}">
       <formula1>=IF(L911&lt;&gt;"",INDIRECT(VLOOKUP(L911,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N911" xr:uid="{8C1EB367-417D-46A6-B9C8-B47F52FAC382}">
+    <dataValidation type="list" sqref="N911" xr:uid="{BEF07468-8E0E-4EEB-9D8F-4E90584BCB89}">
       <formula1>=IF(M911&lt;&gt;"",INDIRECT(VLOOKUP(M911,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M912" xr:uid="{2E637926-9DA8-45CF-A92F-878A1390E79A}">
+    <dataValidation type="list" sqref="M912" xr:uid="{E46367F8-F1AA-442E-9028-69979101EB94}">
       <formula1>=IF(L912&lt;&gt;"",INDIRECT(VLOOKUP(L912,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N912" xr:uid="{4B850205-32A1-4CD3-8529-EF557436032C}">
+    <dataValidation type="list" sqref="N912" xr:uid="{838371E6-034F-4418-8D76-1C76CBEA4E77}">
       <formula1>=IF(M912&lt;&gt;"",INDIRECT(VLOOKUP(M912,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M913" xr:uid="{F363FD2C-35FC-4C75-99EF-F9E64E554384}">
+    <dataValidation type="list" sqref="M913" xr:uid="{FDA0C8E0-CC8F-4C6E-9ECB-06D4D4B2B7B4}">
       <formula1>=IF(L913&lt;&gt;"",INDIRECT(VLOOKUP(L913,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N913" xr:uid="{F8F6F0C7-FC25-4454-B0E4-B642FF77B07A}">
+    <dataValidation type="list" sqref="N913" xr:uid="{C8AF5CEA-F64E-43B2-B62C-2803EEDA43F8}">
       <formula1>=IF(M913&lt;&gt;"",INDIRECT(VLOOKUP(M913,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M914" xr:uid="{D007E1B4-EF0D-4048-B860-3646B1BC213E}">
+    <dataValidation type="list" sqref="M914" xr:uid="{53DE6FDD-37C4-43DE-B8A5-3B9B7393CBB1}">
       <formula1>=IF(L914&lt;&gt;"",INDIRECT(VLOOKUP(L914,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N914" xr:uid="{8DEC9571-8A12-4469-B87C-CF726AD01B82}">
+    <dataValidation type="list" sqref="N914" xr:uid="{0103BDD4-8712-4842-91EE-3765F5A3EE52}">
       <formula1>=IF(M914&lt;&gt;"",INDIRECT(VLOOKUP(M914,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M915" xr:uid="{8F740594-8159-4962-85AC-2D0A8BFC6476}">
+    <dataValidation type="list" sqref="M915" xr:uid="{F904A757-2F25-421A-A8C4-031A8D29D206}">
       <formula1>=IF(L915&lt;&gt;"",INDIRECT(VLOOKUP(L915,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N915" xr:uid="{395F0F6B-B4AC-470A-A39B-A3B34A6350FE}">
+    <dataValidation type="list" sqref="N915" xr:uid="{681E85BD-858C-4176-9C88-B7BBA52384C8}">
       <formula1>=IF(M915&lt;&gt;"",INDIRECT(VLOOKUP(M915,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M916" xr:uid="{56900032-9A53-4929-A159-252D90202BD7}">
+    <dataValidation type="list" sqref="M916" xr:uid="{F5ADB2F7-EAC5-4F66-A7CE-BFCEF5A12813}">
       <formula1>=IF(L916&lt;&gt;"",INDIRECT(VLOOKUP(L916,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N916" xr:uid="{21A20985-C267-4597-A7C1-2FAEADA100B3}">
+    <dataValidation type="list" sqref="N916" xr:uid="{E7E58195-2D95-4FF5-99C2-9F9980BEA0BF}">
       <formula1>=IF(M916&lt;&gt;"",INDIRECT(VLOOKUP(M916,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M917" xr:uid="{02B889F3-8B55-465E-BD43-B7ED3D7604CC}">
+    <dataValidation type="list" sqref="M917" xr:uid="{D31A4F09-5A36-4E2E-BBA6-9366677EF5FE}">
       <formula1>=IF(L917&lt;&gt;"",INDIRECT(VLOOKUP(L917,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N917" xr:uid="{18379426-92C7-4AF7-B9D0-F13EE0C95951}">
+    <dataValidation type="list" sqref="N917" xr:uid="{B8BB8E20-92D7-40D8-B280-49157BF34848}">
       <formula1>=IF(M917&lt;&gt;"",INDIRECT(VLOOKUP(M917,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M918" xr:uid="{8F8CC978-1460-45F4-AB7E-08ABA5E87F35}">
+    <dataValidation type="list" sqref="M918" xr:uid="{E57CD48B-F14E-455A-A225-9723E5803976}">
       <formula1>=IF(L918&lt;&gt;"",INDIRECT(VLOOKUP(L918,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N918" xr:uid="{8FF8B216-E0A1-4597-BBC4-F3D22A3C26FB}">
+    <dataValidation type="list" sqref="N918" xr:uid="{91D67E71-11A4-4EAE-90AE-04E05F292244}">
       <formula1>=IF(M918&lt;&gt;"",INDIRECT(VLOOKUP(M918,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M919" xr:uid="{A1E60F99-BAD1-4A25-8BB0-F6CB2D692ACA}">
+    <dataValidation type="list" sqref="M919" xr:uid="{ED718B38-5FD9-4F80-AE36-23A8BAFBD4CF}">
       <formula1>=IF(L919&lt;&gt;"",INDIRECT(VLOOKUP(L919,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N919" xr:uid="{8494D9EB-39D5-4A43-823B-71DA60F87240}">
+    <dataValidation type="list" sqref="N919" xr:uid="{90A28C30-FF5D-41BA-AA74-9FB4D2028FE3}">
       <formula1>=IF(M919&lt;&gt;"",INDIRECT(VLOOKUP(M919,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M920" xr:uid="{28F779C5-82EB-433D-ACC0-B49A46A70B95}">
+    <dataValidation type="list" sqref="M920" xr:uid="{F9736D72-D6F8-4C01-9EAB-20F97384F0D1}">
       <formula1>=IF(L920&lt;&gt;"",INDIRECT(VLOOKUP(L920,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N920" xr:uid="{BA9F209B-970A-471B-AAC0-3A5E59BB5457}">
+    <dataValidation type="list" sqref="N920" xr:uid="{8B79C1CC-EC05-4955-9AED-D999C3FEAFC3}">
       <formula1>=IF(M920&lt;&gt;"",INDIRECT(VLOOKUP(M920,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M921" xr:uid="{113D0339-D021-43EA-BD36-2682C82096C5}">
+    <dataValidation type="list" sqref="M921" xr:uid="{654E1789-4BAB-4D04-9E4C-4A0C3AC7C7ED}">
       <formula1>=IF(L921&lt;&gt;"",INDIRECT(VLOOKUP(L921,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N921" xr:uid="{AE6E936C-60FC-4094-BC85-78282AF52858}">
+    <dataValidation type="list" sqref="N921" xr:uid="{9060F396-D88D-424C-9B77-2FED2BB20006}">
       <formula1>=IF(M921&lt;&gt;"",INDIRECT(VLOOKUP(M921,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M922" xr:uid="{13C08CB5-6B9F-4111-9DE0-1561FF805318}">
+    <dataValidation type="list" sqref="M922" xr:uid="{56FD29C4-E79D-4A4B-8C51-EDD4AA1A5211}">
       <formula1>=IF(L922&lt;&gt;"",INDIRECT(VLOOKUP(L922,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N922" xr:uid="{4B3B5F93-B1D2-4DB2-86EB-36495F99BB82}">
+    <dataValidation type="list" sqref="N922" xr:uid="{BAA6DB53-41CD-4C61-9712-AEC37C93ECBD}">
       <formula1>=IF(M922&lt;&gt;"",INDIRECT(VLOOKUP(M922,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M923" xr:uid="{984B069A-F897-423D-BA7E-B66505AC67C6}">
+    <dataValidation type="list" sqref="M923" xr:uid="{B8E179B1-A9AC-4587-9DD8-7A382A19652F}">
       <formula1>=IF(L923&lt;&gt;"",INDIRECT(VLOOKUP(L923,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N923" xr:uid="{25980E25-ED86-429A-88A4-172E8058BDA7}">
+    <dataValidation type="list" sqref="N923" xr:uid="{CD66806D-8F73-4A39-A43F-63364D3614F7}">
       <formula1>=IF(M923&lt;&gt;"",INDIRECT(VLOOKUP(M923,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M924" xr:uid="{050BA714-3438-44DC-951F-D8195780787B}">
+    <dataValidation type="list" sqref="M924" xr:uid="{83580C01-AC7B-43C0-9F4E-9CEAB41D36FA}">
       <formula1>=IF(L924&lt;&gt;"",INDIRECT(VLOOKUP(L924,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N924" xr:uid="{0E2D93E1-E7AC-453D-B652-6F5BAE0D7873}">
+    <dataValidation type="list" sqref="N924" xr:uid="{E6878FA7-463E-4007-B5A5-D10019C0F96C}">
       <formula1>=IF(M924&lt;&gt;"",INDIRECT(VLOOKUP(M924,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M925" xr:uid="{7ABBA067-9151-4362-9C9A-BB6467E159E5}">
+    <dataValidation type="list" sqref="M925" xr:uid="{16B97B0A-D178-4F62-A734-4B0F3A433F68}">
       <formula1>=IF(L925&lt;&gt;"",INDIRECT(VLOOKUP(L925,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N925" xr:uid="{1C54A1AB-62B2-4145-82E6-AB98FB50B8BE}">
+    <dataValidation type="list" sqref="N925" xr:uid="{82A83100-2DFA-49D6-8C0F-C9B782452AAB}">
       <formula1>=IF(M925&lt;&gt;"",INDIRECT(VLOOKUP(M925,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M926" xr:uid="{953786C7-AEE5-42E2-9428-6C50377C5877}">
+    <dataValidation type="list" sqref="M926" xr:uid="{3BD339F5-C288-4B13-B55F-459F7919CEA6}">
       <formula1>=IF(L926&lt;&gt;"",INDIRECT(VLOOKUP(L926,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N926" xr:uid="{26E8671E-F793-4335-8902-F4201C716DCC}">
+    <dataValidation type="list" sqref="N926" xr:uid="{BEF82F61-8426-41FD-9FC6-DA57601F49A0}">
       <formula1>=IF(M926&lt;&gt;"",INDIRECT(VLOOKUP(M926,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M927" xr:uid="{2BF5A4B5-5487-4580-B049-C115F80CA88C}">
+    <dataValidation type="list" sqref="M927" xr:uid="{FF7BF718-D55D-47D2-8510-91BEF4CF3A6A}">
       <formula1>=IF(L927&lt;&gt;"",INDIRECT(VLOOKUP(L927,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N927" xr:uid="{2F81FB5B-ABF5-4A7B-9E91-65C30998926F}">
+    <dataValidation type="list" sqref="N927" xr:uid="{951E8AA6-AB8D-4A33-8F27-A279C4794ED5}">
       <formula1>=IF(M927&lt;&gt;"",INDIRECT(VLOOKUP(M927,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M928" xr:uid="{BE41B777-5661-4AC9-8DB1-1E20AF110C64}">
+    <dataValidation type="list" sqref="M928" xr:uid="{DB8CD162-FAB7-442A-AF06-0DD9C2EBF0C6}">
       <formula1>=IF(L928&lt;&gt;"",INDIRECT(VLOOKUP(L928,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N928" xr:uid="{1522A155-46C2-4A1D-9B10-5D9FDB215D6A}">
+    <dataValidation type="list" sqref="N928" xr:uid="{762A3B4B-8504-4F34-BF83-41B8D1BC47C3}">
       <formula1>=IF(M928&lt;&gt;"",INDIRECT(VLOOKUP(M928,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M929" xr:uid="{D954554B-3EAD-496B-BD1D-BBDF2EDAD1EC}">
+    <dataValidation type="list" sqref="M929" xr:uid="{60149E75-546D-4BB1-A98A-508FF9FF7F64}">
       <formula1>=IF(L929&lt;&gt;"",INDIRECT(VLOOKUP(L929,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N929" xr:uid="{6E0BC91D-38A9-4782-A2A0-F40DB51796AC}">
+    <dataValidation type="list" sqref="N929" xr:uid="{CD43DB3A-B8E9-419E-9206-E516235971F6}">
       <formula1>=IF(M929&lt;&gt;"",INDIRECT(VLOOKUP(M929,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M930" xr:uid="{AE3EF2B3-5728-4071-A917-8763BEF743DD}">
+    <dataValidation type="list" sqref="M930" xr:uid="{74C30BBB-B097-421D-B2F7-3A27D18A36CF}">
       <formula1>=IF(L930&lt;&gt;"",INDIRECT(VLOOKUP(L930,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N930" xr:uid="{780E702C-9E9E-4F41-9FCE-FA6E91B4F0E4}">
+    <dataValidation type="list" sqref="N930" xr:uid="{6DCE95EF-35DC-4B29-B9B8-B7982A3839BD}">
       <formula1>=IF(M930&lt;&gt;"",INDIRECT(VLOOKUP(M930,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M931" xr:uid="{B1DB7627-A980-49C6-8EDF-CD1EF7C11562}">
+    <dataValidation type="list" sqref="M931" xr:uid="{56C8E544-03DE-49FB-990D-A0CC28C9EE0E}">
       <formula1>=IF(L931&lt;&gt;"",INDIRECT(VLOOKUP(L931,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N931" xr:uid="{E97C0D3B-D808-4198-A3F0-BDD9090BC3B4}">
+    <dataValidation type="list" sqref="N931" xr:uid="{43B43450-03CC-421D-96AF-B324D20C1D27}">
       <formula1>=IF(M931&lt;&gt;"",INDIRECT(VLOOKUP(M931,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M932" xr:uid="{94C1C606-DEAB-47D4-8DE7-3BC70126E09A}">
+    <dataValidation type="list" sqref="M932" xr:uid="{B97BB66D-EF37-47DB-8533-88B63E30AC3C}">
       <formula1>=IF(L932&lt;&gt;"",INDIRECT(VLOOKUP(L932,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N932" xr:uid="{A97A439D-4756-4322-AAE2-168DB812FAA0}">
+    <dataValidation type="list" sqref="N932" xr:uid="{407977A9-56C9-4229-BDF2-FD97A185D906}">
       <formula1>=IF(M932&lt;&gt;"",INDIRECT(VLOOKUP(M932,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M933" xr:uid="{F3958098-E980-4B20-93EC-80812240775B}">
+    <dataValidation type="list" sqref="M933" xr:uid="{85101306-01B4-4556-BB0D-09D4FB81D6DB}">
       <formula1>=IF(L933&lt;&gt;"",INDIRECT(VLOOKUP(L933,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N933" xr:uid="{8E9B5BB6-08E0-40D2-8D93-D72AE662C8A3}">
+    <dataValidation type="list" sqref="N933" xr:uid="{F6292EE6-4899-491B-B293-D4C11A512BF2}">
       <formula1>=IF(M933&lt;&gt;"",INDIRECT(VLOOKUP(M933,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M934" xr:uid="{3BD7D3D4-769C-4D44-BA48-E1303E06E0D6}">
+    <dataValidation type="list" sqref="M934" xr:uid="{E8481D92-2976-4EA8-A39A-4330C8EF4B59}">
       <formula1>=IF(L934&lt;&gt;"",INDIRECT(VLOOKUP(L934,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N934" xr:uid="{A76A3B7D-6CAB-4580-8090-5DAA610D9B76}">
+    <dataValidation type="list" sqref="N934" xr:uid="{2A9A52D6-B622-478A-BAA9-6ACFBC081D98}">
       <formula1>=IF(M934&lt;&gt;"",INDIRECT(VLOOKUP(M934,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M935" xr:uid="{A35293BE-3E9A-4731-837A-CCA6BD475279}">
+    <dataValidation type="list" sqref="M935" xr:uid="{2B35797A-CBCB-4988-A0FC-F4A5D084B537}">
       <formula1>=IF(L935&lt;&gt;"",INDIRECT(VLOOKUP(L935,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N935" xr:uid="{67CB9A38-396E-4B49-B19B-668EF7189CAB}">
+    <dataValidation type="list" sqref="N935" xr:uid="{83E6DE19-E95E-4E8D-8251-733AB430D82E}">
       <formula1>=IF(M935&lt;&gt;"",INDIRECT(VLOOKUP(M935,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M936" xr:uid="{DC1BF7C7-18EB-4C68-AB9D-6F67BD26FA75}">
+    <dataValidation type="list" sqref="M936" xr:uid="{049AB04E-01EF-415D-8CC6-4310607EF1CD}">
       <formula1>=IF(L936&lt;&gt;"",INDIRECT(VLOOKUP(L936,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N936" xr:uid="{D94C996D-DAE7-4E44-AC35-C35CDD36EAEE}">
+    <dataValidation type="list" sqref="N936" xr:uid="{A44AFEF0-1F0C-48A3-B1E9-F1D2AFCA2939}">
       <formula1>=IF(M936&lt;&gt;"",INDIRECT(VLOOKUP(M936,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M937" xr:uid="{D5058885-21A9-4557-8FBA-10E6FBDA9337}">
+    <dataValidation type="list" sqref="M937" xr:uid="{2FEE6718-1924-47AD-920D-1D200286B8DB}">
       <formula1>=IF(L937&lt;&gt;"",INDIRECT(VLOOKUP(L937,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N937" xr:uid="{D75A8185-AD02-4897-AC47-5C29ECF95E91}">
+    <dataValidation type="list" sqref="N937" xr:uid="{5049453B-2EF9-4C3C-B5A6-6C0481519D79}">
       <formula1>=IF(M937&lt;&gt;"",INDIRECT(VLOOKUP(M937,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M938" xr:uid="{29B21D73-AA61-45DD-A612-C12EC467C29C}">
+    <dataValidation type="list" sqref="M938" xr:uid="{C659994C-BC91-4C98-99D4-BA1B0973042C}">
       <formula1>=IF(L938&lt;&gt;"",INDIRECT(VLOOKUP(L938,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N938" xr:uid="{DD8EDB89-468A-4046-A9C9-E60126E3A538}">
+    <dataValidation type="list" sqref="N938" xr:uid="{84ED225D-6FB4-4CCD-B9BF-5DEEEA91766B}">
       <formula1>=IF(M938&lt;&gt;"",INDIRECT(VLOOKUP(M938,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M939" xr:uid="{DE79313A-8D1A-42CA-85E6-4982C6702F7D}">
+    <dataValidation type="list" sqref="M939" xr:uid="{1E15CEB5-38EF-4B08-840C-07711CE51081}">
       <formula1>=IF(L939&lt;&gt;"",INDIRECT(VLOOKUP(L939,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N939" xr:uid="{17E95D63-C2A4-468E-980E-E7604F7226A5}">
+    <dataValidation type="list" sqref="N939" xr:uid="{D3CEC1E1-38A3-4BFE-B994-47B14E5DAB1C}">
       <formula1>=IF(M939&lt;&gt;"",INDIRECT(VLOOKUP(M939,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M940" xr:uid="{8AD9DAA6-119B-4EB2-8CF7-4F4CA74DF838}">
+    <dataValidation type="list" sqref="M940" xr:uid="{A0173C85-300D-480A-B256-B09316CB3C13}">
       <formula1>=IF(L940&lt;&gt;"",INDIRECT(VLOOKUP(L940,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N940" xr:uid="{899FD4D2-9263-42DC-85CA-AD82B4177441}">
+    <dataValidation type="list" sqref="N940" xr:uid="{F917B69E-9D0B-4524-9A42-93F2F76187CA}">
       <formula1>=IF(M940&lt;&gt;"",INDIRECT(VLOOKUP(M940,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M941" xr:uid="{CB13A106-805D-4E40-8454-39165B331810}">
+    <dataValidation type="list" sqref="M941" xr:uid="{888210D9-6A79-4A7A-9D61-EF6963BEEE1B}">
       <formula1>=IF(L941&lt;&gt;"",INDIRECT(VLOOKUP(L941,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N941" xr:uid="{41AE4E9C-C7DB-4101-A306-0D79B71CFF15}">
+    <dataValidation type="list" sqref="N941" xr:uid="{F5E03E3E-0D51-4DBA-AE5C-12049B71839B}">
       <formula1>=IF(M941&lt;&gt;"",INDIRECT(VLOOKUP(M941,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M942" xr:uid="{C761EE06-C138-428B-92BC-55C38A511845}">
+    <dataValidation type="list" sqref="M942" xr:uid="{645237AC-824E-437E-B16A-D19F9712DB55}">
       <formula1>=IF(L942&lt;&gt;"",INDIRECT(VLOOKUP(L942,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N942" xr:uid="{61CF0D24-0063-4B58-98F1-E036EF20E4A5}">
+    <dataValidation type="list" sqref="N942" xr:uid="{3D4EDB5A-4365-442E-855E-31A4BDCEC32A}">
       <formula1>=IF(M942&lt;&gt;"",INDIRECT(VLOOKUP(M942,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M943" xr:uid="{FA8626BE-FFFC-48AE-8BF4-A81E1AF05BAB}">
+    <dataValidation type="list" sqref="M943" xr:uid="{93F00E37-E4AB-42B6-AEC0-C3FEB41DA86D}">
       <formula1>=IF(L943&lt;&gt;"",INDIRECT(VLOOKUP(L943,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N943" xr:uid="{E698292A-3CF6-4171-9B63-ED428DB1452C}">
+    <dataValidation type="list" sqref="N943" xr:uid="{A155F6AD-4AE6-4B93-B73D-E7A20B8682DE}">
       <formula1>=IF(M943&lt;&gt;"",INDIRECT(VLOOKUP(M943,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M944" xr:uid="{B1F30F64-551D-4FFC-8679-0FDA0410855F}">
+    <dataValidation type="list" sqref="M944" xr:uid="{FDCD4C51-2BD2-4468-836D-0DC63FE2BDBD}">
       <formula1>=IF(L944&lt;&gt;"",INDIRECT(VLOOKUP(L944,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N944" xr:uid="{D5037A17-8859-411E-AD28-6EE2E359287A}">
+    <dataValidation type="list" sqref="N944" xr:uid="{DD841DFB-7678-48F2-B280-93FB59C258ED}">
       <formula1>=IF(M944&lt;&gt;"",INDIRECT(VLOOKUP(M944,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M945" xr:uid="{13B540F5-3F1F-47EF-908F-87DD5166E0F1}">
+    <dataValidation type="list" sqref="M945" xr:uid="{76404F57-ED30-4AF1-9B3D-03150EAD03B3}">
       <formula1>=IF(L945&lt;&gt;"",INDIRECT(VLOOKUP(L945,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N945" xr:uid="{457EEA40-7526-4D0D-9EC9-9D77F0C3239D}">
+    <dataValidation type="list" sqref="N945" xr:uid="{527BC8A8-317C-4510-9A0B-D71537A3982D}">
       <formula1>=IF(M945&lt;&gt;"",INDIRECT(VLOOKUP(M945,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M946" xr:uid="{9E42C94B-4937-45DD-960D-7F7F1FAFDBAF}">
+    <dataValidation type="list" sqref="M946" xr:uid="{6A0D7D85-9D69-4CC9-8919-AC68D34F4E97}">
       <formula1>=IF(L946&lt;&gt;"",INDIRECT(VLOOKUP(L946,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N946" xr:uid="{EAA579EC-5F77-4600-B2FA-B8EA36EDF0E2}">
+    <dataValidation type="list" sqref="N946" xr:uid="{F7497006-DC1D-4F29-9FD2-61D4608FD170}">
       <formula1>=IF(M946&lt;&gt;"",INDIRECT(VLOOKUP(M946,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M947" xr:uid="{41357EAD-8920-405D-9418-B1A3B09D917B}">
+    <dataValidation type="list" sqref="M947" xr:uid="{A538D3FA-92FD-45B9-B5F1-7D780A88417F}">
       <formula1>=IF(L947&lt;&gt;"",INDIRECT(VLOOKUP(L947,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N947" xr:uid="{4D14C9EF-346B-44A7-88FC-24BB503E9D2B}">
+    <dataValidation type="list" sqref="N947" xr:uid="{453171A7-A93C-4045-BF24-9A9F7C4785A8}">
       <formula1>=IF(M947&lt;&gt;"",INDIRECT(VLOOKUP(M947,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M948" xr:uid="{EE0A8B07-0DAD-40E8-87CF-547ACB917BD9}">
+    <dataValidation type="list" sqref="M948" xr:uid="{D1651A67-7330-495C-8A43-2745410B35C3}">
       <formula1>=IF(L948&lt;&gt;"",INDIRECT(VLOOKUP(L948,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N948" xr:uid="{00E1B58B-8226-4D84-A466-786BFAA28E6A}">
+    <dataValidation type="list" sqref="N948" xr:uid="{BA5723FC-F3F7-4F47-A94C-F5823E036BCF}">
       <formula1>=IF(M948&lt;&gt;"",INDIRECT(VLOOKUP(M948,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M949" xr:uid="{7AF73A11-3C08-4B00-A595-EFBBC82CC58B}">
+    <dataValidation type="list" sqref="M949" xr:uid="{36C12FB6-B2D5-4507-BB6C-E27E34BF7726}">
       <formula1>=IF(L949&lt;&gt;"",INDIRECT(VLOOKUP(L949,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N949" xr:uid="{AC6EF0DC-9B8B-41E7-864A-9A90785639A5}">
+    <dataValidation type="list" sqref="N949" xr:uid="{978D4312-881E-48B8-8084-816D0C2AA27D}">
       <formula1>=IF(M949&lt;&gt;"",INDIRECT(VLOOKUP(M949,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M950" xr:uid="{CFF293C6-002A-4C32-87A8-3157EF21306F}">
+    <dataValidation type="list" sqref="M950" xr:uid="{4F137F44-BBD7-4AAF-A40A-BB1078896708}">
       <formula1>=IF(L950&lt;&gt;"",INDIRECT(VLOOKUP(L950,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N950" xr:uid="{08679558-9E7C-4C06-8F25-7CA3AE64725B}">
+    <dataValidation type="list" sqref="N950" xr:uid="{9E5EFE7A-8BCB-470E-99CB-D43F7191E001}">
       <formula1>=IF(M950&lt;&gt;"",INDIRECT(VLOOKUP(M950,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M951" xr:uid="{7C4F9C26-E4AC-4499-8A46-E892639FCD9D}">
+    <dataValidation type="list" sqref="M951" xr:uid="{D1059BA6-F009-4130-9706-A906A735A62B}">
       <formula1>=IF(L951&lt;&gt;"",INDIRECT(VLOOKUP(L951,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N951" xr:uid="{D3EECCC5-7EF0-41C4-8CC5-84647849F536}">
+    <dataValidation type="list" sqref="N951" xr:uid="{41761698-2AC6-4A54-9A98-94AD07A93FFA}">
       <formula1>=IF(M951&lt;&gt;"",INDIRECT(VLOOKUP(M951,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M952" xr:uid="{02DB0BF1-4BA1-431B-8055-CF4C9460B153}">
+    <dataValidation type="list" sqref="M952" xr:uid="{C30604DD-E89A-464C-BE3C-1ED8E2DD07B6}">
       <formula1>=IF(L952&lt;&gt;"",INDIRECT(VLOOKUP(L952,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N952" xr:uid="{C6997EE4-5284-49BB-A229-B0245B39E384}">
+    <dataValidation type="list" sqref="N952" xr:uid="{B5BB7BFD-1F56-425E-A2B2-768235326D39}">
       <formula1>=IF(M952&lt;&gt;"",INDIRECT(VLOOKUP(M952,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M953" xr:uid="{9C6B61CB-A11F-478B-A9FD-E8961E83E853}">
+    <dataValidation type="list" sqref="M953" xr:uid="{1B17446B-4C76-4472-AD03-492D435A725B}">
       <formula1>=IF(L953&lt;&gt;"",INDIRECT(VLOOKUP(L953,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N953" xr:uid="{D596C9EE-107A-42C1-82B8-6D72CF8BAC92}">
+    <dataValidation type="list" sqref="N953" xr:uid="{174E0A3A-81F0-4973-B343-EDCD0AA82E49}">
       <formula1>=IF(M953&lt;&gt;"",INDIRECT(VLOOKUP(M953,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M954" xr:uid="{CD58ACC4-F4A2-48BC-A49F-9D94B926BAA3}">
+    <dataValidation type="list" sqref="M954" xr:uid="{958BB0D4-4A9D-45F1-9BAA-F7C54E6CE1EF}">
       <formula1>=IF(L954&lt;&gt;"",INDIRECT(VLOOKUP(L954,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N954" xr:uid="{E4AF2105-4BF3-448D-A0EF-B5FFBF0989A4}">
+    <dataValidation type="list" sqref="N954" xr:uid="{98EEFE92-8705-43CB-8372-3F26C59CB1B3}">
       <formula1>=IF(M954&lt;&gt;"",INDIRECT(VLOOKUP(M954,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M955" xr:uid="{912F5BBE-3006-4FFC-848A-932D45A0B60B}">
+    <dataValidation type="list" sqref="M955" xr:uid="{CAC94E5A-1B68-4C13-A8CE-CEB95548311E}">
       <formula1>=IF(L955&lt;&gt;"",INDIRECT(VLOOKUP(L955,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N955" xr:uid="{3B0900C4-B67C-4C97-B8B0-2BC4E18B2560}">
+    <dataValidation type="list" sqref="N955" xr:uid="{ED452DBD-3DA4-4E66-A656-FF83B500F1A6}">
       <formula1>=IF(M955&lt;&gt;"",INDIRECT(VLOOKUP(M955,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M956" xr:uid="{FBEAC1E6-8574-4E3E-B355-B47504E79E17}">
+    <dataValidation type="list" sqref="M956" xr:uid="{85C5AC5B-2DEF-4E46-A456-8F3B97C65698}">
       <formula1>=IF(L956&lt;&gt;"",INDIRECT(VLOOKUP(L956,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N956" xr:uid="{172C3C47-3D3F-41DA-A749-5C566682BC2E}">
+    <dataValidation type="list" sqref="N956" xr:uid="{DD582DBC-C9AE-4ED1-8A0C-959D76E70AF3}">
       <formula1>=IF(M956&lt;&gt;"",INDIRECT(VLOOKUP(M956,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M957" xr:uid="{20043B00-A038-44FD-9578-F31720F58023}">
+    <dataValidation type="list" sqref="M957" xr:uid="{B9B20FCC-A0A9-4F66-AD7C-475B4C359EEB}">
       <formula1>=IF(L957&lt;&gt;"",INDIRECT(VLOOKUP(L957,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N957" xr:uid="{FEB9A389-94F3-4626-873F-96AAA603A6DF}">
+    <dataValidation type="list" sqref="N957" xr:uid="{AC39BE59-1B68-47C3-8195-5661E2DA364A}">
       <formula1>=IF(M957&lt;&gt;"",INDIRECT(VLOOKUP(M957,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M958" xr:uid="{6FC93FD7-E6CB-4D2E-9890-587B1C4F57E9}">
+    <dataValidation type="list" sqref="M958" xr:uid="{8FC2973D-066A-448C-B6E2-6D8CD678E014}">
       <formula1>=IF(L958&lt;&gt;"",INDIRECT(VLOOKUP(L958,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N958" xr:uid="{8FF4388D-F510-40D8-A763-F0FD78078D88}">
+    <dataValidation type="list" sqref="N958" xr:uid="{F4982BF9-CB19-4E2E-A039-993C44E548CE}">
       <formula1>=IF(M958&lt;&gt;"",INDIRECT(VLOOKUP(M958,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M959" xr:uid="{057242E6-7008-4D29-90CC-45FE9012E504}">
+    <dataValidation type="list" sqref="M959" xr:uid="{67BA2FA0-00B5-422A-B006-5E12E2672DB5}">
       <formula1>=IF(L959&lt;&gt;"",INDIRECT(VLOOKUP(L959,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N959" xr:uid="{AB69D451-4F81-4413-84AE-85C0B4F02BC2}">
+    <dataValidation type="list" sqref="N959" xr:uid="{82EB6904-55A1-4572-B228-2B7625B0109A}">
       <formula1>=IF(M959&lt;&gt;"",INDIRECT(VLOOKUP(M959,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M960" xr:uid="{B8DDF473-15AE-4B36-B1BA-1C50F068FB6C}">
+    <dataValidation type="list" sqref="M960" xr:uid="{1503B7E8-2BA7-422D-B48D-85FBA416AA22}">
       <formula1>=IF(L960&lt;&gt;"",INDIRECT(VLOOKUP(L960,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N960" xr:uid="{7B602886-A2CA-43AB-8ECD-EC39E3087820}">
+    <dataValidation type="list" sqref="N960" xr:uid="{DFC638A1-4C00-4032-9EE7-20767DFA0093}">
       <formula1>=IF(M960&lt;&gt;"",INDIRECT(VLOOKUP(M960,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M961" xr:uid="{1FF21F1E-568B-45EE-9FF7-E00FF7A572EE}">
+    <dataValidation type="list" sqref="M961" xr:uid="{0BBA4043-80A6-496B-8943-D700E1430A55}">
       <formula1>=IF(L961&lt;&gt;"",INDIRECT(VLOOKUP(L961,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N961" xr:uid="{C1BE8FE0-CB83-40DB-9490-7F94E26E62DF}">
+    <dataValidation type="list" sqref="N961" xr:uid="{A7F6DDB3-D1FA-4480-B630-EEEE70212BA9}">
       <formula1>=IF(M961&lt;&gt;"",INDIRECT(VLOOKUP(M961,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M962" xr:uid="{1243EB3F-B86D-408C-815E-6111B96B6CB4}">
+    <dataValidation type="list" sqref="M962" xr:uid="{92364B85-A942-4FE4-B749-852E6CF3039A}">
       <formula1>=IF(L962&lt;&gt;"",INDIRECT(VLOOKUP(L962,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N962" xr:uid="{087DCC9F-4B7C-431F-B55F-5E344AF8E7B7}">
+    <dataValidation type="list" sqref="N962" xr:uid="{FF29B7A3-5F20-4B63-9AAB-394CC1FEDFD8}">
       <formula1>=IF(M962&lt;&gt;"",INDIRECT(VLOOKUP(M962,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M963" xr:uid="{D0412EDB-C52A-49D8-9734-405B8F4E1A85}">
+    <dataValidation type="list" sqref="M963" xr:uid="{E54496A7-8976-495B-905D-67D8BAAC0ED7}">
       <formula1>=IF(L963&lt;&gt;"",INDIRECT(VLOOKUP(L963,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N963" xr:uid="{EB4BE247-2D61-4210-B5BD-16AADD69C975}">
+    <dataValidation type="list" sqref="N963" xr:uid="{CF65B253-CE3B-4374-BA8D-B2B02804D589}">
       <formula1>=IF(M963&lt;&gt;"",INDIRECT(VLOOKUP(M963,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M964" xr:uid="{51C9EF2D-E150-462C-8627-AFDD56A3C6B4}">
+    <dataValidation type="list" sqref="M964" xr:uid="{5DE2F1F1-2DEF-4AAD-A07D-AE3E2B673BC7}">
       <formula1>=IF(L964&lt;&gt;"",INDIRECT(VLOOKUP(L964,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N964" xr:uid="{805461A7-31DD-441C-815B-F83849B03A11}">
+    <dataValidation type="list" sqref="N964" xr:uid="{64AA93B3-7D52-4C90-98D8-BA8B77E4C269}">
       <formula1>=IF(M964&lt;&gt;"",INDIRECT(VLOOKUP(M964,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M965" xr:uid="{4FB2059C-C987-4E39-8BF3-491C5475865E}">
+    <dataValidation type="list" sqref="M965" xr:uid="{842CCD84-582B-4F19-92A1-8DD48B531F1A}">
       <formula1>=IF(L965&lt;&gt;"",INDIRECT(VLOOKUP(L965,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N965" xr:uid="{AB3682E3-ECA5-4D6E-AA50-485C18B6C4E7}">
+    <dataValidation type="list" sqref="N965" xr:uid="{56934E22-668C-496A-BA47-67969C3AA30C}">
       <formula1>=IF(M965&lt;&gt;"",INDIRECT(VLOOKUP(M965,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M966" xr:uid="{EA150D84-30C5-4384-ACB8-F147F44A733B}">
+    <dataValidation type="list" sqref="M966" xr:uid="{36326A07-29AB-4C29-A146-9C9A67F67700}">
       <formula1>=IF(L966&lt;&gt;"",INDIRECT(VLOOKUP(L966,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N966" xr:uid="{6B639470-8D14-4072-9D0B-A98F9E7AA2C2}">
+    <dataValidation type="list" sqref="N966" xr:uid="{287EE513-06AE-410A-821B-64D307BEF3BE}">
       <formula1>=IF(M966&lt;&gt;"",INDIRECT(VLOOKUP(M966,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M967" xr:uid="{5B98DADF-6AF2-4A00-9011-4A63771AA1E9}">
+    <dataValidation type="list" sqref="M967" xr:uid="{49D64EAD-245A-419A-A475-75A3DAA2196F}">
       <formula1>=IF(L967&lt;&gt;"",INDIRECT(VLOOKUP(L967,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N967" xr:uid="{B7365263-FEFF-40E5-9A55-A624B5DC9AE9}">
+    <dataValidation type="list" sqref="N967" xr:uid="{4DC3E0C1-C0E8-41C5-9327-102BCBFDEDD2}">
       <formula1>=IF(M967&lt;&gt;"",INDIRECT(VLOOKUP(M967,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M968" xr:uid="{7B7055E3-74A7-49B3-B1FE-92204FE97803}">
+    <dataValidation type="list" sqref="M968" xr:uid="{079490A7-DC83-4779-96F4-8E3B64996D43}">
       <formula1>=IF(L968&lt;&gt;"",INDIRECT(VLOOKUP(L968,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N968" xr:uid="{EDE891C4-7D05-48AC-80DB-1E8676FC264C}">
+    <dataValidation type="list" sqref="N968" xr:uid="{57CD877E-B25C-4898-9B34-440015299934}">
       <formula1>=IF(M968&lt;&gt;"",INDIRECT(VLOOKUP(M968,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M969" xr:uid="{969DC5E7-6093-495E-AD59-FFF6483CE838}">
+    <dataValidation type="list" sqref="M969" xr:uid="{F92F9E9C-2A95-4211-90E9-93A648971731}">
       <formula1>=IF(L969&lt;&gt;"",INDIRECT(VLOOKUP(L969,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N969" xr:uid="{66614E57-0A73-4375-A0EC-B0A1D4A87DBF}">
+    <dataValidation type="list" sqref="N969" xr:uid="{EF63D40E-2950-4B24-B3E6-605052D1877E}">
       <formula1>=IF(M969&lt;&gt;"",INDIRECT(VLOOKUP(M969,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M970" xr:uid="{DF5ED184-5664-42BB-B311-718CF09819C9}">
+    <dataValidation type="list" sqref="M970" xr:uid="{0B15C4EA-A20C-4D5C-9594-56608BF7E8C4}">
       <formula1>=IF(L970&lt;&gt;"",INDIRECT(VLOOKUP(L970,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N970" xr:uid="{E24E63D2-B517-42B3-BADD-42FBA0874491}">
+    <dataValidation type="list" sqref="N970" xr:uid="{37479C42-1EB7-4D84-8352-7AFA4F45A1EB}">
       <formula1>=IF(M970&lt;&gt;"",INDIRECT(VLOOKUP(M970,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M971" xr:uid="{C4C6B8D9-B1F0-46A9-8024-489FDE2E0AE8}">
+    <dataValidation type="list" sqref="M971" xr:uid="{C675427C-0CA1-4EF9-AE89-10966ABA2A60}">
       <formula1>=IF(L971&lt;&gt;"",INDIRECT(VLOOKUP(L971,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N971" xr:uid="{6069884D-468A-47E9-8589-C58AFB89BD29}">
+    <dataValidation type="list" sqref="N971" xr:uid="{3C481994-CB58-4713-A15E-5B5DC6E83BB2}">
       <formula1>=IF(M971&lt;&gt;"",INDIRECT(VLOOKUP(M971,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M972" xr:uid="{17E1E4E6-7B66-4B69-B084-C586C0D17504}">
+    <dataValidation type="list" sqref="M972" xr:uid="{FB1C63E3-2853-4C39-993A-9D2723A53BD9}">
       <formula1>=IF(L972&lt;&gt;"",INDIRECT(VLOOKUP(L972,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N972" xr:uid="{1AC04F07-F856-406E-B4FE-B80CC6613074}">
+    <dataValidation type="list" sqref="N972" xr:uid="{DAE2D30D-3A5F-4617-A3F0-E1290A0652B9}">
       <formula1>=IF(M972&lt;&gt;"",INDIRECT(VLOOKUP(M972,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M973" xr:uid="{918A7CFC-33BD-454F-9921-212120F7FC11}">
+    <dataValidation type="list" sqref="M973" xr:uid="{16DB9A93-75C7-42AB-B340-3037568A5607}">
       <formula1>=IF(L973&lt;&gt;"",INDIRECT(VLOOKUP(L973,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N973" xr:uid="{913CBDAC-047D-4C32-8F48-4B3B52A609BD}">
+    <dataValidation type="list" sqref="N973" xr:uid="{6C7082F5-36F0-4FDF-9B0B-CE5777C5894F}">
       <formula1>=IF(M973&lt;&gt;"",INDIRECT(VLOOKUP(M973,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M974" xr:uid="{DE998178-6820-493E-ADFD-AB9774FFA161}">
+    <dataValidation type="list" sqref="M974" xr:uid="{DD431329-2214-444C-A9AA-26B265029155}">
       <formula1>=IF(L974&lt;&gt;"",INDIRECT(VLOOKUP(L974,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N974" xr:uid="{6331FA21-5CA8-4A37-AF03-6D22C56FBEF3}">
+    <dataValidation type="list" sqref="N974" xr:uid="{A481EED0-117F-42B9-935A-68008BA850D1}">
       <formula1>=IF(M974&lt;&gt;"",INDIRECT(VLOOKUP(M974,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M975" xr:uid="{7540C2A4-5FBD-4348-BA87-2883EF3F3CC2}">
+    <dataValidation type="list" sqref="M975" xr:uid="{62F63E9F-A9AB-4343-A966-DB80CE263C4D}">
       <formula1>=IF(L975&lt;&gt;"",INDIRECT(VLOOKUP(L975,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N975" xr:uid="{5D561E92-025C-49C6-8E35-FFE48AA08EBF}">
+    <dataValidation type="list" sqref="N975" xr:uid="{03E3509F-3E00-460F-9CEB-C11F841273C6}">
       <formula1>=IF(M975&lt;&gt;"",INDIRECT(VLOOKUP(M975,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M976" xr:uid="{E7985EED-3BBE-421A-8084-6905CB1700C2}">
+    <dataValidation type="list" sqref="M976" xr:uid="{5759B394-05A0-448C-B390-C5CBD41C6FF0}">
       <formula1>=IF(L976&lt;&gt;"",INDIRECT(VLOOKUP(L976,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N976" xr:uid="{A09F1E06-2CB6-4EDE-A7FE-E8B152D97B99}">
+    <dataValidation type="list" sqref="N976" xr:uid="{1072E1AB-F3D3-4F5D-9F6E-6F6CC01F4E72}">
       <formula1>=IF(M976&lt;&gt;"",INDIRECT(VLOOKUP(M976,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M977" xr:uid="{CD20B12D-CD3B-463A-9DD2-9FD028184F99}">
+    <dataValidation type="list" sqref="M977" xr:uid="{442C03AA-F26F-4066-AE21-50088659B2BB}">
       <formula1>=IF(L977&lt;&gt;"",INDIRECT(VLOOKUP(L977,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N977" xr:uid="{C575812E-2CC2-47FE-BC42-FB244591EF07}">
+    <dataValidation type="list" sqref="N977" xr:uid="{87403C29-532E-4638-A97A-4C8921D56819}">
       <formula1>=IF(M977&lt;&gt;"",INDIRECT(VLOOKUP(M977,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M978" xr:uid="{CB3C6296-D6CE-4484-B6B0-D2CFF0BCE814}">
+    <dataValidation type="list" sqref="M978" xr:uid="{F13D52D2-CE63-4C4D-8A82-23EB283951F3}">
       <formula1>=IF(L978&lt;&gt;"",INDIRECT(VLOOKUP(L978,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N978" xr:uid="{A6A542EF-6C74-4856-AD0C-7C6749551EC8}">
+    <dataValidation type="list" sqref="N978" xr:uid="{AEAC7819-1F66-4C0B-98B7-80F748444DD1}">
       <formula1>=IF(M978&lt;&gt;"",INDIRECT(VLOOKUP(M978,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M979" xr:uid="{7BD47619-C25C-4FB7-BAC8-EB2E3389B1D1}">
+    <dataValidation type="list" sqref="M979" xr:uid="{748ED3A5-ABC0-4F76-AAFC-B8CF28E896AD}">
       <formula1>=IF(L979&lt;&gt;"",INDIRECT(VLOOKUP(L979,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N979" xr:uid="{6B3D9EAE-AE5D-483C-BDC7-9EE409E75FD9}">
+    <dataValidation type="list" sqref="N979" xr:uid="{4CD83AB5-1D26-4101-AA24-54FFA9D31630}">
       <formula1>=IF(M979&lt;&gt;"",INDIRECT(VLOOKUP(M979,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M980" xr:uid="{EA0FB225-4ACB-47C2-A04F-66A2382C6600}">
+    <dataValidation type="list" sqref="M980" xr:uid="{B5A2684A-AB03-49A0-8AD9-620DC5B88697}">
       <formula1>=IF(L980&lt;&gt;"",INDIRECT(VLOOKUP(L980,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N980" xr:uid="{9F56CE4E-61E3-4604-80FA-C9CF57D1EB81}">
+    <dataValidation type="list" sqref="N980" xr:uid="{1ED381DB-0B8F-4C7A-8BB3-104213FDEA89}">
       <formula1>=IF(M980&lt;&gt;"",INDIRECT(VLOOKUP(M980,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M981" xr:uid="{4CE06CE7-0838-4ACD-A673-9F692AFD006E}">
+    <dataValidation type="list" sqref="M981" xr:uid="{55E4BA36-D405-4E1E-A6C0-A1A29CFABA22}">
       <formula1>=IF(L981&lt;&gt;"",INDIRECT(VLOOKUP(L981,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N981" xr:uid="{B7FB8997-9575-4B87-84C8-061D95919FCF}">
+    <dataValidation type="list" sqref="N981" xr:uid="{45450DDD-DDBD-40CF-BCAC-1EF1EBE4F83A}">
       <formula1>=IF(M981&lt;&gt;"",INDIRECT(VLOOKUP(M981,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M982" xr:uid="{421B642C-EE4E-42C8-9528-22E5C39CF342}">
+    <dataValidation type="list" sqref="M982" xr:uid="{9A9FA82E-2342-484E-A09D-294611F5C956}">
       <formula1>=IF(L982&lt;&gt;"",INDIRECT(VLOOKUP(L982,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N982" xr:uid="{57F3D00B-1C5B-41D2-8988-EF9333EB585B}">
+    <dataValidation type="list" sqref="N982" xr:uid="{1943CB41-F546-4F08-AB83-AF4F8519D211}">
       <formula1>=IF(M982&lt;&gt;"",INDIRECT(VLOOKUP(M982,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M983" xr:uid="{55F1D8F9-FF6B-4382-9F82-12859EFFA8FD}">
+    <dataValidation type="list" sqref="M983" xr:uid="{E8F7D0B1-14CA-45D4-B90D-ECDC6E231EA7}">
       <formula1>=IF(L983&lt;&gt;"",INDIRECT(VLOOKUP(L983,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N983" xr:uid="{677675E0-BBA6-4C2B-9DBA-7C37559D732E}">
+    <dataValidation type="list" sqref="N983" xr:uid="{3B96E941-8819-4C96-A965-059BC8F97133}">
       <formula1>=IF(M983&lt;&gt;"",INDIRECT(VLOOKUP(M983,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M984" xr:uid="{54A96F9E-2E8E-4D55-AF35-FD5FB0E3372A}">
+    <dataValidation type="list" sqref="M984" xr:uid="{809B6AE4-00E1-41D5-A692-9DCDD0FDDB12}">
       <formula1>=IF(L984&lt;&gt;"",INDIRECT(VLOOKUP(L984,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N984" xr:uid="{C00E06E3-A34D-4F33-B49C-C91142F0AE8B}">
+    <dataValidation type="list" sqref="N984" xr:uid="{E7AE44AE-05AD-42AB-965C-5BF2208F2549}">
       <formula1>=IF(M984&lt;&gt;"",INDIRECT(VLOOKUP(M984,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M985" xr:uid="{1F6E6E21-6BCE-4A59-A29A-65B8A5D53DA6}">
+    <dataValidation type="list" sqref="M985" xr:uid="{F9FE9039-B79D-4C9A-B811-BA0BD2C5AA04}">
       <formula1>=IF(L985&lt;&gt;"",INDIRECT(VLOOKUP(L985,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N985" xr:uid="{08F61D76-AA16-44C9-AB26-4A48C57A68BA}">
+    <dataValidation type="list" sqref="N985" xr:uid="{A966BEDB-D672-480F-9F4E-8D7D71D0C64E}">
       <formula1>=IF(M985&lt;&gt;"",INDIRECT(VLOOKUP(M985,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M986" xr:uid="{EEF14651-8DBA-4127-AB2C-92DF08211BB7}">
+    <dataValidation type="list" sqref="M986" xr:uid="{08D2CA6C-B4DB-44ED-B833-CE1C72796763}">
       <formula1>=IF(L986&lt;&gt;"",INDIRECT(VLOOKUP(L986,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N986" xr:uid="{1B79FBCA-C6FD-47C9-A8C3-CDFA0440A4B6}">
+    <dataValidation type="list" sqref="N986" xr:uid="{FEF9995C-CB41-439A-914A-B5828FF17128}">
       <formula1>=IF(M986&lt;&gt;"",INDIRECT(VLOOKUP(M986,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M987" xr:uid="{485E2FAB-64B1-4964-B5C2-BA1A8816C47D}">
+    <dataValidation type="list" sqref="M987" xr:uid="{19E3D71B-2638-4619-A77C-3B2E8C318F1D}">
       <formula1>=IF(L987&lt;&gt;"",INDIRECT(VLOOKUP(L987,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N987" xr:uid="{4F475865-1F7D-49C0-9FF7-8D523C906D4E}">
+    <dataValidation type="list" sqref="N987" xr:uid="{44DFE283-AE2A-4193-814F-39CEC95770E0}">
       <formula1>=IF(M987&lt;&gt;"",INDIRECT(VLOOKUP(M987,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M988" xr:uid="{C21EBE9E-C67B-4DE8-A063-2E6D82676139}">
+    <dataValidation type="list" sqref="M988" xr:uid="{7A048068-1AB1-4AD1-A9E2-64CB36351D81}">
       <formula1>=IF(L988&lt;&gt;"",INDIRECT(VLOOKUP(L988,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N988" xr:uid="{9088B6D2-3762-407D-BF24-419F7893AD0A}">
+    <dataValidation type="list" sqref="N988" xr:uid="{D94540F8-C72B-4220-A0AB-24E2B7B5F5DC}">
       <formula1>=IF(M988&lt;&gt;"",INDIRECT(VLOOKUP(M988,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M989" xr:uid="{973C0271-220B-4BFB-AB76-CF18FFF0A72F}">
+    <dataValidation type="list" sqref="M989" xr:uid="{2FD1AB8C-B12B-4E13-9BAD-C4AA19E541F4}">
       <formula1>=IF(L989&lt;&gt;"",INDIRECT(VLOOKUP(L989,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N989" xr:uid="{40BAC668-5036-4F69-80E0-DD6F511B72E0}">
+    <dataValidation type="list" sqref="N989" xr:uid="{4F42A4E6-6B4D-4B86-A2D3-7ECC27928B97}">
       <formula1>=IF(M989&lt;&gt;"",INDIRECT(VLOOKUP(M989,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M990" xr:uid="{1DC69DDB-9F62-41F3-AB72-229F9E623BAF}">
+    <dataValidation type="list" sqref="M990" xr:uid="{43D9ADBE-CE49-4C8C-A932-1058819E15E0}">
       <formula1>=IF(L990&lt;&gt;"",INDIRECT(VLOOKUP(L990,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N990" xr:uid="{F3ECBAFA-14C4-401C-A6BD-6340BA171EEB}">
+    <dataValidation type="list" sqref="N990" xr:uid="{85DFC952-537B-4A79-8EEA-CF1554E43B94}">
       <formula1>=IF(M990&lt;&gt;"",INDIRECT(VLOOKUP(M990,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M991" xr:uid="{418CAFE6-08C1-4EB8-92E8-1BED07A1559A}">
+    <dataValidation type="list" sqref="M991" xr:uid="{55F0A20B-FF12-42FA-ABD7-CB3CC7DD0ED8}">
       <formula1>=IF(L991&lt;&gt;"",INDIRECT(VLOOKUP(L991,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N991" xr:uid="{9F5578C1-325C-4FC8-A40A-E658541C661D}">
+    <dataValidation type="list" sqref="N991" xr:uid="{41DF73B7-97FE-445C-9D68-9D970BCC2BDF}">
       <formula1>=IF(M991&lt;&gt;"",INDIRECT(VLOOKUP(M991,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M992" xr:uid="{D7BA43E0-8434-4004-AFE7-ED446DC3D001}">
+    <dataValidation type="list" sqref="M992" xr:uid="{07587D70-6CB5-4F2C-95E4-1680AC79DCC7}">
       <formula1>=IF(L992&lt;&gt;"",INDIRECT(VLOOKUP(L992,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N992" xr:uid="{54098FCC-1BA4-4168-9A30-E29E9647C714}">
+    <dataValidation type="list" sqref="N992" xr:uid="{B15144B1-0652-4C39-A6F8-DAFA942AA056}">
       <formula1>=IF(M992&lt;&gt;"",INDIRECT(VLOOKUP(M992,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M993" xr:uid="{52F75312-E7E2-42BF-946E-4B708A57B26C}">
+    <dataValidation type="list" sqref="M993" xr:uid="{653ACEF3-971C-4015-9FB5-0F501D837CCA}">
       <formula1>=IF(L993&lt;&gt;"",INDIRECT(VLOOKUP(L993,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N993" xr:uid="{A1F33E72-3C10-4999-B03E-AC1C5AFFC6C1}">
+    <dataValidation type="list" sqref="N993" xr:uid="{E9A596A4-A1BB-4E07-9954-513CD5A889C5}">
       <formula1>=IF(M993&lt;&gt;"",INDIRECT(VLOOKUP(M993,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M994" xr:uid="{933E5D32-D253-4433-983C-93FD1246FA90}">
+    <dataValidation type="list" sqref="M994" xr:uid="{D386C266-2117-481D-999C-9D017B917012}">
       <formula1>=IF(L994&lt;&gt;"",INDIRECT(VLOOKUP(L994,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N994" xr:uid="{4BFBF1D6-339F-4490-A358-1DFFA2F786DB}">
+    <dataValidation type="list" sqref="N994" xr:uid="{C435237F-1A7B-447F-971C-7DEAB9A3EE81}">
       <formula1>=IF(M994&lt;&gt;"",INDIRECT(VLOOKUP(M994,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M995" xr:uid="{CF6E1CE0-33D7-471E-8905-FE5AC78C4F1E}">
+    <dataValidation type="list" sqref="M995" xr:uid="{D6BDE7DA-87F9-4FE5-83B0-E77930E68453}">
       <formula1>=IF(L995&lt;&gt;"",INDIRECT(VLOOKUP(L995,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N995" xr:uid="{9382C239-DD08-4D83-9B73-AFCE991A03EA}">
+    <dataValidation type="list" sqref="N995" xr:uid="{9B6194AD-306D-4006-A714-B5AF64060AB7}">
       <formula1>=IF(M995&lt;&gt;"",INDIRECT(VLOOKUP(M995,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M996" xr:uid="{9562ECF9-17B3-4373-87D1-AA42E10592DB}">
+    <dataValidation type="list" sqref="M996" xr:uid="{D4AC9C4A-4A48-47DB-A3AD-71DDAFBD23BC}">
       <formula1>=IF(L996&lt;&gt;"",INDIRECT(VLOOKUP(L996,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N996" xr:uid="{53A8C73C-9AB7-41CC-BEB9-868CE55BAA4C}">
+    <dataValidation type="list" sqref="N996" xr:uid="{3FBBAC19-A6FB-4B2A-A230-8836C75D8B81}">
       <formula1>=IF(M996&lt;&gt;"",INDIRECT(VLOOKUP(M996,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M997" xr:uid="{E97A0267-FAA1-44FF-80D3-5A2BF82E85EC}">
+    <dataValidation type="list" sqref="M997" xr:uid="{D24799BF-2ABF-4EB3-B8F2-42219A1DBBEE}">
       <formula1>=IF(L997&lt;&gt;"",INDIRECT(VLOOKUP(L997,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N997" xr:uid="{91E6D202-0D77-47B3-88B5-01337D5B9724}">
+    <dataValidation type="list" sqref="N997" xr:uid="{D3F1E613-BC51-481F-A04B-DC9048A30ED3}">
       <formula1>=IF(M997&lt;&gt;"",INDIRECT(VLOOKUP(M997,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M998" xr:uid="{4223E667-278B-4BF4-B506-1E7437E4623F}">
+    <dataValidation type="list" sqref="M998" xr:uid="{17BBA373-DF53-464F-B2C4-0BA8FCA30B64}">
       <formula1>=IF(L998&lt;&gt;"",INDIRECT(VLOOKUP(L998,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N998" xr:uid="{78B1D7ED-8876-4B05-AFB7-857F3191DA6A}">
+    <dataValidation type="list" sqref="N998" xr:uid="{8333E206-9890-4AF3-88B5-69B75C5B90AC}">
       <formula1>=IF(M998&lt;&gt;"",INDIRECT(VLOOKUP(M998,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M999" xr:uid="{2383E7E0-7DFA-4C8C-B14F-DE6649F9AC7A}">
+    <dataValidation type="list" sqref="M999" xr:uid="{14EB10CB-C80F-40C0-8C1A-D97AB3020486}">
       <formula1>=IF(L999&lt;&gt;"",INDIRECT(VLOOKUP(L999,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N999" xr:uid="{3FBBAC5D-08C8-4CE8-8B2A-B0142E7826BF}">
+    <dataValidation type="list" sqref="N999" xr:uid="{49F18055-D16B-49DA-B05F-87CF6ED1BBC8}">
       <formula1>=IF(M999&lt;&gt;"",INDIRECT(VLOOKUP(M999,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="M1000" xr:uid="{2C32A15B-29D5-421A-8711-034B31229299}">
+    <dataValidation type="list" sqref="M1000" xr:uid="{836E3147-655E-48C4-96D1-36CE27D3861B}">
       <formula1>=IF(L1000&lt;&gt;"",INDIRECT(VLOOKUP(L1000,ThangLuongData,3,FALSE)),"")</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="N1000" xr:uid="{FC8A59F1-4B9D-4B87-944E-441F57EB36FB}">
+    <dataValidation type="list" sqref="N1000" xr:uid="{77845006-C680-4F48-8F01-5CBA0D748549}">
       <formula1>=IF(M1000&lt;&gt;"",INDIRECT(VLOOKUP(M1000,NgachLuongData,4,FALSE)),"")</formula1>
     </dataValidation>
   </dataValidations>
